--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -1453,20 +1453,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jalen Smith</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.008</v>
+        <v>2.759</v>
       </c>
       <c r="E36" t="n">
-        <v>23.8</v>
+        <v>27.1</v>
       </c>
       <c r="F36" t="n">
         <v>0.3</v>
       </c>
       <c r="G36" t="n">
-        <v>1.144</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="37">
@@ -4440,20 +4440,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2.293</v>
+        <v>2.22</v>
       </c>
       <c r="E139" t="n">
-        <v>24.8</v>
+        <v>28</v>
       </c>
       <c r="F139" t="n">
         <v>0.767</v>
       </c>
       <c r="G139" t="n">
-        <v>1.583</v>
+        <v>1.742</v>
       </c>
     </row>
     <row r="140">
@@ -4469,20 +4469,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1.158</v>
+        <v>2.293</v>
       </c>
       <c r="E140" t="n">
-        <v>31.6</v>
+        <v>24.8</v>
       </c>
       <c r="F140" t="n">
         <v>0.767</v>
       </c>
       <c r="G140" t="n">
-        <v>1.269</v>
+        <v>1.583</v>
       </c>
     </row>
     <row r="141">
@@ -4498,20 +4498,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2.405</v>
+        <v>1.158</v>
       </c>
       <c r="E141" t="n">
-        <v>18</v>
+        <v>31.6</v>
       </c>
       <c r="F141" t="n">
         <v>0.767</v>
       </c>
       <c r="G141" t="n">
-        <v>1.187</v>
+        <v>1.269</v>
       </c>
     </row>
     <row r="142">
@@ -4527,20 +4527,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1.081</v>
+        <v>2.405</v>
       </c>
       <c r="E142" t="n">
-        <v>28.8</v>
+        <v>18</v>
       </c>
       <c r="F142" t="n">
         <v>0.767</v>
       </c>
       <c r="G142" t="n">
-        <v>1.108</v>
+        <v>1.187</v>
       </c>
     </row>
     <row r="143">
@@ -4556,20 +4556,20 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.584</v>
+        <v>1.081</v>
       </c>
       <c r="E143" t="n">
-        <v>17.1</v>
+        <v>28.8</v>
       </c>
       <c r="F143" t="n">
         <v>0.767</v>
       </c>
       <c r="G143" t="n">
-        <v>0.48</v>
+        <v>1.108</v>
       </c>
     </row>
     <row r="144">
@@ -4585,20 +4585,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.015</v>
+        <v>0.584</v>
       </c>
       <c r="E144" t="n">
-        <v>28.9</v>
+        <v>17.1</v>
       </c>
       <c r="F144" t="n">
         <v>0.767</v>
       </c>
       <c r="G144" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="145">
@@ -4614,20 +4614,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mike Conley</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-1.643</v>
+        <v>0.015</v>
       </c>
       <c r="E145" t="n">
-        <v>16.1</v>
+        <v>28.9</v>
       </c>
       <c r="F145" t="n">
         <v>0.767</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.294</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="146">
@@ -6992,20 +6992,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.857</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E227" t="n">
-        <v>24.7</v>
+        <v>27.2</v>
       </c>
       <c r="F227" t="n">
         <v>0.167</v>
       </c>
       <c r="G227" t="n">
-        <v>0.527</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="228">
@@ -7021,20 +7021,20 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-0.552</v>
+        <v>0.857</v>
       </c>
       <c r="E228" t="n">
-        <v>18.6</v>
+        <v>24.7</v>
       </c>
       <c r="F228" t="n">
         <v>0.167</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.15</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="229">
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>9.807</v>
+        <v>9.959</v>
       </c>
       <c r="F12" t="n">
-        <v>1.424</v>
+        <v>1.535</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>8.984</v>
+        <v>9.807</v>
       </c>
       <c r="F13" t="n">
-        <v>0.743</v>
+        <v>1.424</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7819,26 +7819,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>8.756</v>
+        <v>8.984</v>
       </c>
       <c r="F14" t="n">
-        <v>0.999</v>
+        <v>0.743</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7848,26 +7848,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>7.923</v>
+        <v>8.756</v>
       </c>
       <c r="F15" t="n">
-        <v>1.052</v>
+        <v>0.999</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -8063,10 +8063,10 @@
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.47</v>
+        <v>5.051</v>
       </c>
       <c r="F22" t="n">
-        <v>0.514</v>
+        <v>0.608</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.643</v>
+        <v>-2.937</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.948</v>
+        <v>-0.777</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -477,10 +477,10 @@
         <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>4.651</v>
+        <v>4.697</v>
       </c>
     </row>
     <row r="3">
@@ -506,10 +506,10 @@
         <v>23.4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.627</v>
+        <v>2.659</v>
       </c>
     </row>
     <row r="4">
@@ -535,10 +535,10 @@
         <v>32.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.717</v>
+        <v>1.762</v>
       </c>
     </row>
     <row r="5">
@@ -564,10 +564,10 @@
         <v>29.3</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.661</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="6">
@@ -593,10 +593,10 @@
         <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.214</v>
+        <v>1.257</v>
       </c>
     </row>
     <row r="7">
@@ -622,10 +622,10 @@
         <v>28.5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.009</v>
+        <v>1.049</v>
       </c>
     </row>
     <row r="8">
@@ -651,10 +651,10 @@
         <v>20.2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.96</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="9">
@@ -680,10 +680,10 @@
         <v>20.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.391</v>
+        <v>-0.363</v>
       </c>
     </row>
     <row r="10">
@@ -989,20 +989,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tyrese Martin</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.271</v>
+        <v>-1.883</v>
       </c>
       <c r="E20" t="n">
-        <v>15.7</v>
+        <v>20.5</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.393</v>
+        <v>-0.774</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.883</v>
+        <v>-4.023</v>
       </c>
       <c r="E21" t="n">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.774</v>
+        <v>-1.357</v>
       </c>
     </row>
     <row r="22">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-4.023</v>
+        <v>-3.105</v>
       </c>
       <c r="E22" t="n">
-        <v>16.5</v>
+        <v>22.4</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.357</v>
+        <v>-1.421</v>
       </c>
     </row>
     <row r="23">
@@ -1076,20 +1076,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Drake Powell</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-3.105</v>
+        <v>-4.671</v>
       </c>
       <c r="E23" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="F23" t="n">
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.421</v>
+        <v>-2.084</v>
       </c>
     </row>
     <row r="24">
@@ -1105,20 +1105,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Drake Powell</t>
+          <t>Nolan Traore</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-4.671</v>
+        <v>-4.826</v>
       </c>
       <c r="E24" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="F24" t="n">
         <v>0.067</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.084</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="25">
@@ -1405,10 +1405,10 @@
         <v>33.5</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G34" t="n">
-        <v>3.373</v>
+        <v>3.396</v>
       </c>
     </row>
     <row r="35">
@@ -1434,10 +1434,10 @@
         <v>28.9</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G35" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="36">
@@ -1463,10 +1463,10 @@
         <v>27.1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G36" t="n">
-        <v>1.725</v>
+        <v>1.744</v>
       </c>
     </row>
     <row r="37">
@@ -1492,10 +1492,10 @@
         <v>32.9</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G37" t="n">
-        <v>1.107</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="38">
@@ -1521,10 +1521,10 @@
         <v>30.9</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G38" t="n">
-        <v>0.155</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="39">
@@ -1550,10 +1550,10 @@
         <v>25.6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G39" t="n">
-        <v>0.137</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="40">
@@ -1579,10 +1579,10 @@
         <v>32.2</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.783</v>
+        <v>-1.761</v>
       </c>
     </row>
     <row r="41">
@@ -1608,10 +1608,10 @@
         <v>24</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.883</v>
+        <v>-1.867</v>
       </c>
     </row>
     <row r="42">
@@ -1637,10 +1637,10 @@
         <v>32.4</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G42" t="n">
-        <v>5.356</v>
+        <v>5.334</v>
       </c>
     </row>
     <row r="43">
@@ -1666,10 +1666,10 @@
         <v>34.5</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G43" t="n">
-        <v>4.854</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="44">
@@ -1695,10 +1695,10 @@
         <v>31.5</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G44" t="n">
-        <v>3.085</v>
+        <v>3.063</v>
       </c>
     </row>
     <row r="45">
@@ -1724,10 +1724,10 @@
         <v>28.5</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G45" t="n">
-        <v>1.475</v>
+        <v>1.455</v>
       </c>
     </row>
     <row r="46">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Max Strus</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.846</v>
+        <v>1.474</v>
       </c>
       <c r="E46" t="n">
-        <v>31.7</v>
+        <v>27.9</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G46" t="n">
-        <v>1.087</v>
+        <v>1.303</v>
       </c>
     </row>
     <row r="47">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Keon Ellis</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.068</v>
+        <v>0.846</v>
       </c>
       <c r="E47" t="n">
-        <v>27.6</v>
+        <v>31.7</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G47" t="n">
-        <v>0.421</v>
+        <v>1.065</v>
       </c>
     </row>
     <row r="48">
@@ -1801,20 +1801,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nae'Qwan Tomlin</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.413</v>
+        <v>-0.068</v>
       </c>
       <c r="E48" t="n">
-        <v>16.6</v>
+        <v>27.6</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G48" t="n">
-        <v>0.133</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="49">
@@ -1840,10 +1840,10 @@
         <v>22.6</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G49" t="n">
-        <v>0.079</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="50">
@@ -2101,10 +2101,10 @@
         <v>35.9</v>
       </c>
       <c r="F58" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G58" t="n">
-        <v>11.934</v>
+        <v>11.909</v>
       </c>
     </row>
     <row r="59">
@@ -2130,10 +2130,10 @@
         <v>34.4</v>
       </c>
       <c r="F59" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>5.097</v>
+        <v>5.073</v>
       </c>
     </row>
     <row r="60">
@@ -2149,20 +2149,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.577</v>
+        <v>3.542</v>
       </c>
       <c r="E60" t="n">
-        <v>35.7</v>
+        <v>26.8</v>
       </c>
       <c r="F60" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G60" t="n">
-        <v>1.048</v>
+        <v>2.427</v>
       </c>
     </row>
     <row r="61">
@@ -2178,20 +2178,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="E61" t="n">
-        <v>25.6</v>
+        <v>35.7</v>
       </c>
       <c r="F61" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.745</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="62">
@@ -2207,20 +2207,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-0.923</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>29.4</v>
+        <v>25.6</v>
       </c>
       <c r="F62" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.055</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="63">
@@ -2236,20 +2236,20 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-1.3</v>
+        <v>-0.923</v>
       </c>
       <c r="E63" t="n">
-        <v>33.9</v>
+        <v>29.4</v>
       </c>
       <c r="F63" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.33</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="64">
@@ -2265,20 +2265,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-2.368</v>
+        <v>-1.3</v>
       </c>
       <c r="E64" t="n">
-        <v>19.8</v>
+        <v>33.9</v>
       </c>
       <c r="F64" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.634</v>
+        <v>-0.354</v>
       </c>
     </row>
     <row r="65">
@@ -2304,10 +2304,10 @@
         <v>21.7</v>
       </c>
       <c r="F65" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.74</v>
+        <v>-0.755</v>
       </c>
     </row>
     <row r="66">
@@ -2565,10 +2565,10 @@
         <v>20.7</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G74" t="n">
-        <v>2.538</v>
+        <v>2.553</v>
       </c>
     </row>
     <row r="75">
@@ -2594,10 +2594,10 @@
         <v>21.6</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G75" t="n">
-        <v>1.509</v>
+        <v>1.524</v>
       </c>
     </row>
     <row r="76">
@@ -2623,10 +2623,10 @@
         <v>33.2</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G76" t="n">
-        <v>1.03</v>
+        <v>1.053</v>
       </c>
     </row>
     <row r="77">
@@ -2652,10 +2652,10 @@
         <v>33.7</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G77" t="n">
-        <v>0.989</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="78">
@@ -2681,10 +2681,10 @@
         <v>25.4</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G78" t="n">
-        <v>0.293</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="79">
@@ -2710,10 +2710,10 @@
         <v>21.2</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G79" t="n">
-        <v>0.161</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="80">
@@ -2739,10 +2739,10 @@
         <v>25.7</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.127</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="81">
@@ -2768,10 +2768,10 @@
         <v>29.9</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.309</v>
+        <v>-0.288</v>
       </c>
     </row>
     <row r="82">
@@ -3261,10 +3261,10 @@
         <v>30.1</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G98" t="n">
-        <v>6.757</v>
+        <v>6.778</v>
       </c>
     </row>
     <row r="99">
@@ -3290,10 +3290,10 @@
         <v>35.6</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G99" t="n">
-        <v>4.822</v>
+        <v>4.847</v>
       </c>
     </row>
     <row r="100">
@@ -3319,10 +3319,10 @@
         <v>27.4</v>
       </c>
       <c r="F100" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G100" t="n">
-        <v>1.406</v>
+        <v>1.425</v>
       </c>
     </row>
     <row r="101">
@@ -3348,10 +3348,10 @@
         <v>30.5</v>
       </c>
       <c r="F101" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G101" t="n">
-        <v>0.93</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="102">
@@ -3367,20 +3367,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.966</v>
+        <v>1.054</v>
       </c>
       <c r="E102" t="n">
-        <v>26.6</v>
+        <v>26.9</v>
       </c>
       <c r="F102" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G102" t="n">
-        <v>0.848</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="103">
@@ -3396,20 +3396,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-0.604</v>
+        <v>0.966</v>
       </c>
       <c r="E103" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.021</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="104">
@@ -3425,20 +3425,20 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.733</v>
+        <v>-0.604</v>
       </c>
       <c r="E104" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="F104" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.089</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="105">
@@ -3464,10 +3464,10 @@
         <v>29.4</v>
       </c>
       <c r="F105" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.606</v>
+        <v>-0.585</v>
       </c>
     </row>
     <row r="106">
@@ -3628,20 +3628,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jarred Vanderbilt</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-1.372</v>
+        <v>0.549</v>
       </c>
       <c r="E111" t="n">
-        <v>16.4</v>
+        <v>25.6</v>
       </c>
       <c r="F111" t="n">
         <v>0.633</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.252</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="112">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dalton Knecht</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-1.618</v>
+        <v>-1.858</v>
       </c>
       <c r="E112" t="n">
-        <v>16.8</v>
+        <v>25.9</v>
       </c>
       <c r="F112" t="n">
         <v>0.633</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.345</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="113">
@@ -4208,20 +4208,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Bobby Portis</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-0.983</v>
+        <v>1.925</v>
       </c>
       <c r="E131" t="n">
-        <v>25.2</v>
+        <v>24.6</v>
       </c>
       <c r="F131" t="n">
         <v>0.233</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.394</v>
+        <v>1.107</v>
       </c>
     </row>
     <row r="132">
@@ -4237,20 +4237,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cole Anthony</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-2.304</v>
+        <v>0.972</v>
       </c>
       <c r="E132" t="n">
-        <v>15.9</v>
+        <v>22.9</v>
       </c>
       <c r="F132" t="n">
         <v>0.233</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-2.912</v>
+        <v>-0.983</v>
       </c>
       <c r="E133" t="n">
-        <v>15.7</v>
+        <v>25.2</v>
       </c>
       <c r="F133" t="n">
         <v>0.233</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.875</v>
+        <v>-0.394</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Cole Anthony</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.66</v>
+        <v>-2.304</v>
       </c>
       <c r="E134" t="n">
-        <v>19.4</v>
+        <v>15.9</v>
       </c>
       <c r="F134" t="n">
         <v>0.233</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.979</v>
+        <v>-0.6850000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -4324,20 +4324,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-2.39</v>
+        <v>-2.66</v>
       </c>
       <c r="E135" t="n">
-        <v>22</v>
+        <v>19.4</v>
       </c>
       <c r="F135" t="n">
         <v>0.233</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.986</v>
+        <v>-0.979</v>
       </c>
     </row>
     <row r="136">
@@ -4353,20 +4353,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-2.567</v>
+        <v>-2.39</v>
       </c>
       <c r="E136" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
       <c r="F136" t="n">
         <v>0.233</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.995</v>
+        <v>-0.986</v>
       </c>
     </row>
     <row r="137">
@@ -4382,20 +4382,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Gary Trent Jr.</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-3.496</v>
+        <v>-2.567</v>
       </c>
       <c r="E137" t="n">
-        <v>15.5</v>
+        <v>20.5</v>
       </c>
       <c r="F137" t="n">
         <v>0.233</v>
       </c>
       <c r="G137" t="n">
-        <v>-1.056</v>
+        <v>-0.995</v>
       </c>
     </row>
     <row r="138">
@@ -4421,10 +4421,10 @@
         <v>30.9</v>
       </c>
       <c r="F138" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="G138" t="n">
-        <v>2.12</v>
+        <v>2.162</v>
       </c>
     </row>
     <row r="139">
@@ -4450,10 +4450,10 @@
         <v>28</v>
       </c>
       <c r="F139" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="G139" t="n">
-        <v>1.742</v>
+        <v>1.781</v>
       </c>
     </row>
     <row r="140">
@@ -4479,10 +4479,10 @@
         <v>24.8</v>
       </c>
       <c r="F140" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="G140" t="n">
-        <v>1.583</v>
+        <v>1.617</v>
       </c>
     </row>
     <row r="141">
@@ -4508,10 +4508,10 @@
         <v>31.6</v>
       </c>
       <c r="F141" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="G141" t="n">
-        <v>1.269</v>
+        <v>1.313</v>
       </c>
     </row>
     <row r="142">
@@ -4537,10 +4537,10 @@
         <v>18</v>
       </c>
       <c r="F142" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="G142" t="n">
-        <v>1.187</v>
+        <v>1.212</v>
       </c>
     </row>
     <row r="143">
@@ -4566,10 +4566,10 @@
         <v>28.8</v>
       </c>
       <c r="F143" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="G143" t="n">
-        <v>1.108</v>
+        <v>1.148</v>
       </c>
     </row>
     <row r="144">
@@ -4585,20 +4585,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.584</v>
+        <v>0.015</v>
       </c>
       <c r="E144" t="n">
-        <v>17.1</v>
+        <v>28.9</v>
       </c>
       <c r="F144" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="G144" t="n">
-        <v>0.48</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="145">
@@ -4614,20 +4614,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.015</v>
+        <v>0.584</v>
       </c>
       <c r="E145" t="n">
-        <v>28.9</v>
+        <v>17.1</v>
       </c>
       <c r="F145" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="G145" t="n">
-        <v>0.47</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="146">
@@ -4653,10 +4653,10 @@
         <v>34.3</v>
       </c>
       <c r="F146" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G146" t="n">
-        <v>3.114</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="147">
@@ -4682,10 +4682,10 @@
         <v>28.6</v>
       </c>
       <c r="F147" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G147" t="n">
-        <v>2.609</v>
+        <v>2.589</v>
       </c>
     </row>
     <row r="148">
@@ -4711,10 +4711,10 @@
         <v>30.5</v>
       </c>
       <c r="F148" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G148" t="n">
-        <v>2.195</v>
+        <v>2.174</v>
       </c>
     </row>
     <row r="149">
@@ -4740,10 +4740,10 @@
         <v>32.5</v>
       </c>
       <c r="F149" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G149" t="n">
-        <v>1.404</v>
+        <v>1.381</v>
       </c>
     </row>
     <row r="150">
@@ -4769,10 +4769,10 @@
         <v>20.7</v>
       </c>
       <c r="F150" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.184</v>
+        <v>-0.198</v>
       </c>
     </row>
     <row r="151">
@@ -4798,10 +4798,10 @@
         <v>19.8</v>
       </c>
       <c r="F151" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.656</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="152">
@@ -4827,10 +4827,10 @@
         <v>20.8</v>
       </c>
       <c r="F152" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.763</v>
+        <v>-0.778</v>
       </c>
     </row>
     <row r="153">
@@ -4856,10 +4856,10 @@
         <v>28.3</v>
       </c>
       <c r="F153" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.228</v>
+        <v>-1.248</v>
       </c>
     </row>
     <row r="154">
@@ -5581,10 +5581,10 @@
         <v>34.9</v>
       </c>
       <c r="F178" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G178" t="n">
-        <v>4.142</v>
+        <v>4.118</v>
       </c>
     </row>
     <row r="179">
@@ -5610,10 +5610,10 @@
         <v>32.4</v>
       </c>
       <c r="F179" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G179" t="n">
-        <v>1.493</v>
+        <v>1.471</v>
       </c>
     </row>
     <row r="180">
@@ -5639,10 +5639,10 @@
         <v>22.6</v>
       </c>
       <c r="F180" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G180" t="n">
-        <v>0.326</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="181">
@@ -5668,10 +5668,10 @@
         <v>22.6</v>
       </c>
       <c r="F181" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G181" t="n">
-        <v>0.165</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="182">
@@ -5697,10 +5697,10 @@
         <v>32.4</v>
       </c>
       <c r="F182" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.044</v>
+        <v>-0.066</v>
       </c>
     </row>
     <row r="183">
@@ -5726,10 +5726,10 @@
         <v>25.9</v>
       </c>
       <c r="F183" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.194</v>
+        <v>-0.212</v>
       </c>
     </row>
     <row r="184">
@@ -5755,10 +5755,10 @@
         <v>32.9</v>
       </c>
       <c r="F184" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.243</v>
+        <v>-0.265</v>
       </c>
     </row>
     <row r="185">
@@ -5784,10 +5784,10 @@
         <v>21.9</v>
       </c>
       <c r="F185" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.54</v>
+        <v>-0.555</v>
       </c>
     </row>
     <row r="186">
@@ -5813,10 +5813,10 @@
         <v>30.6</v>
       </c>
       <c r="F186" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G186" t="n">
-        <v>2.506</v>
+        <v>2.485</v>
       </c>
     </row>
     <row r="187">
@@ -5842,10 +5842,10 @@
         <v>30</v>
       </c>
       <c r="F187" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G187" t="n">
-        <v>2.158</v>
+        <v>2.138</v>
       </c>
     </row>
     <row r="188">
@@ -5871,10 +5871,10 @@
         <v>34.7</v>
       </c>
       <c r="F188" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G188" t="n">
-        <v>2.055</v>
+        <v>2.031</v>
       </c>
     </row>
     <row r="189">
@@ -5900,10 +5900,10 @@
         <v>23.9</v>
       </c>
       <c r="F189" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G189" t="n">
-        <v>0.865</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="190">
@@ -5929,10 +5929,10 @@
         <v>26.7</v>
       </c>
       <c r="F190" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G190" t="n">
-        <v>0.34</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="191">
@@ -5958,10 +5958,10 @@
         <v>29.3</v>
       </c>
       <c r="F191" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G191" t="n">
-        <v>0.315</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="192">
@@ -5987,10 +5987,10 @@
         <v>18</v>
       </c>
       <c r="F192" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.481</v>
+        <v>-0.494</v>
       </c>
     </row>
     <row r="193">
@@ -6016,10 +6016,10 @@
         <v>32.4</v>
       </c>
       <c r="F193" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G193" t="n">
-        <v>-1.141</v>
+        <v>-1.163</v>
       </c>
     </row>
     <row r="194">
@@ -6528,20 +6528,20 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1.754</v>
+        <v>3.004</v>
       </c>
       <c r="E211" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="F211" t="n">
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>1.738</v>
+        <v>2.525</v>
       </c>
     </row>
     <row r="212">
@@ -6557,20 +6557,20 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.701</v>
+        <v>1.754</v>
       </c>
       <c r="E212" t="n">
-        <v>27.9</v>
+        <v>30.7</v>
       </c>
       <c r="F212" t="n">
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>0.97</v>
+        <v>1.738</v>
       </c>
     </row>
     <row r="213">
@@ -6586,20 +6586,20 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.945</v>
+        <v>0.701</v>
       </c>
       <c r="E213" t="n">
-        <v>22</v>
+        <v>27.9</v>
       </c>
       <c r="F213" t="n">
         <v>0.967</v>
       </c>
       <c r="G213" t="n">
-        <v>0.874</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="214">
@@ -6615,20 +6615,20 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.765</v>
+        <v>0.945</v>
       </c>
       <c r="E214" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
       <c r="F214" t="n">
         <v>0.967</v>
       </c>
       <c r="G214" t="n">
-        <v>0.847</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="215">
@@ -6644,20 +6644,20 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.163</v>
+        <v>0.765</v>
       </c>
       <c r="E215" t="n">
-        <v>31.3</v>
+        <v>23.5</v>
       </c>
       <c r="F215" t="n">
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>0.738</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="216">
@@ -6673,20 +6673,20 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>-0.746</v>
+        <v>0.163</v>
       </c>
       <c r="E216" t="n">
-        <v>20.2</v>
+        <v>31.3</v>
       </c>
       <c r="F216" t="n">
         <v>0.967</v>
       </c>
       <c r="G216" t="n">
-        <v>0.093</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="217">
@@ -6702,20 +6702,20 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Carter Bryant</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>-3.708</v>
+        <v>-0.746</v>
       </c>
       <c r="E217" t="n">
-        <v>16.8</v>
+        <v>20.2</v>
       </c>
       <c r="F217" t="n">
         <v>0.967</v>
       </c>
       <c r="G217" t="n">
-        <v>-0.962</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="218">
@@ -6741,10 +6741,10 @@
         <v>34</v>
       </c>
       <c r="F218" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="G218" t="n">
-        <v>3.15</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="219">
@@ -6770,10 +6770,10 @@
         <v>28.7</v>
       </c>
       <c r="F219" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="G219" t="n">
-        <v>1.659</v>
+        <v>1.619</v>
       </c>
     </row>
     <row r="220">
@@ -6799,10 +6799,10 @@
         <v>19.2</v>
       </c>
       <c r="F220" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="G220" t="n">
-        <v>1.547</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="221">
@@ -6828,10 +6828,10 @@
         <v>32.9</v>
       </c>
       <c r="F221" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="G221" t="n">
-        <v>1.443</v>
+        <v>1.397</v>
       </c>
     </row>
     <row r="222">
@@ -6857,10 +6857,10 @@
         <v>34.7</v>
       </c>
       <c r="F222" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="G222" t="n">
-        <v>1.225</v>
+        <v>1.177</v>
       </c>
     </row>
     <row r="223">
@@ -6886,10 +6886,10 @@
         <v>26</v>
       </c>
       <c r="F223" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="G223" t="n">
-        <v>1.081</v>
+        <v>1.045</v>
       </c>
     </row>
     <row r="224">
@@ -6915,10 +6915,10 @@
         <v>19.8</v>
       </c>
       <c r="F224" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.05</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="225">
@@ -6944,10 +6944,10 @@
         <v>20.5</v>
       </c>
       <c r="F225" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.248</v>
+        <v>-0.277</v>
       </c>
     </row>
     <row r="226">
@@ -7050,20 +7050,20 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Svi Mykhailiuk</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-1.054</v>
+        <v>-0.412</v>
       </c>
       <c r="E229" t="n">
-        <v>18.9</v>
+        <v>24.7</v>
       </c>
       <c r="F229" t="n">
         <v>0.167</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.349</v>
+        <v>-0.126</v>
       </c>
     </row>
     <row r="230">
@@ -7195,20 +7195,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Corey Kispert</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.664</v>
+        <v>3.136</v>
       </c>
       <c r="E234" t="n">
-        <v>21</v>
+        <v>23.2</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>0.305</v>
+        <v>1.532</v>
       </c>
     </row>
     <row r="235">
@@ -7471,26 +7471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>17.839</v>
+        <v>19.977</v>
       </c>
       <c r="F2" t="n">
-        <v>2.125</v>
+        <v>2.676</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
     </row>
@@ -7500,26 +7500,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>17.335</v>
+        <v>18.407</v>
       </c>
       <c r="F3" t="n">
-        <v>2.414</v>
+        <v>2.336</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
     </row>
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>17.065</v>
+        <v>17.515</v>
       </c>
       <c r="F4" t="n">
-        <v>1.938</v>
+        <v>2.538</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7558,26 +7558,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>16.49</v>
+        <v>17.335</v>
       </c>
       <c r="F5" t="n">
-        <v>2.302</v>
+        <v>2.414</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
     </row>
@@ -7628,10 +7628,10 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>14.047</v>
+        <v>15.207</v>
       </c>
       <c r="F7" t="n">
-        <v>2.127</v>
+        <v>2.35</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -7645,26 +7645,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>13.448</v>
+        <v>14.841</v>
       </c>
       <c r="F8" t="n">
-        <v>2.297</v>
+        <v>2.078</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7674,26 +7674,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>12.587</v>
+        <v>13.75</v>
       </c>
       <c r="F9" t="n">
-        <v>1.394</v>
+        <v>2.297</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7703,26 +7703,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>11.354</v>
+        <v>12.587</v>
       </c>
       <c r="F10" t="n">
-        <v>1.24</v>
+        <v>1.394</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>9.959</v>
+        <v>10.248</v>
       </c>
       <c r="F12" t="n">
         <v>1.535</v>
@@ -7802,7 +7802,7 @@
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>9.807</v>
+        <v>9.506</v>
       </c>
       <c r="F13" t="n">
         <v>1.424</v>
@@ -7877,26 +7877,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>6.617</v>
+        <v>6.518</v>
       </c>
       <c r="F16" t="n">
-        <v>0.732</v>
+        <v>1.235</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
     </row>
@@ -7906,26 +7906,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>6.518</v>
+        <v>6.462</v>
       </c>
       <c r="F17" t="n">
-        <v>1.235</v>
+        <v>0.732</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6.491</v>
+        <v>6.34</v>
       </c>
       <c r="F18" t="n">
         <v>0.716</v>
@@ -7976,7 +7976,7 @@
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>6.084</v>
+        <v>6.231</v>
       </c>
       <c r="F19" t="n">
         <v>1.14</v>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>5.105</v>
+        <v>5.214</v>
       </c>
       <c r="F21" t="n">
-        <v>0.439</v>
+        <v>0.608</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
     </row>
@@ -8051,26 +8051,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>5.051</v>
+        <v>4.951</v>
       </c>
       <c r="F22" t="n">
-        <v>0.608</v>
+        <v>0.439</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
     </row>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.707</v>
+        <v>-0.76</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.784</v>
+        <v>-0.73</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
     </row>
@@ -8225,26 +8225,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.937</v>
+        <v>-2.707</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.777</v>
+        <v>-0.784</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
     </row>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.372</v>
+        <v>-2.714</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.893</v>
+        <v>-0.697</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
     </row>
@@ -8295,14 +8295,14 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.989</v>
+        <v>-3.762</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.135</v>
+        <v>-0.826</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corey Kispert</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
     </row>
@@ -8324,10 +8324,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.64</v>
+        <v>-9.387</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.351</v>
+        <v>-2.795</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.275</v>
+        <v>6.046</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>4.697</v>
+        <v>4.958</v>
       </c>
     </row>
     <row r="3">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.878</v>
+        <v>4.869</v>
       </c>
       <c r="E3" t="n">
         <v>23.4</v>
@@ -509,7 +509,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.659</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.057</v>
+        <v>2.216</v>
       </c>
       <c r="E4" t="n">
-        <v>32.2</v>
+        <v>33.1</v>
       </c>
       <c r="F4" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.762</v>
+        <v>1.921</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.223</v>
+        <v>2.26</v>
       </c>
       <c r="E5" t="n">
-        <v>29.3</v>
+        <v>27.9</v>
       </c>
       <c r="F5" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.701</v>
+        <v>1.642</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.381</v>
+        <v>1.679</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>32.6</v>
       </c>
       <c r="F6" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.257</v>
+        <v>1.523</v>
       </c>
     </row>
     <row r="7">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.201</v>
+        <v>1.367</v>
       </c>
       <c r="E7" t="n">
-        <v>28.5</v>
+        <v>28.8</v>
       </c>
       <c r="F7" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.049</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.78</v>
+        <v>1.769</v>
       </c>
       <c r="E8" t="n">
         <v>20.2</v>
@@ -654,7 +654,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.988</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="9">
@@ -670,20 +670,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.421</v>
+        <v>-1.199</v>
       </c>
       <c r="E9" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="F9" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.363</v>
+        <v>-0.273</v>
       </c>
     </row>
     <row r="10">
@@ -699,20 +699,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.032</v>
+        <v>4.104</v>
       </c>
       <c r="E10" t="n">
-        <v>36.1</v>
+        <v>33.9</v>
       </c>
       <c r="F10" t="n">
         <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>3.711</v>
+        <v>3.531</v>
       </c>
     </row>
     <row r="11">
@@ -728,20 +728,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.239</v>
+        <v>3.852</v>
       </c>
       <c r="E11" t="n">
-        <v>34.1</v>
+        <v>35.5</v>
       </c>
       <c r="F11" t="n">
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>3.656</v>
+        <v>3.511</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3.834</v>
+        <v>3.567</v>
       </c>
       <c r="E12" t="n">
-        <v>34.1</v>
+        <v>33.7</v>
       </c>
       <c r="F12" t="n">
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>3.364</v>
+        <v>3.135</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.272</v>
+        <v>2.117</v>
       </c>
       <c r="E13" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="F13" t="n">
         <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>2.132</v>
+        <v>2.021</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.654</v>
+        <v>2.583</v>
       </c>
       <c r="E14" t="n">
-        <v>26.1</v>
+        <v>27.5</v>
       </c>
       <c r="F14" t="n">
         <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.934</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="15">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="E15" t="n">
         <v>20.4</v>
@@ -857,7 +857,7 @@
         <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.587</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.026</v>
+        <v>-0.155</v>
       </c>
       <c r="E16" t="n">
-        <v>25.4</v>
+        <v>24.7</v>
       </c>
       <c r="F16" t="n">
         <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.489</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.761</v>
+        <v>-0.741</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
+        <v>26.2</v>
       </c>
       <c r="F17" t="n">
         <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.078</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.731</v>
+        <v>2.533</v>
       </c>
       <c r="E18" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="F18" t="n">
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>1.381</v>
+        <v>1.262</v>
       </c>
     </row>
     <row r="19">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.859</v>
+        <v>-0.55</v>
       </c>
       <c r="E19" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.385</v>
+        <v>-0.231</v>
       </c>
     </row>
     <row r="20">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.883</v>
+        <v>-1.942</v>
       </c>
       <c r="E20" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.774</v>
+        <v>-0.833</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-4.023</v>
+        <v>-1.805</v>
       </c>
       <c r="E21" t="n">
-        <v>16.5</v>
+        <v>24.3</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.357</v>
+        <v>-0.879</v>
       </c>
     </row>
     <row r="22">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-3.105</v>
+        <v>-3.116</v>
       </c>
       <c r="E22" t="n">
         <v>22.4</v>
@@ -1060,7 +1060,7 @@
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.421</v>
+        <v>-1.426</v>
       </c>
     </row>
     <row r="23">
@@ -1076,20 +1076,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Drake Powell</t>
+          <t>Nolan Traore</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4.671</v>
+        <v>-4.646</v>
       </c>
       <c r="E23" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="F23" t="n">
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.084</v>
+        <v>-2.025</v>
       </c>
     </row>
     <row r="24">
@@ -1105,20 +1105,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nolan Traore</t>
+          <t>Drake Powell</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-4.826</v>
+        <v>-4.719</v>
       </c>
       <c r="E24" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="F24" t="n">
         <v>0.067</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.14</v>
+        <v>-2.179</v>
       </c>
     </row>
     <row r="25">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-5.725</v>
+        <v>-5.577</v>
       </c>
       <c r="E25" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="F25" t="n">
         <v>0.067</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.607</v>
+        <v>-2.591</v>
       </c>
     </row>
     <row r="26">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.151</v>
+        <v>5.577</v>
       </c>
       <c r="E26" t="n">
-        <v>27.7</v>
+        <v>27</v>
       </c>
       <c r="F26" t="n">
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.373</v>
+        <v>3.526</v>
       </c>
     </row>
     <row r="27">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3.583</v>
+        <v>3.509</v>
       </c>
       <c r="E27" t="n">
-        <v>30.5</v>
+        <v>28.6</v>
       </c>
       <c r="F27" t="n">
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>2.722</v>
+        <v>2.511</v>
       </c>
     </row>
     <row r="28">
@@ -1225,16 +1225,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.924</v>
+        <v>1.998</v>
       </c>
       <c r="E28" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F28" t="n">
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1.663</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="29">
@@ -1254,16 +1254,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.513</v>
+        <v>1.789</v>
       </c>
       <c r="E29" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="F29" t="n">
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.311</v>
+        <v>1.481</v>
       </c>
     </row>
     <row r="30">
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.724</v>
+        <v>0.656</v>
       </c>
       <c r="E30" t="n">
-        <v>30.4</v>
+        <v>29.1</v>
       </c>
       <c r="F30" t="n">
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>0.901</v>
+        <v>0.822</v>
       </c>
     </row>
     <row r="31">
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5</v>
+        <v>0.944</v>
       </c>
       <c r="E31" t="n">
-        <v>19.9</v>
+        <v>20.5</v>
       </c>
       <c r="F31" t="n">
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0.498</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="32">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1.465</v>
+        <v>-1.469</v>
       </c>
       <c r="E32" t="n">
         <v>19.2</v>
@@ -1350,7 +1350,7 @@
         <v>0.7</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.305</v>
+        <v>-0.307</v>
       </c>
     </row>
     <row r="33">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-3.935</v>
+        <v>-3.942</v>
       </c>
       <c r="E33" t="n">
         <v>20.9</v>
@@ -1379,7 +1379,7 @@
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.407</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="34">
@@ -1399,16 +1399,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.527</v>
+        <v>4.489</v>
       </c>
       <c r="E34" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="F34" t="n">
         <v>0.333</v>
       </c>
       <c r="G34" t="n">
-        <v>3.396</v>
+        <v>3.588</v>
       </c>
     </row>
     <row r="35">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.393</v>
+        <v>3.404</v>
       </c>
       <c r="E35" t="n">
-        <v>28.9</v>
+        <v>29.4</v>
       </c>
       <c r="F35" t="n">
         <v>0.333</v>
       </c>
       <c r="G35" t="n">
-        <v>2.24</v>
+        <v>2.288</v>
       </c>
     </row>
     <row r="36">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.759</v>
+        <v>2.748</v>
       </c>
       <c r="E36" t="n">
         <v>27.1</v>
@@ -1466,7 +1466,7 @@
         <v>0.333</v>
       </c>
       <c r="G36" t="n">
-        <v>1.744</v>
+        <v>1.738</v>
       </c>
     </row>
     <row r="37">
@@ -1486,16 +1486,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.313</v>
+        <v>1.231</v>
       </c>
       <c r="E37" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="F37" t="n">
         <v>0.333</v>
       </c>
       <c r="G37" t="n">
-        <v>1.13</v>
+        <v>1.069</v>
       </c>
     </row>
     <row r="38">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Leonard Miller</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-0.059</v>
+        <v>0.076</v>
       </c>
       <c r="E38" t="n">
-        <v>30.9</v>
+        <v>24.8</v>
       </c>
       <c r="F38" t="n">
         <v>0.333</v>
       </c>
       <c r="G38" t="n">
-        <v>0.177</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="39">
@@ -1540,20 +1540,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Leonard Miller</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-0.043</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>25.6</v>
+        <v>30.9</v>
       </c>
       <c r="F39" t="n">
         <v>0.333</v>
       </c>
       <c r="G39" t="n">
-        <v>0.155</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="40">
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-2.956</v>
+        <v>-3.017</v>
       </c>
       <c r="E40" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="F40" t="n">
         <v>0.333</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.761</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="41">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-4.068</v>
+        <v>-3.981</v>
       </c>
       <c r="E41" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="F41" t="n">
         <v>0.333</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.867</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="42">
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7.133</v>
+        <v>7.086</v>
       </c>
       <c r="E42" t="n">
-        <v>32.4</v>
+        <v>34.1</v>
       </c>
       <c r="F42" t="n">
         <v>0.767</v>
       </c>
       <c r="G42" t="n">
-        <v>5.334</v>
+        <v>5.576</v>
       </c>
     </row>
     <row r="43">
@@ -1660,16 +1660,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5.96</v>
+        <v>5.944</v>
       </c>
       <c r="E43" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="F43" t="n">
         <v>0.767</v>
       </c>
       <c r="G43" t="n">
-        <v>4.83</v>
+        <v>4.986</v>
       </c>
     </row>
     <row r="44">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.901</v>
+        <v>3.859</v>
       </c>
       <c r="E44" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="F44" t="n">
         <v>0.767</v>
       </c>
       <c r="G44" t="n">
-        <v>3.063</v>
+        <v>3.016</v>
       </c>
     </row>
     <row r="45">
@@ -1714,20 +1714,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.688</v>
+        <v>4.177</v>
       </c>
       <c r="E45" t="n">
-        <v>28.5</v>
+        <v>29.1</v>
       </c>
       <c r="F45" t="n">
         <v>0.767</v>
       </c>
       <c r="G45" t="n">
-        <v>1.455</v>
+        <v>2.993</v>
       </c>
     </row>
     <row r="46">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.474</v>
+        <v>1.804</v>
       </c>
       <c r="E46" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="F46" t="n">
         <v>0.767</v>
       </c>
       <c r="G46" t="n">
-        <v>1.303</v>
+        <v>1.538</v>
       </c>
     </row>
     <row r="47">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Max Strus</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.846</v>
+        <v>1.204</v>
       </c>
       <c r="E47" t="n">
-        <v>31.7</v>
+        <v>27.6</v>
       </c>
       <c r="F47" t="n">
         <v>0.767</v>
       </c>
       <c r="G47" t="n">
-        <v>1.065</v>
+        <v>1.132</v>
       </c>
     </row>
     <row r="48">
@@ -1801,20 +1801,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Keon Ellis</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.068</v>
+        <v>0.836</v>
       </c>
       <c r="E48" t="n">
-        <v>27.6</v>
+        <v>31.7</v>
       </c>
       <c r="F48" t="n">
         <v>0.767</v>
       </c>
       <c r="G48" t="n">
-        <v>0.402</v>
+        <v>1.058</v>
       </c>
     </row>
     <row r="49">
@@ -1830,20 +1830,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.633</v>
+        <v>-0.218</v>
       </c>
       <c r="E49" t="n">
-        <v>22.6</v>
+        <v>26.9</v>
       </c>
       <c r="F49" t="n">
         <v>0.767</v>
       </c>
       <c r="G49" t="n">
-        <v>0.063</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="50">
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.442</v>
+        <v>2.567</v>
       </c>
       <c r="E50" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="F50" t="n">
         <v>0.2</v>
       </c>
       <c r="G50" t="n">
-        <v>1.164</v>
+        <v>1.182</v>
       </c>
     </row>
     <row r="51">
@@ -1892,16 +1892,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.056</v>
+        <v>1.161</v>
       </c>
       <c r="E51" t="n">
-        <v>31.2</v>
+        <v>33.3</v>
       </c>
       <c r="F51" t="n">
         <v>0.2</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.944</v>
       </c>
     </row>
     <row r="52">
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.802</v>
       </c>
       <c r="E52" t="n">
-        <v>23.3</v>
+        <v>21.1</v>
       </c>
       <c r="F52" t="n">
         <v>0.2</v>
       </c>
       <c r="G52" t="n">
-        <v>0.495</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="53">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>26.8</v>
+        <v>29.2</v>
       </c>
       <c r="F53" t="n">
         <v>0.2</v>
       </c>
       <c r="G53" t="n">
-        <v>0.151</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -1979,16 +1979,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1.138</v>
+        <v>-0.916</v>
       </c>
       <c r="E54" t="n">
-        <v>20.3</v>
+        <v>21.6</v>
       </c>
       <c r="F54" t="n">
         <v>0.2</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.397</v>
+        <v>-0.322</v>
       </c>
     </row>
     <row r="55">
@@ -2004,20 +2004,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>Ryan Nembhard</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.302</v>
+        <v>-1.693</v>
       </c>
       <c r="E55" t="n">
-        <v>30.3</v>
+        <v>18.3</v>
       </c>
       <c r="F55" t="n">
         <v>0.2</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.695</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="56">
@@ -2037,16 +2037,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-1.395</v>
+        <v>-1.403</v>
       </c>
       <c r="E56" t="n">
-        <v>28.2</v>
+        <v>27.8</v>
       </c>
       <c r="F56" t="n">
         <v>0.2</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.702</v>
+        <v>-0.696</v>
       </c>
     </row>
     <row r="57">
@@ -2062,20 +2062,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>P.J. Washington</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-2.516</v>
+        <v>-1.273</v>
       </c>
       <c r="E57" t="n">
-        <v>23.2</v>
+        <v>32</v>
       </c>
       <c r="F57" t="n">
         <v>0.2</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.121</v>
+        <v>-0.715</v>
       </c>
     </row>
     <row r="58">
@@ -2095,16 +2095,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.143</v>
+        <v>15.178</v>
       </c>
       <c r="E58" t="n">
-        <v>35.9</v>
+        <v>35.5</v>
       </c>
       <c r="F58" t="n">
         <v>0.8</v>
       </c>
       <c r="G58" t="n">
-        <v>11.909</v>
+        <v>11.815</v>
       </c>
     </row>
     <row r="59">
@@ -2124,16 +2124,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6.276</v>
+        <v>6.153</v>
       </c>
       <c r="E59" t="n">
-        <v>34.4</v>
+        <v>33.7</v>
       </c>
       <c r="F59" t="n">
         <v>0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>5.073</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="60">
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.542</v>
+        <v>3.532</v>
       </c>
       <c r="E60" t="n">
-        <v>26.8</v>
+        <v>26.5</v>
       </c>
       <c r="F60" t="n">
         <v>0.8</v>
       </c>
       <c r="G60" t="n">
-        <v>2.427</v>
+        <v>2.389</v>
       </c>
     </row>
     <row r="61">
@@ -2182,16 +2182,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.577</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>35.7</v>
+        <v>34.1</v>
       </c>
       <c r="F61" t="n">
         <v>0.8</v>
       </c>
       <c r="G61" t="n">
-        <v>1.024</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="62">
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="E62" t="n">
-        <v>25.6</v>
+        <v>24.3</v>
       </c>
       <c r="F62" t="n">
         <v>0.8</v>
       </c>
       <c r="G62" t="n">
-        <v>0.728</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="63">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-0.923</v>
+        <v>-0.543</v>
       </c>
       <c r="E63" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="F63" t="n">
         <v>0.8</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.075</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="64">
@@ -2269,16 +2269,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1.3</v>
+        <v>-1.262</v>
       </c>
       <c r="E64" t="n">
-        <v>33.9</v>
+        <v>32.8</v>
       </c>
       <c r="F64" t="n">
         <v>0.8</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.354</v>
+        <v>-0.316</v>
       </c>
     </row>
     <row r="65">
@@ -2298,16 +2298,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-2.47</v>
+        <v>-2.312</v>
       </c>
       <c r="E65" t="n">
-        <v>21.7</v>
+        <v>20.4</v>
       </c>
       <c r="F65" t="n">
         <v>0.8</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.755</v>
+        <v>-0.642</v>
       </c>
     </row>
     <row r="66">
@@ -2327,16 +2327,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.1</v>
+        <v>4.971</v>
       </c>
       <c r="E66" t="n">
-        <v>25.4</v>
+        <v>28.1</v>
       </c>
       <c r="F66" t="n">
         <v>0.867</v>
       </c>
       <c r="G66" t="n">
-        <v>3.161</v>
+        <v>3.412</v>
       </c>
     </row>
     <row r="67">
@@ -2356,16 +2356,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.728</v>
+        <v>1.649</v>
       </c>
       <c r="E67" t="n">
-        <v>24.4</v>
+        <v>26.3</v>
       </c>
       <c r="F67" t="n">
         <v>0.867</v>
       </c>
       <c r="G67" t="n">
-        <v>1.317</v>
+        <v>1.377</v>
       </c>
     </row>
     <row r="68">
@@ -2385,16 +2385,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.205</v>
+        <v>0.406</v>
       </c>
       <c r="E68" t="n">
-        <v>19.1</v>
+        <v>20.9</v>
       </c>
       <c r="F68" t="n">
         <v>0.867</v>
       </c>
       <c r="G68" t="n">
-        <v>0.426</v>
+        <v>0.553</v>
       </c>
     </row>
     <row r="69">
@@ -2410,20 +2410,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.078</v>
+        <v>-0.096</v>
       </c>
       <c r="E69" t="n">
-        <v>25</v>
+        <v>27.6</v>
       </c>
       <c r="F69" t="n">
         <v>0.867</v>
       </c>
       <c r="G69" t="n">
-        <v>0.41</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="70">
@@ -2439,20 +2439,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.232</v>
+        <v>-0.226</v>
       </c>
       <c r="E70" t="n">
-        <v>27.8</v>
+        <v>29</v>
       </c>
       <c r="F70" t="n">
         <v>0.867</v>
       </c>
       <c r="G70" t="n">
-        <v>0.367</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="71">
@@ -2468,20 +2468,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Colby Jones</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-0.306</v>
+        <v>-0.166</v>
       </c>
       <c r="E71" t="n">
-        <v>28.3</v>
+        <v>24.6</v>
       </c>
       <c r="F71" t="n">
         <v>0.867</v>
       </c>
       <c r="G71" t="n">
-        <v>0.33</v>
+        <v>0.359</v>
       </c>
     </row>
     <row r="72">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Colby Jones</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-0.677</v>
+        <v>-0.306</v>
       </c>
       <c r="E72" t="n">
-        <v>20.5</v>
+        <v>28.3</v>
       </c>
       <c r="F72" t="n">
         <v>0.867</v>
       </c>
       <c r="G72" t="n">
-        <v>0.081</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="73">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ronald Holland II</t>
+          <t>Caris LeVert</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-2.324</v>
+        <v>-1.077</v>
       </c>
       <c r="E73" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="F73" t="n">
         <v>0.867</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.571</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5.485</v>
+        <v>5.089</v>
       </c>
       <c r="E74" t="n">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="F74" t="n">
         <v>0.433</v>
       </c>
       <c r="G74" t="n">
-        <v>2.553</v>
+        <v>2.446</v>
       </c>
     </row>
     <row r="75">
@@ -2588,16 +2588,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2.955</v>
+        <v>3.333</v>
       </c>
       <c r="E75" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="F75" t="n">
         <v>0.433</v>
       </c>
       <c r="G75" t="n">
-        <v>1.524</v>
+        <v>1.744</v>
       </c>
     </row>
     <row r="76">
@@ -2617,16 +2617,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.088</v>
+        <v>0.908</v>
       </c>
       <c r="E76" t="n">
-        <v>33.2</v>
+        <v>31.8</v>
       </c>
       <c r="F76" t="n">
         <v>0.433</v>
       </c>
       <c r="G76" t="n">
-        <v>1.053</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="77">
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.008</v>
+        <v>0.854</v>
       </c>
       <c r="E77" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
       <c r="F77" t="n">
         <v>0.433</v>
       </c>
       <c r="G77" t="n">
-        <v>1.012</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="78">
@@ -2671,20 +2671,20 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Pat Spencer</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.154</v>
+        <v>0.03</v>
       </c>
       <c r="E78" t="n">
-        <v>25.4</v>
+        <v>21.3</v>
       </c>
       <c r="F78" t="n">
         <v>0.433</v>
       </c>
       <c r="G78" t="n">
-        <v>0.311</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="79">
@@ -2700,20 +2700,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pat Spencer</t>
+          <t>Will Richard</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.034</v>
+        <v>-0.547</v>
       </c>
       <c r="E79" t="n">
-        <v>21.2</v>
+        <v>25.3</v>
       </c>
       <c r="F79" t="n">
         <v>0.433</v>
       </c>
       <c r="G79" t="n">
-        <v>0.176</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="80">
@@ -2729,20 +2729,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Will Richard</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-0.638</v>
+        <v>-1.034</v>
       </c>
       <c r="E80" t="n">
-        <v>25.7</v>
+        <v>30.8</v>
       </c>
       <c r="F80" t="n">
         <v>0.433</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.11</v>
+        <v>-0.385</v>
       </c>
     </row>
     <row r="81">
@@ -2758,20 +2758,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-0.896</v>
+        <v>-3.372</v>
       </c>
       <c r="E81" t="n">
-        <v>29.9</v>
+        <v>19.1</v>
       </c>
       <c r="F81" t="n">
         <v>0.433</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.288</v>
+        <v>-1.169</v>
       </c>
     </row>
     <row r="82">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.104</v>
+        <v>4.126</v>
       </c>
       <c r="E82" t="n">
-        <v>35.5</v>
+        <v>35.7</v>
       </c>
       <c r="F82" t="n">
         <v>0.733</v>
       </c>
       <c r="G82" t="n">
-        <v>3.579</v>
+        <v>3.614</v>
       </c>
     </row>
     <row r="83">
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3.475</v>
+        <v>3.741</v>
       </c>
       <c r="E83" t="n">
-        <v>31.7</v>
+        <v>32.6</v>
       </c>
       <c r="F83" t="n">
         <v>0.733</v>
       </c>
       <c r="G83" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="84">
@@ -2849,16 +2849,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.881</v>
+        <v>1.939</v>
       </c>
       <c r="E84" t="n">
-        <v>37.5</v>
+        <v>38.4</v>
       </c>
       <c r="F84" t="n">
         <v>0.733</v>
       </c>
       <c r="G84" t="n">
-        <v>2.044</v>
+        <v>2.137</v>
       </c>
     </row>
     <row r="85">
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2.2</v>
+        <v>2.325</v>
       </c>
       <c r="E85" t="n">
-        <v>31.6</v>
+        <v>30.2</v>
       </c>
       <c r="F85" t="n">
         <v>0.733</v>
       </c>
       <c r="G85" t="n">
-        <v>1.931</v>
+        <v>1.923</v>
       </c>
     </row>
     <row r="86">
@@ -2907,16 +2907,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.877</v>
+        <v>1.79</v>
       </c>
       <c r="E86" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="F86" t="n">
         <v>0.733</v>
       </c>
       <c r="G86" t="n">
-        <v>0.874</v>
+        <v>0.801</v>
       </c>
     </row>
     <row r="87">
@@ -2936,16 +2936,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-0.408</v>
+        <v>-0.781</v>
       </c>
       <c r="E87" t="n">
-        <v>35</v>
+        <v>36.7</v>
       </c>
       <c r="F87" t="n">
         <v>0.733</v>
       </c>
       <c r="G87" t="n">
-        <v>0.237</v>
+        <v>-0.037</v>
       </c>
     </row>
     <row r="88">
@@ -2965,16 +2965,16 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-1.165</v>
+        <v>-1.584</v>
       </c>
       <c r="E88" t="n">
-        <v>26.5</v>
+        <v>23.6</v>
       </c>
       <c r="F88" t="n">
         <v>0.733</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.238</v>
+        <v>-0.418</v>
       </c>
     </row>
     <row r="89">
@@ -2994,16 +2994,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-6.017</v>
+        <v>-6.144</v>
       </c>
       <c r="E89" t="n">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="F89" t="n">
         <v>0.733</v>
       </c>
       <c r="G89" t="n">
-        <v>-2.223</v>
+        <v>-2.161</v>
       </c>
     </row>
     <row r="90">
@@ -3023,16 +3023,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.232</v>
+        <v>2.175</v>
       </c>
       <c r="E90" t="n">
-        <v>31.7</v>
+        <v>30.8</v>
       </c>
       <c r="F90" t="n">
         <v>0.133</v>
       </c>
       <c r="G90" t="n">
-        <v>1.562</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="91">
@@ -3052,16 +3052,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.603</v>
+        <v>2.563</v>
       </c>
       <c r="E91" t="n">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="F91" t="n">
         <v>0.133</v>
       </c>
       <c r="G91" t="n">
-        <v>1.32</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="92">
@@ -3081,16 +3081,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.115</v>
+        <v>1.491</v>
       </c>
       <c r="E92" t="n">
-        <v>27.7</v>
+        <v>28.5</v>
       </c>
       <c r="F92" t="n">
         <v>0.133</v>
       </c>
       <c r="G92" t="n">
-        <v>0.719</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-2.32</v>
+        <v>-1.594</v>
       </c>
       <c r="E93" t="n">
-        <v>22.3</v>
+        <v>32.5</v>
       </c>
       <c r="F93" t="n">
         <v>0.133</v>
       </c>
       <c r="G93" t="n">
-        <v>-1.014</v>
+        <v>-0.988</v>
       </c>
     </row>
     <row r="94">
@@ -3135,20 +3135,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-1.969</v>
+        <v>-2.581</v>
       </c>
       <c r="E94" t="n">
-        <v>31</v>
+        <v>21.4</v>
       </c>
       <c r="F94" t="n">
         <v>0.133</v>
       </c>
       <c r="G94" t="n">
-        <v>-1.185</v>
+        <v>-1.091</v>
       </c>
     </row>
     <row r="95">
@@ -3168,16 +3168,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.268</v>
+        <v>-2.47</v>
       </c>
       <c r="E95" t="n">
-        <v>26.7</v>
+        <v>28.8</v>
       </c>
       <c r="F95" t="n">
         <v>0.133</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.187</v>
+        <v>-1.404</v>
       </c>
     </row>
     <row r="96">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.445</v>
+        <v>-2.455</v>
       </c>
       <c r="E96" t="n">
         <v>30.3</v>
@@ -3206,7 +3206,7 @@
         <v>0.133</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.458</v>
+        <v>-1.465</v>
       </c>
     </row>
     <row r="97">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-3.219</v>
+        <v>-3.23</v>
       </c>
       <c r="E97" t="n">
         <v>22.8</v>
@@ -3235,7 +3235,7 @@
         <v>0.133</v>
       </c>
       <c r="G97" t="n">
-        <v>-1.464</v>
+        <v>-1.469</v>
       </c>
     </row>
     <row r="98">
@@ -3255,16 +3255,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.203</v>
+        <v>10.32</v>
       </c>
       <c r="E98" t="n">
-        <v>30.1</v>
+        <v>31.1</v>
       </c>
       <c r="F98" t="n">
         <v>0.6</v>
       </c>
       <c r="G98" t="n">
-        <v>6.778</v>
+        <v>7.067</v>
       </c>
     </row>
     <row r="99">
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5.944</v>
+        <v>5.933</v>
       </c>
       <c r="E99" t="n">
         <v>35.6</v>
@@ -3293,7 +3293,7 @@
         <v>0.6</v>
       </c>
       <c r="G99" t="n">
-        <v>4.847</v>
+        <v>4.839</v>
       </c>
     </row>
     <row r="100">
@@ -3313,16 +3313,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1.894</v>
+        <v>3.115</v>
       </c>
       <c r="E100" t="n">
-        <v>27.4</v>
+        <v>28.2</v>
       </c>
       <c r="F100" t="n">
         <v>0.6</v>
       </c>
       <c r="G100" t="n">
-        <v>1.425</v>
+        <v>2.183</v>
       </c>
     </row>
     <row r="101">
@@ -3342,16 +3342,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.899</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="F101" t="n">
         <v>0.6</v>
       </c>
       <c r="G101" t="n">
-        <v>0.951</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="102">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1.054</v>
+        <v>0.954</v>
       </c>
       <c r="E102" t="n">
-        <v>26.9</v>
+        <v>26</v>
       </c>
       <c r="F102" t="n">
         <v>0.6</v>
       </c>
       <c r="G102" t="n">
-        <v>0.926</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="103">
@@ -3396,20 +3396,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.966</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E103" t="n">
-        <v>26.6</v>
+        <v>27.2</v>
       </c>
       <c r="F103" t="n">
         <v>0.6</v>
       </c>
       <c r="G103" t="n">
-        <v>0.867</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="104">
@@ -3429,16 +3429,16 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.604</v>
+        <v>-0.485</v>
       </c>
       <c r="E104" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="F104" t="n">
         <v>0.6</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.002</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="105">
@@ -3458,16 +3458,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-1.555</v>
+        <v>-1.36</v>
       </c>
       <c r="E105" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="F105" t="n">
         <v>0.6</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.585</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="106">
@@ -3487,16 +3487,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.259</v>
+        <v>12.048</v>
       </c>
       <c r="E106" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="F106" t="n">
         <v>0.633</v>
       </c>
       <c r="G106" t="n">
-        <v>10.144</v>
+        <v>9.949</v>
       </c>
     </row>
     <row r="107">
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4.767</v>
+        <v>4.656</v>
       </c>
       <c r="E107" t="n">
-        <v>38.3</v>
+        <v>38.8</v>
       </c>
       <c r="F107" t="n">
         <v>0.633</v>
       </c>
       <c r="G107" t="n">
-        <v>4.314</v>
+        <v>4.278</v>
       </c>
     </row>
     <row r="108">
@@ -3545,16 +3545,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4.752</v>
+        <v>4.509</v>
       </c>
       <c r="E108" t="n">
-        <v>33.6</v>
+        <v>34.6</v>
       </c>
       <c r="F108" t="n">
         <v>0.633</v>
       </c>
       <c r="G108" t="n">
-        <v>3.767</v>
+        <v>3.705</v>
       </c>
     </row>
     <row r="109">
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.842</v>
+        <v>2.235</v>
       </c>
       <c r="E109" t="n">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="F109" t="n">
         <v>0.633</v>
       </c>
       <c r="G109" t="n">
-        <v>0.954</v>
+        <v>1.175</v>
       </c>
     </row>
     <row r="110">
@@ -3603,16 +3603,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.386</v>
+        <v>1.322</v>
       </c>
       <c r="E110" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="F110" t="n">
         <v>0.633</v>
       </c>
       <c r="G110" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="111">
@@ -3632,16 +3632,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.549</v>
+        <v>0.491</v>
       </c>
       <c r="E111" t="n">
-        <v>25.6</v>
+        <v>26.7</v>
       </c>
       <c r="F111" t="n">
         <v>0.633</v>
       </c>
       <c r="G111" t="n">
-        <v>0.631</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="112">
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-1.858</v>
+        <v>-1.869</v>
       </c>
       <c r="E112" t="n">
         <v>25.9</v>
@@ -3670,7 +3670,7 @@
         <v>0.633</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.66</v>
+        <v>-0.666</v>
       </c>
     </row>
     <row r="113">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-5.013</v>
+        <v>-5.023</v>
       </c>
       <c r="E113" t="n">
         <v>17.6</v>
@@ -3699,7 +3699,7 @@
         <v>0.633</v>
       </c>
       <c r="G113" t="n">
-        <v>-1.607</v>
+        <v>-1.611</v>
       </c>
     </row>
     <row r="114">
@@ -3715,20 +3715,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3.533</v>
+        <v>4.046</v>
       </c>
       <c r="E114" t="n">
-        <v>24.9</v>
+        <v>23.8</v>
       </c>
       <c r="F114" t="n">
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>1.968</v>
+        <v>2.141</v>
       </c>
     </row>
     <row r="115">
@@ -3744,20 +3744,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jock Landale</t>
+          <t>Javon Small</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.393</v>
+        <v>3.195</v>
       </c>
       <c r="E115" t="n">
-        <v>27.2</v>
+        <v>26.3</v>
       </c>
       <c r="F115" t="n">
         <v>0.267</v>
       </c>
       <c r="G115" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.893</v>
       </c>
     </row>
     <row r="116">
@@ -3773,20 +3773,20 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Jock Landale</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.993</v>
+        <v>1.382</v>
       </c>
       <c r="E116" t="n">
-        <v>25.9</v>
+        <v>27.2</v>
       </c>
       <c r="F116" t="n">
         <v>0.267</v>
       </c>
       <c r="G116" t="n">
-        <v>0.68</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -3802,11 +3802,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.347</v>
+        <v>0.793</v>
       </c>
       <c r="E117" t="n">
         <v>25.7</v>
@@ -3815,7 +3815,7 @@
         <v>0.267</v>
       </c>
       <c r="G117" t="n">
-        <v>0.328</v>
+        <v>0.5679999999999999</v>
       </c>
     </row>
     <row r="118">
@@ -3831,20 +3831,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>GG Jackson</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.378</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E118" t="n">
-        <v>23.3</v>
+        <v>27</v>
       </c>
       <c r="F118" t="n">
         <v>0.267</v>
       </c>
       <c r="G118" t="n">
-        <v>0.313</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="119">
@@ -3864,16 +3864,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-0.543</v>
+        <v>-0.744</v>
       </c>
       <c r="E119" t="n">
-        <v>25</v>
+        <v>25.8</v>
       </c>
       <c r="F119" t="n">
         <v>0.267</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.144</v>
+        <v>-0.257</v>
       </c>
     </row>
     <row r="120">
@@ -3893,16 +3893,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-2.029</v>
+        <v>-1.857</v>
       </c>
       <c r="E120" t="n">
-        <v>25.4</v>
+        <v>24.3</v>
       </c>
       <c r="F120" t="n">
         <v>0.267</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.806</v>
       </c>
     </row>
     <row r="121">
@@ -3922,16 +3922,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-4.561</v>
+        <v>-4.746</v>
       </c>
       <c r="E121" t="n">
-        <v>27.8</v>
+        <v>28.9</v>
       </c>
       <c r="F121" t="n">
         <v>0.267</v>
       </c>
       <c r="G121" t="n">
-        <v>-2.485</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="122">
@@ -3951,16 +3951,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2.78</v>
+        <v>3.081</v>
       </c>
       <c r="E122" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="F122" t="n">
         <v>0.667</v>
       </c>
       <c r="G122" t="n">
-        <v>2.242</v>
+        <v>2.468</v>
       </c>
     </row>
     <row r="123">
@@ -3980,16 +3980,16 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.318</v>
+        <v>2.427</v>
       </c>
       <c r="E123" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="F123" t="n">
         <v>0.667</v>
       </c>
       <c r="G123" t="n">
-        <v>2.22</v>
+        <v>2.304</v>
       </c>
     </row>
     <row r="124">
@@ -4009,16 +4009,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2.816</v>
+        <v>2.846</v>
       </c>
       <c r="E124" t="n">
-        <v>26.2</v>
+        <v>23.9</v>
       </c>
       <c r="F124" t="n">
         <v>0.667</v>
       </c>
       <c r="G124" t="n">
-        <v>1.901</v>
+        <v>1.751</v>
       </c>
     </row>
     <row r="125">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2.27</v>
+        <v>2.131</v>
       </c>
       <c r="E125" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="F125" t="n">
         <v>0.667</v>
       </c>
       <c r="G125" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="126">
@@ -4067,16 +4067,16 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1.538</v>
+        <v>1.581</v>
       </c>
       <c r="E126" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F126" t="n">
         <v>0.667</v>
       </c>
       <c r="G126" t="n">
-        <v>1.379</v>
+        <v>1.312</v>
       </c>
     </row>
     <row r="127">
@@ -4096,16 +4096,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.093</v>
+        <v>0.191</v>
       </c>
       <c r="E127" t="n">
-        <v>28.8</v>
+        <v>26.9</v>
       </c>
       <c r="F127" t="n">
         <v>0.667</v>
       </c>
       <c r="G127" t="n">
-        <v>0.455</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="128">
@@ -4125,16 +4125,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.048</v>
+        <v>-0.007</v>
       </c>
       <c r="E128" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F128" t="n">
         <v>0.667</v>
       </c>
       <c r="G128" t="n">
-        <v>0.387</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="129">
@@ -4154,16 +4154,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.594</v>
+        <v>-0.609</v>
       </c>
       <c r="E129" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="F129" t="n">
         <v>0.667</v>
       </c>
       <c r="G129" t="n">
-        <v>0.046</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="130">
@@ -4183,16 +4183,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2.168</v>
+        <v>2.201</v>
       </c>
       <c r="E130" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="F130" t="n">
         <v>0.233</v>
       </c>
       <c r="G130" t="n">
-        <v>1.598</v>
+        <v>1.627</v>
       </c>
     </row>
     <row r="131">
@@ -4212,16 +4212,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1.925</v>
+        <v>1.85</v>
       </c>
       <c r="E131" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="F131" t="n">
         <v>0.233</v>
       </c>
       <c r="G131" t="n">
-        <v>1.107</v>
+        <v>1.099</v>
       </c>
     </row>
     <row r="132">
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.972</v>
+        <v>0.93</v>
       </c>
       <c r="E132" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="F132" t="n">
         <v>0.233</v>
       </c>
       <c r="G132" t="n">
-        <v>0.574</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-0.983</v>
+        <v>0.425</v>
       </c>
       <c r="E133" t="n">
-        <v>25.2</v>
+        <v>18.2</v>
       </c>
       <c r="F133" t="n">
         <v>0.233</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.394</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cole Anthony</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.304</v>
+        <v>-1.366</v>
       </c>
       <c r="E134" t="n">
-        <v>15.9</v>
+        <v>27.9</v>
       </c>
       <c r="F134" t="n">
         <v>0.233</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.658</v>
       </c>
     </row>
     <row r="135">
@@ -4324,20 +4324,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-2.66</v>
+        <v>-2.4</v>
       </c>
       <c r="E135" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="F135" t="n">
         <v>0.233</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.979</v>
+        <v>-0.907</v>
       </c>
     </row>
     <row r="136">
@@ -4357,16 +4357,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-2.39</v>
+        <v>-2.297</v>
       </c>
       <c r="E136" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="F136" t="n">
         <v>0.233</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.986</v>
+        <v>-0.9340000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -4382,20 +4382,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-2.567</v>
+        <v>-3.594</v>
       </c>
       <c r="E137" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="F137" t="n">
         <v>0.233</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.995</v>
+        <v>-1.378</v>
       </c>
     </row>
     <row r="138">
@@ -4415,16 +4415,16 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2.526</v>
+        <v>2.355</v>
       </c>
       <c r="E138" t="n">
-        <v>30.9</v>
+        <v>30.2</v>
       </c>
       <c r="F138" t="n">
         <v>0.833</v>
       </c>
       <c r="G138" t="n">
-        <v>2.162</v>
+        <v>2.004</v>
       </c>
     </row>
     <row r="139">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2.22</v>
+        <v>2.209</v>
       </c>
       <c r="E139" t="n">
         <v>28</v>
@@ -4453,7 +4453,7 @@
         <v>0.833</v>
       </c>
       <c r="G139" t="n">
-        <v>1.781</v>
+        <v>1.774</v>
       </c>
     </row>
     <row r="140">
@@ -4473,16 +4473,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.293</v>
+        <v>2.104</v>
       </c>
       <c r="E140" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="F140" t="n">
         <v>0.833</v>
       </c>
       <c r="G140" t="n">
-        <v>1.617</v>
+        <v>1.499</v>
       </c>
     </row>
     <row r="141">
@@ -4498,20 +4498,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1.158</v>
+        <v>2.578</v>
       </c>
       <c r="E141" t="n">
-        <v>31.6</v>
+        <v>19.7</v>
       </c>
       <c r="F141" t="n">
         <v>0.833</v>
       </c>
       <c r="G141" t="n">
-        <v>1.313</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="142">
@@ -4527,20 +4527,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2.405</v>
+        <v>1.242</v>
       </c>
       <c r="E142" t="n">
-        <v>18</v>
+        <v>31.6</v>
       </c>
       <c r="F142" t="n">
         <v>0.833</v>
       </c>
       <c r="G142" t="n">
-        <v>1.212</v>
+        <v>1.367</v>
       </c>
     </row>
     <row r="143">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1.081</v>
+        <v>0.951</v>
       </c>
       <c r="E143" t="n">
         <v>28.8</v>
@@ -4569,7 +4569,7 @@
         <v>0.833</v>
       </c>
       <c r="G143" t="n">
-        <v>1.148</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="144">
@@ -4585,20 +4585,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.015</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E144" t="n">
-        <v>28.9</v>
+        <v>16.9</v>
       </c>
       <c r="F144" t="n">
         <v>0.833</v>
       </c>
       <c r="G144" t="n">
-        <v>0.511</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="145">
@@ -4614,20 +4614,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Mike Conley</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.584</v>
+        <v>-1.654</v>
       </c>
       <c r="E145" t="n">
-        <v>17.1</v>
+        <v>16.1</v>
       </c>
       <c r="F145" t="n">
         <v>0.833</v>
       </c>
       <c r="G145" t="n">
-        <v>0.504</v>
+        <v>-0.275</v>
       </c>
     </row>
     <row r="146">
@@ -4647,16 +4647,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4.019</v>
+        <v>3.863</v>
       </c>
       <c r="E146" t="n">
-        <v>34.3</v>
+        <v>35.3</v>
       </c>
       <c r="F146" t="n">
         <v>0.3</v>
       </c>
       <c r="G146" t="n">
-        <v>3.09</v>
+        <v>3.059</v>
       </c>
     </row>
     <row r="147">
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4.051</v>
+        <v>4.16</v>
       </c>
       <c r="E147" t="n">
-        <v>28.6</v>
+        <v>30.7</v>
       </c>
       <c r="F147" t="n">
         <v>0.3</v>
       </c>
       <c r="G147" t="n">
-        <v>2.589</v>
+        <v>2.857</v>
       </c>
     </row>
     <row r="148">
@@ -4705,16 +4705,16 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3.124</v>
+        <v>2.992</v>
       </c>
       <c r="E148" t="n">
-        <v>30.5</v>
+        <v>30.2</v>
       </c>
       <c r="F148" t="n">
         <v>0.3</v>
       </c>
       <c r="G148" t="n">
-        <v>2.174</v>
+        <v>2.074</v>
       </c>
     </row>
     <row r="149">
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1.738</v>
+        <v>1.716</v>
       </c>
       <c r="E149" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="F149" t="n">
         <v>0.3</v>
       </c>
       <c r="G149" t="n">
-        <v>1.381</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="150">
@@ -4759,11 +4759,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jose Alvarado</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-0.761</v>
+        <v>0.464</v>
       </c>
       <c r="E150" t="n">
         <v>20.7</v>
@@ -4772,7 +4772,7 @@
         <v>0.3</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.198</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="151">
@@ -4788,20 +4788,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Jose Alvarado</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-1.926</v>
+        <v>-0.772</v>
       </c>
       <c r="E151" t="n">
-        <v>19.8</v>
+        <v>20.7</v>
       </c>
       <c r="F151" t="n">
         <v>0.3</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.67</v>
+        <v>-0.203</v>
       </c>
     </row>
     <row r="152">
@@ -4821,16 +4821,16 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-2.096</v>
+        <v>-1.923</v>
       </c>
       <c r="E152" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="F152" t="n">
         <v>0.3</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.778</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="153">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-2.419</v>
+        <v>-2.265</v>
       </c>
       <c r="E153" t="n">
-        <v>28.3</v>
+        <v>29.6</v>
       </c>
       <c r="F153" t="n">
         <v>0.3</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.248</v>
+        <v>-1.213</v>
       </c>
     </row>
     <row r="154">
@@ -4879,16 +4879,16 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3.986</v>
+        <v>3.997</v>
       </c>
       <c r="E154" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="F154" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G154" t="n">
-        <v>3.767</v>
+        <v>3.755</v>
       </c>
     </row>
     <row r="155">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3.235</v>
+        <v>3.398</v>
       </c>
       <c r="E155" t="n">
-        <v>30.8</v>
+        <v>30</v>
       </c>
       <c r="F155" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G155" t="n">
-        <v>2.671</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="156">
@@ -4937,16 +4937,16 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2.749</v>
+        <v>2.652</v>
       </c>
       <c r="E156" t="n">
-        <v>27.7</v>
+        <v>29.1</v>
       </c>
       <c r="F156" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>2.123</v>
+        <v>2.174</v>
       </c>
     </row>
     <row r="157">
@@ -4962,20 +4962,20 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2.287</v>
+        <v>3.899</v>
       </c>
       <c r="E157" t="n">
-        <v>29.7</v>
+        <v>20.1</v>
       </c>
       <c r="F157" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G157" t="n">
-        <v>1.993</v>
+        <v>2.027</v>
       </c>
     </row>
     <row r="158">
@@ -4991,20 +4991,20 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1.844</v>
+        <v>2.272</v>
       </c>
       <c r="E158" t="n">
-        <v>33</v>
+        <v>29.2</v>
       </c>
       <c r="F158" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G158" t="n">
-        <v>1.911</v>
+        <v>1.952</v>
       </c>
     </row>
     <row r="159">
@@ -5020,20 +5020,20 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3.555</v>
+        <v>1.745</v>
       </c>
       <c r="E159" t="n">
-        <v>19.5</v>
+        <v>33.5</v>
       </c>
       <c r="F159" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G159" t="n">
-        <v>1.82</v>
+        <v>1.868</v>
       </c>
     </row>
     <row r="160">
@@ -5049,20 +5049,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Mohamed Diawara</t>
+          <t>Jordan Clarkson</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-2.113</v>
+        <v>-2.635</v>
       </c>
       <c r="E160" t="n">
-        <v>16.1</v>
+        <v>17.3</v>
       </c>
       <c r="F160" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.396</v>
+        <v>-0.613</v>
       </c>
     </row>
     <row r="161">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-4.392</v>
+        <v>-4.395</v>
       </c>
       <c r="E161" t="n">
         <v>18.1</v>
@@ -5091,7 +5091,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G161" t="n">
-        <v>-1.302</v>
+        <v>-1.303</v>
       </c>
     </row>
     <row r="162">
@@ -5111,16 +5111,16 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>12.405</v>
+        <v>12.358</v>
       </c>
       <c r="E162" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>9.438000000000001</v>
+        <v>9.385</v>
       </c>
     </row>
     <row r="163">
@@ -5140,16 +5140,16 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>3.993</v>
+        <v>4.181</v>
       </c>
       <c r="E163" t="n">
-        <v>30.4</v>
+        <v>29.6</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>3.16</v>
+        <v>3.193</v>
       </c>
     </row>
     <row r="164">
@@ -5165,20 +5165,20 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1.925</v>
+        <v>4</v>
       </c>
       <c r="E164" t="n">
-        <v>26.9</v>
+        <v>22.6</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>1.64</v>
+        <v>2.355</v>
       </c>
     </row>
     <row r="165">
@@ -5198,16 +5198,16 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.558</v>
+        <v>2.381</v>
       </c>
       <c r="E165" t="n">
-        <v>28.9</v>
+        <v>27.4</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>1.542</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="166">
@@ -5223,20 +5223,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1.976</v>
+        <v>2.057</v>
       </c>
       <c r="E166" t="n">
-        <v>24.3</v>
+        <v>25.4</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1.509</v>
+        <v>1.618</v>
       </c>
     </row>
     <row r="167">
@@ -5252,20 +5252,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Jaylin Williams</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.419</v>
+        <v>1.875</v>
       </c>
       <c r="E167" t="n">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1.213</v>
+        <v>1.489</v>
       </c>
     </row>
     <row r="168">
@@ -5285,16 +5285,16 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.055</v>
+        <v>0.067</v>
       </c>
       <c r="E168" t="n">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.613</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="169">
@@ -5314,16 +5314,16 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-4.016</v>
+        <v>-4.209</v>
       </c>
       <c r="E169" t="n">
-        <v>28.3</v>
+        <v>26.1</v>
       </c>
       <c r="F169" t="n">
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>-1.78</v>
+        <v>-1.745</v>
       </c>
     </row>
     <row r="170">
@@ -5343,16 +5343,16 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3.296</v>
+        <v>3.209</v>
       </c>
       <c r="E170" t="n">
-        <v>29.4</v>
+        <v>30.2</v>
       </c>
       <c r="F170" t="n">
         <v>0.467</v>
       </c>
       <c r="G170" t="n">
-        <v>2.304</v>
+        <v>2.311</v>
       </c>
     </row>
     <row r="171">
@@ -5372,16 +5372,16 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1.834</v>
+        <v>1.987</v>
       </c>
       <c r="E171" t="n">
-        <v>34.6</v>
+        <v>35.6</v>
       </c>
       <c r="F171" t="n">
         <v>0.467</v>
       </c>
       <c r="G171" t="n">
-        <v>1.658</v>
+        <v>1.821</v>
       </c>
     </row>
     <row r="172">
@@ -5401,16 +5401,16 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1.818</v>
+        <v>1.63</v>
       </c>
       <c r="E172" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="F172" t="n">
         <v>0.467</v>
       </c>
       <c r="G172" t="n">
-        <v>1.618</v>
+        <v>1.499</v>
       </c>
     </row>
     <row r="173">
@@ -5426,20 +5426,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-0.059</v>
+        <v>-0.281</v>
       </c>
       <c r="E173" t="n">
-        <v>20.6</v>
+        <v>29.4</v>
       </c>
       <c r="F173" t="n">
         <v>0.467</v>
       </c>
       <c r="G173" t="n">
-        <v>0.175</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="174">
@@ -5455,20 +5455,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-0.403</v>
+        <v>-0.271</v>
       </c>
       <c r="E174" t="n">
-        <v>29.1</v>
+        <v>21</v>
       </c>
       <c r="F174" t="n">
         <v>0.467</v>
       </c>
       <c r="G174" t="n">
-        <v>0.038</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="175">
@@ -5488,16 +5488,16 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-0.796</v>
+        <v>-0.543</v>
       </c>
       <c r="E175" t="n">
-        <v>29.9</v>
+        <v>30.7</v>
       </c>
       <c r="F175" t="n">
         <v>0.467</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.205</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="176">
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-1.537</v>
+        <v>-1.539</v>
       </c>
       <c r="E176" t="n">
         <v>19.5</v>
@@ -5575,16 +5575,16 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5.256</v>
+        <v>5.02</v>
       </c>
       <c r="E178" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="F178" t="n">
         <v>0.4</v>
       </c>
       <c r="G178" t="n">
-        <v>4.118</v>
+        <v>3.921</v>
       </c>
     </row>
     <row r="179">
@@ -5604,16 +5604,16 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1.779</v>
+        <v>1.69</v>
       </c>
       <c r="E179" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="F179" t="n">
         <v>0.4</v>
       </c>
       <c r="G179" t="n">
-        <v>1.471</v>
+        <v>1.414</v>
       </c>
     </row>
     <row r="180">
@@ -5629,11 +5629,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Justin Edwards</t>
+          <t>Eric Gordon</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.259</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="E180" t="n">
         <v>22.6</v>
@@ -5642,7 +5642,7 @@
         <v>0.4</v>
       </c>
       <c r="G180" t="n">
-        <v>0.311</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="181">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Eric Gordon</t>
+          <t>Justin Edwards</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.191</v>
       </c>
       <c r="E181" t="n">
-        <v>22.6</v>
+        <v>24.3</v>
       </c>
       <c r="F181" t="n">
         <v>0.4</v>
       </c>
       <c r="G181" t="n">
-        <v>0.149</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="182">
@@ -5691,16 +5691,16 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-0.498</v>
+        <v>-0.365</v>
       </c>
       <c r="E182" t="n">
-        <v>32.4</v>
+        <v>33.4</v>
       </c>
       <c r="F182" t="n">
         <v>0.4</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.066</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="183">
@@ -5720,16 +5720,16 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-0.792</v>
+        <v>-0.795</v>
       </c>
       <c r="E183" t="n">
-        <v>25.9</v>
+        <v>24.4</v>
       </c>
       <c r="F183" t="n">
         <v>0.4</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.212</v>
+        <v>-0.201</v>
       </c>
     </row>
     <row r="184">
@@ -5749,16 +5749,16 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>-0.787</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="E184" t="n">
-        <v>32.9</v>
+        <v>34.3</v>
       </c>
       <c r="F184" t="n">
         <v>0.4</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.265</v>
+        <v>-0.291</v>
       </c>
     </row>
     <row r="185">
@@ -5778,16 +5778,16 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>-1.618</v>
+        <v>-1.473</v>
       </c>
       <c r="E185" t="n">
-        <v>21.9</v>
+        <v>23.3</v>
       </c>
       <c r="F185" t="n">
         <v>0.4</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.555</v>
+        <v>-0.521</v>
       </c>
     </row>
     <row r="186">
@@ -5807,16 +5807,16 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3.398</v>
+        <v>3.457</v>
       </c>
       <c r="E186" t="n">
-        <v>30.6</v>
+        <v>30.2</v>
       </c>
       <c r="F186" t="n">
         <v>0.5</v>
       </c>
       <c r="G186" t="n">
-        <v>2.485</v>
+        <v>2.492</v>
       </c>
     </row>
     <row r="187">
@@ -5832,20 +5832,20 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2.924</v>
+        <v>2.425</v>
       </c>
       <c r="E187" t="n">
-        <v>30</v>
+        <v>34.6</v>
       </c>
       <c r="F187" t="n">
         <v>0.5</v>
       </c>
       <c r="G187" t="n">
-        <v>2.138</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="188">
@@ -5861,20 +5861,20 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2.311</v>
+        <v>2.92</v>
       </c>
       <c r="E188" t="n">
-        <v>34.7</v>
+        <v>28.5</v>
       </c>
       <c r="F188" t="n">
         <v>0.5</v>
       </c>
       <c r="G188" t="n">
-        <v>2.031</v>
+        <v>2.033</v>
       </c>
     </row>
     <row r="189">
@@ -5894,16 +5894,16 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1.203</v>
+        <v>1.175</v>
       </c>
       <c r="E189" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="F189" t="n">
         <v>0.5</v>
       </c>
       <c r="G189" t="n">
-        <v>0.848</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="190">
@@ -5923,16 +5923,16 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.079</v>
+        <v>0.075</v>
       </c>
       <c r="E190" t="n">
-        <v>26.7</v>
+        <v>27.5</v>
       </c>
       <c r="F190" t="n">
         <v>0.5</v>
       </c>
       <c r="G190" t="n">
-        <v>0.322</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="191">
@@ -5952,16 +5952,16 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>-0.017</v>
+        <v>0.03</v>
       </c>
       <c r="E191" t="n">
-        <v>29.3</v>
+        <v>28.3</v>
       </c>
       <c r="F191" t="n">
         <v>0.5</v>
       </c>
       <c r="G191" t="n">
-        <v>0.295</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="192">
@@ -5981,16 +5981,16 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-1.815</v>
+        <v>-1.408</v>
       </c>
       <c r="E192" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="F192" t="n">
         <v>0.5</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.494</v>
+        <v>-0.374</v>
       </c>
     </row>
     <row r="193">
@@ -6010,16 +6010,16 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>-2.223</v>
+        <v>-1.824</v>
       </c>
       <c r="E193" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="F193" t="n">
         <v>0.5</v>
       </c>
       <c r="G193" t="n">
-        <v>-1.163</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="194">
@@ -6039,16 +6039,16 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>6.716</v>
+        <v>6.815</v>
       </c>
       <c r="E194" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>2.971</v>
+        <v>3.066</v>
       </c>
     </row>
     <row r="195">
@@ -6068,16 +6068,16 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3.722</v>
+        <v>3.738</v>
       </c>
       <c r="E195" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>2.462</v>
+        <v>2.442</v>
       </c>
     </row>
     <row r="196">
@@ -6097,16 +6097,16 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3.644</v>
+        <v>3.538</v>
       </c>
       <c r="E196" t="n">
-        <v>26.1</v>
+        <v>26.8</v>
       </c>
       <c r="F196" t="n">
         <v>0.367</v>
       </c>
       <c r="G196" t="n">
-        <v>2.185</v>
+        <v>2.179</v>
       </c>
     </row>
     <row r="197">
@@ -6126,16 +6126,16 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2.982</v>
+        <v>2.473</v>
       </c>
       <c r="E197" t="n">
-        <v>30.2</v>
+        <v>29.8</v>
       </c>
       <c r="F197" t="n">
         <v>0.367</v>
       </c>
       <c r="G197" t="n">
-        <v>2.105</v>
+        <v>1.763</v>
       </c>
     </row>
     <row r="198">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-0.028</v>
+        <v>0.135</v>
       </c>
       <c r="E198" t="n">
         <v>32</v>
@@ -6164,7 +6164,7 @@
         <v>0.367</v>
       </c>
       <c r="G198" t="n">
-        <v>0.226</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="199">
@@ -6184,16 +6184,16 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-2.279</v>
+        <v>-2.24</v>
       </c>
       <c r="E199" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="F199" t="n">
         <v>0.367</v>
       </c>
       <c r="G199" t="n">
-        <v>-0.996</v>
+        <v>-0.911</v>
       </c>
     </row>
     <row r="200">
@@ -6209,20 +6209,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-2.521</v>
+        <v>-1.896</v>
       </c>
       <c r="E200" t="n">
-        <v>24</v>
+        <v>31.2</v>
       </c>
       <c r="F200" t="n">
         <v>0.367</v>
       </c>
       <c r="G200" t="n">
-        <v>-1.079</v>
+        <v>-0.993</v>
       </c>
     </row>
     <row r="201">
@@ -6238,20 +6238,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-2.354</v>
+        <v>-2.415</v>
       </c>
       <c r="E201" t="n">
-        <v>32.8</v>
+        <v>24.1</v>
       </c>
       <c r="F201" t="n">
         <v>0.367</v>
       </c>
       <c r="G201" t="n">
-        <v>-1.356</v>
+        <v>-1.028</v>
       </c>
     </row>
     <row r="202">
@@ -6271,16 +6271,16 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1.455</v>
+        <v>1.263</v>
       </c>
       <c r="E202" t="n">
-        <v>28.8</v>
+        <v>30.1</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="203">
@@ -6296,20 +6296,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1.047</v>
+        <v>0.604</v>
       </c>
       <c r="E203" t="n">
-        <v>22.9</v>
+        <v>33</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.547</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="204">
@@ -6325,20 +6325,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.695</v>
+        <v>0.71</v>
       </c>
       <c r="E204" t="n">
-        <v>32.8</v>
+        <v>22.2</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.544</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="205">
@@ -6358,16 +6358,16 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.046</v>
+        <v>0.378</v>
       </c>
       <c r="E205" t="n">
-        <v>20.7</v>
+        <v>21.9</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>0.063</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="206">
@@ -6387,7 +6387,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="E206" t="n">
         <v>23.3</v>
@@ -6396,7 +6396,7 @@
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.019</v>
+        <v>-0.025</v>
       </c>
     </row>
     <row r="207">
@@ -6412,20 +6412,20 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-0.835</v>
+        <v>-0.913</v>
       </c>
       <c r="E207" t="n">
-        <v>20.6</v>
+        <v>32.5</v>
       </c>
       <c r="F207" t="n">
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-0.315</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="208">
@@ -6441,20 +6441,20 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Daeqwon Plowden</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>-0.898</v>
+        <v>-2.965</v>
       </c>
       <c r="E208" t="n">
-        <v>32.9</v>
+        <v>29.2</v>
       </c>
       <c r="F208" t="n">
         <v>0.1</v>
       </c>
       <c r="G208" t="n">
-        <v>-0.547</v>
+        <v>-1.743</v>
       </c>
     </row>
     <row r="209">
@@ -6470,20 +6470,20 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Daeqwon Plowden</t>
+          <t>DaQuan Jeffries</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-3.377</v>
+        <v>-3.854</v>
       </c>
       <c r="E209" t="n">
-        <v>27.5</v>
+        <v>25.9</v>
       </c>
       <c r="F209" t="n">
         <v>0.1</v>
       </c>
       <c r="G209" t="n">
-        <v>-1.879</v>
+        <v>-2.029</v>
       </c>
     </row>
     <row r="210">
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>10.042</v>
+        <v>10.127</v>
       </c>
       <c r="E210" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="F210" t="n">
         <v>0.967</v>
       </c>
       <c r="G210" t="n">
-        <v>7.056</v>
+        <v>6.974</v>
       </c>
     </row>
     <row r="211">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3.004</v>
+        <v>2.92</v>
       </c>
       <c r="E211" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="F211" t="n">
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>2.525</v>
+        <v>2.513</v>
       </c>
     </row>
     <row r="212">
@@ -6561,16 +6561,16 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1.754</v>
+        <v>1.904</v>
       </c>
       <c r="E212" t="n">
-        <v>30.7</v>
+        <v>29.5</v>
       </c>
       <c r="F212" t="n">
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>1.738</v>
+        <v>1.766</v>
       </c>
     </row>
     <row r="213">
@@ -6586,20 +6586,20 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.701</v>
+        <v>1.249</v>
       </c>
       <c r="E213" t="n">
-        <v>27.9</v>
+        <v>23.6</v>
       </c>
       <c r="F213" t="n">
         <v>0.967</v>
       </c>
       <c r="G213" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="214">
@@ -6619,16 +6619,16 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.945</v>
+        <v>1.258</v>
       </c>
       <c r="E214" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="F214" t="n">
         <v>0.967</v>
       </c>
       <c r="G214" t="n">
-        <v>0.874</v>
+        <v>1.039</v>
       </c>
     </row>
     <row r="215">
@@ -6644,20 +6644,20 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.765</v>
+        <v>0.493</v>
       </c>
       <c r="E215" t="n">
-        <v>23.5</v>
+        <v>27.6</v>
       </c>
       <c r="F215" t="n">
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>0.847</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="216">
@@ -6677,16 +6677,16 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.163</v>
+        <v>0.032</v>
       </c>
       <c r="E216" t="n">
-        <v>31.3</v>
+        <v>30.4</v>
       </c>
       <c r="F216" t="n">
         <v>0.967</v>
       </c>
       <c r="G216" t="n">
-        <v>0.738</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="217">
@@ -6706,16 +6706,16 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>-0.746</v>
+        <v>-0.579</v>
       </c>
       <c r="E217" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
       <c r="F217" t="n">
         <v>0.967</v>
       </c>
       <c r="G217" t="n">
-        <v>0.093</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="218">
@@ -6735,16 +6735,16 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>3.851</v>
+        <v>4.08</v>
       </c>
       <c r="E218" t="n">
-        <v>34</v>
+        <v>32.8</v>
       </c>
       <c r="F218" t="n">
         <v>0.533</v>
       </c>
       <c r="G218" t="n">
-        <v>3.102</v>
+        <v>3.149</v>
       </c>
     </row>
     <row r="219">
@@ -6760,20 +6760,20 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2.175</v>
+        <v>3.39</v>
       </c>
       <c r="E219" t="n">
-        <v>28.7</v>
+        <v>21</v>
       </c>
       <c r="F219" t="n">
         <v>0.533</v>
       </c>
       <c r="G219" t="n">
-        <v>1.619</v>
+        <v>1.713</v>
       </c>
     </row>
     <row r="220">
@@ -6789,20 +6789,20 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>3.276</v>
+        <v>2.1</v>
       </c>
       <c r="E220" t="n">
-        <v>19.2</v>
+        <v>27.5</v>
       </c>
       <c r="F220" t="n">
         <v>0.533</v>
       </c>
       <c r="G220" t="n">
-        <v>1.52</v>
+        <v>1.511</v>
       </c>
     </row>
     <row r="221">
@@ -6822,16 +6822,16 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.502</v>
+        <v>1.747</v>
       </c>
       <c r="E221" t="n">
-        <v>32.9</v>
+        <v>30.7</v>
       </c>
       <c r="F221" t="n">
         <v>0.533</v>
       </c>
       <c r="G221" t="n">
-        <v>1.397</v>
+        <v>1.461</v>
       </c>
     </row>
     <row r="222">
@@ -6851,16 +6851,16 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1.093</v>
+        <v>0.894</v>
       </c>
       <c r="E222" t="n">
-        <v>34.7</v>
+        <v>34.1</v>
       </c>
       <c r="F222" t="n">
         <v>0.533</v>
       </c>
       <c r="G222" t="n">
-        <v>1.177</v>
+        <v>1.013</v>
       </c>
     </row>
     <row r="223">
@@ -6880,16 +6880,16 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1.399</v>
+        <v>1.447</v>
       </c>
       <c r="E223" t="n">
-        <v>26</v>
+        <v>23.9</v>
       </c>
       <c r="F223" t="n">
         <v>0.533</v>
       </c>
       <c r="G223" t="n">
-        <v>1.045</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="224">
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.72</v>
+        <v>-0.283</v>
       </c>
       <c r="E224" t="n">
-        <v>19.8</v>
+        <v>20.9</v>
       </c>
       <c r="F224" t="n">
         <v>0.533</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.077</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="225">
@@ -6938,16 +6938,16 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-1.181</v>
+        <v>-1.257</v>
       </c>
       <c r="E225" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="F225" t="n">
         <v>0.533</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.277</v>
+        <v>-0.315</v>
       </c>
     </row>
     <row r="226">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1.525</v>
+        <v>1.515</v>
       </c>
       <c r="E226" t="n">
         <v>22.1</v>
@@ -6976,7 +6976,7 @@
         <v>0.167</v>
       </c>
       <c r="G226" t="n">
-        <v>0.777</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="227">
@@ -6992,20 +6992,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.207</v>
       </c>
       <c r="E227" t="n">
-        <v>27.2</v>
+        <v>24</v>
       </c>
       <c r="F227" t="n">
         <v>0.167</v>
       </c>
       <c r="G227" t="n">
-        <v>0.556</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="228">
@@ -7021,20 +7021,20 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.857</v>
+        <v>0.766</v>
       </c>
       <c r="E228" t="n">
-        <v>24.7</v>
+        <v>26.1</v>
       </c>
       <c r="F228" t="n">
         <v>0.167</v>
       </c>
       <c r="G228" t="n">
-        <v>0.527</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="229">
@@ -7054,16 +7054,16 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-0.412</v>
+        <v>-0.342</v>
       </c>
       <c r="E229" t="n">
-        <v>24.7</v>
+        <v>25.9</v>
       </c>
       <c r="F229" t="n">
         <v>0.167</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.126</v>
+        <v>-0.095</v>
       </c>
     </row>
     <row r="230">
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-1.053</v>
+        <v>-1.064</v>
       </c>
       <c r="E230" t="n">
         <v>20.2</v>
@@ -7092,7 +7092,7 @@
         <v>0.167</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.373</v>
+        <v>-0.378</v>
       </c>
     </row>
     <row r="231">
@@ -7108,20 +7108,20 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Elijah Harkless</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-2.234</v>
+        <v>-1.446</v>
       </c>
       <c r="E231" t="n">
-        <v>24.3</v>
+        <v>29.5</v>
       </c>
       <c r="F231" t="n">
         <v>0.167</v>
       </c>
       <c r="G231" t="n">
-        <v>-1.048</v>
+        <v>-0.786</v>
       </c>
     </row>
     <row r="232">
@@ -7137,20 +7137,20 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Elijah Harkless</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>-1.98</v>
+        <v>-1.819</v>
       </c>
       <c r="E232" t="n">
-        <v>28.5</v>
+        <v>26.4</v>
       </c>
       <c r="F232" t="n">
         <v>0.167</v>
       </c>
       <c r="G232" t="n">
-        <v>-1.078</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="233">
@@ -7170,16 +7170,16 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-3.092</v>
+        <v>-3.383</v>
       </c>
       <c r="E233" t="n">
-        <v>32</v>
+        <v>34.4</v>
       </c>
       <c r="F233" t="n">
         <v>0.167</v>
       </c>
       <c r="G233" t="n">
-        <v>-1.949</v>
+        <v>-2.303</v>
       </c>
     </row>
     <row r="234">
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3.136</v>
+        <v>3.126</v>
       </c>
       <c r="E234" t="n">
         <v>23.2</v>
@@ -7208,7 +7208,7 @@
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>1.532</v>
+        <v>1.527</v>
       </c>
     </row>
     <row r="235">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="E235" t="n">
         <v>31.3</v>
@@ -7237,7 +7237,7 @@
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>0.283</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="236">
@@ -7257,16 +7257,16 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.32</v>
+        <v>-0.296</v>
       </c>
       <c r="E236" t="n">
-        <v>29.4</v>
+        <v>30</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.176</v>
+        <v>-0.164</v>
       </c>
     </row>
     <row r="237">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-0.954</v>
+        <v>-1.002</v>
       </c>
       <c r="E237" t="n">
-        <v>21</v>
+        <v>22.7</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.403</v>
+        <v>-0.457</v>
       </c>
     </row>
     <row r="238">
@@ -7311,20 +7311,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-1.352</v>
+        <v>-1.139</v>
       </c>
       <c r="E238" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="F238" t="n">
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-0.628</v>
+        <v>-0.517</v>
       </c>
     </row>
     <row r="239">
@@ -7340,20 +7340,20 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-2.268</v>
+        <v>-2.689</v>
       </c>
       <c r="E239" t="n">
-        <v>24.3</v>
+        <v>22.5</v>
       </c>
       <c r="F239" t="n">
         <v>0.033</v>
       </c>
       <c r="G239" t="n">
-        <v>-1.13</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="240">
@@ -7373,16 +7373,16 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-2.731</v>
+        <v>-2.711</v>
       </c>
       <c r="E240" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="F240" t="n">
         <v>0.033</v>
       </c>
       <c r="G240" t="n">
-        <v>-1.531</v>
+        <v>-1.534</v>
       </c>
     </row>
     <row r="241">
@@ -7402,16 +7402,16 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>-2.52</v>
+        <v>-2.566</v>
       </c>
       <c r="E241" t="n">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="F241" t="n">
         <v>0.033</v>
       </c>
       <c r="G241" t="n">
-        <v>-1.709</v>
+        <v>-1.72</v>
       </c>
     </row>
   </sheetData>
@@ -7471,26 +7471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>19.977</v>
+        <v>20.606</v>
       </c>
       <c r="F2" t="n">
-        <v>2.676</v>
+        <v>3.086</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7500,26 +7500,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>18.407</v>
+        <v>19.947</v>
       </c>
       <c r="F3" t="n">
-        <v>2.336</v>
+        <v>2.736</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
     </row>
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>17.515</v>
+        <v>18.783</v>
       </c>
       <c r="F4" t="n">
-        <v>2.538</v>
+        <v>2.839</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
     </row>
@@ -7558,26 +7558,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>17.335</v>
+        <v>18.318</v>
       </c>
       <c r="F5" t="n">
-        <v>2.414</v>
+        <v>2.296</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
     </row>
@@ -7587,26 +7587,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>15.951</v>
+        <v>15.713</v>
       </c>
       <c r="F6" t="n">
-        <v>2.097</v>
+        <v>2.401</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7616,26 +7616,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>15.207</v>
+        <v>15.246</v>
       </c>
       <c r="F7" t="n">
-        <v>2.35</v>
+        <v>1.975</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
     </row>
@@ -7657,10 +7657,10 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>14.841</v>
+        <v>15.024</v>
       </c>
       <c r="F8" t="n">
-        <v>2.078</v>
+        <v>2.176</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -7686,10 +7686,10 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>13.75</v>
+        <v>14.572</v>
       </c>
       <c r="F9" t="n">
-        <v>2.297</v>
+        <v>2.376</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -7715,10 +7715,10 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>12.587</v>
+        <v>12.57</v>
       </c>
       <c r="F10" t="n">
-        <v>1.394</v>
+        <v>1.367</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>10.292</v>
+        <v>10.334</v>
       </c>
       <c r="F11" t="n">
-        <v>1.409</v>
+        <v>1.455</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>10.248</v>
+        <v>9.628</v>
       </c>
       <c r="F12" t="n">
-        <v>1.535</v>
+        <v>1.515</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>9.506</v>
+        <v>9.375</v>
       </c>
       <c r="F13" t="n">
-        <v>1.424</v>
+        <v>1.309</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7819,26 +7819,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>8.984</v>
+        <v>9.052</v>
       </c>
       <c r="F14" t="n">
-        <v>0.743</v>
+        <v>1.133</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7848,26 +7848,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>8.756</v>
+        <v>8.898999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.999</v>
+        <v>0.677</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7877,26 +7877,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>6.518</v>
+        <v>7.583</v>
       </c>
       <c r="F16" t="n">
-        <v>1.235</v>
+        <v>1.029</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
     </row>
@@ -7906,26 +7906,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>6.462</v>
+        <v>6.853</v>
       </c>
       <c r="F17" t="n">
-        <v>0.732</v>
+        <v>1.268</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
     </row>
@@ -7935,26 +7935,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6.34</v>
+        <v>6.834</v>
       </c>
       <c r="F18" t="n">
-        <v>0.716</v>
+        <v>0.856</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
     </row>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>6.231</v>
+        <v>6.779</v>
       </c>
       <c r="F19" t="n">
-        <v>1.14</v>
+        <v>0.644</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.521</v>
+        <v>5.432</v>
       </c>
       <c r="F20" t="n">
-        <v>0.427</v>
+        <v>0.61</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
     </row>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>5.214</v>
+        <v>4.601</v>
       </c>
       <c r="F21" t="n">
-        <v>0.608</v>
+        <v>0.374</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
     </row>
@@ -8051,26 +8051,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.951</v>
+        <v>4.544</v>
       </c>
       <c r="F22" t="n">
-        <v>0.439</v>
+        <v>0.658</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -8092,10 +8092,10 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>3.883</v>
+        <v>4.078</v>
       </c>
       <c r="F23" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -8121,14 +8121,14 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.667</v>
+        <v>2.241</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.061</v>
+        <v>0.329</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
     </row>
@@ -8150,10 +8150,10 @@
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.288</v>
+        <v>0.335</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.245</v>
+        <v>-0.105</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -8167,26 +8167,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.673</v>
+        <v>-0.349</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.251</v>
+        <v>-0.531</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
     </row>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.76</v>
+        <v>-2.415</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.73</v>
+        <v>-0.616</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
     </row>
@@ -8225,26 +8225,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.707</v>
+        <v>-2.506</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.784</v>
+        <v>-0.571</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
     </row>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.714</v>
+        <v>-2.721</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.697</v>
+        <v>-0.763</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
     </row>
@@ -8295,10 +8295,10 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.762</v>
+        <v>-3.832</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.826</v>
+        <v>-0.861</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -8324,10 +8324,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-9.387</v>
+        <v>-8.901999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.795</v>
+        <v>-2.478</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.199</v>
+        <v>-1.198</v>
       </c>
       <c r="E9" t="n">
         <v>20.7</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.117</v>
+        <v>2.118</v>
       </c>
       <c r="E13" t="n">
         <v>32.1</v>
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.533</v>
+        <v>2.453</v>
       </c>
       <c r="E18" t="n">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="F18" t="n">
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>1.262</v>
+        <v>1.185</v>
       </c>
     </row>
     <row r="19">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.55</v>
+        <v>-0.297</v>
       </c>
       <c r="E19" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.231</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="20">
@@ -989,20 +989,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.942</v>
+        <v>-1.874</v>
       </c>
       <c r="E20" t="n">
-        <v>21.3</v>
+        <v>22.1</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.833</v>
+        <v>-0.831</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.805</v>
+        <v>-2.023</v>
       </c>
       <c r="E21" t="n">
-        <v>24.3</v>
+        <v>21.7</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.879</v>
+        <v>-0.886</v>
       </c>
     </row>
     <row r="22">
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4.646</v>
+        <v>-4.861</v>
       </c>
       <c r="E23" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="F23" t="n">
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.025</v>
+        <v>-2.057</v>
       </c>
     </row>
     <row r="24">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-4.719</v>
+        <v>-4.685</v>
       </c>
       <c r="E24" t="n">
-        <v>22.5</v>
+        <v>24.5</v>
       </c>
       <c r="F24" t="n">
         <v>0.067</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.179</v>
+        <v>-2.358</v>
       </c>
     </row>
     <row r="25">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-5.577</v>
+        <v>-5.215</v>
       </c>
       <c r="E25" t="n">
-        <v>22.6</v>
+        <v>24.2</v>
       </c>
       <c r="F25" t="n">
         <v>0.067</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.591</v>
+        <v>-2.594</v>
       </c>
     </row>
     <row r="26">
@@ -1399,16 +1399,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.489</v>
+        <v>4.66</v>
       </c>
       <c r="E34" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="F34" t="n">
         <v>0.333</v>
       </c>
       <c r="G34" t="n">
-        <v>3.588</v>
+        <v>3.722</v>
       </c>
     </row>
     <row r="35">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.404</v>
+        <v>3.354</v>
       </c>
       <c r="E35" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="F35" t="n">
         <v>0.333</v>
       </c>
       <c r="G35" t="n">
-        <v>2.288</v>
+        <v>2.267</v>
       </c>
     </row>
     <row r="36">
@@ -1453,20 +1453,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.748</v>
+        <v>1.92</v>
       </c>
       <c r="E36" t="n">
-        <v>27.1</v>
+        <v>24.8</v>
       </c>
       <c r="F36" t="n">
         <v>0.333</v>
       </c>
       <c r="G36" t="n">
-        <v>1.738</v>
+        <v>1.164</v>
       </c>
     </row>
     <row r="37">
@@ -1486,16 +1486,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.231</v>
+        <v>1.174</v>
       </c>
       <c r="E37" t="n">
-        <v>32.8</v>
+        <v>32.6</v>
       </c>
       <c r="F37" t="n">
         <v>0.333</v>
       </c>
       <c r="G37" t="n">
-        <v>1.069</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="38">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.076</v>
+        <v>0.018</v>
       </c>
       <c r="E38" t="n">
         <v>24.8</v>
@@ -1524,7 +1524,7 @@
         <v>0.333</v>
       </c>
       <c r="G38" t="n">
-        <v>0.211</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="39">
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-3.017</v>
+        <v>-2.926</v>
       </c>
       <c r="E40" t="n">
-        <v>32</v>
+        <v>30.7</v>
       </c>
       <c r="F40" t="n">
         <v>0.333</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.79</v>
+        <v>-1.658</v>
       </c>
     </row>
     <row r="41">
@@ -1859,20 +1859,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Marvin Bagley III</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.567</v>
+        <v>1.351</v>
       </c>
       <c r="E50" t="n">
-        <v>20.5</v>
+        <v>33.9</v>
       </c>
       <c r="F50" t="n">
         <v>0.2</v>
       </c>
       <c r="G50" t="n">
-        <v>1.182</v>
+        <v>1.094</v>
       </c>
     </row>
     <row r="51">
@@ -1888,20 +1888,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Marvin Bagley III</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.161</v>
+        <v>2.441</v>
       </c>
       <c r="E51" t="n">
-        <v>33.3</v>
+        <v>19.4</v>
       </c>
       <c r="F51" t="n">
         <v>0.2</v>
       </c>
       <c r="G51" t="n">
-        <v>0.944</v>
+        <v>1.066</v>
       </c>
     </row>
     <row r="52">
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.802</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>21.1</v>
+        <v>20.4</v>
       </c>
       <c r="F52" t="n">
         <v>0.2</v>
       </c>
       <c r="G52" t="n">
-        <v>0.441</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="53">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.113</v>
       </c>
       <c r="E53" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="F53" t="n">
         <v>0.2</v>
       </c>
       <c r="G53" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="54">
@@ -1979,16 +1979,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-0.916</v>
+        <v>-0.893</v>
       </c>
       <c r="E54" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="F54" t="n">
         <v>0.2</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.322</v>
+        <v>-0.305</v>
       </c>
     </row>
     <row r="55">
@@ -2004,20 +2004,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ryan Nembhard</t>
+          <t>P.J. Washington</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.693</v>
+        <v>-1.229</v>
       </c>
       <c r="E55" t="n">
-        <v>18.3</v>
+        <v>31.8</v>
       </c>
       <c r="F55" t="n">
         <v>0.2</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.57</v>
+        <v>-0.681</v>
       </c>
     </row>
     <row r="56">
@@ -2040,13 +2040,13 @@
         <v>-1.403</v>
       </c>
       <c r="E56" t="n">
-        <v>27.8</v>
+        <v>28.1</v>
       </c>
       <c r="F56" t="n">
         <v>0.2</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.696</v>
+        <v>-0.704</v>
       </c>
     </row>
     <row r="57">
@@ -2062,20 +2062,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1.273</v>
+        <v>-2.586</v>
       </c>
       <c r="E57" t="n">
-        <v>32</v>
+        <v>19.7</v>
       </c>
       <c r="F57" t="n">
         <v>0.2</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.715</v>
+        <v>-0.981</v>
       </c>
     </row>
     <row r="58">
@@ -2095,16 +2095,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.178</v>
+        <v>15.212</v>
       </c>
       <c r="E58" t="n">
-        <v>35.5</v>
+        <v>36.2</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>11.815</v>
+        <v>12.098</v>
       </c>
     </row>
     <row r="59">
@@ -2124,16 +2124,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6.153</v>
+        <v>6.401</v>
       </c>
       <c r="E59" t="n">
-        <v>33.7</v>
+        <v>36.1</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>4.88</v>
+        <v>5.435</v>
       </c>
     </row>
     <row r="60">
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.532</v>
+        <v>3.439</v>
       </c>
       <c r="E60" t="n">
-        <v>26.5</v>
+        <v>25.9</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>2.389</v>
+        <v>2.306</v>
       </c>
     </row>
     <row r="61">
@@ -2182,16 +2182,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="E61" t="n">
-        <v>34.1</v>
+        <v>33.6</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>0.966</v>
+        <v>1.108</v>
       </c>
     </row>
     <row r="62">
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.58</v>
+        <v>0.464</v>
       </c>
       <c r="E62" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>0.699</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="63">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-0.543</v>
+        <v>-0.52</v>
       </c>
       <c r="E63" t="n">
-        <v>29.1</v>
+        <v>29.9</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G63" t="n">
-        <v>0.156</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="64">
@@ -2269,16 +2269,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1.262</v>
+        <v>-1.346</v>
       </c>
       <c r="E64" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.316</v>
+        <v>-0.345</v>
       </c>
     </row>
     <row r="65">
@@ -2294,20 +2294,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-2.312</v>
+        <v>-2.517</v>
       </c>
       <c r="E65" t="n">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.642</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="66">
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5.089</v>
+        <v>4.433</v>
       </c>
       <c r="E74" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="F74" t="n">
         <v>0.433</v>
       </c>
       <c r="G74" t="n">
-        <v>2.446</v>
+        <v>2.227</v>
       </c>
     </row>
     <row r="75">
@@ -2588,16 +2588,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3.333</v>
+        <v>3.412</v>
       </c>
       <c r="E75" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="F75" t="n">
         <v>0.433</v>
       </c>
       <c r="G75" t="n">
-        <v>1.744</v>
+        <v>1.849</v>
       </c>
     </row>
     <row r="76">
@@ -2617,16 +2617,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.908</v>
+        <v>1.106</v>
       </c>
       <c r="E76" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="F76" t="n">
         <v>0.433</v>
       </c>
       <c r="G76" t="n">
-        <v>0.889</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="77">
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.854</v>
+        <v>0.884</v>
       </c>
       <c r="E77" t="n">
-        <v>32.5</v>
+        <v>32.2</v>
       </c>
       <c r="F77" t="n">
         <v>0.433</v>
       </c>
       <c r="G77" t="n">
-        <v>0.873</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="78">
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="E78" t="n">
-        <v>21.3</v>
+        <v>20.3</v>
       </c>
       <c r="F78" t="n">
         <v>0.433</v>
       </c>
       <c r="G78" t="n">
-        <v>0.206</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="79">
@@ -2700,20 +2700,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Will Richard</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.547</v>
+        <v>-0.103</v>
       </c>
       <c r="E79" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="F79" t="n">
         <v>0.433</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.06</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="80">
@@ -2729,20 +2729,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Will Richard</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-1.034</v>
+        <v>-0.575</v>
       </c>
       <c r="E80" t="n">
-        <v>30.8</v>
+        <v>24.3</v>
       </c>
       <c r="F80" t="n">
         <v>0.433</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.385</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -2758,20 +2758,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-3.372</v>
+        <v>-1.088</v>
       </c>
       <c r="E81" t="n">
-        <v>19.1</v>
+        <v>31</v>
       </c>
       <c r="F81" t="n">
         <v>0.433</v>
       </c>
       <c r="G81" t="n">
-        <v>-1.169</v>
+        <v>-0.423</v>
       </c>
     </row>
     <row r="82">
@@ -3261,10 +3261,10 @@
         <v>31.1</v>
       </c>
       <c r="F98" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="G98" t="n">
-        <v>7.067</v>
+        <v>7.088</v>
       </c>
     </row>
     <row r="99">
@@ -3290,10 +3290,10 @@
         <v>35.6</v>
       </c>
       <c r="F99" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="G99" t="n">
-        <v>4.839</v>
+        <v>4.864</v>
       </c>
     </row>
     <row r="100">
@@ -3319,10 +3319,10 @@
         <v>28.2</v>
       </c>
       <c r="F100" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="G100" t="n">
-        <v>2.183</v>
+        <v>2.203</v>
       </c>
     </row>
     <row r="101">
@@ -3348,10 +3348,10 @@
         <v>30.4</v>
       </c>
       <c r="F101" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="G101" t="n">
-        <v>0.896</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="102">
@@ -3377,10 +3377,10 @@
         <v>26</v>
       </c>
       <c r="F102" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="G102" t="n">
-        <v>0.84</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="103">
@@ -3406,10 +3406,10 @@
         <v>27.2</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="G103" t="n">
-        <v>0.293</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="104">
@@ -3435,10 +3435,10 @@
         <v>27</v>
       </c>
       <c r="F104" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>0.065</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -3464,10 +3464,10 @@
         <v>29.7</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.47</v>
+        <v>-0.449</v>
       </c>
     </row>
     <row r="106">
@@ -3487,16 +3487,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.048</v>
+        <v>11.984</v>
       </c>
       <c r="E106" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="F106" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G106" t="n">
-        <v>9.949</v>
+        <v>10.026</v>
       </c>
     </row>
     <row r="107">
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4.656</v>
+        <v>4.638</v>
       </c>
       <c r="E107" t="n">
-        <v>38.8</v>
+        <v>39.8</v>
       </c>
       <c r="F107" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G107" t="n">
-        <v>4.278</v>
+        <v>4.339</v>
       </c>
     </row>
     <row r="108">
@@ -3545,16 +3545,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4.509</v>
+        <v>4.575</v>
       </c>
       <c r="E108" t="n">
-        <v>34.6</v>
+        <v>35.4</v>
       </c>
       <c r="F108" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G108" t="n">
-        <v>3.705</v>
+        <v>3.811</v>
       </c>
     </row>
     <row r="109">
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.235</v>
+        <v>2.454</v>
       </c>
       <c r="E109" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="F109" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G109" t="n">
-        <v>1.175</v>
+        <v>1.336</v>
       </c>
     </row>
     <row r="110">
@@ -3603,16 +3603,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.322</v>
+        <v>1.233</v>
       </c>
       <c r="E110" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F110" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G110" t="n">
-        <v>0.863</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -3632,16 +3632,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.491</v>
+        <v>0.548</v>
       </c>
       <c r="E111" t="n">
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="F111" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G111" t="n">
-        <v>0.625</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="112">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-1.869</v>
+        <v>-0.66</v>
       </c>
       <c r="E112" t="n">
-        <v>25.9</v>
+        <v>18.2</v>
       </c>
       <c r="F112" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.666</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="113">
@@ -3686,20 +3686,20 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gabe Vincent</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-5.023</v>
+        <v>-1.908</v>
       </c>
       <c r="E113" t="n">
-        <v>17.6</v>
+        <v>25.5</v>
       </c>
       <c r="F113" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G113" t="n">
-        <v>-1.611</v>
+        <v>-0.696</v>
       </c>
     </row>
     <row r="114">
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1.382</v>
+        <v>1.383</v>
       </c>
       <c r="E116" t="n">
         <v>27.2</v>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2.131</v>
+        <v>2.132</v>
       </c>
       <c r="E125" t="n">
         <v>27.4</v>
@@ -4421,10 +4421,10 @@
         <v>30.2</v>
       </c>
       <c r="F138" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G138" t="n">
-        <v>2.004</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="139">
@@ -4440,20 +4440,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2.209</v>
+        <v>2.104</v>
       </c>
       <c r="E139" t="n">
-        <v>28</v>
+        <v>24.5</v>
       </c>
       <c r="F139" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G139" t="n">
-        <v>1.774</v>
+        <v>1.482</v>
       </c>
     </row>
     <row r="140">
@@ -4469,20 +4469,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.104</v>
+        <v>2.578</v>
       </c>
       <c r="E140" t="n">
-        <v>24.5</v>
+        <v>19.7</v>
       </c>
       <c r="F140" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G140" t="n">
-        <v>1.499</v>
+        <v>1.386</v>
       </c>
     </row>
     <row r="141">
@@ -4498,20 +4498,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2.578</v>
+        <v>1.242</v>
       </c>
       <c r="E141" t="n">
-        <v>19.7</v>
+        <v>31.6</v>
       </c>
       <c r="F141" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G141" t="n">
-        <v>1.4</v>
+        <v>1.345</v>
       </c>
     </row>
     <row r="142">
@@ -4527,20 +4527,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1.242</v>
+        <v>0.951</v>
       </c>
       <c r="E142" t="n">
-        <v>31.6</v>
+        <v>28.8</v>
       </c>
       <c r="F142" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G142" t="n">
-        <v>1.367</v>
+        <v>1.051</v>
       </c>
     </row>
     <row r="143">
@@ -4556,20 +4556,20 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.951</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E143" t="n">
-        <v>28.8</v>
+        <v>16.9</v>
       </c>
       <c r="F143" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G143" t="n">
-        <v>1.071</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="144">
@@ -4585,20 +4585,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Mike Conley</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.6889999999999999</v>
+        <v>-1.654</v>
       </c>
       <c r="E144" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="F144" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G144" t="n">
-        <v>0.535</v>
+        <v>-0.286</v>
       </c>
     </row>
     <row r="145">
@@ -4614,20 +4614,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mike Conley</t>
+          <t>Johnny Juzang</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-1.654</v>
+        <v>-4.685</v>
       </c>
       <c r="E145" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="F145" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.275</v>
+        <v>-1.233</v>
       </c>
     </row>
     <row r="146">
@@ -4656,7 +4656,7 @@
         <v>0.3</v>
       </c>
       <c r="G146" t="n">
-        <v>3.059</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="147">
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4.16</v>
+        <v>4.183</v>
       </c>
       <c r="E147" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="F147" t="n">
         <v>0.3</v>
       </c>
       <c r="G147" t="n">
-        <v>2.857</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="148">
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1.716</v>
+        <v>1.704</v>
       </c>
       <c r="E149" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="F149" t="n">
         <v>0.3</v>
       </c>
       <c r="G149" t="n">
-        <v>1.36</v>
+        <v>1.343</v>
       </c>
     </row>
     <row r="150">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.464</v>
+        <v>0.414</v>
       </c>
       <c r="E150" t="n">
         <v>20.7</v>
@@ -4772,7 +4772,7 @@
         <v>0.3</v>
       </c>
       <c r="G150" t="n">
-        <v>0.329</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="151">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-1.923</v>
+        <v>-1.911</v>
       </c>
       <c r="E152" t="n">
         <v>20.1</v>
@@ -4830,7 +4830,7 @@
         <v>0.3</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.68</v>
+        <v>-0.674</v>
       </c>
     </row>
     <row r="153">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-2.265</v>
+        <v>-2.215</v>
       </c>
       <c r="E153" t="n">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="F153" t="n">
         <v>0.3</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.213</v>
+        <v>-1.194</v>
       </c>
     </row>
     <row r="154">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-4.395</v>
+        <v>-4.394</v>
       </c>
       <c r="E161" t="n">
         <v>18.1</v>
@@ -5111,16 +5111,16 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>12.358</v>
+        <v>12.48</v>
       </c>
       <c r="E162" t="n">
-        <v>33.7</v>
+        <v>34.1</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>9.385</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="163">
@@ -5169,16 +5169,16 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
+        <v>3.997</v>
       </c>
       <c r="E164" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>2.355</v>
+        <v>2.334</v>
       </c>
     </row>
     <row r="165">
@@ -5198,16 +5198,16 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2.381</v>
+        <v>2.075</v>
       </c>
       <c r="E165" t="n">
-        <v>27.4</v>
+        <v>27</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>1.932</v>
+        <v>1.729</v>
       </c>
     </row>
     <row r="166">
@@ -5227,16 +5227,16 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2.057</v>
+        <v>1.874</v>
       </c>
       <c r="E166" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1.618</v>
+        <v>1.537</v>
       </c>
     </row>
     <row r="167">
@@ -5256,16 +5256,16 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.875</v>
+        <v>1.804</v>
       </c>
       <c r="E167" t="n">
-        <v>24.9</v>
+        <v>23.1</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1.489</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="168">
@@ -5285,16 +5285,16 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
       <c r="E168" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.556</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="169">
@@ -5314,16 +5314,16 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-4.209</v>
+        <v>-4.122</v>
       </c>
       <c r="E169" t="n">
-        <v>26.1</v>
+        <v>25.5</v>
       </c>
       <c r="F169" t="n">
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>-1.745</v>
+        <v>-1.656</v>
       </c>
     </row>
     <row r="170">
@@ -5381,7 +5381,7 @@
         <v>0.467</v>
       </c>
       <c r="G171" t="n">
-        <v>1.821</v>
+        <v>1.822</v>
       </c>
     </row>
     <row r="172">
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-0.543</v>
+        <v>-0.542</v>
       </c>
       <c r="E175" t="n">
         <v>30.7</v>
@@ -5813,10 +5813,10 @@
         <v>30.2</v>
       </c>
       <c r="F186" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G186" t="n">
-        <v>2.492</v>
+        <v>2.513</v>
       </c>
     </row>
     <row r="187">
@@ -5842,10 +5842,10 @@
         <v>34.6</v>
       </c>
       <c r="F187" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G187" t="n">
-        <v>2.109</v>
+        <v>2.133</v>
       </c>
     </row>
     <row r="188">
@@ -5871,10 +5871,10 @@
         <v>28.5</v>
       </c>
       <c r="F188" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G188" t="n">
-        <v>2.033</v>
+        <v>2.053</v>
       </c>
     </row>
     <row r="189">
@@ -5900,10 +5900,10 @@
         <v>23.6</v>
       </c>
       <c r="F189" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G189" t="n">
-        <v>0.823</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="190">
@@ -5929,10 +5929,10 @@
         <v>27.5</v>
       </c>
       <c r="F190" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G190" t="n">
-        <v>0.329</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="191">
@@ -5958,10 +5958,10 @@
         <v>28.3</v>
       </c>
       <c r="F191" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G191" t="n">
-        <v>0.312</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="192">
@@ -5987,10 +5987,10 @@
         <v>19.8</v>
       </c>
       <c r="F192" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.374</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="193">
@@ -6010,16 +6010,16 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>-1.824</v>
+        <v>-1.823</v>
       </c>
       <c r="E193" t="n">
         <v>32.3</v>
       </c>
       <c r="F193" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G193" t="n">
-        <v>-0.89</v>
+        <v>-0.868</v>
       </c>
     </row>
     <row r="194">
@@ -6035,20 +6035,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>6.815</v>
+        <v>3.786</v>
       </c>
       <c r="E194" t="n">
-        <v>20.5</v>
+        <v>30.9</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>3.066</v>
+        <v>2.678</v>
       </c>
     </row>
     <row r="195">
@@ -6064,20 +6064,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3.738</v>
+        <v>3.746</v>
       </c>
       <c r="E195" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>2.442</v>
+        <v>2.296</v>
       </c>
     </row>
     <row r="196">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3.538</v>
+        <v>2.657</v>
       </c>
       <c r="E196" t="n">
-        <v>26.8</v>
+        <v>28.7</v>
       </c>
       <c r="F196" t="n">
         <v>0.367</v>
       </c>
       <c r="G196" t="n">
-        <v>2.179</v>
+        <v>1.807</v>
       </c>
     </row>
     <row r="197">
@@ -6122,20 +6122,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Jerami Grant</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2.473</v>
+        <v>0.095</v>
       </c>
       <c r="E197" t="n">
-        <v>29.8</v>
+        <v>31.8</v>
       </c>
       <c r="F197" t="n">
         <v>0.367</v>
       </c>
       <c r="G197" t="n">
-        <v>1.763</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="198">
@@ -6151,20 +6151,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Vít Krejčí</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.135</v>
+        <v>-0.379</v>
       </c>
       <c r="E198" t="n">
-        <v>32</v>
+        <v>19.8</v>
       </c>
       <c r="F198" t="n">
         <v>0.367</v>
       </c>
       <c r="G198" t="n">
-        <v>0.335</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="199">
@@ -6180,20 +6180,20 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Caleb Love</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-2.24</v>
+        <v>-1.6</v>
       </c>
       <c r="E199" t="n">
-        <v>23.3</v>
+        <v>24.6</v>
       </c>
       <c r="F199" t="n">
         <v>0.367</v>
       </c>
       <c r="G199" t="n">
-        <v>-0.911</v>
+        <v>-0.631</v>
       </c>
     </row>
     <row r="200">
@@ -6209,20 +6209,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Caleb Love</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-1.896</v>
+        <v>-2.24</v>
       </c>
       <c r="E200" t="n">
-        <v>31.2</v>
+        <v>23.3</v>
       </c>
       <c r="F200" t="n">
         <v>0.367</v>
       </c>
       <c r="G200" t="n">
-        <v>-0.993</v>
+        <v>-0.911</v>
       </c>
     </row>
     <row r="201">
@@ -6238,20 +6238,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-2.415</v>
+        <v>-1.842</v>
       </c>
       <c r="E201" t="n">
-        <v>24.1</v>
+        <v>29.6</v>
       </c>
       <c r="F201" t="n">
         <v>0.367</v>
       </c>
       <c r="G201" t="n">
-        <v>-1.028</v>
+        <v>-0.911</v>
       </c>
     </row>
     <row r="202">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.71</v>
+        <v>0.711</v>
       </c>
       <c r="E204" t="n">
         <v>22.2</v>
@@ -6354,20 +6354,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.378</v>
+        <v>-0.15</v>
       </c>
       <c r="E205" t="n">
-        <v>21.9</v>
+        <v>23.3</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>0.219</v>
+        <v>-0.025</v>
       </c>
     </row>
     <row r="206">
@@ -6383,20 +6383,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-0.15</v>
+        <v>-0.913</v>
       </c>
       <c r="E206" t="n">
-        <v>23.3</v>
+        <v>32.5</v>
       </c>
       <c r="F206" t="n">
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.025</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="207">
@@ -6412,20 +6412,20 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Daeqwon Plowden</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-0.913</v>
+        <v>-2.965</v>
       </c>
       <c r="E207" t="n">
-        <v>32.5</v>
+        <v>29.2</v>
       </c>
       <c r="F207" t="n">
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-0.55</v>
+        <v>-1.743</v>
       </c>
     </row>
     <row r="208">
@@ -6441,20 +6441,20 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Daeqwon Plowden</t>
+          <t>DaQuan Jeffries</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>-2.965</v>
+        <v>-3.854</v>
       </c>
       <c r="E208" t="n">
-        <v>29.2</v>
+        <v>25.9</v>
       </c>
       <c r="F208" t="n">
         <v>0.1</v>
       </c>
       <c r="G208" t="n">
-        <v>-1.743</v>
+        <v>-2.029</v>
       </c>
     </row>
     <row r="209">
@@ -6470,20 +6470,20 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>DaQuan Jeffries</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-3.854</v>
+        <v>-3.708</v>
       </c>
       <c r="E209" t="n">
-        <v>25.9</v>
+        <v>35</v>
       </c>
       <c r="F209" t="n">
         <v>0.1</v>
       </c>
       <c r="G209" t="n">
-        <v>-2.029</v>
+        <v>-2.628</v>
       </c>
     </row>
     <row r="210">
@@ -6735,16 +6735,16 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4.08</v>
+        <v>4.162</v>
       </c>
       <c r="E218" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="F218" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G218" t="n">
-        <v>3.149</v>
+        <v>3.128</v>
       </c>
     </row>
     <row r="219">
@@ -6764,16 +6764,16 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>3.39</v>
+        <v>3.506</v>
       </c>
       <c r="E219" t="n">
-        <v>21</v>
+        <v>20.1</v>
       </c>
       <c r="F219" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G219" t="n">
-        <v>1.713</v>
+        <v>1.678</v>
       </c>
     </row>
     <row r="220">
@@ -6793,16 +6793,16 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>2.1</v>
+        <v>1.967</v>
       </c>
       <c r="E220" t="n">
-        <v>27.5</v>
+        <v>27.1</v>
       </c>
       <c r="F220" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G220" t="n">
-        <v>1.511</v>
+        <v>1.391</v>
       </c>
     </row>
     <row r="221">
@@ -6822,16 +6822,16 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.747</v>
+        <v>1.405</v>
       </c>
       <c r="E221" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="F221" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G221" t="n">
-        <v>1.461</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="222">
@@ -6851,16 +6851,16 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.894</v>
+        <v>0.862</v>
       </c>
       <c r="E222" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="F222" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G222" t="n">
-        <v>1.013</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="223">
@@ -6880,16 +6880,16 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1.447</v>
+        <v>1.388</v>
       </c>
       <c r="E223" t="n">
-        <v>23.9</v>
+        <v>23</v>
       </c>
       <c r="F223" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G223" t="n">
-        <v>0.987</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="224">
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.283</v>
+        <v>-0.35</v>
       </c>
       <c r="E224" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="F224" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G224" t="n">
-        <v>0.109</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="225">
@@ -6938,16 +6938,16 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-1.257</v>
+        <v>-1.282</v>
       </c>
       <c r="E225" t="n">
-        <v>20.9</v>
+        <v>22.3</v>
       </c>
       <c r="F225" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.315</v>
+        <v>-0.364</v>
       </c>
     </row>
     <row r="226">
@@ -6996,16 +6996,16 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1.207</v>
+        <v>1.221</v>
       </c>
       <c r="E227" t="n">
-        <v>24</v>
+        <v>25.2</v>
       </c>
       <c r="F227" t="n">
         <v>0.167</v>
       </c>
       <c r="G227" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="228">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.766</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E228" t="n">
         <v>26.1</v>
@@ -7034,7 +7034,7 @@
         <v>0.167</v>
       </c>
       <c r="G228" t="n">
-        <v>0.507</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="229">
@@ -7054,16 +7054,16 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-0.342</v>
+        <v>-0.506</v>
       </c>
       <c r="E229" t="n">
-        <v>25.9</v>
+        <v>26.4</v>
       </c>
       <c r="F229" t="n">
         <v>0.167</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.095</v>
+        <v>-0.187</v>
       </c>
     </row>
     <row r="230">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-1.446</v>
+        <v>-1.465</v>
       </c>
       <c r="E231" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
       <c r="F231" t="n">
         <v>0.167</v>
       </c>
       <c r="G231" t="n">
-        <v>-0.786</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="232">
@@ -7141,16 +7141,16 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>-1.819</v>
+        <v>-1.979</v>
       </c>
       <c r="E232" t="n">
-        <v>26.4</v>
+        <v>28.2</v>
       </c>
       <c r="F232" t="n">
         <v>0.167</v>
       </c>
       <c r="G232" t="n">
-        <v>-0.91</v>
+        <v>-1.064</v>
       </c>
     </row>
     <row r="233">
@@ -7170,16 +7170,16 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-3.383</v>
+        <v>-3.391</v>
       </c>
       <c r="E233" t="n">
-        <v>34.4</v>
+        <v>35.3</v>
       </c>
       <c r="F233" t="n">
         <v>0.167</v>
       </c>
       <c r="G233" t="n">
-        <v>-2.303</v>
+        <v>-2.371</v>
       </c>
     </row>
     <row r="234">
@@ -7199,16 +7199,16 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3.126</v>
+        <v>3.237</v>
       </c>
       <c r="E234" t="n">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>1.527</v>
+        <v>1.516</v>
       </c>
     </row>
     <row r="235">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.389</v>
+        <v>0.39</v>
       </c>
       <c r="E235" t="n">
         <v>31.3</v>
@@ -7257,16 +7257,16 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.296</v>
+        <v>-0.264</v>
       </c>
       <c r="E236" t="n">
-        <v>30</v>
+        <v>29.2</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.164</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="237">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-1.002</v>
+        <v>-1.229</v>
       </c>
       <c r="E237" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.457</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="238">
@@ -7311,20 +7311,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-1.139</v>
+        <v>-2.279</v>
       </c>
       <c r="E238" t="n">
-        <v>22.4</v>
+        <v>24.3</v>
       </c>
       <c r="F238" t="n">
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-0.517</v>
+        <v>-1.135</v>
       </c>
     </row>
     <row r="239">
@@ -7344,16 +7344,16 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-2.689</v>
+        <v>-2.704</v>
       </c>
       <c r="E239" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="F239" t="n">
         <v>0.033</v>
       </c>
       <c r="G239" t="n">
-        <v>-1.243</v>
+        <v>-1.277</v>
       </c>
     </row>
     <row r="240">
@@ -7373,16 +7373,16 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-2.711</v>
+        <v>-2.646</v>
       </c>
       <c r="E240" t="n">
-        <v>27.5</v>
+        <v>28.4</v>
       </c>
       <c r="F240" t="n">
         <v>0.033</v>
       </c>
       <c r="G240" t="n">
-        <v>-1.534</v>
+        <v>-1.546</v>
       </c>
     </row>
     <row r="241">
@@ -7402,16 +7402,16 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>-2.566</v>
+        <v>-2.407</v>
       </c>
       <c r="E241" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="F241" t="n">
         <v>0.033</v>
       </c>
       <c r="G241" t="n">
-        <v>-1.72</v>
+        <v>-1.597</v>
       </c>
     </row>
   </sheetData>
@@ -7471,26 +7471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>20.606</v>
+        <v>20.715</v>
       </c>
       <c r="F2" t="n">
-        <v>3.086</v>
+        <v>2.735</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
     </row>
@@ -7500,26 +7500,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>19.947</v>
+        <v>20.606</v>
       </c>
       <c r="F3" t="n">
-        <v>2.736</v>
+        <v>3.086</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>18.783</v>
+        <v>20.249</v>
       </c>
       <c r="F4" t="n">
-        <v>2.839</v>
+        <v>2.858</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
     </row>
@@ -7558,26 +7558,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>18.318</v>
+        <v>18.601</v>
       </c>
       <c r="F5" t="n">
-        <v>2.296</v>
+        <v>2.794</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>15.713</v>
+        <v>15.876</v>
       </c>
       <c r="F6" t="n">
         <v>2.401</v>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>9.628</v>
+        <v>9.052</v>
       </c>
       <c r="F12" t="n">
-        <v>1.515</v>
+        <v>1.133</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>9.375</v>
+        <v>8.992000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.309</v>
+        <v>1.457</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7819,26 +7819,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>9.052</v>
+        <v>8.898999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.133</v>
+        <v>0.677</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7848,26 +7848,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>8.898999999999999</v>
+        <v>7.604</v>
       </c>
       <c r="F15" t="n">
-        <v>0.677</v>
+        <v>1.032</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
     </row>
@@ -7877,26 +7877,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>7.583</v>
+        <v>6.991</v>
       </c>
       <c r="F16" t="n">
-        <v>1.029</v>
+        <v>0.856</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
     </row>
@@ -7906,26 +7906,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>6.853</v>
+        <v>6.779</v>
       </c>
       <c r="F17" t="n">
-        <v>1.268</v>
+        <v>0.644</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
     </row>
@@ -7935,26 +7935,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6.834</v>
+        <v>6.251</v>
       </c>
       <c r="F18" t="n">
-        <v>0.856</v>
+        <v>0.448</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>6.779</v>
+        <v>5.817</v>
       </c>
       <c r="F19" t="n">
-        <v>0.644</v>
+        <v>1.005</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -8005,10 +8005,10 @@
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.432</v>
+        <v>5.028</v>
       </c>
       <c r="F20" t="n">
-        <v>0.61</v>
+        <v>0.519</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>4.601</v>
+        <v>4.629</v>
       </c>
       <c r="F21" t="n">
-        <v>0.374</v>
+        <v>0.528</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
     </row>
@@ -8051,26 +8051,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.544</v>
+        <v>4.601</v>
       </c>
       <c r="F22" t="n">
-        <v>0.658</v>
+        <v>0.374</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4.078</v>
+        <v>4.079</v>
       </c>
       <c r="F23" t="n">
         <v>0.115</v>
@@ -8150,14 +8150,14 @@
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>0.335</v>
+        <v>-0.026</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.105</v>
+        <v>-0.202</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Marvin Bagley III</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
     </row>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.415</v>
+        <v>-2.721</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.616</v>
+        <v>-0.763</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
     </row>
@@ -8237,10 +8237,10 @@
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.506</v>
+        <v>-2.893</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.571</v>
+        <v>-0.639</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.721</v>
+        <v>-4.467</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.763</v>
+        <v>-0.988</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
     </row>
@@ -8283,26 +8283,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.832</v>
+        <v>-5.262</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.861</v>
+        <v>-1.126</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
     </row>
@@ -8324,10 +8324,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-8.901999999999999</v>
+        <v>-9.077</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.478</v>
+        <v>-2.452</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -554,20 +554,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.26</v>
+        <v>1.679</v>
       </c>
       <c r="E5" t="n">
-        <v>27.9</v>
+        <v>32.6</v>
       </c>
       <c r="F5" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.642</v>
+        <v>1.523</v>
       </c>
     </row>
     <row r="6">
@@ -583,20 +583,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.679</v>
+        <v>1.367</v>
       </c>
       <c r="E6" t="n">
-        <v>32.6</v>
+        <v>28.8</v>
       </c>
       <c r="F6" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.523</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="7">
@@ -612,20 +612,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.367</v>
+        <v>1.769</v>
       </c>
       <c r="E7" t="n">
-        <v>28.8</v>
+        <v>20.2</v>
       </c>
       <c r="F7" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.162</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="8">
@@ -641,20 +641,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Jock Landale</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.769</v>
+        <v>1.421</v>
       </c>
       <c r="E8" t="n">
-        <v>20.2</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.984</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="9">
@@ -670,20 +670,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.198</v>
+        <v>-1.272</v>
       </c>
       <c r="E9" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="F9" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.273</v>
+        <v>-0.286</v>
       </c>
     </row>
     <row r="10">
@@ -1598,20 +1598,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nick Richards</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-3.981</v>
+        <v>-5.044</v>
       </c>
       <c r="E41" t="n">
-        <v>24.2</v>
+        <v>22.3</v>
       </c>
       <c r="F41" t="n">
         <v>0.333</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.842</v>
+        <v>-2.186</v>
       </c>
     </row>
     <row r="42">
@@ -4208,20 +4208,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bobby Portis</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1.85</v>
+        <v>0.93</v>
       </c>
       <c r="E131" t="n">
-        <v>25.3</v>
+        <v>22.8</v>
       </c>
       <c r="F131" t="n">
         <v>0.233</v>
       </c>
       <c r="G131" t="n">
-        <v>1.099</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="132">
@@ -4237,20 +4237,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.93</v>
+        <v>0.425</v>
       </c>
       <c r="E132" t="n">
-        <v>22.8</v>
+        <v>18.2</v>
       </c>
       <c r="F132" t="n">
         <v>0.233</v>
       </c>
       <c r="G132" t="n">
-        <v>0.552</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.425</v>
+        <v>-1.366</v>
       </c>
       <c r="E133" t="n">
-        <v>18.2</v>
+        <v>27.9</v>
       </c>
       <c r="F133" t="n">
         <v>0.233</v>
       </c>
       <c r="G133" t="n">
-        <v>0.25</v>
+        <v>-0.658</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Cole Anthony</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-1.366</v>
+        <v>-2.314</v>
       </c>
       <c r="E134" t="n">
-        <v>27.9</v>
+        <v>15.9</v>
       </c>
       <c r="F134" t="n">
         <v>0.233</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.658</v>
+        <v>-0.6879999999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7686,10 +7686,10 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>14.572</v>
+        <v>13.619</v>
       </c>
       <c r="F9" t="n">
-        <v>2.376</v>
+        <v>2.262</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -8005,10 +8005,10 @@
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.028</v>
+        <v>4.684</v>
       </c>
       <c r="F20" t="n">
-        <v>0.519</v>
+        <v>0.386</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -8179,10 +8179,10 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.349</v>
+        <v>-2.136</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.531</v>
+        <v>-1.052</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.046</v>
+        <v>6.142</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>36.6</v>
       </c>
       <c r="F2" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>4.958</v>
+        <v>5.119</v>
       </c>
     </row>
     <row r="3">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.869</v>
+        <v>4.872</v>
       </c>
       <c r="E3" t="n">
         <v>23.4</v>
@@ -509,7 +509,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.655</v>
+        <v>2.657</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.216</v>
+        <v>2.258</v>
       </c>
       <c r="E4" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="F4" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.921</v>
+        <v>1.962</v>
       </c>
     </row>
     <row r="5">
@@ -554,20 +554,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.679</v>
+        <v>2.263</v>
       </c>
       <c r="E5" t="n">
-        <v>32.6</v>
+        <v>27.9</v>
       </c>
       <c r="F5" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.523</v>
+        <v>1.644</v>
       </c>
     </row>
     <row r="6">
@@ -583,20 +583,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.367</v>
+        <v>1.682</v>
       </c>
       <c r="E6" t="n">
-        <v>28.8</v>
+        <v>32.6</v>
       </c>
       <c r="F6" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.162</v>
+        <v>1.526</v>
       </c>
     </row>
     <row r="7">
@@ -612,20 +612,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.769</v>
+        <v>1.322</v>
       </c>
       <c r="E7" t="n">
-        <v>20.2</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.984</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="8">
@@ -641,20 +641,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jock Landale</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.421</v>
+        <v>1.772</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>20.2</v>
       </c>
       <c r="F8" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.702</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="9">
@@ -670,20 +670,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.272</v>
+        <v>-1.195</v>
       </c>
       <c r="E9" t="n">
-        <v>19.5</v>
+        <v>20.7</v>
       </c>
       <c r="F9" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.286</v>
+        <v>-0.271</v>
       </c>
     </row>
     <row r="10">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.104</v>
+        <v>4.108</v>
       </c>
       <c r="E10" t="n">
         <v>33.9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G10" t="n">
-        <v>3.531</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="11">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.852</v>
+        <v>3.854</v>
       </c>
       <c r="E11" t="n">
         <v>35.5</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G11" t="n">
-        <v>3.511</v>
+        <v>3.488</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3.567</v>
+        <v>3.57</v>
       </c>
       <c r="E12" t="n">
         <v>33.7</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G12" t="n">
-        <v>3.135</v>
+        <v>3.114</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.118</v>
+        <v>2.121</v>
       </c>
       <c r="E13" t="n">
         <v>32.1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G13" t="n">
-        <v>2.021</v>
+        <v>2.001</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.583</v>
+        <v>2.586</v>
       </c>
       <c r="E14" t="n">
         <v>27.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G14" t="n">
-        <v>1.992</v>
+        <v>1.975</v>
       </c>
     </row>
     <row r="15">
@@ -854,10 +854,10 @@
         <v>20.4</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G15" t="n">
-        <v>0.586</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.155</v>
+        <v>-0.152</v>
       </c>
       <c r="E16" t="n">
         <v>24.7</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G16" t="n">
-        <v>0.383</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.741</v>
+        <v>-0.738</v>
       </c>
       <c r="E17" t="n">
         <v>26.2</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.453</v>
+        <v>2.457</v>
       </c>
       <c r="E18" t="n">
         <v>22.6</v>
@@ -944,7 +944,7 @@
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>1.185</v>
+        <v>1.186</v>
       </c>
     </row>
     <row r="19">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.297</v>
+        <v>-0.293</v>
       </c>
       <c r="E19" t="n">
         <v>23</v>
@@ -973,7 +973,7 @@
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.11</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="20">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.874</v>
+        <v>-1.871</v>
       </c>
       <c r="E20" t="n">
         <v>22.1</v>
@@ -1002,7 +1002,7 @@
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.831</v>
+        <v>-0.829</v>
       </c>
     </row>
     <row r="21">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2.023</v>
+        <v>-2.019</v>
       </c>
       <c r="E21" t="n">
         <v>21.7</v>
@@ -1031,7 +1031,7 @@
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.886</v>
+        <v>-0.885</v>
       </c>
     </row>
     <row r="22">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-3.116</v>
+        <v>-3.113</v>
       </c>
       <c r="E22" t="n">
         <v>22.4</v>
@@ -1060,7 +1060,7 @@
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.426</v>
+        <v>-1.424</v>
       </c>
     </row>
     <row r="23">
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4.861</v>
+        <v>-4.858</v>
       </c>
       <c r="E23" t="n">
         <v>20.6</v>
@@ -1089,7 +1089,7 @@
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.057</v>
+        <v>-2.056</v>
       </c>
     </row>
     <row r="24">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-4.685</v>
+        <v>-4.682</v>
       </c>
       <c r="E24" t="n">
         <v>24.5</v>
@@ -1118,7 +1118,7 @@
         <v>0.067</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.358</v>
+        <v>-2.356</v>
       </c>
     </row>
     <row r="25">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-5.215</v>
+        <v>-5.212</v>
       </c>
       <c r="E25" t="n">
         <v>24.2</v>
@@ -1147,7 +1147,7 @@
         <v>0.067</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.594</v>
+        <v>-2.592</v>
       </c>
     </row>
     <row r="26">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.577</v>
+        <v>5.617</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>28.2</v>
       </c>
       <c r="F26" t="n">
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.526</v>
+        <v>3.711</v>
       </c>
     </row>
     <row r="27">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3.509</v>
+        <v>3.725</v>
       </c>
       <c r="E27" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="F27" t="n">
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>2.511</v>
+        <v>2.697</v>
       </c>
     </row>
     <row r="28">
@@ -1225,16 +1225,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.998</v>
+        <v>2.035</v>
       </c>
       <c r="E28" t="n">
-        <v>30.7</v>
+        <v>31.3</v>
       </c>
       <c r="F28" t="n">
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1.728</v>
+        <v>1.784</v>
       </c>
     </row>
     <row r="29">
@@ -1254,16 +1254,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.789</v>
+        <v>1.842</v>
       </c>
       <c r="E29" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="F29" t="n">
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.481</v>
+        <v>1.518</v>
       </c>
     </row>
     <row r="30">
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.656</v>
+        <v>0.6</v>
       </c>
       <c r="E30" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="F30" t="n">
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>0.822</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="31">
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.944</v>
+        <v>0.866</v>
       </c>
       <c r="E31" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="F31" t="n">
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0.701</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="32">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1.469</v>
+        <v>-1.468</v>
       </c>
       <c r="E32" t="n">
         <v>19.2</v>
@@ -1350,7 +1350,7 @@
         <v>0.7</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.307</v>
+        <v>-0.306</v>
       </c>
     </row>
     <row r="33">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-3.942</v>
+        <v>-3.94</v>
       </c>
       <c r="E33" t="n">
         <v>20.9</v>
@@ -1379,7 +1379,7 @@
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.41</v>
+        <v>-1.409</v>
       </c>
     </row>
     <row r="34">
@@ -1399,16 +1399,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.66</v>
+        <v>4.311</v>
       </c>
       <c r="E34" t="n">
         <v>35.8</v>
       </c>
       <c r="F34" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G34" t="n">
-        <v>3.722</v>
+        <v>3.435</v>
       </c>
     </row>
     <row r="35">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.354</v>
+        <v>3.573</v>
       </c>
       <c r="E35" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
       <c r="F35" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G35" t="n">
-        <v>2.267</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="36">
@@ -1453,20 +1453,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.92</v>
+        <v>2.751</v>
       </c>
       <c r="E36" t="n">
-        <v>24.8</v>
+        <v>27.1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G36" t="n">
-        <v>1.164</v>
+        <v>1.721</v>
       </c>
     </row>
     <row r="37">
@@ -1482,20 +1482,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.174</v>
+        <v>2.073</v>
       </c>
       <c r="E37" t="n">
-        <v>32.6</v>
+        <v>25</v>
       </c>
       <c r="F37" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G37" t="n">
-        <v>1.024</v>
+        <v>1.234</v>
       </c>
     </row>
     <row r="38">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Leonard Miller</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.018</v>
+        <v>1.068</v>
       </c>
       <c r="E38" t="n">
-        <v>24.8</v>
+        <v>34</v>
       </c>
       <c r="F38" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.181</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="39">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="E39" t="n">
         <v>30.9</v>
       </c>
       <c r="F39" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G39" t="n">
-        <v>0.17</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="40">
@@ -1569,20 +1569,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Leonard Miller</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-2.926</v>
+        <v>-0.644</v>
       </c>
       <c r="E40" t="n">
-        <v>30.7</v>
+        <v>25</v>
       </c>
       <c r="F40" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.658</v>
+        <v>-0.179</v>
       </c>
     </row>
     <row r="41">
@@ -1598,20 +1598,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rob Dillingham</t>
+          <t>Isaac Okoro</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-5.044</v>
+        <v>-2.789</v>
       </c>
       <c r="E41" t="n">
-        <v>22.3</v>
+        <v>30.9</v>
       </c>
       <c r="F41" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.186</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="42">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7.086</v>
+        <v>7.09</v>
       </c>
       <c r="E42" t="n">
         <v>34.1</v>
@@ -1640,7 +1640,7 @@
         <v>0.767</v>
       </c>
       <c r="G42" t="n">
-        <v>5.576</v>
+        <v>5.579</v>
       </c>
     </row>
     <row r="43">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5.944</v>
+        <v>5.948</v>
       </c>
       <c r="E43" t="n">
         <v>35.7</v>
@@ -1669,7 +1669,7 @@
         <v>0.767</v>
       </c>
       <c r="G43" t="n">
-        <v>4.986</v>
+        <v>4.989</v>
       </c>
     </row>
     <row r="44">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.859</v>
+        <v>3.862</v>
       </c>
       <c r="E44" t="n">
         <v>31.3</v>
@@ -1698,7 +1698,7 @@
         <v>0.767</v>
       </c>
       <c r="G44" t="n">
-        <v>3.016</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="45">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.177</v>
+        <v>4.18</v>
       </c>
       <c r="E45" t="n">
         <v>29.1</v>
@@ -1727,7 +1727,7 @@
         <v>0.767</v>
       </c>
       <c r="G45" t="n">
-        <v>2.993</v>
+        <v>2.995</v>
       </c>
     </row>
     <row r="46">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.804</v>
+        <v>1.807</v>
       </c>
       <c r="E46" t="n">
         <v>28.7</v>
@@ -1756,7 +1756,7 @@
         <v>0.767</v>
       </c>
       <c r="G46" t="n">
-        <v>1.538</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="47">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.204</v>
+        <v>1.205</v>
       </c>
       <c r="E47" t="n">
         <v>27.6</v>
@@ -1785,7 +1785,7 @@
         <v>0.767</v>
       </c>
       <c r="G47" t="n">
-        <v>1.132</v>
+        <v>1.133</v>
       </c>
     </row>
     <row r="48">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.836</v>
+        <v>0.839</v>
       </c>
       <c r="E48" t="n">
         <v>31.7</v>
@@ -1814,7 +1814,7 @@
         <v>0.767</v>
       </c>
       <c r="G48" t="n">
-        <v>1.058</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="49">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.218</v>
+        <v>-0.215</v>
       </c>
       <c r="E49" t="n">
         <v>26.9</v>
@@ -1843,7 +1843,7 @@
         <v>0.767</v>
       </c>
       <c r="G49" t="n">
-        <v>0.307</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="50">
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.351</v>
+        <v>1.354</v>
       </c>
       <c r="E50" t="n">
         <v>33.9</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2</v>
+        <v>0.233</v>
       </c>
       <c r="G50" t="n">
-        <v>1.094</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="51">
@@ -1892,16 +1892,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.441</v>
+        <v>2.444</v>
       </c>
       <c r="E51" t="n">
         <v>19.4</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2</v>
+        <v>0.233</v>
       </c>
       <c r="G51" t="n">
-        <v>1.066</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="52">
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="E52" t="n">
         <v>20.4</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2</v>
+        <v>0.233</v>
       </c>
       <c r="G52" t="n">
-        <v>0.431</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="53">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-0.113</v>
+        <v>-0.11</v>
       </c>
       <c r="E53" t="n">
         <v>29.7</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2</v>
+        <v>0.233</v>
       </c>
       <c r="G53" t="n">
-        <v>0.054</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="54">
@@ -1979,16 +1979,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-0.893</v>
+        <v>-0.89</v>
       </c>
       <c r="E54" t="n">
         <v>21.1</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2</v>
+        <v>0.233</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.305</v>
+        <v>-0.289</v>
       </c>
     </row>
     <row r="55">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.229</v>
+        <v>-1.225</v>
       </c>
       <c r="E55" t="n">
         <v>31.8</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2</v>
+        <v>0.233</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.681</v>
+        <v>-0.656</v>
       </c>
     </row>
     <row r="56">
@@ -2037,16 +2037,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-1.403</v>
+        <v>-1.4</v>
       </c>
       <c r="E56" t="n">
         <v>28.1</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2</v>
+        <v>0.233</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.704</v>
+        <v>-0.6830000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -2066,16 +2066,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-2.586</v>
+        <v>-2.583</v>
       </c>
       <c r="E57" t="n">
         <v>19.7</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2</v>
+        <v>0.233</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.981</v>
+        <v>-0.966</v>
       </c>
     </row>
     <row r="58">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.212</v>
+        <v>15.215</v>
       </c>
       <c r="E58" t="n">
         <v>36.2</v>
@@ -2104,7 +2104,7 @@
         <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>12.098</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="59">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6.401</v>
+        <v>6.404</v>
       </c>
       <c r="E59" t="n">
         <v>36.1</v>
@@ -2133,7 +2133,7 @@
         <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>5.435</v>
+        <v>5.437</v>
       </c>
     </row>
     <row r="60">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.439</v>
+        <v>3.442</v>
       </c>
       <c r="E60" t="n">
         <v>25.9</v>
@@ -2162,7 +2162,7 @@
         <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>2.306</v>
+        <v>2.308</v>
       </c>
     </row>
     <row r="61">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.75</v>
+        <v>0.753</v>
       </c>
       <c r="E61" t="n">
         <v>33.6</v>
@@ -2191,7 +2191,7 @@
         <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>1.108</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="62">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.464</v>
+        <v>0.467</v>
       </c>
       <c r="E62" t="n">
         <v>24.7</v>
@@ -2220,7 +2220,7 @@
         <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>0.668</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="63">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-0.52</v>
+        <v>-0.516</v>
       </c>
       <c r="E63" t="n">
         <v>29.9</v>
@@ -2249,7 +2249,7 @@
         <v>0.833</v>
       </c>
       <c r="G63" t="n">
-        <v>0.195</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="64">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1.346</v>
+        <v>-1.343</v>
       </c>
       <c r="E64" t="n">
         <v>32.3</v>
@@ -2278,7 +2278,7 @@
         <v>0.833</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.345</v>
+        <v>-0.342</v>
       </c>
     </row>
     <row r="65">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-2.517</v>
+        <v>-2.514</v>
       </c>
       <c r="E65" t="n">
         <v>21.4</v>
@@ -2307,7 +2307,7 @@
         <v>0.833</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.75</v>
+        <v>-0.748</v>
       </c>
     </row>
     <row r="66">
@@ -2327,16 +2327,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4.971</v>
+        <v>5.303</v>
       </c>
       <c r="E66" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="F66" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G66" t="n">
-        <v>3.412</v>
+        <v>3.695</v>
       </c>
     </row>
     <row r="67">
@@ -2356,16 +2356,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.649</v>
+        <v>1.746</v>
       </c>
       <c r="E67" t="n">
-        <v>26.3</v>
+        <v>25.6</v>
       </c>
       <c r="F67" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G67" t="n">
-        <v>1.377</v>
+        <v>1.412</v>
       </c>
     </row>
     <row r="68">
@@ -2385,16 +2385,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.406</v>
+        <v>0.501</v>
       </c>
       <c r="E68" t="n">
-        <v>20.9</v>
+        <v>22.8</v>
       </c>
       <c r="F68" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G68" t="n">
-        <v>0.553</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="69">
@@ -2410,20 +2410,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Marcus Sasser</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.096</v>
+        <v>0.474</v>
       </c>
       <c r="E69" t="n">
-        <v>27.6</v>
+        <v>18.7</v>
       </c>
       <c r="F69" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G69" t="n">
-        <v>0.444</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="70">
@@ -2443,16 +2443,16 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.226</v>
+        <v>-0.042</v>
       </c>
       <c r="E70" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="F70" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G70" t="n">
-        <v>0.388</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="71">
@@ -2468,20 +2468,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-0.166</v>
+        <v>0.015</v>
       </c>
       <c r="E71" t="n">
-        <v>24.6</v>
+        <v>26.8</v>
       </c>
       <c r="F71" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G71" t="n">
-        <v>0.359</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="72">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Colby Jones</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-0.306</v>
+        <v>-0.046</v>
       </c>
       <c r="E72" t="n">
-        <v>28.3</v>
+        <v>25.5</v>
       </c>
       <c r="F72" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G72" t="n">
-        <v>0.33</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="73">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Caris LeVert</t>
+          <t>Colby Jones</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-1.077</v>
+        <v>-0.306</v>
       </c>
       <c r="E73" t="n">
-        <v>19.2</v>
+        <v>28.3</v>
       </c>
       <c r="F73" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="74">
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.433</v>
+        <v>4.436</v>
       </c>
       <c r="E74" t="n">
         <v>22</v>
       </c>
       <c r="F74" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G74" t="n">
-        <v>2.227</v>
+        <v>2.213</v>
       </c>
     </row>
     <row r="75">
@@ -2588,16 +2588,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3.412</v>
+        <v>3.415</v>
       </c>
       <c r="E75" t="n">
         <v>23.1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G75" t="n">
-        <v>1.849</v>
+        <v>1.834</v>
       </c>
     </row>
     <row r="76">
@@ -2617,16 +2617,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.106</v>
+        <v>1.109</v>
       </c>
       <c r="E76" t="n">
         <v>31.6</v>
       </c>
       <c r="F76" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G76" t="n">
-        <v>1.014</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="77">
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.884</v>
+        <v>0.887</v>
       </c>
       <c r="E77" t="n">
         <v>32.2</v>
       </c>
       <c r="F77" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>0.882</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="78">
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.03</v>
+        <v>-0.027</v>
       </c>
       <c r="E78" t="n">
         <v>20.3</v>
       </c>
       <c r="F78" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G78" t="n">
-        <v>0.171</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="79">
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.103</v>
+        <v>-0.1</v>
       </c>
       <c r="E79" t="n">
         <v>24.6</v>
       </c>
       <c r="F79" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G79" t="n">
-        <v>0.169</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="80">
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-0.575</v>
+        <v>-0.572</v>
       </c>
       <c r="E80" t="n">
         <v>24.3</v>
       </c>
       <c r="F80" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.08699999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-1.088</v>
+        <v>-1.085</v>
       </c>
       <c r="E81" t="n">
         <v>31</v>
       </c>
       <c r="F81" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.423</v>
+        <v>-0.443</v>
       </c>
     </row>
     <row r="82">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.126</v>
+        <v>4.129</v>
       </c>
       <c r="E82" t="n">
         <v>35.7</v>
@@ -2800,7 +2800,7 @@
         <v>0.733</v>
       </c>
       <c r="G82" t="n">
-        <v>3.614</v>
+        <v>3.617</v>
       </c>
     </row>
     <row r="83">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3.741</v>
+        <v>3.744</v>
       </c>
       <c r="E83" t="n">
         <v>32.6</v>
@@ -2829,7 +2829,7 @@
         <v>0.733</v>
       </c>
       <c r="G83" t="n">
-        <v>3.04</v>
+        <v>3.043</v>
       </c>
     </row>
     <row r="84">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.939</v>
+        <v>1.942</v>
       </c>
       <c r="E84" t="n">
         <v>38.4</v>
@@ -2858,7 +2858,7 @@
         <v>0.733</v>
       </c>
       <c r="G84" t="n">
-        <v>2.137</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="85">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2.325</v>
+        <v>2.328</v>
       </c>
       <c r="E85" t="n">
         <v>30.2</v>
@@ -2887,7 +2887,7 @@
         <v>0.733</v>
       </c>
       <c r="G85" t="n">
-        <v>1.923</v>
+        <v>1.925</v>
       </c>
     </row>
     <row r="86">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.79</v>
+        <v>1.793</v>
       </c>
       <c r="E86" t="n">
         <v>15.2</v>
@@ -2916,7 +2916,7 @@
         <v>0.733</v>
       </c>
       <c r="G86" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="87">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-0.781</v>
+        <v>-0.778</v>
       </c>
       <c r="E87" t="n">
         <v>36.7</v>
@@ -2945,7 +2945,7 @@
         <v>0.733</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.037</v>
+        <v>-0.034</v>
       </c>
     </row>
     <row r="88">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-1.584</v>
+        <v>-1.581</v>
       </c>
       <c r="E88" t="n">
         <v>23.6</v>
@@ -2974,7 +2974,7 @@
         <v>0.733</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.418</v>
+        <v>-0.417</v>
       </c>
     </row>
     <row r="89">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-6.144</v>
+        <v>-6.141</v>
       </c>
       <c r="E89" t="n">
         <v>19.2</v>
@@ -3003,7 +3003,7 @@
         <v>0.733</v>
       </c>
       <c r="G89" t="n">
-        <v>-2.161</v>
+        <v>-2.159</v>
       </c>
     </row>
     <row r="90">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.175</v>
+        <v>2.178</v>
       </c>
       <c r="E90" t="n">
         <v>30.8</v>
@@ -3032,7 +3032,7 @@
         <v>0.133</v>
       </c>
       <c r="G90" t="n">
-        <v>1.48</v>
+        <v>1.482</v>
       </c>
     </row>
     <row r="91">
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.563</v>
+        <v>2.567</v>
       </c>
       <c r="E91" t="n">
         <v>22.3</v>
@@ -3061,7 +3061,7 @@
         <v>0.133</v>
       </c>
       <c r="G91" t="n">
-        <v>1.252</v>
+        <v>1.254</v>
       </c>
     </row>
     <row r="92">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.491</v>
+        <v>1.494</v>
       </c>
       <c r="E92" t="n">
         <v>28.5</v>
@@ -3090,7 +3090,7 @@
         <v>0.133</v>
       </c>
       <c r="G92" t="n">
-        <v>0.964</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="93">
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-1.594</v>
+        <v>-1.59</v>
       </c>
       <c r="E93" t="n">
         <v>32.5</v>
@@ -3119,7 +3119,7 @@
         <v>0.133</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.988</v>
+        <v>-0.986</v>
       </c>
     </row>
     <row r="94">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-2.581</v>
+        <v>-2.578</v>
       </c>
       <c r="E94" t="n">
         <v>21.4</v>
@@ -3148,7 +3148,7 @@
         <v>0.133</v>
       </c>
       <c r="G94" t="n">
-        <v>-1.091</v>
+        <v>-1.089</v>
       </c>
     </row>
     <row r="95">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.47</v>
+        <v>-2.467</v>
       </c>
       <c r="E95" t="n">
         <v>28.8</v>
@@ -3177,7 +3177,7 @@
         <v>0.133</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.404</v>
+        <v>-1.402</v>
       </c>
     </row>
     <row r="96">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.455</v>
+        <v>-2.452</v>
       </c>
       <c r="E96" t="n">
         <v>30.3</v>
@@ -3206,7 +3206,7 @@
         <v>0.133</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.465</v>
+        <v>-1.463</v>
       </c>
     </row>
     <row r="97">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-3.23</v>
+        <v>-3.226</v>
       </c>
       <c r="E97" t="n">
         <v>22.8</v>
@@ -3235,7 +3235,7 @@
         <v>0.133</v>
       </c>
       <c r="G97" t="n">
-        <v>-1.469</v>
+        <v>-1.467</v>
       </c>
     </row>
     <row r="98">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.32</v>
+        <v>10.323</v>
       </c>
       <c r="E98" t="n">
         <v>31.1</v>
@@ -3264,7 +3264,7 @@
         <v>0.633</v>
       </c>
       <c r="G98" t="n">
-        <v>7.088</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="99">
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5.933</v>
+        <v>5.936</v>
       </c>
       <c r="E99" t="n">
         <v>35.6</v>
@@ -3293,7 +3293,7 @@
         <v>0.633</v>
       </c>
       <c r="G99" t="n">
-        <v>4.864</v>
+        <v>4.866</v>
       </c>
     </row>
     <row r="100">
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3.115</v>
+        <v>3.119</v>
       </c>
       <c r="E100" t="n">
         <v>28.2</v>
@@ -3322,7 +3322,7 @@
         <v>0.633</v>
       </c>
       <c r="G100" t="n">
-        <v>2.203</v>
+        <v>2.205</v>
       </c>
     </row>
     <row r="101">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="E101" t="n">
         <v>30.4</v>
@@ -3351,7 +3351,7 @@
         <v>0.633</v>
       </c>
       <c r="G101" t="n">
-        <v>0.917</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="102">
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.954</v>
+        <v>0.957</v>
       </c>
       <c r="E102" t="n">
         <v>26</v>
@@ -3380,7 +3380,7 @@
         <v>0.633</v>
       </c>
       <c r="G102" t="n">
-        <v>0.858</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="103">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="E103" t="n">
         <v>27.2</v>
@@ -3409,7 +3409,7 @@
         <v>0.633</v>
       </c>
       <c r="G103" t="n">
-        <v>0.311</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="104">
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.485</v>
+        <v>-0.481</v>
       </c>
       <c r="E104" t="n">
         <v>27</v>
@@ -3438,7 +3438,7 @@
         <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-1.36</v>
+        <v>-1.357</v>
       </c>
       <c r="E105" t="n">
         <v>29.7</v>
@@ -3467,7 +3467,7 @@
         <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.449</v>
+        <v>-0.447</v>
       </c>
     </row>
     <row r="106">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.984</v>
+        <v>11.988</v>
       </c>
       <c r="E106" t="n">
         <v>38.2</v>
@@ -3496,7 +3496,7 @@
         <v>0.6</v>
       </c>
       <c r="G106" t="n">
-        <v>10.026</v>
+        <v>10.029</v>
       </c>
     </row>
     <row r="107">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4.638</v>
+        <v>4.641</v>
       </c>
       <c r="E107" t="n">
         <v>39.8</v>
@@ -3525,7 +3525,7 @@
         <v>0.6</v>
       </c>
       <c r="G107" t="n">
-        <v>4.339</v>
+        <v>4.342</v>
       </c>
     </row>
     <row r="108">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4.575</v>
+        <v>4.578</v>
       </c>
       <c r="E108" t="n">
         <v>35.4</v>
@@ -3554,7 +3554,7 @@
         <v>0.6</v>
       </c>
       <c r="G108" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
     </row>
     <row r="109">
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.454</v>
+        <v>2.457</v>
       </c>
       <c r="E109" t="n">
         <v>21</v>
@@ -3583,7 +3583,7 @@
         <v>0.6</v>
       </c>
       <c r="G109" t="n">
-        <v>1.336</v>
+        <v>1.337</v>
       </c>
     </row>
     <row r="110">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.233</v>
+        <v>1.236</v>
       </c>
       <c r="E110" t="n">
         <v>21.3</v>
@@ -3612,7 +3612,7 @@
         <v>0.6</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.548</v>
+        <v>0.551</v>
       </c>
       <c r="E111" t="n">
         <v>26.9</v>
@@ -3641,7 +3641,7 @@
         <v>0.6</v>
       </c>
       <c r="G111" t="n">
-        <v>0.642</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="112">
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-0.66</v>
+        <v>-0.657</v>
       </c>
       <c r="E112" t="n">
         <v>18.2</v>
@@ -3670,7 +3670,7 @@
         <v>0.6</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.023</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="113">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-1.908</v>
+        <v>-1.904</v>
       </c>
       <c r="E113" t="n">
         <v>25.5</v>
@@ -3699,7 +3699,7 @@
         <v>0.6</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.696</v>
+        <v>-0.694</v>
       </c>
     </row>
     <row r="114">
@@ -3715,20 +3715,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Javon Small</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4.046</v>
+        <v>3.328</v>
       </c>
       <c r="E114" t="n">
-        <v>23.8</v>
+        <v>25.5</v>
       </c>
       <c r="F114" t="n">
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>2.141</v>
+        <v>1.911</v>
       </c>
     </row>
     <row r="115">
@@ -3744,20 +3744,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3.195</v>
+        <v>1.545</v>
       </c>
       <c r="E115" t="n">
-        <v>26.3</v>
+        <v>25.4</v>
       </c>
       <c r="F115" t="n">
         <v>0.267</v>
       </c>
       <c r="G115" t="n">
-        <v>1.893</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="116">
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1.383</v>
+        <v>1.386</v>
       </c>
       <c r="E116" t="n">
         <v>27.2</v>
@@ -3786,7 +3786,7 @@
         <v>0.267</v>
       </c>
       <c r="G116" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>GG Jackson</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.793</v>
+        <v>0.327</v>
       </c>
       <c r="E117" t="n">
-        <v>25.7</v>
+        <v>27.8</v>
       </c>
       <c r="F117" t="n">
         <v>0.267</v>
       </c>
       <c r="G117" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="118">
@@ -3831,20 +3831,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Taylor Hendricks</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.5639999999999999</v>
+        <v>-0.741</v>
       </c>
       <c r="E118" t="n">
-        <v>27</v>
+        <v>25.8</v>
       </c>
       <c r="F118" t="n">
         <v>0.267</v>
       </c>
       <c r="G118" t="n">
-        <v>0.467</v>
+        <v>-0.255</v>
       </c>
     </row>
     <row r="119">
@@ -3860,20 +3860,20 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Walter Clayton Jr.</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-0.744</v>
+        <v>-2.015</v>
       </c>
       <c r="E119" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="F119" t="n">
         <v>0.267</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.257</v>
+        <v>-0.881</v>
       </c>
     </row>
     <row r="120">
@@ -3889,20 +3889,20 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Walter Clayton Jr.</t>
+          <t>Jahmai Mashack</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-1.857</v>
+        <v>-4.025</v>
       </c>
       <c r="E120" t="n">
-        <v>24.3</v>
+        <v>25.3</v>
       </c>
       <c r="F120" t="n">
         <v>0.267</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.806</v>
+        <v>-1.984</v>
       </c>
     </row>
     <row r="121">
@@ -3922,16 +3922,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-4.746</v>
+        <v>-5.131</v>
       </c>
       <c r="E121" t="n">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
       <c r="F121" t="n">
         <v>0.267</v>
       </c>
       <c r="G121" t="n">
-        <v>-2.7</v>
+        <v>-2.971</v>
       </c>
     </row>
     <row r="122">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3.081</v>
+        <v>3.085</v>
       </c>
       <c r="E122" t="n">
         <v>31.6</v>
@@ -3960,7 +3960,7 @@
         <v>0.667</v>
       </c>
       <c r="G122" t="n">
-        <v>2.468</v>
+        <v>2.471</v>
       </c>
     </row>
     <row r="123">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.427</v>
+        <v>2.43</v>
       </c>
       <c r="E123" t="n">
         <v>35.8</v>
@@ -3989,7 +3989,7 @@
         <v>0.667</v>
       </c>
       <c r="G123" t="n">
-        <v>2.304</v>
+        <v>2.307</v>
       </c>
     </row>
     <row r="124">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2.846</v>
+        <v>2.849</v>
       </c>
       <c r="E124" t="n">
         <v>23.9</v>
@@ -4018,7 +4018,7 @@
         <v>0.667</v>
       </c>
       <c r="G124" t="n">
-        <v>1.751</v>
+        <v>1.753</v>
       </c>
     </row>
     <row r="125">
@@ -4034,20 +4034,20 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2.132</v>
+        <v>1.584</v>
       </c>
       <c r="E125" t="n">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="F125" t="n">
         <v>0.667</v>
       </c>
       <c r="G125" t="n">
-        <v>1.6</v>
+        <v>1.314</v>
       </c>
     </row>
     <row r="126">
@@ -4063,20 +4063,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1.581</v>
+        <v>0.195</v>
       </c>
       <c r="E126" t="n">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="F126" t="n">
         <v>0.667</v>
       </c>
       <c r="G126" t="n">
-        <v>1.312</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="127">
@@ -4092,20 +4092,20 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.191</v>
+        <v>-0.003</v>
       </c>
       <c r="E127" t="n">
-        <v>26.9</v>
+        <v>27.7</v>
       </c>
       <c r="F127" t="n">
         <v>0.667</v>
       </c>
       <c r="G127" t="n">
-        <v>0.481</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="128">
@@ -4121,20 +4121,20 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Kasparas Jakučionis</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-0.007</v>
+        <v>-0.199</v>
       </c>
       <c r="E128" t="n">
-        <v>27.7</v>
+        <v>19.9</v>
       </c>
       <c r="F128" t="n">
         <v>0.667</v>
       </c>
       <c r="G128" t="n">
-        <v>0.381</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="129">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.609</v>
+        <v>-0.606</v>
       </c>
       <c r="E129" t="n">
         <v>30.8</v>
@@ -4163,7 +4163,7 @@
         <v>0.667</v>
       </c>
       <c r="G129" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="130">
@@ -4183,16 +4183,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2.201</v>
+        <v>2.315</v>
       </c>
       <c r="E130" t="n">
-        <v>32.1</v>
+        <v>31.2</v>
       </c>
       <c r="F130" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>1.627</v>
+        <v>1.635</v>
       </c>
     </row>
     <row r="131">
@@ -4212,16 +4212,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.93</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E131" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="F131" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>0.552</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="132">
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.425</v>
+        <v>-0.05</v>
       </c>
       <c r="E132" t="n">
-        <v>18.2</v>
+        <v>19.9</v>
       </c>
       <c r="F132" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="G132" t="n">
-        <v>0.25</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Cole Anthony</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-1.366</v>
+        <v>-2.311</v>
       </c>
       <c r="E133" t="n">
-        <v>27.9</v>
+        <v>15.9</v>
       </c>
       <c r="F133" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.658</v>
+        <v>-0.698</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cole Anthony</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.314</v>
+        <v>-1.589</v>
       </c>
       <c r="E134" t="n">
-        <v>15.9</v>
+        <v>28.2</v>
       </c>
       <c r="F134" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.8159999999999999</v>
       </c>
     </row>
     <row r="135">
@@ -4324,20 +4324,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-2.4</v>
+        <v>-2.087</v>
       </c>
       <c r="E135" t="n">
-        <v>20.1</v>
+        <v>22.3</v>
       </c>
       <c r="F135" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.907</v>
+        <v>-0.878</v>
       </c>
     </row>
     <row r="136">
@@ -4353,20 +4353,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-2.297</v>
+        <v>-2.461</v>
       </c>
       <c r="E136" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="F136" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-1.007</v>
       </c>
     </row>
     <row r="137">
@@ -4386,16 +4386,16 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-3.594</v>
+        <v>-3.3</v>
       </c>
       <c r="E137" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="F137" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="G137" t="n">
-        <v>-1.378</v>
+        <v>-1.304</v>
       </c>
     </row>
     <row r="138">
@@ -4415,16 +4415,16 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2.355</v>
+        <v>2.151</v>
       </c>
       <c r="E138" t="n">
-        <v>30.2</v>
+        <v>31</v>
       </c>
       <c r="F138" t="n">
         <v>0.8</v>
       </c>
       <c r="G138" t="n">
-        <v>1.983</v>
+        <v>1.907</v>
       </c>
     </row>
     <row r="139">
@@ -4440,20 +4440,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2.104</v>
+        <v>2.212</v>
       </c>
       <c r="E139" t="n">
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="F139" t="n">
         <v>0.8</v>
       </c>
       <c r="G139" t="n">
-        <v>1.482</v>
+        <v>1.757</v>
       </c>
     </row>
     <row r="140">
@@ -4469,20 +4469,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.578</v>
+        <v>2.033</v>
       </c>
       <c r="E140" t="n">
-        <v>19.7</v>
+        <v>25</v>
       </c>
       <c r="F140" t="n">
         <v>0.8</v>
       </c>
       <c r="G140" t="n">
-        <v>1.386</v>
+        <v>1.474</v>
       </c>
     </row>
     <row r="141">
@@ -4498,20 +4498,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1.242</v>
+        <v>2.414</v>
       </c>
       <c r="E141" t="n">
-        <v>31.6</v>
+        <v>21.3</v>
       </c>
       <c r="F141" t="n">
         <v>0.8</v>
       </c>
       <c r="G141" t="n">
-        <v>1.345</v>
+        <v>1.429</v>
       </c>
     </row>
     <row r="142">
@@ -4527,20 +4527,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.951</v>
+        <v>1.256</v>
       </c>
       <c r="E142" t="n">
-        <v>28.8</v>
+        <v>30.9</v>
       </c>
       <c r="F142" t="n">
         <v>0.8</v>
       </c>
       <c r="G142" t="n">
-        <v>1.051</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="143">
@@ -4556,20 +4556,20 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.904</v>
       </c>
       <c r="E143" t="n">
-        <v>16.9</v>
+        <v>29.8</v>
       </c>
       <c r="F143" t="n">
         <v>0.8</v>
       </c>
       <c r="G143" t="n">
-        <v>0.523</v>
+        <v>1.058</v>
       </c>
     </row>
     <row r="144">
@@ -4585,20 +4585,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Mike Conley</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>-1.654</v>
+        <v>-0.032</v>
       </c>
       <c r="E144" t="n">
-        <v>16.1</v>
+        <v>28.9</v>
       </c>
       <c r="F144" t="n">
         <v>0.8</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.286</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="145">
@@ -4614,20 +4614,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Johnny Juzang</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-4.685</v>
+        <v>0.401</v>
       </c>
       <c r="E145" t="n">
-        <v>15.2</v>
+        <v>18.5</v>
       </c>
       <c r="F145" t="n">
         <v>0.8</v>
       </c>
       <c r="G145" t="n">
-        <v>-1.233</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="146">
@@ -4647,16 +4647,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3.863</v>
+        <v>3.866</v>
       </c>
       <c r="E146" t="n">
         <v>35.3</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G146" t="n">
-        <v>3.06</v>
+        <v>3.086</v>
       </c>
     </row>
     <row r="147">
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4.183</v>
+        <v>4.187</v>
       </c>
       <c r="E147" t="n">
         <v>30.9</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G147" t="n">
-        <v>2.89</v>
+        <v>2.914</v>
       </c>
     </row>
     <row r="148">
@@ -4705,16 +4705,16 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2.992</v>
+        <v>2.994</v>
       </c>
       <c r="E148" t="n">
         <v>30.2</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G148" t="n">
-        <v>2.074</v>
+        <v>2.096</v>
       </c>
     </row>
     <row r="149">
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1.704</v>
+        <v>1.707</v>
       </c>
       <c r="E149" t="n">
         <v>32.2</v>
       </c>
       <c r="F149" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G149" t="n">
-        <v>1.343</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="150">
@@ -4763,16 +4763,16 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.414</v>
+        <v>0.417</v>
       </c>
       <c r="E150" t="n">
         <v>20.7</v>
       </c>
       <c r="F150" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G150" t="n">
-        <v>0.308</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="151">
@@ -4792,16 +4792,16 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-0.772</v>
+        <v>-0.768</v>
       </c>
       <c r="E151" t="n">
         <v>20.7</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.203</v>
+        <v>-0.187</v>
       </c>
     </row>
     <row r="152">
@@ -4821,16 +4821,16 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-1.911</v>
+        <v>-1.907</v>
       </c>
       <c r="E152" t="n">
         <v>20.1</v>
       </c>
       <c r="F152" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.674</v>
+        <v>-0.658</v>
       </c>
     </row>
     <row r="153">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-2.215</v>
+        <v>-2.211</v>
       </c>
       <c r="E153" t="n">
         <v>29.9</v>
       </c>
       <c r="F153" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.194</v>
+        <v>-1.171</v>
       </c>
     </row>
     <row r="154">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3.997</v>
+        <v>4.001</v>
       </c>
       <c r="E154" t="n">
         <v>36.6</v>
@@ -4888,7 +4888,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G154" t="n">
-        <v>3.755</v>
+        <v>3.758</v>
       </c>
     </row>
     <row r="155">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3.398</v>
+        <v>3.401</v>
       </c>
       <c r="E155" t="n">
         <v>30</v>
@@ -4917,7 +4917,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G155" t="n">
-        <v>2.71</v>
+        <v>2.712</v>
       </c>
     </row>
     <row r="156">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2.652</v>
+        <v>2.656</v>
       </c>
       <c r="E156" t="n">
         <v>29.1</v>
@@ -4946,7 +4946,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>2.174</v>
+        <v>2.176</v>
       </c>
     </row>
     <row r="157">
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3.899</v>
+        <v>3.902</v>
       </c>
       <c r="E157" t="n">
         <v>20.1</v>
@@ -4975,7 +4975,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G157" t="n">
-        <v>2.027</v>
+        <v>2.029</v>
       </c>
     </row>
     <row r="158">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2.272</v>
+        <v>2.276</v>
       </c>
       <c r="E158" t="n">
         <v>29.2</v>
@@ -5004,7 +5004,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G158" t="n">
-        <v>1.952</v>
+        <v>1.954</v>
       </c>
     </row>
     <row r="159">
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1.745</v>
+        <v>1.749</v>
       </c>
       <c r="E159" t="n">
         <v>33.5</v>
@@ -5033,7 +5033,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G159" t="n">
-        <v>1.868</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="160">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-2.635</v>
+        <v>-2.632</v>
       </c>
       <c r="E160" t="n">
         <v>17.3</v>
@@ -5062,7 +5062,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.613</v>
+        <v>-0.612</v>
       </c>
     </row>
     <row r="161">
@@ -5091,7 +5091,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G161" t="n">
-        <v>-1.303</v>
+        <v>-1.302</v>
       </c>
     </row>
     <row r="162">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>12.48</v>
+        <v>12.484</v>
       </c>
       <c r="E162" t="n">
         <v>34.1</v>
@@ -5120,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>9.57</v>
+        <v>9.571999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4.181</v>
+        <v>4.184</v>
       </c>
       <c r="E163" t="n">
         <v>29.6</v>
@@ -5149,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>3.193</v>
+        <v>3.195</v>
       </c>
     </row>
     <row r="164">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>3.997</v>
+        <v>4</v>
       </c>
       <c r="E164" t="n">
         <v>22.4</v>
@@ -5178,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>2.334</v>
+        <v>2.335</v>
       </c>
     </row>
     <row r="165">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2.075</v>
+        <v>2.078</v>
       </c>
       <c r="E165" t="n">
         <v>27</v>
@@ -5207,7 +5207,7 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>1.729</v>
+        <v>1.731</v>
       </c>
     </row>
     <row r="166">
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1.874</v>
+        <v>1.878</v>
       </c>
       <c r="E166" t="n">
         <v>25.7</v>
@@ -5236,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1.537</v>
+        <v>1.539</v>
       </c>
     </row>
     <row r="167">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.804</v>
+        <v>1.807</v>
       </c>
       <c r="E167" t="n">
         <v>23.1</v>
@@ -5265,7 +5265,7 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1.35</v>
+        <v>1.351</v>
       </c>
     </row>
     <row r="168">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="E168" t="n">
         <v>24.5</v>
@@ -5294,7 +5294,7 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.544</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="169">
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-4.122</v>
+        <v>-4.118</v>
       </c>
       <c r="E169" t="n">
         <v>25.5</v>
@@ -5323,7 +5323,7 @@
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>-1.656</v>
+        <v>-1.655</v>
       </c>
     </row>
     <row r="170">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3.209</v>
+        <v>3.213</v>
       </c>
       <c r="E170" t="n">
         <v>30.2</v>
@@ -5352,7 +5352,7 @@
         <v>0.467</v>
       </c>
       <c r="G170" t="n">
-        <v>2.311</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="171">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1.987</v>
+        <v>1.99</v>
       </c>
       <c r="E171" t="n">
         <v>35.6</v>
@@ -5381,7 +5381,7 @@
         <v>0.467</v>
       </c>
       <c r="G171" t="n">
-        <v>1.822</v>
+        <v>1.824</v>
       </c>
     </row>
     <row r="172">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1.63</v>
+        <v>1.633</v>
       </c>
       <c r="E172" t="n">
         <v>34.3</v>
@@ -5410,7 +5410,7 @@
         <v>0.467</v>
       </c>
       <c r="G172" t="n">
-        <v>1.499</v>
+        <v>1.501</v>
       </c>
     </row>
     <row r="173">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-0.281</v>
+        <v>-0.278</v>
       </c>
       <c r="E173" t="n">
         <v>29.4</v>
@@ -5439,7 +5439,7 @@
         <v>0.467</v>
       </c>
       <c r="G173" t="n">
-        <v>0.114</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="174">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-0.271</v>
+        <v>-0.268</v>
       </c>
       <c r="E174" t="n">
         <v>21</v>
@@ -5468,7 +5468,7 @@
         <v>0.467</v>
       </c>
       <c r="G174" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="175">
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-0.542</v>
+        <v>-0.539</v>
       </c>
       <c r="E175" t="n">
         <v>30.7</v>
@@ -5497,7 +5497,7 @@
         <v>0.467</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.048</v>
+        <v>-0.046</v>
       </c>
     </row>
     <row r="176">
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-1.539</v>
+        <v>-1.538</v>
       </c>
       <c r="E176" t="n">
         <v>19.5</v>
@@ -5571,20 +5571,20 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5.02</v>
+        <v>6.681</v>
       </c>
       <c r="E178" t="n">
-        <v>34.7</v>
+        <v>35.8</v>
       </c>
       <c r="F178" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G178" t="n">
-        <v>3.921</v>
+        <v>5.309</v>
       </c>
     </row>
     <row r="179">
@@ -5600,20 +5600,20 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1.69</v>
+        <v>5.449</v>
       </c>
       <c r="E179" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="F179" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G179" t="n">
-        <v>1.414</v>
+        <v>4.042</v>
       </c>
     </row>
     <row r="180">
@@ -5629,20 +5629,20 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Eric Gordon</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>-0.08699999999999999</v>
+        <v>2.366</v>
       </c>
       <c r="E180" t="n">
-        <v>22.6</v>
+        <v>31.9</v>
       </c>
       <c r="F180" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G180" t="n">
-        <v>0.148</v>
+        <v>1.859</v>
       </c>
     </row>
     <row r="181">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Justin Edwards</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-0.191</v>
+        <v>-0.152</v>
       </c>
       <c r="E181" t="n">
-        <v>24.3</v>
+        <v>32.3</v>
       </c>
       <c r="F181" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G181" t="n">
-        <v>0.106</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="182">
@@ -5687,20 +5687,20 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Justin Edwards</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-0.365</v>
+        <v>-0.132</v>
       </c>
       <c r="E182" t="n">
-        <v>33.4</v>
+        <v>24.2</v>
       </c>
       <c r="F182" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G182" t="n">
-        <v>0.025</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="183">
@@ -5720,16 +5720,16 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-0.795</v>
+        <v>-0.676</v>
       </c>
       <c r="E183" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="F183" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.201</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="184">
@@ -5749,16 +5749,16 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.646</v>
       </c>
       <c r="E184" t="n">
         <v>34.3</v>
       </c>
       <c r="F184" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.291</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="185">
@@ -5774,20 +5774,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Adem Bona</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>-1.473</v>
+        <v>-0.858</v>
       </c>
       <c r="E185" t="n">
-        <v>23.3</v>
+        <v>31.4</v>
       </c>
       <c r="F185" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.521</v>
+        <v>-0.278</v>
       </c>
     </row>
     <row r="186">
@@ -5807,16 +5807,16 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3.457</v>
+        <v>3.392</v>
       </c>
       <c r="E186" t="n">
-        <v>30.2</v>
+        <v>29.7</v>
       </c>
       <c r="F186" t="n">
         <v>0.533</v>
       </c>
       <c r="G186" t="n">
-        <v>2.513</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="187">
@@ -5836,16 +5836,16 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2.425</v>
+        <v>2.454</v>
       </c>
       <c r="E187" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="F187" t="n">
         <v>0.533</v>
       </c>
       <c r="G187" t="n">
-        <v>2.133</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="188">
@@ -5865,16 +5865,16 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="E188" t="n">
-        <v>28.5</v>
+        <v>27.6</v>
       </c>
       <c r="F188" t="n">
         <v>0.533</v>
       </c>
       <c r="G188" t="n">
-        <v>2.053</v>
+        <v>2.072</v>
       </c>
     </row>
     <row r="189">
@@ -5894,16 +5894,16 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1.175</v>
+        <v>1.12</v>
       </c>
       <c r="E189" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="F189" t="n">
         <v>0.533</v>
       </c>
       <c r="G189" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="190">
@@ -5923,16 +5923,16 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.075</v>
+        <v>0.339</v>
       </c>
       <c r="E190" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="F190" t="n">
         <v>0.533</v>
       </c>
       <c r="G190" t="n">
-        <v>0.348</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="191">
@@ -5952,16 +5952,16 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.03</v>
+        <v>0.053</v>
       </c>
       <c r="E191" t="n">
-        <v>28.3</v>
+        <v>29</v>
       </c>
       <c r="F191" t="n">
         <v>0.533</v>
       </c>
       <c r="G191" t="n">
-        <v>0.332</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="192">
@@ -5977,20 +5977,20 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Rasheer Fleming</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-1.408</v>
+        <v>-1.491</v>
       </c>
       <c r="E192" t="n">
-        <v>19.8</v>
+        <v>32.1</v>
       </c>
       <c r="F192" t="n">
         <v>0.533</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.36</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="193">
@@ -6006,20 +6006,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Rasheer Fleming</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>-1.823</v>
+        <v>-2.056</v>
       </c>
       <c r="E193" t="n">
-        <v>32.3</v>
+        <v>20.6</v>
       </c>
       <c r="F193" t="n">
         <v>0.533</v>
       </c>
       <c r="G193" t="n">
-        <v>-0.868</v>
+        <v>-0.655</v>
       </c>
     </row>
     <row r="194">
@@ -6035,20 +6035,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3.786</v>
+        <v>6.714</v>
       </c>
       <c r="E194" t="n">
-        <v>30.9</v>
+        <v>19.6</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>2.678</v>
+        <v>2.887</v>
       </c>
     </row>
     <row r="195">
@@ -6064,20 +6064,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3.746</v>
+        <v>3.79</v>
       </c>
       <c r="E195" t="n">
-        <v>26.8</v>
+        <v>30.9</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>2.296</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="196">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2.657</v>
+        <v>3.749</v>
       </c>
       <c r="E196" t="n">
-        <v>28.7</v>
+        <v>26.8</v>
       </c>
       <c r="F196" t="n">
         <v>0.367</v>
       </c>
       <c r="G196" t="n">
-        <v>1.807</v>
+        <v>2.298</v>
       </c>
     </row>
     <row r="197">
@@ -6122,20 +6122,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.095</v>
+        <v>2.661</v>
       </c>
       <c r="E197" t="n">
-        <v>31.8</v>
+        <v>28.7</v>
       </c>
       <c r="F197" t="n">
         <v>0.367</v>
       </c>
       <c r="G197" t="n">
-        <v>0.306</v>
+        <v>1.809</v>
       </c>
     </row>
     <row r="198">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-0.379</v>
+        <v>-0.375</v>
       </c>
       <c r="E198" t="n">
         <v>19.8</v>
@@ -6164,7 +6164,7 @@
         <v>0.367</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
     </row>
     <row r="199">
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-1.6</v>
+        <v>-1.597</v>
       </c>
       <c r="E199" t="n">
         <v>24.6</v>
@@ -6193,7 +6193,7 @@
         <v>0.367</v>
       </c>
       <c r="G199" t="n">
-        <v>-0.631</v>
+        <v>-0.629</v>
       </c>
     </row>
     <row r="200">
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-2.24</v>
+        <v>-2.237</v>
       </c>
       <c r="E200" t="n">
         <v>23.3</v>
@@ -6222,7 +6222,7 @@
         <v>0.367</v>
       </c>
       <c r="G200" t="n">
-        <v>-0.911</v>
+        <v>-0.909</v>
       </c>
     </row>
     <row r="201">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-1.842</v>
+        <v>-1.839</v>
       </c>
       <c r="E201" t="n">
         <v>29.6</v>
@@ -6251,7 +6251,7 @@
         <v>0.367</v>
       </c>
       <c r="G201" t="n">
-        <v>-0.911</v>
+        <v>-0.909</v>
       </c>
     </row>
     <row r="202">
@@ -6271,16 +6271,16 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1.263</v>
+        <v>1.394</v>
       </c>
       <c r="E202" t="n">
-        <v>30.1</v>
+        <v>30.6</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>0.855</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="203">
@@ -6300,16 +6300,16 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.604</v>
+        <v>0.673</v>
       </c>
       <c r="E203" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.484</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="204">
@@ -6325,20 +6325,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.711</v>
+        <v>0.464</v>
       </c>
       <c r="E204" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.374</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="205">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-0.15</v>
+        <v>-0.147</v>
       </c>
       <c r="E205" t="n">
         <v>23.3</v>
@@ -6367,7 +6367,7 @@
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.025</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="206">
@@ -6387,16 +6387,16 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-0.913</v>
+        <v>-0.894</v>
       </c>
       <c r="E206" t="n">
-        <v>32.5</v>
+        <v>33.7</v>
       </c>
       <c r="F206" t="n">
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.55</v>
+        <v>-0.5570000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-2.965</v>
+        <v>-2.443</v>
       </c>
       <c r="E207" t="n">
-        <v>29.2</v>
+        <v>30.6</v>
       </c>
       <c r="F207" t="n">
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-1.743</v>
+        <v>-1.494</v>
       </c>
     </row>
     <row r="208">
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>-3.854</v>
+        <v>-4.314</v>
       </c>
       <c r="E208" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="F208" t="n">
         <v>0.1</v>
       </c>
       <c r="G208" t="n">
-        <v>-2.029</v>
+        <v>-2.194</v>
       </c>
     </row>
     <row r="209">
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-3.708</v>
+        <v>-3.585</v>
       </c>
       <c r="E209" t="n">
-        <v>35</v>
+        <v>33.7</v>
       </c>
       <c r="F209" t="n">
         <v>0.1</v>
       </c>
       <c r="G209" t="n">
-        <v>-2.628</v>
+        <v>-2.447</v>
       </c>
     </row>
     <row r="210">
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>10.127</v>
+        <v>10.303</v>
       </c>
       <c r="E210" t="n">
-        <v>30.2</v>
+        <v>29</v>
       </c>
       <c r="F210" t="n">
         <v>0.967</v>
       </c>
       <c r="G210" t="n">
-        <v>6.974</v>
+        <v>6.806</v>
       </c>
     </row>
     <row r="211">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>2.92</v>
+        <v>2.813</v>
       </c>
       <c r="E211" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F211" t="n">
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>2.513</v>
+        <v>2.416</v>
       </c>
     </row>
     <row r="212">
@@ -6561,16 +6561,16 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1.904</v>
+        <v>1.889</v>
       </c>
       <c r="E212" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="F212" t="n">
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>1.766</v>
+        <v>1.785</v>
       </c>
     </row>
     <row r="213">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1.249</v>
+        <v>1.369</v>
       </c>
       <c r="E213" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="F213" t="n">
         <v>0.967</v>
       </c>
       <c r="G213" t="n">
-        <v>1.09</v>
+        <v>1.155</v>
       </c>
     </row>
     <row r="214">
@@ -6619,16 +6619,16 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1.258</v>
+        <v>1.205</v>
       </c>
       <c r="E214" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="F214" t="n">
         <v>0.967</v>
       </c>
       <c r="G214" t="n">
-        <v>1.039</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="215">
@@ -6648,16 +6648,16 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.493</v>
+        <v>0.555</v>
       </c>
       <c r="E215" t="n">
-        <v>27.6</v>
+        <v>27.2</v>
       </c>
       <c r="F215" t="n">
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>0.839</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="216">
@@ -6677,16 +6677,16 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.032</v>
+        <v>0.302</v>
       </c>
       <c r="E216" t="n">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
       <c r="F216" t="n">
         <v>0.967</v>
       </c>
       <c r="G216" t="n">
-        <v>0.634</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="217">
@@ -6706,16 +6706,16 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>-0.579</v>
+        <v>-0.5</v>
       </c>
       <c r="E217" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="F217" t="n">
         <v>0.967</v>
       </c>
       <c r="G217" t="n">
-        <v>0.169</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="218">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4.162</v>
+        <v>4.165</v>
       </c>
       <c r="E218" t="n">
         <v>32.2</v>
@@ -6744,7 +6744,7 @@
         <v>0.5</v>
       </c>
       <c r="G218" t="n">
-        <v>3.128</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="219">
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>3.506</v>
+        <v>3.51</v>
       </c>
       <c r="E219" t="n">
         <v>20.1</v>
@@ -6773,7 +6773,7 @@
         <v>0.5</v>
       </c>
       <c r="G219" t="n">
-        <v>1.678</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="220">
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1.967</v>
+        <v>1.971</v>
       </c>
       <c r="E220" t="n">
         <v>27.1</v>
@@ -6802,7 +6802,7 @@
         <v>0.5</v>
       </c>
       <c r="G220" t="n">
-        <v>1.391</v>
+        <v>1.393</v>
       </c>
     </row>
     <row r="221">
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.405</v>
+        <v>1.408</v>
       </c>
       <c r="E221" t="n">
         <v>30.9</v>
@@ -6831,7 +6831,7 @@
         <v>0.5</v>
       </c>
       <c r="G221" t="n">
-        <v>1.226</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="222">
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.862</v>
+        <v>0.865</v>
       </c>
       <c r="E222" t="n">
         <v>34</v>
@@ -6860,7 +6860,7 @@
         <v>0.5</v>
       </c>
       <c r="G222" t="n">
-        <v>0.964</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="223">
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1.388</v>
+        <v>1.392</v>
       </c>
       <c r="E223" t="n">
         <v>23</v>
@@ -6889,7 +6889,7 @@
         <v>0.5</v>
       </c>
       <c r="G223" t="n">
-        <v>0.904</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="224">
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.35</v>
+        <v>-0.347</v>
       </c>
       <c r="E224" t="n">
         <v>20.7</v>
@@ -6918,7 +6918,7 @@
         <v>0.5</v>
       </c>
       <c r="G224" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="225">
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-1.282</v>
+        <v>-1.279</v>
       </c>
       <c r="E225" t="n">
         <v>22.3</v>
@@ -6947,7 +6947,7 @@
         <v>0.5</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.364</v>
+        <v>-0.362</v>
       </c>
     </row>
     <row r="226">
@@ -6963,20 +6963,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1.515</v>
+        <v>1.555</v>
       </c>
       <c r="E226" t="n">
-        <v>22.1</v>
+        <v>26.7</v>
       </c>
       <c r="F226" t="n">
         <v>0.167</v>
       </c>
       <c r="G226" t="n">
-        <v>0.772</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="227">
@@ -6992,20 +6992,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1.221</v>
+        <v>1.518</v>
       </c>
       <c r="E227" t="n">
-        <v>25.2</v>
+        <v>22.1</v>
       </c>
       <c r="F227" t="n">
         <v>0.167</v>
       </c>
       <c r="G227" t="n">
-        <v>0.73</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="228">
@@ -7025,16 +7025,16 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.713</v>
       </c>
       <c r="E228" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="F228" t="n">
         <v>0.167</v>
       </c>
       <c r="G228" t="n">
-        <v>0.395</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="229">
@@ -7054,16 +7054,16 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-0.506</v>
+        <v>-0.377</v>
       </c>
       <c r="E229" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="F229" t="n">
         <v>0.167</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.187</v>
+        <v>-0.117</v>
       </c>
     </row>
     <row r="230">
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-1.064</v>
+        <v>-1.06</v>
       </c>
       <c r="E230" t="n">
         <v>20.2</v>
@@ -7092,7 +7092,7 @@
         <v>0.167</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.378</v>
+        <v>-0.376</v>
       </c>
     </row>
     <row r="231">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-1.465</v>
+        <v>-1.558</v>
       </c>
       <c r="E231" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="F231" t="n">
         <v>0.167</v>
       </c>
       <c r="G231" t="n">
-        <v>-0.79</v>
+        <v>-0.838</v>
       </c>
     </row>
     <row r="232">
@@ -7141,16 +7141,16 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>-1.979</v>
+        <v>-2.354</v>
       </c>
       <c r="E232" t="n">
-        <v>28.2</v>
+        <v>30.7</v>
       </c>
       <c r="F232" t="n">
         <v>0.167</v>
       </c>
       <c r="G232" t="n">
-        <v>-1.064</v>
+        <v>-1.399</v>
       </c>
     </row>
     <row r="233">
@@ -7170,16 +7170,16 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-3.391</v>
+        <v>-3.081</v>
       </c>
       <c r="E233" t="n">
-        <v>35.3</v>
+        <v>34.7</v>
       </c>
       <c r="F233" t="n">
         <v>0.167</v>
       </c>
       <c r="G233" t="n">
-        <v>-2.371</v>
+        <v>-2.108</v>
       </c>
     </row>
     <row r="234">
@@ -7195,20 +7195,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3.237</v>
+        <v>0.393</v>
       </c>
       <c r="E234" t="n">
-        <v>22.3</v>
+        <v>31.3</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>1.516</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="235">
@@ -7224,20 +7224,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.39</v>
+        <v>-0.26</v>
       </c>
       <c r="E235" t="n">
-        <v>31.3</v>
+        <v>29.2</v>
       </c>
       <c r="F235" t="n">
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>0.276</v>
+        <v>-0.138</v>
       </c>
     </row>
     <row r="236">
@@ -7253,20 +7253,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.264</v>
+        <v>-0.901</v>
       </c>
       <c r="E236" t="n">
-        <v>29.2</v>
+        <v>21.6</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.14</v>
+        <v>-0.389</v>
       </c>
     </row>
     <row r="237">
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-1.229</v>
+        <v>-1.226</v>
       </c>
       <c r="E237" t="n">
         <v>22.6</v>
@@ -7295,7 +7295,7 @@
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5620000000000001</v>
       </c>
     </row>
     <row r="238">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-2.279</v>
+        <v>-2.275</v>
       </c>
       <c r="E238" t="n">
         <v>24.3</v>
@@ -7324,7 +7324,7 @@
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-1.135</v>
+        <v>-1.133</v>
       </c>
     </row>
     <row r="239">
@@ -7340,20 +7340,20 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Tre Johnson</t>
+          <t>Jaden Hardy</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-2.704</v>
+        <v>-3.045</v>
       </c>
       <c r="E239" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="F239" t="n">
         <v>0.033</v>
       </c>
       <c r="G239" t="n">
-        <v>-1.277</v>
+        <v>-1.346</v>
       </c>
     </row>
     <row r="240">
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-2.646</v>
+        <v>-2.642</v>
       </c>
       <c r="E240" t="n">
         <v>28.4</v>
@@ -7382,7 +7382,7 @@
         <v>0.033</v>
       </c>
       <c r="G240" t="n">
-        <v>-1.546</v>
+        <v>-1.544</v>
       </c>
     </row>
     <row r="241">
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>-2.407</v>
+        <v>-2.404</v>
       </c>
       <c r="E241" t="n">
         <v>32.3</v>
@@ -7411,7 +7411,7 @@
         <v>0.033</v>
       </c>
       <c r="G241" t="n">
-        <v>-1.597</v>
+        <v>-1.595</v>
       </c>
     </row>
   </sheetData>
@@ -7483,10 +7483,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>20.715</v>
+        <v>20.732</v>
       </c>
       <c r="F2" t="n">
-        <v>2.735</v>
+        <v>2.738</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7512,10 +7512,10 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>20.606</v>
+        <v>20.623</v>
       </c>
       <c r="F3" t="n">
-        <v>3.086</v>
+        <v>3.09</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>20.249</v>
+        <v>20.265</v>
       </c>
       <c r="F4" t="n">
-        <v>2.858</v>
+        <v>2.861</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7570,10 +7570,10 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>18.601</v>
+        <v>18.614</v>
       </c>
       <c r="F5" t="n">
-        <v>2.794</v>
+        <v>2.798</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -7599,10 +7599,10 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>15.876</v>
+        <v>15.891</v>
       </c>
       <c r="F6" t="n">
-        <v>2.401</v>
+        <v>2.404</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7628,10 +7628,10 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>15.246</v>
+        <v>15.098</v>
       </c>
       <c r="F7" t="n">
-        <v>1.975</v>
+        <v>1.978</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -7657,10 +7657,10 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>15.024</v>
+        <v>15.062</v>
       </c>
       <c r="F8" t="n">
-        <v>2.176</v>
+        <v>2.242</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -7686,10 +7686,10 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>13.619</v>
+        <v>14.762</v>
       </c>
       <c r="F9" t="n">
-        <v>2.262</v>
+        <v>2.39</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -7715,10 +7715,10 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>12.57</v>
+        <v>12.585</v>
       </c>
       <c r="F10" t="n">
-        <v>1.367</v>
+        <v>1.37</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -7732,26 +7732,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>10.334</v>
+        <v>10.998</v>
       </c>
       <c r="F11" t="n">
-        <v>1.455</v>
+        <v>1.504</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>9.052</v>
+        <v>9.872999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.133</v>
+        <v>1.417</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>8.992000000000001</v>
+        <v>9.459</v>
       </c>
       <c r="F13" t="n">
-        <v>1.457</v>
+        <v>1.16</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7819,26 +7819,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>8.898999999999999</v>
+        <v>9.007</v>
       </c>
       <c r="F14" t="n">
-        <v>0.677</v>
+        <v>1.461</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7848,26 +7848,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>7.604</v>
+        <v>8.944000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.032</v>
+        <v>1.167</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
     </row>
@@ -7877,26 +7877,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>6.991</v>
+        <v>8.917</v>
       </c>
       <c r="F16" t="n">
-        <v>0.856</v>
+        <v>0.68</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7918,10 +7918,10 @@
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>6.779</v>
+        <v>8.135999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.644</v>
+        <v>0.956</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -7935,26 +7935,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6.251</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.448</v>
+        <v>1.284</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
     </row>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>5.817</v>
+        <v>7.772</v>
       </c>
       <c r="F19" t="n">
-        <v>1.005</v>
+        <v>1.036</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>4.684</v>
+        <v>7.223</v>
       </c>
       <c r="F20" t="n">
-        <v>0.386</v>
+        <v>1.358</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
     </row>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>4.629</v>
+        <v>7.02</v>
       </c>
       <c r="F21" t="n">
-        <v>0.528</v>
+        <v>0.86</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
     </row>
@@ -8051,26 +8051,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.601</v>
+        <v>5.685</v>
       </c>
       <c r="F22" t="n">
-        <v>0.374</v>
+        <v>1.008</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -8092,10 +8092,10 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4.079</v>
+        <v>4.091</v>
       </c>
       <c r="F23" t="n">
-        <v>0.115</v>
+        <v>0.118</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -8109,26 +8109,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>2.241</v>
+        <v>0.13</v>
       </c>
       <c r="F24" t="n">
-        <v>0.329</v>
+        <v>-0.199</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
     </row>
@@ -8138,26 +8138,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.026</v>
+        <v>-1.943</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.202</v>
+        <v>-0.666</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Javon Small</t>
         </is>
       </c>
     </row>
@@ -8179,10 +8179,10 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.136</v>
+        <v>-2.522</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.052</v>
+        <v>-1.084</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.721</v>
+        <v>-2.623</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.763</v>
+        <v>-0.58</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>John Konchar</t>
         </is>
       </c>
     </row>
@@ -8225,26 +8225,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.893</v>
+        <v>-2.705</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.639</v>
+        <v>-0.759</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
     </row>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.467</v>
+        <v>-4.965</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.988</v>
+        <v>-1.106</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
     </row>
@@ -8283,26 +8283,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.262</v>
+        <v>-6.429</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.126</v>
+        <v>-1.545</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
     </row>
@@ -8324,10 +8324,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-9.077</v>
+        <v>-9.064</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.452</v>
+        <v>-2.449</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -496,20 +496,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.872</v>
+        <v>2.258</v>
       </c>
       <c r="E3" t="n">
-        <v>23.4</v>
+        <v>33.3</v>
       </c>
       <c r="F3" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.657</v>
+        <v>1.962</v>
       </c>
     </row>
     <row r="4">
@@ -525,20 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.258</v>
+        <v>2.263</v>
       </c>
       <c r="E4" t="n">
-        <v>33.3</v>
+        <v>27.9</v>
       </c>
       <c r="F4" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.962</v>
+        <v>1.644</v>
       </c>
     </row>
     <row r="5">
@@ -554,20 +554,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.263</v>
+        <v>1.682</v>
       </c>
       <c r="E5" t="n">
-        <v>27.9</v>
+        <v>32.6</v>
       </c>
       <c r="F5" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.644</v>
+        <v>1.526</v>
       </c>
     </row>
     <row r="6">
@@ -583,20 +583,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.682</v>
+        <v>1.322</v>
       </c>
       <c r="E6" t="n">
-        <v>32.6</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.526</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="7">
@@ -612,20 +612,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jock Landale</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.322</v>
+        <v>1.296</v>
       </c>
       <c r="E7" t="n">
-        <v>29</v>
+        <v>18.2</v>
       </c>
       <c r="F7" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.14</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="8">
@@ -641,20 +641,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.772</v>
+        <v>-1.195</v>
       </c>
       <c r="E8" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="F8" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.985</v>
+        <v>-0.271</v>
       </c>
     </row>
     <row r="9">
@@ -670,20 +670,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.195</v>
+        <v>-1.285</v>
       </c>
       <c r="E9" t="n">
-        <v>20.7</v>
+        <v>18.6</v>
       </c>
       <c r="F9" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.271</v>
+        <v>-0.278</v>
       </c>
     </row>
     <row r="10">
@@ -699,20 +699,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.108</v>
+        <v>3.854</v>
       </c>
       <c r="E10" t="n">
-        <v>33.9</v>
+        <v>35.5</v>
       </c>
       <c r="F10" t="n">
         <v>0.867</v>
       </c>
       <c r="G10" t="n">
-        <v>3.51</v>
+        <v>3.488</v>
       </c>
     </row>
     <row r="11">
@@ -728,20 +728,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.854</v>
+        <v>3.57</v>
       </c>
       <c r="E11" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="F11" t="n">
         <v>0.867</v>
       </c>
       <c r="G11" t="n">
-        <v>3.488</v>
+        <v>3.114</v>
       </c>
     </row>
     <row r="12">
@@ -757,20 +757,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3.57</v>
+        <v>2.121</v>
       </c>
       <c r="E12" t="n">
-        <v>33.7</v>
+        <v>32.1</v>
       </c>
       <c r="F12" t="n">
         <v>0.867</v>
       </c>
       <c r="G12" t="n">
-        <v>3.114</v>
+        <v>2.001</v>
       </c>
     </row>
     <row r="13">
@@ -786,20 +786,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.121</v>
+        <v>2.586</v>
       </c>
       <c r="E13" t="n">
-        <v>32.1</v>
+        <v>27.5</v>
       </c>
       <c r="F13" t="n">
         <v>0.867</v>
       </c>
       <c r="G13" t="n">
-        <v>2.001</v>
+        <v>1.975</v>
       </c>
     </row>
     <row r="14">
@@ -815,20 +815,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Luka Garza</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.586</v>
+        <v>2.679</v>
       </c>
       <c r="E14" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="F14" t="n">
         <v>0.867</v>
       </c>
       <c r="G14" t="n">
-        <v>1.975</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="15">
@@ -960,20 +960,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ziaire Williams</t>
+          <t>Josh Minott</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.293</v>
+        <v>2.579</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>19.9</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.108</v>
+        <v>1.096</v>
       </c>
     </row>
     <row r="20">
@@ -989,20 +989,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Ziaire Williams</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.871</v>
+        <v>-0.293</v>
       </c>
       <c r="E20" t="n">
-        <v>22.1</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.829</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2.019</v>
+        <v>-1.871</v>
       </c>
       <c r="E21" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.885</v>
+        <v>-0.829</v>
       </c>
     </row>
     <row r="22">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-3.113</v>
+        <v>-2.019</v>
       </c>
       <c r="E22" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.424</v>
+        <v>-0.885</v>
       </c>
     </row>
     <row r="23">
@@ -1366,20 +1366,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KJ Simpson</t>
+          <t>Sion James</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-3.94</v>
+        <v>-3.143</v>
       </c>
       <c r="E33" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="F33" t="n">
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.409</v>
+        <v>-0.954</v>
       </c>
     </row>
     <row r="34">
@@ -1453,20 +1453,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.751</v>
+        <v>2.073</v>
       </c>
       <c r="E36" t="n">
-        <v>27.1</v>
+        <v>25</v>
       </c>
       <c r="F36" t="n">
         <v>0.3</v>
       </c>
       <c r="G36" t="n">
-        <v>1.721</v>
+        <v>1.234</v>
       </c>
     </row>
     <row r="37">
@@ -1482,20 +1482,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2.073</v>
+        <v>1.068</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F37" t="n">
         <v>0.3</v>
       </c>
       <c r="G37" t="n">
-        <v>1.234</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="38">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Leonard Miller</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.068</v>
+        <v>-0.644</v>
       </c>
       <c r="E38" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
         <v>0.3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.969</v>
+        <v>-0.179</v>
       </c>
     </row>
     <row r="39">
@@ -1540,20 +1540,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Guerschon Yabusele</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-0.067</v>
+        <v>-1.419</v>
       </c>
       <c r="E39" t="n">
-        <v>30.9</v>
+        <v>23.8</v>
       </c>
       <c r="F39" t="n">
         <v>0.3</v>
       </c>
       <c r="G39" t="n">
-        <v>0.151</v>
+        <v>-0.556</v>
       </c>
     </row>
     <row r="40">
@@ -1569,20 +1569,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Leonard Miller</t>
+          <t>Isaac Okoro</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-0.644</v>
+        <v>-2.789</v>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>30.9</v>
       </c>
       <c r="F40" t="n">
         <v>0.3</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.179</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="41">
@@ -1598,20 +1598,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-2.789</v>
+        <v>-5.247</v>
       </c>
       <c r="E41" t="n">
-        <v>30.9</v>
+        <v>21.9</v>
       </c>
       <c r="F41" t="n">
         <v>0.3</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.6</v>
+        <v>-2.252</v>
       </c>
     </row>
     <row r="42">
@@ -1801,20 +1801,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.839</v>
+        <v>-0.215</v>
       </c>
       <c r="E48" t="n">
-        <v>31.7</v>
+        <v>26.9</v>
       </c>
       <c r="F48" t="n">
         <v>0.767</v>
       </c>
       <c r="G48" t="n">
-        <v>1.06</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="49">
@@ -1830,20 +1830,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Keon Ellis</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.215</v>
+        <v>-0.917</v>
       </c>
       <c r="E49" t="n">
-        <v>26.9</v>
+        <v>19.2</v>
       </c>
       <c r="F49" t="n">
         <v>0.767</v>
       </c>
       <c r="G49" t="n">
-        <v>0.309</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="50">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-1.59</v>
+        <v>-2.386</v>
       </c>
       <c r="E93" t="n">
-        <v>32.5</v>
+        <v>19.5</v>
       </c>
       <c r="F93" t="n">
         <v>0.133</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.986</v>
+        <v>-0.917</v>
       </c>
     </row>
     <row r="94">
@@ -3135,20 +3135,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-2.578</v>
+        <v>-1.59</v>
       </c>
       <c r="E94" t="n">
-        <v>21.4</v>
+        <v>32.5</v>
       </c>
       <c r="F94" t="n">
         <v>0.133</v>
       </c>
       <c r="G94" t="n">
-        <v>-1.089</v>
+        <v>-0.986</v>
       </c>
     </row>
     <row r="95">
@@ -3164,20 +3164,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.467</v>
+        <v>-2.578</v>
       </c>
       <c r="E95" t="n">
-        <v>28.8</v>
+        <v>21.4</v>
       </c>
       <c r="F95" t="n">
         <v>0.133</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.402</v>
+        <v>-1.089</v>
       </c>
     </row>
     <row r="96">
@@ -3193,20 +3193,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.452</v>
+        <v>-2.467</v>
       </c>
       <c r="E96" t="n">
-        <v>30.3</v>
+        <v>28.8</v>
       </c>
       <c r="F96" t="n">
         <v>0.133</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.463</v>
+        <v>-1.402</v>
       </c>
     </row>
     <row r="97">
@@ -3280,20 +3280,20 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5.936</v>
+        <v>3.119</v>
       </c>
       <c r="E99" t="n">
-        <v>35.6</v>
+        <v>28.2</v>
       </c>
       <c r="F99" t="n">
         <v>0.633</v>
       </c>
       <c r="G99" t="n">
-        <v>4.866</v>
+        <v>2.205</v>
       </c>
     </row>
     <row r="100">
@@ -3309,20 +3309,20 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3.119</v>
+        <v>0.82</v>
       </c>
       <c r="E100" t="n">
-        <v>28.2</v>
+        <v>30.4</v>
       </c>
       <c r="F100" t="n">
         <v>0.633</v>
       </c>
       <c r="G100" t="n">
-        <v>2.205</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="101">
@@ -3338,20 +3338,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.82</v>
+        <v>0.957</v>
       </c>
       <c r="E101" t="n">
-        <v>30.4</v>
+        <v>26</v>
       </c>
       <c r="F101" t="n">
         <v>0.633</v>
       </c>
       <c r="G101" t="n">
-        <v>0.919</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="102">
@@ -3367,20 +3367,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.957</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="E102" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="F102" t="n">
         <v>0.633</v>
       </c>
       <c r="G102" t="n">
-        <v>0.86</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="103">
@@ -3715,20 +3715,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3.328</v>
+        <v>4.05</v>
       </c>
       <c r="E114" t="n">
-        <v>25.5</v>
+        <v>23.8</v>
       </c>
       <c r="F114" t="n">
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>1.911</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="115">
@@ -3744,20 +3744,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Javon Small</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.545</v>
+        <v>3.328</v>
       </c>
       <c r="E115" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="F115" t="n">
         <v>0.267</v>
       </c>
       <c r="G115" t="n">
-        <v>0.957</v>
+        <v>1.911</v>
       </c>
     </row>
     <row r="116">
@@ -3773,20 +3773,20 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jock Landale</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1.386</v>
+        <v>1.545</v>
       </c>
       <c r="E116" t="n">
-        <v>27.2</v>
+        <v>25.4</v>
       </c>
       <c r="F116" t="n">
         <v>0.267</v>
       </c>
       <c r="G116" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="117">
@@ -4788,20 +4788,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jose Alvarado</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-0.768</v>
+        <v>-1.907</v>
       </c>
       <c r="E151" t="n">
-        <v>20.7</v>
+        <v>20.1</v>
       </c>
       <c r="F151" t="n">
         <v>0.333</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.187</v>
+        <v>-0.658</v>
       </c>
     </row>
     <row r="152">
@@ -4817,20 +4817,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-1.907</v>
+        <v>-1.995</v>
       </c>
       <c r="E152" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="F152" t="n">
         <v>0.333</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.658</v>
+        <v>-0.6870000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -6325,20 +6325,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.464</v>
+        <v>0.613</v>
       </c>
       <c r="E204" t="n">
-        <v>23.3</v>
+        <v>20.6</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.274</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="205">
@@ -6354,11 +6354,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-0.147</v>
+        <v>0.464</v>
       </c>
       <c r="E205" t="n">
         <v>23.3</v>
@@ -6367,7 +6367,7 @@
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.023</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="206">
@@ -6992,20 +6992,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1.518</v>
+        <v>0.713</v>
       </c>
       <c r="E227" t="n">
-        <v>22.1</v>
+        <v>26.3</v>
       </c>
       <c r="F227" t="n">
         <v>0.167</v>
       </c>
       <c r="G227" t="n">
-        <v>0.774</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="228">
@@ -7021,20 +7021,20 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.713</v>
+        <v>-0.377</v>
       </c>
       <c r="E228" t="n">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="F228" t="n">
         <v>0.167</v>
       </c>
       <c r="G228" t="n">
-        <v>0.482</v>
+        <v>-0.117</v>
       </c>
     </row>
     <row r="229">
@@ -7050,20 +7050,20 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-0.377</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="E229" t="n">
-        <v>26.7</v>
+        <v>18.6</v>
       </c>
       <c r="F229" t="n">
         <v>0.167</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.117</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="230">
@@ -7079,20 +7079,20 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Walter Clayton Jr.</t>
+          <t>Svi Mykhailiuk</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-1.06</v>
+        <v>-0.91</v>
       </c>
       <c r="E230" t="n">
-        <v>20.2</v>
+        <v>19.6</v>
       </c>
       <c r="F230" t="n">
         <v>0.167</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.376</v>
+        <v>-0.303</v>
       </c>
     </row>
     <row r="231">
@@ -7195,20 +7195,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.393</v>
+        <v>2.474</v>
       </c>
       <c r="E234" t="n">
-        <v>31.3</v>
+        <v>20.6</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>0.278</v>
+        <v>1.074</v>
       </c>
     </row>
     <row r="235">
@@ -7224,20 +7224,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Tristan Vukcevic</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>-0.26</v>
+        <v>1.015</v>
       </c>
       <c r="E235" t="n">
-        <v>29.2</v>
+        <v>17.7</v>
       </c>
       <c r="F235" t="n">
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>-0.138</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="236">
@@ -7253,20 +7253,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.901</v>
+        <v>-0.26</v>
       </c>
       <c r="E236" t="n">
-        <v>21.6</v>
+        <v>29.2</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.389</v>
+        <v>-0.138</v>
       </c>
     </row>
     <row r="237">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-1.226</v>
+        <v>-0.901</v>
       </c>
       <c r="E237" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.389</v>
       </c>
     </row>
     <row r="238">
@@ -7311,20 +7311,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-2.275</v>
+        <v>-1.226</v>
       </c>
       <c r="E238" t="n">
-        <v>24.3</v>
+        <v>22.6</v>
       </c>
       <c r="F238" t="n">
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-1.133</v>
+        <v>-0.5620000000000001</v>
       </c>
     </row>
     <row r="239">
@@ -7500,26 +7500,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>20.623</v>
+        <v>20.265</v>
       </c>
       <c r="F3" t="n">
-        <v>3.09</v>
+        <v>2.861</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
     </row>
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>20.265</v>
+        <v>19.503</v>
       </c>
       <c r="F4" t="n">
-        <v>2.861</v>
+        <v>2.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7587,26 +7587,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>15.891</v>
+        <v>15.062</v>
       </c>
       <c r="F6" t="n">
-        <v>2.404</v>
+        <v>2.242</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7628,14 +7628,14 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>15.098</v>
+        <v>12.878</v>
       </c>
       <c r="F7" t="n">
-        <v>1.978</v>
+        <v>1.799</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
     </row>
@@ -7645,26 +7645,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>15.062</v>
+        <v>12.585</v>
       </c>
       <c r="F8" t="n">
-        <v>2.242</v>
+        <v>1.37</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -7674,26 +7674,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>14.762</v>
+        <v>11.73</v>
       </c>
       <c r="F9" t="n">
-        <v>2.39</v>
+        <v>1.748</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7703,26 +7703,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>12.585</v>
+        <v>11.548</v>
       </c>
       <c r="F10" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>9.872999999999999</v>
+        <v>9.914</v>
       </c>
       <c r="F12" t="n">
-        <v>1.417</v>
+        <v>1.259</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>9.459</v>
+        <v>9.872999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.16</v>
+        <v>1.417</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7935,26 +7935,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>8.090999999999999</v>
+        <v>7.272</v>
       </c>
       <c r="F18" t="n">
-        <v>1.284</v>
+        <v>0.882</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
     </row>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>7.772</v>
+        <v>7.223</v>
       </c>
       <c r="F19" t="n">
-        <v>1.036</v>
+        <v>1.358</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>7.223</v>
+        <v>7.02</v>
       </c>
       <c r="F20" t="n">
-        <v>1.358</v>
+        <v>0.86</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
     </row>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>7.02</v>
+        <v>5.685</v>
       </c>
       <c r="F21" t="n">
-        <v>0.86</v>
+        <v>1.008</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -8051,26 +8051,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>5.685</v>
+        <v>4.091</v>
       </c>
       <c r="F22" t="n">
-        <v>1.008</v>
+        <v>0.118</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
     </row>
@@ -8080,26 +8080,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4.091</v>
+        <v>3.411</v>
       </c>
       <c r="F23" t="n">
-        <v>0.118</v>
+        <v>0.116</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
     </row>
@@ -8150,14 +8150,14 @@
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.943</v>
+        <v>-0.738</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.666</v>
+        <v>-0.333</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
     </row>
@@ -8167,26 +8167,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.522</v>
+        <v>-2.159</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.084</v>
+        <v>-0.751</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
     </row>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.623</v>
+        <v>-2.522</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.58</v>
+        <v>-1.084</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
     </row>
@@ -8225,26 +8225,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.705</v>
+        <v>-3.476</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.759</v>
+        <v>-0.821</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>John Konchar</t>
         </is>
       </c>
     </row>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.965</v>
+        <v>-4.113</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.106</v>
+        <v>-0.874</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
     </row>
@@ -8283,26 +8283,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.429</v>
+        <v>-4.635</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.545</v>
+        <v>-1.011</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
     </row>
@@ -8324,10 +8324,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-9.064</v>
+        <v>-6.544</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.449</v>
+        <v>-1.737</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.258</v>
+        <v>2.259</v>
       </c>
       <c r="E3" t="n">
         <v>33.3</v>
@@ -509,7 +509,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>1.962</v>
+        <v>1.963</v>
       </c>
     </row>
     <row r="4">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.263</v>
+        <v>2.264</v>
       </c>
       <c r="E4" t="n">
         <v>27.9</v>
@@ -625,7 +625,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.706</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.285</v>
+        <v>-1.284</v>
       </c>
       <c r="E9" t="n">
         <v>18.6</v>
@@ -728,20 +728,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.57</v>
+        <v>2.121</v>
       </c>
       <c r="E11" t="n">
-        <v>33.7</v>
+        <v>32.1</v>
       </c>
       <c r="F11" t="n">
         <v>0.867</v>
       </c>
       <c r="G11" t="n">
-        <v>3.114</v>
+        <v>2.001</v>
       </c>
     </row>
     <row r="12">
@@ -757,20 +757,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.121</v>
+        <v>2.586</v>
       </c>
       <c r="E12" t="n">
-        <v>32.1</v>
+        <v>27.5</v>
       </c>
       <c r="F12" t="n">
         <v>0.867</v>
       </c>
       <c r="G12" t="n">
-        <v>2.001</v>
+        <v>1.975</v>
       </c>
     </row>
     <row r="13">
@@ -786,20 +786,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Luka Garza</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.586</v>
+        <v>2.68</v>
       </c>
       <c r="E13" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="F13" t="n">
         <v>0.867</v>
       </c>
       <c r="G13" t="n">
-        <v>1.975</v>
+        <v>1.291</v>
       </c>
     </row>
     <row r="14">
@@ -815,20 +815,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luka Garza</t>
+          <t>Dalano Banton</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.679</v>
+        <v>0.476</v>
       </c>
       <c r="E14" t="n">
-        <v>17.5</v>
+        <v>20.4</v>
       </c>
       <c r="F14" t="n">
         <v>0.867</v>
       </c>
       <c r="G14" t="n">
-        <v>1.29</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="15">
@@ -844,20 +844,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dalano Banton</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.475</v>
+        <v>-0.151</v>
       </c>
       <c r="E15" t="n">
-        <v>20.4</v>
+        <v>24.7</v>
       </c>
       <c r="F15" t="n">
         <v>0.867</v>
       </c>
       <c r="G15" t="n">
-        <v>0.572</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="16">
@@ -873,20 +873,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Baylor Scheierman</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.152</v>
+        <v>-0.738</v>
       </c>
       <c r="E16" t="n">
-        <v>24.7</v>
+        <v>26.2</v>
       </c>
       <c r="F16" t="n">
         <v>0.867</v>
       </c>
       <c r="G16" t="n">
-        <v>0.368</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -902,20 +902,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Baylor Scheierman</t>
+          <t>Hugo González</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.738</v>
+        <v>-2.761</v>
       </c>
       <c r="E17" t="n">
-        <v>26.2</v>
+        <v>16.6</v>
       </c>
       <c r="F17" t="n">
         <v>0.867</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.654</v>
       </c>
     </row>
     <row r="18">
@@ -960,20 +960,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Josh Minott</t>
+          <t>Ziaire Williams</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.579</v>
+        <v>-0.293</v>
       </c>
       <c r="E19" t="n">
-        <v>19.9</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>1.096</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="20">
@@ -989,20 +989,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ziaire Williams</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.293</v>
+        <v>-1.87</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>22.1</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.108</v>
+        <v>-0.829</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.871</v>
+        <v>-2.019</v>
       </c>
       <c r="E21" t="n">
-        <v>22.1</v>
+        <v>21.7</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.829</v>
+        <v>-0.884</v>
       </c>
     </row>
     <row r="22">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.019</v>
+        <v>-3.959</v>
       </c>
       <c r="E22" t="n">
-        <v>21.7</v>
+        <v>15.7</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.885</v>
+        <v>-1.276</v>
       </c>
     </row>
     <row r="23">
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4.858</v>
+        <v>-4.857</v>
       </c>
       <c r="E23" t="n">
         <v>20.6</v>
@@ -1089,7 +1089,7 @@
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.056</v>
+        <v>-2.055</v>
       </c>
     </row>
     <row r="24">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-4.682</v>
+        <v>-4.681</v>
       </c>
       <c r="E24" t="n">
         <v>24.5</v>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-5.212</v>
+        <v>-5.211</v>
       </c>
       <c r="E25" t="n">
         <v>24.2</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.617</v>
+        <v>5.618</v>
       </c>
       <c r="E26" t="n">
         <v>28.2</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.035</v>
+        <v>2.036</v>
       </c>
       <c r="E28" t="n">
         <v>31.3</v>
@@ -1263,7 +1263,7 @@
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.518</v>
+        <v>1.519</v>
       </c>
     </row>
     <row r="30">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1.468</v>
+        <v>-1.467</v>
       </c>
       <c r="E32" t="n">
         <v>19.2</v>
@@ -1408,7 +1408,7 @@
         <v>0.3</v>
       </c>
       <c r="G34" t="n">
-        <v>3.435</v>
+        <v>3.436</v>
       </c>
     </row>
     <row r="35">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.073</v>
+        <v>2.074</v>
       </c>
       <c r="E36" t="n">
         <v>25</v>
@@ -1495,7 +1495,7 @@
         <v>0.3</v>
       </c>
       <c r="G37" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="38">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-0.644</v>
+        <v>-0.643</v>
       </c>
       <c r="E38" t="n">
         <v>25</v>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.862</v>
+        <v>3.863</v>
       </c>
       <c r="E44" t="n">
         <v>31.3</v>
@@ -1698,7 +1698,7 @@
         <v>0.767</v>
       </c>
       <c r="G44" t="n">
-        <v>3.018</v>
+        <v>3.019</v>
       </c>
     </row>
     <row r="45">
@@ -1714,20 +1714,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.18</v>
+        <v>1.808</v>
       </c>
       <c r="E45" t="n">
-        <v>29.1</v>
+        <v>28.7</v>
       </c>
       <c r="F45" t="n">
         <v>0.767</v>
       </c>
       <c r="G45" t="n">
-        <v>2.995</v>
+        <v>1.541</v>
       </c>
     </row>
     <row r="46">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.807</v>
+        <v>-0.214</v>
       </c>
       <c r="E46" t="n">
-        <v>28.7</v>
+        <v>26.9</v>
       </c>
       <c r="F46" t="n">
         <v>0.767</v>
       </c>
       <c r="G46" t="n">
-        <v>1.54</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="47">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Lonzo Ball</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.205</v>
+        <v>-0.337</v>
       </c>
       <c r="E47" t="n">
-        <v>27.6</v>
+        <v>16.4</v>
       </c>
       <c r="F47" t="n">
         <v>0.767</v>
       </c>
       <c r="G47" t="n">
-        <v>1.133</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="48">
@@ -1801,20 +1801,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Keon Ellis</t>
+          <t>Nae'Qwan Tomlin</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.215</v>
+        <v>-0.42</v>
       </c>
       <c r="E48" t="n">
-        <v>26.9</v>
+        <v>16.6</v>
       </c>
       <c r="F48" t="n">
         <v>0.767</v>
       </c>
       <c r="G48" t="n">
-        <v>0.309</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="49">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.354</v>
+        <v>1.355</v>
       </c>
       <c r="E50" t="n">
         <v>33.9</v>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.444</v>
+        <v>2.445</v>
       </c>
       <c r="E51" t="n">
         <v>19.4</v>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-0.11</v>
+        <v>-0.109</v>
       </c>
       <c r="E53" t="n">
         <v>29.7</v>
@@ -1959,7 +1959,7 @@
         <v>0.233</v>
       </c>
       <c r="G53" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="54">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-0.89</v>
+        <v>-0.889</v>
       </c>
       <c r="E54" t="n">
         <v>21.1</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-1.4</v>
+        <v>-1.399</v>
       </c>
       <c r="E56" t="n">
         <v>28.1</v>
@@ -2046,7 +2046,7 @@
         <v>0.233</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.6820000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-2.583</v>
+        <v>-2.582</v>
       </c>
       <c r="E57" t="n">
         <v>19.7</v>
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.215</v>
+        <v>15.216</v>
       </c>
       <c r="E58" t="n">
         <v>36.2</v>
@@ -2104,7 +2104,7 @@
         <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>12.1</v>
+        <v>12.101</v>
       </c>
     </row>
     <row r="59">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6.404</v>
+        <v>6.405</v>
       </c>
       <c r="E59" t="n">
         <v>36.1</v>
@@ -2133,7 +2133,7 @@
         <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>5.437</v>
+        <v>5.438</v>
       </c>
     </row>
     <row r="60">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.442</v>
+        <v>3.443</v>
       </c>
       <c r="E60" t="n">
         <v>25.9</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="E61" t="n">
         <v>33.6</v>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="E62" t="n">
         <v>24.7</v>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1.343</v>
+        <v>-1.342</v>
       </c>
       <c r="E64" t="n">
         <v>32.3</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.303</v>
+        <v>5.304</v>
       </c>
       <c r="E66" t="n">
         <v>28.6</v>
@@ -2365,7 +2365,7 @@
         <v>0.9</v>
       </c>
       <c r="G67" t="n">
-        <v>1.412</v>
+        <v>1.413</v>
       </c>
     </row>
     <row r="68">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.501</v>
+        <v>0.502</v>
       </c>
       <c r="E68" t="n">
         <v>22.8</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="E69" t="n">
         <v>18.7</v>
@@ -2481,7 +2481,7 @@
         <v>0.9</v>
       </c>
       <c r="G71" t="n">
-        <v>0.511</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="72">
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-0.046</v>
+        <v>-0.045</v>
       </c>
       <c r="E72" t="n">
         <v>25.5</v>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.109</v>
+        <v>1.11</v>
       </c>
       <c r="E76" t="n">
         <v>31.6</v>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.887</v>
+        <v>0.888</v>
       </c>
       <c r="E77" t="n">
         <v>32.2</v>
@@ -2655,7 +2655,7 @@
         <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>0.862</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="78">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.027</v>
+        <v>-0.026</v>
       </c>
       <c r="E78" t="n">
         <v>20.3</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.1</v>
+        <v>-0.099</v>
       </c>
       <c r="E79" t="n">
         <v>24.6</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-1.085</v>
+        <v>-1.084</v>
       </c>
       <c r="E81" t="n">
         <v>31</v>
@@ -2771,7 +2771,7 @@
         <v>0.4</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.443</v>
+        <v>-0.442</v>
       </c>
     </row>
     <row r="82">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.129</v>
+        <v>4.13</v>
       </c>
       <c r="E82" t="n">
         <v>35.7</v>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3.744</v>
+        <v>3.745</v>
       </c>
       <c r="E83" t="n">
         <v>32.6</v>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.942</v>
+        <v>1.943</v>
       </c>
       <c r="E84" t="n">
         <v>38.4</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.793</v>
+        <v>1.794</v>
       </c>
       <c r="E86" t="n">
         <v>15.2</v>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-0.778</v>
+        <v>-0.777</v>
       </c>
       <c r="E87" t="n">
         <v>36.7</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-1.581</v>
+        <v>-1.58</v>
       </c>
       <c r="E88" t="n">
         <v>23.6</v>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-6.141</v>
+        <v>-6.14</v>
       </c>
       <c r="E89" t="n">
         <v>19.2</v>
@@ -3019,20 +3019,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>T.J. McConnell</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.178</v>
+        <v>5.653</v>
       </c>
       <c r="E90" t="n">
-        <v>30.8</v>
+        <v>19</v>
       </c>
       <c r="F90" t="n">
         <v>0.133</v>
       </c>
       <c r="G90" t="n">
-        <v>1.482</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="91">
@@ -3048,20 +3048,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.567</v>
+        <v>2.178</v>
       </c>
       <c r="E91" t="n">
-        <v>22.3</v>
+        <v>30.8</v>
       </c>
       <c r="F91" t="n">
         <v>0.133</v>
       </c>
       <c r="G91" t="n">
-        <v>1.254</v>
+        <v>1.482</v>
       </c>
     </row>
     <row r="92">
@@ -3077,20 +3077,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.494</v>
+        <v>2.567</v>
       </c>
       <c r="E92" t="n">
-        <v>28.5</v>
+        <v>22.3</v>
       </c>
       <c r="F92" t="n">
         <v>0.133</v>
       </c>
       <c r="G92" t="n">
-        <v>0.966</v>
+        <v>1.254</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-2.386</v>
+        <v>1.494</v>
       </c>
       <c r="E93" t="n">
-        <v>19.5</v>
+        <v>28.5</v>
       </c>
       <c r="F93" t="n">
         <v>0.133</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.917</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="94">
@@ -3135,20 +3135,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-1.59</v>
+        <v>-2.194</v>
       </c>
       <c r="E94" t="n">
-        <v>32.5</v>
+        <v>19.3</v>
       </c>
       <c r="F94" t="n">
         <v>0.133</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.986</v>
+        <v>-0.829</v>
       </c>
     </row>
     <row r="95">
@@ -3164,20 +3164,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.578</v>
+        <v>-2.386</v>
       </c>
       <c r="E95" t="n">
-        <v>21.4</v>
+        <v>19.5</v>
       </c>
       <c r="F95" t="n">
         <v>0.133</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.089</v>
+        <v>-0.917</v>
       </c>
     </row>
     <row r="96">
@@ -3193,20 +3193,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.467</v>
+        <v>-2.577</v>
       </c>
       <c r="E96" t="n">
-        <v>28.8</v>
+        <v>21.4</v>
       </c>
       <c r="F96" t="n">
         <v>0.133</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.402</v>
+        <v>-1.089</v>
       </c>
     </row>
     <row r="97">
@@ -3255,16 +3255,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.323</v>
+        <v>10.264</v>
       </c>
       <c r="E98" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="F98" t="n">
         <v>0.633</v>
       </c>
       <c r="G98" t="n">
-        <v>7.09</v>
+        <v>6.992</v>
       </c>
     </row>
     <row r="99">
@@ -3284,16 +3284,16 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3.119</v>
+        <v>3.19</v>
       </c>
       <c r="E99" t="n">
-        <v>28.2</v>
+        <v>29.3</v>
       </c>
       <c r="F99" t="n">
         <v>0.633</v>
       </c>
       <c r="G99" t="n">
-        <v>2.205</v>
+        <v>2.333</v>
       </c>
     </row>
     <row r="100">
@@ -3313,16 +3313,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.82</v>
+        <v>0.639</v>
       </c>
       <c r="E100" t="n">
-        <v>30.4</v>
+        <v>29.6</v>
       </c>
       <c r="F100" t="n">
         <v>0.633</v>
       </c>
       <c r="G100" t="n">
-        <v>0.919</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="101">
@@ -3342,16 +3342,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.957</v>
+        <v>0.853</v>
       </c>
       <c r="E101" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F101" t="n">
         <v>0.633</v>
       </c>
       <c r="G101" t="n">
-        <v>0.86</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="102">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E102" t="n">
-        <v>25.7</v>
+        <v>24.1</v>
       </c>
       <c r="F102" t="n">
         <v>0.633</v>
       </c>
       <c r="G102" t="n">
-        <v>0.705</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="103">
@@ -3400,16 +3400,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-0.081</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E103" t="n">
-        <v>27.2</v>
+        <v>27.6</v>
       </c>
       <c r="F103" t="n">
         <v>0.633</v>
       </c>
       <c r="G103" t="n">
-        <v>0.313</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="104">
@@ -3429,16 +3429,16 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.481</v>
+        <v>-0.551</v>
       </c>
       <c r="E104" t="n">
-        <v>27</v>
+        <v>26.2</v>
       </c>
       <c r="F104" t="n">
         <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="105">
@@ -3458,16 +3458,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-1.357</v>
+        <v>-1.35</v>
       </c>
       <c r="E105" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="F105" t="n">
         <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.447</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="106">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4.641</v>
+        <v>4.642</v>
       </c>
       <c r="E107" t="n">
         <v>39.8</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4.578</v>
+        <v>4.579</v>
       </c>
       <c r="E108" t="n">
         <v>35.4</v>
@@ -3583,7 +3583,7 @@
         <v>0.6</v>
       </c>
       <c r="G109" t="n">
-        <v>1.337</v>
+        <v>1.338</v>
       </c>
     </row>
     <row r="110">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.236</v>
+        <v>1.237</v>
       </c>
       <c r="E110" t="n">
         <v>21.3</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.551</v>
+        <v>0.552</v>
       </c>
       <c r="E111" t="n">
         <v>26.9</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-0.657</v>
+        <v>-0.656</v>
       </c>
       <c r="E112" t="n">
         <v>18.2</v>
@@ -3670,7 +3670,7 @@
         <v>0.6</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.022</v>
+        <v>-0.021</v>
       </c>
     </row>
     <row r="113">
@@ -3728,7 +3728,7 @@
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>2.142</v>
+        <v>2.143</v>
       </c>
     </row>
     <row r="115">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3.328</v>
+        <v>3.329</v>
       </c>
       <c r="E115" t="n">
         <v>25.5</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="E117" t="n">
         <v>27.8</v>
@@ -3815,7 +3815,7 @@
         <v>0.267</v>
       </c>
       <c r="G117" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="118">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-0.741</v>
+        <v>-0.74</v>
       </c>
       <c r="E118" t="n">
         <v>25.8</v>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-2.015</v>
+        <v>-2.014</v>
       </c>
       <c r="E119" t="n">
         <v>24.2</v>
@@ -3931,7 +3931,7 @@
         <v>0.267</v>
       </c>
       <c r="G121" t="n">
-        <v>-2.971</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="122">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.43</v>
+        <v>2.431</v>
       </c>
       <c r="E123" t="n">
         <v>35.8</v>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1.584</v>
+        <v>1.585</v>
       </c>
       <c r="E125" t="n">
         <v>28</v>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-0.199</v>
+        <v>-0.198</v>
       </c>
       <c r="E128" t="n">
         <v>19.9</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.606</v>
+        <v>-0.605</v>
       </c>
       <c r="E129" t="n">
         <v>30.8</v>
@@ -4163,7 +4163,7 @@
         <v>0.667</v>
       </c>
       <c r="G129" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="130">
@@ -4179,20 +4179,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2.315</v>
+        <v>-0.15</v>
       </c>
       <c r="E130" t="n">
-        <v>31.2</v>
+        <v>21.6</v>
       </c>
       <c r="F130" t="n">
         <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>1.635</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="131">
@@ -4208,20 +4208,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Cole Anthony</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.8120000000000001</v>
+        <v>-2.31</v>
       </c>
       <c r="E131" t="n">
-        <v>22.9</v>
+        <v>15.9</v>
       </c>
       <c r="F131" t="n">
         <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>0.484</v>
+        <v>-0.698</v>
       </c>
     </row>
     <row r="132">
@@ -4237,20 +4237,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-0.05</v>
+        <v>-1.984</v>
       </c>
       <c r="E132" t="n">
-        <v>19.9</v>
+        <v>21.5</v>
       </c>
       <c r="F132" t="n">
         <v>0.2</v>
       </c>
       <c r="G132" t="n">
-        <v>0.062</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cole Anthony</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-2.311</v>
+        <v>-1.646</v>
       </c>
       <c r="E133" t="n">
-        <v>15.9</v>
+        <v>29</v>
       </c>
       <c r="F133" t="n">
         <v>0.2</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.698</v>
+        <v>-0.873</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-1.589</v>
+        <v>-2.919</v>
       </c>
       <c r="E134" t="n">
-        <v>28.2</v>
+        <v>15.7</v>
       </c>
       <c r="F134" t="n">
         <v>0.2</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.888</v>
       </c>
     </row>
     <row r="135">
@@ -4324,20 +4324,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-2.087</v>
+        <v>-2.393</v>
       </c>
       <c r="E135" t="n">
-        <v>22.3</v>
+        <v>21.2</v>
       </c>
       <c r="F135" t="n">
         <v>0.2</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.878</v>
+        <v>-0.969</v>
       </c>
     </row>
     <row r="136">
@@ -4353,20 +4353,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Gary Trent Jr.</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-2.461</v>
+        <v>-3.793</v>
       </c>
       <c r="E136" t="n">
-        <v>21.4</v>
+        <v>16.4</v>
       </c>
       <c r="F136" t="n">
         <v>0.2</v>
       </c>
       <c r="G136" t="n">
-        <v>-1.007</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="137">
@@ -4386,16 +4386,16 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-3.3</v>
+        <v>-4.049</v>
       </c>
       <c r="E137" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="F137" t="n">
         <v>0.2</v>
       </c>
       <c r="G137" t="n">
-        <v>-1.304</v>
+        <v>-1.642</v>
       </c>
     </row>
     <row r="138">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2.151</v>
+        <v>2.152</v>
       </c>
       <c r="E138" t="n">
         <v>31</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2.212</v>
+        <v>2.213</v>
       </c>
       <c r="E139" t="n">
         <v>28</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.904</v>
+        <v>0.905</v>
       </c>
       <c r="E143" t="n">
         <v>29.8</v>
@@ -4585,14 +4585,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>-0.032</v>
+        <v>0.401</v>
       </c>
       <c r="E144" t="n">
-        <v>28.9</v>
+        <v>18.5</v>
       </c>
       <c r="F144" t="n">
         <v>0.8</v>
@@ -4614,20 +4614,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Mike Conley</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.401</v>
+        <v>-1.558</v>
       </c>
       <c r="E145" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="F145" t="n">
         <v>0.8</v>
       </c>
       <c r="G145" t="n">
-        <v>0.462</v>
+        <v>-0.252</v>
       </c>
     </row>
     <row r="146">
@@ -4643,20 +4643,20 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3.866</v>
+        <v>4.187</v>
       </c>
       <c r="E146" t="n">
-        <v>35.3</v>
+        <v>30.9</v>
       </c>
       <c r="F146" t="n">
         <v>0.333</v>
       </c>
       <c r="G146" t="n">
-        <v>3.086</v>
+        <v>2.914</v>
       </c>
     </row>
     <row r="147">
@@ -4672,20 +4672,20 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4.187</v>
+        <v>2.995</v>
       </c>
       <c r="E147" t="n">
-        <v>30.9</v>
+        <v>30.2</v>
       </c>
       <c r="F147" t="n">
         <v>0.333</v>
       </c>
       <c r="G147" t="n">
-        <v>2.914</v>
+        <v>2.096</v>
       </c>
     </row>
     <row r="148">
@@ -4701,20 +4701,20 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2.994</v>
+        <v>1.708</v>
       </c>
       <c r="E148" t="n">
-        <v>30.2</v>
+        <v>32.2</v>
       </c>
       <c r="F148" t="n">
         <v>0.333</v>
       </c>
       <c r="G148" t="n">
-        <v>2.096</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="149">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1.707</v>
+        <v>0.626</v>
       </c>
       <c r="E149" t="n">
-        <v>32.2</v>
+        <v>17.4</v>
       </c>
       <c r="F149" t="n">
         <v>0.333</v>
       </c>
       <c r="G149" t="n">
-        <v>1.368</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="150">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.417</v>
+        <v>0.418</v>
       </c>
       <c r="E150" t="n">
         <v>20.7</v>
@@ -4917,7 +4917,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G155" t="n">
-        <v>2.712</v>
+        <v>2.713</v>
       </c>
     </row>
     <row r="156">
@@ -4946,7 +4946,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>2.176</v>
+        <v>2.177</v>
       </c>
     </row>
     <row r="157">
@@ -5004,7 +5004,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G158" t="n">
-        <v>1.954</v>
+        <v>1.955</v>
       </c>
     </row>
     <row r="159">
@@ -5049,20 +5049,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jordan Clarkson</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-2.632</v>
+        <v>1.391</v>
       </c>
       <c r="E160" t="n">
-        <v>17.3</v>
+        <v>30.6</v>
       </c>
       <c r="F160" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.612</v>
+        <v>1.481</v>
       </c>
     </row>
     <row r="161">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
+        <v>4.001</v>
       </c>
       <c r="E164" t="n">
         <v>22.4</v>
@@ -5178,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>2.335</v>
+        <v>2.336</v>
       </c>
     </row>
     <row r="165">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2.078</v>
+        <v>2.079</v>
       </c>
       <c r="E165" t="n">
         <v>27</v>
@@ -5265,7 +5265,7 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1.351</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="168">
@@ -5323,7 +5323,7 @@
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>-1.655</v>
+        <v>-1.654</v>
       </c>
     </row>
     <row r="170">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1.99</v>
+        <v>1.991</v>
       </c>
       <c r="E171" t="n">
         <v>35.6</v>
@@ -5410,7 +5410,7 @@
         <v>0.467</v>
       </c>
       <c r="G172" t="n">
-        <v>1.501</v>
+        <v>1.502</v>
       </c>
     </row>
     <row r="173">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-0.278</v>
+        <v>-0.277</v>
       </c>
       <c r="E173" t="n">
         <v>29.4</v>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
       <c r="E174" t="n">
         <v>21</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6.681</v>
+        <v>6.682</v>
       </c>
       <c r="E178" t="n">
         <v>35.8</v>
@@ -5584,7 +5584,7 @@
         <v>0.433</v>
       </c>
       <c r="G178" t="n">
-        <v>5.309</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="179">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5.449</v>
+        <v>5.45</v>
       </c>
       <c r="E179" t="n">
         <v>33</v>
@@ -5642,7 +5642,7 @@
         <v>0.433</v>
       </c>
       <c r="G180" t="n">
-        <v>1.859</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="181">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3.392</v>
+        <v>3.393</v>
       </c>
       <c r="E186" t="n">
         <v>29.7</v>
@@ -5816,7 +5816,7 @@
         <v>0.533</v>
       </c>
       <c r="G186" t="n">
-        <v>2.43</v>
+        <v>2.431</v>
       </c>
     </row>
     <row r="187">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3.07</v>
+        <v>3.071</v>
       </c>
       <c r="E188" t="n">
         <v>27.6</v>
@@ -5874,7 +5874,7 @@
         <v>0.533</v>
       </c>
       <c r="G188" t="n">
-        <v>2.072</v>
+        <v>2.073</v>
       </c>
     </row>
     <row r="189">
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1.12</v>
+        <v>1.121</v>
       </c>
       <c r="E189" t="n">
         <v>23.5</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="E191" t="n">
         <v>29</v>
@@ -5961,7 +5961,7 @@
         <v>0.533</v>
       </c>
       <c r="G191" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="192">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-1.491</v>
+        <v>-1.49</v>
       </c>
       <c r="E192" t="n">
         <v>32.1</v>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>-2.056</v>
+        <v>-2.055</v>
       </c>
       <c r="E193" t="n">
         <v>20.6</v>
@@ -6164,7 +6164,7 @@
         <v>0.367</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="199">
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-1.597</v>
+        <v>-1.596</v>
       </c>
       <c r="E199" t="n">
         <v>24.6</v>
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-2.237</v>
+        <v>-2.236</v>
       </c>
       <c r="E200" t="n">
         <v>23.3</v>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-1.839</v>
+        <v>-1.838</v>
       </c>
       <c r="E201" t="n">
         <v>29.6</v>
@@ -6267,20 +6267,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1.394</v>
+        <v>0.674</v>
       </c>
       <c r="E202" t="n">
-        <v>30.6</v>
+        <v>32.5</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>0.953</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="203">
@@ -6296,20 +6296,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.673</v>
+        <v>0.613</v>
       </c>
       <c r="E203" t="n">
-        <v>32.5</v>
+        <v>20.6</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.523</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="204">
@@ -6325,20 +6325,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.613</v>
+        <v>-1.125</v>
       </c>
       <c r="E204" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.307</v>
+        <v>-0.438</v>
       </c>
     </row>
     <row r="205">
@@ -6354,20 +6354,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.464</v>
+        <v>-0.893</v>
       </c>
       <c r="E205" t="n">
-        <v>23.3</v>
+        <v>33.7</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>0.274</v>
+        <v>-0.5570000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -6383,20 +6383,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Doug McDermott</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-0.894</v>
+        <v>-2.197</v>
       </c>
       <c r="E206" t="n">
-        <v>33.7</v>
+        <v>18.6</v>
       </c>
       <c r="F206" t="n">
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.8120000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -6425,7 +6425,7 @@
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-1.494</v>
+        <v>-1.493</v>
       </c>
     </row>
     <row r="208">
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-3.585</v>
+        <v>-3.584</v>
       </c>
       <c r="E209" t="n">
         <v>33.7</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>10.303</v>
+        <v>10.304</v>
       </c>
       <c r="E210" t="n">
         <v>29</v>
@@ -6541,7 +6541,7 @@
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>2.416</v>
+        <v>2.417</v>
       </c>
     </row>
     <row r="212">
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1.889</v>
+        <v>1.89</v>
       </c>
       <c r="E212" t="n">
         <v>30</v>
@@ -6570,7 +6570,7 @@
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>1.785</v>
+        <v>1.786</v>
       </c>
     </row>
     <row r="213">
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1.205</v>
+        <v>1.206</v>
       </c>
       <c r="E214" t="n">
         <v>22.5</v>
@@ -6628,7 +6628,7 @@
         <v>0.967</v>
       </c>
       <c r="G214" t="n">
-        <v>1.018</v>
+        <v>1.019</v>
       </c>
     </row>
     <row r="215">
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.555</v>
+        <v>0.556</v>
       </c>
       <c r="E215" t="n">
         <v>27.2</v>
@@ -6657,7 +6657,7 @@
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>0.862</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="216">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.302</v>
+        <v>0.303</v>
       </c>
       <c r="E216" t="n">
         <v>30.8</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>-0.5</v>
+        <v>-0.499</v>
       </c>
       <c r="E217" t="n">
         <v>21.1</v>
@@ -6715,7 +6715,7 @@
         <v>0.967</v>
       </c>
       <c r="G217" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="218">
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.408</v>
+        <v>1.409</v>
       </c>
       <c r="E221" t="n">
         <v>30.9</v>
@@ -6847,20 +6847,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.865</v>
+        <v>-0.346</v>
       </c>
       <c r="E222" t="n">
-        <v>34</v>
+        <v>20.7</v>
       </c>
       <c r="F222" t="n">
         <v>0.5</v>
       </c>
       <c r="G222" t="n">
-        <v>0.967</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="223">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>A.J. Lawson</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1.392</v>
+        <v>-1.523</v>
       </c>
       <c r="E223" t="n">
-        <v>23</v>
+        <v>15.6</v>
       </c>
       <c r="F223" t="n">
         <v>0.5</v>
       </c>
       <c r="G223" t="n">
-        <v>0.905</v>
+        <v>-0.333</v>
       </c>
     </row>
     <row r="224">
@@ -6905,20 +6905,20 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.347</v>
+        <v>-1.279</v>
       </c>
       <c r="E224" t="n">
-        <v>20.7</v>
+        <v>22.3</v>
       </c>
       <c r="F224" t="n">
         <v>0.5</v>
       </c>
       <c r="G224" t="n">
-        <v>0.066</v>
+        <v>-0.362</v>
       </c>
     </row>
     <row r="225">
@@ -6934,20 +6934,20 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Gradey Dick</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-1.279</v>
+        <v>-2.664</v>
       </c>
       <c r="E225" t="n">
-        <v>22.3</v>
+        <v>15.4</v>
       </c>
       <c r="F225" t="n">
         <v>0.5</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.362</v>
+        <v>-0.695</v>
       </c>
     </row>
     <row r="226">
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-0.91</v>
+        <v>-0.909</v>
       </c>
       <c r="E230" t="n">
         <v>19.6</v>
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-1.558</v>
+        <v>-1.557</v>
       </c>
       <c r="E231" t="n">
         <v>28.9</v>
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-3.081</v>
+        <v>-3.08</v>
       </c>
       <c r="E233" t="n">
         <v>34.7</v>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1.015</v>
+        <v>1.016</v>
       </c>
       <c r="E235" t="n">
         <v>17.7</v>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-0.901</v>
+        <v>-0.9</v>
       </c>
       <c r="E237" t="n">
         <v>21.6</v>
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-3.045</v>
+        <v>-3.044</v>
       </c>
       <c r="E239" t="n">
         <v>21.5</v>
@@ -7382,7 +7382,7 @@
         <v>0.033</v>
       </c>
       <c r="G240" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
     </row>
     <row r="241">
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>-2.404</v>
+        <v>-2.403</v>
       </c>
       <c r="E241" t="n">
         <v>32.3</v>
@@ -7411,7 +7411,7 @@
         <v>0.033</v>
       </c>
       <c r="G241" t="n">
-        <v>-1.595</v>
+        <v>-1.594</v>
       </c>
     </row>
   </sheetData>
@@ -7483,10 +7483,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>20.732</v>
+        <v>20.734</v>
       </c>
       <c r="F2" t="n">
-        <v>2.738</v>
+        <v>2.739</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7512,10 +7512,10 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>20.265</v>
+        <v>20.267</v>
       </c>
       <c r="F3" t="n">
-        <v>2.861</v>
+        <v>2.862</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>19.503</v>
+        <v>18.617</v>
       </c>
       <c r="F4" t="n">
-        <v>2.87</v>
+        <v>2.798</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
     </row>
@@ -7558,26 +7558,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>18.614</v>
+        <v>15.644</v>
       </c>
       <c r="F5" t="n">
-        <v>2.798</v>
+        <v>2.103</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7599,10 +7599,10 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>15.062</v>
+        <v>15.067</v>
       </c>
       <c r="F6" t="n">
-        <v>2.242</v>
+        <v>2.243</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7616,26 +7616,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>12.878</v>
+        <v>14.681</v>
       </c>
       <c r="F7" t="n">
-        <v>1.799</v>
+        <v>1.873</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -7645,26 +7645,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>12.585</v>
+        <v>11.55</v>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>1.561</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7686,10 +7686,10 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>11.73</v>
+        <v>11.533</v>
       </c>
       <c r="F9" t="n">
-        <v>1.748</v>
+        <v>1.727</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -7703,26 +7703,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>11.548</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>1.56</v>
+        <v>1.504</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7732,26 +7732,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>10.998</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.504</v>
+        <v>1.26</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>9.914</v>
+        <v>9.159000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.259</v>
+        <v>1.227</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>9.872999999999999</v>
+        <v>9.112</v>
       </c>
       <c r="F13" t="n">
-        <v>1.417</v>
+        <v>1.008</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
     </row>
@@ -7819,26 +7819,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>9.007</v>
+        <v>8.945</v>
       </c>
       <c r="F14" t="n">
-        <v>1.461</v>
+        <v>1.167</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
     </row>
@@ -7848,26 +7848,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>8.944000000000001</v>
+        <v>8.917</v>
       </c>
       <c r="F15" t="n">
-        <v>1.167</v>
+        <v>0.68</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7877,26 +7877,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>8.917</v>
+        <v>8.138</v>
       </c>
       <c r="F16" t="n">
-        <v>0.68</v>
+        <v>0.956</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
     </row>
@@ -7906,26 +7906,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>8.135999999999999</v>
+        <v>7.224</v>
       </c>
       <c r="F17" t="n">
-        <v>0.956</v>
+        <v>1.359</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
     </row>
@@ -7935,26 +7935,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>7.272</v>
+        <v>7.023</v>
       </c>
       <c r="F18" t="n">
-        <v>0.882</v>
+        <v>0.861</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
     </row>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>7.223</v>
+        <v>6.107</v>
       </c>
       <c r="F19" t="n">
-        <v>1.358</v>
+        <v>0.655</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>7.02</v>
+        <v>5.687</v>
       </c>
       <c r="F20" t="n">
-        <v>0.86</v>
+        <v>1.008</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>5.685</v>
+        <v>4.534</v>
       </c>
       <c r="F21" t="n">
-        <v>1.008</v>
+        <v>0.478</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.091</v>
+        <v>4.092</v>
       </c>
       <c r="F22" t="n">
         <v>0.118</v>
@@ -8092,7 +8092,7 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>3.411</v>
+        <v>3.413</v>
       </c>
       <c r="F23" t="n">
         <v>0.116</v>
@@ -8109,26 +8109,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.13</v>
+        <v>1.691</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.199</v>
+        <v>0.189</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>T.J. McConnell</t>
         </is>
       </c>
     </row>
@@ -8138,26 +8138,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.738</v>
+        <v>0.132</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.333</v>
+        <v>-0.198</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
     </row>
@@ -8167,26 +8167,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.159</v>
+        <v>-0.735</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.751</v>
+        <v>-0.332</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
     </row>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.522</v>
+        <v>-3.476</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.084</v>
+        <v>-0.821</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>John Konchar</t>
         </is>
       </c>
     </row>
@@ -8225,26 +8225,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.476</v>
+        <v>-4.111</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.821</v>
+        <v>-0.873</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
     </row>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.113</v>
+        <v>-7.078</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.874</v>
+        <v>-2.406</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Pete Nance</t>
         </is>
       </c>
     </row>
@@ -8295,14 +8295,14 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.635</v>
+        <v>-7.111</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.011</v>
+        <v>-1.659</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
     </row>
@@ -8324,10 +8324,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.544</v>
+        <v>-8.914</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.737</v>
+        <v>-2.554</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -699,20 +699,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.854</v>
+        <v>4.108</v>
       </c>
       <c r="E10" t="n">
-        <v>35.5</v>
+        <v>33.9</v>
       </c>
       <c r="F10" t="n">
         <v>0.867</v>
       </c>
       <c r="G10" t="n">
-        <v>3.488</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="11">
@@ -728,20 +728,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.121</v>
+        <v>3.571</v>
       </c>
       <c r="E11" t="n">
-        <v>32.1</v>
+        <v>33.7</v>
       </c>
       <c r="F11" t="n">
         <v>0.867</v>
       </c>
       <c r="G11" t="n">
-        <v>2.001</v>
+        <v>3.114</v>
       </c>
     </row>
     <row r="12">
@@ -757,20 +757,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.586</v>
+        <v>2.121</v>
       </c>
       <c r="E12" t="n">
-        <v>27.5</v>
+        <v>32.1</v>
       </c>
       <c r="F12" t="n">
         <v>0.867</v>
       </c>
       <c r="G12" t="n">
-        <v>1.975</v>
+        <v>2.001</v>
       </c>
     </row>
     <row r="13">
@@ -786,20 +786,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luka Garza</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.68</v>
+        <v>2.586</v>
       </c>
       <c r="E13" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="F13" t="n">
         <v>0.867</v>
       </c>
       <c r="G13" t="n">
-        <v>1.291</v>
+        <v>1.975</v>
       </c>
     </row>
     <row r="14">
@@ -815,20 +815,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dalano Banton</t>
+          <t>Luka Garza</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.476</v>
+        <v>2.68</v>
       </c>
       <c r="E14" t="n">
-        <v>20.4</v>
+        <v>17.5</v>
       </c>
       <c r="F14" t="n">
         <v>0.867</v>
       </c>
       <c r="G14" t="n">
-        <v>0.572</v>
+        <v>1.291</v>
       </c>
     </row>
     <row r="15">
@@ -844,20 +844,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Dalano Banton</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.151</v>
+        <v>0.476</v>
       </c>
       <c r="E15" t="n">
-        <v>24.7</v>
+        <v>20.4</v>
       </c>
       <c r="F15" t="n">
         <v>0.867</v>
       </c>
       <c r="G15" t="n">
-        <v>0.368</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="16">
@@ -873,20 +873,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Baylor Scheierman</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.738</v>
+        <v>-0.151</v>
       </c>
       <c r="E16" t="n">
-        <v>26.2</v>
+        <v>24.7</v>
       </c>
       <c r="F16" t="n">
         <v>0.867</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="17">
@@ -902,20 +902,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hugo González</t>
+          <t>Baylor Scheierman</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.761</v>
+        <v>-0.738</v>
       </c>
       <c r="E17" t="n">
-        <v>16.6</v>
+        <v>26.2</v>
       </c>
       <c r="F17" t="n">
         <v>0.867</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.654</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -960,20 +960,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ziaire Williams</t>
+          <t>Josh Minott</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.293</v>
+        <v>2.579</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>19.9</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.108</v>
+        <v>1.096</v>
       </c>
     </row>
     <row r="20">
@@ -989,20 +989,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Ziaire Williams</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.87</v>
+        <v>-0.293</v>
       </c>
       <c r="E20" t="n">
-        <v>22.1</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.829</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2.019</v>
+        <v>-1.87</v>
       </c>
       <c r="E21" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.884</v>
+        <v>-0.829</v>
       </c>
     </row>
     <row r="22">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-3.959</v>
+        <v>-2.019</v>
       </c>
       <c r="E22" t="n">
-        <v>15.7</v>
+        <v>21.7</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.276</v>
+        <v>-0.884</v>
       </c>
     </row>
     <row r="23">
@@ -2323,20 +2323,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.304</v>
+        <v>1.746</v>
       </c>
       <c r="E66" t="n">
-        <v>28.6</v>
+        <v>25.6</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>3.695</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="67">
@@ -2352,20 +2352,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.746</v>
+        <v>0.502</v>
       </c>
       <c r="E67" t="n">
-        <v>25.6</v>
+        <v>22.8</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>1.413</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="68">
@@ -2381,20 +2381,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Marcus Sasser</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.502</v>
+        <v>0.475</v>
       </c>
       <c r="E68" t="n">
-        <v>22.8</v>
+        <v>18.7</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.665</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="69">
@@ -2410,17 +2410,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Marcus Sasser</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.475</v>
+        <v>-0.042</v>
       </c>
       <c r="E69" t="n">
-        <v>18.7</v>
+        <v>28.8</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G69" t="n">
         <v>0.535</v>
@@ -2439,20 +2439,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Colby Jones</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.042</v>
+        <v>-0.306</v>
       </c>
       <c r="E70" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0.515</v>
+        <v>0.369</v>
       </c>
     </row>
     <row r="71">
@@ -2468,20 +2468,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Caris LeVert</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.015</v>
+        <v>-1.11</v>
       </c>
       <c r="E71" t="n">
-        <v>26.8</v>
+        <v>18.7</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0.512</v>
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Wendell Moore Jr.</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-0.045</v>
+        <v>-2.211</v>
       </c>
       <c r="E72" t="n">
-        <v>25.5</v>
+        <v>16.9</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>0.453</v>
+        <v>-0.449</v>
       </c>
     </row>
     <row r="73">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Colby Jones</t>
+          <t>Ronald Holland II</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-0.306</v>
+        <v>-2.529</v>
       </c>
       <c r="E73" t="n">
-        <v>28.3</v>
+        <v>17.9</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>0.35</v>
+        <v>-0.594</v>
       </c>
     </row>
     <row r="74">
@@ -2565,10 +2565,10 @@
         <v>22</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G74" t="n">
-        <v>2.213</v>
+        <v>2.229</v>
       </c>
     </row>
     <row r="75">
@@ -2594,10 +2594,10 @@
         <v>23.1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G75" t="n">
-        <v>1.834</v>
+        <v>1.851</v>
       </c>
     </row>
     <row r="76">
@@ -2623,10 +2623,10 @@
         <v>31.6</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G76" t="n">
-        <v>0.994</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="77">
@@ -2652,10 +2652,10 @@
         <v>32.2</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G77" t="n">
-        <v>0.863</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="78">
@@ -2681,10 +2681,10 @@
         <v>20.3</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G78" t="n">
-        <v>0.158</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="79">
@@ -2710,10 +2710,10 @@
         <v>24.6</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G79" t="n">
-        <v>0.154</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="80">
@@ -2739,10 +2739,10 @@
         <v>24.3</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -2768,10 +2768,10 @@
         <v>31</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.442</v>
+        <v>-0.421</v>
       </c>
     </row>
     <row r="82">
@@ -3019,20 +3019,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>T.J. McConnell</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>5.653</v>
+        <v>2.178</v>
       </c>
       <c r="E90" t="n">
-        <v>19</v>
+        <v>30.8</v>
       </c>
       <c r="F90" t="n">
         <v>0.133</v>
       </c>
       <c r="G90" t="n">
-        <v>2.29</v>
+        <v>1.482</v>
       </c>
     </row>
     <row r="91">
@@ -3048,20 +3048,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.178</v>
+        <v>2.567</v>
       </c>
       <c r="E91" t="n">
-        <v>30.8</v>
+        <v>22.3</v>
       </c>
       <c r="F91" t="n">
         <v>0.133</v>
       </c>
       <c r="G91" t="n">
-        <v>1.482</v>
+        <v>1.254</v>
       </c>
     </row>
     <row r="92">
@@ -3077,20 +3077,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2.567</v>
+        <v>1.494</v>
       </c>
       <c r="E92" t="n">
-        <v>22.3</v>
+        <v>28.5</v>
       </c>
       <c r="F92" t="n">
         <v>0.133</v>
       </c>
       <c r="G92" t="n">
-        <v>1.254</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.494</v>
+        <v>-2.386</v>
       </c>
       <c r="E93" t="n">
-        <v>28.5</v>
+        <v>19.5</v>
       </c>
       <c r="F93" t="n">
         <v>0.133</v>
       </c>
       <c r="G93" t="n">
-        <v>0.967</v>
+        <v>-0.917</v>
       </c>
     </row>
     <row r="94">
@@ -3135,20 +3135,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-2.194</v>
+        <v>-1.59</v>
       </c>
       <c r="E94" t="n">
-        <v>19.3</v>
+        <v>32.5</v>
       </c>
       <c r="F94" t="n">
         <v>0.133</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.829</v>
+        <v>-0.985</v>
       </c>
     </row>
     <row r="95">
@@ -3164,20 +3164,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.386</v>
+        <v>-2.577</v>
       </c>
       <c r="E95" t="n">
-        <v>19.5</v>
+        <v>21.4</v>
       </c>
       <c r="F95" t="n">
         <v>0.133</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.917</v>
+        <v>-1.089</v>
       </c>
     </row>
     <row r="96">
@@ -3193,20 +3193,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.577</v>
+        <v>-2.466</v>
       </c>
       <c r="E96" t="n">
-        <v>21.4</v>
+        <v>28.8</v>
       </c>
       <c r="F96" t="n">
         <v>0.133</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.089</v>
+        <v>-1.401</v>
       </c>
     </row>
     <row r="97">
@@ -4179,20 +4179,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>-0.15</v>
+        <v>2.315</v>
       </c>
       <c r="E130" t="n">
-        <v>21.6</v>
+        <v>31.2</v>
       </c>
       <c r="F130" t="n">
         <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>0.022</v>
+        <v>1.635</v>
       </c>
     </row>
     <row r="131">
@@ -4208,20 +4208,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cole Anthony</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-2.31</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E131" t="n">
-        <v>15.9</v>
+        <v>22.9</v>
       </c>
       <c r="F131" t="n">
         <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.698</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="132">
@@ -4237,20 +4237,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-1.984</v>
+        <v>-0.15</v>
       </c>
       <c r="E132" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="F132" t="n">
         <v>0.2</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.8</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-1.646</v>
+        <v>-1.984</v>
       </c>
       <c r="E133" t="n">
-        <v>29</v>
+        <v>21.5</v>
       </c>
       <c r="F133" t="n">
         <v>0.2</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.873</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.919</v>
+        <v>-1.646</v>
       </c>
       <c r="E134" t="n">
-        <v>15.7</v>
+        <v>29</v>
       </c>
       <c r="F134" t="n">
         <v>0.2</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.888</v>
+        <v>-0.873</v>
       </c>
     </row>
     <row r="135">
@@ -4885,10 +4885,10 @@
         <v>36.6</v>
       </c>
       <c r="F154" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G154" t="n">
-        <v>3.758</v>
+        <v>3.733</v>
       </c>
     </row>
     <row r="155">
@@ -4914,10 +4914,10 @@
         <v>30</v>
       </c>
       <c r="F155" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G155" t="n">
-        <v>2.713</v>
+        <v>2.692</v>
       </c>
     </row>
     <row r="156">
@@ -4943,10 +4943,10 @@
         <v>29.1</v>
       </c>
       <c r="F156" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G156" t="n">
-        <v>2.177</v>
+        <v>2.157</v>
       </c>
     </row>
     <row r="157">
@@ -4972,10 +4972,10 @@
         <v>20.1</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G157" t="n">
-        <v>2.029</v>
+        <v>2.015</v>
       </c>
     </row>
     <row r="158">
@@ -5001,10 +5001,10 @@
         <v>29.2</v>
       </c>
       <c r="F158" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G158" t="n">
-        <v>1.955</v>
+        <v>1.934</v>
       </c>
     </row>
     <row r="159">
@@ -5030,10 +5030,10 @@
         <v>33.5</v>
       </c>
       <c r="F159" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G159" t="n">
-        <v>1.87</v>
+        <v>1.847</v>
       </c>
     </row>
     <row r="160">
@@ -5049,20 +5049,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Jordan Clarkson</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1.391</v>
+        <v>-2.632</v>
       </c>
       <c r="E160" t="n">
-        <v>30.6</v>
+        <v>17.3</v>
       </c>
       <c r="F160" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G160" t="n">
-        <v>1.481</v>
+        <v>-0.624</v>
       </c>
     </row>
     <row r="161">
@@ -5088,10 +5088,10 @@
         <v>18.1</v>
       </c>
       <c r="F161" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G161" t="n">
-        <v>-1.302</v>
+        <v>-1.315</v>
       </c>
     </row>
     <row r="162">
@@ -5165,20 +5165,20 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4.001</v>
+        <v>1.878</v>
       </c>
       <c r="E164" t="n">
-        <v>22.4</v>
+        <v>25.7</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>2.336</v>
+        <v>1.539</v>
       </c>
     </row>
     <row r="165">
@@ -5194,20 +5194,20 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2.079</v>
+        <v>1.807</v>
       </c>
       <c r="E165" t="n">
-        <v>27</v>
+        <v>23.1</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>1.731</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="166">
@@ -5223,20 +5223,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1.878</v>
+        <v>0.068</v>
       </c>
       <c r="E166" t="n">
-        <v>25.7</v>
+        <v>24.5</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1.539</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="167">
@@ -5252,20 +5252,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.807</v>
+        <v>-1.31</v>
       </c>
       <c r="E167" t="n">
-        <v>23.1</v>
+        <v>19</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1.352</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="168">
@@ -5281,20 +5281,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.068</v>
+        <v>-1.382</v>
       </c>
       <c r="E168" t="n">
-        <v>24.5</v>
+        <v>18.6</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.546</v>
+        <v>-0.148</v>
       </c>
     </row>
     <row r="169">
@@ -5581,10 +5581,10 @@
         <v>35.8</v>
       </c>
       <c r="F178" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G178" t="n">
-        <v>5.31</v>
+        <v>5.285</v>
       </c>
     </row>
     <row r="179">
@@ -5610,10 +5610,10 @@
         <v>33</v>
       </c>
       <c r="F179" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G179" t="n">
-        <v>4.042</v>
+        <v>4.019</v>
       </c>
     </row>
     <row r="180">
@@ -5639,10 +5639,10 @@
         <v>31.9</v>
       </c>
       <c r="F180" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G180" t="n">
-        <v>1.86</v>
+        <v>1.838</v>
       </c>
     </row>
     <row r="181">
@@ -5668,10 +5668,10 @@
         <v>32.3</v>
       </c>
       <c r="F181" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G181" t="n">
-        <v>0.189</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="182">
@@ -5697,10 +5697,10 @@
         <v>24.2</v>
       </c>
       <c r="F182" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G182" t="n">
-        <v>0.152</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="183">
@@ -5726,10 +5726,10 @@
         <v>24.3</v>
       </c>
       <c r="F183" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.123</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="184">
@@ -5755,10 +5755,10 @@
         <v>34.3</v>
       </c>
       <c r="F184" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.152</v>
+        <v>-0.176</v>
       </c>
     </row>
     <row r="185">
@@ -5784,10 +5784,10 @@
         <v>31.4</v>
       </c>
       <c r="F185" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.278</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="186">
@@ -5813,10 +5813,10 @@
         <v>29.7</v>
       </c>
       <c r="F186" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G186" t="n">
-        <v>2.431</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="187">
@@ -5842,10 +5842,10 @@
         <v>34.5</v>
       </c>
       <c r="F187" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G187" t="n">
-        <v>2.15</v>
+        <v>2.126</v>
       </c>
     </row>
     <row r="188">
@@ -5871,10 +5871,10 @@
         <v>27.6</v>
       </c>
       <c r="F188" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G188" t="n">
-        <v>2.073</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="189">
@@ -5900,10 +5900,10 @@
         <v>23.5</v>
       </c>
       <c r="F189" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G189" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="190">
@@ -5929,10 +5929,10 @@
         <v>27.4</v>
       </c>
       <c r="F190" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G190" t="n">
-        <v>0.499</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="191">
@@ -5958,10 +5958,10 @@
         <v>29</v>
       </c>
       <c r="F191" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G191" t="n">
-        <v>0.355</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="192">
@@ -5987,10 +5987,10 @@
         <v>32.1</v>
       </c>
       <c r="F192" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.64</v>
+        <v>-0.662</v>
       </c>
     </row>
     <row r="193">
@@ -6016,10 +6016,10 @@
         <v>20.6</v>
       </c>
       <c r="F193" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G193" t="n">
-        <v>-0.655</v>
+        <v>-0.669</v>
       </c>
     </row>
     <row r="194">
@@ -6035,20 +6035,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>6.714</v>
+        <v>3.79</v>
       </c>
       <c r="E194" t="n">
-        <v>19.6</v>
+        <v>30.9</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>2.887</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="195">
@@ -6064,20 +6064,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3.79</v>
+        <v>3.749</v>
       </c>
       <c r="E195" t="n">
-        <v>30.9</v>
+        <v>26.8</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>2.68</v>
+        <v>2.298</v>
       </c>
     </row>
     <row r="196">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3.749</v>
+        <v>2.661</v>
       </c>
       <c r="E196" t="n">
-        <v>26.8</v>
+        <v>28.7</v>
       </c>
       <c r="F196" t="n">
         <v>0.367</v>
       </c>
       <c r="G196" t="n">
-        <v>2.298</v>
+        <v>1.809</v>
       </c>
     </row>
     <row r="197">
@@ -6122,20 +6122,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Jerami Grant</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2.661</v>
+        <v>0.099</v>
       </c>
       <c r="E197" t="n">
-        <v>28.7</v>
+        <v>31.8</v>
       </c>
       <c r="F197" t="n">
         <v>0.367</v>
       </c>
       <c r="G197" t="n">
-        <v>1.809</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="198">
@@ -6267,20 +6267,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.674</v>
+        <v>1.394</v>
       </c>
       <c r="E202" t="n">
-        <v>32.5</v>
+        <v>30.6</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>0.523</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="203">
@@ -6296,20 +6296,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.613</v>
+        <v>0.674</v>
       </c>
       <c r="E203" t="n">
-        <v>20.6</v>
+        <v>32.5</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.307</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="204">
@@ -6325,20 +6325,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>-1.125</v>
+        <v>0.613</v>
       </c>
       <c r="E204" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.438</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="205">
@@ -6354,20 +6354,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-0.893</v>
+        <v>0.465</v>
       </c>
       <c r="E205" t="n">
-        <v>33.7</v>
+        <v>23.3</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="206">
@@ -6383,20 +6383,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Doug McDermott</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-2.197</v>
+        <v>-0.893</v>
       </c>
       <c r="E206" t="n">
-        <v>18.6</v>
+        <v>33.7</v>
       </c>
       <c r="F206" t="n">
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.5570000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -6741,10 +6741,10 @@
         <v>32.2</v>
       </c>
       <c r="F218" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G218" t="n">
-        <v>3.13</v>
+        <v>3.153</v>
       </c>
     </row>
     <row r="219">
@@ -6770,10 +6770,10 @@
         <v>20.1</v>
       </c>
       <c r="F219" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G219" t="n">
-        <v>1.68</v>
+        <v>1.694</v>
       </c>
     </row>
     <row r="220">
@@ -6799,10 +6799,10 @@
         <v>27.1</v>
       </c>
       <c r="F220" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G220" t="n">
-        <v>1.393</v>
+        <v>1.412</v>
       </c>
     </row>
     <row r="221">
@@ -6828,10 +6828,10 @@
         <v>30.9</v>
       </c>
       <c r="F221" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G221" t="n">
-        <v>1.228</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="222">
@@ -6847,20 +6847,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>-0.346</v>
+        <v>0.866</v>
       </c>
       <c r="E222" t="n">
-        <v>20.7</v>
+        <v>34</v>
       </c>
       <c r="F222" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G222" t="n">
-        <v>0.066</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="223">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>A.J. Lawson</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>-1.523</v>
+        <v>1.392</v>
       </c>
       <c r="E223" t="n">
-        <v>15.6</v>
+        <v>23</v>
       </c>
       <c r="F223" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G223" t="n">
-        <v>-0.333</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="224">
@@ -6905,20 +6905,20 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-1.279</v>
+        <v>-0.346</v>
       </c>
       <c r="E224" t="n">
-        <v>22.3</v>
+        <v>20.7</v>
       </c>
       <c r="F224" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.362</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="225">
@@ -6934,20 +6934,20 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Gradey Dick</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-2.664</v>
+        <v>-1.279</v>
       </c>
       <c r="E225" t="n">
-        <v>15.4</v>
+        <v>22.3</v>
       </c>
       <c r="F225" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.695</v>
+        <v>-0.347</v>
       </c>
     </row>
     <row r="226">
@@ -7195,20 +7195,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>2.474</v>
+        <v>3.241</v>
       </c>
       <c r="E234" t="n">
-        <v>20.6</v>
+        <v>22.3</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>1.074</v>
+        <v>1.518</v>
       </c>
     </row>
     <row r="235">
@@ -7224,20 +7224,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Tristan Vukcevic</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1.016</v>
+        <v>-0.26</v>
       </c>
       <c r="E235" t="n">
-        <v>17.7</v>
+        <v>29.2</v>
       </c>
       <c r="F235" t="n">
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>0.387</v>
+        <v>-0.138</v>
       </c>
     </row>
     <row r="236">
@@ -7253,20 +7253,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.26</v>
+        <v>-0.9</v>
       </c>
       <c r="E236" t="n">
-        <v>29.2</v>
+        <v>21.6</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.138</v>
+        <v>-0.389</v>
       </c>
     </row>
     <row r="237">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-0.9</v>
+        <v>-1.226</v>
       </c>
       <c r="E237" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.389</v>
+        <v>-0.5620000000000001</v>
       </c>
     </row>
     <row r="238">
@@ -7311,20 +7311,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-1.226</v>
+        <v>-2.701</v>
       </c>
       <c r="E238" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="F238" t="n">
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-1.275</v>
       </c>
     </row>
     <row r="239">
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>18.617</v>
+        <v>15.644</v>
       </c>
       <c r="F4" t="n">
-        <v>2.798</v>
+        <v>2.103</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7558,26 +7558,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>15.644</v>
+        <v>15.067</v>
       </c>
       <c r="F5" t="n">
-        <v>2.103</v>
+        <v>2.243</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7587,26 +7587,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>15.067</v>
+        <v>14.279</v>
       </c>
       <c r="F6" t="n">
-        <v>2.243</v>
+        <v>1.701</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
     </row>
@@ -7616,26 +7616,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>14.681</v>
+        <v>12.902</v>
       </c>
       <c r="F7" t="n">
-        <v>1.873</v>
+        <v>1.832</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
     </row>
@@ -7645,26 +7645,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>11.55</v>
+        <v>12.439</v>
       </c>
       <c r="F8" t="n">
-        <v>1.561</v>
+        <v>1.37</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -7674,26 +7674,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>11.533</v>
+        <v>11.55</v>
       </c>
       <c r="F9" t="n">
-        <v>1.727</v>
+        <v>1.561</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7703,26 +7703,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>11.533</v>
       </c>
       <c r="F10" t="n">
-        <v>1.504</v>
+        <v>1.727</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7732,26 +7732,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>9.914999999999999</v>
+        <v>10.828</v>
       </c>
       <c r="F11" t="n">
-        <v>1.26</v>
+        <v>1.504</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>9.159000000000001</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.227</v>
+        <v>1.26</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>9.112</v>
+        <v>9.159000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.008</v>
+        <v>1.227</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7819,26 +7819,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>8.945</v>
+        <v>9.154999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.167</v>
+        <v>1.461</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7848,26 +7848,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>8.917</v>
+        <v>8.945</v>
       </c>
       <c r="F15" t="n">
-        <v>0.68</v>
+        <v>1.167</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
     </row>
@@ -7877,26 +7877,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>8.138</v>
+        <v>8.917</v>
       </c>
       <c r="F16" t="n">
-        <v>0.956</v>
+        <v>0.68</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7906,26 +7906,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>7.224</v>
+        <v>6.868</v>
       </c>
       <c r="F17" t="n">
-        <v>1.359</v>
+        <v>0.861</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
     </row>
@@ -7935,26 +7935,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>7.023</v>
+        <v>5.833</v>
       </c>
       <c r="F18" t="n">
-        <v>0.861</v>
+        <v>1.008</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>6.107</v>
+        <v>4.646</v>
       </c>
       <c r="F19" t="n">
-        <v>0.655</v>
+        <v>0.532</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.687</v>
+        <v>4.534</v>
       </c>
       <c r="F20" t="n">
-        <v>1.008</v>
+        <v>0.478</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
     </row>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>4.534</v>
+        <v>4.092</v>
       </c>
       <c r="F21" t="n">
-        <v>0.478</v>
+        <v>0.118</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
     </row>
@@ -8051,26 +8051,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.092</v>
+        <v>3.413</v>
       </c>
       <c r="F22" t="n">
-        <v>0.118</v>
+        <v>0.116</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
     </row>
@@ -8080,26 +8080,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>3.413</v>
+        <v>2.451</v>
       </c>
       <c r="F23" t="n">
-        <v>0.116</v>
+        <v>-0.434</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
     </row>
@@ -8109,26 +8109,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>1.691</v>
+        <v>0.132</v>
       </c>
       <c r="F24" t="n">
-        <v>0.189</v>
+        <v>-0.198</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>T.J. McConnell</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
     </row>
@@ -8138,26 +8138,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>0.132</v>
+        <v>-0.735</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.198</v>
+        <v>-0.332</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
     </row>
@@ -8167,26 +8167,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.735</v>
+        <v>-2.156</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.332</v>
+        <v>-0.751</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
     </row>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.476</v>
+        <v>-3.373</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.821</v>
+        <v>-1.361</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
     </row>
@@ -8225,26 +8225,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.111</v>
+        <v>-3.476</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.873</v>
+        <v>-0.821</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>John Konchar</t>
         </is>
       </c>
     </row>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.078</v>
+        <v>-4.634</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.406</v>
+        <v>-1.011</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
     </row>
@@ -8283,26 +8283,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.111</v>
+        <v>-5.329</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.659</v>
+        <v>-1.242</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
     </row>
@@ -8324,10 +8324,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-8.914</v>
+        <v>-6.542</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.554</v>
+        <v>-1.737</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.142</v>
+        <v>8.407</v>
       </c>
       <c r="E2" t="n">
-        <v>36.6</v>
+        <v>34.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5.119</v>
+        <v>8.887</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.259</v>
+        <v>3.577</v>
       </c>
       <c r="E3" t="n">
-        <v>33.3</v>
+        <v>32.7</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.963</v>
+        <v>4.055</v>
       </c>
     </row>
     <row r="4">
@@ -525,20 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.264</v>
+        <v>2.485</v>
       </c>
       <c r="E4" t="n">
-        <v>27.9</v>
+        <v>31.7</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.644</v>
+        <v>2.955</v>
       </c>
     </row>
     <row r="5">
@@ -554,20 +554,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.682</v>
+        <v>2.439</v>
       </c>
       <c r="E5" t="n">
-        <v>32.6</v>
+        <v>28.2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.526</v>
+        <v>2.723</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.322</v>
+        <v>2.264</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.14</v>
+        <v>2.628</v>
       </c>
     </row>
     <row r="7">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.296</v>
+        <v>0.72</v>
       </c>
       <c r="E7" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.707</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="8">
@@ -641,20 +641,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.195</v>
+        <v>-1.786</v>
       </c>
       <c r="E8" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.271</v>
+        <v>-0.091</v>
       </c>
     </row>
     <row r="9">
@@ -670,20 +670,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.284</v>
+        <v>-1.945</v>
       </c>
       <c r="E9" t="n">
-        <v>18.6</v>
+        <v>19.8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.278</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="10">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.108</v>
+        <v>6.502</v>
       </c>
       <c r="E10" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="F10" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>3.51</v>
+        <v>7.387</v>
       </c>
     </row>
     <row r="11">
@@ -728,20 +728,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.571</v>
+        <v>5.036</v>
       </c>
       <c r="E11" t="n">
-        <v>33.7</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>3.114</v>
+        <v>5.928</v>
       </c>
     </row>
     <row r="12">
@@ -757,20 +757,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.121</v>
+        <v>5.043</v>
       </c>
       <c r="E12" t="n">
-        <v>32.1</v>
+        <v>33.9</v>
       </c>
       <c r="F12" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>2.001</v>
+        <v>5.928</v>
       </c>
     </row>
     <row r="13">
@@ -786,20 +786,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.586</v>
+        <v>4.054</v>
       </c>
       <c r="E13" t="n">
-        <v>27.5</v>
+        <v>32.2</v>
       </c>
       <c r="F13" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>1.975</v>
+        <v>4.917</v>
       </c>
     </row>
     <row r="14">
@@ -815,20 +815,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luka Garza</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.68</v>
+        <v>2.102</v>
       </c>
       <c r="E14" t="n">
-        <v>17.5</v>
+        <v>25.9</v>
       </c>
       <c r="F14" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.291</v>
+        <v>2.283</v>
       </c>
     </row>
     <row r="15">
@@ -844,20 +844,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dalano Banton</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.476</v>
+        <v>-0.79</v>
       </c>
       <c r="E15" t="n">
-        <v>20.4</v>
+        <v>26.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.572</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -873,20 +873,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Dalano Banton</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.151</v>
+        <v>-0.329</v>
       </c>
       <c r="E16" t="n">
-        <v>24.7</v>
+        <v>17.9</v>
       </c>
       <c r="F16" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.368</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.738</v>
+        <v>-1.449</v>
       </c>
       <c r="E17" t="n">
-        <v>26.2</v>
+        <v>27.1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.475</v>
       </c>
     </row>
     <row r="18">
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.457</v>
+        <v>3.046</v>
       </c>
       <c r="E18" t="n">
-        <v>22.6</v>
+        <v>23.1</v>
       </c>
       <c r="F18" t="n">
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>1.186</v>
+        <v>1.154</v>
       </c>
     </row>
     <row r="19">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.579</v>
+        <v>2.025</v>
       </c>
       <c r="E19" t="n">
-        <v>19.9</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>1.096</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20">
@@ -989,20 +989,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ziaire Williams</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.293</v>
+        <v>-4.698</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.108</v>
+        <v>-0.038</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Ziaire Williams</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.87</v>
+        <v>-0.883</v>
       </c>
       <c r="E21" t="n">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.829</v>
+        <v>-0.258</v>
       </c>
     </row>
     <row r="22">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.019</v>
+        <v>-1.994</v>
       </c>
       <c r="E22" t="n">
-        <v>21.7</v>
+        <v>23.9</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.884</v>
+        <v>-0.9340000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4.857</v>
+        <v>-5.274</v>
       </c>
       <c r="E23" t="n">
-        <v>20.6</v>
+        <v>22.5</v>
       </c>
       <c r="F23" t="n">
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.055</v>
+        <v>-1.524</v>
       </c>
     </row>
     <row r="24">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-4.681</v>
+        <v>-4.898</v>
       </c>
       <c r="E24" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
         <v>0.067</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.356</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="25">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-5.211</v>
+        <v>-6.069</v>
       </c>
       <c r="E25" t="n">
-        <v>24.2</v>
+        <v>23.2</v>
       </c>
       <c r="F25" t="n">
         <v>0.067</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.592</v>
+        <v>-2.336</v>
       </c>
     </row>
     <row r="26">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.618</v>
+        <v>7.158</v>
       </c>
       <c r="E26" t="n">
-        <v>28.2</v>
+        <v>28.5</v>
       </c>
       <c r="F26" t="n">
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.711</v>
+        <v>7.372</v>
       </c>
     </row>
     <row r="27">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3.725</v>
+        <v>4.533</v>
       </c>
       <c r="E27" t="n">
-        <v>29.3</v>
+        <v>30.1</v>
       </c>
       <c r="F27" t="n">
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>2.697</v>
+        <v>5.104</v>
       </c>
     </row>
     <row r="28">
@@ -1225,16 +1225,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.036</v>
+        <v>2.666</v>
       </c>
       <c r="E28" t="n">
-        <v>31.3</v>
+        <v>30.7</v>
       </c>
       <c r="F28" t="n">
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1.784</v>
+        <v>3.307</v>
       </c>
     </row>
     <row r="29">
@@ -1250,20 +1250,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.842</v>
+        <v>1.207</v>
       </c>
       <c r="E29" t="n">
-        <v>28.7</v>
+        <v>29.7</v>
       </c>
       <c r="F29" t="n">
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.519</v>
+        <v>1.845</v>
       </c>
     </row>
     <row r="30">
@@ -1279,20 +1279,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.6</v>
+        <v>1.185</v>
       </c>
       <c r="E30" t="n">
-        <v>29.2</v>
+        <v>28.1</v>
       </c>
       <c r="F30" t="n">
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>0.79</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="31">
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.866</v>
+        <v>0.827</v>
       </c>
       <c r="E31" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
       <c r="F31" t="n">
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0.674</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="32">
@@ -1337,11 +1337,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Antonio Reeves</t>
+          <t>Grant Williams</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1.467</v>
+        <v>-0.832</v>
       </c>
       <c r="E32" t="n">
         <v>19.2</v>
@@ -1350,7 +1350,7 @@
         <v>0.7</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.306</v>
+        <v>-0.007</v>
       </c>
     </row>
     <row r="33">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-3.143</v>
+        <v>-3.619</v>
       </c>
       <c r="E33" t="n">
-        <v>18.7</v>
+        <v>18.1</v>
       </c>
       <c r="F33" t="n">
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.954</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="34">
@@ -1399,16 +1399,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.311</v>
+        <v>5.796</v>
       </c>
       <c r="E34" t="n">
-        <v>35.8</v>
+        <v>34.1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G34" t="n">
-        <v>3.436</v>
+        <v>6.115</v>
       </c>
     </row>
     <row r="35">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.573</v>
+        <v>3.963</v>
       </c>
       <c r="E35" t="n">
-        <v>29.2</v>
+        <v>28.8</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G35" t="n">
-        <v>2.36</v>
+        <v>4.064</v>
       </c>
     </row>
     <row r="36">
@@ -1453,20 +1453,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.074</v>
+        <v>1.428</v>
       </c>
       <c r="E36" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G36" t="n">
-        <v>1.234</v>
+        <v>1.754</v>
       </c>
     </row>
     <row r="37">
@@ -1482,20 +1482,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.068</v>
+        <v>2.264</v>
       </c>
       <c r="E37" t="n">
-        <v>34</v>
+        <v>23.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G37" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="38">
@@ -1515,16 +1515,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-0.643</v>
+        <v>-1.236</v>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.179</v>
+        <v>-0.463</v>
       </c>
     </row>
     <row r="39">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1.419</v>
+        <v>-2.006</v>
       </c>
       <c r="E39" t="n">
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.556</v>
+        <v>-0.881</v>
       </c>
     </row>
     <row r="40">
@@ -1569,20 +1569,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Patrick Williams</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-2.789</v>
+        <v>-4.132</v>
       </c>
       <c r="E40" t="n">
-        <v>30.9</v>
+        <v>22.3</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6</v>
+        <v>-1.005</v>
       </c>
     </row>
     <row r="41">
@@ -1598,20 +1598,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rob Dillingham</t>
+          <t>Isaac Okoro</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-5.247</v>
+        <v>-3.45</v>
       </c>
       <c r="E41" t="n">
-        <v>21.9</v>
+        <v>30.7</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.252</v>
+        <v>-3.061</v>
       </c>
     </row>
     <row r="42">
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7.09</v>
+        <v>9.026</v>
       </c>
       <c r="E42" t="n">
-        <v>34.1</v>
+        <v>32.6</v>
       </c>
       <c r="F42" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G42" t="n">
-        <v>5.579</v>
+        <v>9.771000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1660,16 +1660,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5.948</v>
+        <v>8.439</v>
       </c>
       <c r="E43" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="F43" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G43" t="n">
-        <v>4.989</v>
+        <v>9.226000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.863</v>
+        <v>4.376</v>
       </c>
       <c r="E44" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="F44" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G44" t="n">
-        <v>3.019</v>
+        <v>5.091</v>
       </c>
     </row>
     <row r="45">
@@ -1714,20 +1714,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.808</v>
+        <v>3.717</v>
       </c>
       <c r="E45" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="F45" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G45" t="n">
-        <v>1.541</v>
+        <v>4.185</v>
       </c>
     </row>
     <row r="46">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Keon Ellis</t>
+          <t>Max Strus</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-0.214</v>
+        <v>0.65</v>
       </c>
       <c r="E46" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="F46" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G46" t="n">
-        <v>0.309</v>
+        <v>1.284</v>
       </c>
     </row>
     <row r="47">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lonzo Ball</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.337</v>
+        <v>-0.571</v>
       </c>
       <c r="E47" t="n">
-        <v>16.4</v>
+        <v>22.5</v>
       </c>
       <c r="F47" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G47" t="n">
-        <v>0.147</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="48">
@@ -1801,20 +1801,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nae'Qwan Tomlin</t>
+          <t>Craig Porter Jr.</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.42</v>
+        <v>1.956</v>
       </c>
       <c r="E48" t="n">
-        <v>16.6</v>
+        <v>17.7</v>
       </c>
       <c r="F48" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="49">
@@ -1830,20 +1830,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.917</v>
+        <v>-0.76</v>
       </c>
       <c r="E49" t="n">
-        <v>19.2</v>
+        <v>26.4</v>
       </c>
       <c r="F49" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.06</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="50">
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.355</v>
+        <v>2.618</v>
       </c>
       <c r="E50" t="n">
-        <v>33.9</v>
+        <v>32.9</v>
       </c>
       <c r="F50" t="n">
         <v>0.233</v>
       </c>
       <c r="G50" t="n">
-        <v>1.12</v>
+        <v>2.838</v>
       </c>
     </row>
     <row r="51">
@@ -1888,20 +1888,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Marvin Bagley III</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.445</v>
+        <v>1.489</v>
       </c>
       <c r="E51" t="n">
-        <v>19.4</v>
+        <v>23.4</v>
       </c>
       <c r="F51" t="n">
         <v>0.233</v>
       </c>
       <c r="G51" t="n">
-        <v>1.081</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="52">
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.8169999999999999</v>
+        <v>1.075</v>
       </c>
       <c r="E52" t="n">
-        <v>20.4</v>
+        <v>21.9</v>
       </c>
       <c r="F52" t="n">
         <v>0.233</v>
       </c>
       <c r="G52" t="n">
-        <v>0.447</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="53">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Dwight Powell</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-0.109</v>
+        <v>-2.099</v>
       </c>
       <c r="E53" t="n">
-        <v>29.7</v>
+        <v>16.5</v>
       </c>
       <c r="F53" t="n">
         <v>0.233</v>
       </c>
       <c r="G53" t="n">
-        <v>0.077</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="54">
@@ -1975,20 +1975,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Ryan Nembhard</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-0.889</v>
+        <v>-2.001</v>
       </c>
       <c r="E54" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="F54" t="n">
         <v>0.233</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.289</v>
+        <v>-0.042</v>
       </c>
     </row>
     <row r="55">
@@ -2004,20 +2004,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.225</v>
+        <v>-4.443</v>
       </c>
       <c r="E55" t="n">
-        <v>31.8</v>
+        <v>17.6</v>
       </c>
       <c r="F55" t="n">
         <v>0.233</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.656</v>
+        <v>-0.089</v>
       </c>
     </row>
     <row r="56">
@@ -2033,20 +2033,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-1.399</v>
+        <v>-2.787</v>
       </c>
       <c r="E56" t="n">
-        <v>28.1</v>
+        <v>21.4</v>
       </c>
       <c r="F56" t="n">
         <v>0.233</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="57">
@@ -2062,20 +2062,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-2.582</v>
+        <v>-1.541</v>
       </c>
       <c r="E57" t="n">
-        <v>19.7</v>
+        <v>28.8</v>
       </c>
       <c r="F57" t="n">
         <v>0.233</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.966</v>
+        <v>-1.236</v>
       </c>
     </row>
     <row r="58">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.216</v>
+        <v>18.207</v>
       </c>
       <c r="E58" t="n">
         <v>36.2</v>
@@ -2104,7 +2104,7 @@
         <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>12.101</v>
+        <v>19.028</v>
       </c>
     </row>
     <row r="59">
@@ -2124,16 +2124,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6.405</v>
+        <v>9.095000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>36.1</v>
+        <v>35.5</v>
       </c>
       <c r="F59" t="n">
         <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>5.438</v>
+        <v>9.917999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.443</v>
+        <v>2.869</v>
       </c>
       <c r="E60" t="n">
-        <v>25.9</v>
+        <v>27.6</v>
       </c>
       <c r="F60" t="n">
         <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>2.308</v>
+        <v>3.321</v>
       </c>
     </row>
     <row r="61">
@@ -2182,16 +2182,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.754</v>
+        <v>0.08</v>
       </c>
       <c r="E61" t="n">
-        <v>33.6</v>
+        <v>32.7</v>
       </c>
       <c r="F61" t="n">
         <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>1.11</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="62">
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.468</v>
+        <v>0.334</v>
       </c>
       <c r="E62" t="n">
-        <v>24.7</v>
+        <v>25.9</v>
       </c>
       <c r="F62" t="n">
         <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="63">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-0.516</v>
+        <v>-1.142</v>
       </c>
       <c r="E63" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="F63" t="n">
         <v>0.833</v>
       </c>
       <c r="G63" t="n">
-        <v>0.197</v>
+        <v>-0.298</v>
       </c>
     </row>
     <row r="64">
@@ -2265,20 +2265,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1.342</v>
+        <v>-2.833</v>
       </c>
       <c r="E64" t="n">
-        <v>32.3</v>
+        <v>21.9</v>
       </c>
       <c r="F64" t="n">
         <v>0.833</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.342</v>
+        <v>-0.446</v>
       </c>
     </row>
     <row r="65">
@@ -2294,20 +2294,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-2.514</v>
+        <v>-1.987</v>
       </c>
       <c r="E65" t="n">
-        <v>21.4</v>
+        <v>32.3</v>
       </c>
       <c r="F65" t="n">
         <v>0.833</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.748</v>
+        <v>-1.146</v>
       </c>
     </row>
     <row r="66">
@@ -2323,20 +2323,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.746</v>
+        <v>5.549</v>
       </c>
       <c r="E66" t="n">
-        <v>25.6</v>
+        <v>27.8</v>
       </c>
       <c r="F66" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>1.43</v>
+        <v>5.868</v>
       </c>
     </row>
     <row r="67">
@@ -2352,20 +2352,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.502</v>
+        <v>1.524</v>
       </c>
       <c r="E67" t="n">
-        <v>22.8</v>
+        <v>26.3</v>
       </c>
       <c r="F67" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>0.681</v>
+        <v>1.956</v>
       </c>
     </row>
     <row r="68">
@@ -2381,20 +2381,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Marcus Sasser</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.475</v>
+        <v>-0.26</v>
       </c>
       <c r="E68" t="n">
-        <v>18.7</v>
+        <v>28.9</v>
       </c>
       <c r="F68" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.548</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="69">
@@ -2410,20 +2410,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.042</v>
+        <v>-0.177</v>
       </c>
       <c r="E69" t="n">
-        <v>28.8</v>
+        <v>26.5</v>
       </c>
       <c r="F69" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>0.535</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="70">
@@ -2439,20 +2439,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Colby Jones</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.306</v>
+        <v>-0.417</v>
       </c>
       <c r="E70" t="n">
-        <v>28.3</v>
+        <v>25.9</v>
       </c>
       <c r="F70" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0.369</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="71">
@@ -2468,20 +2468,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Caris LeVert</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-1.11</v>
+        <v>-0.036</v>
       </c>
       <c r="E71" t="n">
-        <v>18.7</v>
+        <v>20.7</v>
       </c>
       <c r="F71" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="72">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wendell Moore Jr.</t>
+          <t>Colby Jones</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-2.211</v>
+        <v>-0.919</v>
       </c>
       <c r="E72" t="n">
-        <v>16.9</v>
+        <v>23.4</v>
       </c>
       <c r="F72" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.449</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="73">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ronald Holland II</t>
+          <t>Caris LeVert</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-2.529</v>
+        <v>-1.605</v>
       </c>
       <c r="E73" t="n">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="F73" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.594</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="74">
@@ -2555,20 +2555,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.436</v>
+        <v>1.659</v>
       </c>
       <c r="E74" t="n">
-        <v>22</v>
+        <v>33.4</v>
       </c>
       <c r="F74" t="n">
         <v>0.433</v>
       </c>
       <c r="G74" t="n">
-        <v>2.229</v>
+        <v>2.084</v>
       </c>
     </row>
     <row r="75">
@@ -2584,20 +2584,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gary Payton II</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3.415</v>
+        <v>0.822</v>
       </c>
       <c r="E75" t="n">
-        <v>23.1</v>
+        <v>32.4</v>
       </c>
       <c r="F75" t="n">
         <v>0.433</v>
       </c>
       <c r="G75" t="n">
-        <v>1.851</v>
+        <v>1.247</v>
       </c>
     </row>
     <row r="76">
@@ -2613,20 +2613,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.11</v>
+        <v>4.31</v>
       </c>
       <c r="E76" t="n">
-        <v>31.6</v>
+        <v>21.6</v>
       </c>
       <c r="F76" t="n">
         <v>0.433</v>
       </c>
       <c r="G76" t="n">
-        <v>1.016</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="77">
@@ -2642,20 +2642,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Gary Payton II</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.888</v>
+        <v>2.772</v>
       </c>
       <c r="E77" t="n">
-        <v>32.2</v>
+        <v>22</v>
       </c>
       <c r="F77" t="n">
         <v>0.433</v>
       </c>
       <c r="G77" t="n">
-        <v>0.885</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="78">
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.026</v>
+        <v>-0.572</v>
       </c>
       <c r="E78" t="n">
-        <v>20.3</v>
+        <v>21.2</v>
       </c>
       <c r="F78" t="n">
         <v>0.433</v>
       </c>
       <c r="G78" t="n">
-        <v>0.172</v>
+        <v>-0.021</v>
       </c>
     </row>
     <row r="79">
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.099</v>
+        <v>-0.612</v>
       </c>
       <c r="E79" t="n">
-        <v>24.6</v>
+        <v>25.1</v>
       </c>
       <c r="F79" t="n">
         <v>0.433</v>
       </c>
       <c r="G79" t="n">
-        <v>0.171</v>
+        <v>-0.118</v>
       </c>
     </row>
     <row r="80">
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-0.572</v>
+        <v>-1.148</v>
       </c>
       <c r="E80" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="F80" t="n">
         <v>0.433</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.349</v>
       </c>
     </row>
     <row r="81">
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-1.084</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="E81" t="n">
-        <v>31</v>
+        <v>29.9</v>
       </c>
       <c r="F81" t="n">
         <v>0.433</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.421</v>
+        <v>-0.367</v>
       </c>
     </row>
     <row r="82">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.13</v>
+        <v>6.481</v>
       </c>
       <c r="E82" t="n">
-        <v>35.7</v>
+        <v>36.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G82" t="n">
-        <v>3.617</v>
+        <v>7.244</v>
       </c>
     </row>
     <row r="83">
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3.745</v>
+        <v>5.639</v>
       </c>
       <c r="E83" t="n">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="F83" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G83" t="n">
-        <v>3.043</v>
+        <v>6.377</v>
       </c>
     </row>
     <row r="84">
@@ -2849,16 +2849,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.943</v>
+        <v>3.661</v>
       </c>
       <c r="E84" t="n">
         <v>38.4</v>
       </c>
       <c r="F84" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G84" t="n">
-        <v>2.14</v>
+        <v>4.427</v>
       </c>
     </row>
     <row r="85">
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2.328</v>
+        <v>3.171</v>
       </c>
       <c r="E85" t="n">
-        <v>30.2</v>
+        <v>32</v>
       </c>
       <c r="F85" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G85" t="n">
-        <v>1.925</v>
+        <v>3.906</v>
       </c>
     </row>
     <row r="86">
@@ -2903,20 +2903,20 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Clint Capela</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.794</v>
+        <v>-0.571</v>
       </c>
       <c r="E86" t="n">
-        <v>15.2</v>
+        <v>36.1</v>
       </c>
       <c r="F86" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G86" t="n">
-        <v>0.802</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="87">
@@ -2932,20 +2932,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Josh Okogie</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-0.777</v>
+        <v>-2.953</v>
       </c>
       <c r="E87" t="n">
-        <v>36.7</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.034</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="88">
@@ -2961,20 +2961,20 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Dorian Finney-Smith</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-1.58</v>
+        <v>-6.718</v>
       </c>
       <c r="E88" t="n">
-        <v>23.6</v>
+        <v>19.2</v>
       </c>
       <c r="F88" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.417</v>
+        <v>-0.316</v>
       </c>
     </row>
     <row r="89">
@@ -2990,20 +2990,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dorian Finney-Smith</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-6.14</v>
+        <v>-2.149</v>
       </c>
       <c r="E89" t="n">
-        <v>19.2</v>
+        <v>25.6</v>
       </c>
       <c r="F89" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G89" t="n">
-        <v>-2.159</v>
+        <v>-1.006</v>
       </c>
     </row>
     <row r="90">
@@ -3023,16 +3023,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.178</v>
+        <v>2.942</v>
       </c>
       <c r="E90" t="n">
-        <v>30.8</v>
+        <v>31.9</v>
       </c>
       <c r="F90" t="n">
         <v>0.133</v>
       </c>
       <c r="G90" t="n">
-        <v>1.482</v>
+        <v>3.048</v>
       </c>
     </row>
     <row r="91">
@@ -3052,16 +3052,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.567</v>
+        <v>1.962</v>
       </c>
       <c r="E91" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="F91" t="n">
         <v>0.133</v>
       </c>
       <c r="G91" t="n">
-        <v>1.254</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="92">
@@ -3077,20 +3077,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.494</v>
+        <v>1.695</v>
       </c>
       <c r="E92" t="n">
-        <v>28.5</v>
+        <v>17.5</v>
       </c>
       <c r="F92" t="n">
         <v>0.133</v>
       </c>
       <c r="G92" t="n">
-        <v>0.967</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-2.386</v>
+        <v>1.607</v>
       </c>
       <c r="E93" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="F93" t="n">
         <v>0.133</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.917</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="94">
@@ -3135,20 +3135,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-1.59</v>
+        <v>-0.616</v>
       </c>
       <c r="E94" t="n">
-        <v>32.5</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
         <v>0.133</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.985</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="95">
@@ -3164,20 +3164,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.577</v>
+        <v>-2.944</v>
       </c>
       <c r="E95" t="n">
-        <v>21.4</v>
+        <v>20.5</v>
       </c>
       <c r="F95" t="n">
         <v>0.133</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.089</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="96">
@@ -3193,20 +3193,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.466</v>
+        <v>-2.669</v>
       </c>
       <c r="E96" t="n">
-        <v>28.8</v>
+        <v>21.9</v>
       </c>
       <c r="F96" t="n">
         <v>0.133</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.401</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -3226,16 +3226,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-3.226</v>
+        <v>-3.805</v>
       </c>
       <c r="E97" t="n">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
       <c r="F97" t="n">
         <v>0.133</v>
       </c>
       <c r="G97" t="n">
-        <v>-1.467</v>
+        <v>-0.907</v>
       </c>
     </row>
     <row r="98">
@@ -3255,16 +3255,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.264</v>
+        <v>11.725</v>
       </c>
       <c r="E98" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="F98" t="n">
         <v>0.633</v>
       </c>
       <c r="G98" t="n">
-        <v>6.992</v>
+        <v>12.134</v>
       </c>
     </row>
     <row r="99">
@@ -3284,16 +3284,16 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3.19</v>
+        <v>3.62</v>
       </c>
       <c r="E99" t="n">
-        <v>29.3</v>
+        <v>28.3</v>
       </c>
       <c r="F99" t="n">
         <v>0.633</v>
       </c>
       <c r="G99" t="n">
-        <v>2.333</v>
+        <v>3.957</v>
       </c>
     </row>
     <row r="100">
@@ -3309,20 +3309,20 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.639</v>
+        <v>0.184</v>
       </c>
       <c r="E100" t="n">
-        <v>29.6</v>
+        <v>26.6</v>
       </c>
       <c r="F100" t="n">
         <v>0.633</v>
       </c>
       <c r="G100" t="n">
-        <v>0.784</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="101">
@@ -3338,20 +3338,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.853</v>
+        <v>0.062</v>
       </c>
       <c r="E101" t="n">
-        <v>24</v>
+        <v>29.6</v>
       </c>
       <c r="F101" t="n">
         <v>0.633</v>
       </c>
       <c r="G101" t="n">
-        <v>0.742</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="102">
@@ -3367,20 +3367,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.276</v>
       </c>
       <c r="E102" t="n">
-        <v>24.1</v>
+        <v>25.5</v>
       </c>
       <c r="F102" t="n">
         <v>0.633</v>
       </c>
       <c r="G102" t="n">
-        <v>0.663</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="103">
@@ -3396,20 +3396,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.334</v>
       </c>
       <c r="E103" t="n">
-        <v>27.6</v>
+        <v>26.2</v>
       </c>
       <c r="F103" t="n">
         <v>0.633</v>
       </c>
       <c r="G103" t="n">
-        <v>0.414</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="104">
@@ -3425,20 +3425,20 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.551</v>
+        <v>-0.49</v>
       </c>
       <c r="E104" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="F104" t="n">
         <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>0.045</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="105">
@@ -3458,16 +3458,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-1.35</v>
+        <v>-1.544</v>
       </c>
       <c r="E105" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
       <c r="F105" t="n">
         <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.44</v>
+        <v>-0.883</v>
       </c>
     </row>
     <row r="106">
@@ -3487,16 +3487,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.988</v>
+        <v>15.421</v>
       </c>
       <c r="E106" t="n">
-        <v>38.2</v>
+        <v>36.7</v>
       </c>
       <c r="F106" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G106" t="n">
-        <v>10.029</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="107">
@@ -3512,20 +3512,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4.642</v>
+        <v>5.867</v>
       </c>
       <c r="E107" t="n">
-        <v>39.8</v>
+        <v>34.2</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G107" t="n">
-        <v>4.342</v>
+        <v>6.519</v>
       </c>
     </row>
     <row r="108">
@@ -3541,20 +3541,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4.579</v>
+        <v>5.616</v>
       </c>
       <c r="E108" t="n">
-        <v>35.4</v>
+        <v>37.9</v>
       </c>
       <c r="F108" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G108" t="n">
-        <v>3.814</v>
+        <v>6.281</v>
       </c>
     </row>
     <row r="109">
@@ -3570,20 +3570,20 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.457</v>
+        <v>0.028</v>
       </c>
       <c r="E109" t="n">
-        <v>21</v>
+        <v>25.1</v>
       </c>
       <c r="F109" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G109" t="n">
-        <v>1.338</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="110">
@@ -3599,20 +3599,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.237</v>
+        <v>1.996</v>
       </c>
       <c r="E110" t="n">
-        <v>21.3</v>
+        <v>20.5</v>
       </c>
       <c r="F110" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="111">
@@ -3628,20 +3628,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.552</v>
+        <v>0.723</v>
       </c>
       <c r="E111" t="n">
-        <v>26.9</v>
+        <v>21.6</v>
       </c>
       <c r="F111" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G111" t="n">
-        <v>0.644</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="112">
@@ -3661,16 +3661,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-0.656</v>
+        <v>-1.289</v>
       </c>
       <c r="E112" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="F112" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.021</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="113">
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-1.904</v>
+        <v>-2.515</v>
       </c>
       <c r="E113" t="n">
-        <v>25.5</v>
+        <v>24.7</v>
       </c>
       <c r="F113" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.694</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="114">
@@ -3719,16 +3719,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4.05</v>
+        <v>5.092</v>
       </c>
       <c r="E114" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="F114" t="n">
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>2.143</v>
+        <v>2.709</v>
       </c>
     </row>
     <row r="115">
@@ -3748,16 +3748,16 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3.329</v>
+        <v>2.756</v>
       </c>
       <c r="E115" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="F115" t="n">
         <v>0.267</v>
       </c>
       <c r="G115" t="n">
-        <v>1.911</v>
+        <v>2.223</v>
       </c>
     </row>
     <row r="116">
@@ -3777,16 +3777,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1.545</v>
+        <v>0.97</v>
       </c>
       <c r="E116" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="F116" t="n">
         <v>0.267</v>
       </c>
       <c r="G116" t="n">
-        <v>0.957</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="117">
@@ -3806,16 +3806,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.328</v>
+        <v>-0.569</v>
       </c>
       <c r="E117" t="n">
-        <v>27.8</v>
+        <v>26.1</v>
       </c>
       <c r="F117" t="n">
         <v>0.267</v>
       </c>
       <c r="G117" t="n">
-        <v>0.344</v>
+        <v>-0.237</v>
       </c>
     </row>
     <row r="118">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-0.74</v>
+        <v>-1.646</v>
       </c>
       <c r="E118" t="n">
         <v>25.8</v>
@@ -3844,7 +3844,7 @@
         <v>0.267</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.255</v>
+        <v>-1.029</v>
       </c>
     </row>
     <row r="119">
@@ -3864,16 +3864,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-2.014</v>
+        <v>-2.35</v>
       </c>
       <c r="E119" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
       <c r="F119" t="n">
         <v>0.267</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.881</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="120">
@@ -3889,20 +3889,20 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jahmai Mashack</t>
+          <t>Rayan Rupert</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-4.025</v>
+        <v>-5.705</v>
       </c>
       <c r="E120" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="F120" t="n">
         <v>0.267</v>
       </c>
       <c r="G120" t="n">
-        <v>-1.984</v>
+        <v>-2.858</v>
       </c>
     </row>
     <row r="121">
@@ -3918,20 +3918,20 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Rayan Rupert</t>
+          <t>Jahmai Mashack</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-5.131</v>
+        <v>-4.435</v>
       </c>
       <c r="E121" t="n">
-        <v>29.3</v>
+        <v>25.4</v>
       </c>
       <c r="F121" t="n">
         <v>0.267</v>
       </c>
       <c r="G121" t="n">
-        <v>-2.97</v>
+        <v>-2.901</v>
       </c>
     </row>
     <row r="122">
@@ -3947,20 +3947,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3.085</v>
+        <v>2.866</v>
       </c>
       <c r="E122" t="n">
-        <v>31.6</v>
+        <v>35.2</v>
       </c>
       <c r="F122" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G122" t="n">
-        <v>2.471</v>
+        <v>3.462</v>
       </c>
     </row>
     <row r="123">
@@ -3976,20 +3976,20 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.431</v>
+        <v>2.345</v>
       </c>
       <c r="E123" t="n">
-        <v>35.8</v>
+        <v>31.7</v>
       </c>
       <c r="F123" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G123" t="n">
-        <v>2.307</v>
+        <v>2.916</v>
       </c>
     </row>
     <row r="124">
@@ -4005,20 +4005,20 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2.849</v>
+        <v>1.687</v>
       </c>
       <c r="E124" t="n">
-        <v>23.9</v>
+        <v>28.3</v>
       </c>
       <c r="F124" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G124" t="n">
-        <v>1.753</v>
+        <v>2.123</v>
       </c>
     </row>
     <row r="125">
@@ -4034,20 +4034,20 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1.585</v>
+        <v>0.998</v>
       </c>
       <c r="E125" t="n">
-        <v>28</v>
+        <v>26.2</v>
       </c>
       <c r="F125" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G125" t="n">
-        <v>1.314</v>
+        <v>1.264</v>
       </c>
     </row>
     <row r="126">
@@ -4063,20 +4063,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.195</v>
+        <v>2.354</v>
       </c>
       <c r="E126" t="n">
-        <v>26.9</v>
+        <v>23</v>
       </c>
       <c r="F126" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G126" t="n">
-        <v>0.483</v>
+        <v>1.041</v>
       </c>
     </row>
     <row r="127">
@@ -4096,16 +4096,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>-0.003</v>
+        <v>0.411</v>
       </c>
       <c r="E127" t="n">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="F127" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G127" t="n">
-        <v>0.383</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="128">
@@ -4125,16 +4125,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-0.198</v>
+        <v>-0.618</v>
       </c>
       <c r="E128" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="F128" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G128" t="n">
-        <v>0.194</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="129">
@@ -4154,16 +4154,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.605</v>
+        <v>-0.774</v>
       </c>
       <c r="E129" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="F129" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G129" t="n">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="130">
@@ -4183,16 +4183,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2.315</v>
+        <v>4.089</v>
       </c>
       <c r="E130" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="F130" t="n">
         <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>1.635</v>
+        <v>4.249</v>
       </c>
     </row>
     <row r="131">
@@ -4212,16 +4212,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="E131" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="F131" t="n">
         <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>0.484</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="132">
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-0.15</v>
+        <v>-0.727</v>
       </c>
       <c r="E132" t="n">
-        <v>21.6</v>
+        <v>17.9</v>
       </c>
       <c r="F132" t="n">
         <v>0.2</v>
       </c>
       <c r="G132" t="n">
-        <v>0.022</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-1.984</v>
+        <v>-0.422</v>
       </c>
       <c r="E133" t="n">
-        <v>21.5</v>
+        <v>25.2</v>
       </c>
       <c r="F133" t="n">
         <v>0.2</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.8</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-1.646</v>
+        <v>-4.154</v>
       </c>
       <c r="E134" t="n">
-        <v>29</v>
+        <v>21.3</v>
       </c>
       <c r="F134" t="n">
         <v>0.2</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.873</v>
+        <v>-0.643</v>
       </c>
     </row>
     <row r="135">
@@ -4328,16 +4328,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-2.393</v>
+        <v>-2.75</v>
       </c>
       <c r="E135" t="n">
-        <v>21.2</v>
+        <v>22.2</v>
       </c>
       <c r="F135" t="n">
         <v>0.2</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.969</v>
+        <v>-0.644</v>
       </c>
     </row>
     <row r="136">
@@ -4353,20 +4353,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Gary Trent Jr.</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-3.793</v>
+        <v>-2.561</v>
       </c>
       <c r="E136" t="n">
-        <v>16.4</v>
+        <v>22.5</v>
       </c>
       <c r="F136" t="n">
         <v>0.2</v>
       </c>
       <c r="G136" t="n">
-        <v>-1.23</v>
+        <v>-0.677</v>
       </c>
     </row>
     <row r="137">
@@ -4382,20 +4382,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-4.049</v>
+        <v>-2.223</v>
       </c>
       <c r="E137" t="n">
-        <v>20.5</v>
+        <v>26.3</v>
       </c>
       <c r="F137" t="n">
         <v>0.2</v>
       </c>
       <c r="G137" t="n">
-        <v>-1.642</v>
+        <v>-1.608</v>
       </c>
     </row>
     <row r="138">
@@ -4411,20 +4411,20 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2.152</v>
+        <v>7.353</v>
       </c>
       <c r="E138" t="n">
-        <v>31</v>
+        <v>35.6</v>
       </c>
       <c r="F138" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G138" t="n">
-        <v>1.907</v>
+        <v>8.077999999999999</v>
       </c>
     </row>
     <row r="139">
@@ -4440,20 +4440,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2.213</v>
+        <v>3.945</v>
       </c>
       <c r="E139" t="n">
-        <v>28</v>
+        <v>31.7</v>
       </c>
       <c r="F139" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G139" t="n">
-        <v>1.757</v>
+        <v>4.631</v>
       </c>
     </row>
     <row r="140">
@@ -4469,20 +4469,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.033</v>
+        <v>2.668</v>
       </c>
       <c r="E140" t="n">
-        <v>25</v>
+        <v>27.6</v>
       </c>
       <c r="F140" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G140" t="n">
-        <v>1.474</v>
+        <v>3.056</v>
       </c>
     </row>
     <row r="141">
@@ -4498,20 +4498,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2.414</v>
+        <v>1.64</v>
       </c>
       <c r="E141" t="n">
-        <v>21.3</v>
+        <v>30.3</v>
       </c>
       <c r="F141" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G141" t="n">
-        <v>1.429</v>
+        <v>2.321</v>
       </c>
     </row>
     <row r="142">
@@ -4527,20 +4527,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1.256</v>
+        <v>1.889</v>
       </c>
       <c r="E142" t="n">
-        <v>30.9</v>
+        <v>25.5</v>
       </c>
       <c r="F142" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G142" t="n">
-        <v>1.323</v>
+        <v>1.868</v>
       </c>
     </row>
     <row r="143">
@@ -4556,20 +4556,20 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.905</v>
+        <v>0.857</v>
       </c>
       <c r="E143" t="n">
-        <v>29.8</v>
+        <v>31.7</v>
       </c>
       <c r="F143" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G143" t="n">
-        <v>1.058</v>
+        <v>1.574</v>
       </c>
     </row>
     <row r="144">
@@ -4585,20 +4585,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.401</v>
+        <v>1.597</v>
       </c>
       <c r="E144" t="n">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="F144" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G144" t="n">
-        <v>0.463</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="145">
@@ -4614,20 +4614,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mike Conley</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-1.558</v>
+        <v>-0.211</v>
       </c>
       <c r="E145" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.252</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="146">
@@ -4647,16 +4647,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4.187</v>
+        <v>4.848</v>
       </c>
       <c r="E146" t="n">
-        <v>30.9</v>
+        <v>29.8</v>
       </c>
       <c r="F146" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G146" t="n">
-        <v>2.914</v>
+        <v>4.991</v>
       </c>
     </row>
     <row r="147">
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2.995</v>
+        <v>2.331</v>
       </c>
       <c r="E147" t="n">
-        <v>30.2</v>
+        <v>30.7</v>
       </c>
       <c r="F147" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G147" t="n">
-        <v>2.096</v>
+        <v>2.583</v>
       </c>
     </row>
     <row r="148">
@@ -4705,16 +4705,16 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1.708</v>
+        <v>2.249</v>
       </c>
       <c r="E148" t="n">
-        <v>32.2</v>
+        <v>32.7</v>
       </c>
       <c r="F148" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G148" t="n">
-        <v>1.368</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="149">
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.626</v>
+        <v>1.067</v>
       </c>
       <c r="E149" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="F149" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G149" t="n">
-        <v>0.348</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="150">
@@ -4763,16 +4763,16 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.418</v>
+        <v>-0.202</v>
       </c>
       <c r="E150" t="n">
-        <v>20.7</v>
+        <v>18.6</v>
       </c>
       <c r="F150" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G150" t="n">
-        <v>0.324</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="151">
@@ -4788,20 +4788,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-1.907</v>
+        <v>-2.669</v>
       </c>
       <c r="E151" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="F151" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.658</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="152">
@@ -4817,20 +4817,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-1.995</v>
+        <v>-1.444</v>
       </c>
       <c r="E152" t="n">
-        <v>19.8</v>
+        <v>22.4</v>
       </c>
       <c r="F152" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.312</v>
       </c>
     </row>
     <row r="153">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-2.211</v>
+        <v>-2.857</v>
       </c>
       <c r="E153" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="F153" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.171</v>
+        <v>-2.464</v>
       </c>
     </row>
     <row r="154">
@@ -4879,16 +4879,16 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>4.001</v>
+        <v>6.553</v>
       </c>
       <c r="E154" t="n">
-        <v>36.6</v>
+        <v>36.1</v>
       </c>
       <c r="F154" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G154" t="n">
-        <v>3.733</v>
+        <v>7.415</v>
       </c>
     </row>
     <row r="155">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3.401</v>
+        <v>4.228</v>
       </c>
       <c r="E155" t="n">
-        <v>30</v>
+        <v>29.2</v>
       </c>
       <c r="F155" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G155" t="n">
-        <v>2.692</v>
+        <v>4.874</v>
       </c>
     </row>
     <row r="156">
@@ -4937,16 +4937,16 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2.656</v>
+        <v>3.166</v>
       </c>
       <c r="E156" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="F156" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G156" t="n">
-        <v>2.157</v>
+        <v>3.883</v>
       </c>
     </row>
     <row r="157">
@@ -4962,20 +4962,20 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3.902</v>
+        <v>3.041</v>
       </c>
       <c r="E157" t="n">
-        <v>20.1</v>
+        <v>30.3</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G157" t="n">
-        <v>2.015</v>
+        <v>3.823</v>
       </c>
     </row>
     <row r="158">
@@ -4991,20 +4991,20 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2.276</v>
+        <v>1.8</v>
       </c>
       <c r="E158" t="n">
-        <v>29.2</v>
+        <v>33.4</v>
       </c>
       <c r="F158" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G158" t="n">
-        <v>1.934</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="159">
@@ -5020,20 +5020,20 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1.749</v>
+        <v>0.744</v>
       </c>
       <c r="E159" t="n">
-        <v>33.5</v>
+        <v>29.4</v>
       </c>
       <c r="F159" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G159" t="n">
-        <v>1.847</v>
+        <v>1.551</v>
       </c>
     </row>
     <row r="160">
@@ -5049,20 +5049,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jordan Clarkson</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-2.632</v>
+        <v>3.201</v>
       </c>
       <c r="E160" t="n">
-        <v>17.3</v>
+        <v>19.7</v>
       </c>
       <c r="F160" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.624</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="161">
@@ -5078,20 +5078,20 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tosan Evbuomwan</t>
+          <t>Jordan Clarkson</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-4.394</v>
+        <v>-4.208</v>
       </c>
       <c r="E161" t="n">
-        <v>18.1</v>
+        <v>15.7</v>
       </c>
       <c r="F161" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G161" t="n">
-        <v>-1.315</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="162">
@@ -5111,16 +5111,16 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>12.484</v>
+        <v>14.814</v>
       </c>
       <c r="E162" t="n">
-        <v>34.1</v>
+        <v>33.5</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>9.571999999999999</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="163">
@@ -5140,16 +5140,16 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4.184</v>
+        <v>4.044</v>
       </c>
       <c r="E163" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>3.195</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="164">
@@ -5165,20 +5165,20 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1.878</v>
+        <v>1.595</v>
       </c>
       <c r="E164" t="n">
-        <v>25.7</v>
+        <v>27</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>1.539</v>
+        <v>2.231</v>
       </c>
     </row>
     <row r="165">
@@ -5194,20 +5194,20 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.807</v>
+        <v>1.891</v>
       </c>
       <c r="E165" t="n">
-        <v>23.1</v>
+        <v>25.7</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>1.352</v>
+        <v>2.134</v>
       </c>
     </row>
     <row r="166">
@@ -5223,20 +5223,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.068</v>
+        <v>3.338</v>
       </c>
       <c r="E166" t="n">
-        <v>24.5</v>
+        <v>22.5</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.546</v>
+        <v>1.237</v>
       </c>
     </row>
     <row r="167">
@@ -5252,20 +5252,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-1.31</v>
+        <v>0.097</v>
       </c>
       <c r="E167" t="n">
-        <v>19</v>
+        <v>25.7</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>-0.123</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="168">
@@ -5281,20 +5281,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>-1.382</v>
+        <v>1.26</v>
       </c>
       <c r="E168" t="n">
-        <v>18.6</v>
+        <v>22.2</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>-0.148</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="169">
@@ -5314,16 +5314,16 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-4.118</v>
+        <v>-4.532</v>
       </c>
       <c r="E169" t="n">
-        <v>25.5</v>
+        <v>26.1</v>
       </c>
       <c r="F169" t="n">
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>-1.654</v>
+        <v>-2.733</v>
       </c>
     </row>
     <row r="170">
@@ -5339,20 +5339,20 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3.213</v>
+        <v>3.39</v>
       </c>
       <c r="E170" t="n">
-        <v>30.2</v>
+        <v>35.1</v>
       </c>
       <c r="F170" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G170" t="n">
-        <v>2.314</v>
+        <v>3.785</v>
       </c>
     </row>
     <row r="171">
@@ -5368,20 +5368,20 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1.991</v>
+        <v>3.265</v>
       </c>
       <c r="E171" t="n">
-        <v>35.6</v>
+        <v>33.9</v>
       </c>
       <c r="F171" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G171" t="n">
-        <v>1.824</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="172">
@@ -5397,20 +5397,20 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1.633</v>
+        <v>3.122</v>
       </c>
       <c r="E172" t="n">
-        <v>34.3</v>
+        <v>28.5</v>
       </c>
       <c r="F172" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G172" t="n">
-        <v>1.502</v>
+        <v>3.305</v>
       </c>
     </row>
     <row r="173">
@@ -5426,20 +5426,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jett Howard</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-0.277</v>
+        <v>-2.549</v>
       </c>
       <c r="E173" t="n">
-        <v>29.4</v>
+        <v>16.8</v>
       </c>
       <c r="F173" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G173" t="n">
-        <v>0.116</v>
+        <v>-0.029</v>
       </c>
     </row>
     <row r="174">
@@ -5459,16 +5459,16 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-0.267</v>
+        <v>-1.053</v>
       </c>
       <c r="E174" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="F174" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G174" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.098</v>
       </c>
     </row>
     <row r="175">
@@ -5484,20 +5484,20 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-0.539</v>
+        <v>-0.602</v>
       </c>
       <c r="E175" t="n">
-        <v>30.7</v>
+        <v>29.2</v>
       </c>
       <c r="F175" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.046</v>
+        <v>-0.194</v>
       </c>
     </row>
     <row r="176">
@@ -5517,16 +5517,16 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-1.538</v>
+        <v>-2.274</v>
       </c>
       <c r="E176" t="n">
-        <v>19.5</v>
+        <v>22.2</v>
       </c>
       <c r="F176" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.435</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="177">
@@ -5542,20 +5542,20 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Colin Castleton</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>-3.271</v>
+        <v>-1.008</v>
       </c>
       <c r="E177" t="n">
-        <v>21.7</v>
+        <v>29.8</v>
       </c>
       <c r="F177" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G177" t="n">
-        <v>-1.27</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="178">
@@ -5575,16 +5575,16 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6.682</v>
+        <v>9.291</v>
       </c>
       <c r="E178" t="n">
-        <v>35.8</v>
+        <v>36.3</v>
       </c>
       <c r="F178" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G178" t="n">
-        <v>5.285</v>
+        <v>9.750999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -5604,16 +5604,16 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5.45</v>
+        <v>5.555</v>
       </c>
       <c r="E179" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="F179" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G179" t="n">
-        <v>4.019</v>
+        <v>6.002</v>
       </c>
     </row>
     <row r="180">
@@ -5633,16 +5633,16 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2.366</v>
+        <v>2.012</v>
       </c>
       <c r="E180" t="n">
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="F180" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G180" t="n">
-        <v>1.838</v>
+        <v>2.467</v>
       </c>
     </row>
     <row r="181">
@@ -5662,16 +5662,16 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-0.152</v>
+        <v>0.725</v>
       </c>
       <c r="E181" t="n">
-        <v>32.3</v>
+        <v>33.3</v>
       </c>
       <c r="F181" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G181" t="n">
-        <v>0.167</v>
+        <v>1.187</v>
       </c>
     </row>
     <row r="182">
@@ -5687,20 +5687,20 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Justin Edwards</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-0.132</v>
+        <v>-0.186</v>
       </c>
       <c r="E182" t="n">
-        <v>24.2</v>
+        <v>31.5</v>
       </c>
       <c r="F182" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G182" t="n">
-        <v>0.135</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="183">
@@ -5716,20 +5716,20 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Eric Gordon</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-0.676</v>
+        <v>-0.768</v>
       </c>
       <c r="E183" t="n">
-        <v>24.3</v>
+        <v>23</v>
       </c>
       <c r="F183" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.14</v>
+        <v>-0.105</v>
       </c>
     </row>
     <row r="184">
@@ -5745,20 +5745,20 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>-0.646</v>
+        <v>-1.326</v>
       </c>
       <c r="E184" t="n">
-        <v>34.3</v>
+        <v>23.4</v>
       </c>
       <c r="F184" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.176</v>
+        <v>-0.355</v>
       </c>
     </row>
     <row r="185">
@@ -5778,16 +5778,16 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>-0.858</v>
+        <v>-1.474</v>
       </c>
       <c r="E185" t="n">
-        <v>31.4</v>
+        <v>32.7</v>
       </c>
       <c r="F185" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.3</v>
+        <v>-1.002</v>
       </c>
     </row>
     <row r="186">
@@ -5803,20 +5803,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3.393</v>
+        <v>4.811</v>
       </c>
       <c r="E186" t="n">
-        <v>29.7</v>
+        <v>33.1</v>
       </c>
       <c r="F186" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G186" t="n">
-        <v>2.41</v>
+        <v>5.321</v>
       </c>
     </row>
     <row r="187">
@@ -5832,20 +5832,20 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2.454</v>
+        <v>4.258</v>
       </c>
       <c r="E187" t="n">
-        <v>34.5</v>
+        <v>29.7</v>
       </c>
       <c r="F187" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G187" t="n">
-        <v>2.126</v>
+        <v>4.642</v>
       </c>
     </row>
     <row r="188">
@@ -5865,16 +5865,16 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3.071</v>
+        <v>3.237</v>
       </c>
       <c r="E188" t="n">
-        <v>27.6</v>
+        <v>28.6</v>
       </c>
       <c r="F188" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G188" t="n">
-        <v>2.054</v>
+        <v>3.542</v>
       </c>
     </row>
     <row r="189">
@@ -5894,16 +5894,16 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1.121</v>
+        <v>0.981</v>
       </c>
       <c r="E189" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="F189" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G189" t="n">
-        <v>0.794</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="190">
@@ -5923,16 +5923,16 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.339</v>
+        <v>0.262</v>
       </c>
       <c r="E190" t="n">
-        <v>27.4</v>
+        <v>26.4</v>
       </c>
       <c r="F190" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G190" t="n">
-        <v>0.48</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="191">
@@ -5952,16 +5952,16 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.054</v>
+        <v>-0.333</v>
       </c>
       <c r="E191" t="n">
-        <v>29</v>
+        <v>29.4</v>
       </c>
       <c r="F191" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G191" t="n">
-        <v>0.335</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="192">
@@ -5981,16 +5981,16 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-1.49</v>
+        <v>-1.045</v>
       </c>
       <c r="E192" t="n">
-        <v>32.1</v>
+        <v>30.7</v>
       </c>
       <c r="F192" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.662</v>
+        <v>-0.503</v>
       </c>
     </row>
     <row r="193">
@@ -6006,20 +6006,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Rasheer Fleming</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>-2.055</v>
+        <v>-1.866</v>
       </c>
       <c r="E193" t="n">
-        <v>20.6</v>
+        <v>30.3</v>
       </c>
       <c r="F193" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G193" t="n">
-        <v>-0.669</v>
+        <v>-1.303</v>
       </c>
     </row>
     <row r="194">
@@ -6039,16 +6039,16 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3.79</v>
+        <v>5.605</v>
       </c>
       <c r="E194" t="n">
-        <v>30.9</v>
+        <v>28.8</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>2.68</v>
+        <v>5.656</v>
       </c>
     </row>
     <row r="195">
@@ -6064,20 +6064,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3.749</v>
+        <v>2.967</v>
       </c>
       <c r="E195" t="n">
-        <v>26.8</v>
+        <v>30.1</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>2.298</v>
+        <v>3.251</v>
       </c>
     </row>
     <row r="196">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2.661</v>
+        <v>3.346</v>
       </c>
       <c r="E196" t="n">
-        <v>28.7</v>
+        <v>26.2</v>
       </c>
       <c r="F196" t="n">
         <v>0.367</v>
       </c>
       <c r="G196" t="n">
-        <v>1.809</v>
+        <v>2.946</v>
       </c>
     </row>
     <row r="197">
@@ -6122,20 +6122,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Vít Krejčí</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.099</v>
+        <v>-0.952</v>
       </c>
       <c r="E197" t="n">
-        <v>31.8</v>
+        <v>20.6</v>
       </c>
       <c r="F197" t="n">
         <v>0.367</v>
       </c>
       <c r="G197" t="n">
-        <v>0.309</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="198">
@@ -6151,20 +6151,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Vít Krejčí</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-0.375</v>
+        <v>-3.282</v>
       </c>
       <c r="E198" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="F198" t="n">
         <v>0.367</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.003</v>
+        <v>-0.127</v>
       </c>
     </row>
     <row r="199">
@@ -6184,16 +6184,16 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-1.596</v>
+        <v>-2.234</v>
       </c>
       <c r="E199" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="F199" t="n">
         <v>0.367</v>
       </c>
       <c r="G199" t="n">
-        <v>-0.629</v>
+        <v>-0.987</v>
       </c>
     </row>
     <row r="200">
@@ -6209,20 +6209,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Caleb Love</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-2.236</v>
+        <v>-1.605</v>
       </c>
       <c r="E200" t="n">
-        <v>23.3</v>
+        <v>32.1</v>
       </c>
       <c r="F200" t="n">
         <v>0.367</v>
       </c>
       <c r="G200" t="n">
-        <v>-0.909</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="201">
@@ -6238,20 +6238,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Caleb Love</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-1.838</v>
+        <v>-2.814</v>
       </c>
       <c r="E201" t="n">
-        <v>29.6</v>
+        <v>25.2</v>
       </c>
       <c r="F201" t="n">
         <v>0.367</v>
       </c>
       <c r="G201" t="n">
-        <v>-0.909</v>
+        <v>-1.634</v>
       </c>
     </row>
     <row r="202">
@@ -6271,16 +6271,16 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1.394</v>
+        <v>2.855</v>
       </c>
       <c r="E202" t="n">
-        <v>30.6</v>
+        <v>29.3</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>0.953</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="203">
@@ -6300,16 +6300,16 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.674</v>
+        <v>0.285</v>
       </c>
       <c r="E203" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.523</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="204">
@@ -6325,20 +6325,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.613</v>
+        <v>0.377</v>
       </c>
       <c r="E204" t="n">
-        <v>20.6</v>
+        <v>22.8</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.307</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="205">
@@ -6354,20 +6354,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.465</v>
+        <v>-2.244</v>
       </c>
       <c r="E205" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>0.274</v>
+        <v>-0.521</v>
       </c>
     </row>
     <row r="206">
@@ -6387,16 +6387,16 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-0.893</v>
+        <v>-1.19</v>
       </c>
       <c r="E206" t="n">
-        <v>33.7</v>
+        <v>33</v>
       </c>
       <c r="F206" t="n">
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-1.085</v>
       </c>
     </row>
     <row r="207">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-2.443</v>
+        <v>-2.951</v>
       </c>
       <c r="E207" t="n">
-        <v>30.6</v>
+        <v>28.7</v>
       </c>
       <c r="F207" t="n">
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-1.493</v>
+        <v>-2.692</v>
       </c>
     </row>
     <row r="208">
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>-4.314</v>
+        <v>-3.997</v>
       </c>
       <c r="E208" t="n">
-        <v>25</v>
+        <v>26.4</v>
       </c>
       <c r="F208" t="n">
         <v>0.1</v>
       </c>
       <c r="G208" t="n">
-        <v>-2.194</v>
+        <v>-3.138</v>
       </c>
     </row>
     <row r="209">
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-3.584</v>
+        <v>-4.226</v>
       </c>
       <c r="E209" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
       <c r="F209" t="n">
         <v>0.1</v>
       </c>
       <c r="G209" t="n">
-        <v>-2.447</v>
+        <v>-4.101</v>
       </c>
     </row>
     <row r="210">
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>10.304</v>
+        <v>10.978</v>
       </c>
       <c r="E210" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="F210" t="n">
         <v>0.967</v>
       </c>
       <c r="G210" t="n">
-        <v>6.806</v>
+        <v>11.539</v>
       </c>
     </row>
     <row r="211">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>2.813</v>
+        <v>4.323</v>
       </c>
       <c r="E211" t="n">
-        <v>30.7</v>
+        <v>29.1</v>
       </c>
       <c r="F211" t="n">
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>2.417</v>
+        <v>5.056</v>
       </c>
     </row>
     <row r="212">
@@ -6561,16 +6561,16 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1.89</v>
+        <v>3.515</v>
       </c>
       <c r="E212" t="n">
-        <v>30</v>
+        <v>28.9</v>
       </c>
       <c r="F212" t="n">
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>1.786</v>
+        <v>4.259</v>
       </c>
     </row>
     <row r="213">
@@ -6586,20 +6586,20 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1.369</v>
+        <v>0.333</v>
       </c>
       <c r="E213" t="n">
-        <v>23.7</v>
+        <v>30</v>
       </c>
       <c r="F213" t="n">
         <v>0.967</v>
       </c>
       <c r="G213" t="n">
-        <v>1.155</v>
+        <v>1.265</v>
       </c>
     </row>
     <row r="214">
@@ -6615,20 +6615,20 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1.206</v>
+        <v>1.505</v>
       </c>
       <c r="E214" t="n">
-        <v>22.5</v>
+        <v>24.1</v>
       </c>
       <c r="F214" t="n">
         <v>0.967</v>
       </c>
       <c r="G214" t="n">
-        <v>1.019</v>
+        <v>1.258</v>
       </c>
     </row>
     <row r="215">
@@ -6648,16 +6648,16 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.556</v>
+        <v>0.262</v>
       </c>
       <c r="E215" t="n">
-        <v>27.2</v>
+        <v>26.7</v>
       </c>
       <c r="F215" t="n">
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>0.863</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="216">
@@ -6673,20 +6673,20 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.303</v>
+        <v>1.212</v>
       </c>
       <c r="E216" t="n">
-        <v>30.8</v>
+        <v>22.1</v>
       </c>
       <c r="F216" t="n">
         <v>0.967</v>
       </c>
       <c r="G216" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="217">
@@ -6706,16 +6706,16 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>-0.499</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="E217" t="n">
-        <v>21.1</v>
+        <v>20.5</v>
       </c>
       <c r="F217" t="n">
         <v>0.967</v>
       </c>
       <c r="G217" t="n">
-        <v>0.206</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="218">
@@ -6735,16 +6735,16 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4.165</v>
+        <v>5.986</v>
       </c>
       <c r="E218" t="n">
-        <v>32.2</v>
+        <v>32.7</v>
       </c>
       <c r="F218" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G218" t="n">
-        <v>3.153</v>
+        <v>6.518</v>
       </c>
     </row>
     <row r="219">
@@ -6760,20 +6760,20 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>3.51</v>
+        <v>2.19</v>
       </c>
       <c r="E219" t="n">
-        <v>20.1</v>
+        <v>34.3</v>
       </c>
       <c r="F219" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G219" t="n">
-        <v>1.694</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="220">
@@ -6789,20 +6789,20 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1.971</v>
+        <v>1.445</v>
       </c>
       <c r="E220" t="n">
-        <v>27.1</v>
+        <v>31.6</v>
       </c>
       <c r="F220" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G220" t="n">
-        <v>1.412</v>
+        <v>1.991</v>
       </c>
     </row>
     <row r="221">
@@ -6818,20 +6818,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.409</v>
+        <v>1.646</v>
       </c>
       <c r="E221" t="n">
-        <v>30.9</v>
+        <v>26.4</v>
       </c>
       <c r="F221" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G221" t="n">
-        <v>1.25</v>
+        <v>1.795</v>
       </c>
     </row>
     <row r="222">
@@ -6847,20 +6847,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.866</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E222" t="n">
-        <v>34</v>
+        <v>25.6</v>
       </c>
       <c r="F222" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G222" t="n">
-        <v>0.991</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="223">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1.392</v>
+        <v>3.382</v>
       </c>
       <c r="E223" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="F223" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G223" t="n">
-        <v>0.921</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="224">
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.346</v>
+        <v>-0.931</v>
       </c>
       <c r="E224" t="n">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="F224" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G224" t="n">
-        <v>0.081</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="225">
@@ -6938,16 +6938,16 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-1.279</v>
+        <v>-0.971</v>
       </c>
       <c r="E225" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="F225" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.347</v>
+        <v>-0.093</v>
       </c>
     </row>
     <row r="226">
@@ -6967,16 +6967,16 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1.555</v>
+        <v>1.03</v>
       </c>
       <c r="E226" t="n">
-        <v>26.7</v>
+        <v>25.7</v>
       </c>
       <c r="F226" t="n">
         <v>0.167</v>
       </c>
       <c r="G226" t="n">
-        <v>0.959</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="227">
@@ -6996,16 +6996,16 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.713</v>
+        <v>0.837</v>
       </c>
       <c r="E227" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="F227" t="n">
         <v>0.167</v>
       </c>
       <c r="G227" t="n">
-        <v>0.482</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="228">
@@ -7021,20 +7021,20 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-0.377</v>
+        <v>-1.106</v>
       </c>
       <c r="E228" t="n">
-        <v>26.7</v>
+        <v>19</v>
       </c>
       <c r="F228" t="n">
         <v>0.167</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.117</v>
+        <v>-0.046</v>
       </c>
     </row>
     <row r="229">
@@ -7050,20 +7050,20 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>Svi Mykhailiuk</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-1.483</v>
       </c>
       <c r="E229" t="n">
-        <v>18.6</v>
+        <v>20.6</v>
       </c>
       <c r="F229" t="n">
         <v>0.167</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.152</v>
+        <v>-0.151</v>
       </c>
     </row>
     <row r="230">
@@ -7079,20 +7079,20 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Svi Mykhailiuk</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-0.909</v>
+        <v>-0.489</v>
       </c>
       <c r="E230" t="n">
-        <v>19.6</v>
+        <v>27.1</v>
       </c>
       <c r="F230" t="n">
         <v>0.167</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.303</v>
+        <v>-0.278</v>
       </c>
     </row>
     <row r="231">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-1.557</v>
+        <v>-1.919</v>
       </c>
       <c r="E231" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="F231" t="n">
         <v>0.167</v>
       </c>
       <c r="G231" t="n">
-        <v>-0.838</v>
+        <v>-1.694</v>
       </c>
     </row>
     <row r="232">
@@ -7141,16 +7141,16 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>-2.354</v>
+        <v>-2.932</v>
       </c>
       <c r="E232" t="n">
-        <v>30.7</v>
+        <v>27.3</v>
       </c>
       <c r="F232" t="n">
         <v>0.167</v>
       </c>
       <c r="G232" t="n">
-        <v>-1.399</v>
+        <v>-2.433</v>
       </c>
     </row>
     <row r="233">
@@ -7170,16 +7170,16 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-3.08</v>
+        <v>-3.996</v>
       </c>
       <c r="E233" t="n">
-        <v>34.7</v>
+        <v>31.5</v>
       </c>
       <c r="F233" t="n">
         <v>0.167</v>
       </c>
       <c r="G233" t="n">
-        <v>-2.108</v>
+        <v>-3.787</v>
       </c>
     </row>
     <row r="234">
@@ -7199,16 +7199,16 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3.241</v>
+        <v>3.075</v>
       </c>
       <c r="E234" t="n">
-        <v>22.3</v>
+        <v>26.3</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>1.518</v>
+        <v>2.489</v>
       </c>
     </row>
     <row r="235">
@@ -7224,20 +7224,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>-0.26</v>
+        <v>1.523</v>
       </c>
       <c r="E235" t="n">
-        <v>29.2</v>
+        <v>21</v>
       </c>
       <c r="F235" t="n">
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>-0.138</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="236">
@@ -7253,20 +7253,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.9</v>
+        <v>-1.834</v>
       </c>
       <c r="E236" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.389</v>
+        <v>-0.267</v>
       </c>
     </row>
     <row r="237">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-1.226</v>
+        <v>-0.455</v>
       </c>
       <c r="E237" t="n">
-        <v>22.6</v>
+        <v>27.1</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.366</v>
       </c>
     </row>
     <row r="238">
@@ -7311,20 +7311,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Tre Johnson</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-2.701</v>
+        <v>-1.491</v>
       </c>
       <c r="E238" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="F238" t="n">
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-1.275</v>
+        <v>-0.788</v>
       </c>
     </row>
     <row r="239">
@@ -7340,20 +7340,20 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Jaden Hardy</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-3.044</v>
+        <v>-3.187</v>
       </c>
       <c r="E239" t="n">
-        <v>21.5</v>
+        <v>22.3</v>
       </c>
       <c r="F239" t="n">
         <v>0.033</v>
       </c>
       <c r="G239" t="n">
-        <v>-1.346</v>
+        <v>-0.826</v>
       </c>
     </row>
     <row r="240">
@@ -7373,16 +7373,16 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-2.642</v>
+        <v>-1.836</v>
       </c>
       <c r="E240" t="n">
-        <v>28.4</v>
+        <v>27.2</v>
       </c>
       <c r="F240" t="n">
         <v>0.033</v>
       </c>
       <c r="G240" t="n">
-        <v>-1.543</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="241">
@@ -7402,16 +7402,16 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>-2.403</v>
+        <v>-2.464</v>
       </c>
       <c r="E241" t="n">
-        <v>32.3</v>
+        <v>31.3</v>
       </c>
       <c r="F241" t="n">
         <v>0.033</v>
       </c>
       <c r="G241" t="n">
-        <v>-1.594</v>
+        <v>-2.401</v>
       </c>
     </row>
   </sheetData>
@@ -7483,10 +7483,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>20.734</v>
+        <v>32.176</v>
       </c>
       <c r="F2" t="n">
-        <v>2.739</v>
+        <v>3.078</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7500,26 +7500,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>20.267</v>
+        <v>29.715</v>
       </c>
       <c r="F3" t="n">
-        <v>2.862</v>
+        <v>3.354</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>15.644</v>
+        <v>28.78</v>
       </c>
       <c r="F4" t="n">
-        <v>2.103</v>
+        <v>3.231</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
     </row>
@@ -7558,26 +7558,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>15.067</v>
+        <v>26.07</v>
       </c>
       <c r="F5" t="n">
-        <v>2.243</v>
+        <v>2.521</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
     </row>
@@ -7587,26 +7587,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>14.279</v>
+        <v>24.927</v>
       </c>
       <c r="F6" t="n">
-        <v>1.701</v>
+        <v>2.648</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7616,26 +7616,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>12.902</v>
+        <v>24.886</v>
       </c>
       <c r="F7" t="n">
-        <v>1.832</v>
+        <v>2.813</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
     </row>
@@ -7657,10 +7657,10 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>12.439</v>
+        <v>24.463</v>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>2.316</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -7674,26 +7674,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>11.55</v>
+        <v>21.707</v>
       </c>
       <c r="F9" t="n">
-        <v>1.561</v>
+        <v>2.467</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
     </row>
@@ -7703,26 +7703,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>11.533</v>
+        <v>21.08</v>
       </c>
       <c r="F10" t="n">
-        <v>1.727</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7732,26 +7732,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>10.828</v>
+        <v>20.81</v>
       </c>
       <c r="F11" t="n">
-        <v>1.504</v>
+        <v>0.82</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7773,10 +7773,10 @@
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>9.914999999999999</v>
+        <v>19.396</v>
       </c>
       <c r="F12" t="n">
-        <v>1.26</v>
+        <v>1.641</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>9.159000000000001</v>
+        <v>18.223</v>
       </c>
       <c r="F13" t="n">
-        <v>1.227</v>
+        <v>1.729</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7819,26 +7819,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>9.154999999999999</v>
+        <v>17.549</v>
       </c>
       <c r="F14" t="n">
-        <v>1.461</v>
+        <v>1.687</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7848,26 +7848,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>8.945</v>
+        <v>14.143</v>
       </c>
       <c r="F15" t="n">
-        <v>1.167</v>
+        <v>1.695</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7877,26 +7877,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>8.917</v>
+        <v>13.381</v>
       </c>
       <c r="F16" t="n">
-        <v>0.68</v>
+        <v>1.288</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Devin Booker</t>
         </is>
       </c>
     </row>
@@ -7906,26 +7906,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>6.868</v>
+        <v>11.527</v>
       </c>
       <c r="F17" t="n">
-        <v>0.861</v>
+        <v>1.159</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
     </row>
@@ -7935,26 +7935,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>5.833</v>
+        <v>9.555999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.008</v>
+        <v>0.457</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
     </row>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>4.646</v>
+        <v>9.364000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.532</v>
+        <v>0.286</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>4.534</v>
+        <v>7.809</v>
       </c>
       <c r="F20" t="n">
-        <v>0.478</v>
+        <v>0.129</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
     </row>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>4.092</v>
+        <v>7.583</v>
       </c>
       <c r="F21" t="n">
-        <v>0.118</v>
+        <v>0.328</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
     </row>
@@ -8051,26 +8051,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>3.413</v>
+        <v>7.23</v>
       </c>
       <c r="F22" t="n">
-        <v>0.116</v>
+        <v>0.415</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
     </row>
@@ -8080,26 +8080,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>2.451</v>
+        <v>4.127</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.434</v>
+        <v>0.802</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
     </row>
@@ -8109,26 +8109,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.132</v>
+        <v>2.313</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.198</v>
+        <v>-0.228</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
     </row>
@@ -8138,26 +8138,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.735</v>
+        <v>2.006</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.332</v>
+        <v>-0.961</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
     </row>
@@ -8167,26 +8167,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.156</v>
+        <v>0.713</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.751</v>
+        <v>-1.031</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
     </row>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.373</v>
+        <v>-2.598</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.361</v>
+        <v>-0.736</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
     </row>
@@ -8225,26 +8225,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.476</v>
+        <v>-3.51</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.821</v>
+        <v>-0.834</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
     </row>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.634</v>
+        <v>-5.616</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.011</v>
+        <v>-2.343</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
     </row>
@@ -8283,26 +8283,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.329</v>
+        <v>-6.722</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.242</v>
+        <v>-1.257</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>John Konchar</t>
         </is>
       </c>
     </row>
@@ -8312,26 +8312,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.542</v>
+        <v>-8.164</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.737</v>
+        <v>-1.386</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
     </row>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -480,7 +480,7 @@
         <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>8.887</v>
+        <v>6.337</v>
       </c>
     </row>
     <row r="3">
@@ -509,7 +509,7 @@
         <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>4.055</v>
+        <v>2.777</v>
       </c>
     </row>
     <row r="4">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.485</v>
+        <v>2.484</v>
       </c>
       <c r="E4" t="n">
         <v>31.7</v>
@@ -538,7 +538,7 @@
         <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.955</v>
+        <v>1.968</v>
       </c>
     </row>
     <row r="5">
@@ -567,7 +567,7 @@
         <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.723</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="6">
@@ -596,7 +596,7 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.628</v>
+        <v>1.666</v>
       </c>
     </row>
     <row r="7">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="E7" t="n">
         <v>18</v>
@@ -625,7 +625,7 @@
         <v>0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.033</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.786</v>
+        <v>-1.787</v>
       </c>
       <c r="E8" t="n">
         <v>19.7</v>
@@ -654,7 +654,7 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.091</v>
+        <v>-0.528</v>
       </c>
     </row>
     <row r="9">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.945</v>
+        <v>-1.946</v>
       </c>
       <c r="E9" t="n">
         <v>19.8</v>
@@ -683,7 +683,7 @@
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.11</v>
+        <v>-0.598</v>
       </c>
     </row>
     <row r="10">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.502</v>
+        <v>6.501</v>
       </c>
       <c r="E10" t="n">
         <v>34.4</v>
@@ -712,7 +712,7 @@
         <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>7.387</v>
+        <v>5.297</v>
       </c>
     </row>
     <row r="11">
@@ -741,7 +741,7 @@
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>5.928</v>
+        <v>4.331</v>
       </c>
     </row>
     <row r="12">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.043</v>
+        <v>5.042</v>
       </c>
       <c r="E12" t="n">
         <v>33.9</v>
@@ -770,7 +770,7 @@
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>5.928</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="13">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.054</v>
+        <v>4.053</v>
       </c>
       <c r="E13" t="n">
         <v>32.2</v>
@@ -799,7 +799,7 @@
         <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>4.917</v>
+        <v>3.319</v>
       </c>
     </row>
     <row r="14">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.102</v>
+        <v>2.101</v>
       </c>
       <c r="E14" t="n">
         <v>25.9</v>
@@ -828,7 +828,7 @@
         <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2.283</v>
+        <v>1.621</v>
       </c>
     </row>
     <row r="15">
@@ -844,20 +844,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Dalano Banton</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.79</v>
+        <v>-0.329</v>
       </c>
       <c r="E15" t="n">
-        <v>26.2</v>
+        <v>17.9</v>
       </c>
       <c r="F15" t="n">
         <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="16">
@@ -873,20 +873,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dalano Banton</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.329</v>
+        <v>-0.79</v>
       </c>
       <c r="E16" t="n">
-        <v>17.9</v>
+        <v>26.2</v>
       </c>
       <c r="F16" t="n">
         <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.015</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="17">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.449</v>
+        <v>-1.45</v>
       </c>
       <c r="E17" t="n">
         <v>27.1</v>
@@ -915,7 +915,7 @@
         <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.475</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="18">
@@ -944,7 +944,7 @@
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>1.154</v>
+        <v>1.499</v>
       </c>
     </row>
     <row r="19">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.025</v>
+        <v>2.024</v>
       </c>
       <c r="E19" t="n">
         <v>17</v>
@@ -973,7 +973,7 @@
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>0.03</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="20">
@@ -989,20 +989,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Ziaire Williams</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-4.698</v>
+        <v>-0.884</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>22.7</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.038</v>
+        <v>-0.387</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ziaire Williams</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.883</v>
+        <v>-1.994</v>
       </c>
       <c r="E21" t="n">
-        <v>22.7</v>
+        <v>23.9</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.258</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="22">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.994</v>
+        <v>-4.698</v>
       </c>
       <c r="E22" t="n">
-        <v>23.9</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-1.546</v>
       </c>
     </row>
     <row r="23">
@@ -1076,20 +1076,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nolan Traore</t>
+          <t>Drake Powell</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-5.274</v>
+        <v>-4.899</v>
       </c>
       <c r="E23" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.524</v>
+        <v>-2.315</v>
       </c>
     </row>
     <row r="24">
@@ -1105,20 +1105,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Drake Powell</t>
+          <t>Nolan Traore</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-4.898</v>
+        <v>-5.275</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="F24" t="n">
         <v>0.067</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.71</v>
+        <v>-2.445</v>
       </c>
     </row>
     <row r="25">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-6.069</v>
+        <v>-6.07</v>
       </c>
       <c r="E25" t="n">
         <v>23.2</v>
@@ -1147,7 +1147,7 @@
         <v>0.067</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.336</v>
+        <v>-2.908</v>
       </c>
     </row>
     <row r="26">
@@ -1176,7 +1176,7 @@
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>7.372</v>
+        <v>4.671</v>
       </c>
     </row>
     <row r="27">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.533</v>
+        <v>4.532</v>
       </c>
       <c r="E27" t="n">
         <v>30.1</v>
@@ -1205,7 +1205,7 @@
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>5.104</v>
+        <v>3.285</v>
       </c>
     </row>
     <row r="28">
@@ -1234,7 +1234,7 @@
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>3.307</v>
+        <v>2.152</v>
       </c>
     </row>
     <row r="29">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.207</v>
+        <v>1.206</v>
       </c>
       <c r="E29" t="n">
         <v>29.7</v>
@@ -1263,7 +1263,7 @@
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.845</v>
+        <v>1.178</v>
       </c>
     </row>
     <row r="30">
@@ -1292,7 +1292,7 @@
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1.735</v>
+        <v>1.102</v>
       </c>
     </row>
     <row r="31">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.827</v>
+        <v>0.826</v>
       </c>
       <c r="E31" t="n">
         <v>19.9</v>
@@ -1321,7 +1321,7 @@
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0.121</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="32">
@@ -1350,7 +1350,7 @@
         <v>0.7</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.007</v>
+        <v>-0.053</v>
       </c>
     </row>
     <row r="33">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-3.619</v>
+        <v>-3.62</v>
       </c>
       <c r="E33" t="n">
         <v>18.1</v>
@@ -1379,7 +1379,7 @@
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.081</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="34">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.796</v>
+        <v>5.795</v>
       </c>
       <c r="E34" t="n">
         <v>34.1</v>
@@ -1408,7 +1408,7 @@
         <v>0.333</v>
       </c>
       <c r="G34" t="n">
-        <v>6.115</v>
+        <v>4.353</v>
       </c>
     </row>
     <row r="35">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.963</v>
+        <v>3.962</v>
       </c>
       <c r="E35" t="n">
         <v>28.8</v>
@@ -1437,7 +1437,7 @@
         <v>0.333</v>
       </c>
       <c r="G35" t="n">
-        <v>4.064</v>
+        <v>2.575</v>
       </c>
     </row>
     <row r="36">
@@ -1453,20 +1453,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.428</v>
+        <v>2.263</v>
       </c>
       <c r="E36" t="n">
-        <v>33.3</v>
+        <v>23.4</v>
       </c>
       <c r="F36" t="n">
         <v>0.333</v>
       </c>
       <c r="G36" t="n">
-        <v>1.754</v>
+        <v>1.265</v>
       </c>
     </row>
     <row r="37">
@@ -1482,20 +1482,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2.264</v>
+        <v>1.427</v>
       </c>
       <c r="E37" t="n">
-        <v>23.4</v>
+        <v>33.3</v>
       </c>
       <c r="F37" t="n">
         <v>0.333</v>
       </c>
       <c r="G37" t="n">
-        <v>1.06</v>
+        <v>1.222</v>
       </c>
     </row>
     <row r="38">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-1.236</v>
+        <v>-1.237</v>
       </c>
       <c r="E38" t="n">
         <v>24.1</v>
@@ -1524,7 +1524,7 @@
         <v>0.333</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.463</v>
+        <v>-0.453</v>
       </c>
     </row>
     <row r="39">
@@ -1553,7 +1553,7 @@
         <v>0.333</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.881</v>
+        <v>-0.843</v>
       </c>
     </row>
     <row r="40">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-4.132</v>
+        <v>-4.133</v>
       </c>
       <c r="E40" t="n">
         <v>22.3</v>
@@ -1582,7 +1582,7 @@
         <v>0.333</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.005</v>
+        <v>-1.765</v>
       </c>
     </row>
     <row r="41">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-3.45</v>
+        <v>-3.451</v>
       </c>
       <c r="E41" t="n">
         <v>30.7</v>
@@ -1611,7 +1611,7 @@
         <v>0.333</v>
       </c>
       <c r="G41" t="n">
-        <v>-3.061</v>
+        <v>-1.991</v>
       </c>
     </row>
     <row r="42">
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9.026</v>
+        <v>9.097</v>
       </c>
       <c r="E42" t="n">
-        <v>32.6</v>
+        <v>33.2</v>
       </c>
       <c r="F42" t="n">
         <v>0.8</v>
       </c>
       <c r="G42" t="n">
-        <v>9.771000000000001</v>
+        <v>6.838</v>
       </c>
     </row>
     <row r="43">
@@ -1660,16 +1660,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8.439</v>
+        <v>8.458</v>
       </c>
       <c r="E43" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="F43" t="n">
         <v>0.8</v>
       </c>
       <c r="G43" t="n">
-        <v>9.226000000000001</v>
+        <v>6.799</v>
       </c>
     </row>
     <row r="44">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.376</v>
+        <v>4.624</v>
       </c>
       <c r="E44" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="F44" t="n">
         <v>0.8</v>
       </c>
       <c r="G44" t="n">
-        <v>5.091</v>
+        <v>3.522</v>
       </c>
     </row>
     <row r="45">
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3.717</v>
+        <v>3.828</v>
       </c>
       <c r="E45" t="n">
-        <v>28.2</v>
+        <v>27.8</v>
       </c>
       <c r="F45" t="n">
         <v>0.8</v>
       </c>
       <c r="G45" t="n">
-        <v>4.185</v>
+        <v>2.684</v>
       </c>
     </row>
     <row r="46">
@@ -1747,16 +1747,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.65</v>
+        <v>1.544</v>
       </c>
       <c r="E46" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="F46" t="n">
         <v>0.8</v>
       </c>
       <c r="G46" t="n">
-        <v>1.284</v>
+        <v>1.328</v>
       </c>
     </row>
     <row r="47">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Craig Porter Jr.</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.571</v>
+        <v>1.923</v>
       </c>
       <c r="E47" t="n">
-        <v>22.5</v>
+        <v>17.7</v>
       </c>
       <c r="F47" t="n">
         <v>0.8</v>
       </c>
       <c r="G47" t="n">
-        <v>0.066</v>
+        <v>1.001</v>
       </c>
     </row>
     <row r="48">
@@ -1801,20 +1801,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Craig Porter Jr.</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1.956</v>
+        <v>-0.598</v>
       </c>
       <c r="E48" t="n">
-        <v>17.7</v>
+        <v>21.6</v>
       </c>
       <c r="F48" t="n">
         <v>0.8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.06</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="49">
@@ -1834,16 +1834,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.76</v>
+        <v>-0.774</v>
       </c>
       <c r="E49" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="F49" t="n">
         <v>0.8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.032</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="50">
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.618</v>
+        <v>2.373</v>
       </c>
       <c r="E50" t="n">
-        <v>32.9</v>
+        <v>33.2</v>
       </c>
       <c r="F50" t="n">
         <v>0.233</v>
       </c>
       <c r="G50" t="n">
-        <v>2.838</v>
+        <v>1.804</v>
       </c>
     </row>
     <row r="51">
@@ -1892,16 +1892,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.489</v>
+        <v>1.62</v>
       </c>
       <c r="E51" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="F51" t="n">
         <v>0.233</v>
       </c>
       <c r="G51" t="n">
-        <v>0.701</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="52">
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.075</v>
+        <v>1.182</v>
       </c>
       <c r="E52" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="F52" t="n">
         <v>0.233</v>
       </c>
       <c r="G52" t="n">
-        <v>0.294</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="53">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-2.099</v>
+        <v>-2.1</v>
       </c>
       <c r="E53" t="n">
         <v>16.5</v>
@@ -1959,7 +1959,7 @@
         <v>0.233</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.02</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="54">
@@ -1979,16 +1979,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-2.001</v>
+        <v>-2.071</v>
       </c>
       <c r="E54" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="F54" t="n">
         <v>0.233</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.042</v>
+        <v>-0.672</v>
       </c>
     </row>
     <row r="55">
@@ -2004,20 +2004,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-4.443</v>
+        <v>-1.648</v>
       </c>
       <c r="E55" t="n">
-        <v>17.6</v>
+        <v>28.3</v>
       </c>
       <c r="F55" t="n">
         <v>0.233</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.089</v>
+        <v>-0.833</v>
       </c>
     </row>
     <row r="56">
@@ -2037,16 +2037,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-2.787</v>
+        <v>-2.984</v>
       </c>
       <c r="E56" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="F56" t="n">
         <v>0.233</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.44</v>
+        <v>-1.238</v>
       </c>
     </row>
     <row r="57">
@@ -2062,20 +2062,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1.541</v>
+        <v>-4.444</v>
       </c>
       <c r="E57" t="n">
-        <v>28.8</v>
+        <v>17.6</v>
       </c>
       <c r="F57" t="n">
         <v>0.233</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.236</v>
+        <v>-1.544</v>
       </c>
     </row>
     <row r="58">
@@ -2104,7 +2104,7 @@
         <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>19.028</v>
+        <v>14.349</v>
       </c>
     </row>
     <row r="59">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>9.095000000000001</v>
+        <v>9.093999999999999</v>
       </c>
       <c r="E59" t="n">
         <v>35.5</v>
@@ -2133,7 +2133,7 @@
         <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>9.917999999999999</v>
+        <v>7.339</v>
       </c>
     </row>
     <row r="60">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.869</v>
+        <v>2.868</v>
       </c>
       <c r="E60" t="n">
         <v>27.6</v>
@@ -2162,7 +2162,7 @@
         <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>3.321</v>
+        <v>2.129</v>
       </c>
     </row>
     <row r="61">
@@ -2178,20 +2178,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.08</v>
+        <v>0.334</v>
       </c>
       <c r="E61" t="n">
-        <v>32.7</v>
+        <v>25.9</v>
       </c>
       <c r="F61" t="n">
         <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>0.909</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="62">
@@ -2207,20 +2207,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.334</v>
+        <v>0.079</v>
       </c>
       <c r="E62" t="n">
-        <v>25.9</v>
+        <v>32.7</v>
       </c>
       <c r="F62" t="n">
         <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>0.89</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="63">
@@ -2249,7 +2249,7 @@
         <v>0.833</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.298</v>
+        <v>-0.191</v>
       </c>
     </row>
     <row r="64">
@@ -2265,20 +2265,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-2.833</v>
+        <v>-1.987</v>
       </c>
       <c r="E64" t="n">
-        <v>21.9</v>
+        <v>32.3</v>
       </c>
       <c r="F64" t="n">
         <v>0.833</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.446</v>
+        <v>-0.778</v>
       </c>
     </row>
     <row r="65">
@@ -2294,20 +2294,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-1.987</v>
+        <v>-2.833</v>
       </c>
       <c r="E65" t="n">
-        <v>32.3</v>
+        <v>21.9</v>
       </c>
       <c r="F65" t="n">
         <v>0.833</v>
       </c>
       <c r="G65" t="n">
-        <v>-1.146</v>
+        <v>-0.913</v>
       </c>
     </row>
     <row r="66">
@@ -2327,16 +2327,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.549</v>
+        <v>5.455</v>
       </c>
       <c r="E66" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="F66" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>5.868</v>
+        <v>3.652</v>
       </c>
     </row>
     <row r="67">
@@ -2356,16 +2356,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.524</v>
+        <v>1.555</v>
       </c>
       <c r="E67" t="n">
-        <v>26.3</v>
+        <v>25.8</v>
       </c>
       <c r="F67" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>1.956</v>
+        <v>1.339</v>
       </c>
     </row>
     <row r="68">
@@ -2385,16 +2385,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-0.26</v>
+        <v>-0.031</v>
       </c>
       <c r="E68" t="n">
-        <v>28.9</v>
+        <v>28.3</v>
       </c>
       <c r="F68" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.639</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="69">
@@ -2410,20 +2410,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.177</v>
+        <v>-0.027</v>
       </c>
       <c r="E69" t="n">
-        <v>26.5</v>
+        <v>21.8</v>
       </c>
       <c r="F69" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>0.618</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="70">
@@ -2439,20 +2439,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.417</v>
+        <v>-0.194</v>
       </c>
       <c r="E70" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="F70" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0.389</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="71">
@@ -2468,20 +2468,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-0.036</v>
+        <v>-0.585</v>
       </c>
       <c r="E71" t="n">
-        <v>20.7</v>
+        <v>27.5</v>
       </c>
       <c r="F71" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0.108</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="72">
@@ -2510,7 +2510,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="73">
@@ -2530,16 +2530,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-1.605</v>
+        <v>-1.698</v>
       </c>
       <c r="E73" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="F73" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.028</v>
+        <v>-0.305</v>
       </c>
     </row>
     <row r="74">
@@ -2555,20 +2555,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.659</v>
+        <v>4.309</v>
       </c>
       <c r="E74" t="n">
-        <v>33.4</v>
+        <v>21.6</v>
       </c>
       <c r="F74" t="n">
         <v>0.433</v>
       </c>
       <c r="G74" t="n">
-        <v>2.084</v>
+        <v>2.131</v>
       </c>
     </row>
     <row r="75">
@@ -2584,20 +2584,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Gary Payton II</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.822</v>
+        <v>2.772</v>
       </c>
       <c r="E75" t="n">
-        <v>32.4</v>
+        <v>22</v>
       </c>
       <c r="F75" t="n">
         <v>0.433</v>
       </c>
       <c r="G75" t="n">
-        <v>1.247</v>
+        <v>1.472</v>
       </c>
     </row>
     <row r="76">
@@ -2613,20 +2613,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4.31</v>
+        <v>1.658</v>
       </c>
       <c r="E76" t="n">
-        <v>21.6</v>
+        <v>33.4</v>
       </c>
       <c r="F76" t="n">
         <v>0.433</v>
       </c>
       <c r="G76" t="n">
-        <v>0.895</v>
+        <v>1.453</v>
       </c>
     </row>
     <row r="77">
@@ -2642,20 +2642,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Gary Payton II</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2.772</v>
+        <v>0.821</v>
       </c>
       <c r="E77" t="n">
-        <v>22</v>
+        <v>32.4</v>
       </c>
       <c r="F77" t="n">
         <v>0.433</v>
       </c>
       <c r="G77" t="n">
-        <v>0.756</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="78">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.572</v>
+        <v>-0.573</v>
       </c>
       <c r="E78" t="n">
         <v>21.2</v>
@@ -2684,7 +2684,7 @@
         <v>0.433</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.021</v>
+        <v>-0.061</v>
       </c>
     </row>
     <row r="79">
@@ -2713,7 +2713,7 @@
         <v>0.433</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.118</v>
+        <v>-0.094</v>
       </c>
     </row>
     <row r="80">
@@ -2729,20 +2729,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Will Richard</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-1.148</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>23.9</v>
+        <v>29.9</v>
       </c>
       <c r="F80" t="n">
         <v>0.433</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.349</v>
+        <v>-0.235</v>
       </c>
     </row>
     <row r="81">
@@ -2758,20 +2758,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Will Richard</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-1.149</v>
       </c>
       <c r="E81" t="n">
-        <v>29.9</v>
+        <v>23.9</v>
       </c>
       <c r="F81" t="n">
         <v>0.433</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.367</v>
+        <v>-0.356</v>
       </c>
     </row>
     <row r="82">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6.481</v>
+        <v>6.458</v>
       </c>
       <c r="E82" t="n">
-        <v>36.4</v>
+        <v>35.9</v>
       </c>
       <c r="F82" t="n">
         <v>0.767</v>
       </c>
       <c r="G82" t="n">
-        <v>7.244</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="83">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5.639</v>
+        <v>6.108</v>
       </c>
       <c r="E83" t="n">
         <v>33</v>
@@ -2829,7 +2829,7 @@
         <v>0.767</v>
       </c>
       <c r="G83" t="n">
-        <v>6.377</v>
+        <v>4.722</v>
       </c>
     </row>
     <row r="84">
@@ -2849,16 +2849,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3.661</v>
+        <v>3.696</v>
       </c>
       <c r="E84" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
       <c r="F84" t="n">
         <v>0.767</v>
       </c>
       <c r="G84" t="n">
-        <v>4.427</v>
+        <v>3.546</v>
       </c>
     </row>
     <row r="85">
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.171</v>
+        <v>3.078</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>31.1</v>
       </c>
       <c r="F85" t="n">
         <v>0.767</v>
       </c>
       <c r="G85" t="n">
-        <v>3.906</v>
+        <v>2.489</v>
       </c>
     </row>
     <row r="86">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-0.571</v>
+        <v>-0.464</v>
       </c>
       <c r="E86" t="n">
         <v>36.1</v>
@@ -2916,7 +2916,7 @@
         <v>0.767</v>
       </c>
       <c r="G86" t="n">
-        <v>0.195</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="87">
@@ -2932,20 +2932,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Josh Okogie</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-2.953</v>
+        <v>-1.972</v>
       </c>
       <c r="E87" t="n">
-        <v>16</v>
+        <v>24.7</v>
       </c>
       <c r="F87" t="n">
         <v>0.767</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.017</v>
+        <v>-0.621</v>
       </c>
     </row>
     <row r="88">
@@ -2961,20 +2961,20 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dorian Finney-Smith</t>
+          <t>Josh Okogie</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-6.718</v>
+        <v>-2.954</v>
       </c>
       <c r="E88" t="n">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="F88" t="n">
         <v>0.767</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.316</v>
+        <v>-0.727</v>
       </c>
     </row>
     <row r="89">
@@ -2990,20 +2990,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Dorian Finney-Smith</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-2.149</v>
+        <v>-6.718</v>
       </c>
       <c r="E89" t="n">
-        <v>25.6</v>
+        <v>19.2</v>
       </c>
       <c r="F89" t="n">
         <v>0.767</v>
       </c>
       <c r="G89" t="n">
-        <v>-1.006</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="90">
@@ -3032,7 +3032,7 @@
         <v>0.133</v>
       </c>
       <c r="G90" t="n">
-        <v>3.048</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="91">
@@ -3061,7 +3061,7 @@
         <v>0.133</v>
       </c>
       <c r="G91" t="n">
-        <v>0.991</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="92">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.695</v>
+        <v>1.694</v>
       </c>
       <c r="E92" t="n">
         <v>17.5</v>
@@ -3090,7 +3090,7 @@
         <v>0.133</v>
       </c>
       <c r="G92" t="n">
-        <v>0.036</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="93">
@@ -3119,7 +3119,7 @@
         <v>0.133</v>
       </c>
       <c r="G93" t="n">
-        <v>0.036</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="94">
@@ -3148,7 +3148,7 @@
         <v>0.133</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.023</v>
+        <v>-0.191</v>
       </c>
     </row>
     <row r="95">
@@ -3164,20 +3164,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.944</v>
+        <v>-2.67</v>
       </c>
       <c r="E95" t="n">
-        <v>20.5</v>
+        <v>21.9</v>
       </c>
       <c r="F95" t="n">
         <v>0.133</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.31</v>
+        <v>-1.157</v>
       </c>
     </row>
     <row r="96">
@@ -3193,20 +3193,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.669</v>
+        <v>-2.945</v>
       </c>
       <c r="E96" t="n">
-        <v>21.9</v>
+        <v>20.5</v>
       </c>
       <c r="F96" t="n">
         <v>0.133</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-1.202</v>
       </c>
     </row>
     <row r="97">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-3.805</v>
+        <v>-3.806</v>
       </c>
       <c r="E97" t="n">
         <v>22.1</v>
@@ -3235,7 +3235,7 @@
         <v>0.133</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.907</v>
+        <v>-1.694</v>
       </c>
     </row>
     <row r="98">
@@ -3255,16 +3255,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.725</v>
+        <v>11.746</v>
       </c>
       <c r="E98" t="n">
-        <v>30.7</v>
+        <v>30</v>
       </c>
       <c r="F98" t="n">
         <v>0.633</v>
       </c>
       <c r="G98" t="n">
-        <v>12.134</v>
+        <v>7.727</v>
       </c>
     </row>
     <row r="99">
@@ -3284,16 +3284,16 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3.62</v>
+        <v>3.829</v>
       </c>
       <c r="E99" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="F99" t="n">
         <v>0.633</v>
       </c>
       <c r="G99" t="n">
-        <v>3.957</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="100">
@@ -3313,16 +3313,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.184</v>
+        <v>0.244</v>
       </c>
       <c r="E100" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="F100" t="n">
         <v>0.633</v>
       </c>
       <c r="G100" t="n">
-        <v>0.673</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="101">
@@ -3342,16 +3342,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.062</v>
+        <v>0.108</v>
       </c>
       <c r="E101" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="F101" t="n">
         <v>0.633</v>
       </c>
       <c r="G101" t="n">
-        <v>0.672</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="102">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.276</v>
+        <v>0.241</v>
       </c>
       <c r="E102" t="n">
-        <v>25.5</v>
+        <v>24.9</v>
       </c>
       <c r="F102" t="n">
         <v>0.633</v>
       </c>
       <c r="G102" t="n">
-        <v>0.643</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="103">
@@ -3400,16 +3400,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-0.334</v>
+        <v>-0.269</v>
       </c>
       <c r="E103" t="n">
-        <v>26.2</v>
+        <v>26.6</v>
       </c>
       <c r="F103" t="n">
         <v>0.633</v>
       </c>
       <c r="G103" t="n">
-        <v>0.236</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="104">
@@ -3429,16 +3429,16 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.49</v>
+        <v>-0.322</v>
       </c>
       <c r="E104" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="F104" t="n">
         <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>0.117</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="105">
@@ -3458,16 +3458,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-1.544</v>
+        <v>-1.36</v>
       </c>
       <c r="E105" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="F105" t="n">
         <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.883</v>
+        <v>-0.446</v>
       </c>
     </row>
     <row r="106">
@@ -3487,16 +3487,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>15.421</v>
+        <v>15.372</v>
       </c>
       <c r="E106" t="n">
-        <v>36.7</v>
+        <v>37.3</v>
       </c>
       <c r="F106" t="n">
         <v>0.667</v>
       </c>
       <c r="G106" t="n">
-        <v>16.08</v>
+        <v>12.476</v>
       </c>
     </row>
     <row r="107">
@@ -3512,20 +3512,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5.867</v>
+        <v>5.617</v>
       </c>
       <c r="E107" t="n">
-        <v>34.2</v>
+        <v>37.9</v>
       </c>
       <c r="F107" t="n">
         <v>0.667</v>
       </c>
       <c r="G107" t="n">
-        <v>6.519</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="108">
@@ -3541,20 +3541,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5.616</v>
+        <v>5.977</v>
       </c>
       <c r="E108" t="n">
-        <v>37.9</v>
+        <v>34.3</v>
       </c>
       <c r="F108" t="n">
         <v>0.667</v>
       </c>
       <c r="G108" t="n">
-        <v>6.281</v>
+        <v>4.742</v>
       </c>
     </row>
     <row r="109">
@@ -3570,20 +3570,20 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.028</v>
+        <v>2.324</v>
       </c>
       <c r="E109" t="n">
-        <v>25.1</v>
+        <v>20.4</v>
       </c>
       <c r="F109" t="n">
         <v>0.667</v>
       </c>
       <c r="G109" t="n">
-        <v>0.454</v>
+        <v>1.273</v>
       </c>
     </row>
     <row r="110">
@@ -3599,20 +3599,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.996</v>
+        <v>0.894</v>
       </c>
       <c r="E110" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="F110" t="n">
         <v>0.667</v>
       </c>
       <c r="G110" t="n">
-        <v>0.297</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="111">
@@ -3628,20 +3628,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.723</v>
+        <v>0.144</v>
       </c>
       <c r="E111" t="n">
-        <v>21.6</v>
+        <v>25.1</v>
       </c>
       <c r="F111" t="n">
         <v>0.667</v>
       </c>
       <c r="G111" t="n">
-        <v>0.271</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="112">
@@ -3661,16 +3661,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-1.289</v>
+        <v>-1.246</v>
       </c>
       <c r="E112" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="F112" t="n">
         <v>0.667</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.012</v>
+        <v>-0.216</v>
       </c>
     </row>
     <row r="113">
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-2.515</v>
+        <v>-2.503</v>
       </c>
       <c r="E113" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="F113" t="n">
         <v>0.667</v>
       </c>
       <c r="G113" t="n">
-        <v>-1.11</v>
+        <v>-0.955</v>
       </c>
     </row>
     <row r="114">
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5.092</v>
+        <v>5.091</v>
       </c>
       <c r="E114" t="n">
         <v>24</v>
@@ -3728,7 +3728,7 @@
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>2.709</v>
+        <v>2.683</v>
       </c>
     </row>
     <row r="115">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2.756</v>
+        <v>2.755</v>
       </c>
       <c r="E115" t="n">
         <v>25.7</v>
@@ -3757,7 +3757,7 @@
         <v>0.267</v>
       </c>
       <c r="G115" t="n">
-        <v>2.223</v>
+        <v>1.618</v>
       </c>
     </row>
     <row r="116">
@@ -3786,7 +3786,7 @@
         <v>0.267</v>
       </c>
       <c r="G116" t="n">
-        <v>0.915</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="117">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-0.569</v>
+        <v>-0.57</v>
       </c>
       <c r="E117" t="n">
         <v>26.1</v>
@@ -3815,7 +3815,7 @@
         <v>0.267</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.237</v>
+        <v>-0.165</v>
       </c>
     </row>
     <row r="118">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-1.646</v>
+        <v>-1.647</v>
       </c>
       <c r="E118" t="n">
         <v>25.8</v>
@@ -3844,7 +3844,7 @@
         <v>0.267</v>
       </c>
       <c r="G118" t="n">
-        <v>-1.029</v>
+        <v>-0.742</v>
       </c>
     </row>
     <row r="119">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-2.35</v>
+        <v>-2.351</v>
       </c>
       <c r="E119" t="n">
         <v>25.3</v>
@@ -3873,7 +3873,7 @@
         <v>0.267</v>
       </c>
       <c r="G119" t="n">
-        <v>-1.42</v>
+        <v>-1.097</v>
       </c>
     </row>
     <row r="120">
@@ -3889,20 +3889,20 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Rayan Rupert</t>
+          <t>Jahmai Mashack</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-5.705</v>
+        <v>-4.435</v>
       </c>
       <c r="E120" t="n">
-        <v>24.2</v>
+        <v>25.4</v>
       </c>
       <c r="F120" t="n">
         <v>0.267</v>
       </c>
       <c r="G120" t="n">
-        <v>-2.858</v>
+        <v>-2.204</v>
       </c>
     </row>
     <row r="121">
@@ -3918,20 +3918,20 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jahmai Mashack</t>
+          <t>Rayan Rupert</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-4.435</v>
+        <v>-5.706</v>
       </c>
       <c r="E121" t="n">
-        <v>25.4</v>
+        <v>24.2</v>
       </c>
       <c r="F121" t="n">
         <v>0.267</v>
       </c>
       <c r="G121" t="n">
-        <v>-2.901</v>
+        <v>-2.739</v>
       </c>
     </row>
     <row r="122">
@@ -3960,7 +3960,7 @@
         <v>0.6</v>
       </c>
       <c r="G122" t="n">
-        <v>3.462</v>
+        <v>2.539</v>
       </c>
     </row>
     <row r="123">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.345</v>
+        <v>2.344</v>
       </c>
       <c r="E123" t="n">
         <v>31.7</v>
@@ -3989,7 +3989,7 @@
         <v>0.6</v>
       </c>
       <c r="G123" t="n">
-        <v>2.916</v>
+        <v>1.942</v>
       </c>
     </row>
     <row r="124">
@@ -4005,20 +4005,20 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1.687</v>
+        <v>2.354</v>
       </c>
       <c r="E124" t="n">
-        <v>28.3</v>
+        <v>23</v>
       </c>
       <c r="F124" t="n">
         <v>0.6</v>
       </c>
       <c r="G124" t="n">
-        <v>2.123</v>
+        <v>1.414</v>
       </c>
     </row>
     <row r="125">
@@ -4034,20 +4034,20 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.998</v>
+        <v>1.687</v>
       </c>
       <c r="E125" t="n">
-        <v>26.2</v>
+        <v>28.3</v>
       </c>
       <c r="F125" t="n">
         <v>0.6</v>
       </c>
       <c r="G125" t="n">
-        <v>1.264</v>
+        <v>1.346</v>
       </c>
     </row>
     <row r="126">
@@ -4063,20 +4063,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2.354</v>
+        <v>0.997</v>
       </c>
       <c r="E126" t="n">
-        <v>23</v>
+        <v>26.2</v>
       </c>
       <c r="F126" t="n">
         <v>0.6</v>
       </c>
       <c r="G126" t="n">
-        <v>1.041</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="127">
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.411</v>
+        <v>0.41</v>
       </c>
       <c r="E127" t="n">
         <v>27.4</v>
@@ -4105,7 +4105,7 @@
         <v>0.6</v>
       </c>
       <c r="G127" t="n">
-        <v>0.892</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="128">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-0.618</v>
+        <v>-0.619</v>
       </c>
       <c r="E128" t="n">
         <v>19.3</v>
@@ -4134,7 +4134,7 @@
         <v>0.6</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.001</v>
+        <v>-0.008</v>
       </c>
     </row>
     <row r="129">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.774</v>
+        <v>-0.775</v>
       </c>
       <c r="E129" t="n">
         <v>30.2</v>
@@ -4163,7 +4163,7 @@
         <v>0.6</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.17</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="130">
@@ -4183,16 +4183,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4.089</v>
+        <v>3.886</v>
       </c>
       <c r="E130" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="F130" t="n">
         <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>4.249</v>
+        <v>2.668</v>
       </c>
     </row>
     <row r="131">
@@ -4212,16 +4212,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.501</v>
+        <v>0.555</v>
       </c>
       <c r="E131" t="n">
-        <v>22.5</v>
+        <v>23.1</v>
       </c>
       <c r="F131" t="n">
         <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>0.199</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="132">
@@ -4237,20 +4237,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-0.727</v>
+        <v>-0.404</v>
       </c>
       <c r="E132" t="n">
-        <v>17.9</v>
+        <v>24.9</v>
       </c>
       <c r="F132" t="n">
         <v>0.2</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.013</v>
+        <v>-0.106</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-0.422</v>
+        <v>-1.43</v>
       </c>
       <c r="E133" t="n">
-        <v>25.2</v>
+        <v>20</v>
       </c>
       <c r="F133" t="n">
         <v>0.2</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.15</v>
+        <v>-0.513</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-4.154</v>
+        <v>-2.572</v>
       </c>
       <c r="E134" t="n">
-        <v>21.3</v>
+        <v>22.5</v>
       </c>
       <c r="F134" t="n">
         <v>0.2</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.643</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="135">
@@ -4328,16 +4328,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-2.75</v>
+        <v>-2.632</v>
       </c>
       <c r="E135" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="F135" t="n">
         <v>0.2</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.644</v>
+        <v>-1.119</v>
       </c>
     </row>
     <row r="136">
@@ -4353,20 +4353,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-2.561</v>
+        <v>-2.513</v>
       </c>
       <c r="E136" t="n">
-        <v>22.5</v>
+        <v>26.8</v>
       </c>
       <c r="F136" t="n">
         <v>0.2</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.677</v>
+        <v>-1.293</v>
       </c>
     </row>
     <row r="137">
@@ -4382,20 +4382,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-2.223</v>
+        <v>-3.482</v>
       </c>
       <c r="E137" t="n">
-        <v>26.3</v>
+        <v>21.9</v>
       </c>
       <c r="F137" t="n">
         <v>0.2</v>
       </c>
       <c r="G137" t="n">
-        <v>-1.608</v>
+        <v>-1.499</v>
       </c>
     </row>
     <row r="138">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7.353</v>
+        <v>7.352</v>
       </c>
       <c r="E138" t="n">
         <v>35.6</v>
@@ -4424,7 +4424,7 @@
         <v>0.733</v>
       </c>
       <c r="G138" t="n">
-        <v>8.077999999999999</v>
+        <v>5.999</v>
       </c>
     </row>
     <row r="139">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3.945</v>
+        <v>3.944</v>
       </c>
       <c r="E139" t="n">
         <v>31.7</v>
@@ -4453,7 +4453,7 @@
         <v>0.733</v>
       </c>
       <c r="G139" t="n">
-        <v>4.631</v>
+        <v>3.085</v>
       </c>
     </row>
     <row r="140">
@@ -4482,7 +4482,7 @@
         <v>0.733</v>
       </c>
       <c r="G140" t="n">
-        <v>3.056</v>
+        <v>1.958</v>
       </c>
     </row>
     <row r="141">
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1.64</v>
+        <v>1.639</v>
       </c>
       <c r="E141" t="n">
         <v>30.3</v>
@@ -4511,7 +4511,7 @@
         <v>0.733</v>
       </c>
       <c r="G141" t="n">
-        <v>2.321</v>
+        <v>1.499</v>
       </c>
     </row>
     <row r="142">
@@ -4540,7 +4540,7 @@
         <v>0.733</v>
       </c>
       <c r="G142" t="n">
-        <v>1.868</v>
+        <v>1.394</v>
       </c>
     </row>
     <row r="143">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.857</v>
+        <v>0.856</v>
       </c>
       <c r="E143" t="n">
         <v>31.7</v>
@@ -4569,7 +4569,7 @@
         <v>0.733</v>
       </c>
       <c r="G143" t="n">
-        <v>1.574</v>
+        <v>1.048</v>
       </c>
     </row>
     <row r="144">
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1.597</v>
+        <v>1.596</v>
       </c>
       <c r="E144" t="n">
         <v>19.7</v>
@@ -4598,7 +4598,7 @@
         <v>0.733</v>
       </c>
       <c r="G144" t="n">
-        <v>0.161</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="145">
@@ -4627,7 +4627,7 @@
         <v>0.733</v>
       </c>
       <c r="G145" t="n">
-        <v>0.018</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="146">
@@ -4656,7 +4656,7 @@
         <v>0.3</v>
       </c>
       <c r="G146" t="n">
-        <v>4.991</v>
+        <v>3.192</v>
       </c>
     </row>
     <row r="147">
@@ -4672,20 +4672,20 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2.331</v>
+        <v>2.248</v>
       </c>
       <c r="E147" t="n">
-        <v>30.7</v>
+        <v>32.7</v>
       </c>
       <c r="F147" t="n">
         <v>0.3</v>
       </c>
       <c r="G147" t="n">
-        <v>2.583</v>
+        <v>1.734</v>
       </c>
     </row>
     <row r="148">
@@ -4701,20 +4701,20 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2.249</v>
+        <v>2.33</v>
       </c>
       <c r="E148" t="n">
-        <v>32.7</v>
+        <v>30.7</v>
       </c>
       <c r="F148" t="n">
         <v>0.3</v>
       </c>
       <c r="G148" t="n">
-        <v>2.535</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="149">
@@ -4743,7 +4743,7 @@
         <v>0.3</v>
       </c>
       <c r="G149" t="n">
-        <v>0.078</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="150">
@@ -4772,7 +4772,7 @@
         <v>0.3</v>
       </c>
       <c r="G150" t="n">
-        <v>0.004</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="151">
@@ -4788,20 +4788,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-2.669</v>
+        <v>-1.445</v>
       </c>
       <c r="E151" t="n">
-        <v>19.9</v>
+        <v>22.4</v>
       </c>
       <c r="F151" t="n">
         <v>0.3</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.185</v>
+        <v>-0.533</v>
       </c>
     </row>
     <row r="152">
@@ -4817,20 +4817,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-1.444</v>
+        <v>-2.669</v>
       </c>
       <c r="E152" t="n">
-        <v>22.4</v>
+        <v>19.9</v>
       </c>
       <c r="F152" t="n">
         <v>0.3</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.312</v>
+        <v>-0.982</v>
       </c>
     </row>
     <row r="153">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-2.857</v>
+        <v>-2.858</v>
       </c>
       <c r="E153" t="n">
         <v>29.5</v>
@@ -4859,7 +4859,7 @@
         <v>0.3</v>
       </c>
       <c r="G153" t="n">
-        <v>-2.464</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="154">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>6.553</v>
+        <v>6.611</v>
       </c>
       <c r="E154" t="n">
         <v>36.1</v>
@@ -4888,7 +4888,7 @@
         <v>0.867</v>
       </c>
       <c r="G154" t="n">
-        <v>7.415</v>
+        <v>5.626</v>
       </c>
     </row>
     <row r="155">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4.228</v>
+        <v>4.173</v>
       </c>
       <c r="E155" t="n">
-        <v>29.2</v>
+        <v>29.5</v>
       </c>
       <c r="F155" t="n">
         <v>0.867</v>
       </c>
       <c r="G155" t="n">
-        <v>4.874</v>
+        <v>3.097</v>
       </c>
     </row>
     <row r="156">
@@ -4937,16 +4937,16 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3.166</v>
+        <v>3.266</v>
       </c>
       <c r="E156" t="n">
-        <v>29.4</v>
+        <v>29.9</v>
       </c>
       <c r="F156" t="n">
         <v>0.867</v>
       </c>
       <c r="G156" t="n">
-        <v>3.883</v>
+        <v>2.572</v>
       </c>
     </row>
     <row r="157">
@@ -4966,16 +4966,16 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3.041</v>
+        <v>3.003</v>
       </c>
       <c r="E157" t="n">
-        <v>30.3</v>
+        <v>30.9</v>
       </c>
       <c r="F157" t="n">
         <v>0.867</v>
       </c>
       <c r="G157" t="n">
-        <v>3.823</v>
+        <v>2.492</v>
       </c>
     </row>
     <row r="158">
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1.8</v>
+        <v>1.684</v>
       </c>
       <c r="E158" t="n">
-        <v>33.4</v>
+        <v>33.7</v>
       </c>
       <c r="F158" t="n">
         <v>0.867</v>
       </c>
       <c r="G158" t="n">
-        <v>2.658</v>
+        <v>1.792</v>
       </c>
     </row>
     <row r="159">
@@ -5020,20 +5020,20 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.744</v>
+        <v>3.052</v>
       </c>
       <c r="E159" t="n">
-        <v>29.4</v>
+        <v>19.7</v>
       </c>
       <c r="F159" t="n">
         <v>0.867</v>
       </c>
       <c r="G159" t="n">
-        <v>1.551</v>
+        <v>1.606</v>
       </c>
     </row>
     <row r="160">
@@ -5049,20 +5049,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3.201</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="E160" t="n">
-        <v>19.7</v>
+        <v>28.9</v>
       </c>
       <c r="F160" t="n">
         <v>0.867</v>
       </c>
       <c r="G160" t="n">
-        <v>0.282</v>
+        <v>0.859</v>
       </c>
     </row>
     <row r="161">
@@ -5078,20 +5078,20 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jordan Clarkson</t>
+          <t>Jose Alvarado</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-4.208</v>
+        <v>-0.108</v>
       </c>
       <c r="E161" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="F161" t="n">
         <v>0.867</v>
       </c>
       <c r="G161" t="n">
-        <v>-0.023</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="162">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>14.814</v>
+        <v>14.813</v>
       </c>
       <c r="E162" t="n">
         <v>33.5</v>
@@ -5120,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>15.76</v>
+        <v>11.027</v>
       </c>
     </row>
     <row r="163">
@@ -5149,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>4.88</v>
+        <v>3.116</v>
       </c>
     </row>
     <row r="164">
@@ -5165,20 +5165,20 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1.595</v>
+        <v>3.337</v>
       </c>
       <c r="E164" t="n">
-        <v>27</v>
+        <v>22.5</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>2.231</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="165">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.891</v>
+        <v>1.89</v>
       </c>
       <c r="E165" t="n">
         <v>25.7</v>
@@ -5207,7 +5207,7 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>2.134</v>
+        <v>1.549</v>
       </c>
     </row>
     <row r="166">
@@ -5223,20 +5223,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3.338</v>
+        <v>1.594</v>
       </c>
       <c r="E166" t="n">
-        <v>22.5</v>
+        <v>27</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1.237</v>
+        <v>1.461</v>
       </c>
     </row>
     <row r="167">
@@ -5252,20 +5252,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.097</v>
+        <v>1.26</v>
       </c>
       <c r="E167" t="n">
-        <v>25.7</v>
+        <v>22.2</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.045</v>
       </c>
     </row>
     <row r="168">
@@ -5281,20 +5281,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1.26</v>
+        <v>0.096</v>
       </c>
       <c r="E168" t="n">
-        <v>22.2</v>
+        <v>25.7</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.57</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="169">
@@ -5323,7 +5323,7 @@
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>-2.733</v>
+        <v>-1.917</v>
       </c>
     </row>
     <row r="170">
@@ -5352,7 +5352,7 @@
         <v>0.4</v>
       </c>
       <c r="G170" t="n">
-        <v>3.785</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="171">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3.265</v>
+        <v>3.264</v>
       </c>
       <c r="E171" t="n">
         <v>33.9</v>
@@ -5381,7 +5381,7 @@
         <v>0.4</v>
       </c>
       <c r="G171" t="n">
-        <v>3.655</v>
+        <v>2.586</v>
       </c>
     </row>
     <row r="172">
@@ -5410,7 +5410,7 @@
         <v>0.4</v>
       </c>
       <c r="G172" t="n">
-        <v>3.305</v>
+        <v>2.094</v>
       </c>
     </row>
     <row r="173">
@@ -5426,20 +5426,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jett Howard</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-2.549</v>
+        <v>-0.603</v>
       </c>
       <c r="E173" t="n">
-        <v>16.8</v>
+        <v>29.2</v>
       </c>
       <c r="F173" t="n">
         <v>0.4</v>
       </c>
       <c r="G173" t="n">
-        <v>-0.029</v>
+        <v>-0.124</v>
       </c>
     </row>
     <row r="174">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-1.053</v>
+        <v>-1.054</v>
       </c>
       <c r="E174" t="n">
         <v>21.1</v>
@@ -5468,7 +5468,7 @@
         <v>0.4</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.098</v>
+        <v>-0.288</v>
       </c>
     </row>
     <row r="175">
@@ -5484,20 +5484,20 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-0.602</v>
+        <v>-1.008</v>
       </c>
       <c r="E175" t="n">
-        <v>29.2</v>
+        <v>29.8</v>
       </c>
       <c r="F175" t="n">
         <v>0.4</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.194</v>
+        <v>-0.378</v>
       </c>
     </row>
     <row r="176">
@@ -5513,20 +5513,20 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Orlando Robinson</t>
+          <t>Jett Howard</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-2.274</v>
+        <v>-2.549</v>
       </c>
       <c r="E176" t="n">
-        <v>22.2</v>
+        <v>16.8</v>
       </c>
       <c r="F176" t="n">
         <v>0.4</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.47</v>
+        <v>-0.754</v>
       </c>
     </row>
     <row r="177">
@@ -5542,20 +5542,20 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Orlando Robinson</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>-1.008</v>
+        <v>-2.274</v>
       </c>
       <c r="E177" t="n">
-        <v>29.8</v>
+        <v>22.2</v>
       </c>
       <c r="F177" t="n">
         <v>0.4</v>
       </c>
       <c r="G177" t="n">
-        <v>-0.59</v>
+        <v>-0.866</v>
       </c>
     </row>
     <row r="178">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>9.291</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="E178" t="n">
         <v>36.3</v>
@@ -5584,7 +5584,7 @@
         <v>0.467</v>
       </c>
       <c r="G178" t="n">
-        <v>9.750999999999999</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="179">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5.555</v>
+        <v>5.554</v>
       </c>
       <c r="E179" t="n">
         <v>33.5</v>
@@ -5613,7 +5613,7 @@
         <v>0.467</v>
       </c>
       <c r="G179" t="n">
-        <v>6.002</v>
+        <v>4.203</v>
       </c>
     </row>
     <row r="180">
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2.012</v>
+        <v>2.011</v>
       </c>
       <c r="E180" t="n">
         <v>33</v>
@@ -5642,7 +5642,7 @@
         <v>0.467</v>
       </c>
       <c r="G180" t="n">
-        <v>2.467</v>
+        <v>1.703</v>
       </c>
     </row>
     <row r="181">
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.725</v>
+        <v>0.724</v>
       </c>
       <c r="E181" t="n">
         <v>33.3</v>
@@ -5671,7 +5671,7 @@
         <v>0.467</v>
       </c>
       <c r="G181" t="n">
-        <v>1.187</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="182">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-0.186</v>
+        <v>-0.187</v>
       </c>
       <c r="E182" t="n">
         <v>31.5</v>
@@ -5700,7 +5700,7 @@
         <v>0.467</v>
       </c>
       <c r="G182" t="n">
-        <v>0.278</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="183">
@@ -5729,7 +5729,7 @@
         <v>0.467</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.105</v>
+        <v>-0.144</v>
       </c>
     </row>
     <row r="184">
@@ -5758,7 +5758,7 @@
         <v>0.467</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.355</v>
+        <v>-0.419</v>
       </c>
     </row>
     <row r="185">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>-1.474</v>
+        <v>-1.475</v>
       </c>
       <c r="E185" t="n">
         <v>32.7</v>
@@ -5787,7 +5787,7 @@
         <v>0.467</v>
       </c>
       <c r="G185" t="n">
-        <v>-1.002</v>
+        <v>-0.6879999999999999</v>
       </c>
     </row>
     <row r="186">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>4.811</v>
+        <v>4.81</v>
       </c>
       <c r="E186" t="n">
         <v>33.1</v>
@@ -5816,7 +5816,7 @@
         <v>0.533</v>
       </c>
       <c r="G186" t="n">
-        <v>5.321</v>
+        <v>3.684</v>
       </c>
     </row>
     <row r="187">
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4.258</v>
+        <v>4.257</v>
       </c>
       <c r="E187" t="n">
         <v>29.7</v>
@@ -5845,7 +5845,7 @@
         <v>0.533</v>
       </c>
       <c r="G187" t="n">
-        <v>4.642</v>
+        <v>2.967</v>
       </c>
     </row>
     <row r="188">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3.237</v>
+        <v>3.236</v>
       </c>
       <c r="E188" t="n">
         <v>28.6</v>
@@ -5874,7 +5874,7 @@
         <v>0.533</v>
       </c>
       <c r="G188" t="n">
-        <v>3.542</v>
+        <v>2.244</v>
       </c>
     </row>
     <row r="189">
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="E189" t="n">
         <v>24.4</v>
@@ -5903,7 +5903,7 @@
         <v>0.533</v>
       </c>
       <c r="G189" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="190">
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.262</v>
+        <v>0.261</v>
       </c>
       <c r="E190" t="n">
         <v>26.4</v>
@@ -5932,7 +5932,7 @@
         <v>0.533</v>
       </c>
       <c r="G190" t="n">
-        <v>0.639</v>
+        <v>0.436</v>
       </c>
     </row>
     <row r="191">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>-0.333</v>
+        <v>-0.334</v>
       </c>
       <c r="E191" t="n">
         <v>29.4</v>
@@ -5961,7 +5961,7 @@
         <v>0.533</v>
       </c>
       <c r="G191" t="n">
-        <v>0.193</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="192">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-1.045</v>
+        <v>-1.046</v>
       </c>
       <c r="E192" t="n">
         <v>30.7</v>
@@ -5990,7 +5990,7 @@
         <v>0.533</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.503</v>
+        <v>-0.328</v>
       </c>
     </row>
     <row r="193">
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>-1.866</v>
+        <v>-1.867</v>
       </c>
       <c r="E193" t="n">
         <v>30.3</v>
@@ -6019,7 +6019,7 @@
         <v>0.533</v>
       </c>
       <c r="G193" t="n">
-        <v>-1.303</v>
+        <v>-0.842</v>
       </c>
     </row>
     <row r="194">
@@ -6039,16 +6039,16 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>5.605</v>
+        <v>5.577</v>
       </c>
       <c r="E194" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>5.656</v>
+        <v>3.575</v>
       </c>
     </row>
     <row r="195">
@@ -6068,16 +6068,16 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>2.967</v>
+        <v>2.951</v>
       </c>
       <c r="E195" t="n">
-        <v>30.1</v>
+        <v>29.4</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>3.251</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="196">
@@ -6097,16 +6097,16 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3.346</v>
+        <v>3.344</v>
       </c>
       <c r="E196" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="F196" t="n">
         <v>0.367</v>
       </c>
       <c r="G196" t="n">
-        <v>2.946</v>
+        <v>2.001</v>
       </c>
     </row>
     <row r="197">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>-0.952</v>
+        <v>-0.953</v>
       </c>
       <c r="E197" t="n">
         <v>20.6</v>
@@ -6135,7 +6135,7 @@
         <v>0.367</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.068</v>
+        <v>-0.252</v>
       </c>
     </row>
     <row r="198">
@@ -6151,20 +6151,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-3.282</v>
+        <v>-1.442</v>
       </c>
       <c r="E198" t="n">
-        <v>18.8</v>
+        <v>31.8</v>
       </c>
       <c r="F198" t="n">
         <v>0.367</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.127</v>
+        <v>-0.713</v>
       </c>
     </row>
     <row r="199">
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-2.234</v>
+        <v>-1.928</v>
       </c>
       <c r="E199" t="n">
         <v>24.2</v>
@@ -6193,7 +6193,7 @@
         <v>0.367</v>
       </c>
       <c r="G199" t="n">
-        <v>-0.987</v>
+        <v>-0.786</v>
       </c>
     </row>
     <row r="200">
@@ -6209,20 +6209,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-1.605</v>
+        <v>-3.362</v>
       </c>
       <c r="E200" t="n">
-        <v>32.1</v>
+        <v>19.4</v>
       </c>
       <c r="F200" t="n">
         <v>0.367</v>
       </c>
       <c r="G200" t="n">
-        <v>-1.228</v>
+        <v>-1.213</v>
       </c>
     </row>
     <row r="201">
@@ -6242,16 +6242,16 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-2.814</v>
+        <v>-2.965</v>
       </c>
       <c r="E201" t="n">
-        <v>25.2</v>
+        <v>24.1</v>
       </c>
       <c r="F201" t="n">
         <v>0.367</v>
       </c>
       <c r="G201" t="n">
-        <v>-1.634</v>
+        <v>-1.304</v>
       </c>
     </row>
     <row r="202">
@@ -6280,7 +6280,7 @@
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>2.839</v>
+        <v>1.805</v>
       </c>
     </row>
     <row r="203">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.285</v>
+        <v>0.284</v>
       </c>
       <c r="E203" t="n">
         <v>31.6</v>
@@ -6309,7 +6309,7 @@
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.381</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="204">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="E204" t="n">
         <v>22.8</v>
@@ -6338,7 +6338,7 @@
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.153</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="205">
@@ -6354,20 +6354,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-2.244</v>
+        <v>-1.191</v>
       </c>
       <c r="E205" t="n">
-        <v>22.1</v>
+        <v>33</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.521</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="206">
@@ -6383,20 +6383,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-1.19</v>
+        <v>-2.245</v>
       </c>
       <c r="E206" t="n">
-        <v>33</v>
+        <v>22.1</v>
       </c>
       <c r="F206" t="n">
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-1.085</v>
+        <v>-0.988</v>
       </c>
     </row>
     <row r="207">
@@ -6425,7 +6425,7 @@
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-2.692</v>
+        <v>-1.706</v>
       </c>
     </row>
     <row r="208">
@@ -6454,7 +6454,7 @@
         <v>0.1</v>
       </c>
       <c r="G208" t="n">
-        <v>-3.138</v>
+        <v>-2.141</v>
       </c>
     </row>
     <row r="209">
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-4.226</v>
+        <v>-4.227</v>
       </c>
       <c r="E209" t="n">
         <v>32.5</v>
@@ -6483,7 +6483,7 @@
         <v>0.1</v>
       </c>
       <c r="G209" t="n">
-        <v>-4.101</v>
+        <v>-2.791</v>
       </c>
     </row>
     <row r="210">
@@ -6512,7 +6512,7 @@
         <v>0.967</v>
       </c>
       <c r="G210" t="n">
-        <v>11.539</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="211">
@@ -6541,7 +6541,7 @@
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>5.056</v>
+        <v>3.209</v>
       </c>
     </row>
     <row r="212">
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>3.515</v>
+        <v>3.514</v>
       </c>
       <c r="E212" t="n">
         <v>28.9</v>
@@ -6570,7 +6570,7 @@
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>4.259</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="213">
@@ -6586,20 +6586,20 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.333</v>
+        <v>1.504</v>
       </c>
       <c r="E213" t="n">
-        <v>30</v>
+        <v>24.1</v>
       </c>
       <c r="F213" t="n">
         <v>0.967</v>
       </c>
       <c r="G213" t="n">
-        <v>1.265</v>
+        <v>1.239</v>
       </c>
     </row>
     <row r="214">
@@ -6615,20 +6615,20 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1.505</v>
+        <v>1.211</v>
       </c>
       <c r="E214" t="n">
-        <v>24.1</v>
+        <v>22.1</v>
       </c>
       <c r="F214" t="n">
         <v>0.967</v>
       </c>
       <c r="G214" t="n">
-        <v>1.258</v>
+        <v>1.002</v>
       </c>
     </row>
     <row r="215">
@@ -6644,20 +6644,20 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.262</v>
+        <v>0.333</v>
       </c>
       <c r="E215" t="n">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="F215" t="n">
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>1.023</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -6673,20 +6673,20 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1.212</v>
+        <v>0.262</v>
       </c>
       <c r="E216" t="n">
-        <v>22.1</v>
+        <v>26.7</v>
       </c>
       <c r="F216" t="n">
         <v>0.967</v>
       </c>
       <c r="G216" t="n">
-        <v>0.524</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="217">
@@ -6715,7 +6715,7 @@
         <v>0.967</v>
       </c>
       <c r="G217" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="218">
@@ -6735,16 +6735,16 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>5.986</v>
+        <v>6.29</v>
       </c>
       <c r="E218" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="F218" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G218" t="n">
-        <v>6.518</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="219">
@@ -6764,16 +6764,16 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2.19</v>
+        <v>2.055</v>
       </c>
       <c r="E219" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="F219" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G219" t="n">
-        <v>2.75</v>
+        <v>1.868</v>
       </c>
     </row>
     <row r="220">
@@ -6789,20 +6789,20 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1.445</v>
+        <v>3.428</v>
       </c>
       <c r="E220" t="n">
-        <v>31.6</v>
+        <v>20</v>
       </c>
       <c r="F220" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G220" t="n">
-        <v>1.991</v>
+        <v>1.661</v>
       </c>
     </row>
     <row r="221">
@@ -6818,20 +6818,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.646</v>
+        <v>1.607</v>
       </c>
       <c r="E221" t="n">
-        <v>26.4</v>
+        <v>31.1</v>
       </c>
       <c r="F221" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G221" t="n">
-        <v>1.795</v>
+        <v>1.409</v>
       </c>
     </row>
     <row r="222">
@@ -6847,20 +6847,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.739</v>
       </c>
       <c r="E222" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="F222" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G222" t="n">
-        <v>0.995</v>
+        <v>1.299</v>
       </c>
     </row>
     <row r="223">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>3.382</v>
+        <v>0.86</v>
       </c>
       <c r="E223" t="n">
-        <v>19.5</v>
+        <v>24.2</v>
       </c>
       <c r="F223" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G223" t="n">
-        <v>0.247</v>
+        <v>0.719</v>
       </c>
     </row>
     <row r="224">
@@ -6905,20 +6905,20 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.931</v>
+        <v>-0.653</v>
       </c>
       <c r="E224" t="n">
-        <v>21.3</v>
+        <v>22.3</v>
       </c>
       <c r="F224" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="225">
@@ -6934,20 +6934,20 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-0.971</v>
+        <v>-0.903</v>
       </c>
       <c r="E225" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="F225" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.093</v>
+        <v>-0.153</v>
       </c>
     </row>
     <row r="226">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1.03</v>
+        <v>1.029</v>
       </c>
       <c r="E226" t="n">
         <v>25.7</v>
@@ -6976,7 +6976,7 @@
         <v>0.167</v>
       </c>
       <c r="G226" t="n">
-        <v>0.881</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="227">
@@ -7005,7 +7005,7 @@
         <v>0.167</v>
       </c>
       <c r="G227" t="n">
-        <v>0.786</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="228">
@@ -7021,20 +7021,20 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-1.106</v>
+        <v>-0.49</v>
       </c>
       <c r="E228" t="n">
-        <v>19</v>
+        <v>27.1</v>
       </c>
       <c r="F228" t="n">
         <v>0.167</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.046</v>
+        <v>-0.182</v>
       </c>
     </row>
     <row r="229">
@@ -7050,20 +7050,20 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Svi Mykhailiuk</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-1.483</v>
+        <v>-1.107</v>
       </c>
       <c r="E229" t="n">
-        <v>20.6</v>
+        <v>19</v>
       </c>
       <c r="F229" t="n">
         <v>0.167</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.151</v>
+        <v>-0.373</v>
       </c>
     </row>
     <row r="230">
@@ -7079,20 +7079,20 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Svi Mykhailiuk</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-0.489</v>
+        <v>-1.484</v>
       </c>
       <c r="E230" t="n">
-        <v>27.1</v>
+        <v>20.6</v>
       </c>
       <c r="F230" t="n">
         <v>0.167</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.278</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="231">
@@ -7121,7 +7121,7 @@
         <v>0.167</v>
       </c>
       <c r="G231" t="n">
-        <v>-1.694</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="232">
@@ -7150,7 +7150,7 @@
         <v>0.167</v>
       </c>
       <c r="G232" t="n">
-        <v>-2.433</v>
+        <v>-1.574</v>
       </c>
     </row>
     <row r="233">
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-3.996</v>
+        <v>-3.997</v>
       </c>
       <c r="E233" t="n">
         <v>31.5</v>
@@ -7179,7 +7179,7 @@
         <v>0.167</v>
       </c>
       <c r="G233" t="n">
-        <v>-3.787</v>
+        <v>-2.511</v>
       </c>
     </row>
     <row r="234">
@@ -7208,7 +7208,7 @@
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>2.489</v>
+        <v>1.704</v>
       </c>
     </row>
     <row r="235">
@@ -7237,7 +7237,7 @@
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>0.219</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="236">
@@ -7253,20 +7253,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-1.834</v>
+        <v>-0.456</v>
       </c>
       <c r="E236" t="n">
-        <v>21.1</v>
+        <v>27.1</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.267</v>
+        <v>-0.239</v>
       </c>
     </row>
     <row r="237">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-0.455</v>
+        <v>-1.491</v>
       </c>
       <c r="E237" t="n">
-        <v>27.1</v>
+        <v>24.3</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.366</v>
+        <v>-0.737</v>
       </c>
     </row>
     <row r="238">
@@ -7311,20 +7311,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-1.491</v>
+        <v>-1.835</v>
       </c>
       <c r="E238" t="n">
-        <v>24.3</v>
+        <v>21.1</v>
       </c>
       <c r="F238" t="n">
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-0.788</v>
+        <v>-0.792</v>
       </c>
     </row>
     <row r="239">
@@ -7340,20 +7340,20 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Tre Johnson</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-3.187</v>
+        <v>-1.836</v>
       </c>
       <c r="E239" t="n">
-        <v>22.3</v>
+        <v>27.2</v>
       </c>
       <c r="F239" t="n">
         <v>0.033</v>
       </c>
       <c r="G239" t="n">
-        <v>-0.826</v>
+        <v>-1.021</v>
       </c>
     </row>
     <row r="240">
@@ -7369,20 +7369,20 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Bub Carrington</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-1.836</v>
+        <v>-3.188</v>
       </c>
       <c r="E240" t="n">
-        <v>27.2</v>
+        <v>22.3</v>
       </c>
       <c r="F240" t="n">
         <v>0.033</v>
       </c>
       <c r="G240" t="n">
-        <v>-1.57</v>
+        <v>-1.464</v>
       </c>
     </row>
     <row r="241">
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>-2.464</v>
+        <v>-2.465</v>
       </c>
       <c r="E241" t="n">
         <v>31.3</v>
@@ -7411,7 +7411,7 @@
         <v>0.033</v>
       </c>
       <c r="G241" t="n">
-        <v>-2.401</v>
+        <v>-1.585</v>
       </c>
     </row>
   </sheetData>
@@ -7471,26 +7471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>32.176</v>
+        <v>23.4</v>
       </c>
       <c r="F2" t="n">
-        <v>3.078</v>
+        <v>3.322</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
     </row>
@@ -7500,26 +7500,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>29.715</v>
+        <v>23.188</v>
       </c>
       <c r="F3" t="n">
-        <v>3.354</v>
+        <v>3.078</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
     </row>
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>28.78</v>
+        <v>22.278</v>
       </c>
       <c r="F4" t="n">
-        <v>3.231</v>
+        <v>3.513</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7558,26 +7558,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>26.07</v>
+        <v>18.898</v>
       </c>
       <c r="F5" t="n">
-        <v>2.521</v>
+        <v>2.813</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
     </row>
@@ -7587,26 +7587,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>24.927</v>
+        <v>18.731</v>
       </c>
       <c r="F6" t="n">
-        <v>2.648</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
     </row>
@@ -7616,26 +7616,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>24.886</v>
+        <v>18.289</v>
       </c>
       <c r="F7" t="n">
-        <v>2.813</v>
+        <v>2.78</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -7645,26 +7645,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>24.463</v>
+        <v>17.014</v>
       </c>
       <c r="F8" t="n">
-        <v>2.316</v>
+        <v>2.648</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>21.707</v>
+        <v>16.138</v>
       </c>
       <c r="F9" t="n">
         <v>2.467</v>
@@ -7715,7 +7715,7 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>21.08</v>
+        <v>13.808</v>
       </c>
       <c r="F10" t="n">
         <v>2.02</v>
@@ -7732,26 +7732,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>20.81</v>
+        <v>13.046</v>
       </c>
       <c r="F11" t="n">
-        <v>0.82</v>
+        <v>1.728</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>19.396</v>
+        <v>12.657</v>
       </c>
       <c r="F12" t="n">
-        <v>1.641</v>
+        <v>0.904</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>18.223</v>
+        <v>11.868</v>
       </c>
       <c r="F13" t="n">
-        <v>1.729</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7831,10 +7831,10 @@
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>17.549</v>
+        <v>11.683</v>
       </c>
       <c r="F14" t="n">
-        <v>1.687</v>
+        <v>1.777</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -7860,10 +7860,10 @@
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>14.143</v>
+        <v>11.413</v>
       </c>
       <c r="F15" t="n">
-        <v>1.695</v>
+        <v>1.803</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -7889,10 +7889,10 @@
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>13.381</v>
+        <v>9.054</v>
       </c>
       <c r="F16" t="n">
-        <v>1.288</v>
+        <v>1.287</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -7918,10 +7918,10 @@
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>11.527</v>
+        <v>8.571999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.159</v>
+        <v>1.158</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -7947,10 +7947,10 @@
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>9.555999999999999</v>
+        <v>6.235</v>
       </c>
       <c r="F18" t="n">
-        <v>0.457</v>
+        <v>0.444</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>9.364000000000001</v>
+        <v>5.158</v>
       </c>
       <c r="F19" t="n">
-        <v>0.286</v>
+        <v>0.802</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>7.809</v>
+        <v>5.04</v>
       </c>
       <c r="F20" t="n">
-        <v>0.129</v>
+        <v>0.286</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
     </row>
@@ -8034,10 +8034,10 @@
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>7.583</v>
+        <v>4.363</v>
       </c>
       <c r="F21" t="n">
-        <v>0.328</v>
+        <v>0.327</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>7.23</v>
+        <v>4.109</v>
       </c>
       <c r="F22" t="n">
         <v>0.415</v>
@@ -8080,26 +8080,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4.127</v>
+        <v>3.338</v>
       </c>
       <c r="F23" t="n">
-        <v>0.802</v>
+        <v>0.153</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
     </row>
@@ -8121,10 +8121,10 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>2.313</v>
+        <v>0.139</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.228</v>
+        <v>-0.229</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -8150,10 +8150,10 @@
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>2.006</v>
+        <v>-1.544</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.961</v>
+        <v>-1.009</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -8167,26 +8167,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>0.713</v>
+        <v>-1.983</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.031</v>
+        <v>-0.737</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
     </row>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.598</v>
+        <v>-2.609</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.736</v>
+        <v>-1.074</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.51</v>
+        <v>-3.454</v>
       </c>
       <c r="F28" t="n">
         <v>-0.834</v>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.616</v>
+        <v>-5.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.343</v>
+        <v>-1.258</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>John Konchar</t>
         </is>
       </c>
     </row>
@@ -8283,26 +8283,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.722</v>
+        <v>-6.092</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.257</v>
+        <v>-1.387</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
     </row>
@@ -8312,26 +8312,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-8.164</v>
+        <v>-8.323</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.386</v>
+        <v>-2.344</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
     </row>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.407</v>
+        <v>8.34</v>
       </c>
       <c r="E2" t="n">
         <v>34.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G2" t="n">
-        <v>6.337</v>
+        <v>6.321</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.577</v>
+        <v>3.53</v>
       </c>
       <c r="E3" t="n">
-        <v>32.7</v>
+        <v>33.4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G3" t="n">
-        <v>2.777</v>
+        <v>2.825</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.484</v>
+        <v>2.554</v>
       </c>
       <c r="E4" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G4" t="n">
-        <v>1.968</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.439</v>
+        <v>2.548</v>
       </c>
       <c r="E5" t="n">
-        <v>28.2</v>
+        <v>29.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G5" t="n">
-        <v>1.728</v>
+        <v>1.869</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.264</v>
+        <v>2.206</v>
       </c>
       <c r="E6" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G6" t="n">
-        <v>1.666</v>
+        <v>1.667</v>
       </c>
     </row>
     <row r="7">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.719</v>
+        <v>0.899</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>19.2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G7" t="n">
-        <v>0.458</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.787</v>
+        <v>-1.626</v>
       </c>
       <c r="E8" t="n">
-        <v>19.7</v>
+        <v>19.1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.528</v>
+        <v>-0.435</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.946</v>
+        <v>-2.136</v>
       </c>
       <c r="E9" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.598</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="10">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.501</v>
+        <v>6.382</v>
       </c>
       <c r="E10" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="F10" t="n">
         <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.297</v>
+        <v>5.253</v>
       </c>
     </row>
     <row r="11">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.036</v>
+        <v>5.409</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>34.7</v>
       </c>
       <c r="F11" t="n">
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>4.331</v>
+        <v>4.567</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.042</v>
+        <v>4.897</v>
       </c>
       <c r="E12" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="F12" t="n">
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2</v>
+        <v>4.121</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.053</v>
+        <v>3.983</v>
       </c>
       <c r="E13" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
         <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.319</v>
+        <v>3.256</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.101</v>
+        <v>2.132</v>
       </c>
       <c r="E14" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
         <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.621</v>
+        <v>1.639</v>
       </c>
     </row>
     <row r="15">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.79</v>
+        <v>-0.886</v>
       </c>
       <c r="E16" t="n">
-        <v>26.2</v>
+        <v>25.7</v>
       </c>
       <c r="F16" t="n">
         <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.45</v>
+        <v>-1.543</v>
       </c>
       <c r="E17" t="n">
-        <v>27.1</v>
+        <v>26.7</v>
       </c>
       <c r="F17" t="n">
         <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.31</v>
+        <v>-0.357</v>
       </c>
     </row>
     <row r="18">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.994</v>
+        <v>-1.995</v>
       </c>
       <c r="E21" t="n">
         <v>23.9</v>
@@ -1047,20 +1047,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-4.698</v>
+        <v>-2.338</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>21.4</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.546</v>
+        <v>-1.015</v>
       </c>
     </row>
     <row r="23">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7.158</v>
+        <v>7.161</v>
       </c>
       <c r="E26" t="n">
         <v>28.5</v>
@@ -1176,7 +1176,7 @@
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>4.671</v>
+        <v>4.673</v>
       </c>
     </row>
     <row r="27">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.532</v>
+        <v>4.534</v>
       </c>
       <c r="E27" t="n">
         <v>30.1</v>
@@ -1205,7 +1205,7 @@
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>3.285</v>
+        <v>3.287</v>
       </c>
     </row>
     <row r="28">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.666</v>
+        <v>2.668</v>
       </c>
       <c r="E28" t="n">
         <v>30.7</v>
@@ -1234,7 +1234,7 @@
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>2.152</v>
+        <v>2.154</v>
       </c>
     </row>
     <row r="29">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.206</v>
+        <v>1.208</v>
       </c>
       <c r="E29" t="n">
         <v>29.7</v>
@@ -1263,7 +1263,7 @@
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.178</v>
+        <v>1.179</v>
       </c>
     </row>
     <row r="30">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.185</v>
+        <v>1.187</v>
       </c>
       <c r="E30" t="n">
         <v>28.1</v>
@@ -1292,7 +1292,7 @@
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1.102</v>
+        <v>1.103</v>
       </c>
     </row>
     <row r="31">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="E31" t="n">
         <v>19.9</v>
@@ -1321,7 +1321,7 @@
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0.633</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="32">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.832</v>
+        <v>-0.83</v>
       </c>
       <c r="E32" t="n">
         <v>19.2</v>
@@ -1350,7 +1350,7 @@
         <v>0.7</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.053</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="33">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-3.62</v>
+        <v>-3.592</v>
       </c>
       <c r="E33" t="n">
         <v>18.1</v>
@@ -1379,7 +1379,7 @@
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.1</v>
+        <v>-1.089</v>
       </c>
     </row>
     <row r="34">
@@ -1405,10 +1405,10 @@
         <v>34.1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G34" t="n">
-        <v>4.353</v>
+        <v>4.329</v>
       </c>
     </row>
     <row r="35">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.962</v>
+        <v>4.069</v>
       </c>
       <c r="E35" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="F35" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G35" t="n">
-        <v>2.575</v>
+        <v>2.611</v>
       </c>
     </row>
     <row r="36">
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.263</v>
+        <v>2.317</v>
       </c>
       <c r="E36" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G36" t="n">
-        <v>1.265</v>
+        <v>1.321</v>
       </c>
     </row>
     <row r="37">
@@ -1486,16 +1486,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.427</v>
+        <v>1.396</v>
       </c>
       <c r="E37" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="F37" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G37" t="n">
-        <v>1.222</v>
+        <v>1.166</v>
       </c>
     </row>
     <row r="38">
@@ -1515,16 +1515,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-1.237</v>
+        <v>-0.335</v>
       </c>
       <c r="E38" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="F38" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.453</v>
+        <v>-0.018</v>
       </c>
     </row>
     <row r="39">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-2.006</v>
+        <v>-2.058</v>
       </c>
       <c r="E39" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.843</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="40">
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-4.133</v>
+        <v>-4.305</v>
       </c>
       <c r="E40" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="F40" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.765</v>
+        <v>-1.879</v>
       </c>
     </row>
     <row r="41">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-3.451</v>
+        <v>-3.527</v>
       </c>
       <c r="E41" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="F41" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.991</v>
+        <v>-2.041</v>
       </c>
     </row>
     <row r="42">
@@ -1640,7 +1640,7 @@
         <v>0.8</v>
       </c>
       <c r="G42" t="n">
-        <v>6.838</v>
+        <v>6.837</v>
       </c>
     </row>
     <row r="43">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Craig Porter Jr.</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.923</v>
+        <v>1.134</v>
       </c>
       <c r="E47" t="n">
-        <v>17.7</v>
+        <v>28.9</v>
       </c>
       <c r="F47" t="n">
         <v>0.8</v>
       </c>
       <c r="G47" t="n">
-        <v>1.001</v>
+        <v>1.164</v>
       </c>
     </row>
     <row r="48">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.62</v>
+        <v>1.619</v>
       </c>
       <c r="E51" t="n">
         <v>23.9</v>
@@ -1946,20 +1946,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dwight Powell</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-2.1</v>
+        <v>0.624</v>
       </c>
       <c r="E53" t="n">
-        <v>16.5</v>
+        <v>29.9</v>
       </c>
       <c r="F53" t="n">
         <v>0.233</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.64</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="54">
@@ -1975,20 +1975,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ryan Nembhard</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-2.071</v>
+        <v>-1.431</v>
       </c>
       <c r="E54" t="n">
-        <v>17.6</v>
+        <v>21</v>
       </c>
       <c r="F54" t="n">
         <v>0.233</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.672</v>
+        <v>-0.523</v>
       </c>
     </row>
     <row r="55">
@@ -2033,20 +2033,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>P.J. Washington</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-2.984</v>
+        <v>-1.593</v>
       </c>
       <c r="E56" t="n">
-        <v>21.6</v>
+        <v>32.1</v>
       </c>
       <c r="F56" t="n">
         <v>0.233</v>
       </c>
       <c r="G56" t="n">
-        <v>-1.238</v>
+        <v>-0.911</v>
       </c>
     </row>
     <row r="57">
@@ -2062,20 +2062,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-4.444</v>
+        <v>-2.984</v>
       </c>
       <c r="E57" t="n">
-        <v>17.6</v>
+        <v>21.6</v>
       </c>
       <c r="F57" t="n">
         <v>0.233</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.544</v>
+        <v>-1.238</v>
       </c>
     </row>
     <row r="58">
@@ -2095,16 +2095,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>18.207</v>
+        <v>18.173</v>
       </c>
       <c r="E58" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="F58" t="n">
         <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>14.349</v>
+        <v>14.298</v>
       </c>
     </row>
     <row r="59">
@@ -2124,16 +2124,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>9.093999999999999</v>
+        <v>9.113</v>
       </c>
       <c r="E59" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="F59" t="n">
         <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>7.339</v>
+        <v>7.293</v>
       </c>
     </row>
     <row r="60">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.868</v>
+        <v>2.737</v>
       </c>
       <c r="E60" t="n">
         <v>27.6</v>
@@ -2162,7 +2162,7 @@
         <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>2.129</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="61">
@@ -2182,16 +2182,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.334</v>
+        <v>0.486</v>
       </c>
       <c r="E61" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="F61" t="n">
         <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>0.631</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="62">
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.079</v>
+        <v>0.049</v>
       </c>
       <c r="E62" t="n">
-        <v>32.7</v>
+        <v>31.6</v>
       </c>
       <c r="F62" t="n">
         <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>0.622</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="63">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-1.142</v>
+        <v>-1.037</v>
       </c>
       <c r="E63" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="F63" t="n">
         <v>0.833</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.191</v>
+        <v>-0.121</v>
       </c>
     </row>
     <row r="64">
@@ -2269,16 +2269,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1.987</v>
+        <v>-2.044</v>
       </c>
       <c r="E64" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>0.833</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.778</v>
+        <v>-0.8070000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2298,16 +2298,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-2.833</v>
+        <v>-2.786</v>
       </c>
       <c r="E65" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F65" t="n">
         <v>0.833</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.913</v>
+        <v>-0.883</v>
       </c>
     </row>
     <row r="66">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.194</v>
+        <v>-0.195</v>
       </c>
       <c r="E70" t="n">
         <v>25.8</v>
@@ -2771,7 +2771,7 @@
         <v>0.433</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.356</v>
+        <v>-0.357</v>
       </c>
     </row>
     <row r="82">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6.458</v>
+        <v>6.629</v>
       </c>
       <c r="E82" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="F82" t="n">
         <v>0.767</v>
       </c>
       <c r="G82" t="n">
-        <v>5.4</v>
+        <v>5.503</v>
       </c>
     </row>
     <row r="83">
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6.108</v>
+        <v>6.199</v>
       </c>
       <c r="E83" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="F83" t="n">
         <v>0.767</v>
       </c>
       <c r="G83" t="n">
-        <v>4.722</v>
+        <v>4.775</v>
       </c>
     </row>
     <row r="84">
@@ -2849,16 +2849,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3.696</v>
+        <v>3.762</v>
       </c>
       <c r="E84" t="n">
-        <v>38.1</v>
+        <v>38.7</v>
       </c>
       <c r="F84" t="n">
         <v>0.767</v>
       </c>
       <c r="G84" t="n">
-        <v>3.546</v>
+        <v>3.648</v>
       </c>
     </row>
     <row r="85">
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.078</v>
+        <v>3.236</v>
       </c>
       <c r="E85" t="n">
-        <v>31.1</v>
+        <v>30.1</v>
       </c>
       <c r="F85" t="n">
         <v>0.767</v>
       </c>
       <c r="G85" t="n">
-        <v>2.489</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="86">
@@ -2907,16 +2907,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-0.464</v>
+        <v>-0.434</v>
       </c>
       <c r="E86" t="n">
-        <v>36.1</v>
+        <v>36.6</v>
       </c>
       <c r="F86" t="n">
         <v>0.767</v>
       </c>
       <c r="G86" t="n">
-        <v>0.228</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="87">
@@ -2936,16 +2936,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-1.972</v>
+        <v>-1.649</v>
       </c>
       <c r="E87" t="n">
-        <v>24.7</v>
+        <v>25.1</v>
       </c>
       <c r="F87" t="n">
         <v>0.767</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.621</v>
+        <v>-0.462</v>
       </c>
     </row>
     <row r="88">
@@ -3003,7 +3003,7 @@
         <v>0.767</v>
       </c>
       <c r="G89" t="n">
-        <v>-2.38</v>
+        <v>-2.381</v>
       </c>
     </row>
     <row r="90">
@@ -3023,16 +3023,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.942</v>
+        <v>3.028</v>
       </c>
       <c r="E90" t="n">
-        <v>31.9</v>
+        <v>31.6</v>
       </c>
       <c r="F90" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="G90" t="n">
-        <v>2.04</v>
+        <v>2.102</v>
       </c>
     </row>
     <row r="91">
@@ -3048,20 +3048,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1.962</v>
+        <v>2.828</v>
       </c>
       <c r="E91" t="n">
-        <v>23.8</v>
+        <v>28.7</v>
       </c>
       <c r="F91" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="G91" t="n">
-        <v>1.04</v>
+        <v>1.791</v>
       </c>
     </row>
     <row r="92">
@@ -3077,20 +3077,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.694</v>
+        <v>1.933</v>
       </c>
       <c r="E92" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="F92" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>0.666</v>
+        <v>1.008</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Obi Toppin</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.607</v>
+        <v>-0.697</v>
       </c>
       <c r="E93" t="n">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="F93" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>0.637</v>
+        <v>-0.208</v>
       </c>
     </row>
     <row r="94">
@@ -3135,20 +3135,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-0.616</v>
+        <v>-2.147</v>
       </c>
       <c r="E94" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F94" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.191</v>
+        <v>-0.909</v>
       </c>
     </row>
     <row r="95">
@@ -3164,20 +3164,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.67</v>
+        <v>-2.946</v>
       </c>
       <c r="E95" t="n">
-        <v>21.9</v>
+        <v>20.2</v>
       </c>
       <c r="F95" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.157</v>
+        <v>-1.168</v>
       </c>
     </row>
     <row r="96">
@@ -3193,20 +3193,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.945</v>
+        <v>-3.042</v>
       </c>
       <c r="E96" t="n">
-        <v>20.5</v>
+        <v>27.3</v>
       </c>
       <c r="F96" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.202</v>
+        <v>-1.636</v>
       </c>
     </row>
     <row r="97">
@@ -3226,16 +3226,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-3.806</v>
+        <v>-3.96</v>
       </c>
       <c r="E97" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="F97" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="G97" t="n">
-        <v>-1.694</v>
+        <v>-1.721</v>
       </c>
     </row>
     <row r="98">
@@ -3293,7 +3293,7 @@
         <v>0.633</v>
       </c>
       <c r="G99" t="n">
-        <v>2.62</v>
+        <v>2.619</v>
       </c>
     </row>
     <row r="100">
@@ -3409,7 +3409,7 @@
         <v>0.633</v>
       </c>
       <c r="G103" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="104">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>15.372</v>
+        <v>15.371</v>
       </c>
       <c r="E106" t="n">
         <v>37.3</v>
@@ -3554,7 +3554,7 @@
         <v>0.667</v>
       </c>
       <c r="G108" t="n">
-        <v>4.742</v>
+        <v>4.741</v>
       </c>
     </row>
     <row r="109">
@@ -3715,20 +3715,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Javon Small</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5.091</v>
+        <v>2.932</v>
       </c>
       <c r="E114" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="F114" t="n">
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>2.683</v>
+        <v>1.671</v>
       </c>
     </row>
     <row r="115">
@@ -3744,20 +3744,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2.755</v>
+        <v>1.014</v>
       </c>
       <c r="E115" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="F115" t="n">
         <v>0.267</v>
       </c>
       <c r="G115" t="n">
-        <v>1.618</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="116">
@@ -3773,20 +3773,20 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.97</v>
+        <v>0.324</v>
       </c>
       <c r="E116" t="n">
-        <v>25.7</v>
+        <v>23.9</v>
       </c>
       <c r="F116" t="n">
         <v>0.267</v>
       </c>
       <c r="G116" t="n">
-        <v>0.663</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="117">
@@ -3806,16 +3806,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-0.57</v>
+        <v>-0.47</v>
       </c>
       <c r="E117" t="n">
-        <v>26.1</v>
+        <v>25.5</v>
       </c>
       <c r="F117" t="n">
         <v>0.267</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.165</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="118">
@@ -3864,16 +3864,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-2.351</v>
+        <v>-2.195</v>
       </c>
       <c r="E119" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="F119" t="n">
         <v>0.267</v>
       </c>
       <c r="G119" t="n">
-        <v>-1.097</v>
+        <v>-1.035</v>
       </c>
     </row>
     <row r="120">
@@ -3893,16 +3893,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-4.435</v>
+        <v>-4.574</v>
       </c>
       <c r="E120" t="n">
-        <v>25.4</v>
+        <v>26.4</v>
       </c>
       <c r="F120" t="n">
         <v>0.267</v>
       </c>
       <c r="G120" t="n">
-        <v>-2.204</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="121">
@@ -3951,16 +3951,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2.866</v>
+        <v>2.974</v>
       </c>
       <c r="E122" t="n">
-        <v>35.2</v>
+        <v>35.5</v>
       </c>
       <c r="F122" t="n">
         <v>0.6</v>
       </c>
       <c r="G122" t="n">
-        <v>2.539</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="123">
@@ -3980,16 +3980,16 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.344</v>
+        <v>2.276</v>
       </c>
       <c r="E123" t="n">
-        <v>31.7</v>
+        <v>32.7</v>
       </c>
       <c r="F123" t="n">
         <v>0.6</v>
       </c>
       <c r="G123" t="n">
-        <v>1.942</v>
+        <v>1.961</v>
       </c>
     </row>
     <row r="124">
@@ -4009,16 +4009,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2.354</v>
+        <v>2.293</v>
       </c>
       <c r="E124" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="F124" t="n">
         <v>0.6</v>
       </c>
       <c r="G124" t="n">
-        <v>1.414</v>
+        <v>1.389</v>
       </c>
     </row>
     <row r="125">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1.687</v>
+        <v>1.669</v>
       </c>
       <c r="E125" t="n">
-        <v>28.3</v>
+        <v>29</v>
       </c>
       <c r="F125" t="n">
         <v>0.6</v>
       </c>
       <c r="G125" t="n">
-        <v>1.346</v>
+        <v>1.371</v>
       </c>
     </row>
     <row r="126">
@@ -4067,16 +4067,16 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.997</v>
+        <v>1.013</v>
       </c>
       <c r="E126" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="F126" t="n">
         <v>0.6</v>
       </c>
       <c r="G126" t="n">
-        <v>0.873</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="127">
@@ -4096,16 +4096,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.41</v>
+        <v>0.302</v>
       </c>
       <c r="E127" t="n">
-        <v>27.4</v>
+        <v>27.7</v>
       </c>
       <c r="F127" t="n">
         <v>0.6</v>
       </c>
       <c r="G127" t="n">
-        <v>0.576</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="128">
@@ -4154,16 +4154,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.775</v>
+        <v>-0.653</v>
       </c>
       <c r="E129" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="F129" t="n">
         <v>0.6</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.11</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="130">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-0.404</v>
+        <v>-0.405</v>
       </c>
       <c r="E132" t="n">
         <v>24.9</v>
@@ -4270,16 +4270,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-1.43</v>
+        <v>-0.967</v>
       </c>
       <c r="E133" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="F133" t="n">
         <v>0.2</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.513</v>
+        <v>-0.334</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.572</v>
+        <v>-2.552</v>
       </c>
       <c r="E134" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F134" t="n">
         <v>0.2</v>
       </c>
       <c r="G134" t="n">
-        <v>-1.11</v>
+        <v>-1.112</v>
       </c>
     </row>
     <row r="135">
@@ -4324,20 +4324,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-2.632</v>
+        <v>-2.657</v>
       </c>
       <c r="E135" t="n">
-        <v>22.1</v>
+        <v>22.8</v>
       </c>
       <c r="F135" t="n">
         <v>0.2</v>
       </c>
       <c r="G135" t="n">
-        <v>-1.119</v>
+        <v>-1.168</v>
       </c>
     </row>
     <row r="136">
@@ -4357,16 +4357,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-2.513</v>
+        <v>-2.348</v>
       </c>
       <c r="E136" t="n">
-        <v>26.8</v>
+        <v>27.9</v>
       </c>
       <c r="F136" t="n">
         <v>0.2</v>
       </c>
       <c r="G136" t="n">
-        <v>-1.293</v>
+        <v>-1.251</v>
       </c>
     </row>
     <row r="137">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.668</v>
+        <v>2.667</v>
       </c>
       <c r="E140" t="n">
         <v>27.6</v>
@@ -4540,7 +4540,7 @@
         <v>0.733</v>
       </c>
       <c r="G142" t="n">
-        <v>1.394</v>
+        <v>1.393</v>
       </c>
     </row>
     <row r="143">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-0.211</v>
+        <v>-0.212</v>
       </c>
       <c r="E145" t="n">
         <v>18.5</v>
@@ -4653,10 +4653,10 @@
         <v>29.8</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G146" t="n">
-        <v>3.192</v>
+        <v>3.213</v>
       </c>
     </row>
     <row r="147">
@@ -4682,10 +4682,10 @@
         <v>32.7</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G147" t="n">
-        <v>1.734</v>
+        <v>1.756</v>
       </c>
     </row>
     <row r="148">
@@ -4711,10 +4711,10 @@
         <v>30.7</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G148" t="n">
-        <v>1.68</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="149">
@@ -4740,10 +4740,10 @@
         <v>19.3</v>
       </c>
       <c r="F149" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G149" t="n">
-        <v>0.55</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -4763,16 +4763,16 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-0.202</v>
+        <v>-0.203</v>
       </c>
       <c r="E150" t="n">
         <v>18.6</v>
       </c>
       <c r="F150" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G150" t="n">
-        <v>0.038</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="151">
@@ -4798,10 +4798,10 @@
         <v>22.4</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.533</v>
+        <v>-0.518</v>
       </c>
     </row>
     <row r="152">
@@ -4827,10 +4827,10 @@
         <v>19.9</v>
       </c>
       <c r="F152" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.982</v>
+        <v>-0.968</v>
       </c>
     </row>
     <row r="153">
@@ -4856,10 +4856,10 @@
         <v>29.5</v>
       </c>
       <c r="F153" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.57</v>
+        <v>-1.549</v>
       </c>
     </row>
     <row r="154">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4.173</v>
+        <v>4.172</v>
       </c>
       <c r="E155" t="n">
-        <v>29.5</v>
+        <v>29.9</v>
       </c>
       <c r="F155" t="n">
         <v>0.867</v>
       </c>
       <c r="G155" t="n">
-        <v>3.097</v>
+        <v>3.134</v>
       </c>
     </row>
     <row r="156">
@@ -4933,20 +4933,20 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3.266</v>
+        <v>2.984</v>
       </c>
       <c r="E156" t="n">
-        <v>29.9</v>
+        <v>30.9</v>
       </c>
       <c r="F156" t="n">
         <v>0.867</v>
       </c>
       <c r="G156" t="n">
-        <v>2.572</v>
+        <v>2.483</v>
       </c>
     </row>
     <row r="157">
@@ -4962,20 +4962,20 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3.003</v>
+        <v>3.102</v>
       </c>
       <c r="E157" t="n">
-        <v>30.9</v>
+        <v>29.6</v>
       </c>
       <c r="F157" t="n">
         <v>0.867</v>
       </c>
       <c r="G157" t="n">
-        <v>2.492</v>
+        <v>2.447</v>
       </c>
     </row>
     <row r="158">
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1.684</v>
+        <v>1.607</v>
       </c>
       <c r="E158" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
       <c r="F158" t="n">
         <v>0.867</v>
       </c>
       <c r="G158" t="n">
-        <v>1.792</v>
+        <v>1.749</v>
       </c>
     </row>
     <row r="159">
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3.052</v>
+        <v>3.051</v>
       </c>
       <c r="E159" t="n">
         <v>19.7</v>
@@ -5078,20 +5078,20 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jose Alvarado</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-0.108</v>
+        <v>-1.333</v>
       </c>
       <c r="E161" t="n">
-        <v>15.5</v>
+        <v>24.8</v>
       </c>
       <c r="F161" t="n">
         <v>0.867</v>
       </c>
       <c r="G161" t="n">
-        <v>0.245</v>
+        <v>-0.241</v>
       </c>
     </row>
     <row r="162">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.26</v>
+        <v>1.259</v>
       </c>
       <c r="E167" t="n">
         <v>22.2</v>
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-4.532</v>
+        <v>-4.533</v>
       </c>
       <c r="E169" t="n">
         <v>26.1</v>
@@ -5343,16 +5343,16 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3.39</v>
+        <v>3.318</v>
       </c>
       <c r="E170" t="n">
-        <v>35.1</v>
+        <v>35.4</v>
       </c>
       <c r="F170" t="n">
         <v>0.4</v>
       </c>
       <c r="G170" t="n">
-        <v>2.77</v>
+        <v>2.744</v>
       </c>
     </row>
     <row r="171">
@@ -5372,16 +5372,16 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3.264</v>
+        <v>3.181</v>
       </c>
       <c r="E171" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="F171" t="n">
         <v>0.4</v>
       </c>
       <c r="G171" t="n">
-        <v>2.586</v>
+        <v>2.549</v>
       </c>
     </row>
     <row r="172">
@@ -5401,16 +5401,16 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3.122</v>
+        <v>3.163</v>
       </c>
       <c r="E172" t="n">
-        <v>28.5</v>
+        <v>30.2</v>
       </c>
       <c r="F172" t="n">
         <v>0.4</v>
       </c>
       <c r="G172" t="n">
-        <v>2.094</v>
+        <v>2.239</v>
       </c>
     </row>
     <row r="173">
@@ -5426,20 +5426,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-0.603</v>
+        <v>1.996</v>
       </c>
       <c r="E173" t="n">
-        <v>29.2</v>
+        <v>28.8</v>
       </c>
       <c r="F173" t="n">
         <v>0.4</v>
       </c>
       <c r="G173" t="n">
-        <v>-0.124</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="174">
@@ -5455,20 +5455,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-1.054</v>
+        <v>-0.665</v>
       </c>
       <c r="E174" t="n">
-        <v>21.1</v>
+        <v>29.3</v>
       </c>
       <c r="F174" t="n">
         <v>0.4</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.288</v>
+        <v>-0.162</v>
       </c>
     </row>
     <row r="175">
@@ -5488,16 +5488,16 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-1.008</v>
+        <v>-1.196</v>
       </c>
       <c r="E175" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="F175" t="n">
         <v>0.4</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.378</v>
+        <v>-0.491</v>
       </c>
     </row>
     <row r="176">
@@ -5513,20 +5513,20 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Jett Howard</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-2.549</v>
+        <v>-1.593</v>
       </c>
       <c r="E176" t="n">
-        <v>16.8</v>
+        <v>20.6</v>
       </c>
       <c r="F176" t="n">
         <v>0.4</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.754</v>
+        <v>-0.512</v>
       </c>
     </row>
     <row r="177">
@@ -5575,16 +5575,16 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>9.289999999999999</v>
+        <v>9.182</v>
       </c>
       <c r="E178" t="n">
-        <v>36.3</v>
+        <v>37</v>
       </c>
       <c r="F178" t="n">
         <v>0.467</v>
       </c>
       <c r="G178" t="n">
-        <v>7.38</v>
+        <v>7.435</v>
       </c>
     </row>
     <row r="179">
@@ -5633,16 +5633,16 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2.011</v>
+        <v>1.835</v>
       </c>
       <c r="E180" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="F180" t="n">
         <v>0.467</v>
       </c>
       <c r="G180" t="n">
-        <v>1.703</v>
+        <v>1.568</v>
       </c>
     </row>
     <row r="181">
@@ -5662,16 +5662,16 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.724</v>
+        <v>0.763</v>
       </c>
       <c r="E181" t="n">
-        <v>33.3</v>
+        <v>32.9</v>
       </c>
       <c r="F181" t="n">
         <v>0.467</v>
       </c>
       <c r="G181" t="n">
-        <v>0.827</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="182">
@@ -5691,16 +5691,16 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-0.187</v>
+        <v>-0.181</v>
       </c>
       <c r="E182" t="n">
-        <v>31.5</v>
+        <v>32.2</v>
       </c>
       <c r="F182" t="n">
         <v>0.467</v>
       </c>
       <c r="G182" t="n">
-        <v>0.184</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="183">
@@ -5749,16 +5749,16 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>-1.326</v>
+        <v>-1.338</v>
       </c>
       <c r="E184" t="n">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="F184" t="n">
         <v>0.467</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.419</v>
+        <v>-0.415</v>
       </c>
     </row>
     <row r="185">
@@ -5778,16 +5778,16 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>-1.475</v>
+        <v>-1.566</v>
       </c>
       <c r="E185" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="F185" t="n">
         <v>0.467</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.744</v>
       </c>
     </row>
     <row r="186">
@@ -5813,10 +5813,10 @@
         <v>33.1</v>
       </c>
       <c r="F186" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G186" t="n">
-        <v>3.684</v>
+        <v>3.707</v>
       </c>
     </row>
     <row r="187">
@@ -5842,10 +5842,10 @@
         <v>29.7</v>
       </c>
       <c r="F187" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G187" t="n">
-        <v>2.967</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="188">
@@ -5871,10 +5871,10 @@
         <v>28.6</v>
       </c>
       <c r="F188" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G188" t="n">
-        <v>2.244</v>
+        <v>2.264</v>
       </c>
     </row>
     <row r="189">
@@ -5900,10 +5900,10 @@
         <v>24.4</v>
       </c>
       <c r="F189" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G189" t="n">
-        <v>0.77</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="190">
@@ -5929,10 +5929,10 @@
         <v>26.4</v>
       </c>
       <c r="F190" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G190" t="n">
-        <v>0.436</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="191">
@@ -5958,10 +5958,10 @@
         <v>29.4</v>
       </c>
       <c r="F191" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G191" t="n">
-        <v>0.123</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="192">
@@ -5987,10 +5987,10 @@
         <v>30.7</v>
       </c>
       <c r="F192" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.328</v>
+        <v>-0.307</v>
       </c>
     </row>
     <row r="193">
@@ -6016,10 +6016,10 @@
         <v>30.3</v>
       </c>
       <c r="F193" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G193" t="n">
-        <v>-0.842</v>
+        <v>-0.821</v>
       </c>
     </row>
     <row r="194">
@@ -6271,16 +6271,16 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>2.855</v>
+        <v>2.779</v>
       </c>
       <c r="E202" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>1.805</v>
+        <v>1.763</v>
       </c>
     </row>
     <row r="203">
@@ -6296,20 +6296,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.284</v>
+        <v>0.331</v>
       </c>
       <c r="E203" t="n">
-        <v>31.6</v>
+        <v>23.1</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.253</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="204">
@@ -6325,20 +6325,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.376</v>
+        <v>0.104</v>
       </c>
       <c r="E204" t="n">
-        <v>22.8</v>
+        <v>31.9</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.226</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="205">
@@ -6354,20 +6354,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-1.191</v>
+        <v>-1.585</v>
       </c>
       <c r="E205" t="n">
-        <v>33</v>
+        <v>22.6</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.75</v>
+        <v>-0.699</v>
       </c>
     </row>
     <row r="206">
@@ -6383,20 +6383,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-2.245</v>
+        <v>-1.262</v>
       </c>
       <c r="E206" t="n">
-        <v>22.1</v>
+        <v>33</v>
       </c>
       <c r="F206" t="n">
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.988</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="207">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-2.951</v>
+        <v>-3.462</v>
       </c>
       <c r="E207" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="F207" t="n">
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-1.706</v>
+        <v>-2.018</v>
       </c>
     </row>
     <row r="208">
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-4.227</v>
+        <v>-4.271</v>
       </c>
       <c r="E209" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="F209" t="n">
         <v>0.1</v>
       </c>
       <c r="G209" t="n">
-        <v>-2.791</v>
+        <v>-2.864</v>
       </c>
     </row>
     <row r="210">
@@ -6599,7 +6599,7 @@
         <v>0.967</v>
       </c>
       <c r="G213" t="n">
-        <v>1.239</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="214">
@@ -6657,7 +6657,7 @@
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.262</v>
+        <v>0.261</v>
       </c>
       <c r="E216" t="n">
         <v>26.7</v>
@@ -6735,16 +6735,16 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>6.29</v>
+        <v>6.277</v>
       </c>
       <c r="E218" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="F218" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G218" t="n">
-        <v>4.65</v>
+        <v>4.579</v>
       </c>
     </row>
     <row r="219">
@@ -6764,16 +6764,16 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2.055</v>
+        <v>2.054</v>
       </c>
       <c r="E219" t="n">
         <v>34.2</v>
       </c>
       <c r="F219" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G219" t="n">
-        <v>1.868</v>
+        <v>1.821</v>
       </c>
     </row>
     <row r="220">
@@ -6793,16 +6793,16 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>3.428</v>
+        <v>3.462</v>
       </c>
       <c r="E220" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="F220" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G220" t="n">
-        <v>1.661</v>
+        <v>1.683</v>
       </c>
     </row>
     <row r="221">
@@ -6822,16 +6822,16 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.607</v>
+        <v>1.72</v>
       </c>
       <c r="E221" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="F221" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G221" t="n">
-        <v>1.409</v>
+        <v>1.434</v>
       </c>
     </row>
     <row r="222">
@@ -6851,16 +6851,16 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1.739</v>
+        <v>1.729</v>
       </c>
       <c r="E222" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="F222" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G222" t="n">
-        <v>1.299</v>
+        <v>1.248</v>
       </c>
     </row>
     <row r="223">
@@ -6880,16 +6880,16 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.86</v>
+        <v>0.863</v>
       </c>
       <c r="E223" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="F223" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G223" t="n">
-        <v>0.719</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="224">
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.653</v>
+        <v>-0.614</v>
       </c>
       <c r="E224" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="F224" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.04</v>
+        <v>-0.054</v>
       </c>
     </row>
     <row r="225">
@@ -6938,16 +6938,16 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-0.903</v>
+        <v>-0.99</v>
       </c>
       <c r="E225" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="F225" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.153</v>
+        <v>-0.225</v>
       </c>
     </row>
     <row r="226">
@@ -6963,20 +6963,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1.029</v>
+        <v>1.16</v>
       </c>
       <c r="E226" t="n">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="F226" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="G226" t="n">
-        <v>0.641</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="227">
@@ -6992,20 +6992,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.837</v>
+        <v>0.947</v>
       </c>
       <c r="E227" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="F227" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="G227" t="n">
-        <v>0.546</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="228">
@@ -7025,16 +7025,16 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-0.49</v>
+        <v>-0.352</v>
       </c>
       <c r="E228" t="n">
-        <v>27.1</v>
+        <v>26.7</v>
       </c>
       <c r="F228" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.182</v>
+        <v>-0.122</v>
       </c>
     </row>
     <row r="229">
@@ -7060,10 +7060,10 @@
         <v>19</v>
       </c>
       <c r="F229" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.373</v>
+        <v>-0.386</v>
       </c>
     </row>
     <row r="230">
@@ -7089,10 +7089,10 @@
         <v>20.6</v>
       </c>
       <c r="F230" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.579</v>
       </c>
     </row>
     <row r="231">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-1.919</v>
+        <v>-1.835</v>
       </c>
       <c r="E231" t="n">
-        <v>29.6</v>
+        <v>30</v>
       </c>
       <c r="F231" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="G231" t="n">
-        <v>-1.082</v>
+        <v>-1.064</v>
       </c>
     </row>
     <row r="232">
@@ -7147,10 +7147,10 @@
         <v>27.3</v>
       </c>
       <c r="F232" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="G232" t="n">
-        <v>-1.574</v>
+        <v>-1.593</v>
       </c>
     </row>
     <row r="233">
@@ -7170,16 +7170,16 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-3.997</v>
+        <v>-3.91</v>
       </c>
       <c r="E233" t="n">
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
       <c r="F233" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="G233" t="n">
-        <v>-2.511</v>
+        <v>-2.558</v>
       </c>
     </row>
     <row r="234">
@@ -7195,20 +7195,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3.075</v>
+        <v>1.621</v>
       </c>
       <c r="E234" t="n">
-        <v>26.3</v>
+        <v>21.1</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>1.704</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="235">
@@ -7224,20 +7224,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1.523</v>
+        <v>-0.877</v>
       </c>
       <c r="E235" t="n">
-        <v>21</v>
+        <v>27.1</v>
       </c>
       <c r="F235" t="n">
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>0.68</v>
+        <v>-0.477</v>
       </c>
     </row>
     <row r="236">
@@ -7253,20 +7253,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.456</v>
+        <v>-1.494</v>
       </c>
       <c r="E236" t="n">
-        <v>27.1</v>
+        <v>24.6</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.239</v>
+        <v>-0.748</v>
       </c>
     </row>
     <row r="237">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-1.491</v>
+        <v>-1.928</v>
       </c>
       <c r="E237" t="n">
-        <v>24.3</v>
+        <v>21.4</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.737</v>
+        <v>-0.843</v>
       </c>
     </row>
     <row r="238">
@@ -7311,20 +7311,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-1.835</v>
+        <v>-1.929</v>
       </c>
       <c r="E238" t="n">
-        <v>21.1</v>
+        <v>27.2</v>
       </c>
       <c r="F238" t="n">
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-0.792</v>
+        <v>-1.073</v>
       </c>
     </row>
     <row r="239">
@@ -7340,20 +7340,20 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bub Carrington</t>
+          <t>Jaden Hardy</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-1.836</v>
+        <v>-3.232</v>
       </c>
       <c r="E239" t="n">
-        <v>27.2</v>
+        <v>20.6</v>
       </c>
       <c r="F239" t="n">
         <v>0.033</v>
       </c>
       <c r="G239" t="n">
-        <v>-1.021</v>
+        <v>-1.372</v>
       </c>
     </row>
     <row r="240">
@@ -7373,16 +7373,16 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-3.188</v>
+        <v>-3.189</v>
       </c>
       <c r="E240" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="F240" t="n">
         <v>0.033</v>
       </c>
       <c r="G240" t="n">
-        <v>-1.464</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="241">
@@ -7402,16 +7402,16 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>-2.465</v>
+        <v>-2.568</v>
       </c>
       <c r="E241" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="F241" t="n">
         <v>0.033</v>
       </c>
       <c r="G241" t="n">
-        <v>-1.585</v>
+        <v>-1.663</v>
       </c>
     </row>
   </sheetData>
@@ -7483,7 +7483,7 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>23.4</v>
+        <v>23.399</v>
       </c>
       <c r="F2" t="n">
         <v>3.322</v>
@@ -7512,10 +7512,10 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>23.188</v>
+        <v>23.11</v>
       </c>
       <c r="F3" t="n">
-        <v>3.078</v>
+        <v>3.086</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>22.278</v>
+        <v>22.44</v>
       </c>
       <c r="F4" t="n">
-        <v>3.513</v>
+        <v>3.414</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>18.898</v>
       </c>
       <c r="F5" t="n">
-        <v>2.813</v>
+        <v>2.812</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -7599,10 +7599,10 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>18.731</v>
+        <v>18.7</v>
       </c>
       <c r="F6" t="n">
-        <v>2.52</v>
+        <v>2.506</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7628,10 +7628,10 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>18.289</v>
+        <v>17.663</v>
       </c>
       <c r="F7" t="n">
-        <v>2.78</v>
+        <v>2.594</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>17.014</v>
+        <v>17.012</v>
       </c>
       <c r="F8" t="n">
         <v>2.648</v>
@@ -7686,10 +7686,10 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>16.138</v>
+        <v>16.137</v>
       </c>
       <c r="F9" t="n">
-        <v>2.467</v>
+        <v>2.466</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -7715,10 +7715,10 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>13.808</v>
+        <v>14.205</v>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>2.039</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -7732,26 +7732,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>13.046</v>
+        <v>13.119</v>
       </c>
       <c r="F11" t="n">
-        <v>1.728</v>
+        <v>1.009</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>12.657</v>
+        <v>12.936</v>
       </c>
       <c r="F12" t="n">
-        <v>0.904</v>
+        <v>1.685</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7802,10 +7802,10 @@
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.868</v>
+        <v>11.889</v>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.646</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>11.683</v>
+        <v>11.681</v>
       </c>
       <c r="F14" t="n">
         <v>1.777</v>
@@ -7860,10 +7860,10 @@
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>11.413</v>
+        <v>11.152</v>
       </c>
       <c r="F15" t="n">
-        <v>1.803</v>
+        <v>1.813</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>9.054</v>
+        <v>9.215</v>
       </c>
       <c r="F16" t="n">
         <v>1.287</v>
@@ -7918,10 +7918,10 @@
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>8.571999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="F17" t="n">
-        <v>1.158</v>
+        <v>1.157</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -7935,26 +7935,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6.235</v>
+        <v>6.941</v>
       </c>
       <c r="F18" t="n">
-        <v>0.444</v>
+        <v>0.741</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
     </row>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>5.158</v>
+        <v>6.235</v>
       </c>
       <c r="F19" t="n">
-        <v>0.802</v>
+        <v>0.444</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.04</v>
+        <v>5.157</v>
       </c>
       <c r="F20" t="n">
-        <v>0.286</v>
+        <v>0.802</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -8034,10 +8034,10 @@
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>4.363</v>
+        <v>4.589</v>
       </c>
       <c r="F21" t="n">
-        <v>0.327</v>
+        <v>0.419</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.109</v>
+        <v>4.25</v>
       </c>
       <c r="F22" t="n">
         <v>0.415</v>
@@ -8109,26 +8109,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.139</v>
+        <v>0.413</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.229</v>
+        <v>-0.232</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
     </row>
@@ -8138,26 +8138,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.544</v>
+        <v>-0.741</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.009</v>
+        <v>-0.625</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
     </row>
@@ -8167,26 +8167,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.983</v>
+        <v>-2.439</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.737</v>
+        <v>-0.996</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
     </row>
@@ -8196,26 +8196,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.609</v>
+        <v>-4.352</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.074</v>
+        <v>-1.29</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Javon Small</t>
         </is>
       </c>
     </row>
@@ -8225,26 +8225,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.454</v>
+        <v>-5.01</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.834</v>
+        <v>-1.189</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
     </row>
@@ -8254,26 +8254,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.1</v>
+        <v>-6.417</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.258</v>
+        <v>-1.42</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
     </row>
@@ -8283,26 +8283,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.092</v>
+        <v>-6.928</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.387</v>
+        <v>-1.7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
     </row>
@@ -8324,10 +8324,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-8.323</v>
+        <v>-7.792</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.344</v>
+        <v>-2.049</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.34</v>
+        <v>8.335000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>34.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>6.321</v>
+        <v>6.341</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.53</v>
+        <v>3.525</v>
       </c>
       <c r="E3" t="n">
         <v>33.4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.825</v>
+        <v>2.845</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.554</v>
+        <v>2.549</v>
       </c>
       <c r="E4" t="n">
         <v>31.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>2.054</v>
+        <v>2.073</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.548</v>
+        <v>2.543</v>
       </c>
       <c r="E5" t="n">
         <v>29.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.869</v>
+        <v>1.886</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.206</v>
+        <v>2.2</v>
       </c>
       <c r="E6" t="n">
         <v>29.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.667</v>
+        <v>1.684</v>
       </c>
     </row>
     <row r="7">
@@ -612,20 +612,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jock Landale</t>
+          <t>Keaton Wallace</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.899</v>
+        <v>-0.602</v>
       </c>
       <c r="E7" t="n">
-        <v>19.2</v>
+        <v>15.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.574</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.626</v>
+        <v>-1.632</v>
       </c>
       <c r="E8" t="n">
         <v>19.1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.435</v>
+        <v>-0.424</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.136</v>
+        <v>-2.141</v>
       </c>
       <c r="E9" t="n">
         <v>20.1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.67</v>
+        <v>-0.658</v>
       </c>
     </row>
     <row r="10">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.382</v>
+        <v>6.377</v>
       </c>
       <c r="E10" t="n">
         <v>34.6</v>
@@ -712,7 +712,7 @@
         <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.253</v>
+        <v>5.249</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.409</v>
+        <v>5.406</v>
       </c>
       <c r="E11" t="n">
         <v>34.7</v>
@@ -741,7 +741,7 @@
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>4.567</v>
+        <v>4.565</v>
       </c>
     </row>
     <row r="12">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.897</v>
+        <v>4.892</v>
       </c>
       <c r="E12" t="n">
         <v>34.1</v>
@@ -770,7 +770,7 @@
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>4.121</v>
+        <v>4.118</v>
       </c>
     </row>
     <row r="13">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.983</v>
+        <v>3.978</v>
       </c>
       <c r="E13" t="n">
         <v>32</v>
@@ -799,7 +799,7 @@
         <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.256</v>
+        <v>3.253</v>
       </c>
     </row>
     <row r="14">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.132</v>
+        <v>2.127</v>
       </c>
       <c r="E14" t="n">
         <v>26</v>
@@ -828,7 +828,7 @@
         <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.639</v>
+        <v>1.636</v>
       </c>
     </row>
     <row r="15">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.329</v>
+        <v>-0.33</v>
       </c>
       <c r="E15" t="n">
         <v>17.9</v>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.886</v>
+        <v>-0.891</v>
       </c>
       <c r="E16" t="n">
         <v>25.7</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="17">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.543</v>
+        <v>-1.548</v>
       </c>
       <c r="E17" t="n">
         <v>26.7</v>
@@ -915,7 +915,7 @@
         <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.357</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="18">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.046</v>
+        <v>3.04</v>
       </c>
       <c r="E18" t="n">
         <v>23.1</v>
@@ -944,7 +944,7 @@
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>1.499</v>
+        <v>1.497</v>
       </c>
     </row>
     <row r="19">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.024</v>
+        <v>2.019</v>
       </c>
       <c r="E19" t="n">
         <v>17</v>
@@ -973,7 +973,7 @@
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>0.739</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="20">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.884</v>
+        <v>-0.889</v>
       </c>
       <c r="E20" t="n">
         <v>22.7</v>
@@ -1002,7 +1002,7 @@
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.387</v>
+        <v>-0.389</v>
       </c>
     </row>
     <row r="21">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.995</v>
+        <v>-2</v>
       </c>
       <c r="E21" t="n">
         <v>23.9</v>
@@ -1031,7 +1031,7 @@
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.96</v>
+        <v>-0.962</v>
       </c>
     </row>
     <row r="22">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.338</v>
+        <v>-2.343</v>
       </c>
       <c r="E22" t="n">
         <v>21.4</v>
@@ -1060,7 +1060,7 @@
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.015</v>
+        <v>-1.017</v>
       </c>
     </row>
     <row r="23">
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4.899</v>
+        <v>-4.904</v>
       </c>
       <c r="E23" t="n">
         <v>23</v>
@@ -1089,7 +1089,7 @@
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.315</v>
+        <v>-2.318</v>
       </c>
     </row>
     <row r="24">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-5.275</v>
+        <v>-5.28</v>
       </c>
       <c r="E24" t="n">
         <v>22.5</v>
@@ -1118,7 +1118,7 @@
         <v>0.067</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.445</v>
+        <v>-2.447</v>
       </c>
     </row>
     <row r="25">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-6.07</v>
+        <v>-6.075</v>
       </c>
       <c r="E25" t="n">
         <v>23.2</v>
@@ -1147,7 +1147,7 @@
         <v>0.067</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.908</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="26">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7.161</v>
+        <v>7.11</v>
       </c>
       <c r="E26" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="F26" t="n">
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>4.673</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="27">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.534</v>
+        <v>4.387</v>
       </c>
       <c r="E27" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="F27" t="n">
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>3.287</v>
+        <v>3.166</v>
       </c>
     </row>
     <row r="28">
@@ -1225,16 +1225,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.668</v>
+        <v>2.871</v>
       </c>
       <c r="E28" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="F28" t="n">
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>2.154</v>
+        <v>2.265</v>
       </c>
     </row>
     <row r="29">
@@ -1254,16 +1254,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.208</v>
+        <v>1.419</v>
       </c>
       <c r="E29" t="n">
-        <v>29.7</v>
+        <v>29.1</v>
       </c>
       <c r="F29" t="n">
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.179</v>
+        <v>1.283</v>
       </c>
     </row>
     <row r="30">
@@ -1279,20 +1279,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.187</v>
+        <v>1.956</v>
       </c>
       <c r="E30" t="n">
-        <v>28.1</v>
+        <v>17.4</v>
       </c>
       <c r="F30" t="n">
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1.103</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="31">
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.828</v>
+        <v>0.775</v>
       </c>
       <c r="E31" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="F31" t="n">
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0.634</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="32">
@@ -1337,20 +1337,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Sion James</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.83</v>
+        <v>-3.672</v>
       </c>
       <c r="E32" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="F32" t="n">
         <v>0.7</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.052</v>
+        <v>-1.155</v>
       </c>
     </row>
     <row r="33">
@@ -1366,20 +1366,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sion James</t>
+          <t>Tre Mann</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-3.592</v>
+        <v>-5.662</v>
       </c>
       <c r="E33" t="n">
-        <v>18.1</v>
+        <v>16.2</v>
       </c>
       <c r="F33" t="n">
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.089</v>
+        <v>-1.671</v>
       </c>
     </row>
     <row r="34">
@@ -1399,16 +1399,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.795</v>
+        <v>5.79</v>
       </c>
       <c r="E34" t="n">
         <v>34.1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G34" t="n">
-        <v>4.329</v>
+        <v>4.349</v>
       </c>
     </row>
     <row r="35">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.069</v>
+        <v>4.064</v>
       </c>
       <c r="E35" t="n">
         <v>28.7</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G35" t="n">
-        <v>2.611</v>
+        <v>2.628</v>
       </c>
     </row>
     <row r="36">
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.317</v>
+        <v>2.312</v>
       </c>
       <c r="E36" t="n">
         <v>24.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G36" t="n">
-        <v>1.321</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="37">
@@ -1486,16 +1486,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.396</v>
+        <v>1.391</v>
       </c>
       <c r="E37" t="n">
         <v>33</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G37" t="n">
-        <v>1.166</v>
+        <v>1.185</v>
       </c>
     </row>
     <row r="38">
@@ -1515,16 +1515,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-0.335</v>
+        <v>-0.34</v>
       </c>
       <c r="E38" t="n">
         <v>24.2</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.018</v>
+        <v>-0.004</v>
       </c>
     </row>
     <row r="39">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-2.058</v>
+        <v>-2.063</v>
       </c>
       <c r="E39" t="n">
         <v>24.6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9</v>
+        <v>-0.885</v>
       </c>
     </row>
     <row r="40">
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-4.305</v>
+        <v>-4.31</v>
       </c>
       <c r="E40" t="n">
         <v>22.5</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.879</v>
+        <v>-1.865</v>
       </c>
     </row>
     <row r="41">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-3.527</v>
+        <v>-3.532</v>
       </c>
       <c r="E41" t="n">
         <v>30.4</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.041</v>
+        <v>-2.023</v>
       </c>
     </row>
     <row r="42">
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9.097</v>
+        <v>8.955</v>
       </c>
       <c r="E42" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G42" t="n">
-        <v>6.837</v>
+        <v>6.739</v>
       </c>
     </row>
     <row r="43">
@@ -1660,16 +1660,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8.458</v>
+        <v>8.298</v>
       </c>
       <c r="E43" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G43" t="n">
-        <v>6.799</v>
+        <v>6.576</v>
       </c>
     </row>
     <row r="44">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.624</v>
+        <v>4.566</v>
       </c>
       <c r="E44" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G44" t="n">
-        <v>3.522</v>
+        <v>3.327</v>
       </c>
     </row>
     <row r="45">
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3.828</v>
+        <v>3.945</v>
       </c>
       <c r="E45" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G45" t="n">
         <v>2.684</v>
@@ -1747,16 +1747,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.544</v>
+        <v>1.468</v>
       </c>
       <c r="E46" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G46" t="n">
-        <v>1.328</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="47">
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.134</v>
+        <v>0.882</v>
       </c>
       <c r="E47" t="n">
         <v>28.9</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G47" t="n">
-        <v>1.164</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="48">
@@ -1805,16 +1805,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.598</v>
+        <v>-0.599</v>
       </c>
       <c r="E48" t="n">
-        <v>21.6</v>
+        <v>20.4</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G48" t="n">
-        <v>0.091</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="49">
@@ -1834,16 +1834,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.774</v>
+        <v>-0.849</v>
       </c>
       <c r="E49" t="n">
-        <v>27.5</v>
+        <v>26.8</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G49" t="n">
-        <v>0.015</v>
+        <v>-0.065</v>
       </c>
     </row>
     <row r="50">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.373</v>
+        <v>2.368</v>
       </c>
       <c r="E50" t="n">
         <v>33.2</v>
@@ -1872,7 +1872,7 @@
         <v>0.233</v>
       </c>
       <c r="G50" t="n">
-        <v>1.804</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="51">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.619</v>
+        <v>1.614</v>
       </c>
       <c r="E51" t="n">
         <v>23.9</v>
@@ -1901,7 +1901,7 @@
         <v>0.233</v>
       </c>
       <c r="G51" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="52">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.182</v>
+        <v>1.177</v>
       </c>
       <c r="E52" t="n">
         <v>22.3</v>
@@ -1930,7 +1930,7 @@
         <v>0.233</v>
       </c>
       <c r="G52" t="n">
-        <v>0.658</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="53">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.624</v>
+        <v>0.619</v>
       </c>
       <c r="E53" t="n">
         <v>29.9</v>
@@ -1959,7 +1959,7 @@
         <v>0.233</v>
       </c>
       <c r="G53" t="n">
-        <v>0.535</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="54">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1.431</v>
+        <v>-1.436</v>
       </c>
       <c r="E54" t="n">
         <v>21</v>
@@ -1988,7 +1988,7 @@
         <v>0.233</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.523</v>
+        <v>-0.525</v>
       </c>
     </row>
     <row r="55">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.648</v>
+        <v>-1.654</v>
       </c>
       <c r="E55" t="n">
         <v>28.3</v>
@@ -2017,7 +2017,7 @@
         <v>0.233</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.833</v>
+        <v>-0.836</v>
       </c>
     </row>
     <row r="56">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-1.593</v>
+        <v>-1.598</v>
       </c>
       <c r="E56" t="n">
         <v>32.1</v>
@@ -2046,7 +2046,7 @@
         <v>0.233</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.911</v>
+        <v>-0.914</v>
       </c>
     </row>
     <row r="57">
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-2.984</v>
+        <v>-2.989</v>
       </c>
       <c r="E57" t="n">
         <v>21.6</v>
@@ -2075,7 +2075,7 @@
         <v>0.233</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.238</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="58">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>18.173</v>
+        <v>18.168</v>
       </c>
       <c r="E58" t="n">
         <v>36.1</v>
@@ -2104,7 +2104,7 @@
         <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>14.298</v>
+        <v>14.294</v>
       </c>
     </row>
     <row r="59">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>9.113</v>
+        <v>9.108000000000001</v>
       </c>
       <c r="E59" t="n">
         <v>35.2</v>
@@ -2133,7 +2133,7 @@
         <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>7.293</v>
+        <v>7.289</v>
       </c>
     </row>
     <row r="60">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.737</v>
+        <v>2.732</v>
       </c>
       <c r="E60" t="n">
         <v>27.6</v>
@@ -2162,7 +2162,7 @@
         <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>2.05</v>
+        <v>2.047</v>
       </c>
     </row>
     <row r="61">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.486</v>
+        <v>0.481</v>
       </c>
       <c r="E61" t="n">
         <v>25.4</v>
@@ -2191,7 +2191,7 @@
         <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>0.699</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="62">
@@ -2207,20 +2207,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.049</v>
+        <v>-1.042</v>
       </c>
       <c r="E62" t="n">
-        <v>31.6</v>
+        <v>28.6</v>
       </c>
       <c r="F62" t="n">
         <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>0.581</v>
+        <v>-0.124</v>
       </c>
     </row>
     <row r="63">
@@ -2236,20 +2236,20 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-1.037</v>
+        <v>-2.351</v>
       </c>
       <c r="E63" t="n">
-        <v>28.6</v>
+        <v>15.7</v>
       </c>
       <c r="F63" t="n">
         <v>0.833</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.121</v>
+        <v>-0.495</v>
       </c>
     </row>
     <row r="64">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-2.044</v>
+        <v>-2.049</v>
       </c>
       <c r="E64" t="n">
         <v>32</v>
@@ -2278,7 +2278,7 @@
         <v>0.833</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.8110000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-2.786</v>
+        <v>-2.791</v>
       </c>
       <c r="E65" t="n">
         <v>21.7</v>
@@ -2307,7 +2307,7 @@
         <v>0.833</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.883</v>
+        <v>-0.885</v>
       </c>
     </row>
     <row r="66">
@@ -2327,16 +2327,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.455</v>
+        <v>5.59</v>
       </c>
       <c r="E66" t="n">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="F66" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>3.652</v>
+        <v>3.802</v>
       </c>
     </row>
     <row r="67">
@@ -2356,16 +2356,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.555</v>
+        <v>1.481</v>
       </c>
       <c r="E67" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="F67" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>1.339</v>
+        <v>1.327</v>
       </c>
     </row>
     <row r="68">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-0.031</v>
+        <v>-0.022</v>
       </c>
       <c r="E68" t="n">
         <v>28.3</v>
@@ -2394,7 +2394,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.532</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="69">
@@ -2410,20 +2410,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.027</v>
+        <v>-0.057</v>
       </c>
       <c r="E69" t="n">
-        <v>21.8</v>
+        <v>26.1</v>
       </c>
       <c r="F69" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>0.412</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="70">
@@ -2439,20 +2439,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.195</v>
+        <v>-0.102</v>
       </c>
       <c r="E70" t="n">
-        <v>25.8</v>
+        <v>22.8</v>
       </c>
       <c r="F70" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0.398</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="71">
@@ -2472,16 +2472,16 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-0.585</v>
+        <v>-0.424</v>
       </c>
       <c r="E71" t="n">
-        <v>27.5</v>
+        <v>29.3</v>
       </c>
       <c r="F71" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="72">
@@ -2530,16 +2530,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-1.698</v>
+        <v>-1.525</v>
       </c>
       <c r="E73" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="F73" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.305</v>
+        <v>-0.237</v>
       </c>
     </row>
     <row r="74">
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.309</v>
+        <v>4.535</v>
       </c>
       <c r="E74" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="F74" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G74" t="n">
-        <v>2.131</v>
+        <v>2.274</v>
       </c>
     </row>
     <row r="75">
@@ -2584,20 +2584,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gary Payton II</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2.772</v>
+        <v>1.986</v>
       </c>
       <c r="E75" t="n">
-        <v>22</v>
+        <v>32.2</v>
       </c>
       <c r="F75" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G75" t="n">
-        <v>1.472</v>
+        <v>1.599</v>
       </c>
     </row>
     <row r="76">
@@ -2613,20 +2613,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Gary Payton II</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.658</v>
+        <v>2.884</v>
       </c>
       <c r="E76" t="n">
-        <v>33.4</v>
+        <v>22.1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G76" t="n">
-        <v>1.453</v>
+        <v>1.515</v>
       </c>
     </row>
     <row r="77">
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.821</v>
+        <v>0.601</v>
       </c>
       <c r="E77" t="n">
-        <v>32.4</v>
+        <v>32.8</v>
       </c>
       <c r="F77" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>0.848</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.573</v>
+        <v>-0.513</v>
       </c>
       <c r="E78" t="n">
-        <v>21.2</v>
+        <v>22.1</v>
       </c>
       <c r="F78" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.061</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="79">
@@ -2700,20 +2700,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.612</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="E79" t="n">
-        <v>25.1</v>
+        <v>29.9</v>
       </c>
       <c r="F79" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.094</v>
+        <v>-0.102</v>
       </c>
     </row>
     <row r="80">
@@ -2729,20 +2729,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.884</v>
       </c>
       <c r="E80" t="n">
-        <v>29.9</v>
+        <v>25.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.235</v>
+        <v>-0.253</v>
       </c>
     </row>
     <row r="81">
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-1.149</v>
+        <v>-1.207</v>
       </c>
       <c r="E81" t="n">
-        <v>23.9</v>
+        <v>24.6</v>
       </c>
       <c r="F81" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.357</v>
+        <v>-0.414</v>
       </c>
     </row>
     <row r="82">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6.629</v>
+        <v>6.624</v>
       </c>
       <c r="E82" t="n">
         <v>35.7</v>
       </c>
       <c r="F82" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G82" t="n">
-        <v>5.503</v>
+        <v>5.524</v>
       </c>
     </row>
     <row r="83">
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6.199</v>
+        <v>6.194</v>
       </c>
       <c r="E83" t="n">
         <v>32.9</v>
       </c>
       <c r="F83" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G83" t="n">
-        <v>4.775</v>
+        <v>4.794</v>
       </c>
     </row>
     <row r="84">
@@ -2849,16 +2849,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3.762</v>
+        <v>3.757</v>
       </c>
       <c r="E84" t="n">
         <v>38.7</v>
       </c>
       <c r="F84" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G84" t="n">
-        <v>3.648</v>
+        <v>3.671</v>
       </c>
     </row>
     <row r="85">
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.236</v>
+        <v>3.231</v>
       </c>
       <c r="E85" t="n">
         <v>30.1</v>
       </c>
       <c r="F85" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G85" t="n">
-        <v>2.51</v>
+        <v>2.528</v>
       </c>
     </row>
     <row r="86">
@@ -2907,16 +2907,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-0.434</v>
+        <v>-0.439</v>
       </c>
       <c r="E86" t="n">
         <v>36.6</v>
       </c>
       <c r="F86" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.253</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="87">
@@ -2936,16 +2936,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-1.649</v>
+        <v>-1.654</v>
       </c>
       <c r="E87" t="n">
         <v>25.1</v>
       </c>
       <c r="F87" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.462</v>
+        <v>-0.447</v>
       </c>
     </row>
     <row r="88">
@@ -2965,16 +2965,16 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-2.954</v>
+        <v>-2.959</v>
       </c>
       <c r="E88" t="n">
         <v>16</v>
       </c>
       <c r="F88" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.727</v>
+        <v>-0.718</v>
       </c>
     </row>
     <row r="89">
@@ -2994,16 +2994,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-6.718</v>
+        <v>-6.724</v>
       </c>
       <c r="E89" t="n">
         <v>19.2</v>
       </c>
       <c r="F89" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G89" t="n">
-        <v>-2.381</v>
+        <v>-2.369</v>
       </c>
     </row>
     <row r="90">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3.028</v>
+        <v>3.023</v>
       </c>
       <c r="E90" t="n">
         <v>31.6</v>
@@ -3032,7 +3032,7 @@
         <v>0.167</v>
       </c>
       <c r="G90" t="n">
-        <v>2.102</v>
+        <v>2.099</v>
       </c>
     </row>
     <row r="91">
@@ -3048,20 +3048,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.828</v>
+        <v>1.928</v>
       </c>
       <c r="E91" t="n">
-        <v>28.7</v>
+        <v>23</v>
       </c>
       <c r="F91" t="n">
         <v>0.167</v>
       </c>
       <c r="G91" t="n">
-        <v>1.791</v>
+        <v>1.005</v>
       </c>
     </row>
     <row r="92">
@@ -3077,20 +3077,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.933</v>
+        <v>1.995</v>
       </c>
       <c r="E92" t="n">
-        <v>23</v>
+        <v>17.4</v>
       </c>
       <c r="F92" t="n">
         <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>1.008</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-0.697</v>
+        <v>1.819</v>
       </c>
       <c r="E93" t="n">
-        <v>18.8</v>
+        <v>16.9</v>
       </c>
       <c r="F93" t="n">
         <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.208</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="94">
@@ -3135,20 +3135,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-2.147</v>
+        <v>-0.703</v>
       </c>
       <c r="E94" t="n">
-        <v>22</v>
+        <v>18.8</v>
       </c>
       <c r="F94" t="n">
         <v>0.167</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.909</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="95">
@@ -3164,20 +3164,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.946</v>
+        <v>-2.152</v>
       </c>
       <c r="E95" t="n">
-        <v>20.2</v>
+        <v>22</v>
       </c>
       <c r="F95" t="n">
         <v>0.167</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.168</v>
+        <v>-0.911</v>
       </c>
     </row>
     <row r="96">
@@ -3193,20 +3193,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-3.042</v>
+        <v>-2.952</v>
       </c>
       <c r="E96" t="n">
-        <v>27.3</v>
+        <v>20.2</v>
       </c>
       <c r="F96" t="n">
         <v>0.167</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.636</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="97">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-3.96</v>
+        <v>-3.965</v>
       </c>
       <c r="E97" t="n">
         <v>21.8</v>
@@ -3235,7 +3235,7 @@
         <v>0.167</v>
       </c>
       <c r="G97" t="n">
-        <v>-1.721</v>
+        <v>-1.723</v>
       </c>
     </row>
     <row r="98">
@@ -3255,16 +3255,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.746</v>
+        <v>11.624</v>
       </c>
       <c r="E98" t="n">
-        <v>30</v>
+        <v>30.4</v>
       </c>
       <c r="F98" t="n">
         <v>0.633</v>
       </c>
       <c r="G98" t="n">
-        <v>7.727</v>
+        <v>7.756</v>
       </c>
     </row>
     <row r="99">
@@ -3284,16 +3284,16 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3.829</v>
+        <v>3.667</v>
       </c>
       <c r="E99" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="F99" t="n">
         <v>0.633</v>
       </c>
       <c r="G99" t="n">
-        <v>2.619</v>
+        <v>2.547</v>
       </c>
     </row>
     <row r="100">
@@ -3313,16 +3313,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.244</v>
+        <v>0.458</v>
       </c>
       <c r="E100" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="F100" t="n">
         <v>0.633</v>
       </c>
       <c r="G100" t="n">
-        <v>0.496</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="101">
@@ -3338,20 +3338,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.108</v>
+        <v>0.477</v>
       </c>
       <c r="E101" t="n">
-        <v>29.7</v>
+        <v>24.9</v>
       </c>
       <c r="F101" t="n">
         <v>0.633</v>
       </c>
       <c r="G101" t="n">
-        <v>0.458</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="102">
@@ -3367,20 +3367,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.241</v>
+        <v>0.05</v>
       </c>
       <c r="E102" t="n">
-        <v>24.9</v>
+        <v>29.5</v>
       </c>
       <c r="F102" t="n">
         <v>0.633</v>
       </c>
       <c r="G102" t="n">
-        <v>0.454</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="103">
@@ -3396,14 +3396,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-0.269</v>
+        <v>-0.284</v>
       </c>
       <c r="E103" t="n">
-        <v>26.6</v>
+        <v>27.5</v>
       </c>
       <c r="F103" t="n">
         <v>0.633</v>
@@ -3425,20 +3425,20 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.322</v>
+        <v>-0.278</v>
       </c>
       <c r="E104" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="F104" t="n">
         <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>0.172</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="105">
@@ -3458,16 +3458,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-1.36</v>
+        <v>-1.642</v>
       </c>
       <c r="E105" t="n">
-        <v>29.5</v>
+        <v>28.9</v>
       </c>
       <c r="F105" t="n">
         <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.446</v>
+        <v>-0.609</v>
       </c>
     </row>
     <row r="106">
@@ -3487,16 +3487,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>15.371</v>
+        <v>15.68</v>
       </c>
       <c r="E106" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="F106" t="n">
         <v>0.667</v>
       </c>
       <c r="G106" t="n">
-        <v>12.476</v>
+        <v>12.823</v>
       </c>
     </row>
     <row r="107">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5.617</v>
+        <v>5.471</v>
       </c>
       <c r="E107" t="n">
         <v>37.9</v>
@@ -3525,7 +3525,7 @@
         <v>0.667</v>
       </c>
       <c r="G107" t="n">
-        <v>4.96</v>
+        <v>4.844</v>
       </c>
     </row>
     <row r="108">
@@ -3545,16 +3545,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5.977</v>
+        <v>5.956</v>
       </c>
       <c r="E108" t="n">
-        <v>34.3</v>
+        <v>34</v>
       </c>
       <c r="F108" t="n">
         <v>0.667</v>
       </c>
       <c r="G108" t="n">
-        <v>4.741</v>
+        <v>4.689</v>
       </c>
     </row>
     <row r="109">
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.324</v>
+        <v>2.306</v>
       </c>
       <c r="E109" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="F109" t="n">
         <v>0.667</v>
       </c>
       <c r="G109" t="n">
-        <v>1.273</v>
+        <v>1.279</v>
       </c>
     </row>
     <row r="110">
@@ -3603,16 +3603,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.894</v>
+        <v>0.724</v>
       </c>
       <c r="E110" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="F110" t="n">
         <v>0.667</v>
       </c>
       <c r="G110" t="n">
-        <v>0.697</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="111">
@@ -3632,16 +3632,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.144</v>
+        <v>0.236</v>
       </c>
       <c r="E111" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="F111" t="n">
         <v>0.667</v>
       </c>
       <c r="G111" t="n">
-        <v>0.423</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="112">
@@ -3661,16 +3661,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-1.246</v>
+        <v>-1.181</v>
       </c>
       <c r="E112" t="n">
-        <v>17.9</v>
+        <v>19.5</v>
       </c>
       <c r="F112" t="n">
         <v>0.667</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.216</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="113">
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-2.503</v>
+        <v>-2.378</v>
       </c>
       <c r="E113" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="F113" t="n">
         <v>0.667</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.955</v>
+        <v>-0.872</v>
       </c>
     </row>
     <row r="114">
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2.932</v>
+        <v>2.927</v>
       </c>
       <c r="E114" t="n">
         <v>25.1</v>
@@ -3728,7 +3728,7 @@
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>1.671</v>
+        <v>1.668</v>
       </c>
     </row>
     <row r="115">
@@ -3744,20 +3744,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.014</v>
+        <v>0.319</v>
       </c>
       <c r="E115" t="n">
-        <v>25.4</v>
+        <v>23.9</v>
       </c>
       <c r="F115" t="n">
         <v>0.267</v>
       </c>
       <c r="G115" t="n">
-        <v>0.677</v>
+        <v>0.291</v>
       </c>
     </row>
     <row r="116">
@@ -3773,20 +3773,20 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>GG Jackson</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.324</v>
+        <v>-0.475</v>
       </c>
       <c r="E116" t="n">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="F116" t="n">
         <v>0.267</v>
       </c>
       <c r="G116" t="n">
-        <v>0.294</v>
+        <v>-0.111</v>
       </c>
     </row>
     <row r="117">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Taylor Hendricks</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-0.47</v>
+        <v>-1.652</v>
       </c>
       <c r="E117" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="F117" t="n">
         <v>0.267</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.108</v>
+        <v>-0.744</v>
       </c>
     </row>
     <row r="118">
@@ -3831,11 +3831,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Walter Clayton Jr.</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-1.647</v>
+        <v>-2.2</v>
       </c>
       <c r="E118" t="n">
         <v>25.8</v>
@@ -3844,7 +3844,7 @@
         <v>0.267</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.742</v>
+        <v>-1.037</v>
       </c>
     </row>
     <row r="119">
@@ -3860,20 +3860,20 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Walter Clayton Jr.</t>
+          <t>Jahmai Mashack</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-2.195</v>
+        <v>-4.579</v>
       </c>
       <c r="E119" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="F119" t="n">
         <v>0.267</v>
       </c>
       <c r="G119" t="n">
-        <v>-1.035</v>
+        <v>-2.373</v>
       </c>
     </row>
     <row r="120">
@@ -3889,49 +3889,49 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jahmai Mashack</t>
+          <t>Rayan Rupert</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-4.574</v>
+        <v>-5.711</v>
       </c>
       <c r="E120" t="n">
-        <v>26.4</v>
+        <v>24.2</v>
       </c>
       <c r="F120" t="n">
         <v>0.267</v>
       </c>
       <c r="G120" t="n">
-        <v>-2.37</v>
+        <v>-2.742</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Rayan Rupert</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-5.706</v>
+        <v>2.969</v>
       </c>
       <c r="E121" t="n">
-        <v>24.2</v>
+        <v>35.5</v>
       </c>
       <c r="F121" t="n">
-        <v>0.267</v>
+        <v>0.6</v>
       </c>
       <c r="G121" t="n">
-        <v>-2.739</v>
+        <v>2.642</v>
       </c>
     </row>
     <row r="122">
@@ -3947,20 +3947,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2.974</v>
+        <v>2.271</v>
       </c>
       <c r="E122" t="n">
-        <v>35.5</v>
+        <v>32.7</v>
       </c>
       <c r="F122" t="n">
         <v>0.6</v>
       </c>
       <c r="G122" t="n">
-        <v>2.646</v>
+        <v>1.957</v>
       </c>
     </row>
     <row r="123">
@@ -3976,20 +3976,20 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.276</v>
+        <v>2.288</v>
       </c>
       <c r="E123" t="n">
-        <v>32.7</v>
+        <v>23.1</v>
       </c>
       <c r="F123" t="n">
         <v>0.6</v>
       </c>
       <c r="G123" t="n">
-        <v>1.961</v>
+        <v>1.387</v>
       </c>
     </row>
     <row r="124">
@@ -4005,20 +4005,20 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2.293</v>
+        <v>1.664</v>
       </c>
       <c r="E124" t="n">
-        <v>23.1</v>
+        <v>29</v>
       </c>
       <c r="F124" t="n">
         <v>0.6</v>
       </c>
       <c r="G124" t="n">
-        <v>1.389</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="125">
@@ -4034,20 +4034,20 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1.669</v>
+        <v>1.007</v>
       </c>
       <c r="E125" t="n">
-        <v>29</v>
+        <v>26.9</v>
       </c>
       <c r="F125" t="n">
         <v>0.6</v>
       </c>
       <c r="G125" t="n">
-        <v>1.371</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="126">
@@ -4063,20 +4063,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1.013</v>
+        <v>0.297</v>
       </c>
       <c r="E126" t="n">
-        <v>26.9</v>
+        <v>27.7</v>
       </c>
       <c r="F126" t="n">
         <v>0.6</v>
       </c>
       <c r="G126" t="n">
-        <v>0.903</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="127">
@@ -4092,20 +4092,20 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Kasparas Jakučionis</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.302</v>
+        <v>-0.624</v>
       </c>
       <c r="E127" t="n">
-        <v>27.7</v>
+        <v>19.3</v>
       </c>
       <c r="F127" t="n">
         <v>0.6</v>
       </c>
       <c r="G127" t="n">
-        <v>0.521</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="128">
@@ -4121,49 +4121,49 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Kasparas Jakučionis</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-0.619</v>
+        <v>-0.658</v>
       </c>
       <c r="E128" t="n">
-        <v>19.3</v>
+        <v>30.3</v>
       </c>
       <c r="F128" t="n">
         <v>0.6</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.008</v>
+        <v>-0.037</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.653</v>
+        <v>0.549</v>
       </c>
       <c r="E129" t="n">
-        <v>30.3</v>
+        <v>23.1</v>
       </c>
       <c r="F129" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.033</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="130">
@@ -4179,20 +4179,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>3.886</v>
+        <v>-0.41</v>
       </c>
       <c r="E130" t="n">
-        <v>31.3</v>
+        <v>24.9</v>
       </c>
       <c r="F130" t="n">
         <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>2.668</v>
+        <v>-0.109</v>
       </c>
     </row>
     <row r="131">
@@ -4208,20 +4208,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.555</v>
+        <v>-0.972</v>
       </c>
       <c r="E131" t="n">
-        <v>23.1</v>
+        <v>20.9</v>
       </c>
       <c r="F131" t="n">
         <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>0.363</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="132">
@@ -4237,20 +4237,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-0.405</v>
+        <v>-2.557</v>
       </c>
       <c r="E132" t="n">
-        <v>24.9</v>
+        <v>22.7</v>
       </c>
       <c r="F132" t="n">
         <v>0.2</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.106</v>
+        <v>-1.115</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-0.967</v>
+        <v>-3.635</v>
       </c>
       <c r="E133" t="n">
-        <v>20.9</v>
+        <v>16.3</v>
       </c>
       <c r="F133" t="n">
         <v>0.2</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.334</v>
+        <v>-1.167</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.552</v>
+        <v>-2.662</v>
       </c>
       <c r="E134" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="F134" t="n">
         <v>0.2</v>
       </c>
       <c r="G134" t="n">
-        <v>-1.112</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="135">
@@ -4324,20 +4324,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-2.657</v>
+        <v>-2.353</v>
       </c>
       <c r="E135" t="n">
-        <v>22.8</v>
+        <v>27.9</v>
       </c>
       <c r="F135" t="n">
         <v>0.2</v>
       </c>
       <c r="G135" t="n">
-        <v>-1.168</v>
+        <v>-1.254</v>
       </c>
     </row>
     <row r="136">
@@ -4353,49 +4353,49 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-2.348</v>
+        <v>-3.486</v>
       </c>
       <c r="E136" t="n">
-        <v>27.9</v>
+        <v>21.9</v>
       </c>
       <c r="F136" t="n">
         <v>0.2</v>
       </c>
       <c r="G136" t="n">
-        <v>-1.251</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-3.482</v>
+        <v>7.347</v>
       </c>
       <c r="E137" t="n">
-        <v>21.9</v>
+        <v>35.6</v>
       </c>
       <c r="F137" t="n">
-        <v>0.2</v>
+        <v>0.767</v>
       </c>
       <c r="G137" t="n">
-        <v>-1.499</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="138">
@@ -4411,20 +4411,20 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7.352</v>
+        <v>3.98</v>
       </c>
       <c r="E138" t="n">
-        <v>35.6</v>
+        <v>31.6</v>
       </c>
       <c r="F138" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G138" t="n">
-        <v>5.999</v>
+        <v>3.129</v>
       </c>
     </row>
     <row r="139">
@@ -4440,20 +4440,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3.944</v>
+        <v>2.998</v>
       </c>
       <c r="E139" t="n">
-        <v>31.7</v>
+        <v>28</v>
       </c>
       <c r="F139" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G139" t="n">
-        <v>3.085</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="140">
@@ -4469,20 +4469,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.667</v>
+        <v>1.655</v>
       </c>
       <c r="E140" t="n">
-        <v>27.6</v>
+        <v>30.2</v>
       </c>
       <c r="F140" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G140" t="n">
-        <v>1.958</v>
+        <v>1.524</v>
       </c>
     </row>
     <row r="141">
@@ -4498,20 +4498,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1.639</v>
+        <v>1.713</v>
       </c>
       <c r="E141" t="n">
-        <v>30.3</v>
+        <v>25.1</v>
       </c>
       <c r="F141" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G141" t="n">
-        <v>1.499</v>
+        <v>1.299</v>
       </c>
     </row>
     <row r="142">
@@ -4527,20 +4527,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1.889</v>
+        <v>0.863</v>
       </c>
       <c r="E142" t="n">
-        <v>25.5</v>
+        <v>31.2</v>
       </c>
       <c r="F142" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G142" t="n">
-        <v>1.393</v>
+        <v>1.061</v>
       </c>
     </row>
     <row r="143">
@@ -4556,20 +4556,20 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.856</v>
+        <v>1.581</v>
       </c>
       <c r="E143" t="n">
-        <v>31.7</v>
+        <v>20.2</v>
       </c>
       <c r="F143" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G143" t="n">
-        <v>1.048</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="144">
@@ -4585,49 +4585,49 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1.596</v>
+        <v>-0.351</v>
       </c>
       <c r="E144" t="n">
-        <v>19.7</v>
+        <v>17.9</v>
       </c>
       <c r="F144" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G144" t="n">
-        <v>0.954</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-0.212</v>
+        <v>4.897</v>
       </c>
       <c r="E145" t="n">
-        <v>18.5</v>
+        <v>34.2</v>
       </c>
       <c r="F145" t="n">
-        <v>0.733</v>
+        <v>0.3</v>
       </c>
       <c r="G145" t="n">
-        <v>0.201</v>
+        <v>3.699</v>
       </c>
     </row>
     <row r="146">
@@ -4647,16 +4647,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4.848</v>
+        <v>4.866</v>
       </c>
       <c r="E146" t="n">
-        <v>29.8</v>
+        <v>29.2</v>
       </c>
       <c r="F146" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G146" t="n">
-        <v>3.213</v>
+        <v>3.146</v>
       </c>
     </row>
     <row r="147">
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2.248</v>
+        <v>2.286</v>
       </c>
       <c r="E147" t="n">
-        <v>32.7</v>
+        <v>32.1</v>
       </c>
       <c r="F147" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G147" t="n">
-        <v>1.756</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="148">
@@ -4701,20 +4701,20 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2.33</v>
+        <v>0.971</v>
       </c>
       <c r="E148" t="n">
-        <v>30.7</v>
+        <v>19.7</v>
       </c>
       <c r="F148" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G148" t="n">
-        <v>1.701</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="149">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1.067</v>
+        <v>-0.235</v>
       </c>
       <c r="E149" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="F149" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G149" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="150">
@@ -4759,20 +4759,20 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-0.203</v>
+        <v>-1.442</v>
       </c>
       <c r="E150" t="n">
-        <v>18.6</v>
+        <v>21.5</v>
       </c>
       <c r="F150" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G150" t="n">
-        <v>0.051</v>
+        <v>-0.512</v>
       </c>
     </row>
     <row r="151">
@@ -4788,20 +4788,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-1.445</v>
+        <v>-2.674</v>
       </c>
       <c r="E151" t="n">
-        <v>22.4</v>
+        <v>19.9</v>
       </c>
       <c r="F151" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.518</v>
+        <v>-0.984</v>
       </c>
     </row>
     <row r="152">
@@ -4817,49 +4817,49 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-2.669</v>
+        <v>-3.014</v>
       </c>
       <c r="E152" t="n">
-        <v>19.9</v>
+        <v>29</v>
       </c>
       <c r="F152" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.968</v>
+        <v>-1.642</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-2.858</v>
+        <v>6.606</v>
       </c>
       <c r="E153" t="n">
-        <v>29.5</v>
+        <v>36.1</v>
       </c>
       <c r="F153" t="n">
-        <v>0.333</v>
+        <v>0.867</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.549</v>
+        <v>5.622</v>
       </c>
     </row>
     <row r="154">
@@ -4875,20 +4875,20 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>6.611</v>
+        <v>4.167</v>
       </c>
       <c r="E154" t="n">
-        <v>36.1</v>
+        <v>29.9</v>
       </c>
       <c r="F154" t="n">
         <v>0.867</v>
       </c>
       <c r="G154" t="n">
-        <v>5.626</v>
+        <v>3.131</v>
       </c>
     </row>
     <row r="155">
@@ -4904,20 +4904,20 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4.172</v>
+        <v>2.979</v>
       </c>
       <c r="E155" t="n">
-        <v>29.9</v>
+        <v>30.9</v>
       </c>
       <c r="F155" t="n">
         <v>0.867</v>
       </c>
       <c r="G155" t="n">
-        <v>3.134</v>
+        <v>2.479</v>
       </c>
     </row>
     <row r="156">
@@ -4933,20 +4933,20 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2.984</v>
+        <v>3.097</v>
       </c>
       <c r="E156" t="n">
-        <v>30.9</v>
+        <v>29.6</v>
       </c>
       <c r="F156" t="n">
         <v>0.867</v>
       </c>
       <c r="G156" t="n">
-        <v>2.483</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="157">
@@ -4962,20 +4962,20 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3.102</v>
+        <v>1.601</v>
       </c>
       <c r="E157" t="n">
-        <v>29.6</v>
+        <v>34</v>
       </c>
       <c r="F157" t="n">
         <v>0.867</v>
       </c>
       <c r="G157" t="n">
-        <v>2.447</v>
+        <v>1.746</v>
       </c>
     </row>
     <row r="158">
@@ -4991,20 +4991,20 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1.607</v>
+        <v>3.046</v>
       </c>
       <c r="E158" t="n">
-        <v>34</v>
+        <v>19.7</v>
       </c>
       <c r="F158" t="n">
         <v>0.867</v>
       </c>
       <c r="G158" t="n">
-        <v>1.749</v>
+        <v>1.604</v>
       </c>
     </row>
     <row r="159">
@@ -5020,20 +5020,20 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3.051</v>
+        <v>0.553</v>
       </c>
       <c r="E159" t="n">
-        <v>19.7</v>
+        <v>28.9</v>
       </c>
       <c r="F159" t="n">
         <v>0.867</v>
       </c>
       <c r="G159" t="n">
-        <v>1.606</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="160">
@@ -5049,49 +5049,49 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.5580000000000001</v>
+        <v>-1.338</v>
       </c>
       <c r="E160" t="n">
-        <v>28.9</v>
+        <v>24.8</v>
       </c>
       <c r="F160" t="n">
         <v>0.867</v>
       </c>
       <c r="G160" t="n">
-        <v>0.859</v>
+        <v>-0.244</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-1.333</v>
+        <v>14.848</v>
       </c>
       <c r="E161" t="n">
-        <v>24.8</v>
+        <v>34.3</v>
       </c>
       <c r="F161" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>-0.241</v>
+        <v>11.332</v>
       </c>
     </row>
     <row r="162">
@@ -5107,20 +5107,20 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>14.813</v>
+        <v>3.938</v>
       </c>
       <c r="E162" t="n">
-        <v>33.5</v>
+        <v>29.9</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>11.027</v>
+        <v>3.077</v>
       </c>
     </row>
     <row r="163">
@@ -5136,20 +5136,20 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4.044</v>
+        <v>3.205</v>
       </c>
       <c r="E163" t="n">
-        <v>29.7</v>
+        <v>22.4</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>3.116</v>
+        <v>1.962</v>
       </c>
     </row>
     <row r="164">
@@ -5165,20 +5165,20 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>3.337</v>
+        <v>1.751</v>
       </c>
       <c r="E164" t="n">
-        <v>22.5</v>
+        <v>27.2</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>2.03</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="165">
@@ -5198,16 +5198,16 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.89</v>
+        <v>1.798</v>
       </c>
       <c r="E165" t="n">
-        <v>25.7</v>
+        <v>26.3</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>1.549</v>
+        <v>1.535</v>
       </c>
     </row>
     <row r="166">
@@ -5223,20 +5223,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1.594</v>
+        <v>1.204</v>
       </c>
       <c r="E166" t="n">
-        <v>27</v>
+        <v>21.6</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1.461</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="167">
@@ -5252,20 +5252,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.259</v>
+        <v>-0.046</v>
       </c>
       <c r="E167" t="n">
-        <v>22.2</v>
+        <v>25.1</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1.045</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="168">
@@ -5281,49 +5281,49 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.096</v>
+        <v>-4.619</v>
       </c>
       <c r="E168" t="n">
-        <v>25.7</v>
+        <v>25.2</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.587</v>
+        <v>-1.902</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-4.533</v>
+        <v>3.312</v>
       </c>
       <c r="E169" t="n">
-        <v>26.1</v>
+        <v>35.4</v>
       </c>
       <c r="F169" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G169" t="n">
-        <v>-1.917</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="170">
@@ -5339,20 +5339,20 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3.318</v>
+        <v>3.176</v>
       </c>
       <c r="E170" t="n">
-        <v>35.4</v>
+        <v>34.2</v>
       </c>
       <c r="F170" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G170" t="n">
-        <v>2.744</v>
+        <v>2.569</v>
       </c>
     </row>
     <row r="171">
@@ -5368,20 +5368,20 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3.181</v>
+        <v>3.158</v>
       </c>
       <c r="E171" t="n">
-        <v>34.2</v>
+        <v>30.2</v>
       </c>
       <c r="F171" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G171" t="n">
-        <v>2.549</v>
+        <v>2.257</v>
       </c>
     </row>
     <row r="172">
@@ -5397,20 +5397,20 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3.163</v>
+        <v>1.991</v>
       </c>
       <c r="E172" t="n">
-        <v>30.2</v>
+        <v>28.8</v>
       </c>
       <c r="F172" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G172" t="n">
-        <v>2.239</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="173">
@@ -5426,20 +5426,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1.996</v>
+        <v>-0.67</v>
       </c>
       <c r="E173" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="F173" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G173" t="n">
-        <v>1.44</v>
+        <v>-0.145</v>
       </c>
     </row>
     <row r="174">
@@ -5455,20 +5455,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-0.665</v>
+        <v>-1.201</v>
       </c>
       <c r="E174" t="n">
-        <v>29.3</v>
+        <v>29.6</v>
       </c>
       <c r="F174" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.162</v>
+        <v>-0.474</v>
       </c>
     </row>
     <row r="175">
@@ -5484,20 +5484,20 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-1.196</v>
+        <v>-1.598</v>
       </c>
       <c r="E175" t="n">
-        <v>29.6</v>
+        <v>20.6</v>
       </c>
       <c r="F175" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.491</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="176">
@@ -5513,49 +5513,49 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Orlando Robinson</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-1.593</v>
+        <v>-2.275</v>
       </c>
       <c r="E176" t="n">
-        <v>20.6</v>
+        <v>22.2</v>
       </c>
       <c r="F176" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.512</v>
+        <v>-0.851</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Orlando Robinson</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>-2.274</v>
+        <v>9.177</v>
       </c>
       <c r="E177" t="n">
-        <v>22.2</v>
+        <v>37</v>
       </c>
       <c r="F177" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G177" t="n">
-        <v>-0.866</v>
+        <v>7.431</v>
       </c>
     </row>
     <row r="178">
@@ -5571,20 +5571,20 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>9.182</v>
+        <v>5.549</v>
       </c>
       <c r="E178" t="n">
-        <v>37</v>
+        <v>33.5</v>
       </c>
       <c r="F178" t="n">
         <v>0.467</v>
       </c>
       <c r="G178" t="n">
-        <v>7.435</v>
+        <v>4.199</v>
       </c>
     </row>
     <row r="179">
@@ -5600,20 +5600,20 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5.554</v>
+        <v>1.83</v>
       </c>
       <c r="E179" t="n">
-        <v>33.5</v>
+        <v>32.7</v>
       </c>
       <c r="F179" t="n">
         <v>0.467</v>
       </c>
       <c r="G179" t="n">
-        <v>4.203</v>
+        <v>1.564</v>
       </c>
     </row>
     <row r="180">
@@ -5629,20 +5629,20 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1.835</v>
+        <v>0.758</v>
       </c>
       <c r="E180" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="F180" t="n">
         <v>0.467</v>
       </c>
       <c r="G180" t="n">
-        <v>1.568</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="181">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.763</v>
+        <v>-0.187</v>
       </c>
       <c r="E181" t="n">
-        <v>32.9</v>
+        <v>32.2</v>
       </c>
       <c r="F181" t="n">
         <v>0.467</v>
       </c>
       <c r="G181" t="n">
-        <v>0.842</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="182">
@@ -5687,20 +5687,20 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Eric Gordon</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-0.181</v>
+        <v>-0.769</v>
       </c>
       <c r="E182" t="n">
-        <v>32.2</v>
+        <v>23</v>
       </c>
       <c r="F182" t="n">
         <v>0.467</v>
       </c>
       <c r="G182" t="n">
-        <v>0.191</v>
+        <v>-0.144</v>
       </c>
     </row>
     <row r="183">
@@ -5716,20 +5716,20 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Eric Gordon</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-0.768</v>
+        <v>-1.343</v>
       </c>
       <c r="E183" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="F183" t="n">
         <v>0.467</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.144</v>
+        <v>-0.417</v>
       </c>
     </row>
     <row r="184">
@@ -5745,49 +5745,49 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>-1.338</v>
+        <v>-1.571</v>
       </c>
       <c r="E184" t="n">
-        <v>22.9</v>
+        <v>32.5</v>
       </c>
       <c r="F184" t="n">
         <v>0.467</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.415</v>
+        <v>-0.747</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>-1.566</v>
+        <v>4.901</v>
       </c>
       <c r="E185" t="n">
-        <v>32.5</v>
+        <v>33.4</v>
       </c>
       <c r="F185" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.744</v>
+        <v>3.761</v>
       </c>
     </row>
     <row r="186">
@@ -5803,20 +5803,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>4.81</v>
+        <v>4.182</v>
       </c>
       <c r="E186" t="n">
-        <v>33.1</v>
+        <v>29.5</v>
       </c>
       <c r="F186" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G186" t="n">
-        <v>3.707</v>
+        <v>2.874</v>
       </c>
     </row>
     <row r="187">
@@ -5832,20 +5832,20 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4.257</v>
+        <v>2.739</v>
       </c>
       <c r="E187" t="n">
-        <v>29.7</v>
+        <v>28.9</v>
       </c>
       <c r="F187" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G187" t="n">
-        <v>2.988</v>
+        <v>1.952</v>
       </c>
     </row>
     <row r="188">
@@ -5861,20 +5861,20 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3.236</v>
+        <v>0.921</v>
       </c>
       <c r="E188" t="n">
-        <v>28.6</v>
+        <v>24.7</v>
       </c>
       <c r="F188" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G188" t="n">
-        <v>2.264</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="189">
@@ -5890,20 +5890,20 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.98</v>
+        <v>0.363</v>
       </c>
       <c r="E189" t="n">
-        <v>24.4</v>
+        <v>26.7</v>
       </c>
       <c r="F189" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G189" t="n">
-        <v>0.787</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="190">
@@ -5919,20 +5919,20 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.261</v>
+        <v>-0.334</v>
       </c>
       <c r="E190" t="n">
-        <v>26.4</v>
+        <v>29.3</v>
       </c>
       <c r="F190" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G190" t="n">
-        <v>0.454</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="191">
@@ -5948,20 +5948,20 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>-0.334</v>
+        <v>-1.422</v>
       </c>
       <c r="E191" t="n">
-        <v>29.4</v>
+        <v>30</v>
       </c>
       <c r="F191" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G191" t="n">
-        <v>0.143</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="192">
@@ -5977,49 +5977,49 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-1.046</v>
+        <v>-2.113</v>
       </c>
       <c r="E192" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F192" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.307</v>
+        <v>-1.003</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>-1.867</v>
+        <v>5.747</v>
       </c>
       <c r="E193" t="n">
-        <v>30.3</v>
+        <v>29.4</v>
       </c>
       <c r="F193" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.367</v>
       </c>
       <c r="G193" t="n">
-        <v>-0.821</v>
+        <v>3.739</v>
       </c>
     </row>
     <row r="194">
@@ -6035,20 +6035,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>5.577</v>
+        <v>3.151</v>
       </c>
       <c r="E194" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>3.575</v>
+        <v>2.171</v>
       </c>
     </row>
     <row r="195">
@@ -6064,20 +6064,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>2.951</v>
+        <v>3.178</v>
       </c>
       <c r="E195" t="n">
-        <v>29.4</v>
+        <v>25.8</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>2.03</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="196">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Vít Krejčí</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3.344</v>
+        <v>-0.958</v>
       </c>
       <c r="E196" t="n">
-        <v>25.9</v>
+        <v>20.6</v>
       </c>
       <c r="F196" t="n">
         <v>0.367</v>
       </c>
       <c r="G196" t="n">
-        <v>2.001</v>
+        <v>-0.254</v>
       </c>
     </row>
     <row r="197">
@@ -6122,20 +6122,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Vít Krejčí</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>-0.953</v>
+        <v>-1.408</v>
       </c>
       <c r="E197" t="n">
-        <v>20.6</v>
+        <v>31.7</v>
       </c>
       <c r="F197" t="n">
         <v>0.367</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.252</v>
+        <v>-0.6870000000000001</v>
       </c>
     </row>
     <row r="198">
@@ -6151,20 +6151,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-1.442</v>
+        <v>-2.331</v>
       </c>
       <c r="E198" t="n">
-        <v>31.8</v>
+        <v>24.3</v>
       </c>
       <c r="F198" t="n">
         <v>0.367</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.713</v>
+        <v>-0.996</v>
       </c>
     </row>
     <row r="199">
@@ -6180,20 +6180,20 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-1.928</v>
+        <v>-3.312</v>
       </c>
       <c r="E199" t="n">
-        <v>24.2</v>
+        <v>19.6</v>
       </c>
       <c r="F199" t="n">
         <v>0.367</v>
       </c>
       <c r="G199" t="n">
-        <v>-0.786</v>
+        <v>-1.203</v>
       </c>
     </row>
     <row r="200">
@@ -6209,49 +6209,49 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Caleb Love</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-3.362</v>
+        <v>-2.97</v>
       </c>
       <c r="E200" t="n">
-        <v>19.4</v>
+        <v>24.1</v>
       </c>
       <c r="F200" t="n">
         <v>0.367</v>
       </c>
       <c r="G200" t="n">
-        <v>-1.213</v>
+        <v>-1.306</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Caleb Love</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-2.965</v>
+        <v>2.774</v>
       </c>
       <c r="E201" t="n">
-        <v>24.1</v>
+        <v>29.4</v>
       </c>
       <c r="F201" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G201" t="n">
-        <v>-1.304</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="202">
@@ -6267,20 +6267,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>2.779</v>
+        <v>0.098</v>
       </c>
       <c r="E202" t="n">
-        <v>29.4</v>
+        <v>31.9</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>1.763</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="203">
@@ -6296,20 +6296,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.331</v>
+        <v>0.062</v>
       </c>
       <c r="E203" t="n">
-        <v>23.1</v>
+        <v>21.1</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.207</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="204">
@@ -6325,20 +6325,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.104</v>
+        <v>-1.59</v>
       </c>
       <c r="E204" t="n">
-        <v>31.9</v>
+        <v>22.6</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.135</v>
+        <v>-0.701</v>
       </c>
     </row>
     <row r="205">
@@ -6354,20 +6354,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-1.585</v>
+        <v>-1.268</v>
       </c>
       <c r="E205" t="n">
-        <v>22.6</v>
+        <v>33</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.699</v>
+        <v>-0.803</v>
       </c>
     </row>
     <row r="206">
@@ -6383,20 +6383,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Daeqwon Plowden</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-1.262</v>
+        <v>-3.468</v>
       </c>
       <c r="E206" t="n">
-        <v>33</v>
+        <v>28.8</v>
       </c>
       <c r="F206" t="n">
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.8</v>
+        <v>-2.021</v>
       </c>
     </row>
     <row r="207">
@@ -6412,20 +6412,20 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Daeqwon Plowden</t>
+          <t>DaQuan Jeffries</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-3.462</v>
+        <v>-3.998</v>
       </c>
       <c r="E207" t="n">
-        <v>28.8</v>
+        <v>26.4</v>
       </c>
       <c r="F207" t="n">
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-2.018</v>
+        <v>-2.141</v>
       </c>
     </row>
     <row r="208">
@@ -6441,49 +6441,49 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DaQuan Jeffries</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>-3.997</v>
+        <v>-4.277</v>
       </c>
       <c r="E208" t="n">
-        <v>26.4</v>
+        <v>33</v>
       </c>
       <c r="F208" t="n">
         <v>0.1</v>
       </c>
       <c r="G208" t="n">
-        <v>-2.141</v>
+        <v>-2.867</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-4.271</v>
+        <v>11.286</v>
       </c>
       <c r="E209" t="n">
-        <v>33</v>
+        <v>29.9</v>
       </c>
       <c r="F209" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G209" t="n">
-        <v>-2.864</v>
+        <v>7.627</v>
       </c>
     </row>
     <row r="210">
@@ -6499,20 +6499,20 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>10.978</v>
+        <v>4.226</v>
       </c>
       <c r="E210" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="F210" t="n">
         <v>0.967</v>
       </c>
       <c r="G210" t="n">
-        <v>7.36</v>
+        <v>3.093</v>
       </c>
     </row>
     <row r="211">
@@ -6528,20 +6528,20 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>4.323</v>
+        <v>3.702</v>
       </c>
       <c r="E211" t="n">
-        <v>29.1</v>
+        <v>29.9</v>
       </c>
       <c r="F211" t="n">
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>3.209</v>
+        <v>2.905</v>
       </c>
     </row>
     <row r="212">
@@ -6557,20 +6557,20 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>3.514</v>
+        <v>1.528</v>
       </c>
       <c r="E212" t="n">
-        <v>28.9</v>
+        <v>23.3</v>
       </c>
       <c r="F212" t="n">
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>2.7</v>
+        <v>1.211</v>
       </c>
     </row>
     <row r="213">
@@ -6586,20 +6586,20 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1.504</v>
+        <v>1.031</v>
       </c>
       <c r="E213" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="F213" t="n">
         <v>0.967</v>
       </c>
       <c r="G213" t="n">
-        <v>1.238</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="214">
@@ -6615,20 +6615,20 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1.211</v>
+        <v>0.293</v>
       </c>
       <c r="E214" t="n">
-        <v>22.1</v>
+        <v>27.2</v>
       </c>
       <c r="F214" t="n">
         <v>0.967</v>
       </c>
       <c r="G214" t="n">
-        <v>1.002</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="215">
@@ -6648,16 +6648,16 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.333</v>
+        <v>0.121</v>
       </c>
       <c r="E215" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="F215" t="n">
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="216">
@@ -6673,49 +6673,49 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.261</v>
+        <v>-0.922</v>
       </c>
       <c r="E216" t="n">
-        <v>26.7</v>
+        <v>20.7</v>
       </c>
       <c r="F216" t="n">
         <v>0.967</v>
       </c>
       <c r="G216" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>-0.9429999999999999</v>
+        <v>6.272</v>
       </c>
       <c r="E217" t="n">
-        <v>20.5</v>
+        <v>32.4</v>
       </c>
       <c r="F217" t="n">
-        <v>0.967</v>
+        <v>0.533</v>
       </c>
       <c r="G217" t="n">
-        <v>0.01</v>
+        <v>4.598</v>
       </c>
     </row>
     <row r="218">
@@ -6731,20 +6731,20 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>6.277</v>
+        <v>2.049</v>
       </c>
       <c r="E218" t="n">
-        <v>32.4</v>
+        <v>34.2</v>
       </c>
       <c r="F218" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G218" t="n">
-        <v>4.579</v>
+        <v>1.841</v>
       </c>
     </row>
     <row r="219">
@@ -6760,20 +6760,20 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2.054</v>
+        <v>3.457</v>
       </c>
       <c r="E219" t="n">
-        <v>34.2</v>
+        <v>20.4</v>
       </c>
       <c r="F219" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G219" t="n">
-        <v>1.821</v>
+        <v>1.695</v>
       </c>
     </row>
     <row r="220">
@@ -6789,20 +6789,20 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>3.462</v>
+        <v>1.715</v>
       </c>
       <c r="E220" t="n">
-        <v>20.4</v>
+        <v>31</v>
       </c>
       <c r="F220" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G220" t="n">
-        <v>1.683</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="221">
@@ -6818,20 +6818,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="E221" t="n">
-        <v>31</v>
+        <v>26.9</v>
       </c>
       <c r="F221" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G221" t="n">
-        <v>1.434</v>
+        <v>1.264</v>
       </c>
     </row>
     <row r="222">
@@ -6847,20 +6847,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1.729</v>
+        <v>0.858</v>
       </c>
       <c r="E222" t="n">
-        <v>26.9</v>
+        <v>23.5</v>
       </c>
       <c r="F222" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G222" t="n">
-        <v>1.248</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="223">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.863</v>
+        <v>-0.619</v>
       </c>
       <c r="E223" t="n">
-        <v>23.5</v>
+        <v>22.8</v>
       </c>
       <c r="F223" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G223" t="n">
-        <v>0.666</v>
+        <v>-0.041</v>
       </c>
     </row>
     <row r="224">
@@ -6905,49 +6905,49 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.614</v>
+        <v>-0.995</v>
       </c>
       <c r="E224" t="n">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
       <c r="F224" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.054</v>
+        <v>-0.212</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-0.99</v>
+        <v>1.155</v>
       </c>
       <c r="E225" t="n">
-        <v>22.1</v>
+        <v>26.5</v>
       </c>
       <c r="F225" t="n">
-        <v>0.5</v>
+        <v>0.133</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.225</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="226">
@@ -6963,20 +6963,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1.16</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E226" t="n">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="F226" t="n">
         <v>0.133</v>
       </c>
       <c r="G226" t="n">
-        <v>0.715</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="227">
@@ -6992,20 +6992,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Kevin Love</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.947</v>
+        <v>1.116</v>
       </c>
       <c r="E227" t="n">
-        <v>25.7</v>
+        <v>15.5</v>
       </c>
       <c r="F227" t="n">
         <v>0.133</v>
       </c>
       <c r="G227" t="n">
-        <v>0.577</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="228">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-0.352</v>
+        <v>-0.357</v>
       </c>
       <c r="E228" t="n">
         <v>26.7</v>
@@ -7034,7 +7034,7 @@
         <v>0.133</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.122</v>
+        <v>-0.124</v>
       </c>
     </row>
     <row r="229">
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-1.107</v>
+        <v>-1.112</v>
       </c>
       <c r="E229" t="n">
         <v>19</v>
@@ -7063,7 +7063,7 @@
         <v>0.133</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.386</v>
+        <v>-0.388</v>
       </c>
     </row>
     <row r="230">
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-1.484</v>
+        <v>-1.489</v>
       </c>
       <c r="E230" t="n">
         <v>20.6</v>
@@ -7092,7 +7092,7 @@
         <v>0.133</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.579</v>
+        <v>-0.582</v>
       </c>
     </row>
     <row r="231">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-1.835</v>
+        <v>-1.841</v>
       </c>
       <c r="E231" t="n">
         <v>30</v>
@@ -7121,7 +7121,7 @@
         <v>0.133</v>
       </c>
       <c r="G231" t="n">
-        <v>-1.064</v>
+        <v>-1.067</v>
       </c>
     </row>
     <row r="232">
@@ -7137,49 +7137,49 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Elijah Harkless</t>
+          <t>Cody Williams</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>-2.932</v>
+        <v>-3.915</v>
       </c>
       <c r="E232" t="n">
-        <v>27.3</v>
+        <v>32.5</v>
       </c>
       <c r="F232" t="n">
         <v>0.133</v>
       </c>
       <c r="G232" t="n">
-        <v>-1.593</v>
+        <v>-2.561</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-3.91</v>
+        <v>1.616</v>
       </c>
       <c r="E233" t="n">
-        <v>32.5</v>
+        <v>21.1</v>
       </c>
       <c r="F233" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G233" t="n">
-        <v>-2.558</v>
+        <v>0.726</v>
       </c>
     </row>
     <row r="234">
@@ -7195,20 +7195,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1.621</v>
+        <v>-0.882</v>
       </c>
       <c r="E234" t="n">
-        <v>21.1</v>
+        <v>27.1</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>0.728</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="235">
@@ -7224,20 +7224,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>-0.877</v>
+        <v>-1.499</v>
       </c>
       <c r="E235" t="n">
-        <v>27.1</v>
+        <v>24.6</v>
       </c>
       <c r="F235" t="n">
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>-0.477</v>
+        <v>-0.751</v>
       </c>
     </row>
     <row r="236">
@@ -7253,20 +7253,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-1.494</v>
+        <v>-1.933</v>
       </c>
       <c r="E236" t="n">
-        <v>24.6</v>
+        <v>21.4</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.748</v>
+        <v>-0.845</v>
       </c>
     </row>
     <row r="237">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-1.928</v>
+        <v>-1.934</v>
       </c>
       <c r="E237" t="n">
-        <v>21.4</v>
+        <v>27.2</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.843</v>
+        <v>-1.076</v>
       </c>
     </row>
     <row r="238">
@@ -7311,20 +7311,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bub Carrington</t>
+          <t>Jaden Hardy</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-1.929</v>
+        <v>-3.237</v>
       </c>
       <c r="E238" t="n">
-        <v>27.2</v>
+        <v>20.6</v>
       </c>
       <c r="F238" t="n">
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-1.073</v>
+        <v>-1.374</v>
       </c>
     </row>
     <row r="239">
@@ -7340,20 +7340,20 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Jaden Hardy</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-3.232</v>
+        <v>-3.194</v>
       </c>
       <c r="E239" t="n">
-        <v>20.6</v>
+        <v>22.5</v>
       </c>
       <c r="F239" t="n">
         <v>0.033</v>
       </c>
       <c r="G239" t="n">
-        <v>-1.372</v>
+        <v>-1.483</v>
       </c>
     </row>
     <row r="240">
@@ -7369,49 +7369,20 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Tre Johnson</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-3.189</v>
+        <v>-2.573</v>
       </c>
       <c r="E240" t="n">
-        <v>22.5</v>
+        <v>31.5</v>
       </c>
       <c r="F240" t="n">
         <v>0.033</v>
       </c>
       <c r="G240" t="n">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Will Riley</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>-2.568</v>
-      </c>
-      <c r="E241" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="F241" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G241" t="n">
-        <v>-1.663</v>
+        <v>-1.666</v>
       </c>
     </row>
   </sheetData>
@@ -7483,10 +7454,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>23.399</v>
+        <v>23.661</v>
       </c>
       <c r="F2" t="n">
-        <v>3.322</v>
+        <v>3.352</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7512,10 +7483,10 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>23.11</v>
+        <v>22.012</v>
       </c>
       <c r="F3" t="n">
-        <v>3.086</v>
+        <v>2.782</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7541,10 +7512,10 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>22.44</v>
+        <v>21.528</v>
       </c>
       <c r="F4" t="n">
-        <v>3.414</v>
+        <v>3.333</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7570,10 +7541,10 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>18.898</v>
+        <v>19.056</v>
       </c>
       <c r="F5" t="n">
-        <v>2.812</v>
+        <v>2.76</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -7599,10 +7570,10 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>18.7</v>
+        <v>18.679</v>
       </c>
       <c r="F6" t="n">
-        <v>2.506</v>
+        <v>2.501</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7628,10 +7599,10 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>17.663</v>
+        <v>17.638</v>
       </c>
       <c r="F7" t="n">
-        <v>2.594</v>
+        <v>2.589</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -7657,10 +7628,10 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>17.012</v>
+        <v>17.202</v>
       </c>
       <c r="F8" t="n">
-        <v>2.648</v>
+        <v>2.658</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -7686,10 +7657,10 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>16.137</v>
+        <v>16.378</v>
       </c>
       <c r="F9" t="n">
-        <v>2.466</v>
+        <v>2.473</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -7715,10 +7686,10 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>14.205</v>
+        <v>13.735</v>
       </c>
       <c r="F10" t="n">
-        <v>2.039</v>
+        <v>1.847</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -7744,10 +7715,10 @@
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>13.119</v>
+        <v>13.258</v>
       </c>
       <c r="F11" t="n">
-        <v>1.009</v>
+        <v>1.004</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -7773,10 +7744,10 @@
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>12.936</v>
+        <v>12.913</v>
       </c>
       <c r="F12" t="n">
-        <v>1.685</v>
+        <v>1.68</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -7790,26 +7761,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.889</v>
+        <v>11.698</v>
       </c>
       <c r="F13" t="n">
-        <v>1.646</v>
+        <v>1.759</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7819,26 +7790,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>11.681</v>
+        <v>11.277</v>
       </c>
       <c r="F14" t="n">
-        <v>1.777</v>
+        <v>1.808</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7848,26 +7819,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>11.152</v>
+        <v>10.089</v>
       </c>
       <c r="F15" t="n">
-        <v>1.813</v>
+        <v>1.148</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7877,26 +7848,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>9.215</v>
+        <v>8.725</v>
       </c>
       <c r="F16" t="n">
-        <v>1.287</v>
+        <v>1.152</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
     </row>
@@ -7906,26 +7877,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>8.75</v>
+        <v>8.321</v>
       </c>
       <c r="F17" t="n">
-        <v>1.157</v>
+        <v>1.155</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Devin Booker</t>
         </is>
       </c>
     </row>
@@ -7947,10 +7918,10 @@
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6.941</v>
+        <v>7.078</v>
       </c>
       <c r="F18" t="n">
-        <v>0.741</v>
+        <v>0.737</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -7976,10 +7947,10 @@
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>6.235</v>
+        <v>6.618</v>
       </c>
       <c r="F19" t="n">
-        <v>0.444</v>
+        <v>0.503</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -7993,26 +7964,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.157</v>
+        <v>5.985</v>
       </c>
       <c r="F20" t="n">
-        <v>0.802</v>
+        <v>0.707</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
     </row>
@@ -8022,26 +7993,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>4.589</v>
+        <v>5.251</v>
       </c>
       <c r="F21" t="n">
-        <v>0.419</v>
+        <v>0.855</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -8051,26 +8022,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.25</v>
+        <v>4.72</v>
       </c>
       <c r="F22" t="n">
-        <v>0.415</v>
+        <v>0.414</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
     </row>
@@ -8092,10 +8063,10 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>3.338</v>
+        <v>3.367</v>
       </c>
       <c r="F23" t="n">
-        <v>0.153</v>
+        <v>0.137</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -8109,26 +8080,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.413</v>
+        <v>0.572</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.232</v>
+        <v>-0.126</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
     </row>
@@ -8138,26 +8109,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.741</v>
+        <v>0.391</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.625</v>
+        <v>-0.237</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
     </row>
@@ -8167,26 +8138,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.439</v>
+        <v>-3.032</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.996</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
     </row>
@@ -8205,13 +8176,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.352</v>
+        <v>-5.048</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.29</v>
+        <v>-1.624</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -8225,26 +8196,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.01</v>
+        <v>-6.291</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.189</v>
+        <v>-1.941</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Myles Turner</t>
         </is>
       </c>
     </row>
@@ -8266,10 +8237,10 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.417</v>
+        <v>-6.57</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.42</v>
+        <v>-1.458</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -8295,10 +8266,10 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.928</v>
+        <v>-6.949</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.7</v>
+        <v>-1.704</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -8324,10 +8295,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.792</v>
+        <v>-7.809</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.049</v>
+        <v>-2.054</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G240"/>
+  <dimension ref="A1:G239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2033,20 +2033,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-1.598</v>
+        <v>-2.989</v>
       </c>
       <c r="E56" t="n">
-        <v>32.1</v>
+        <v>21.6</v>
       </c>
       <c r="F56" t="n">
         <v>0.233</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.914</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="57">
@@ -2062,20 +2062,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-2.989</v>
+        <v>-4.448</v>
       </c>
       <c r="E57" t="n">
-        <v>21.6</v>
+        <v>17.6</v>
       </c>
       <c r="F57" t="n">
         <v>0.233</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.24</v>
+        <v>-1.546</v>
       </c>
     </row>
     <row r="58">
@@ -3831,20 +3831,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Walter Clayton Jr.</t>
+          <t>Jahmai Mashack</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-2.2</v>
+        <v>-4.579</v>
       </c>
       <c r="E118" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="F118" t="n">
         <v>0.267</v>
       </c>
       <c r="G118" t="n">
-        <v>-1.037</v>
+        <v>-2.373</v>
       </c>
     </row>
     <row r="119">
@@ -3860,49 +3860,49 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jahmai Mashack</t>
+          <t>Rayan Rupert</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-4.579</v>
+        <v>-5.711</v>
       </c>
       <c r="E119" t="n">
-        <v>26.4</v>
+        <v>24.2</v>
       </c>
       <c r="F119" t="n">
         <v>0.267</v>
       </c>
       <c r="G119" t="n">
-        <v>-2.373</v>
+        <v>-2.742</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Rayan Rupert</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-5.711</v>
+        <v>2.969</v>
       </c>
       <c r="E120" t="n">
-        <v>24.2</v>
+        <v>35.5</v>
       </c>
       <c r="F120" t="n">
-        <v>0.267</v>
+        <v>0.6</v>
       </c>
       <c r="G120" t="n">
-        <v>-2.742</v>
+        <v>2.642</v>
       </c>
     </row>
     <row r="121">
@@ -3918,20 +3918,20 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2.969</v>
+        <v>2.271</v>
       </c>
       <c r="E121" t="n">
-        <v>35.5</v>
+        <v>32.7</v>
       </c>
       <c r="F121" t="n">
         <v>0.6</v>
       </c>
       <c r="G121" t="n">
-        <v>2.642</v>
+        <v>1.957</v>
       </c>
     </row>
     <row r="122">
@@ -3947,20 +3947,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2.271</v>
+        <v>2.288</v>
       </c>
       <c r="E122" t="n">
-        <v>32.7</v>
+        <v>23.1</v>
       </c>
       <c r="F122" t="n">
         <v>0.6</v>
       </c>
       <c r="G122" t="n">
-        <v>1.957</v>
+        <v>1.387</v>
       </c>
     </row>
     <row r="123">
@@ -3976,20 +3976,20 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.288</v>
+        <v>1.664</v>
       </c>
       <c r="E123" t="n">
-        <v>23.1</v>
+        <v>29</v>
       </c>
       <c r="F123" t="n">
         <v>0.6</v>
       </c>
       <c r="G123" t="n">
-        <v>1.387</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="124">
@@ -4005,20 +4005,20 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1.664</v>
+        <v>1.007</v>
       </c>
       <c r="E124" t="n">
-        <v>29</v>
+        <v>26.9</v>
       </c>
       <c r="F124" t="n">
         <v>0.6</v>
       </c>
       <c r="G124" t="n">
-        <v>1.368</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="125">
@@ -4034,20 +4034,20 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1.007</v>
+        <v>0.297</v>
       </c>
       <c r="E125" t="n">
-        <v>26.9</v>
+        <v>27.7</v>
       </c>
       <c r="F125" t="n">
         <v>0.6</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="126">
@@ -4063,20 +4063,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Kasparas Jakučionis</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.297</v>
+        <v>-0.624</v>
       </c>
       <c r="E126" t="n">
-        <v>27.7</v>
+        <v>19.3</v>
       </c>
       <c r="F126" t="n">
         <v>0.6</v>
       </c>
       <c r="G126" t="n">
-        <v>0.518</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="127">
@@ -4092,49 +4092,49 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kasparas Jakučionis</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>-0.624</v>
+        <v>-0.658</v>
       </c>
       <c r="E127" t="n">
-        <v>19.3</v>
+        <v>30.3</v>
       </c>
       <c r="F127" t="n">
         <v>0.6</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.01</v>
+        <v>-0.037</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-0.658</v>
+        <v>0.549</v>
       </c>
       <c r="E128" t="n">
-        <v>30.3</v>
+        <v>23.1</v>
       </c>
       <c r="F128" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.037</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="129">
@@ -4150,20 +4150,20 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.549</v>
+        <v>-0.41</v>
       </c>
       <c r="E129" t="n">
-        <v>23.1</v>
+        <v>24.9</v>
       </c>
       <c r="F129" t="n">
         <v>0.2</v>
       </c>
       <c r="G129" t="n">
-        <v>0.36</v>
+        <v>-0.109</v>
       </c>
     </row>
     <row r="130">
@@ -4179,20 +4179,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>-0.41</v>
+        <v>-0.972</v>
       </c>
       <c r="E130" t="n">
-        <v>24.9</v>
+        <v>20.9</v>
       </c>
       <c r="F130" t="n">
         <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>-0.109</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="131">
@@ -4208,20 +4208,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-0.972</v>
+        <v>-2.557</v>
       </c>
       <c r="E131" t="n">
-        <v>20.9</v>
+        <v>22.7</v>
       </c>
       <c r="F131" t="n">
         <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.336</v>
+        <v>-1.115</v>
       </c>
     </row>
     <row r="132">
@@ -4237,20 +4237,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-2.557</v>
+        <v>-3.635</v>
       </c>
       <c r="E132" t="n">
-        <v>22.7</v>
+        <v>16.3</v>
       </c>
       <c r="F132" t="n">
         <v>0.2</v>
       </c>
       <c r="G132" t="n">
-        <v>-1.115</v>
+        <v>-1.167</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-3.635</v>
+        <v>-2.662</v>
       </c>
       <c r="E133" t="n">
-        <v>16.3</v>
+        <v>22.8</v>
       </c>
       <c r="F133" t="n">
         <v>0.2</v>
       </c>
       <c r="G133" t="n">
-        <v>-1.167</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.662</v>
+        <v>-2.353</v>
       </c>
       <c r="E134" t="n">
-        <v>22.8</v>
+        <v>27.9</v>
       </c>
       <c r="F134" t="n">
         <v>0.2</v>
       </c>
       <c r="G134" t="n">
-        <v>-1.17</v>
+        <v>-1.254</v>
       </c>
     </row>
     <row r="135">
@@ -4324,49 +4324,49 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-2.353</v>
+        <v>-3.486</v>
       </c>
       <c r="E135" t="n">
-        <v>27.9</v>
+        <v>21.9</v>
       </c>
       <c r="F135" t="n">
         <v>0.2</v>
       </c>
       <c r="G135" t="n">
-        <v>-1.254</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-3.486</v>
+        <v>7.347</v>
       </c>
       <c r="E136" t="n">
-        <v>21.9</v>
+        <v>35.6</v>
       </c>
       <c r="F136" t="n">
-        <v>0.2</v>
+        <v>0.767</v>
       </c>
       <c r="G136" t="n">
-        <v>-1.5</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="137">
@@ -4382,20 +4382,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>7.347</v>
+        <v>3.98</v>
       </c>
       <c r="E137" t="n">
-        <v>35.6</v>
+        <v>31.6</v>
       </c>
       <c r="F137" t="n">
         <v>0.767</v>
       </c>
       <c r="G137" t="n">
-        <v>6.02</v>
+        <v>3.129</v>
       </c>
     </row>
     <row r="138">
@@ -4411,20 +4411,20 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3.98</v>
+        <v>2.998</v>
       </c>
       <c r="E138" t="n">
-        <v>31.6</v>
+        <v>28</v>
       </c>
       <c r="F138" t="n">
         <v>0.767</v>
       </c>
       <c r="G138" t="n">
-        <v>3.129</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="139">
@@ -4440,20 +4440,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2.998</v>
+        <v>1.655</v>
       </c>
       <c r="E139" t="n">
-        <v>28</v>
+        <v>30.2</v>
       </c>
       <c r="F139" t="n">
         <v>0.767</v>
       </c>
       <c r="G139" t="n">
-        <v>2.2</v>
+        <v>1.524</v>
       </c>
     </row>
     <row r="140">
@@ -4469,20 +4469,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1.655</v>
+        <v>1.713</v>
       </c>
       <c r="E140" t="n">
-        <v>30.2</v>
+        <v>25.1</v>
       </c>
       <c r="F140" t="n">
         <v>0.767</v>
       </c>
       <c r="G140" t="n">
-        <v>1.524</v>
+        <v>1.299</v>
       </c>
     </row>
     <row r="141">
@@ -4498,20 +4498,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1.713</v>
+        <v>0.863</v>
       </c>
       <c r="E141" t="n">
-        <v>25.1</v>
+        <v>31.2</v>
       </c>
       <c r="F141" t="n">
         <v>0.767</v>
       </c>
       <c r="G141" t="n">
-        <v>1.299</v>
+        <v>1.061</v>
       </c>
     </row>
     <row r="142">
@@ -4527,20 +4527,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.863</v>
+        <v>1.581</v>
       </c>
       <c r="E142" t="n">
-        <v>31.2</v>
+        <v>20.2</v>
       </c>
       <c r="F142" t="n">
         <v>0.767</v>
       </c>
       <c r="G142" t="n">
-        <v>1.061</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="143">
@@ -4556,49 +4556,49 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1.581</v>
+        <v>-0.351</v>
       </c>
       <c r="E143" t="n">
-        <v>20.2</v>
+        <v>17.9</v>
       </c>
       <c r="F143" t="n">
         <v>0.767</v>
       </c>
       <c r="G143" t="n">
-        <v>0.99</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>-0.351</v>
+        <v>4.897</v>
       </c>
       <c r="E144" t="n">
-        <v>17.9</v>
+        <v>34.2</v>
       </c>
       <c r="F144" t="n">
-        <v>0.767</v>
+        <v>0.3</v>
       </c>
       <c r="G144" t="n">
-        <v>0.155</v>
+        <v>3.699</v>
       </c>
     </row>
     <row r="145">
@@ -4614,20 +4614,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4.897</v>
+        <v>4.866</v>
       </c>
       <c r="E145" t="n">
-        <v>34.2</v>
+        <v>29.2</v>
       </c>
       <c r="F145" t="n">
         <v>0.3</v>
       </c>
       <c r="G145" t="n">
-        <v>3.699</v>
+        <v>3.146</v>
       </c>
     </row>
     <row r="146">
@@ -4643,20 +4643,20 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4.866</v>
+        <v>2.286</v>
       </c>
       <c r="E146" t="n">
-        <v>29.2</v>
+        <v>32.1</v>
       </c>
       <c r="F146" t="n">
         <v>0.3</v>
       </c>
       <c r="G146" t="n">
-        <v>3.146</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="147">
@@ -4672,20 +4672,20 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2.286</v>
+        <v>0.971</v>
       </c>
       <c r="E147" t="n">
-        <v>32.1</v>
+        <v>19.7</v>
       </c>
       <c r="F147" t="n">
         <v>0.3</v>
       </c>
       <c r="G147" t="n">
-        <v>1.73</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="148">
@@ -4701,20 +4701,20 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.971</v>
+        <v>-0.235</v>
       </c>
       <c r="E148" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="F148" t="n">
         <v>0.3</v>
       </c>
       <c r="G148" t="n">
-        <v>0.521</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="149">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-0.235</v>
+        <v>-1.442</v>
       </c>
       <c r="E149" t="n">
-        <v>19.9</v>
+        <v>21.5</v>
       </c>
       <c r="F149" t="n">
         <v>0.3</v>
       </c>
       <c r="G149" t="n">
-        <v>0.027</v>
+        <v>-0.512</v>
       </c>
     </row>
     <row r="150">
@@ -4759,20 +4759,20 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-1.442</v>
+        <v>-2.674</v>
       </c>
       <c r="E150" t="n">
-        <v>21.5</v>
+        <v>19.9</v>
       </c>
       <c r="F150" t="n">
         <v>0.3</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.512</v>
+        <v>-0.984</v>
       </c>
     </row>
     <row r="151">
@@ -4788,49 +4788,49 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-2.674</v>
+        <v>-3.014</v>
       </c>
       <c r="E151" t="n">
-        <v>19.9</v>
+        <v>29</v>
       </c>
       <c r="F151" t="n">
         <v>0.3</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.984</v>
+        <v>-1.642</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-3.014</v>
+        <v>6.606</v>
       </c>
       <c r="E152" t="n">
-        <v>29</v>
+        <v>36.1</v>
       </c>
       <c r="F152" t="n">
-        <v>0.3</v>
+        <v>0.867</v>
       </c>
       <c r="G152" t="n">
-        <v>-1.642</v>
+        <v>5.622</v>
       </c>
     </row>
     <row r="153">
@@ -4846,20 +4846,20 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>6.606</v>
+        <v>2.979</v>
       </c>
       <c r="E153" t="n">
-        <v>36.1</v>
+        <v>30.9</v>
       </c>
       <c r="F153" t="n">
         <v>0.867</v>
       </c>
       <c r="G153" t="n">
-        <v>5.622</v>
+        <v>2.479</v>
       </c>
     </row>
     <row r="154">
@@ -4875,20 +4875,20 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>4.167</v>
+        <v>3.097</v>
       </c>
       <c r="E154" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="F154" t="n">
         <v>0.867</v>
       </c>
       <c r="G154" t="n">
-        <v>3.131</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="155">
@@ -4904,20 +4904,20 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2.979</v>
+        <v>1.601</v>
       </c>
       <c r="E155" t="n">
-        <v>30.9</v>
+        <v>34</v>
       </c>
       <c r="F155" t="n">
         <v>0.867</v>
       </c>
       <c r="G155" t="n">
-        <v>2.479</v>
+        <v>1.746</v>
       </c>
     </row>
     <row r="156">
@@ -4933,20 +4933,20 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3.097</v>
+        <v>3.046</v>
       </c>
       <c r="E156" t="n">
-        <v>29.6</v>
+        <v>19.7</v>
       </c>
       <c r="F156" t="n">
         <v>0.867</v>
       </c>
       <c r="G156" t="n">
-        <v>2.444</v>
+        <v>1.604</v>
       </c>
     </row>
     <row r="157">
@@ -4962,20 +4962,20 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1.601</v>
+        <v>0.553</v>
       </c>
       <c r="E157" t="n">
-        <v>34</v>
+        <v>28.9</v>
       </c>
       <c r="F157" t="n">
         <v>0.867</v>
       </c>
       <c r="G157" t="n">
-        <v>1.746</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="158">
@@ -4991,20 +4991,20 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3.046</v>
+        <v>-1.338</v>
       </c>
       <c r="E158" t="n">
-        <v>19.7</v>
+        <v>24.8</v>
       </c>
       <c r="F158" t="n">
         <v>0.867</v>
       </c>
       <c r="G158" t="n">
-        <v>1.604</v>
+        <v>-0.244</v>
       </c>
     </row>
     <row r="159">
@@ -5020,49 +5020,49 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Jordan Clarkson</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.553</v>
+        <v>-3.401</v>
       </c>
       <c r="E159" t="n">
-        <v>28.9</v>
+        <v>15.9</v>
       </c>
       <c r="F159" t="n">
         <v>0.867</v>
       </c>
       <c r="G159" t="n">
-        <v>0.856</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-1.338</v>
+        <v>14.848</v>
       </c>
       <c r="E160" t="n">
-        <v>24.8</v>
+        <v>34.3</v>
       </c>
       <c r="F160" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.244</v>
+        <v>11.332</v>
       </c>
     </row>
     <row r="161">
@@ -5078,20 +5078,20 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>14.848</v>
+        <v>3.938</v>
       </c>
       <c r="E161" t="n">
-        <v>34.3</v>
+        <v>29.9</v>
       </c>
       <c r="F161" t="n">
         <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>11.332</v>
+        <v>3.077</v>
       </c>
     </row>
     <row r="162">
@@ -5107,20 +5107,20 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>3.938</v>
+        <v>3.205</v>
       </c>
       <c r="E162" t="n">
-        <v>29.9</v>
+        <v>22.4</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>3.077</v>
+        <v>1.962</v>
       </c>
     </row>
     <row r="163">
@@ -5136,20 +5136,20 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>3.205</v>
+        <v>1.751</v>
       </c>
       <c r="E163" t="n">
-        <v>22.4</v>
+        <v>27.2</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1.962</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="164">
@@ -5165,20 +5165,20 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1.751</v>
+        <v>1.798</v>
       </c>
       <c r="E164" t="n">
-        <v>27.2</v>
+        <v>26.3</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>1.56</v>
+        <v>1.535</v>
       </c>
     </row>
     <row r="165">
@@ -5194,20 +5194,20 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.798</v>
+        <v>1.204</v>
       </c>
       <c r="E165" t="n">
-        <v>26.3</v>
+        <v>21.6</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>1.535</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="166">
@@ -5223,20 +5223,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1.204</v>
+        <v>-0.046</v>
       </c>
       <c r="E166" t="n">
-        <v>21.6</v>
+        <v>25.1</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.993</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="167">
@@ -5252,49 +5252,49 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-0.046</v>
+        <v>-4.619</v>
       </c>
       <c r="E167" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0.499</v>
+        <v>-1.902</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>-4.619</v>
+        <v>3.312</v>
       </c>
       <c r="E168" t="n">
-        <v>25.2</v>
+        <v>35.4</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G168" t="n">
-        <v>-1.902</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="169">
@@ -5310,20 +5310,20 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3.312</v>
+        <v>3.176</v>
       </c>
       <c r="E169" t="n">
-        <v>35.4</v>
+        <v>34.2</v>
       </c>
       <c r="F169" t="n">
         <v>0.433</v>
       </c>
       <c r="G169" t="n">
-        <v>2.765</v>
+        <v>2.569</v>
       </c>
     </row>
     <row r="170">
@@ -5339,20 +5339,20 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3.176</v>
+        <v>3.158</v>
       </c>
       <c r="E170" t="n">
-        <v>34.2</v>
+        <v>30.2</v>
       </c>
       <c r="F170" t="n">
         <v>0.433</v>
       </c>
       <c r="G170" t="n">
-        <v>2.569</v>
+        <v>2.257</v>
       </c>
     </row>
     <row r="171">
@@ -5368,20 +5368,20 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3.158</v>
+        <v>1.991</v>
       </c>
       <c r="E171" t="n">
-        <v>30.2</v>
+        <v>28.8</v>
       </c>
       <c r="F171" t="n">
         <v>0.433</v>
       </c>
       <c r="G171" t="n">
-        <v>2.257</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="172">
@@ -5397,20 +5397,20 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1.991</v>
+        <v>-0.67</v>
       </c>
       <c r="E172" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="F172" t="n">
         <v>0.433</v>
       </c>
       <c r="G172" t="n">
-        <v>1.457</v>
+        <v>-0.145</v>
       </c>
     </row>
     <row r="173">
@@ -5426,20 +5426,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-0.67</v>
+        <v>-1.201</v>
       </c>
       <c r="E173" t="n">
-        <v>29.3</v>
+        <v>29.6</v>
       </c>
       <c r="F173" t="n">
         <v>0.433</v>
       </c>
       <c r="G173" t="n">
-        <v>-0.145</v>
+        <v>-0.474</v>
       </c>
     </row>
     <row r="174">
@@ -5455,20 +5455,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-1.201</v>
+        <v>-1.598</v>
       </c>
       <c r="E174" t="n">
-        <v>29.6</v>
+        <v>20.6</v>
       </c>
       <c r="F174" t="n">
         <v>0.433</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.474</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="175">
@@ -5484,49 +5484,49 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Orlando Robinson</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-1.598</v>
+        <v>-2.275</v>
       </c>
       <c r="E175" t="n">
-        <v>20.6</v>
+        <v>22.2</v>
       </c>
       <c r="F175" t="n">
         <v>0.433</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.5</v>
+        <v>-0.851</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Orlando Robinson</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-2.275</v>
+        <v>9.177</v>
       </c>
       <c r="E176" t="n">
-        <v>22.2</v>
+        <v>37</v>
       </c>
       <c r="F176" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.851</v>
+        <v>7.431</v>
       </c>
     </row>
     <row r="177">
@@ -5542,20 +5542,20 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>9.177</v>
+        <v>5.549</v>
       </c>
       <c r="E177" t="n">
-        <v>37</v>
+        <v>33.5</v>
       </c>
       <c r="F177" t="n">
         <v>0.467</v>
       </c>
       <c r="G177" t="n">
-        <v>7.431</v>
+        <v>4.199</v>
       </c>
     </row>
     <row r="178">
@@ -5571,20 +5571,20 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5.549</v>
+        <v>1.83</v>
       </c>
       <c r="E178" t="n">
-        <v>33.5</v>
+        <v>32.7</v>
       </c>
       <c r="F178" t="n">
         <v>0.467</v>
       </c>
       <c r="G178" t="n">
-        <v>4.199</v>
+        <v>1.564</v>
       </c>
     </row>
     <row r="179">
@@ -5600,20 +5600,20 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1.83</v>
+        <v>0.758</v>
       </c>
       <c r="E179" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="F179" t="n">
         <v>0.467</v>
       </c>
       <c r="G179" t="n">
-        <v>1.564</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="180">
@@ -5629,20 +5629,20 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.758</v>
+        <v>-0.187</v>
       </c>
       <c r="E180" t="n">
-        <v>32.9</v>
+        <v>32.2</v>
       </c>
       <c r="F180" t="n">
         <v>0.467</v>
       </c>
       <c r="G180" t="n">
-        <v>0.839</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="181">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Eric Gordon</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-0.187</v>
+        <v>-0.769</v>
       </c>
       <c r="E181" t="n">
-        <v>32.2</v>
+        <v>23</v>
       </c>
       <c r="F181" t="n">
         <v>0.467</v>
       </c>
       <c r="G181" t="n">
-        <v>0.188</v>
+        <v>-0.144</v>
       </c>
     </row>
     <row r="182">
@@ -5687,20 +5687,20 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Eric Gordon</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-0.769</v>
+        <v>-1.343</v>
       </c>
       <c r="E182" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="F182" t="n">
         <v>0.467</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.144</v>
+        <v>-0.417</v>
       </c>
     </row>
     <row r="183">
@@ -5716,49 +5716,49 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-1.343</v>
+        <v>-1.571</v>
       </c>
       <c r="E183" t="n">
-        <v>22.9</v>
+        <v>32.5</v>
       </c>
       <c r="F183" t="n">
         <v>0.467</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.417</v>
+        <v>-0.747</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>-1.571</v>
+        <v>4.901</v>
       </c>
       <c r="E184" t="n">
-        <v>32.5</v>
+        <v>33.4</v>
       </c>
       <c r="F184" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.747</v>
+        <v>3.761</v>
       </c>
     </row>
     <row r="185">
@@ -5774,20 +5774,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4.901</v>
+        <v>4.182</v>
       </c>
       <c r="E185" t="n">
-        <v>33.4</v>
+        <v>29.5</v>
       </c>
       <c r="F185" t="n">
         <v>0.5</v>
       </c>
       <c r="G185" t="n">
-        <v>3.761</v>
+        <v>2.874</v>
       </c>
     </row>
     <row r="186">
@@ -5803,20 +5803,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>4.182</v>
+        <v>2.739</v>
       </c>
       <c r="E186" t="n">
-        <v>29.5</v>
+        <v>28.9</v>
       </c>
       <c r="F186" t="n">
         <v>0.5</v>
       </c>
       <c r="G186" t="n">
-        <v>2.874</v>
+        <v>1.952</v>
       </c>
     </row>
     <row r="187">
@@ -5832,20 +5832,20 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2.739</v>
+        <v>0.921</v>
       </c>
       <c r="E187" t="n">
-        <v>28.9</v>
+        <v>24.7</v>
       </c>
       <c r="F187" t="n">
         <v>0.5</v>
       </c>
       <c r="G187" t="n">
-        <v>1.952</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="188">
@@ -5861,20 +5861,20 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.921</v>
+        <v>0.363</v>
       </c>
       <c r="E188" t="n">
-        <v>24.7</v>
+        <v>26.7</v>
       </c>
       <c r="F188" t="n">
         <v>0.5</v>
       </c>
       <c r="G188" t="n">
-        <v>0.731</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="189">
@@ -5890,20 +5890,20 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.363</v>
+        <v>-0.334</v>
       </c>
       <c r="E189" t="n">
-        <v>26.7</v>
+        <v>29.3</v>
       </c>
       <c r="F189" t="n">
         <v>0.5</v>
       </c>
       <c r="G189" t="n">
-        <v>0.481</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="190">
@@ -5919,20 +5919,20 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>-0.334</v>
+        <v>-1.422</v>
       </c>
       <c r="E190" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F190" t="n">
         <v>0.5</v>
       </c>
       <c r="G190" t="n">
-        <v>0.101</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="191">
@@ -5948,49 +5948,49 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>-1.422</v>
+        <v>-2.113</v>
       </c>
       <c r="E191" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="F191" t="n">
         <v>0.5</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.576</v>
+        <v>-1.003</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-2.113</v>
+        <v>5.747</v>
       </c>
       <c r="E192" t="n">
-        <v>29.8</v>
+        <v>29.4</v>
       </c>
       <c r="F192" t="n">
-        <v>0.5</v>
+        <v>0.367</v>
       </c>
       <c r="G192" t="n">
-        <v>-1.003</v>
+        <v>3.739</v>
       </c>
     </row>
     <row r="193">
@@ -6006,20 +6006,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>5.747</v>
+        <v>3.151</v>
       </c>
       <c r="E193" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="F193" t="n">
         <v>0.367</v>
       </c>
       <c r="G193" t="n">
-        <v>3.739</v>
+        <v>2.171</v>
       </c>
     </row>
     <row r="194">
@@ -6035,20 +6035,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3.151</v>
+        <v>3.178</v>
       </c>
       <c r="E194" t="n">
-        <v>29.6</v>
+        <v>25.8</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>2.171</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="195">
@@ -6064,20 +6064,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Vít Krejčí</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3.178</v>
+        <v>-0.958</v>
       </c>
       <c r="E195" t="n">
-        <v>25.8</v>
+        <v>20.6</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>1.903</v>
+        <v>-0.254</v>
       </c>
     </row>
     <row r="196">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Vít Krejčí</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>-0.958</v>
+        <v>-1.408</v>
       </c>
       <c r="E196" t="n">
-        <v>20.6</v>
+        <v>31.7</v>
       </c>
       <c r="F196" t="n">
         <v>0.367</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.254</v>
+        <v>-0.6870000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -6122,20 +6122,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>-1.408</v>
+        <v>-2.331</v>
       </c>
       <c r="E197" t="n">
-        <v>31.7</v>
+        <v>24.3</v>
       </c>
       <c r="F197" t="n">
         <v>0.367</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.996</v>
       </c>
     </row>
     <row r="198">
@@ -6151,20 +6151,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-2.331</v>
+        <v>-3.312</v>
       </c>
       <c r="E198" t="n">
-        <v>24.3</v>
+        <v>19.6</v>
       </c>
       <c r="F198" t="n">
         <v>0.367</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.996</v>
+        <v>-1.203</v>
       </c>
     </row>
     <row r="199">
@@ -6180,49 +6180,49 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Caleb Love</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-3.312</v>
+        <v>-2.97</v>
       </c>
       <c r="E199" t="n">
-        <v>19.6</v>
+        <v>24.1</v>
       </c>
       <c r="F199" t="n">
         <v>0.367</v>
       </c>
       <c r="G199" t="n">
-        <v>-1.203</v>
+        <v>-1.306</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Caleb Love</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-2.97</v>
+        <v>2.774</v>
       </c>
       <c r="E200" t="n">
-        <v>24.1</v>
+        <v>29.4</v>
       </c>
       <c r="F200" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G200" t="n">
-        <v>-1.306</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="201">
@@ -6238,20 +6238,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2.774</v>
+        <v>0.098</v>
       </c>
       <c r="E201" t="n">
-        <v>29.4</v>
+        <v>31.9</v>
       </c>
       <c r="F201" t="n">
         <v>0.1</v>
       </c>
       <c r="G201" t="n">
-        <v>1.76</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="202">
@@ -6267,20 +6267,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.098</v>
+        <v>0.062</v>
       </c>
       <c r="E202" t="n">
-        <v>31.9</v>
+        <v>21.1</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>0.132</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -6296,20 +6296,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.062</v>
+        <v>-1.59</v>
       </c>
       <c r="E203" t="n">
-        <v>21.1</v>
+        <v>22.6</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.701</v>
       </c>
     </row>
     <row r="204">
@@ -6325,20 +6325,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>-1.59</v>
+        <v>-1.268</v>
       </c>
       <c r="E204" t="n">
-        <v>22.6</v>
+        <v>33</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.701</v>
+        <v>-0.803</v>
       </c>
     </row>
     <row r="205">
@@ -6354,20 +6354,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Daeqwon Plowden</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-1.268</v>
+        <v>-3.468</v>
       </c>
       <c r="E205" t="n">
-        <v>33</v>
+        <v>28.8</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.803</v>
+        <v>-2.021</v>
       </c>
     </row>
     <row r="206">
@@ -6383,20 +6383,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Daeqwon Plowden</t>
+          <t>DaQuan Jeffries</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-3.468</v>
+        <v>-3.998</v>
       </c>
       <c r="E206" t="n">
-        <v>28.8</v>
+        <v>26.4</v>
       </c>
       <c r="F206" t="n">
         <v>0.1</v>
       </c>
       <c r="G206" t="n">
-        <v>-2.021</v>
+        <v>-2.141</v>
       </c>
     </row>
     <row r="207">
@@ -6412,49 +6412,49 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>DaQuan Jeffries</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-3.998</v>
+        <v>-4.277</v>
       </c>
       <c r="E207" t="n">
-        <v>26.4</v>
+        <v>33</v>
       </c>
       <c r="F207" t="n">
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-2.141</v>
+        <v>-2.867</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>-4.277</v>
+        <v>11.286</v>
       </c>
       <c r="E208" t="n">
-        <v>33</v>
+        <v>29.9</v>
       </c>
       <c r="F208" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G208" t="n">
-        <v>-2.867</v>
+        <v>7.627</v>
       </c>
     </row>
     <row r="209">
@@ -6470,20 +6470,20 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>11.286</v>
+        <v>4.226</v>
       </c>
       <c r="E209" t="n">
-        <v>29.9</v>
+        <v>28.6</v>
       </c>
       <c r="F209" t="n">
         <v>0.967</v>
       </c>
       <c r="G209" t="n">
-        <v>7.627</v>
+        <v>3.093</v>
       </c>
     </row>
     <row r="210">
@@ -6499,20 +6499,20 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>4.226</v>
+        <v>3.702</v>
       </c>
       <c r="E210" t="n">
-        <v>28.6</v>
+        <v>29.9</v>
       </c>
       <c r="F210" t="n">
         <v>0.967</v>
       </c>
       <c r="G210" t="n">
-        <v>3.093</v>
+        <v>2.905</v>
       </c>
     </row>
     <row r="211">
@@ -6528,20 +6528,20 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3.702</v>
+        <v>1.528</v>
       </c>
       <c r="E211" t="n">
-        <v>29.9</v>
+        <v>23.3</v>
       </c>
       <c r="F211" t="n">
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>2.905</v>
+        <v>1.211</v>
       </c>
     </row>
     <row r="212">
@@ -6557,20 +6557,20 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1.528</v>
+        <v>1.031</v>
       </c>
       <c r="E212" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="F212" t="n">
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>1.211</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="213">
@@ -6586,20 +6586,20 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1.031</v>
+        <v>0.293</v>
       </c>
       <c r="E213" t="n">
-        <v>22.9</v>
+        <v>27.2</v>
       </c>
       <c r="F213" t="n">
         <v>0.967</v>
       </c>
       <c r="G213" t="n">
-        <v>0.954</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="214">
@@ -6615,20 +6615,20 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.293</v>
+        <v>0.121</v>
       </c>
       <c r="E214" t="n">
-        <v>27.2</v>
+        <v>29.9</v>
       </c>
       <c r="F214" t="n">
         <v>0.967</v>
       </c>
       <c r="G214" t="n">
-        <v>0.715</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="215">
@@ -6644,49 +6644,49 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.121</v>
+        <v>-0.922</v>
       </c>
       <c r="E215" t="n">
-        <v>29.9</v>
+        <v>20.7</v>
       </c>
       <c r="F215" t="n">
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>0.678</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>-0.922</v>
+        <v>6.272</v>
       </c>
       <c r="E216" t="n">
-        <v>20.7</v>
+        <v>32.4</v>
       </c>
       <c r="F216" t="n">
-        <v>0.967</v>
+        <v>0.533</v>
       </c>
       <c r="G216" t="n">
-        <v>0.019</v>
+        <v>4.598</v>
       </c>
     </row>
     <row r="217">
@@ -6702,20 +6702,20 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>6.272</v>
+        <v>2.049</v>
       </c>
       <c r="E217" t="n">
-        <v>32.4</v>
+        <v>34.2</v>
       </c>
       <c r="F217" t="n">
         <v>0.533</v>
       </c>
       <c r="G217" t="n">
-        <v>4.598</v>
+        <v>1.841</v>
       </c>
     </row>
     <row r="218">
@@ -6731,20 +6731,20 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>2.049</v>
+        <v>3.457</v>
       </c>
       <c r="E218" t="n">
-        <v>34.2</v>
+        <v>20.4</v>
       </c>
       <c r="F218" t="n">
         <v>0.533</v>
       </c>
       <c r="G218" t="n">
-        <v>1.841</v>
+        <v>1.695</v>
       </c>
     </row>
     <row r="219">
@@ -6760,20 +6760,20 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>3.457</v>
+        <v>1.715</v>
       </c>
       <c r="E219" t="n">
-        <v>20.4</v>
+        <v>31</v>
       </c>
       <c r="F219" t="n">
         <v>0.533</v>
       </c>
       <c r="G219" t="n">
-        <v>1.695</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="220">
@@ -6789,20 +6789,20 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1.715</v>
+        <v>1.724</v>
       </c>
       <c r="E220" t="n">
-        <v>31</v>
+        <v>26.9</v>
       </c>
       <c r="F220" t="n">
         <v>0.533</v>
       </c>
       <c r="G220" t="n">
-        <v>1.452</v>
+        <v>1.264</v>
       </c>
     </row>
     <row r="221">
@@ -6818,20 +6818,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.724</v>
+        <v>0.858</v>
       </c>
       <c r="E221" t="n">
-        <v>26.9</v>
+        <v>23.5</v>
       </c>
       <c r="F221" t="n">
         <v>0.533</v>
       </c>
       <c r="G221" t="n">
-        <v>1.264</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="222">
@@ -6847,20 +6847,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.858</v>
+        <v>-0.619</v>
       </c>
       <c r="E222" t="n">
-        <v>23.5</v>
+        <v>22.8</v>
       </c>
       <c r="F222" t="n">
         <v>0.533</v>
       </c>
       <c r="G222" t="n">
-        <v>0.68</v>
+        <v>-0.041</v>
       </c>
     </row>
     <row r="223">
@@ -6876,49 +6876,49 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>-0.619</v>
+        <v>-0.995</v>
       </c>
       <c r="E223" t="n">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
       <c r="F223" t="n">
         <v>0.533</v>
       </c>
       <c r="G223" t="n">
-        <v>-0.041</v>
+        <v>-0.212</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.995</v>
+        <v>1.155</v>
       </c>
       <c r="E224" t="n">
-        <v>22.1</v>
+        <v>26.5</v>
       </c>
       <c r="F224" t="n">
-        <v>0.533</v>
+        <v>0.133</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.212</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="225">
@@ -6934,20 +6934,20 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1.155</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E225" t="n">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="F225" t="n">
         <v>0.133</v>
       </c>
       <c r="G225" t="n">
-        <v>0.712</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="226">
@@ -6963,20 +6963,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Kevin Love</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.116</v>
       </c>
       <c r="E226" t="n">
-        <v>25.7</v>
+        <v>15.5</v>
       </c>
       <c r="F226" t="n">
         <v>0.133</v>
       </c>
       <c r="G226" t="n">
-        <v>0.575</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="227">
@@ -6992,20 +6992,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Kevin Love</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1.116</v>
+        <v>-0.357</v>
       </c>
       <c r="E227" t="n">
-        <v>15.5</v>
+        <v>26.7</v>
       </c>
       <c r="F227" t="n">
         <v>0.133</v>
       </c>
       <c r="G227" t="n">
-        <v>0.403</v>
+        <v>-0.124</v>
       </c>
     </row>
     <row r="228">
@@ -7021,20 +7021,20 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-0.357</v>
+        <v>-1.112</v>
       </c>
       <c r="E228" t="n">
-        <v>26.7</v>
+        <v>19</v>
       </c>
       <c r="F228" t="n">
         <v>0.133</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.124</v>
+        <v>-0.388</v>
       </c>
     </row>
     <row r="229">
@@ -7050,20 +7050,20 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>Svi Mykhailiuk</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-1.112</v>
+        <v>-1.489</v>
       </c>
       <c r="E229" t="n">
-        <v>19</v>
+        <v>20.6</v>
       </c>
       <c r="F229" t="n">
         <v>0.133</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.388</v>
+        <v>-0.582</v>
       </c>
     </row>
     <row r="230">
@@ -7079,20 +7079,20 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Svi Mykhailiuk</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-1.489</v>
+        <v>-1.841</v>
       </c>
       <c r="E230" t="n">
-        <v>20.6</v>
+        <v>30</v>
       </c>
       <c r="F230" t="n">
         <v>0.133</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.582</v>
+        <v>-1.067</v>
       </c>
     </row>
     <row r="231">
@@ -7108,49 +7108,49 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Cody Williams</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-1.841</v>
+        <v>-3.915</v>
       </c>
       <c r="E231" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="F231" t="n">
         <v>0.133</v>
       </c>
       <c r="G231" t="n">
-        <v>-1.067</v>
+        <v>-2.561</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>-3.915</v>
+        <v>1.616</v>
       </c>
       <c r="E232" t="n">
-        <v>32.5</v>
+        <v>21.1</v>
       </c>
       <c r="F232" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G232" t="n">
-        <v>-2.561</v>
+        <v>0.726</v>
       </c>
     </row>
     <row r="233">
@@ -7166,20 +7166,20 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1.616</v>
+        <v>-0.882</v>
       </c>
       <c r="E233" t="n">
-        <v>21.1</v>
+        <v>27.1</v>
       </c>
       <c r="F233" t="n">
         <v>0.033</v>
       </c>
       <c r="G233" t="n">
-        <v>0.726</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="234">
@@ -7195,20 +7195,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>-0.882</v>
+        <v>-1.499</v>
       </c>
       <c r="E234" t="n">
-        <v>27.1</v>
+        <v>24.6</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>-0.48</v>
+        <v>-0.751</v>
       </c>
     </row>
     <row r="235">
@@ -7224,20 +7224,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>-1.499</v>
+        <v>-1.933</v>
       </c>
       <c r="E235" t="n">
-        <v>24.6</v>
+        <v>21.4</v>
       </c>
       <c r="F235" t="n">
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>-0.751</v>
+        <v>-0.845</v>
       </c>
     </row>
     <row r="236">
@@ -7253,20 +7253,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-1.933</v>
+        <v>-1.934</v>
       </c>
       <c r="E236" t="n">
-        <v>21.4</v>
+        <v>27.2</v>
       </c>
       <c r="F236" t="n">
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.845</v>
+        <v>-1.076</v>
       </c>
     </row>
     <row r="237">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bub Carrington</t>
+          <t>Jaden Hardy</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-1.934</v>
+        <v>-3.237</v>
       </c>
       <c r="E237" t="n">
-        <v>27.2</v>
+        <v>20.6</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-1.076</v>
+        <v>-1.374</v>
       </c>
     </row>
     <row r="238">
@@ -7311,20 +7311,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Jaden Hardy</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-3.237</v>
+        <v>-3.194</v>
       </c>
       <c r="E238" t="n">
-        <v>20.6</v>
+        <v>22.5</v>
       </c>
       <c r="F238" t="n">
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-1.374</v>
+        <v>-1.483</v>
       </c>
     </row>
     <row r="239">
@@ -7340,48 +7340,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Tre Johnson</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-3.194</v>
+        <v>-2.573</v>
       </c>
       <c r="E239" t="n">
-        <v>22.5</v>
+        <v>31.5</v>
       </c>
       <c r="F239" t="n">
         <v>0.033</v>
       </c>
       <c r="G239" t="n">
-        <v>-1.483</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Will Riley</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>-2.573</v>
-      </c>
-      <c r="E240" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="F240" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G240" t="n">
         <v>-1.666</v>
       </c>
     </row>
@@ -7587,26 +7558,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>17.638</v>
+        <v>17.202</v>
       </c>
       <c r="F7" t="n">
-        <v>2.589</v>
+        <v>2.658</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7616,26 +7587,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>17.202</v>
+        <v>16.378</v>
       </c>
       <c r="F8" t="n">
-        <v>2.658</v>
+        <v>2.473</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
     </row>
@@ -7645,26 +7616,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>16.378</v>
+        <v>13.735</v>
       </c>
       <c r="F9" t="n">
-        <v>2.473</v>
+        <v>1.847</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7674,26 +7645,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>13.735</v>
+        <v>13.667</v>
       </c>
       <c r="F10" t="n">
-        <v>1.847</v>
+        <v>1.643</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -8121,10 +8092,10 @@
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>0.391</v>
+        <v>-0.241</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.237</v>
+        <v>-0.594</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -8176,13 +8147,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.048</v>
+        <v>-4.011</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.624</v>
+        <v>-1.528</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -3483,20 +3483,20 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>15.68</v>
+        <v>5.471</v>
       </c>
       <c r="E106" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="F106" t="n">
         <v>0.667</v>
       </c>
       <c r="G106" t="n">
-        <v>12.823</v>
+        <v>4.844</v>
       </c>
     </row>
     <row r="107">
@@ -3512,20 +3512,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5.471</v>
+        <v>5.956</v>
       </c>
       <c r="E107" t="n">
-        <v>37.9</v>
+        <v>34</v>
       </c>
       <c r="F107" t="n">
         <v>0.667</v>
       </c>
       <c r="G107" t="n">
-        <v>4.844</v>
+        <v>4.689</v>
       </c>
     </row>
     <row r="108">
@@ -3541,20 +3541,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5.956</v>
+        <v>2.306</v>
       </c>
       <c r="E108" t="n">
-        <v>34</v>
+        <v>20.7</v>
       </c>
       <c r="F108" t="n">
         <v>0.667</v>
       </c>
       <c r="G108" t="n">
-        <v>4.689</v>
+        <v>1.279</v>
       </c>
     </row>
     <row r="109">
@@ -3570,20 +3570,20 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.306</v>
+        <v>0.724</v>
       </c>
       <c r="E109" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="F109" t="n">
         <v>0.667</v>
       </c>
       <c r="G109" t="n">
-        <v>1.279</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="110">
@@ -3599,20 +3599,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.724</v>
+        <v>0.236</v>
       </c>
       <c r="E110" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="F110" t="n">
         <v>0.667</v>
       </c>
       <c r="G110" t="n">
-        <v>0.625</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="111">
@@ -3628,20 +3628,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.236</v>
+        <v>-1.181</v>
       </c>
       <c r="E111" t="n">
-        <v>25.6</v>
+        <v>19.5</v>
       </c>
       <c r="F111" t="n">
         <v>0.667</v>
       </c>
       <c r="G111" t="n">
-        <v>0.482</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="112">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Dalton Knecht</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-1.181</v>
+        <v>-1.862</v>
       </c>
       <c r="E112" t="n">
-        <v>19.5</v>
+        <v>15.8</v>
       </c>
       <c r="F112" t="n">
         <v>0.667</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.209</v>
+        <v>-0.393</v>
       </c>
     </row>
     <row r="113">
@@ -6006,20 +6006,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3.151</v>
+        <v>6.038</v>
       </c>
       <c r="E193" t="n">
-        <v>29.6</v>
+        <v>18.5</v>
       </c>
       <c r="F193" t="n">
         <v>0.367</v>
       </c>
       <c r="G193" t="n">
-        <v>2.171</v>
+        <v>2.468</v>
       </c>
     </row>
     <row r="194">
@@ -6035,20 +6035,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3.178</v>
+        <v>3.151</v>
       </c>
       <c r="E194" t="n">
-        <v>25.8</v>
+        <v>29.6</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>1.903</v>
+        <v>2.171</v>
       </c>
     </row>
     <row r="195">
@@ -6064,20 +6064,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Vít Krejčí</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>-0.958</v>
+        <v>3.178</v>
       </c>
       <c r="E195" t="n">
-        <v>20.6</v>
+        <v>25.8</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>-0.254</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="196">
@@ -7413,26 +7413,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>23.661</v>
+        <v>22.012</v>
       </c>
       <c r="F2" t="n">
-        <v>3.352</v>
+        <v>2.782</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
     </row>
@@ -7442,26 +7442,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>22.012</v>
+        <v>21.528</v>
       </c>
       <c r="F3" t="n">
-        <v>2.782</v>
+        <v>3.333</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7471,26 +7471,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>21.528</v>
+        <v>19.056</v>
       </c>
       <c r="F4" t="n">
-        <v>3.333</v>
+        <v>2.76</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
     </row>
@@ -7500,26 +7500,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>19.056</v>
+        <v>18.679</v>
       </c>
       <c r="F5" t="n">
-        <v>2.76</v>
+        <v>2.501</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
     </row>
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>18.679</v>
+        <v>17.202</v>
       </c>
       <c r="F6" t="n">
-        <v>2.501</v>
+        <v>2.658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7558,26 +7558,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>17.202</v>
+        <v>16.378</v>
       </c>
       <c r="F7" t="n">
-        <v>2.658</v>
+        <v>2.473</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
     </row>
@@ -7587,26 +7587,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>16.378</v>
+        <v>13.735</v>
       </c>
       <c r="F8" t="n">
-        <v>2.473</v>
+        <v>1.847</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7616,26 +7616,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>13.735</v>
+        <v>13.667</v>
       </c>
       <c r="F9" t="n">
-        <v>1.847</v>
+        <v>1.643</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -7645,26 +7645,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>13.667</v>
+        <v>13.258</v>
       </c>
       <c r="F10" t="n">
-        <v>1.643</v>
+        <v>1.004</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7674,26 +7674,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>13.258</v>
+        <v>12.913</v>
       </c>
       <c r="F11" t="n">
-        <v>1.004</v>
+        <v>1.68</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7703,26 +7703,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>12.913</v>
+        <v>11.698</v>
       </c>
       <c r="F12" t="n">
-        <v>1.68</v>
+        <v>1.759</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7732,26 +7732,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.698</v>
+        <v>11.277</v>
       </c>
       <c r="F13" t="n">
-        <v>1.759</v>
+        <v>1.808</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>11.277</v>
+        <v>10.445</v>
       </c>
       <c r="F14" t="n">
-        <v>1.808</v>
+        <v>1.159</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
     </row>
@@ -7935,26 +7935,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.985</v>
+        <v>6.089</v>
       </c>
       <c r="F20" t="n">
-        <v>0.707</v>
+        <v>1.012</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
     </row>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>5.251</v>
+        <v>5.985</v>
       </c>
       <c r="F21" t="n">
-        <v>0.855</v>
+        <v>0.707</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.72</v>
+        <v>5.251</v>
       </c>
       <c r="F22" t="n">
-        <v>0.414</v>
+        <v>0.855</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>3.367</v>
+        <v>4.72</v>
       </c>
       <c r="F23" t="n">
-        <v>0.137</v>
+        <v>0.414</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
     </row>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -1279,20 +1279,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.956</v>
+        <v>1.127</v>
       </c>
       <c r="E30" t="n">
-        <v>17.4</v>
+        <v>27.7</v>
       </c>
       <c r="F30" t="n">
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>0.961</v>
+        <v>1.053</v>
       </c>
     </row>
     <row r="31">
@@ -1337,20 +1337,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sion James</t>
+          <t>Grant Williams</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-3.672</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="F32" t="n">
         <v>0.7</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.155</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="33">
@@ -1366,20 +1366,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tre Mann</t>
+          <t>Sion James</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-5.662</v>
+        <v>-3.672</v>
       </c>
       <c r="E33" t="n">
-        <v>16.2</v>
+        <v>18.7</v>
       </c>
       <c r="F33" t="n">
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.671</v>
+        <v>-1.155</v>
       </c>
     </row>
     <row r="34">
@@ -3019,20 +3019,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>T.J. McConnell</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3.023</v>
+        <v>5.65</v>
       </c>
       <c r="E90" t="n">
-        <v>31.6</v>
+        <v>17.6</v>
       </c>
       <c r="F90" t="n">
         <v>0.167</v>
       </c>
       <c r="G90" t="n">
-        <v>2.099</v>
+        <v>2.135</v>
       </c>
     </row>
     <row r="91">
@@ -3048,20 +3048,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1.928</v>
+        <v>3.023</v>
       </c>
       <c r="E91" t="n">
-        <v>23</v>
+        <v>31.6</v>
       </c>
       <c r="F91" t="n">
         <v>0.167</v>
       </c>
       <c r="G91" t="n">
-        <v>1.005</v>
+        <v>2.099</v>
       </c>
     </row>
     <row r="92">
@@ -3077,20 +3077,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.995</v>
+        <v>1.928</v>
       </c>
       <c r="E92" t="n">
-        <v>17.4</v>
+        <v>23</v>
       </c>
       <c r="F92" t="n">
         <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>0.784</v>
+        <v>1.005</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Obi Toppin</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.819</v>
+        <v>1.995</v>
       </c>
       <c r="E93" t="n">
-        <v>16.9</v>
+        <v>17.4</v>
       </c>
       <c r="F93" t="n">
         <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>0.698</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="94">
@@ -7703,26 +7703,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>11.698</v>
+        <v>11.855</v>
       </c>
       <c r="F12" t="n">
-        <v>1.759</v>
+        <v>1.666</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7732,26 +7732,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.277</v>
+        <v>11.698</v>
       </c>
       <c r="F13" t="n">
-        <v>1.808</v>
+        <v>1.759</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7761,26 +7761,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>10.445</v>
+        <v>11.277</v>
       </c>
       <c r="F14" t="n">
-        <v>1.159</v>
+        <v>1.808</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>10.089</v>
+        <v>10.445</v>
       </c>
       <c r="F15" t="n">
-        <v>1.148</v>
+        <v>1.159</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
     </row>
@@ -8063,14 +8063,14 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.572</v>
+        <v>2.009</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.126</v>
+        <v>0.353</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>T.J. McConnell</t>
         </is>
       </c>
     </row>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -3077,20 +3077,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.928</v>
+        <v>2.823</v>
       </c>
       <c r="E92" t="n">
-        <v>23</v>
+        <v>28.7</v>
       </c>
       <c r="F92" t="n">
         <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>1.005</v>
+        <v>1.788</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.995</v>
+        <v>1.928</v>
       </c>
       <c r="E93" t="n">
-        <v>17.4</v>
+        <v>23</v>
       </c>
       <c r="F93" t="n">
         <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>0.784</v>
+        <v>1.005</v>
       </c>
     </row>
     <row r="94">
@@ -8063,10 +8063,10 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>2.009</v>
+        <v>3.013</v>
       </c>
       <c r="F24" t="n">
-        <v>0.353</v>
+        <v>0.457</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.335000000000001</v>
+        <v>8.276999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G2" t="n">
-        <v>6.341</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.525</v>
+        <v>3.685</v>
       </c>
       <c r="E3" t="n">
-        <v>33.4</v>
+        <v>33.7</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.845</v>
+        <v>3.012</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.549</v>
+        <v>2.557</v>
       </c>
       <c r="E4" t="n">
-        <v>31.9</v>
+        <v>32.4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.073</v>
+        <v>2.131</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.543</v>
+        <v>2.549</v>
       </c>
       <c r="E5" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.886</v>
+        <v>1.928</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>2.043</v>
       </c>
       <c r="E6" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1.684</v>
+        <v>1.636</v>
       </c>
     </row>
     <row r="7">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.602</v>
+        <v>-0.601</v>
       </c>
       <c r="E7" t="n">
         <v>15.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.012</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.632</v>
+        <v>-1.572</v>
       </c>
       <c r="E8" t="n">
-        <v>19.1</v>
+        <v>18.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.424</v>
+        <v>-0.374</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.141</v>
+        <v>-1.914</v>
       </c>
       <c r="E9" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.658</v>
+        <v>-0.544</v>
       </c>
     </row>
     <row r="10">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.377</v>
+        <v>6.578</v>
       </c>
       <c r="E10" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="F10" t="n">
         <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.249</v>
+        <v>5.431</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.406</v>
+        <v>5.562</v>
       </c>
       <c r="E11" t="n">
         <v>34.7</v>
@@ -741,7 +741,7 @@
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>4.565</v>
+        <v>4.675</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.892</v>
+        <v>4.743</v>
       </c>
       <c r="E12" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="F12" t="n">
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>4.118</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.978</v>
+        <v>4.021</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="F13" t="n">
         <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.253</v>
+        <v>3.308</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.127</v>
+        <v>2.237</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>27.2</v>
       </c>
       <c r="F14" t="n">
         <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.636</v>
+        <v>1.775</v>
       </c>
     </row>
     <row r="15">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.891</v>
+        <v>-0.616</v>
       </c>
       <c r="E16" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="F16" t="n">
         <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.548</v>
+        <v>-1.39</v>
       </c>
       <c r="E17" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="F17" t="n">
         <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.36</v>
+        <v>-0.268</v>
       </c>
     </row>
     <row r="18">
@@ -931,20 +931,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Josh Minott</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.04</v>
+        <v>1.966</v>
       </c>
       <c r="E18" t="n">
-        <v>23.1</v>
+        <v>18.4</v>
       </c>
       <c r="F18" t="n">
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>1.497</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="19">
@@ -960,20 +960,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Josh Minott</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.019</v>
+        <v>-2.247</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>21.4</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>0.737</v>
+        <v>-0.974</v>
       </c>
     </row>
     <row r="20">
@@ -989,20 +989,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ziaire Williams</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.889</v>
+        <v>-2.113</v>
       </c>
       <c r="E20" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.389</v>
+        <v>-0.987</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2</v>
+        <v>-4.703</v>
       </c>
       <c r="E21" t="n">
-        <v>23.9</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.962</v>
+        <v>-1.548</v>
       </c>
     </row>
     <row r="22">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Jalen Wilson</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.343</v>
+        <v>-5.138</v>
       </c>
       <c r="E22" t="n">
-        <v>21.4</v>
+        <v>15.3</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.017</v>
+        <v>-1.619</v>
       </c>
     </row>
     <row r="23">
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4.904</v>
+        <v>-4.901</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="F23" t="n">
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.318</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="24">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-5.28</v>
+        <v>-5.327</v>
       </c>
       <c r="E24" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="F24" t="n">
         <v>0.067</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.447</v>
+        <v>-2.459</v>
       </c>
     </row>
     <row r="25">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-6.075</v>
+        <v>-6.129</v>
       </c>
       <c r="E25" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="F25" t="n">
         <v>0.067</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.91</v>
+        <v>-2.939</v>
       </c>
     </row>
     <row r="26">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7.11</v>
+        <v>7.206</v>
       </c>
       <c r="E26" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="F26" t="n">
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>4.617</v>
+        <v>4.628</v>
       </c>
     </row>
     <row r="27">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.387</v>
+        <v>4.368</v>
       </c>
       <c r="E27" t="n">
         <v>29.9</v>
@@ -1205,7 +1205,7 @@
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>3.166</v>
+        <v>3.158</v>
       </c>
     </row>
     <row r="28">
@@ -1225,16 +1225,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.871</v>
+        <v>2.844</v>
       </c>
       <c r="E28" t="n">
-        <v>30.4</v>
+        <v>31.1</v>
       </c>
       <c r="F28" t="n">
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>2.265</v>
+        <v>2.294</v>
       </c>
     </row>
     <row r="29">
@@ -1254,16 +1254,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.419</v>
+        <v>1.548</v>
       </c>
       <c r="E29" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="F29" t="n">
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.283</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="30">
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.775</v>
+        <v>0.819</v>
       </c>
       <c r="E31" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="F31" t="n">
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0.623</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="32">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-3.672</v>
+        <v>-3.621</v>
       </c>
       <c r="E33" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="F33" t="n">
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.155</v>
+        <v>-1.132</v>
       </c>
     </row>
     <row r="34">
@@ -1399,16 +1399,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.79</v>
+        <v>5.795</v>
       </c>
       <c r="E34" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="F34" t="n">
         <v>0.333</v>
       </c>
       <c r="G34" t="n">
-        <v>4.349</v>
+        <v>4.413</v>
       </c>
     </row>
     <row r="35">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.064</v>
+        <v>3.917</v>
       </c>
       <c r="E35" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="F35" t="n">
         <v>0.333</v>
       </c>
       <c r="G35" t="n">
-        <v>2.628</v>
+        <v>2.526</v>
       </c>
     </row>
     <row r="36">
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.312</v>
+        <v>2.386</v>
       </c>
       <c r="E36" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="F36" t="n">
         <v>0.333</v>
       </c>
       <c r="G36" t="n">
-        <v>1.335</v>
+        <v>1.414</v>
       </c>
     </row>
     <row r="37">
@@ -1486,16 +1486,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.391</v>
+        <v>1.481</v>
       </c>
       <c r="E37" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="F37" t="n">
         <v>0.333</v>
       </c>
       <c r="G37" t="n">
-        <v>1.185</v>
+        <v>1.229</v>
       </c>
     </row>
     <row r="38">
@@ -1515,16 +1515,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-0.34</v>
+        <v>-0.538</v>
       </c>
       <c r="E38" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="F38" t="n">
         <v>0.333</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.004</v>
+        <v>-0.102</v>
       </c>
     </row>
     <row r="39">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-2.063</v>
+        <v>-1.942</v>
       </c>
       <c r="E39" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="F39" t="n">
         <v>0.333</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.885</v>
+        <v>-0.8129999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1569,20 +1569,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Patrick Williams</t>
+          <t>Isaac Okoro</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-4.31</v>
+        <v>-3.348</v>
       </c>
       <c r="E40" t="n">
-        <v>22.5</v>
+        <v>30.4</v>
       </c>
       <c r="F40" t="n">
         <v>0.333</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.865</v>
+        <v>-1.909</v>
       </c>
     </row>
     <row r="41">
@@ -1598,20 +1598,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-3.532</v>
+        <v>-6.208</v>
       </c>
       <c r="E41" t="n">
-        <v>30.4</v>
+        <v>21.8</v>
       </c>
       <c r="F41" t="n">
         <v>0.333</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.023</v>
+        <v>-2.673</v>
       </c>
     </row>
     <row r="42">
@@ -1685,20 +1685,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Max Strus</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.566</v>
+        <v>1.468</v>
       </c>
       <c r="E44" t="n">
-        <v>30.1</v>
+        <v>27</v>
       </c>
       <c r="F44" t="n">
         <v>0.733</v>
       </c>
       <c r="G44" t="n">
-        <v>3.327</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="45">
@@ -1714,20 +1714,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Craig Porter Jr.</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3.945</v>
+        <v>1.918</v>
       </c>
       <c r="E45" t="n">
-        <v>27.5</v>
+        <v>17.7</v>
       </c>
       <c r="F45" t="n">
         <v>0.733</v>
       </c>
       <c r="G45" t="n">
-        <v>2.684</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="46">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.468</v>
+        <v>-0.598</v>
       </c>
       <c r="E46" t="n">
-        <v>27</v>
+        <v>20.4</v>
       </c>
       <c r="F46" t="n">
         <v>0.733</v>
       </c>
       <c r="G46" t="n">
-        <v>1.238</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="47">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.882</v>
+        <v>-0.848</v>
       </c>
       <c r="E47" t="n">
-        <v>28.9</v>
+        <v>26.8</v>
       </c>
       <c r="F47" t="n">
         <v>0.733</v>
       </c>
       <c r="G47" t="n">
-        <v>0.972</v>
+        <v>-0.064</v>
       </c>
     </row>
     <row r="48">
@@ -1801,20 +1801,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Lonzo Ball</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.599</v>
+        <v>-1.356</v>
       </c>
       <c r="E48" t="n">
-        <v>20.4</v>
+        <v>17.6</v>
       </c>
       <c r="F48" t="n">
         <v>0.733</v>
       </c>
       <c r="G48" t="n">
-        <v>0.057</v>
+        <v>-0.228</v>
       </c>
     </row>
     <row r="49">
@@ -1830,20 +1830,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Keon Ellis</t>
+          <t>Nae'Qwan Tomlin</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.849</v>
+        <v>-1.528</v>
       </c>
       <c r="E49" t="n">
-        <v>26.8</v>
+        <v>16.2</v>
       </c>
       <c r="F49" t="n">
         <v>0.733</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.065</v>
+        <v>-0.268</v>
       </c>
     </row>
     <row r="50">
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.368</v>
+        <v>2.309</v>
       </c>
       <c r="E50" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="F50" t="n">
         <v>0.233</v>
       </c>
       <c r="G50" t="n">
-        <v>1.8</v>
+        <v>1.746</v>
       </c>
     </row>
     <row r="51">
@@ -1892,16 +1892,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.614</v>
+        <v>1.544</v>
       </c>
       <c r="E51" t="n">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="F51" t="n">
         <v>0.233</v>
       </c>
       <c r="G51" t="n">
-        <v>0.919</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="52">
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.177</v>
+        <v>1.112</v>
       </c>
       <c r="E52" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="F52" t="n">
         <v>0.233</v>
       </c>
       <c r="G52" t="n">
-        <v>0.656</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="53">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.619</v>
+        <v>0.634</v>
       </c>
       <c r="E53" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="F53" t="n">
         <v>0.233</v>
       </c>
       <c r="G53" t="n">
-        <v>0.531</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="54">
@@ -1979,16 +1979,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1.436</v>
+        <v>-1.679</v>
       </c>
       <c r="E54" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="F54" t="n">
         <v>0.233</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.525</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="55">
@@ -2004,20 +2004,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>P.J. Washington</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.654</v>
+        <v>-1.598</v>
       </c>
       <c r="E55" t="n">
-        <v>28.3</v>
+        <v>32.1</v>
       </c>
       <c r="F55" t="n">
         <v>0.233</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.836</v>
+        <v>-0.914</v>
       </c>
     </row>
     <row r="56">
@@ -2033,20 +2033,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-2.989</v>
+        <v>-1.895</v>
       </c>
       <c r="E56" t="n">
-        <v>21.6</v>
+        <v>27.8</v>
       </c>
       <c r="F56" t="n">
         <v>0.233</v>
       </c>
       <c r="G56" t="n">
-        <v>-1.24</v>
+        <v>-0.962</v>
       </c>
     </row>
     <row r="57">
@@ -2062,20 +2062,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-4.448</v>
+        <v>-3.158</v>
       </c>
       <c r="E57" t="n">
-        <v>17.6</v>
+        <v>21.4</v>
       </c>
       <c r="F57" t="n">
         <v>0.233</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.546</v>
+        <v>-1.306</v>
       </c>
     </row>
     <row r="58">
@@ -2095,16 +2095,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>18.168</v>
+        <v>17.996</v>
       </c>
       <c r="E58" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="F58" t="n">
         <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>14.294</v>
+        <v>14.079</v>
       </c>
     </row>
     <row r="59">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>9.108000000000001</v>
+        <v>9.311999999999999</v>
       </c>
       <c r="E59" t="n">
         <v>35.2</v>
@@ -2133,7 +2133,7 @@
         <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>7.289</v>
+        <v>7.435</v>
       </c>
     </row>
     <row r="60">
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.732</v>
+        <v>2.376</v>
       </c>
       <c r="E60" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="F60" t="n">
         <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>2.047</v>
+        <v>1.836</v>
       </c>
     </row>
     <row r="61">
@@ -2182,16 +2182,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.481</v>
+        <v>0.446</v>
       </c>
       <c r="E61" t="n">
-        <v>25.4</v>
+        <v>24</v>
       </c>
       <c r="F61" t="n">
         <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>0.697</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="62">
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-1.042</v>
+        <v>-0.828</v>
       </c>
       <c r="E62" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="F62" t="n">
         <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.124</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="63">
@@ -2269,16 +2269,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-2.049</v>
+        <v>-1.872</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="F64" t="n">
         <v>0.833</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2298,16 +2298,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-2.791</v>
+        <v>-2.691</v>
       </c>
       <c r="E65" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="F65" t="n">
         <v>0.833</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.885</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="66">
@@ -2327,16 +2327,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.59</v>
+        <v>5.518</v>
       </c>
       <c r="E66" t="n">
-        <v>28</v>
+        <v>29.5</v>
       </c>
       <c r="F66" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>3.802</v>
+        <v>3.968</v>
       </c>
     </row>
     <row r="67">
@@ -2356,16 +2356,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.481</v>
+        <v>1.655</v>
       </c>
       <c r="E67" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F67" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>1.327</v>
+        <v>1.434</v>
       </c>
     </row>
     <row r="68">
@@ -2385,16 +2385,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-0.022</v>
+        <v>-0.036</v>
       </c>
       <c r="E68" t="n">
-        <v>28.3</v>
+        <v>26.7</v>
       </c>
       <c r="F68" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.537</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="69">
@@ -2417,13 +2417,13 @@
         <v>-0.057</v>
       </c>
       <c r="E69" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="F69" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>0.477</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="70">
@@ -2439,20 +2439,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.102</v>
+        <v>-0.227</v>
       </c>
       <c r="E70" t="n">
-        <v>22.8</v>
+        <v>30.7</v>
       </c>
       <c r="F70" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0.394</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="71">
@@ -2468,20 +2468,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-0.424</v>
+        <v>0.001</v>
       </c>
       <c r="E71" t="n">
-        <v>29.3</v>
+        <v>23.1</v>
       </c>
       <c r="F71" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0.311</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="72">
@@ -2530,16 +2530,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-1.525</v>
+        <v>-1.608</v>
       </c>
       <c r="E73" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.237</v>
+        <v>-0.268</v>
       </c>
     </row>
     <row r="74">
@@ -2565,10 +2565,10 @@
         <v>22.1</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G74" t="n">
-        <v>2.274</v>
+        <v>2.289</v>
       </c>
     </row>
     <row r="75">
@@ -2594,10 +2594,10 @@
         <v>32.2</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G75" t="n">
-        <v>1.599</v>
+        <v>1.621</v>
       </c>
     </row>
     <row r="76">
@@ -2623,10 +2623,10 @@
         <v>22.1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G76" t="n">
-        <v>1.515</v>
+        <v>1.531</v>
       </c>
     </row>
     <row r="77">
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.601</v>
+        <v>0.602</v>
       </c>
       <c r="E77" t="n">
         <v>32.8</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G77" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="78">
@@ -2681,10 +2681,10 @@
         <v>22.1</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.052</v>
+        <v>-0.037</v>
       </c>
     </row>
     <row r="79">
@@ -2710,10 +2710,10 @@
         <v>29.9</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.102</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="80">
@@ -2739,10 +2739,10 @@
         <v>25.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.253</v>
+        <v>-0.236</v>
       </c>
     </row>
     <row r="81">
@@ -2768,10 +2768,10 @@
         <v>24.6</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.414</v>
+        <v>-0.397</v>
       </c>
     </row>
     <row r="82">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6.624</v>
+        <v>6.619</v>
       </c>
       <c r="E82" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="F82" t="n">
         <v>0.8</v>
       </c>
       <c r="G82" t="n">
-        <v>5.524</v>
+        <v>5.499</v>
       </c>
     </row>
     <row r="83">
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6.194</v>
+        <v>6.397</v>
       </c>
       <c r="E83" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="F83" t="n">
         <v>0.8</v>
       </c>
       <c r="G83" t="n">
-        <v>4.794</v>
+        <v>4.881</v>
       </c>
     </row>
     <row r="84">
@@ -2849,16 +2849,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3.757</v>
+        <v>3.838</v>
       </c>
       <c r="E84" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="F84" t="n">
         <v>0.8</v>
       </c>
       <c r="G84" t="n">
-        <v>3.671</v>
+        <v>3.713</v>
       </c>
     </row>
     <row r="85">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.231</v>
+        <v>3.582</v>
       </c>
       <c r="E85" t="n">
         <v>30.1</v>
@@ -2887,7 +2887,7 @@
         <v>0.8</v>
       </c>
       <c r="G85" t="n">
-        <v>2.528</v>
+        <v>2.748</v>
       </c>
     </row>
     <row r="86">
@@ -2907,16 +2907,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-0.439</v>
+        <v>-0.477</v>
       </c>
       <c r="E86" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="F86" t="n">
         <v>0.8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.275</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="87">
@@ -2936,16 +2936,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-1.654</v>
+        <v>-1.862</v>
       </c>
       <c r="E87" t="n">
-        <v>25.1</v>
+        <v>24.5</v>
       </c>
       <c r="F87" t="n">
         <v>0.8</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.447</v>
+        <v>-0.541</v>
       </c>
     </row>
     <row r="88">
@@ -2974,7 +2974,7 @@
         <v>0.8</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.718</v>
+        <v>-0.717</v>
       </c>
     </row>
     <row r="89">
@@ -2994,16 +2994,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-6.724</v>
+        <v>-6.802</v>
       </c>
       <c r="E89" t="n">
-        <v>19.2</v>
+        <v>18.3</v>
       </c>
       <c r="F89" t="n">
         <v>0.8</v>
       </c>
       <c r="G89" t="n">
-        <v>-2.369</v>
+        <v>-2.285</v>
       </c>
     </row>
     <row r="90">
@@ -3019,20 +3019,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>T.J. McConnell</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>5.65</v>
+        <v>2.129</v>
       </c>
       <c r="E90" t="n">
-        <v>17.6</v>
+        <v>22.3</v>
       </c>
       <c r="F90" t="n">
         <v>0.167</v>
       </c>
       <c r="G90" t="n">
-        <v>2.135</v>
+        <v>1.066</v>
       </c>
     </row>
     <row r="91">
@@ -3048,20 +3048,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3.023</v>
+        <v>2.25</v>
       </c>
       <c r="E91" t="n">
-        <v>31.6</v>
+        <v>17</v>
       </c>
       <c r="F91" t="n">
         <v>0.167</v>
       </c>
       <c r="G91" t="n">
-        <v>2.099</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="92">
@@ -3077,20 +3077,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2.823</v>
+        <v>2.005</v>
       </c>
       <c r="E92" t="n">
-        <v>28.7</v>
+        <v>16.4</v>
       </c>
       <c r="F92" t="n">
         <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>1.788</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3106,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.928</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="E93" t="n">
-        <v>23</v>
+        <v>18.4</v>
       </c>
       <c r="F93" t="n">
         <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>1.005</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="94">
@@ -3135,20 +3135,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-0.703</v>
+        <v>-1.79</v>
       </c>
       <c r="E94" t="n">
-        <v>18.8</v>
+        <v>22.2</v>
       </c>
       <c r="F94" t="n">
         <v>0.167</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.21</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="95">
@@ -3164,20 +3164,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.152</v>
+        <v>-2.965</v>
       </c>
       <c r="E95" t="n">
-        <v>22</v>
+        <v>17.9</v>
       </c>
       <c r="F95" t="n">
         <v>0.167</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.911</v>
+        <v>-1.042</v>
       </c>
     </row>
     <row r="96">
@@ -3197,16 +3197,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.952</v>
+        <v>-2.789</v>
       </c>
       <c r="E96" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="F96" t="n">
         <v>0.167</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.17</v>
+        <v>-1.089</v>
       </c>
     </row>
     <row r="97">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-3.965</v>
+        <v>-3.628</v>
       </c>
       <c r="E97" t="n">
         <v>21.8</v>
@@ -3235,7 +3235,7 @@
         <v>0.167</v>
       </c>
       <c r="G97" t="n">
-        <v>-1.723</v>
+        <v>-1.572</v>
       </c>
     </row>
     <row r="98">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.624</v>
+        <v>11.625</v>
       </c>
       <c r="E98" t="n">
         <v>30.4</v>
@@ -3264,7 +3264,7 @@
         <v>0.633</v>
       </c>
       <c r="G98" t="n">
-        <v>7.756</v>
+        <v>7.757</v>
       </c>
     </row>
     <row r="99">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-0.284</v>
+        <v>-0.283</v>
       </c>
       <c r="E103" t="n">
         <v>27.5</v>
@@ -3467,7 +3467,7 @@
         <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.609</v>
+        <v>-0.608</v>
       </c>
     </row>
     <row r="106">
@@ -3483,20 +3483,20 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5.471</v>
+        <v>5.956</v>
       </c>
       <c r="E106" t="n">
-        <v>37.9</v>
+        <v>34</v>
       </c>
       <c r="F106" t="n">
         <v>0.667</v>
       </c>
       <c r="G106" t="n">
-        <v>4.844</v>
+        <v>4.689</v>
       </c>
     </row>
     <row r="107">
@@ -3512,20 +3512,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5.956</v>
+        <v>2.306</v>
       </c>
       <c r="E107" t="n">
-        <v>34</v>
+        <v>20.7</v>
       </c>
       <c r="F107" t="n">
         <v>0.667</v>
       </c>
       <c r="G107" t="n">
-        <v>4.689</v>
+        <v>1.279</v>
       </c>
     </row>
     <row r="108">
@@ -3541,20 +3541,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2.306</v>
+        <v>0.724</v>
       </c>
       <c r="E108" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="F108" t="n">
         <v>0.667</v>
       </c>
       <c r="G108" t="n">
-        <v>1.279</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="109">
@@ -3570,20 +3570,20 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.724</v>
+        <v>0.237</v>
       </c>
       <c r="E109" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="F109" t="n">
         <v>0.667</v>
       </c>
       <c r="G109" t="n">
-        <v>0.625</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="110">
@@ -3599,20 +3599,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.236</v>
+        <v>-1.181</v>
       </c>
       <c r="E110" t="n">
-        <v>25.6</v>
+        <v>19.5</v>
       </c>
       <c r="F110" t="n">
         <v>0.667</v>
       </c>
       <c r="G110" t="n">
-        <v>0.482</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="111">
@@ -3628,20 +3628,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Dalton Knecht</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-1.181</v>
+        <v>-1.862</v>
       </c>
       <c r="E111" t="n">
-        <v>19.5</v>
+        <v>15.8</v>
       </c>
       <c r="F111" t="n">
         <v>0.667</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.209</v>
+        <v>-0.393</v>
       </c>
     </row>
     <row r="112">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dalton Knecht</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-1.862</v>
+        <v>-2.378</v>
       </c>
       <c r="E112" t="n">
-        <v>15.8</v>
+        <v>24.5</v>
       </c>
       <c r="F112" t="n">
         <v>0.667</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.393</v>
+        <v>-0.872</v>
       </c>
     </row>
     <row r="113">
@@ -3686,20 +3686,20 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Maxi Kleber</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-2.378</v>
+        <v>-6.511</v>
       </c>
       <c r="E113" t="n">
-        <v>24.5</v>
+        <v>15.5</v>
       </c>
       <c r="F113" t="n">
         <v>0.667</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.872</v>
+        <v>-1.883</v>
       </c>
     </row>
     <row r="114">
@@ -3715,20 +3715,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2.927</v>
+        <v>1.009</v>
       </c>
       <c r="E114" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="F114" t="n">
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>1.668</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="115">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.319</v>
+        <v>0.2</v>
       </c>
       <c r="E115" t="n">
         <v>23.9</v>
@@ -3757,7 +3757,7 @@
         <v>0.267</v>
       </c>
       <c r="G115" t="n">
-        <v>0.291</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="116">
@@ -3777,16 +3777,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-0.475</v>
+        <v>-0.133</v>
       </c>
       <c r="E116" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="F116" t="n">
         <v>0.267</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.111</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -3806,16 +3806,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-1.652</v>
+        <v>-1.823</v>
       </c>
       <c r="E117" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="F117" t="n">
         <v>0.267</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.744</v>
+        <v>-0.8149999999999999</v>
       </c>
     </row>
     <row r="118">
@@ -3831,20 +3831,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jahmai Mashack</t>
+          <t>Walter Clayton Jr.</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-4.579</v>
+        <v>-2.2</v>
       </c>
       <c r="E118" t="n">
-        <v>26.4</v>
+        <v>25.8</v>
       </c>
       <c r="F118" t="n">
         <v>0.267</v>
       </c>
       <c r="G118" t="n">
-        <v>-2.373</v>
+        <v>-1.037</v>
       </c>
     </row>
     <row r="119">
@@ -3864,16 +3864,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-5.711</v>
+        <v>-5.478</v>
       </c>
       <c r="E119" t="n">
-        <v>24.2</v>
+        <v>25.4</v>
       </c>
       <c r="F119" t="n">
         <v>0.267</v>
       </c>
       <c r="G119" t="n">
-        <v>-2.742</v>
+        <v>-2.762</v>
       </c>
     </row>
     <row r="120">
@@ -3893,16 +3893,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2.969</v>
+        <v>3.015</v>
       </c>
       <c r="E120" t="n">
-        <v>35.5</v>
+        <v>35.7</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G120" t="n">
-        <v>2.642</v>
+        <v>2.666</v>
       </c>
     </row>
     <row r="121">
@@ -3928,10 +3928,10 @@
         <v>32.7</v>
       </c>
       <c r="F121" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>1.957</v>
+        <v>1.935</v>
       </c>
     </row>
     <row r="122">
@@ -3947,20 +3947,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2.288</v>
+        <v>1.718</v>
       </c>
       <c r="E122" t="n">
-        <v>23.1</v>
+        <v>28.6</v>
       </c>
       <c r="F122" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>1.387</v>
+        <v>1.361</v>
       </c>
     </row>
     <row r="123">
@@ -3976,20 +3976,20 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1.664</v>
+        <v>2.338</v>
       </c>
       <c r="E123" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F123" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G123" t="n">
-        <v>1.368</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="124">
@@ -4009,16 +4009,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1.007</v>
+        <v>1.017</v>
       </c>
       <c r="E124" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="F124" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="125">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.297</v>
+        <v>0.414</v>
       </c>
       <c r="E125" t="n">
-        <v>27.7</v>
+        <v>28.7</v>
       </c>
       <c r="F125" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G125" t="n">
-        <v>0.518</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="126">
@@ -4063,20 +4063,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kasparas Jakučionis</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-0.624</v>
+        <v>-0.517</v>
       </c>
       <c r="E126" t="n">
-        <v>19.3</v>
+        <v>31.6</v>
       </c>
       <c r="F126" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.01</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="127">
@@ -4092,20 +4092,20 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Kasparas Jakučionis</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>-0.658</v>
+        <v>-0.644</v>
       </c>
       <c r="E127" t="n">
-        <v>30.3</v>
+        <v>19</v>
       </c>
       <c r="F127" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.037</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="128">
@@ -4121,20 +4121,20 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.549</v>
+        <v>3.881</v>
       </c>
       <c r="E128" t="n">
-        <v>23.1</v>
+        <v>31.3</v>
       </c>
       <c r="F128" t="n">
         <v>0.2</v>
       </c>
       <c r="G128" t="n">
-        <v>0.36</v>
+        <v>2.665</v>
       </c>
     </row>
     <row r="129">
@@ -4150,20 +4150,20 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.41</v>
+        <v>0.619</v>
       </c>
       <c r="E129" t="n">
-        <v>24.9</v>
+        <v>23.3</v>
       </c>
       <c r="F129" t="n">
         <v>0.2</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.109</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="130">
@@ -4179,20 +4179,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>-0.972</v>
+        <v>-0.312</v>
       </c>
       <c r="E130" t="n">
-        <v>20.9</v>
+        <v>24.8</v>
       </c>
       <c r="F130" t="n">
         <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>-0.336</v>
+        <v>-0.058</v>
       </c>
     </row>
     <row r="131">
@@ -4208,20 +4208,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-2.557</v>
+        <v>-0.673</v>
       </c>
       <c r="E131" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="F131" t="n">
         <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>-1.115</v>
+        <v>-0.222</v>
       </c>
     </row>
     <row r="132">
@@ -4237,20 +4237,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-3.635</v>
+        <v>-2.167</v>
       </c>
       <c r="E132" t="n">
-        <v>16.3</v>
+        <v>29.5</v>
       </c>
       <c r="F132" t="n">
         <v>0.2</v>
       </c>
       <c r="G132" t="n">
-        <v>-1.167</v>
+        <v>-1.209</v>
       </c>
     </row>
     <row r="133">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-2.662</v>
+        <v>-2.619</v>
       </c>
       <c r="E133" t="n">
-        <v>22.8</v>
+        <v>24.2</v>
       </c>
       <c r="F133" t="n">
         <v>0.2</v>
       </c>
       <c r="G133" t="n">
-        <v>-1.17</v>
+        <v>-1.221</v>
       </c>
     </row>
     <row r="134">
@@ -4295,20 +4295,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.353</v>
+        <v>-2.721</v>
       </c>
       <c r="E134" t="n">
-        <v>27.9</v>
+        <v>23.7</v>
       </c>
       <c r="F134" t="n">
         <v>0.2</v>
       </c>
       <c r="G134" t="n">
-        <v>-1.254</v>
+        <v>-1.245</v>
       </c>
     </row>
     <row r="135">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-3.486</v>
+        <v>-4.055</v>
       </c>
       <c r="E135" t="n">
         <v>21.9</v>
@@ -4337,7 +4337,7 @@
         <v>0.2</v>
       </c>
       <c r="G135" t="n">
-        <v>-1.5</v>
+        <v>-1.763</v>
       </c>
     </row>
     <row r="136">
@@ -4357,16 +4357,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>7.347</v>
+        <v>7.217</v>
       </c>
       <c r="E136" t="n">
-        <v>35.6</v>
+        <v>34.8</v>
       </c>
       <c r="F136" t="n">
         <v>0.767</v>
       </c>
       <c r="G136" t="n">
-        <v>6.02</v>
+        <v>5.787</v>
       </c>
     </row>
     <row r="137">
@@ -4386,16 +4386,16 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3.98</v>
+        <v>4.064</v>
       </c>
       <c r="E137" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="F137" t="n">
         <v>0.767</v>
       </c>
       <c r="G137" t="n">
-        <v>3.129</v>
+        <v>3.202</v>
       </c>
     </row>
     <row r="138">
@@ -4415,16 +4415,16 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2.998</v>
+        <v>2.981</v>
       </c>
       <c r="E138" t="n">
-        <v>28</v>
+        <v>28.3</v>
       </c>
       <c r="F138" t="n">
         <v>0.767</v>
       </c>
       <c r="G138" t="n">
-        <v>2.2</v>
+        <v>2.212</v>
       </c>
     </row>
     <row r="139">
@@ -4444,16 +4444,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1.655</v>
+        <v>1.471</v>
       </c>
       <c r="E139" t="n">
-        <v>30.2</v>
+        <v>29.8</v>
       </c>
       <c r="F139" t="n">
         <v>0.767</v>
       </c>
       <c r="G139" t="n">
-        <v>1.524</v>
+        <v>1.391</v>
       </c>
     </row>
     <row r="140">
@@ -4473,16 +4473,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1.713</v>
+        <v>1.742</v>
       </c>
       <c r="E140" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="F140" t="n">
         <v>0.767</v>
       </c>
       <c r="G140" t="n">
-        <v>1.299</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="141">
@@ -4502,16 +4502,16 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.863</v>
+        <v>0.783</v>
       </c>
       <c r="E141" t="n">
-        <v>31.2</v>
+        <v>30.5</v>
       </c>
       <c r="F141" t="n">
         <v>0.767</v>
       </c>
       <c r="G141" t="n">
-        <v>1.061</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="142">
@@ -4531,16 +4531,16 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1.581</v>
+        <v>1.201</v>
       </c>
       <c r="E142" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="F142" t="n">
         <v>0.767</v>
       </c>
       <c r="G142" t="n">
-        <v>0.99</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="143">
@@ -4560,16 +4560,16 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>-0.351</v>
+        <v>-0.223</v>
       </c>
       <c r="E143" t="n">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="F143" t="n">
         <v>0.767</v>
       </c>
       <c r="G143" t="n">
-        <v>0.155</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="144">
@@ -4589,16 +4589,16 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4.897</v>
+        <v>4.783</v>
       </c>
       <c r="E144" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="F144" t="n">
         <v>0.3</v>
       </c>
       <c r="G144" t="n">
-        <v>3.699</v>
+        <v>3.611</v>
       </c>
     </row>
     <row r="145">
@@ -4618,16 +4618,16 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4.866</v>
+        <v>4.769</v>
       </c>
       <c r="E145" t="n">
-        <v>29.2</v>
+        <v>30.5</v>
       </c>
       <c r="F145" t="n">
         <v>0.3</v>
       </c>
       <c r="G145" t="n">
-        <v>3.146</v>
+        <v>3.216</v>
       </c>
     </row>
     <row r="146">
@@ -4643,20 +4643,20 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2.286</v>
+        <v>2.603</v>
       </c>
       <c r="E146" t="n">
-        <v>32.1</v>
+        <v>30.5</v>
       </c>
       <c r="F146" t="n">
         <v>0.3</v>
       </c>
       <c r="G146" t="n">
-        <v>1.73</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="147">
@@ -4672,20 +4672,20 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.971</v>
+        <v>2.204</v>
       </c>
       <c r="E147" t="n">
-        <v>19.7</v>
+        <v>32.5</v>
       </c>
       <c r="F147" t="n">
         <v>0.3</v>
       </c>
       <c r="G147" t="n">
-        <v>0.521</v>
+        <v>1.694</v>
       </c>
     </row>
     <row r="148">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-0.235</v>
+        <v>-0.289</v>
       </c>
       <c r="E148" t="n">
         <v>19.9</v>
@@ -4714,7 +4714,7 @@
         <v>0.3</v>
       </c>
       <c r="G148" t="n">
-        <v>0.027</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="149">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-1.442</v>
+        <v>-1.232</v>
       </c>
       <c r="E149" t="n">
         <v>21.5</v>
@@ -4743,7 +4743,7 @@
         <v>0.3</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.512</v>
+        <v>-0.418</v>
       </c>
     </row>
     <row r="150">
@@ -4792,16 +4792,16 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-3.014</v>
+        <v>-3.156</v>
       </c>
       <c r="E151" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="F151" t="n">
         <v>0.3</v>
       </c>
       <c r="G151" t="n">
-        <v>-1.642</v>
+        <v>-1.745</v>
       </c>
     </row>
     <row r="152">
@@ -4821,16 +4821,16 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>6.606</v>
+        <v>6.404</v>
       </c>
       <c r="E152" t="n">
-        <v>36.1</v>
+        <v>36.5</v>
       </c>
       <c r="F152" t="n">
         <v>0.867</v>
       </c>
       <c r="G152" t="n">
-        <v>5.622</v>
+        <v>5.536</v>
       </c>
     </row>
     <row r="153">
@@ -4846,20 +4846,20 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2.979</v>
+        <v>4.168</v>
       </c>
       <c r="E153" t="n">
-        <v>30.9</v>
+        <v>29.9</v>
       </c>
       <c r="F153" t="n">
         <v>0.867</v>
       </c>
       <c r="G153" t="n">
-        <v>2.479</v>
+        <v>3.131</v>
       </c>
     </row>
     <row r="154">
@@ -4875,20 +4875,20 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3.097</v>
+        <v>2.971</v>
       </c>
       <c r="E154" t="n">
-        <v>29.6</v>
+        <v>31.2</v>
       </c>
       <c r="F154" t="n">
         <v>0.867</v>
       </c>
       <c r="G154" t="n">
-        <v>2.444</v>
+        <v>2.493</v>
       </c>
     </row>
     <row r="155">
@@ -4904,20 +4904,20 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1.601</v>
+        <v>3.047</v>
       </c>
       <c r="E155" t="n">
-        <v>34</v>
+        <v>29.5</v>
       </c>
       <c r="F155" t="n">
         <v>0.867</v>
       </c>
       <c r="G155" t="n">
-        <v>1.746</v>
+        <v>2.406</v>
       </c>
     </row>
     <row r="156">
@@ -4933,20 +4933,20 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3.046</v>
+        <v>1.75</v>
       </c>
       <c r="E156" t="n">
-        <v>19.7</v>
+        <v>34.8</v>
       </c>
       <c r="F156" t="n">
         <v>0.867</v>
       </c>
       <c r="G156" t="n">
-        <v>1.604</v>
+        <v>1.898</v>
       </c>
     </row>
     <row r="157">
@@ -4962,20 +4962,20 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.553</v>
+        <v>2.991</v>
       </c>
       <c r="E157" t="n">
-        <v>28.9</v>
+        <v>19.4</v>
       </c>
       <c r="F157" t="n">
         <v>0.867</v>
       </c>
       <c r="G157" t="n">
-        <v>0.856</v>
+        <v>1.563</v>
       </c>
     </row>
     <row r="158">
@@ -4991,20 +4991,20 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>-1.338</v>
+        <v>0.197</v>
       </c>
       <c r="E158" t="n">
-        <v>24.8</v>
+        <v>28.1</v>
       </c>
       <c r="F158" t="n">
         <v>0.867</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.244</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="159">
@@ -5020,20 +5020,20 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jordan Clarkson</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-3.401</v>
+        <v>-1.2</v>
       </c>
       <c r="E159" t="n">
-        <v>15.9</v>
+        <v>25.1</v>
       </c>
       <c r="F159" t="n">
         <v>0.867</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.84</v>
+        <v>-0.175</v>
       </c>
     </row>
     <row r="160">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>14.848</v>
+        <v>14.849</v>
       </c>
       <c r="E160" t="n">
         <v>34.3</v>
@@ -5091,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>3.077</v>
+        <v>3.078</v>
       </c>
     </row>
     <row r="162">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.204</v>
+        <v>1.205</v>
       </c>
       <c r="E165" t="n">
         <v>21.6</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-0.046</v>
+        <v>-0.045</v>
       </c>
       <c r="E166" t="n">
         <v>25.1</v>
@@ -5285,16 +5285,16 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3.312</v>
+        <v>3.186</v>
       </c>
       <c r="E168" t="n">
-        <v>35.4</v>
+        <v>34.8</v>
       </c>
       <c r="F168" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G168" t="n">
-        <v>2.765</v>
+        <v>2.601</v>
       </c>
     </row>
     <row r="169">
@@ -5314,16 +5314,16 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3.176</v>
+        <v>3.04</v>
       </c>
       <c r="E169" t="n">
-        <v>34.2</v>
+        <v>33.6</v>
       </c>
       <c r="F169" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G169" t="n">
-        <v>2.569</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="170">
@@ -5343,16 +5343,16 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3.158</v>
+        <v>2.978</v>
       </c>
       <c r="E170" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="F170" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G170" t="n">
-        <v>2.257</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="171">
@@ -5372,16 +5372,16 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1.991</v>
+        <v>1.644</v>
       </c>
       <c r="E171" t="n">
-        <v>28.8</v>
+        <v>27.3</v>
       </c>
       <c r="F171" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G171" t="n">
-        <v>1.457</v>
+        <v>1.163</v>
       </c>
     </row>
     <row r="172">
@@ -5401,16 +5401,16 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-0.67</v>
+        <v>-0.658</v>
       </c>
       <c r="E172" t="n">
-        <v>29.3</v>
+        <v>28.8</v>
       </c>
       <c r="F172" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G172" t="n">
-        <v>-0.145</v>
+        <v>-0.155</v>
       </c>
     </row>
     <row r="173">
@@ -5430,16 +5430,16 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-1.201</v>
+        <v>-1.115</v>
       </c>
       <c r="E173" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="F173" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G173" t="n">
-        <v>-0.474</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="174">
@@ -5459,16 +5459,16 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-1.598</v>
+        <v>-1.664</v>
       </c>
       <c r="E174" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="F174" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.5</v>
+        <v>-0.536</v>
       </c>
     </row>
     <row r="175">
@@ -5494,10 +5494,10 @@
         <v>22.2</v>
       </c>
       <c r="F175" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.851</v>
+        <v>-0.866</v>
       </c>
     </row>
     <row r="176">
@@ -5517,16 +5517,16 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>9.177</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E176" t="n">
-        <v>37</v>
+        <v>36.4</v>
       </c>
       <c r="F176" t="n">
         <v>0.467</v>
       </c>
       <c r="G176" t="n">
-        <v>7.431</v>
+        <v>7.337</v>
       </c>
     </row>
     <row r="177">
@@ -5546,16 +5546,16 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>5.549</v>
+        <v>5.192</v>
       </c>
       <c r="E177" t="n">
-        <v>33.5</v>
+        <v>34.1</v>
       </c>
       <c r="F177" t="n">
         <v>0.467</v>
       </c>
       <c r="G177" t="n">
-        <v>4.199</v>
+        <v>4.022</v>
       </c>
     </row>
     <row r="178">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1.83</v>
+        <v>2.736</v>
       </c>
       <c r="E178" t="n">
         <v>32.7</v>
@@ -5584,7 +5584,7 @@
         <v>0.467</v>
       </c>
       <c r="G178" t="n">
-        <v>1.564</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="179">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.758</v>
+        <v>0.782</v>
       </c>
       <c r="E179" t="n">
         <v>32.9</v>
@@ -5613,7 +5613,7 @@
         <v>0.467</v>
       </c>
       <c r="G179" t="n">
-        <v>0.839</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="180">
@@ -5633,16 +5633,16 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>-0.187</v>
+        <v>-0.226</v>
       </c>
       <c r="E180" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="F180" t="n">
         <v>0.467</v>
       </c>
       <c r="G180" t="n">
-        <v>0.188</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="181">
@@ -5691,16 +5691,16 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-1.343</v>
+        <v>-1.275</v>
       </c>
       <c r="E182" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="F182" t="n">
         <v>0.467</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.417</v>
+        <v>-0.396</v>
       </c>
     </row>
     <row r="183">
@@ -5720,16 +5720,16 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-1.571</v>
+        <v>-1.395</v>
       </c>
       <c r="E183" t="n">
-        <v>32.5</v>
+        <v>30.7</v>
       </c>
       <c r="F183" t="n">
         <v>0.467</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.747</v>
+        <v>-0.593</v>
       </c>
     </row>
     <row r="184">
@@ -5749,16 +5749,16 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4.901</v>
+        <v>4.902</v>
       </c>
       <c r="E184" t="n">
         <v>33.4</v>
       </c>
       <c r="F184" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G184" t="n">
-        <v>3.761</v>
+        <v>3.784</v>
       </c>
     </row>
     <row r="185">
@@ -5778,16 +5778,16 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4.182</v>
+        <v>4.183</v>
       </c>
       <c r="E185" t="n">
         <v>29.5</v>
       </c>
       <c r="F185" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G185" t="n">
-        <v>2.874</v>
+        <v>2.894</v>
       </c>
     </row>
     <row r="186">
@@ -5813,10 +5813,10 @@
         <v>28.9</v>
       </c>
       <c r="F186" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G186" t="n">
-        <v>1.952</v>
+        <v>1.972</v>
       </c>
     </row>
     <row r="187">
@@ -5842,10 +5842,10 @@
         <v>24.7</v>
       </c>
       <c r="F187" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G187" t="n">
-        <v>0.731</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="188">
@@ -5871,10 +5871,10 @@
         <v>26.7</v>
       </c>
       <c r="F188" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="G188" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G188" t="n">
-        <v>0.481</v>
       </c>
     </row>
     <row r="189">
@@ -5900,10 +5900,10 @@
         <v>29.3</v>
       </c>
       <c r="F189" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G189" t="n">
-        <v>0.101</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="190">
@@ -5929,10 +5929,10 @@
         <v>30</v>
       </c>
       <c r="F190" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.576</v>
+        <v>-0.555</v>
       </c>
     </row>
     <row r="191">
@@ -5958,10 +5958,10 @@
         <v>29.8</v>
       </c>
       <c r="F191" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G191" t="n">
-        <v>-1.003</v>
+        <v>-0.982</v>
       </c>
     </row>
     <row r="192">
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3.151</v>
+        <v>3.152</v>
       </c>
       <c r="E194" t="n">
         <v>29.6</v>
@@ -6048,7 +6048,7 @@
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>2.171</v>
+        <v>2.172</v>
       </c>
     </row>
     <row r="195">
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3.178</v>
+        <v>3.179</v>
       </c>
       <c r="E195" t="n">
         <v>25.8</v>
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>-2.331</v>
+        <v>-2.33</v>
       </c>
       <c r="E197" t="n">
         <v>24.3</v>
@@ -6213,16 +6213,16 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>2.774</v>
+        <v>2.804</v>
       </c>
       <c r="E200" t="n">
-        <v>29.4</v>
+        <v>30.1</v>
       </c>
       <c r="F200" t="n">
         <v>0.1</v>
       </c>
       <c r="G200" t="n">
-        <v>1.76</v>
+        <v>1.823</v>
       </c>
     </row>
     <row r="201">
@@ -6242,16 +6242,16 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.098</v>
+        <v>0.215</v>
       </c>
       <c r="E201" t="n">
-        <v>31.9</v>
+        <v>32.2</v>
       </c>
       <c r="F201" t="n">
         <v>0.1</v>
       </c>
       <c r="G201" t="n">
-        <v>0.132</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="202">
@@ -6267,20 +6267,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.062</v>
+        <v>0.326</v>
       </c>
       <c r="E202" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="203">
@@ -6300,16 +6300,16 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>-1.59</v>
+        <v>-1.434</v>
       </c>
       <c r="E203" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>-0.701</v>
+        <v>-0.619</v>
       </c>
     </row>
     <row r="204">
@@ -6329,16 +6329,16 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>-1.268</v>
+        <v>-1.366</v>
       </c>
       <c r="E204" t="n">
-        <v>33</v>
+        <v>32.3</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.803</v>
+        <v>-0.852</v>
       </c>
     </row>
     <row r="205">
@@ -6358,16 +6358,16 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-3.468</v>
+        <v>-3.249</v>
       </c>
       <c r="E205" t="n">
-        <v>28.8</v>
+        <v>28.5</v>
       </c>
       <c r="F205" t="n">
         <v>0.1</v>
       </c>
       <c r="G205" t="n">
-        <v>-2.021</v>
+        <v>-1.873</v>
       </c>
     </row>
     <row r="206">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-4.277</v>
+        <v>-4.361</v>
       </c>
       <c r="E207" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="F207" t="n">
         <v>0.1</v>
       </c>
       <c r="G207" t="n">
-        <v>-2.867</v>
+        <v>-2.949</v>
       </c>
     </row>
     <row r="208">
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>11.286</v>
+        <v>11.6</v>
       </c>
       <c r="E208" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="F208" t="n">
         <v>0.967</v>
       </c>
       <c r="G208" t="n">
-        <v>7.627</v>
+        <v>7.731</v>
       </c>
     </row>
     <row r="209">
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>4.226</v>
+        <v>4.339</v>
       </c>
       <c r="E209" t="n">
-        <v>28.6</v>
+        <v>29.1</v>
       </c>
       <c r="F209" t="n">
         <v>0.967</v>
       </c>
       <c r="G209" t="n">
-        <v>3.093</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="210">
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>3.702</v>
+        <v>3.614</v>
       </c>
       <c r="E210" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F210" t="n">
         <v>0.967</v>
       </c>
       <c r="G210" t="n">
-        <v>2.905</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="211">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1.528</v>
+        <v>1.672</v>
       </c>
       <c r="E211" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="F211" t="n">
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>1.211</v>
+        <v>1.291</v>
       </c>
     </row>
     <row r="212">
@@ -6561,16 +6561,16 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1.031</v>
+        <v>0.966</v>
       </c>
       <c r="E212" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="F212" t="n">
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>0.954</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="213">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.293</v>
+        <v>0.321</v>
       </c>
       <c r="E213" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="F213" t="n">
         <v>0.967</v>
       </c>
       <c r="G213" t="n">
-        <v>0.715</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="214">
@@ -6619,16 +6619,16 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.121</v>
+        <v>0.161</v>
       </c>
       <c r="E214" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="F214" t="n">
         <v>0.967</v>
       </c>
       <c r="G214" t="n">
-        <v>0.678</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="215">
@@ -6648,16 +6648,16 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>-0.922</v>
+        <v>-0.92</v>
       </c>
       <c r="E215" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="F215" t="n">
         <v>0.967</v>
       </c>
       <c r="G215" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="216">
@@ -6677,16 +6677,16 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>6.272</v>
+        <v>6.234</v>
       </c>
       <c r="E216" t="n">
         <v>32.4</v>
       </c>
       <c r="F216" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G216" t="n">
-        <v>4.598</v>
+        <v>4.547</v>
       </c>
     </row>
     <row r="217">
@@ -6702,20 +6702,20 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>2.049</v>
+        <v>3.642</v>
       </c>
       <c r="E217" t="n">
-        <v>34.2</v>
+        <v>21.5</v>
       </c>
       <c r="F217" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G217" t="n">
-        <v>1.841</v>
+        <v>1.856</v>
       </c>
     </row>
     <row r="218">
@@ -6731,20 +6731,20 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>3.457</v>
+        <v>1.926</v>
       </c>
       <c r="E218" t="n">
-        <v>20.4</v>
+        <v>33.9</v>
       </c>
       <c r="F218" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G218" t="n">
-        <v>1.695</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="219">
@@ -6764,16 +6764,16 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1.715</v>
+        <v>1.553</v>
       </c>
       <c r="E219" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="F219" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G219" t="n">
-        <v>1.452</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="220">
@@ -6793,16 +6793,16 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1.724</v>
+        <v>1.834</v>
       </c>
       <c r="E220" t="n">
         <v>26.9</v>
       </c>
       <c r="F220" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G220" t="n">
-        <v>1.264</v>
+        <v>1.307</v>
       </c>
     </row>
     <row r="221">
@@ -6822,16 +6822,16 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0.858</v>
+        <v>1.034</v>
       </c>
       <c r="E221" t="n">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="F221" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G221" t="n">
-        <v>0.68</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="222">
@@ -6851,16 +6851,16 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>-0.619</v>
+        <v>-0.441</v>
       </c>
       <c r="E222" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="F222" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G222" t="n">
-        <v>-0.041</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="223">
@@ -6880,16 +6880,16 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>-0.995</v>
+        <v>-0.877</v>
       </c>
       <c r="E223" t="n">
-        <v>22.1</v>
+        <v>23</v>
       </c>
       <c r="F223" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G223" t="n">
-        <v>-0.212</v>
+        <v>-0.181</v>
       </c>
     </row>
     <row r="224">
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1.155</v>
+        <v>1.319</v>
       </c>
       <c r="E224" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="F224" t="n">
         <v>0.133</v>
       </c>
       <c r="G224" t="n">
-        <v>0.712</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="225">
@@ -6938,16 +6938,16 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.251</v>
       </c>
       <c r="E225" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="F225" t="n">
         <v>0.133</v>
       </c>
       <c r="G225" t="n">
-        <v>0.575</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="226">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1.116</v>
+        <v>1.117</v>
       </c>
       <c r="E226" t="n">
         <v>15.5</v>
@@ -6996,16 +6996,16 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>-0.357</v>
+        <v>-0.124</v>
       </c>
       <c r="E227" t="n">
-        <v>26.7</v>
+        <v>27.2</v>
       </c>
       <c r="F227" t="n">
         <v>0.133</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.124</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="228">
@@ -7063,7 +7063,7 @@
         <v>0.133</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.582</v>
+        <v>-0.581</v>
       </c>
     </row>
     <row r="230">
@@ -7083,16 +7083,16 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-1.841</v>
+        <v>-2.068</v>
       </c>
       <c r="E230" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="F230" t="n">
         <v>0.133</v>
       </c>
       <c r="G230" t="n">
-        <v>-1.067</v>
+        <v>-1.219</v>
       </c>
     </row>
     <row r="231">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-3.915</v>
+        <v>-3.95</v>
       </c>
       <c r="E231" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="F231" t="n">
         <v>0.133</v>
       </c>
       <c r="G231" t="n">
-        <v>-2.561</v>
+        <v>-2.726</v>
       </c>
     </row>
     <row r="232">
@@ -7141,16 +7141,16 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1.616</v>
+        <v>1.796</v>
       </c>
       <c r="E232" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="F232" t="n">
         <v>0.033</v>
       </c>
       <c r="G232" t="n">
-        <v>0.726</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="233">
@@ -7166,20 +7166,20 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-0.882</v>
+        <v>-0.873</v>
       </c>
       <c r="E233" t="n">
-        <v>27.1</v>
+        <v>25</v>
       </c>
       <c r="F233" t="n">
         <v>0.033</v>
       </c>
       <c r="G233" t="n">
-        <v>-0.48</v>
+        <v>-0.438</v>
       </c>
     </row>
     <row r="234">
@@ -7195,20 +7195,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>-1.499</v>
+        <v>-0.965</v>
       </c>
       <c r="E234" t="n">
-        <v>24.6</v>
+        <v>26.9</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>-0.751</v>
+        <v>-0.523</v>
       </c>
     </row>
     <row r="235">
@@ -7228,16 +7228,16 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>-1.933</v>
+        <v>-1.834</v>
       </c>
       <c r="E235" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="F235" t="n">
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>-0.845</v>
+        <v>-0.8070000000000001</v>
       </c>
     </row>
     <row r="236">
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-1.934</v>
+        <v>-1.89</v>
       </c>
       <c r="E236" t="n">
         <v>27.2</v>
@@ -7266,7 +7266,7 @@
         <v>0.033</v>
       </c>
       <c r="G236" t="n">
-        <v>-1.076</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="237">
@@ -7286,16 +7286,16 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-3.237</v>
+        <v>-3.41</v>
       </c>
       <c r="E237" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="F237" t="n">
         <v>0.033</v>
       </c>
       <c r="G237" t="n">
-        <v>-1.374</v>
+        <v>-1.471</v>
       </c>
     </row>
     <row r="238">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-3.194</v>
+        <v>-3.323</v>
       </c>
       <c r="E238" t="n">
         <v>22.5</v>
@@ -7324,7 +7324,7 @@
         <v>0.033</v>
       </c>
       <c r="G238" t="n">
-        <v>-1.483</v>
+        <v>-1.545</v>
       </c>
     </row>
     <row r="239">
@@ -7344,16 +7344,16 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-2.573</v>
+        <v>-2.502</v>
       </c>
       <c r="E239" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="F239" t="n">
         <v>0.033</v>
       </c>
       <c r="G239" t="n">
-        <v>-1.666</v>
+        <v>-1.614</v>
       </c>
     </row>
   </sheetData>
@@ -7425,10 +7425,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>22.012</v>
+        <v>21.981</v>
       </c>
       <c r="F2" t="n">
-        <v>2.782</v>
+        <v>2.798</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7442,26 +7442,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>21.528</v>
+        <v>19.316</v>
       </c>
       <c r="F3" t="n">
-        <v>3.333</v>
+        <v>2.601</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>19.056</v>
+        <v>19.057</v>
       </c>
       <c r="F4" t="n">
         <v>2.76</v>
@@ -7500,26 +7500,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>18.679</v>
+        <v>17.486</v>
       </c>
       <c r="F5" t="n">
-        <v>2.501</v>
+        <v>2.719</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7529,26 +7529,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>17.202</v>
+        <v>17.474</v>
       </c>
       <c r="F6" t="n">
-        <v>2.658</v>
+        <v>2.541</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -7570,10 +7570,10 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>16.378</v>
+        <v>15.966</v>
       </c>
       <c r="F7" t="n">
-        <v>2.473</v>
+        <v>2.404</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -7587,26 +7587,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>13.735</v>
+        <v>15.025</v>
       </c>
       <c r="F8" t="n">
-        <v>1.847</v>
+        <v>2.039</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7616,26 +7616,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>13.667</v>
+        <v>14.059</v>
       </c>
       <c r="F9" t="n">
-        <v>1.643</v>
+        <v>1.878</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7657,10 +7657,10 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>13.258</v>
+        <v>13.546</v>
       </c>
       <c r="F10" t="n">
-        <v>1.004</v>
+        <v>1.042</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -7686,10 +7686,10 @@
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>12.913</v>
+        <v>13.425</v>
       </c>
       <c r="F11" t="n">
-        <v>1.68</v>
+        <v>1.781</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -7715,10 +7715,10 @@
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>11.855</v>
+        <v>12.004</v>
       </c>
       <c r="F12" t="n">
-        <v>1.666</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.698</v>
+        <v>11.7</v>
       </c>
       <c r="F13" t="n">
         <v>1.759</v>
@@ -7773,10 +7773,10 @@
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>11.277</v>
+        <v>11.331</v>
       </c>
       <c r="F14" t="n">
-        <v>1.808</v>
+        <v>1.863</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -7790,26 +7790,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>10.445</v>
+        <v>8.768000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.159</v>
+        <v>1.202</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
     </row>
@@ -7819,26 +7819,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>8.725</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.152</v>
+        <v>1.155</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Devin Booker</t>
         </is>
       </c>
     </row>
@@ -7848,26 +7848,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>8.321</v>
+        <v>7.22</v>
       </c>
       <c r="F17" t="n">
-        <v>1.155</v>
+        <v>0.876</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
     </row>
@@ -7877,26 +7877,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>7.078</v>
+        <v>7.01</v>
       </c>
       <c r="F18" t="n">
-        <v>0.737</v>
+        <v>0.541</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
     </row>
@@ -7906,26 +7906,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>6.618</v>
+        <v>6.298</v>
       </c>
       <c r="F19" t="n">
-        <v>0.503</v>
+        <v>0.642</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>6.089</v>
+        <v>6.09</v>
       </c>
       <c r="F20" t="n">
         <v>1.012</v>
@@ -7964,26 +7964,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>5.985</v>
+        <v>5.397</v>
       </c>
       <c r="F21" t="n">
-        <v>0.707</v>
+        <v>0.855</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7993,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>5.251</v>
+        <v>4.085</v>
       </c>
       <c r="F22" t="n">
-        <v>0.855</v>
+        <v>0.193</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
     </row>
@@ -8022,26 +8022,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4.72</v>
+        <v>3.718</v>
       </c>
       <c r="F23" t="n">
-        <v>0.414</v>
+        <v>-0.339</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>LeBron James</t>
         </is>
       </c>
     </row>
@@ -8051,26 +8051,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>3.013</v>
+        <v>-0.058</v>
       </c>
       <c r="F24" t="n">
-        <v>0.457</v>
+        <v>-0.341</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>T.J. McConnell</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
     </row>
@@ -8080,26 +8080,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.241</v>
+        <v>-1.944</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.594</v>
+        <v>-0.669</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Jay Huff</t>
         </is>
       </c>
     </row>
@@ -8109,26 +8109,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.032</v>
+        <v>-2.656</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-1.006</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
     </row>
@@ -8138,26 +8138,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.011</v>
+        <v>-2.951</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.528</v>
+        <v>-0.632</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
     </row>
@@ -8167,26 +8167,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.291</v>
+        <v>-3.635</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.941</v>
+        <v>-1.404</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
     </row>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.57</v>
+        <v>-6.195</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.458</v>
+        <v>-1.383</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.949</v>
+        <v>-6.652</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.704</v>
+        <v>-1.625</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -8266,14 +8266,14 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.809</v>
+        <v>-12.147</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.054</v>
+        <v>-3.574</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Josh Minott</t>
         </is>
       </c>
     </row>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,41 +426,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G239"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team_abbr</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>player_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sbpm</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>avg_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team_pct_net_rtg</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>bpm_contribution</t>
         </is>
@@ -471,16 +483,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.276999999999999</v>
+        <v>8.236000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G2" t="n">
-        <v>6.27</v>
+        <v>6.559</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +512,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.685</v>
+        <v>3.674</v>
       </c>
       <c r="E3" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G3" t="n">
-        <v>3.012</v>
+        <v>3.066</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +541,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.557</v>
+        <v>2.648</v>
       </c>
       <c r="E4" t="n">
-        <v>32.4</v>
+        <v>32.1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G4" t="n">
-        <v>2.131</v>
+        <v>2.219</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +570,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.549</v>
+        <v>2.578</v>
       </c>
       <c r="E5" t="n">
         <v>29.4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G5" t="n">
-        <v>1.928</v>
+        <v>1.987</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +599,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.043</v>
+        <v>2.316</v>
       </c>
       <c r="E6" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G6" t="n">
-        <v>1.636</v>
+        <v>1.829</v>
       </c>
     </row>
     <row r="7">
@@ -616,16 +628,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.601</v>
+        <v>-0.604</v>
       </c>
       <c r="E7" t="n">
         <v>15.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +657,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.572</v>
+        <v>-1.717</v>
       </c>
       <c r="E8" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.374</v>
+        <v>-0.392</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +686,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.914</v>
+        <v>-1.63</v>
       </c>
       <c r="E9" t="n">
-        <v>19.9</v>
+        <v>20.6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.544</v>
+        <v>-0.413</v>
       </c>
     </row>
     <row r="10">
@@ -703,7 +715,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.578</v>
+        <v>6.582</v>
       </c>
       <c r="E10" t="n">
         <v>34.9</v>
@@ -712,7 +724,7 @@
         <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.431</v>
+        <v>5.436</v>
       </c>
     </row>
     <row r="11">
@@ -732,16 +744,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.562</v>
+        <v>5.915</v>
       </c>
       <c r="E11" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="F11" t="n">
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>4.675</v>
+        <v>4.893</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +773,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.743</v>
+        <v>4.788</v>
       </c>
       <c r="E12" t="n">
-        <v>34.3</v>
+        <v>33.8</v>
       </c>
       <c r="F12" t="n">
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>4.03</v>
+        <v>4.001</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +802,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.021</v>
+        <v>4.071</v>
       </c>
       <c r="E13" t="n">
-        <v>32.3</v>
+        <v>31.8</v>
       </c>
       <c r="F13" t="n">
         <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.308</v>
+        <v>3.289</v>
       </c>
     </row>
     <row r="14">
@@ -815,20 +827,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Nikola Vučević</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.237</v>
+        <v>3.315</v>
       </c>
       <c r="E14" t="n">
-        <v>27.2</v>
+        <v>23.2</v>
       </c>
       <c r="F14" t="n">
         <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.775</v>
+        <v>2.041</v>
       </c>
     </row>
     <row r="15">
@@ -844,20 +856,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dalano Banton</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.33</v>
+        <v>2.407</v>
       </c>
       <c r="E15" t="n">
-        <v>17.9</v>
+        <v>27.3</v>
       </c>
       <c r="F15" t="n">
         <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.213</v>
+        <v>1.879</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +889,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.616</v>
+        <v>-0.482</v>
       </c>
       <c r="E16" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="F16" t="n">
         <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.152</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +918,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.39</v>
+        <v>-1.471</v>
       </c>
       <c r="E17" t="n">
-        <v>26.2</v>
+        <v>25.7</v>
       </c>
       <c r="F17" t="n">
         <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.268</v>
+        <v>-0.305</v>
       </c>
     </row>
     <row r="18">
@@ -935,16 +947,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.966</v>
+        <v>1.943</v>
       </c>
       <c r="E18" t="n">
-        <v>18.4</v>
+        <v>19.3</v>
       </c>
       <c r="F18" t="n">
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>0.779</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -960,20 +972,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-2.247</v>
+        <v>-4.788</v>
       </c>
       <c r="E19" t="n">
-        <v>21.4</v>
+        <v>15.7</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.974</v>
+        <v>-1.543</v>
       </c>
     </row>
     <row r="20">
@@ -989,20 +1001,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Jalen Wilson</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-2.113</v>
+        <v>-5.14</v>
       </c>
       <c r="E20" t="n">
-        <v>23.2</v>
+        <v>15.3</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.987</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="21">
@@ -1018,20 +1030,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Nolan Traore</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-4.703</v>
+        <v>-5.129</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>22.4</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.548</v>
+        <v>-2.365</v>
       </c>
     </row>
     <row r="22">
@@ -1047,20 +1059,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jalen Wilson</t>
+          <t>Drake Powell</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-5.138</v>
+        <v>-4.874</v>
       </c>
       <c r="E22" t="n">
-        <v>15.3</v>
+        <v>24.4</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.619</v>
+        <v>-2.443</v>
       </c>
     </row>
     <row r="23">
@@ -1076,78 +1088,78 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Drake Powell</t>
+          <t>Ben Saraf</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4.901</v>
+        <v>-6.131</v>
       </c>
       <c r="E23" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="F23" t="n">
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nolan Traore</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-5.327</v>
+        <v>7.261</v>
       </c>
       <c r="E24" t="n">
-        <v>22.4</v>
+        <v>28.5</v>
       </c>
       <c r="F24" t="n">
-        <v>0.067</v>
+        <v>0.7</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.459</v>
+        <v>4.735</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ben Saraf</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-6.129</v>
+        <v>4.433</v>
       </c>
       <c r="E25" t="n">
-        <v>23.3</v>
+        <v>29.9</v>
       </c>
       <c r="F25" t="n">
-        <v>0.067</v>
+        <v>0.7</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.939</v>
+        <v>3.194</v>
       </c>
     </row>
     <row r="26">
@@ -1163,20 +1175,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7.206</v>
+        <v>2.99</v>
       </c>
       <c r="E26" t="n">
-        <v>28.1</v>
+        <v>31.2</v>
       </c>
       <c r="F26" t="n">
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>4.628</v>
+        <v>2.401</v>
       </c>
     </row>
     <row r="27">
@@ -1192,20 +1204,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.368</v>
+        <v>1.534</v>
       </c>
       <c r="E27" t="n">
-        <v>29.9</v>
+        <v>28.5</v>
       </c>
       <c r="F27" t="n">
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>3.158</v>
+        <v>1.326</v>
       </c>
     </row>
     <row r="28">
@@ -1221,20 +1233,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.844</v>
+        <v>1.098</v>
       </c>
       <c r="E28" t="n">
-        <v>31.1</v>
+        <v>27.8</v>
       </c>
       <c r="F28" t="n">
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>2.294</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="29">
@@ -1250,20 +1262,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.548</v>
+        <v>0.901</v>
       </c>
       <c r="E29" t="n">
-        <v>28.8</v>
+        <v>20.1</v>
       </c>
       <c r="F29" t="n">
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.35</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="30">
@@ -1279,20 +1291,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Grant Williams</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.127</v>
+        <v>-0.71</v>
       </c>
       <c r="E30" t="n">
-        <v>27.7</v>
+        <v>18.9</v>
       </c>
       <c r="F30" t="n">
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1.053</v>
+        <v>-0.004</v>
       </c>
     </row>
     <row r="31">
@@ -1308,78 +1320,78 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Sion James</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.819</v>
+        <v>-3.44</v>
       </c>
       <c r="E31" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0.65</v>
+        <v>-1.085</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Tre Jones</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.6929999999999999</v>
+        <v>3.988</v>
       </c>
       <c r="E32" t="n">
-        <v>18.8</v>
+        <v>28.5</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="G32" t="n">
-        <v>0.003</v>
+        <v>2.546</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sion James</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-3.621</v>
+        <v>2.421</v>
       </c>
       <c r="E33" t="n">
-        <v>18.6</v>
+        <v>26</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.132</v>
+        <v>1.475</v>
       </c>
     </row>
     <row r="34">
@@ -1395,20 +1407,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Leonard Miller</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.795</v>
+        <v>-0.556</v>
       </c>
       <c r="E34" t="n">
-        <v>34.6</v>
+        <v>24.3</v>
       </c>
       <c r="F34" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G34" t="n">
-        <v>4.413</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="35">
@@ -1424,20 +1436,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tre Jones</t>
+          <t>Jaden Ivey</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.917</v>
+        <v>-0.621</v>
       </c>
       <c r="E35" t="n">
-        <v>28.5</v>
+        <v>19.6</v>
       </c>
       <c r="F35" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G35" t="n">
-        <v>2.526</v>
+        <v>-0.131</v>
       </c>
     </row>
     <row r="36">
@@ -1453,20 +1465,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Guerschon Yabusele</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.386</v>
+        <v>-2.182</v>
       </c>
       <c r="E36" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G36" t="n">
-        <v>1.414</v>
+        <v>-0.946</v>
       </c>
     </row>
     <row r="37">
@@ -1482,20 +1494,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Isaac Okoro</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.481</v>
+        <v>-3.306</v>
       </c>
       <c r="E37" t="n">
-        <v>32.5</v>
+        <v>29.7</v>
       </c>
       <c r="F37" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G37" t="n">
-        <v>1.229</v>
+        <v>-1.861</v>
       </c>
     </row>
     <row r="38">
@@ -1511,20 +1523,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Leonard Miller</t>
+          <t>Patrick Williams</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-0.538</v>
+        <v>-4.685</v>
       </c>
       <c r="E38" t="n">
-        <v>23.9</v>
+        <v>20.7</v>
       </c>
       <c r="F38" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.102</v>
+        <v>-1.891</v>
       </c>
     </row>
     <row r="39">
@@ -1540,78 +1552,78 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Guerschon Yabusele</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1.942</v>
+        <v>-6.34</v>
       </c>
       <c r="E39" t="n">
-        <v>24.3</v>
+        <v>21.4</v>
       </c>
       <c r="F39" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-2.692</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-3.348</v>
+        <v>8.946999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>30.4</v>
+        <v>33.4</v>
       </c>
       <c r="F40" t="n">
-        <v>0.333</v>
+        <v>0.767</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.909</v>
+        <v>6.758</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rob Dillingham</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-6.208</v>
+        <v>8.19</v>
       </c>
       <c r="E41" t="n">
-        <v>21.8</v>
+        <v>35</v>
       </c>
       <c r="F41" t="n">
-        <v>0.333</v>
+        <v>0.767</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.673</v>
+        <v>6.526</v>
       </c>
     </row>
     <row r="42">
@@ -1627,20 +1639,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8.955</v>
+        <v>4.538</v>
       </c>
       <c r="E42" t="n">
-        <v>33.4</v>
+        <v>30.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G42" t="n">
-        <v>6.739</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="43">
@@ -1656,20 +1668,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8.298</v>
+        <v>3.902</v>
       </c>
       <c r="E43" t="n">
-        <v>34.9</v>
+        <v>27.2</v>
       </c>
       <c r="F43" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G43" t="n">
-        <v>6.576</v>
+        <v>2.642</v>
       </c>
     </row>
     <row r="44">
@@ -1689,16 +1701,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.468</v>
+        <v>1.859</v>
       </c>
       <c r="E44" t="n">
         <v>27</v>
       </c>
       <c r="F44" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G44" t="n">
-        <v>1.238</v>
+        <v>1.476</v>
       </c>
     </row>
     <row r="45">
@@ -1714,20 +1726,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Craig Porter Jr.</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.918</v>
+        <v>0.706</v>
       </c>
       <c r="E45" t="n">
-        <v>17.7</v>
+        <v>29.4</v>
       </c>
       <c r="F45" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G45" t="n">
-        <v>0.975</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="46">
@@ -1747,16 +1759,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-0.598</v>
+        <v>-0.555</v>
       </c>
       <c r="E46" t="n">
-        <v>20.4</v>
+        <v>19.5</v>
       </c>
       <c r="F46" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G46" t="n">
-        <v>0.057</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1776,74 +1788,74 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.848</v>
+        <v>-0.929</v>
       </c>
       <c r="E47" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="F47" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.064</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lonzo Ball</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1.356</v>
+        <v>2.769</v>
       </c>
       <c r="E48" t="n">
-        <v>17.6</v>
+        <v>33.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.733</v>
+        <v>0.233</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.228</v>
+        <v>2.094</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nae'Qwan Tomlin</t>
+          <t>Marvin Bagley III</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1.528</v>
+        <v>2.213</v>
       </c>
       <c r="E49" t="n">
-        <v>16.2</v>
+        <v>21.3</v>
       </c>
       <c r="F49" t="n">
-        <v>0.733</v>
+        <v>0.233</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.268</v>
+        <v>1.086</v>
       </c>
     </row>
     <row r="50">
@@ -1859,20 +1871,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.309</v>
+        <v>1.557</v>
       </c>
       <c r="E50" t="n">
-        <v>33</v>
+        <v>22.5</v>
       </c>
       <c r="F50" t="n">
         <v>0.233</v>
       </c>
       <c r="G50" t="n">
-        <v>1.746</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="51">
@@ -1888,20 +1900,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Brandon Williams</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.544</v>
+        <v>1.197</v>
       </c>
       <c r="E51" t="n">
-        <v>22.7</v>
+        <v>22</v>
       </c>
       <c r="F51" t="n">
         <v>0.233</v>
       </c>
       <c r="G51" t="n">
-        <v>0.842</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="52">
@@ -1917,20 +1929,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brandon Williams</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.112</v>
+        <v>0.535</v>
       </c>
       <c r="E52" t="n">
-        <v>22.1</v>
+        <v>28.5</v>
       </c>
       <c r="F52" t="n">
         <v>0.233</v>
       </c>
       <c r="G52" t="n">
-        <v>0.619</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="53">
@@ -1946,20 +1958,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.634</v>
+        <v>-1.563</v>
       </c>
       <c r="E53" t="n">
-        <v>29.7</v>
+        <v>20.8</v>
       </c>
       <c r="F53" t="n">
         <v>0.233</v>
       </c>
       <c r="G53" t="n">
-        <v>0.537</v>
+        <v>-0.577</v>
       </c>
     </row>
     <row r="54">
@@ -1975,20 +1987,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1.679</v>
+        <v>-1.808</v>
       </c>
       <c r="E54" t="n">
-        <v>20.6</v>
+        <v>27.9</v>
       </c>
       <c r="F54" t="n">
         <v>0.233</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.62</v>
+        <v>-0.914</v>
       </c>
     </row>
     <row r="55">
@@ -2008,74 +2020,74 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.598</v>
+        <v>-1.779</v>
       </c>
       <c r="E55" t="n">
-        <v>32.1</v>
+        <v>31.5</v>
       </c>
       <c r="F55" t="n">
         <v>0.233</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.914</v>
+        <v>-1.016</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-1.895</v>
+        <v>9.124000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>27.8</v>
+        <v>35.7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.233</v>
+        <v>0.8</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.962</v>
+        <v>7.375</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-3.158</v>
+        <v>2.016</v>
       </c>
       <c r="E57" t="n">
-        <v>21.4</v>
+        <v>28.2</v>
       </c>
       <c r="F57" t="n">
-        <v>0.233</v>
+        <v>0.8</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.306</v>
+        <v>1.654</v>
       </c>
     </row>
     <row r="58">
@@ -2091,20 +2103,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17.996</v>
+        <v>0.429</v>
       </c>
       <c r="E58" t="n">
-        <v>35.9</v>
+        <v>24.1</v>
       </c>
       <c r="F58" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G58" t="n">
-        <v>14.079</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="59">
@@ -2120,20 +2132,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>9.311999999999999</v>
+        <v>-0.672</v>
       </c>
       <c r="E59" t="n">
-        <v>35.2</v>
+        <v>29.4</v>
       </c>
       <c r="F59" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>7.435</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="60">
@@ -2149,20 +2161,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Jalen Pickett</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.376</v>
+        <v>-1.603</v>
       </c>
       <c r="E60" t="n">
-        <v>27.4</v>
+        <v>15.7</v>
       </c>
       <c r="F60" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G60" t="n">
-        <v>1.836</v>
+        <v>-0.262</v>
       </c>
     </row>
     <row r="61">
@@ -2178,20 +2190,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.446</v>
+        <v>-2.354</v>
       </c>
       <c r="E61" t="n">
-        <v>24</v>
+        <v>15.7</v>
       </c>
       <c r="F61" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.641</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="62">
@@ -2207,20 +2219,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-0.828</v>
+        <v>-1.69</v>
       </c>
       <c r="E62" t="n">
-        <v>28.3</v>
+        <v>31.9</v>
       </c>
       <c r="F62" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G62" t="n">
-        <v>0.003</v>
+        <v>-0.591</v>
       </c>
     </row>
     <row r="63">
@@ -2236,78 +2248,78 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Julian Strawther</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-2.351</v>
+        <v>-2.752</v>
       </c>
       <c r="E63" t="n">
-        <v>15.7</v>
+        <v>20.1</v>
       </c>
       <c r="F63" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.495</v>
+        <v>-0.819</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1.872</v>
+        <v>5.511</v>
       </c>
       <c r="E64" t="n">
-        <v>31.9</v>
+        <v>29.4</v>
       </c>
       <c r="F64" t="n">
-        <v>0.833</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.952</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-2.691</v>
+        <v>1.708</v>
       </c>
       <c r="E65" t="n">
-        <v>21.4</v>
+        <v>25.9</v>
       </c>
       <c r="F65" t="n">
-        <v>0.833</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.828</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="66">
@@ -2323,20 +2335,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.518</v>
+        <v>0.177</v>
       </c>
       <c r="E66" t="n">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="F66" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>3.968</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="67">
@@ -2352,20 +2364,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.655</v>
+        <v>-0.039</v>
       </c>
       <c r="E67" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="F67" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>1.434</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="68">
@@ -2381,20 +2393,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-0.036</v>
+        <v>-0.059</v>
       </c>
       <c r="E68" t="n">
-        <v>26.7</v>
+        <v>25.7</v>
       </c>
       <c r="F68" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.498</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="69">
@@ -2410,20 +2422,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.057</v>
+        <v>-0.136</v>
       </c>
       <c r="E69" t="n">
-        <v>25.7</v>
+        <v>23.8</v>
       </c>
       <c r="F69" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>0.47</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="70">
@@ -2439,20 +2451,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Colby Jones</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.227</v>
+        <v>-0.917</v>
       </c>
       <c r="E70" t="n">
-        <v>30.7</v>
+        <v>23.4</v>
       </c>
       <c r="F70" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0.452</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="71">
@@ -2468,78 +2480,78 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Caris LeVert</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.001</v>
+        <v>-1.611</v>
       </c>
       <c r="E71" t="n">
-        <v>23.1</v>
+        <v>19</v>
       </c>
       <c r="F71" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0.449</v>
+        <v>-0.269</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Colby Jones</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-0.919</v>
+        <v>7.585</v>
       </c>
       <c r="E72" t="n">
-        <v>23.4</v>
+        <v>30.4</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>0.007</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Caris LeVert</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-1.608</v>
+        <v>4.1</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>22.8</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.268</v>
+        <v>2.139</v>
       </c>
     </row>
     <row r="74">
@@ -2555,20 +2567,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.535</v>
+        <v>2.1</v>
       </c>
       <c r="E74" t="n">
-        <v>22.1</v>
+        <v>31.9</v>
       </c>
       <c r="F74" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G74" t="n">
-        <v>2.289</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="75">
@@ -2584,20 +2596,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Gary Payton II</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.986</v>
+        <v>2.851</v>
       </c>
       <c r="E75" t="n">
-        <v>32.2</v>
+        <v>23.2</v>
       </c>
       <c r="F75" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G75" t="n">
-        <v>1.621</v>
+        <v>1.572</v>
       </c>
     </row>
     <row r="76">
@@ -2613,20 +2625,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gary Payton II</t>
+          <t>Pat Spencer</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2.884</v>
+        <v>-0.395</v>
       </c>
       <c r="E76" t="n">
         <v>22.1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G76" t="n">
-        <v>1.531</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="77">
@@ -2642,20 +2654,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.602</v>
+        <v>-0.471</v>
       </c>
       <c r="E77" t="n">
-        <v>32.8</v>
+        <v>30.6</v>
       </c>
       <c r="F77" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>0.707</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="78">
@@ -2671,20 +2683,20 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pat Spencer</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.513</v>
+        <v>-1.095</v>
       </c>
       <c r="E78" t="n">
-        <v>22.1</v>
+        <v>25.2</v>
       </c>
       <c r="F78" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.037</v>
+        <v>-0.364</v>
       </c>
     </row>
     <row r="79">
@@ -2700,78 +2712,78 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Will Richard</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-1.357</v>
       </c>
       <c r="E79" t="n">
-        <v>29.9</v>
+        <v>23.8</v>
       </c>
       <c r="F79" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.081</v>
+        <v>-0.474</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-0.884</v>
+        <v>6.705</v>
       </c>
       <c r="E80" t="n">
-        <v>25.1</v>
+        <v>35</v>
       </c>
       <c r="F80" t="n">
-        <v>0.433</v>
+        <v>0.833</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.236</v>
+        <v>5.493</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Will Richard</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-1.207</v>
+        <v>6.323</v>
       </c>
       <c r="E81" t="n">
-        <v>24.6</v>
+        <v>31.9</v>
       </c>
       <c r="F81" t="n">
-        <v>0.433</v>
+        <v>0.833</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.397</v>
+        <v>4.749</v>
       </c>
     </row>
     <row r="82">
@@ -2787,20 +2799,20 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6.619</v>
+        <v>3.896</v>
       </c>
       <c r="E82" t="n">
-        <v>35.6</v>
+        <v>37.9</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G82" t="n">
-        <v>5.499</v>
+        <v>3.737</v>
       </c>
     </row>
     <row r="83">
@@ -2816,20 +2828,20 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6.397</v>
+        <v>3.663</v>
       </c>
       <c r="E83" t="n">
-        <v>32.5</v>
+        <v>29.6</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G83" t="n">
-        <v>4.881</v>
+        <v>2.776</v>
       </c>
     </row>
     <row r="84">
@@ -2845,20 +2857,20 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3.838</v>
+        <v>-0.477</v>
       </c>
       <c r="E84" t="n">
-        <v>38.4</v>
+        <v>35.6</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G84" t="n">
-        <v>3.713</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="85">
@@ -2874,20 +2886,20 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.582</v>
+        <v>-1.754</v>
       </c>
       <c r="E85" t="n">
-        <v>30.1</v>
+        <v>24.2</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G85" t="n">
-        <v>2.748</v>
+        <v>-0.465</v>
       </c>
     </row>
     <row r="86">
@@ -2903,20 +2915,20 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Josh Okogie</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-0.477</v>
+        <v>-2.961</v>
       </c>
       <c r="E86" t="n">
-        <v>36.8</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G86" t="n">
-        <v>0.248</v>
+        <v>-0.707</v>
       </c>
     </row>
     <row r="87">
@@ -2932,78 +2944,78 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Dorian Finney-Smith</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-1.862</v>
+        <v>-6.804</v>
       </c>
       <c r="E87" t="n">
-        <v>24.5</v>
+        <v>18.3</v>
       </c>
       <c r="F87" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.541</v>
+        <v>-2.273</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Josh Okogie</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-2.959</v>
+        <v>2.004</v>
       </c>
       <c r="E88" t="n">
-        <v>16</v>
+        <v>22.2</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8</v>
+        <v>0.167</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.717</v>
+        <v>1.005</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dorian Finney-Smith</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-6.802</v>
+        <v>1.915</v>
       </c>
       <c r="E89" t="n">
-        <v>18.3</v>
+        <v>16.7</v>
       </c>
       <c r="F89" t="n">
-        <v>0.8</v>
+        <v>0.167</v>
       </c>
       <c r="G89" t="n">
-        <v>-2.285</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="90">
@@ -3019,20 +3031,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.129</v>
+        <v>1.944</v>
       </c>
       <c r="E90" t="n">
-        <v>22.3</v>
+        <v>16.1</v>
       </c>
       <c r="F90" t="n">
         <v>0.167</v>
       </c>
       <c r="G90" t="n">
-        <v>1.066</v>
+        <v>0.709</v>
       </c>
     </row>
     <row r="91">
@@ -3048,20 +3060,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.25</v>
+        <v>-0.179</v>
       </c>
       <c r="E91" t="n">
-        <v>17</v>
+        <v>18.2</v>
       </c>
       <c r="F91" t="n">
         <v>0.167</v>
       </c>
       <c r="G91" t="n">
-        <v>0.854</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="92">
@@ -3077,20 +3089,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Obi Toppin</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2.005</v>
+        <v>-1.735</v>
       </c>
       <c r="E92" t="n">
-        <v>16.4</v>
+        <v>22.3</v>
       </c>
       <c r="F92" t="n">
         <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>0.741</v>
+        <v>-0.727</v>
       </c>
     </row>
     <row r="93">
@@ -3106,20 +3118,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-1.51</v>
       </c>
       <c r="E93" t="n">
-        <v>18.4</v>
+        <v>31.4</v>
       </c>
       <c r="F93" t="n">
         <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.152</v>
+        <v>-0.878</v>
       </c>
     </row>
     <row r="94">
@@ -3135,20 +3147,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-1.79</v>
+        <v>-3.034</v>
       </c>
       <c r="E94" t="n">
-        <v>22.2</v>
+        <v>18.6</v>
       </c>
       <c r="F94" t="n">
         <v>0.167</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.75</v>
+        <v>-1.113</v>
       </c>
     </row>
     <row r="95">
@@ -3164,78 +3176,78 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Kam Jones</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.965</v>
+        <v>-2.973</v>
       </c>
       <c r="E95" t="n">
-        <v>17.9</v>
+        <v>21.9</v>
       </c>
       <c r="F95" t="n">
         <v>0.167</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.042</v>
+        <v>-1.279</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.789</v>
+        <v>11.751</v>
       </c>
       <c r="E96" t="n">
-        <v>19.9</v>
+        <v>30.6</v>
       </c>
       <c r="F96" t="n">
-        <v>0.167</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.089</v>
+        <v>7.841</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kam Jones</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-3.628</v>
+        <v>3.334</v>
       </c>
       <c r="E97" t="n">
-        <v>21.8</v>
+        <v>28.8</v>
       </c>
       <c r="F97" t="n">
-        <v>0.167</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G97" t="n">
-        <v>-1.572</v>
+        <v>2.342</v>
       </c>
     </row>
     <row r="98">
@@ -3251,20 +3263,20 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.625</v>
+        <v>0.472</v>
       </c>
       <c r="E98" t="n">
-        <v>30.4</v>
+        <v>26.6</v>
       </c>
       <c r="F98" t="n">
-        <v>0.633</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>7.757</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="99">
@@ -3280,20 +3292,20 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3.667</v>
+        <v>0.314</v>
       </c>
       <c r="E99" t="n">
-        <v>28.4</v>
+        <v>24.8</v>
       </c>
       <c r="F99" t="n">
-        <v>0.633</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G99" t="n">
-        <v>2.547</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="100">
@@ -3309,20 +3321,20 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.458</v>
+        <v>-0.141</v>
       </c>
       <c r="E100" t="n">
-        <v>26.9</v>
+        <v>28.8</v>
       </c>
       <c r="F100" t="n">
-        <v>0.633</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>0.612</v>
+        <v>0.256</v>
       </c>
     </row>
     <row r="101">
@@ -3338,20 +3350,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.477</v>
+        <v>-0.294</v>
       </c>
       <c r="E101" t="n">
-        <v>24.9</v>
+        <v>25.7</v>
       </c>
       <c r="F101" t="n">
-        <v>0.633</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>0.576</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="102">
@@ -3367,20 +3379,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.05</v>
+        <v>-0.473</v>
       </c>
       <c r="E102" t="n">
-        <v>29.5</v>
+        <v>26.9</v>
       </c>
       <c r="F102" t="n">
-        <v>0.633</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G102" t="n">
-        <v>0.42</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="103">
@@ -3396,78 +3408,78 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-0.283</v>
+        <v>-1.54</v>
       </c>
       <c r="E103" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="F103" t="n">
-        <v>0.633</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>0.201</v>
+        <v>-0.578</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.278</v>
+        <v>2.267</v>
       </c>
       <c r="E104" t="n">
-        <v>26.4</v>
+        <v>21.2</v>
       </c>
       <c r="F104" t="n">
         <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>0.195</v>
+        <v>1.281</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-1.642</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="E105" t="n">
-        <v>28.9</v>
+        <v>22.4</v>
       </c>
       <c r="F105" t="n">
         <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.608</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="106">
@@ -3483,20 +3495,20 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5.956</v>
+        <v>0.211</v>
       </c>
       <c r="E106" t="n">
-        <v>34</v>
+        <v>25.7</v>
       </c>
       <c r="F106" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G106" t="n">
-        <v>4.689</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="107">
@@ -3512,20 +3524,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2.306</v>
+        <v>-1.288</v>
       </c>
       <c r="E107" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="F107" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G107" t="n">
-        <v>1.279</v>
+        <v>-0.286</v>
       </c>
     </row>
     <row r="108">
@@ -3541,20 +3553,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Dalton Knecht</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.724</v>
+        <v>-1.863</v>
       </c>
       <c r="E108" t="n">
-        <v>21.6</v>
+        <v>15.8</v>
       </c>
       <c r="F108" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G108" t="n">
-        <v>0.625</v>
+        <v>-0.404</v>
       </c>
     </row>
     <row r="109">
@@ -3570,20 +3582,20 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Jarred Vanderbilt</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.237</v>
+        <v>-2.217</v>
       </c>
       <c r="E109" t="n">
-        <v>25.6</v>
+        <v>15.4</v>
       </c>
       <c r="F109" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G109" t="n">
-        <v>0.482</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="110">
@@ -3599,20 +3611,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>-1.181</v>
+        <v>-2.479</v>
       </c>
       <c r="E110" t="n">
-        <v>19.5</v>
+        <v>24.2</v>
       </c>
       <c r="F110" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.209</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="111">
@@ -3628,78 +3640,78 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dalton Knecht</t>
+          <t>Maxi Kleber</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-1.862</v>
+        <v>-6.512</v>
       </c>
       <c r="E111" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="F111" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.393</v>
+        <v>-1.894</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-2.378</v>
+        <v>1.213</v>
       </c>
       <c r="E112" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="F112" t="n">
-        <v>0.667</v>
+        <v>0.267</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.872</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Maxi Kleber</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-6.511</v>
+        <v>0.124</v>
       </c>
       <c r="E113" t="n">
-        <v>15.5</v>
+        <v>23.9</v>
       </c>
       <c r="F113" t="n">
-        <v>0.667</v>
+        <v>0.267</v>
       </c>
       <c r="G113" t="n">
-        <v>-1.883</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="114">
@@ -3715,20 +3727,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Walter Clayton Jr.</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.009</v>
+        <v>-1.95</v>
       </c>
       <c r="E114" t="n">
-        <v>25.4</v>
+        <v>24.9</v>
       </c>
       <c r="F114" t="n">
         <v>0.267</v>
       </c>
       <c r="G114" t="n">
-        <v>0.675</v>
+        <v>-0.874</v>
       </c>
     </row>
     <row r="115">
@@ -3744,20 +3756,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Taylor Hendricks</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.2</v>
+        <v>-1.942</v>
       </c>
       <c r="E115" t="n">
-        <v>23.9</v>
+        <v>25.3</v>
       </c>
       <c r="F115" t="n">
         <v>0.267</v>
       </c>
       <c r="G115" t="n">
-        <v>0.233</v>
+        <v>-0.883</v>
       </c>
     </row>
     <row r="116">
@@ -3773,107 +3785,107 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Rayan Rupert</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-0.133</v>
+        <v>-5.725</v>
       </c>
       <c r="E116" t="n">
-        <v>25.6</v>
+        <v>26.7</v>
       </c>
       <c r="F116" t="n">
         <v>0.267</v>
       </c>
       <c r="G116" t="n">
-        <v>0.07099999999999999</v>
+        <v>-3.034</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-1.823</v>
+        <v>3.012</v>
       </c>
       <c r="E117" t="n">
-        <v>25.1</v>
+        <v>35.7</v>
       </c>
       <c r="F117" t="n">
-        <v>0.267</v>
+        <v>0.533</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.8149999999999999</v>
+        <v>2.639</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Walter Clayton Jr.</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-2.2</v>
+        <v>2.269</v>
       </c>
       <c r="E118" t="n">
-        <v>25.8</v>
+        <v>32.7</v>
       </c>
       <c r="F118" t="n">
-        <v>0.267</v>
+        <v>0.533</v>
       </c>
       <c r="G118" t="n">
-        <v>-1.037</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rayan Rupert</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-5.478</v>
+        <v>2.403</v>
       </c>
       <c r="E119" t="n">
-        <v>25.4</v>
+        <v>28.3</v>
       </c>
       <c r="F119" t="n">
-        <v>0.267</v>
+        <v>0.533</v>
       </c>
       <c r="G119" t="n">
-        <v>-2.762</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="120">
@@ -3889,20 +3901,20 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>3.015</v>
+        <v>1.716</v>
       </c>
       <c r="E120" t="n">
-        <v>35.7</v>
+        <v>28.6</v>
       </c>
       <c r="F120" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.533</v>
       </c>
       <c r="G120" t="n">
-        <v>2.666</v>
+        <v>1.339</v>
       </c>
     </row>
     <row r="121">
@@ -3918,20 +3930,20 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2.271</v>
+        <v>2.335</v>
       </c>
       <c r="E121" t="n">
-        <v>32.7</v>
+        <v>22</v>
       </c>
       <c r="F121" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.533</v>
       </c>
       <c r="G121" t="n">
-        <v>1.935</v>
+        <v>1.315</v>
       </c>
     </row>
     <row r="122">
@@ -3947,20 +3959,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1.718</v>
+        <v>1.015</v>
       </c>
       <c r="E122" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="F122" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.533</v>
       </c>
       <c r="G122" t="n">
-        <v>1.361</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="123">
@@ -3976,20 +3988,20 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.338</v>
+        <v>0.411</v>
       </c>
       <c r="E123" t="n">
-        <v>22</v>
+        <v>28.7</v>
       </c>
       <c r="F123" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.533</v>
       </c>
       <c r="G123" t="n">
-        <v>1.332</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -4005,107 +4017,107 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1.017</v>
+        <v>-0.52</v>
       </c>
       <c r="E124" t="n">
-        <v>26.8</v>
+        <v>31.6</v>
       </c>
       <c r="F124" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.533</v>
       </c>
       <c r="G124" t="n">
-        <v>0.886</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.414</v>
+        <v>-0.629</v>
       </c>
       <c r="E125" t="n">
-        <v>28.7</v>
+        <v>23.8</v>
       </c>
       <c r="F125" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="G125" t="n">
-        <v>0.586</v>
+        <v>-0.213</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Cole Anthony</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-0.517</v>
+        <v>-2.029</v>
       </c>
       <c r="E126" t="n">
-        <v>31.6</v>
+        <v>15.7</v>
       </c>
       <c r="F126" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="G126" t="n">
-        <v>0.033</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kasparas Jakučionis</t>
+          <t>Gary Harris</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>-0.644</v>
+        <v>-3.391</v>
       </c>
       <c r="E127" t="n">
-        <v>19</v>
+        <v>15.4</v>
       </c>
       <c r="F127" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.031</v>
+        <v>-1.021</v>
       </c>
     </row>
     <row r="128">
@@ -4121,20 +4133,20 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3.881</v>
+        <v>-3.637</v>
       </c>
       <c r="E128" t="n">
-        <v>31.3</v>
+        <v>16.3</v>
       </c>
       <c r="F128" t="n">
         <v>0.2</v>
       </c>
       <c r="G128" t="n">
-        <v>2.665</v>
+        <v>-1.168</v>
       </c>
     </row>
     <row r="129">
@@ -4150,11 +4162,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.619</v>
+        <v>-2.615</v>
       </c>
       <c r="E129" t="n">
         <v>23.3</v>
@@ -4163,7 +4175,7 @@
         <v>0.2</v>
       </c>
       <c r="G129" t="n">
-        <v>0.397</v>
+        <v>-1.171</v>
       </c>
     </row>
     <row r="130">
@@ -4179,20 +4191,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>-0.312</v>
+        <v>-2.483</v>
       </c>
       <c r="E130" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="F130" t="n">
         <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>-0.058</v>
+        <v>-1.184</v>
       </c>
     </row>
     <row r="131">
@@ -4208,20 +4220,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-0.673</v>
+        <v>-3.168</v>
       </c>
       <c r="E131" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="F131" t="n">
         <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.222</v>
+        <v>-1.387</v>
       </c>
     </row>
     <row r="132">
@@ -4241,103 +4253,103 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-2.167</v>
+        <v>-2.561</v>
       </c>
       <c r="E132" t="n">
-        <v>29.5</v>
+        <v>29.1</v>
       </c>
       <c r="F132" t="n">
         <v>0.2</v>
       </c>
       <c r="G132" t="n">
-        <v>-1.209</v>
+        <v>-1.433</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-2.619</v>
+        <v>3.993</v>
       </c>
       <c r="E133" t="n">
-        <v>24.2</v>
+        <v>31.8</v>
       </c>
       <c r="F133" t="n">
-        <v>0.2</v>
+        <v>0.733</v>
       </c>
       <c r="G133" t="n">
-        <v>-1.221</v>
+        <v>3.135</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.721</v>
+        <v>2.946</v>
       </c>
       <c r="E134" t="n">
-        <v>23.7</v>
+        <v>29.2</v>
       </c>
       <c r="F134" t="n">
-        <v>0.2</v>
+        <v>0.733</v>
       </c>
       <c r="G134" t="n">
-        <v>-1.245</v>
+        <v>2.235</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-4.055</v>
+        <v>1.347</v>
       </c>
       <c r="E135" t="n">
-        <v>21.9</v>
+        <v>29.7</v>
       </c>
       <c r="F135" t="n">
-        <v>0.2</v>
+        <v>0.733</v>
       </c>
       <c r="G135" t="n">
-        <v>-1.763</v>
+        <v>1.289</v>
       </c>
     </row>
     <row r="136">
@@ -4353,20 +4365,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>7.217</v>
+        <v>1.588</v>
       </c>
       <c r="E136" t="n">
-        <v>34.8</v>
+        <v>25.6</v>
       </c>
       <c r="F136" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="G136" t="n">
-        <v>5.787</v>
+        <v>1.239</v>
       </c>
     </row>
     <row r="137">
@@ -4382,20 +4394,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>4.064</v>
+        <v>1.427</v>
       </c>
       <c r="E137" t="n">
-        <v>31.8</v>
+        <v>21.7</v>
       </c>
       <c r="F137" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="G137" t="n">
-        <v>3.202</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="138">
@@ -4411,20 +4423,20 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2.981</v>
+        <v>0.638</v>
       </c>
       <c r="E138" t="n">
-        <v>28.3</v>
+        <v>30.7</v>
       </c>
       <c r="F138" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="G138" t="n">
-        <v>2.212</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="139">
@@ -4440,20 +4452,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1.471</v>
+        <v>-0.228</v>
       </c>
       <c r="E139" t="n">
-        <v>29.8</v>
+        <v>18.2</v>
       </c>
       <c r="F139" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="G139" t="n">
-        <v>1.391</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="140">
@@ -4469,107 +4481,107 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Mike Conley</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1.742</v>
+        <v>-2.12</v>
       </c>
       <c r="E140" t="n">
-        <v>25.6</v>
+        <v>17</v>
       </c>
       <c r="F140" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="G140" t="n">
-        <v>1.34</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.783</v>
+        <v>4.617</v>
       </c>
       <c r="E141" t="n">
-        <v>30.5</v>
+        <v>30.1</v>
       </c>
       <c r="F141" t="n">
-        <v>0.767</v>
+        <v>0.333</v>
       </c>
       <c r="G141" t="n">
-        <v>0.986</v>
+        <v>3.108</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1.201</v>
+        <v>2.221</v>
       </c>
       <c r="E142" t="n">
-        <v>20.5</v>
+        <v>32</v>
       </c>
       <c r="F142" t="n">
-        <v>0.767</v>
+        <v>0.333</v>
       </c>
       <c r="G142" t="n">
-        <v>0.84</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>-0.223</v>
+        <v>1.002</v>
       </c>
       <c r="E143" t="n">
-        <v>18.4</v>
+        <v>20.1</v>
       </c>
       <c r="F143" t="n">
-        <v>0.767</v>
+        <v>0.333</v>
       </c>
       <c r="G143" t="n">
-        <v>0.208</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="144">
@@ -4585,20 +4597,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4.783</v>
+        <v>-0.355</v>
       </c>
       <c r="E144" t="n">
-        <v>34.1</v>
+        <v>20.8</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G144" t="n">
-        <v>3.611</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="145">
@@ -4614,20 +4626,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4.769</v>
+        <v>-0.986</v>
       </c>
       <c r="E145" t="n">
-        <v>30.5</v>
+        <v>22.7</v>
       </c>
       <c r="F145" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G145" t="n">
-        <v>3.216</v>
+        <v>-0.309</v>
       </c>
     </row>
     <row r="146">
@@ -4643,20 +4655,20 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2.603</v>
+        <v>-2.677</v>
       </c>
       <c r="E146" t="n">
-        <v>30.5</v>
+        <v>19.9</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G146" t="n">
-        <v>1.842</v>
+        <v>-0.971</v>
       </c>
     </row>
     <row r="147">
@@ -4672,20 +4684,20 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2.204</v>
+        <v>-3.19</v>
       </c>
       <c r="E147" t="n">
-        <v>32.5</v>
+        <v>28</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G147" t="n">
-        <v>1.694</v>
+        <v>-1.665</v>
       </c>
     </row>
     <row r="148">
@@ -4701,107 +4713,107 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Jordan Hawkins</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-0.289</v>
+        <v>-6.227</v>
       </c>
       <c r="E148" t="n">
-        <v>19.9</v>
+        <v>15.6</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G148" t="n">
-        <v>0.004</v>
+        <v>-1.911</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-1.232</v>
+        <v>6.369</v>
       </c>
       <c r="E149" t="n">
-        <v>21.5</v>
+        <v>36.4</v>
       </c>
       <c r="F149" t="n">
-        <v>0.3</v>
+        <v>0.867</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.418</v>
+        <v>5.483</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-2.674</v>
+        <v>4.255</v>
       </c>
       <c r="E150" t="n">
-        <v>19.9</v>
+        <v>29.9</v>
       </c>
       <c r="F150" t="n">
-        <v>0.3</v>
+        <v>0.867</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.984</v>
+        <v>3.195</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-3.156</v>
+        <v>2.984</v>
       </c>
       <c r="E151" t="n">
-        <v>29.3</v>
+        <v>29.7</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3</v>
+        <v>0.867</v>
       </c>
       <c r="G151" t="n">
-        <v>-1.745</v>
+        <v>2.384</v>
       </c>
     </row>
     <row r="152">
@@ -4817,20 +4829,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>6.404</v>
+        <v>2.848</v>
       </c>
       <c r="E152" t="n">
-        <v>36.5</v>
+        <v>30.1</v>
       </c>
       <c r="F152" t="n">
         <v>0.867</v>
       </c>
       <c r="G152" t="n">
-        <v>5.536</v>
+        <v>2.326</v>
       </c>
     </row>
     <row r="153">
@@ -4846,20 +4858,20 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4.168</v>
+        <v>2.018</v>
       </c>
       <c r="E153" t="n">
-        <v>29.9</v>
+        <v>34.3</v>
       </c>
       <c r="F153" t="n">
         <v>0.867</v>
       </c>
       <c r="G153" t="n">
-        <v>3.131</v>
+        <v>2.063</v>
       </c>
     </row>
     <row r="154">
@@ -4875,20 +4887,20 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2.971</v>
+        <v>3.283</v>
       </c>
       <c r="E154" t="n">
-        <v>31.2</v>
+        <v>19.9</v>
       </c>
       <c r="F154" t="n">
         <v>0.867</v>
       </c>
       <c r="G154" t="n">
-        <v>2.493</v>
+        <v>1.723</v>
       </c>
     </row>
     <row r="155">
@@ -4904,20 +4916,20 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3.047</v>
+        <v>0.361</v>
       </c>
       <c r="E155" t="n">
-        <v>29.5</v>
+        <v>26.8</v>
       </c>
       <c r="F155" t="n">
         <v>0.867</v>
       </c>
       <c r="G155" t="n">
-        <v>2.406</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -4933,107 +4945,107 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1.75</v>
+        <v>-1.099</v>
       </c>
       <c r="E156" t="n">
-        <v>34.8</v>
+        <v>24.4</v>
       </c>
       <c r="F156" t="n">
         <v>0.867</v>
       </c>
       <c r="G156" t="n">
-        <v>1.898</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2.991</v>
+        <v>14.773</v>
       </c>
       <c r="E157" t="n">
-        <v>19.4</v>
+        <v>34.1</v>
       </c>
       <c r="F157" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>1.563</v>
+        <v>11.191</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.197</v>
+        <v>3.869</v>
       </c>
       <c r="E158" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F158" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>0.622</v>
+        <v>2.921</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-1.2</v>
+        <v>3.4</v>
       </c>
       <c r="E159" t="n">
-        <v>25.1</v>
+        <v>22.3</v>
       </c>
       <c r="F159" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.175</v>
+        <v>2.044</v>
       </c>
     </row>
     <row r="160">
@@ -5049,20 +5061,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>14.849</v>
+        <v>1.816</v>
       </c>
       <c r="E160" t="n">
-        <v>34.3</v>
+        <v>25.4</v>
       </c>
       <c r="F160" t="n">
         <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>11.332</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="161">
@@ -5078,20 +5090,20 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3.938</v>
+        <v>1.548</v>
       </c>
       <c r="E161" t="n">
-        <v>29.9</v>
+        <v>21.1</v>
       </c>
       <c r="F161" t="n">
         <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>3.078</v>
+        <v>1.119</v>
       </c>
     </row>
     <row r="162">
@@ -5107,20 +5119,20 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>3.205</v>
+        <v>0.397</v>
       </c>
       <c r="E162" t="n">
-        <v>22.4</v>
+        <v>19.6</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>1.962</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="163">
@@ -5136,20 +5148,20 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1.751</v>
+        <v>-0.021</v>
       </c>
       <c r="E163" t="n">
-        <v>27.2</v>
+        <v>24.5</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1.56</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="164">
@@ -5165,107 +5177,107 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1.798</v>
+        <v>-4.439</v>
       </c>
       <c r="E164" t="n">
-        <v>26.3</v>
+        <v>24.7</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>1.535</v>
+        <v>-1.773</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.205</v>
+        <v>3.246</v>
       </c>
       <c r="E165" t="n">
-        <v>21.6</v>
+        <v>33.9</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G165" t="n">
-        <v>0.993</v>
+        <v>2.601</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-0.045</v>
+        <v>3.03</v>
       </c>
       <c r="E166" t="n">
-        <v>25.1</v>
+        <v>35.2</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G166" t="n">
-        <v>0.499</v>
+        <v>2.537</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-4.619</v>
+        <v>2.939</v>
       </c>
       <c r="E167" t="n">
-        <v>25.2</v>
+        <v>30.6</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G167" t="n">
-        <v>-1.902</v>
+        <v>2.149</v>
       </c>
     </row>
     <row r="168">
@@ -5281,20 +5293,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3.186</v>
+        <v>1.676</v>
       </c>
       <c r="E168" t="n">
-        <v>34.8</v>
+        <v>26</v>
       </c>
       <c r="F168" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G168" t="n">
-        <v>2.601</v>
+        <v>1.143</v>
       </c>
     </row>
     <row r="169">
@@ -5310,20 +5322,20 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3.04</v>
+        <v>0.312</v>
       </c>
       <c r="E169" t="n">
-        <v>33.6</v>
+        <v>30.1</v>
       </c>
       <c r="F169" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G169" t="n">
-        <v>2.411</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="170">
@@ -5339,20 +5351,20 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2.978</v>
+        <v>-0.644</v>
       </c>
       <c r="E170" t="n">
         <v>30.1</v>
       </c>
       <c r="F170" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G170" t="n">
-        <v>2.12</v>
+        <v>-0.132</v>
       </c>
     </row>
     <row r="171">
@@ -5368,20 +5380,20 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1.644</v>
+        <v>-1.171</v>
       </c>
       <c r="E171" t="n">
-        <v>27.3</v>
+        <v>28.7</v>
       </c>
       <c r="F171" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G171" t="n">
-        <v>1.163</v>
+        <v>-0.442</v>
       </c>
     </row>
     <row r="172">
@@ -5397,107 +5409,107 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Orlando Robinson</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-0.658</v>
+        <v>-2.273</v>
       </c>
       <c r="E172" t="n">
-        <v>28.8</v>
+        <v>22.2</v>
       </c>
       <c r="F172" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="G172" t="n">
-        <v>-0.155</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-1.115</v>
+        <v>9.098000000000001</v>
       </c>
       <c r="E173" t="n">
-        <v>29.5</v>
+        <v>36.5</v>
       </c>
       <c r="F173" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G173" t="n">
-        <v>-0.44</v>
+        <v>7.268</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-1.664</v>
+        <v>5.211</v>
       </c>
       <c r="E174" t="n">
-        <v>20.3</v>
+        <v>34.2</v>
       </c>
       <c r="F174" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.536</v>
+        <v>4.046</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Orlando Robinson</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-2.275</v>
+        <v>2.811</v>
       </c>
       <c r="E175" t="n">
-        <v>22.2</v>
+        <v>32.4</v>
       </c>
       <c r="F175" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.866</v>
+        <v>2.216</v>
       </c>
     </row>
     <row r="176">
@@ -5513,20 +5525,20 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>9.199999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="E176" t="n">
-        <v>36.4</v>
+        <v>32.6</v>
       </c>
       <c r="F176" t="n">
         <v>0.467</v>
       </c>
       <c r="G176" t="n">
-        <v>7.337</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="177">
@@ -5542,20 +5554,20 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>5.192</v>
+        <v>-0.385</v>
       </c>
       <c r="E177" t="n">
-        <v>34.1</v>
+        <v>31.2</v>
       </c>
       <c r="F177" t="n">
         <v>0.467</v>
       </c>
       <c r="G177" t="n">
-        <v>4.022</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="178">
@@ -5571,20 +5583,20 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Eric Gordon</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2.736</v>
+        <v>-0.767</v>
       </c>
       <c r="E178" t="n">
-        <v>32.7</v>
+        <v>23</v>
       </c>
       <c r="F178" t="n">
         <v>0.467</v>
       </c>
       <c r="G178" t="n">
-        <v>2.182</v>
+        <v>-0.144</v>
       </c>
     </row>
     <row r="179">
@@ -5600,20 +5612,20 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.782</v>
+        <v>-1.381</v>
       </c>
       <c r="E179" t="n">
-        <v>32.9</v>
+        <v>23.7</v>
       </c>
       <c r="F179" t="n">
         <v>0.467</v>
       </c>
       <c r="G179" t="n">
-        <v>0.856</v>
+        <v>-0.451</v>
       </c>
     </row>
     <row r="180">
@@ -5629,107 +5641,107 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>-0.226</v>
+        <v>-1.51</v>
       </c>
       <c r="E180" t="n">
-        <v>32.1</v>
+        <v>29.9</v>
       </c>
       <c r="F180" t="n">
         <v>0.467</v>
       </c>
       <c r="G180" t="n">
-        <v>0.161</v>
+        <v>-0.649</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Eric Gordon</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-0.769</v>
+        <v>4.841</v>
       </c>
       <c r="E181" t="n">
-        <v>23</v>
+        <v>33.7</v>
       </c>
       <c r="F181" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.144</v>
+        <v>3.746</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-1.275</v>
+        <v>4.062</v>
       </c>
       <c r="E182" t="n">
-        <v>23.5</v>
+        <v>29.4</v>
       </c>
       <c r="F182" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.396</v>
+        <v>2.791</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-1.395</v>
+        <v>2.601</v>
       </c>
       <c r="E183" t="n">
-        <v>30.7</v>
+        <v>28.1</v>
       </c>
       <c r="F183" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.593</v>
+        <v>1.818</v>
       </c>
     </row>
     <row r="184">
@@ -5745,20 +5757,20 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4.902</v>
+        <v>0.844</v>
       </c>
       <c r="E184" t="n">
-        <v>33.4</v>
+        <v>23.7</v>
       </c>
       <c r="F184" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G184" t="n">
-        <v>3.784</v>
+        <v>0.662</v>
       </c>
     </row>
     <row r="185">
@@ -5774,20 +5786,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4.183</v>
+        <v>0.277</v>
       </c>
       <c r="E185" t="n">
-        <v>29.5</v>
+        <v>26.4</v>
       </c>
       <c r="F185" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G185" t="n">
-        <v>2.894</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="186">
@@ -5803,20 +5815,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2.739</v>
+        <v>-0.385</v>
       </c>
       <c r="E186" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="F186" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G186" t="n">
-        <v>1.972</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="187">
@@ -5832,20 +5844,20 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.921</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="E187" t="n">
-        <v>24.7</v>
+        <v>30.2</v>
       </c>
       <c r="F187" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G187" t="n">
-        <v>0.748</v>
+        <v>-0.277</v>
       </c>
     </row>
     <row r="188">
@@ -5861,107 +5873,107 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.363</v>
+        <v>-2.124</v>
       </c>
       <c r="E188" t="n">
-        <v>26.7</v>
+        <v>29.5</v>
       </c>
       <c r="F188" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G188" t="n">
-        <v>0.5</v>
+        <v>-0.997</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>-0.334</v>
+        <v>5.757</v>
       </c>
       <c r="E189" t="n">
-        <v>29.3</v>
+        <v>29.8</v>
       </c>
       <c r="F189" t="n">
-        <v>0.533</v>
+        <v>0.367</v>
       </c>
       <c r="G189" t="n">
-        <v>0.122</v>
+        <v>3.803</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>-1.422</v>
+        <v>5.996</v>
       </c>
       <c r="E190" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F190" t="n">
-        <v>0.533</v>
+        <v>0.367</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.555</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>-2.113</v>
+        <v>3.313</v>
       </c>
       <c r="E191" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="F191" t="n">
-        <v>0.533</v>
+        <v>0.367</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.982</v>
+        <v>2.299</v>
       </c>
     </row>
     <row r="192">
@@ -5977,20 +5989,20 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>5.747</v>
+        <v>3.097</v>
       </c>
       <c r="E192" t="n">
-        <v>29.4</v>
+        <v>26.4</v>
       </c>
       <c r="F192" t="n">
         <v>0.367</v>
       </c>
       <c r="G192" t="n">
-        <v>3.739</v>
+        <v>1.907</v>
       </c>
     </row>
     <row r="193">
@@ -6006,20 +6018,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>6.038</v>
+        <v>-1.27</v>
       </c>
       <c r="E193" t="n">
-        <v>18.5</v>
+        <v>31.6</v>
       </c>
       <c r="F193" t="n">
         <v>0.367</v>
       </c>
       <c r="G193" t="n">
-        <v>2.468</v>
+        <v>-0.596</v>
       </c>
     </row>
     <row r="194">
@@ -6035,20 +6047,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3.152</v>
+        <v>-2.075</v>
       </c>
       <c r="E194" t="n">
-        <v>29.6</v>
+        <v>24.1</v>
       </c>
       <c r="F194" t="n">
         <v>0.367</v>
       </c>
       <c r="G194" t="n">
-        <v>2.172</v>
+        <v>-0.857</v>
       </c>
     </row>
     <row r="195">
@@ -6064,20 +6076,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3.179</v>
+        <v>-3.273</v>
       </c>
       <c r="E195" t="n">
-        <v>25.8</v>
+        <v>19.1</v>
       </c>
       <c r="F195" t="n">
         <v>0.367</v>
       </c>
       <c r="G195" t="n">
-        <v>1.903</v>
+        <v>-1.155</v>
       </c>
     </row>
     <row r="196">
@@ -6093,107 +6105,107 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Caleb Love</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>-1.408</v>
+        <v>-2.973</v>
       </c>
       <c r="E196" t="n">
-        <v>31.7</v>
+        <v>24.1</v>
       </c>
       <c r="F196" t="n">
         <v>0.367</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-1.308</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>-2.33</v>
+        <v>0.461</v>
       </c>
       <c r="E197" t="n">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
       <c r="F197" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.996</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-3.312</v>
+        <v>0.193</v>
       </c>
       <c r="E198" t="n">
-        <v>19.6</v>
+        <v>32.1</v>
       </c>
       <c r="F198" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G198" t="n">
-        <v>-1.203</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Caleb Love</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-2.97</v>
+        <v>0.058</v>
       </c>
       <c r="E199" t="n">
-        <v>24.1</v>
+        <v>20.6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G199" t="n">
-        <v>-1.306</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="200">
@@ -6209,20 +6221,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>2.804</v>
+        <v>-1.096</v>
       </c>
       <c r="E200" t="n">
-        <v>30.1</v>
+        <v>31.9</v>
       </c>
       <c r="F200" t="n">
         <v>0.1</v>
       </c>
       <c r="G200" t="n">
-        <v>1.823</v>
+        <v>-0.661</v>
       </c>
     </row>
     <row r="201">
@@ -6238,20 +6250,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.215</v>
+        <v>-1.692</v>
       </c>
       <c r="E201" t="n">
-        <v>32.2</v>
+        <v>22.4</v>
       </c>
       <c r="F201" t="n">
         <v>0.1</v>
       </c>
       <c r="G201" t="n">
-        <v>0.211</v>
+        <v>-0.743</v>
       </c>
     </row>
     <row r="202">
@@ -6267,20 +6279,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Daeqwon Plowden</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.326</v>
+        <v>-3.151</v>
       </c>
       <c r="E202" t="n">
-        <v>23.1</v>
+        <v>28.9</v>
       </c>
       <c r="F202" t="n">
         <v>0.1</v>
       </c>
       <c r="G202" t="n">
-        <v>0.205</v>
+        <v>-1.838</v>
       </c>
     </row>
     <row r="203">
@@ -6296,20 +6308,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>DaQuan Jeffries</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>-1.434</v>
+        <v>-3.996</v>
       </c>
       <c r="E203" t="n">
-        <v>22.3</v>
+        <v>26.4</v>
       </c>
       <c r="F203" t="n">
         <v>0.1</v>
       </c>
       <c r="G203" t="n">
-        <v>-0.619</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="204">
@@ -6325,107 +6337,107 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>-1.366</v>
+        <v>-4.166</v>
       </c>
       <c r="E204" t="n">
-        <v>32.3</v>
+        <v>33.8</v>
       </c>
       <c r="F204" t="n">
         <v>0.1</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.852</v>
+        <v>-2.867</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Daeqwon Plowden</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-3.249</v>
+        <v>11.787</v>
       </c>
       <c r="E205" t="n">
-        <v>28.5</v>
+        <v>30.6</v>
       </c>
       <c r="F205" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G205" t="n">
-        <v>-1.873</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DaQuan Jeffries</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-3.998</v>
+        <v>4.028</v>
       </c>
       <c r="E206" t="n">
-        <v>26.4</v>
+        <v>29.7</v>
       </c>
       <c r="F206" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G206" t="n">
-        <v>-2.141</v>
+        <v>3.086</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-4.361</v>
+        <v>3.497</v>
       </c>
       <c r="E207" t="n">
-        <v>33.2</v>
+        <v>31.4</v>
       </c>
       <c r="F207" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G207" t="n">
-        <v>-2.949</v>
+        <v>2.916</v>
       </c>
     </row>
     <row r="208">
@@ -6441,20 +6453,20 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>11.6</v>
+        <v>1.671</v>
       </c>
       <c r="E208" t="n">
-        <v>29.5</v>
+        <v>23.4</v>
       </c>
       <c r="F208" t="n">
         <v>0.967</v>
       </c>
       <c r="G208" t="n">
-        <v>7.731</v>
+        <v>1.285</v>
       </c>
     </row>
     <row r="209">
@@ -6470,20 +6482,20 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>4.339</v>
+        <v>0.826</v>
       </c>
       <c r="E209" t="n">
-        <v>29.1</v>
+        <v>23</v>
       </c>
       <c r="F209" t="n">
         <v>0.967</v>
       </c>
       <c r="G209" t="n">
-        <v>3.22</v>
+        <v>0.859</v>
       </c>
     </row>
     <row r="210">
@@ -6499,20 +6511,20 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>3.614</v>
+        <v>0.395</v>
       </c>
       <c r="E210" t="n">
-        <v>30.1</v>
+        <v>27.3</v>
       </c>
       <c r="F210" t="n">
         <v>0.967</v>
       </c>
       <c r="G210" t="n">
-        <v>2.87</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="211">
@@ -6528,20 +6540,20 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1.672</v>
+        <v>0.151</v>
       </c>
       <c r="E211" t="n">
-        <v>23.5</v>
+        <v>30.6</v>
       </c>
       <c r="F211" t="n">
         <v>0.967</v>
       </c>
       <c r="G211" t="n">
-        <v>1.291</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="212">
@@ -6557,107 +6569,107 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.966</v>
+        <v>-0.873</v>
       </c>
       <c r="E212" t="n">
-        <v>23.3</v>
+        <v>20.7</v>
       </c>
       <c r="F212" t="n">
         <v>0.967</v>
       </c>
       <c r="G212" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.321</v>
+        <v>6.192</v>
       </c>
       <c r="E213" t="n">
-        <v>27</v>
+        <v>31.5</v>
       </c>
       <c r="F213" t="n">
-        <v>0.967</v>
+        <v>0.6</v>
       </c>
       <c r="G213" t="n">
-        <v>0.725</v>
+        <v>4.464</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.161</v>
+        <v>3.602</v>
       </c>
       <c r="E214" t="n">
-        <v>29.5</v>
+        <v>21.3</v>
       </c>
       <c r="F214" t="n">
-        <v>0.967</v>
+        <v>0.6</v>
       </c>
       <c r="G214" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.867</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>-0.92</v>
+        <v>2.009</v>
       </c>
       <c r="E215" t="n">
-        <v>21</v>
+        <v>33.2</v>
       </c>
       <c r="F215" t="n">
-        <v>0.967</v>
+        <v>0.6</v>
       </c>
       <c r="G215" t="n">
-        <v>0.02</v>
+        <v>1.803</v>
       </c>
     </row>
     <row r="216">
@@ -6673,20 +6685,20 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>6.234</v>
+        <v>1.705</v>
       </c>
       <c r="E216" t="n">
-        <v>32.4</v>
+        <v>30.9</v>
       </c>
       <c r="F216" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G216" t="n">
-        <v>4.547</v>
+        <v>1.482</v>
       </c>
     </row>
     <row r="217">
@@ -6702,20 +6714,20 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>3.642</v>
+        <v>1.981</v>
       </c>
       <c r="E217" t="n">
-        <v>21.5</v>
+        <v>26.6</v>
       </c>
       <c r="F217" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G217" t="n">
-        <v>1.856</v>
+        <v>1.433</v>
       </c>
     </row>
     <row r="218">
@@ -6731,20 +6743,20 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1.926</v>
+        <v>1.112</v>
       </c>
       <c r="E218" t="n">
-        <v>33.9</v>
+        <v>22.7</v>
       </c>
       <c r="F218" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G218" t="n">
-        <v>1.714</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -6760,20 +6772,20 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1.553</v>
+        <v>-0.309</v>
       </c>
       <c r="E219" t="n">
-        <v>30.9</v>
+        <v>24.1</v>
       </c>
       <c r="F219" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G219" t="n">
-        <v>1.323</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="220">
@@ -6789,107 +6801,107 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1.834</v>
+        <v>-0.955</v>
       </c>
       <c r="E220" t="n">
-        <v>26.9</v>
+        <v>23.7</v>
       </c>
       <c r="F220" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G220" t="n">
-        <v>1.307</v>
+        <v>-0.175</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.034</v>
+        <v>1.255</v>
       </c>
       <c r="E221" t="n">
-        <v>23</v>
+        <v>26.7</v>
       </c>
       <c r="F221" t="n">
-        <v>0.5</v>
+        <v>0.133</v>
       </c>
       <c r="G221" t="n">
-        <v>0.736</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>-0.441</v>
+        <v>1.102</v>
       </c>
       <c r="E222" t="n">
-        <v>23.7</v>
+        <v>26.3</v>
       </c>
       <c r="F222" t="n">
-        <v>0.5</v>
+        <v>0.133</v>
       </c>
       <c r="G222" t="n">
-        <v>0.029</v>
+        <v>0.676</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Oscar Tshiebwe</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>-0.877</v>
+        <v>1.856</v>
       </c>
       <c r="E223" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F223" t="n">
-        <v>0.5</v>
+        <v>0.133</v>
       </c>
       <c r="G223" t="n">
-        <v>-0.181</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="224">
@@ -6905,20 +6917,20 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1.319</v>
+        <v>-0.186</v>
       </c>
       <c r="E224" t="n">
-        <v>26.6</v>
+        <v>27.7</v>
       </c>
       <c r="F224" t="n">
         <v>0.133</v>
       </c>
       <c r="G224" t="n">
-        <v>0.805</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="225">
@@ -6934,20 +6946,20 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1.251</v>
+        <v>-1.114</v>
       </c>
       <c r="E225" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F225" t="n">
         <v>0.133</v>
       </c>
       <c r="G225" t="n">
-        <v>0.749</v>
+        <v>-0.389</v>
       </c>
     </row>
     <row r="226">
@@ -6963,20 +6975,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Kevin Love</t>
+          <t>Svi Mykhailiuk</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1.117</v>
+        <v>-1.131</v>
       </c>
       <c r="E226" t="n">
-        <v>15.5</v>
+        <v>19.4</v>
       </c>
       <c r="F226" t="n">
         <v>0.133</v>
       </c>
       <c r="G226" t="n">
-        <v>0.403</v>
+        <v>-0.403</v>
       </c>
     </row>
     <row r="227">
@@ -6992,20 +7004,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>-0.124</v>
+        <v>-2.06</v>
       </c>
       <c r="E227" t="n">
-        <v>27.2</v>
+        <v>30.3</v>
       </c>
       <c r="F227" t="n">
         <v>0.133</v>
       </c>
       <c r="G227" t="n">
-        <v>0.006</v>
+        <v>-1.217</v>
       </c>
     </row>
     <row r="228">
@@ -7021,107 +7033,107 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>Cody Williams</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-1.112</v>
+        <v>-3.755</v>
       </c>
       <c r="E228" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F228" t="n">
         <v>0.133</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.388</v>
+        <v>-2.639</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Svi Mykhailiuk</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-1.489</v>
+        <v>1.793</v>
       </c>
       <c r="E229" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="F229" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.581</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-2.068</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="E230" t="n">
-        <v>30.3</v>
+        <v>24.2</v>
       </c>
       <c r="F230" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G230" t="n">
-        <v>-1.219</v>
+        <v>-0.455</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-3.95</v>
+        <v>-0.967</v>
       </c>
       <c r="E231" t="n">
-        <v>34.3</v>
+        <v>26.9</v>
       </c>
       <c r="F231" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G231" t="n">
-        <v>-2.726</v>
+        <v>-0.524</v>
       </c>
     </row>
     <row r="232">
@@ -7137,20 +7149,20 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1.796</v>
+        <v>-1.613</v>
       </c>
       <c r="E232" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="F232" t="n">
         <v>0.033</v>
       </c>
       <c r="G232" t="n">
-        <v>0.796</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="233">
@@ -7166,20 +7178,20 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Sharife Cooper</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-0.873</v>
+        <v>-2.408</v>
       </c>
       <c r="E233" t="n">
-        <v>25</v>
+        <v>18.2</v>
       </c>
       <c r="F233" t="n">
         <v>0.033</v>
       </c>
       <c r="G233" t="n">
-        <v>-0.438</v>
+        <v>-0.899</v>
       </c>
     </row>
     <row r="234">
@@ -7195,20 +7207,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>-0.965</v>
+        <v>-1.908</v>
       </c>
       <c r="E234" t="n">
-        <v>26.9</v>
+        <v>27.9</v>
       </c>
       <c r="F234" t="n">
         <v>0.033</v>
       </c>
       <c r="G234" t="n">
-        <v>-0.523</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="235">
@@ -7224,136 +7236,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>-1.834</v>
+        <v>-2.078</v>
       </c>
       <c r="E235" t="n">
-        <v>21.5</v>
+        <v>32.2</v>
       </c>
       <c r="F235" t="n">
         <v>0.033</v>
       </c>
       <c r="G235" t="n">
-        <v>-0.8070000000000001</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Bub Carrington</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>-1.89</v>
-      </c>
-      <c r="E236" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="F236" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G236" t="n">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Jaden Hardy</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>-3.41</v>
-      </c>
-      <c r="E237" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F237" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G237" t="n">
-        <v>-1.471</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Tre Johnson</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>-3.323</v>
-      </c>
-      <c r="E238" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F238" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G238" t="n">
-        <v>-1.545</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Will Riley</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>-2.502</v>
-      </c>
-      <c r="E239" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="F239" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G239" t="n">
-        <v>-1.614</v>
+        <v>-1.37</v>
       </c>
     </row>
   </sheetData>
@@ -7371,37 +7267,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team_abbr</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_eligible</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team_bpm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>avg_sbpm</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>top_player</t>
         </is>
@@ -7413,26 +7309,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>21.981</v>
+        <v>21.669</v>
       </c>
       <c r="F2" t="n">
-        <v>2.798</v>
+        <v>3.332</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7454,10 +7350,10 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>19.316</v>
+        <v>21.458</v>
       </c>
       <c r="F3" t="n">
-        <v>2.601</v>
+        <v>3.141</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7483,10 +7379,10 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>19.057</v>
+        <v>18.062</v>
       </c>
       <c r="F4" t="n">
-        <v>2.76</v>
+        <v>2.668</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7512,10 +7408,10 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>17.486</v>
+        <v>17.793</v>
       </c>
       <c r="F5" t="n">
-        <v>2.719</v>
+        <v>2.685</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -7541,10 +7437,10 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>17.474</v>
+        <v>17.741</v>
       </c>
       <c r="F6" t="n">
-        <v>2.541</v>
+        <v>2.627</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7558,26 +7454,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>15.966</v>
+        <v>14.876</v>
       </c>
       <c r="F7" t="n">
-        <v>2.404</v>
+        <v>1.938</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7587,26 +7483,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>15.025</v>
+        <v>13.574</v>
       </c>
       <c r="F8" t="n">
-        <v>2.039</v>
+        <v>1.074</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7616,26 +7512,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>14.059</v>
+        <v>13.171</v>
       </c>
       <c r="F9" t="n">
-        <v>1.878</v>
+        <v>1.73</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7645,26 +7541,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>13.546</v>
+        <v>12.278</v>
       </c>
       <c r="F10" t="n">
-        <v>1.042</v>
+        <v>1.758</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7674,26 +7570,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>13.425</v>
+        <v>11.828</v>
       </c>
       <c r="F11" t="n">
-        <v>1.781</v>
+        <v>1.917</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7703,26 +7599,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>12.004</v>
+        <v>11.09</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>1.678</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7732,26 +7628,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.7</v>
+        <v>10.371</v>
       </c>
       <c r="F13" t="n">
-        <v>1.759</v>
+        <v>1.58</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
     </row>
@@ -7761,26 +7657,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>11.331</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.863</v>
+        <v>1.665</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7686,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>8.768000000000001</v>
+        <v>9.452999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.202</v>
+        <v>1.199</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7831,10 +7727,10 @@
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>8.483000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="F16" t="n">
-        <v>1.155</v>
+        <v>1.147</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -7848,26 +7744,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>7.22</v>
+        <v>7.544</v>
       </c>
       <c r="F17" t="n">
-        <v>0.876</v>
+        <v>0.312</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
     </row>
@@ -7877,26 +7773,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>7.01</v>
+        <v>7.474</v>
       </c>
       <c r="F18" t="n">
-        <v>0.541</v>
+        <v>0.889</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
     </row>
@@ -7906,26 +7802,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>6.298</v>
+        <v>7.181</v>
       </c>
       <c r="F19" t="n">
-        <v>0.642</v>
+        <v>0.579</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
     </row>
@@ -7947,10 +7843,10 @@
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>6.09</v>
+        <v>6.613</v>
       </c>
       <c r="F20" t="n">
-        <v>1.012</v>
+        <v>1.072</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -7964,26 +7860,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>5.397</v>
+        <v>2.623</v>
       </c>
       <c r="F21" t="n">
-        <v>0.855</v>
+        <v>0.39</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
     </row>
@@ -7993,26 +7889,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.085</v>
+        <v>0.505</v>
       </c>
       <c r="F22" t="n">
-        <v>0.193</v>
+        <v>-0.699</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
     </row>
@@ -8022,26 +7918,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>3.718</v>
+        <v>-1.563</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.339</v>
+        <v>-0.446</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Jay Huff</t>
         </is>
       </c>
     </row>
@@ -8051,26 +7947,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.058</v>
+        <v>-1.733</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.341</v>
+        <v>-1.416</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
     </row>
@@ -8080,26 +7976,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.944</v>
+        <v>-2.568</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.669</v>
+        <v>-0.504</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
     </row>
@@ -8109,26 +8005,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.656</v>
+        <v>-3.63</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.006</v>
+        <v>-1.41</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Tre Jones</t>
         </is>
       </c>
     </row>
@@ -8138,26 +8034,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.951</v>
+        <v>-3.851</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.632</v>
+        <v>-1.656</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
     </row>
@@ -8167,26 +8063,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.635</v>
+        <v>-4.233</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.404</v>
+        <v>-1.159</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
     </row>
@@ -8208,14 +8104,14 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.195</v>
+        <v>-7.708</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.383</v>
+        <v>-1.674</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Malik Monk</t>
         </is>
       </c>
     </row>
@@ -8225,26 +8121,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.652</v>
+        <v>-8.177</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.625</v>
+        <v>-2.564</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Pete Nance</t>
         </is>
       </c>
     </row>
@@ -8263,13 +8159,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>-12.147</v>
+        <v>-10.102</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.574</v>
+        <v>-4.02</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -1233,20 +1233,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.098</v>
+        <v>2.102</v>
       </c>
       <c r="E28" t="n">
-        <v>27.8</v>
+        <v>18.4</v>
       </c>
       <c r="F28" t="n">
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1.042</v>
+        <v>1.072</v>
       </c>
     </row>
     <row r="29">
@@ -1262,20 +1262,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.901</v>
+        <v>1.098</v>
       </c>
       <c r="E29" t="n">
-        <v>20.1</v>
+        <v>27.8</v>
       </c>
       <c r="F29" t="n">
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.669</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="30">
@@ -2045,20 +2045,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>9.124000000000001</v>
+        <v>18.051</v>
       </c>
       <c r="E56" t="n">
-        <v>35.7</v>
+        <v>36.3</v>
       </c>
       <c r="F56" t="n">
         <v>0.8</v>
       </c>
       <c r="G56" t="n">
-        <v>7.375</v>
+        <v>14.258</v>
       </c>
     </row>
     <row r="57">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.016</v>
+        <v>9.124000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>28.2</v>
+        <v>35.7</v>
       </c>
       <c r="F57" t="n">
         <v>0.8</v>
       </c>
       <c r="G57" t="n">
-        <v>1.654</v>
+        <v>7.375</v>
       </c>
     </row>
     <row r="58">
@@ -2103,20 +2103,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.429</v>
+        <v>2.016</v>
       </c>
       <c r="E58" t="n">
-        <v>24.1</v>
+        <v>28.2</v>
       </c>
       <c r="F58" t="n">
         <v>0.8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.616</v>
+        <v>1.654</v>
       </c>
     </row>
     <row r="59">
@@ -2132,20 +2132,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-0.672</v>
+        <v>0.429</v>
       </c>
       <c r="E59" t="n">
-        <v>29.4</v>
+        <v>24.1</v>
       </c>
       <c r="F59" t="n">
         <v>0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.078</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="60">
@@ -2161,20 +2161,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jalen Pickett</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-1.603</v>
+        <v>-0.672</v>
       </c>
       <c r="E60" t="n">
-        <v>15.7</v>
+        <v>29.4</v>
       </c>
       <c r="F60" t="n">
         <v>0.8</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.262</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="61">
@@ -4597,20 +4597,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>-0.355</v>
+        <v>-0.986</v>
       </c>
       <c r="E144" t="n">
-        <v>20.8</v>
+        <v>22.7</v>
       </c>
       <c r="F144" t="n">
         <v>0.333</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.309</v>
       </c>
     </row>
     <row r="145">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-0.986</v>
+        <v>-2.677</v>
       </c>
       <c r="E145" t="n">
-        <v>22.7</v>
+        <v>19.9</v>
       </c>
       <c r="F145" t="n">
         <v>0.333</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.309</v>
+        <v>-0.971</v>
       </c>
     </row>
     <row r="146">
@@ -4655,20 +4655,20 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Micah Peavy</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>-2.677</v>
+        <v>-5.119</v>
       </c>
       <c r="E146" t="n">
-        <v>19.9</v>
+        <v>15.5</v>
       </c>
       <c r="F146" t="n">
         <v>0.333</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.971</v>
+        <v>-1.545</v>
       </c>
     </row>
     <row r="147">
@@ -5119,20 +5119,20 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Jaylin Williams</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.397</v>
+        <v>1.239</v>
       </c>
       <c r="E162" t="n">
-        <v>19.6</v>
+        <v>21</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0.57</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="163">
@@ -6627,20 +6627,20 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>3.602</v>
+        <v>4.638</v>
       </c>
       <c r="E214" t="n">
-        <v>21.3</v>
+        <v>33</v>
       </c>
       <c r="F214" t="n">
         <v>0.6</v>
       </c>
       <c r="G214" t="n">
-        <v>1.867</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="215">
@@ -6917,20 +6917,20 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Kevin Love</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.186</v>
+        <v>1.114</v>
       </c>
       <c r="E224" t="n">
-        <v>27.7</v>
+        <v>15.5</v>
       </c>
       <c r="F224" t="n">
         <v>0.133</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.031</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="225">
@@ -6946,20 +6946,20 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-1.114</v>
+        <v>-0.186</v>
       </c>
       <c r="E225" t="n">
-        <v>19</v>
+        <v>27.7</v>
       </c>
       <c r="F225" t="n">
         <v>0.133</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.389</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="226">
@@ -6975,20 +6975,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Svi Mykhailiuk</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>-1.131</v>
+        <v>-1.114</v>
       </c>
       <c r="E226" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="F226" t="n">
         <v>0.133</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.403</v>
+        <v>-0.389</v>
       </c>
     </row>
     <row r="227">
@@ -7004,20 +7004,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Svi Mykhailiuk</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>-2.06</v>
+        <v>-1.131</v>
       </c>
       <c r="E227" t="n">
-        <v>30.3</v>
+        <v>19.4</v>
       </c>
       <c r="F227" t="n">
         <v>0.133</v>
       </c>
       <c r="G227" t="n">
-        <v>-1.217</v>
+        <v>-0.403</v>
       </c>
     </row>
     <row r="228">
@@ -7309,26 +7309,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>21.669</v>
+        <v>22.064</v>
       </c>
       <c r="F2" t="n">
-        <v>3.332</v>
+        <v>2.769</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
     </row>
@@ -7338,26 +7338,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>21.458</v>
+        <v>21.669</v>
       </c>
       <c r="F3" t="n">
-        <v>3.141</v>
+        <v>3.332</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -7367,26 +7367,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>18.062</v>
+        <v>21.458</v>
       </c>
       <c r="F4" t="n">
-        <v>2.668</v>
+        <v>3.141</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
     </row>
@@ -7396,26 +7396,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>17.793</v>
+        <v>18.472</v>
       </c>
       <c r="F5" t="n">
-        <v>2.685</v>
+        <v>2.773</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
     </row>
@@ -7425,26 +7425,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>17.741</v>
+        <v>17.793</v>
       </c>
       <c r="F6" t="n">
-        <v>2.627</v>
+        <v>2.685</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7454,26 +7454,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>14.876</v>
+        <v>17.741</v>
       </c>
       <c r="F7" t="n">
-        <v>1.938</v>
+        <v>2.627</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -7483,26 +7483,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>13.574</v>
+        <v>14.876</v>
       </c>
       <c r="F8" t="n">
-        <v>1.074</v>
+        <v>1.938</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7512,26 +7512,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>13.171</v>
+        <v>13.574</v>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>1.074</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7541,26 +7541,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>12.278</v>
+        <v>13.561</v>
       </c>
       <c r="F10" t="n">
-        <v>1.758</v>
+        <v>2.047</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7570,26 +7570,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>11.828</v>
+        <v>13.171</v>
       </c>
       <c r="F11" t="n">
-        <v>1.917</v>
+        <v>1.73</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7599,26 +7599,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>11.09</v>
+        <v>12.681</v>
       </c>
       <c r="F12" t="n">
-        <v>1.678</v>
+        <v>1.908</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7628,26 +7628,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>10.371</v>
+        <v>11.09</v>
       </c>
       <c r="F13" t="n">
-        <v>1.58</v>
+        <v>1.678</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7657,26 +7657,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>9.539999999999999</v>
+        <v>10.371</v>
       </c>
       <c r="F14" t="n">
-        <v>1.665</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Stephen Curry</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
     </row>
@@ -7686,26 +7686,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>9.452999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.199</v>
+        <v>1.665</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
     </row>
@@ -7715,26 +7715,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>8.24</v>
+        <v>9.452999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.147</v>
+        <v>1.199</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7744,26 +7744,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>7.544</v>
+        <v>8.24</v>
       </c>
       <c r="F17" t="n">
-        <v>0.312</v>
+        <v>1.147</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Devin Booker</t>
         </is>
       </c>
     </row>
@@ -7889,26 +7889,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.505</v>
+        <v>-0.949</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.699</v>
+        <v>-0.107</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
     </row>
@@ -7918,26 +7918,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.563</v>
+        <v>-1.031</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.446</v>
+        <v>-1.295</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
     </row>
@@ -7947,26 +7947,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.733</v>
+        <v>-1.563</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.416</v>
+        <v>-0.446</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Jay Huff</t>
         </is>
       </c>
     </row>
@@ -7976,26 +7976,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.568</v>
+        <v>-1.733</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.504</v>
+        <v>-1.416</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
     </row>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G235"/>
+  <dimension ref="A1:G229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.236000000000001</v>
+        <v>8.125</v>
       </c>
       <c r="E2" t="n">
-        <v>35.4</v>
+        <v>36.1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G2" t="n">
-        <v>6.559</v>
+        <v>6.579</v>
       </c>
     </row>
     <row r="3">
@@ -512,16 +512,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.674</v>
+        <v>3.872</v>
       </c>
       <c r="E3" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G3" t="n">
-        <v>3.066</v>
+        <v>3.199</v>
       </c>
     </row>
     <row r="4">
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.648</v>
+        <v>2.586</v>
       </c>
       <c r="E4" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G4" t="n">
-        <v>2.219</v>
+        <v>2.208</v>
       </c>
     </row>
     <row r="5">
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.578</v>
+        <v>2.43</v>
       </c>
       <c r="E5" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G5" t="n">
-        <v>1.987</v>
+        <v>1.901</v>
       </c>
     </row>
     <row r="6">
@@ -599,16 +599,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.316</v>
+        <v>2.332</v>
       </c>
       <c r="E6" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G6" t="n">
-        <v>1.829</v>
+        <v>1.828</v>
       </c>
     </row>
     <row r="7">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.604</v>
+        <v>-0.603</v>
       </c>
       <c r="E7" t="n">
         <v>15.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G7" t="n">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="8">
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.717</v>
+        <v>-1.716</v>
       </c>
       <c r="E8" t="n">
         <v>17.9</v>
       </c>
       <c r="F8" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.392</v>
+        <v>-0.404</v>
       </c>
     </row>
     <row r="9">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.63</v>
+        <v>-1.764</v>
       </c>
       <c r="E9" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.413</v>
+        <v>-0.487</v>
       </c>
     </row>
     <row r="10">
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.582</v>
+        <v>6.514</v>
       </c>
       <c r="E10" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>5.436</v>
+        <v>5.385</v>
       </c>
     </row>
     <row r="11">
@@ -744,16 +744,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.915</v>
+        <v>5.602</v>
       </c>
       <c r="E11" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>4.893</v>
+        <v>4.679</v>
       </c>
     </row>
     <row r="12">
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.788</v>
+        <v>4.789</v>
       </c>
       <c r="E12" t="n">
-        <v>33.8</v>
+        <v>34.3</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>4.001</v>
+        <v>4.092</v>
       </c>
     </row>
     <row r="13">
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.071</v>
+        <v>4.067</v>
       </c>
       <c r="E13" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>3.289</v>
+        <v>3.322</v>
       </c>
     </row>
     <row r="14">
@@ -827,20 +827,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nikola Vučević</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.315</v>
+        <v>2.673</v>
       </c>
       <c r="E14" t="n">
-        <v>23.2</v>
+        <v>28.4</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>2.041</v>
+        <v>2.136</v>
       </c>
     </row>
     <row r="15">
@@ -856,20 +856,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Nikola Vučević</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.407</v>
+        <v>2.954</v>
       </c>
       <c r="E15" t="n">
-        <v>27.3</v>
+        <v>21.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.879</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="16">
@@ -889,16 +889,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.482</v>
+        <v>-0.578</v>
       </c>
       <c r="E16" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.224</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="17">
@@ -918,16 +918,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.471</v>
+        <v>-1.593</v>
       </c>
       <c r="E17" t="n">
-        <v>25.7</v>
+        <v>24.3</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.305</v>
+        <v>-0.333</v>
       </c>
     </row>
     <row r="18">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.943</v>
+        <v>1.944</v>
       </c>
       <c r="E18" t="n">
         <v>19.3</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-4.788</v>
+        <v>-4.787</v>
       </c>
       <c r="E19" t="n">
         <v>15.7</v>
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-5.14</v>
+        <v>-4.845</v>
       </c>
       <c r="E20" t="n">
-        <v>15.3</v>
+        <v>16.1</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.62</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="21">
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-5.129</v>
+        <v>-4.857</v>
       </c>
       <c r="E21" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.365</v>
+        <v>-2.274</v>
       </c>
     </row>
     <row r="22">
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-4.874</v>
+        <v>-4.831</v>
       </c>
       <c r="E22" t="n">
-        <v>24.4</v>
+        <v>26.7</v>
       </c>
       <c r="F22" t="n">
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.443</v>
+        <v>-2.651</v>
       </c>
     </row>
     <row r="23">
@@ -1092,16 +1092,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-6.131</v>
+        <v>-6.13</v>
       </c>
       <c r="E23" t="n">
-        <v>23.3</v>
+        <v>24.6</v>
       </c>
       <c r="F23" t="n">
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.94</v>
+        <v>-3.103</v>
       </c>
     </row>
     <row r="24">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7.261</v>
+        <v>7.509</v>
       </c>
       <c r="E24" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="G24" t="n">
-        <v>4.735</v>
+        <v>4.884</v>
       </c>
     </row>
     <row r="25">
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.433</v>
+        <v>4.224</v>
       </c>
       <c r="E25" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="G25" t="n">
-        <v>3.194</v>
+        <v>3.068</v>
       </c>
     </row>
     <row r="26">
@@ -1179,16 +1179,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.99</v>
+        <v>2.754</v>
       </c>
       <c r="E26" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="G26" t="n">
-        <v>2.401</v>
+        <v>2.271</v>
       </c>
     </row>
     <row r="27">
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.534</v>
+        <v>1.793</v>
       </c>
       <c r="E27" t="n">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="G27" t="n">
-        <v>1.326</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="28">
@@ -1233,20 +1233,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.102</v>
+        <v>1.165</v>
       </c>
       <c r="E28" t="n">
-        <v>18.4</v>
+        <v>27.5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="G28" t="n">
-        <v>1.072</v>
+        <v>1.087</v>
       </c>
     </row>
     <row r="29">
@@ -1262,20 +1262,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.098</v>
+        <v>0.902</v>
       </c>
       <c r="E29" t="n">
-        <v>27.8</v>
+        <v>20.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="G29" t="n">
-        <v>1.042</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1295,16 +1295,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.71</v>
+        <v>-0.282</v>
       </c>
       <c r="E30" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.004</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="31">
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-3.44</v>
+        <v>-3.432</v>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.085</v>
+        <v>-1.101</v>
       </c>
     </row>
     <row r="32">
@@ -1353,16 +1353,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.988</v>
+        <v>4.183</v>
       </c>
       <c r="E32" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G32" t="n">
-        <v>2.546</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="33">
@@ -1382,16 +1382,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.421</v>
+        <v>2.316</v>
       </c>
       <c r="E33" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G33" t="n">
-        <v>1.475</v>
+        <v>1.491</v>
       </c>
     </row>
     <row r="34">
@@ -1407,20 +1407,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Leonard Miller</t>
+          <t>Jaden Ivey</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.556</v>
+        <v>-0.62</v>
       </c>
       <c r="E34" t="n">
-        <v>24.3</v>
+        <v>19.6</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.13</v>
+        <v>-0.117</v>
       </c>
     </row>
     <row r="35">
@@ -1436,20 +1436,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jaden Ivey</t>
+          <t>Leonard Miller</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.621</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>19.6</v>
+        <v>26.5</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.131</v>
+        <v>-0.194</v>
       </c>
     </row>
     <row r="36">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-2.182</v>
+        <v>-2.501</v>
       </c>
       <c r="E36" t="n">
-        <v>24.1</v>
+        <v>25.1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.946</v>
+        <v>-1.133</v>
       </c>
     </row>
     <row r="37">
@@ -1494,20 +1494,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Patrick Williams</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-3.306</v>
+        <v>-4.266</v>
       </c>
       <c r="E37" t="n">
-        <v>29.7</v>
+        <v>21.6</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.861</v>
+        <v>-1.766</v>
       </c>
     </row>
     <row r="38">
@@ -1523,20 +1523,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Patrick Williams</t>
+          <t>Isaac Okoro</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-4.685</v>
+        <v>-3.311</v>
       </c>
       <c r="E38" t="n">
-        <v>20.7</v>
+        <v>30.2</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.891</v>
+        <v>-1.872</v>
       </c>
     </row>
     <row r="39">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-6.34</v>
+        <v>-5.868</v>
       </c>
       <c r="E39" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.692</v>
+        <v>-2.559</v>
       </c>
     </row>
     <row r="40">
@@ -1581,20 +1581,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8.946999999999999</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>33.4</v>
+        <v>34.9</v>
       </c>
       <c r="F40" t="n">
         <v>0.767</v>
       </c>
       <c r="G40" t="n">
-        <v>6.758</v>
+        <v>6.571</v>
       </c>
     </row>
     <row r="41">
@@ -1610,20 +1610,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8.19</v>
+        <v>4.633</v>
       </c>
       <c r="E41" t="n">
-        <v>35</v>
+        <v>30.1</v>
       </c>
       <c r="F41" t="n">
         <v>0.767</v>
       </c>
       <c r="G41" t="n">
-        <v>6.526</v>
+        <v>3.385</v>
       </c>
     </row>
     <row r="42">
@@ -1639,20 +1639,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Max Strus</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4.538</v>
+        <v>1.22</v>
       </c>
       <c r="E42" t="n">
-        <v>30.5</v>
+        <v>27.1</v>
       </c>
       <c r="F42" t="n">
         <v>0.767</v>
       </c>
       <c r="G42" t="n">
-        <v>3.37</v>
+        <v>1.121</v>
       </c>
     </row>
     <row r="43">
@@ -1668,20 +1668,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Craig Porter Jr.</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3.902</v>
+        <v>1.581</v>
       </c>
       <c r="E43" t="n">
-        <v>27.2</v>
+        <v>16.7</v>
       </c>
       <c r="F43" t="n">
         <v>0.767</v>
       </c>
       <c r="G43" t="n">
-        <v>2.642</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.859</v>
+        <v>-0.3</v>
       </c>
       <c r="E44" t="n">
-        <v>27</v>
+        <v>20.1</v>
       </c>
       <c r="F44" t="n">
         <v>0.767</v>
       </c>
       <c r="G44" t="n">
-        <v>1.476</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="45">
@@ -1726,20 +1726,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.706</v>
+        <v>-0.629</v>
       </c>
       <c r="E45" t="n">
-        <v>29.4</v>
+        <v>26.9</v>
       </c>
       <c r="F45" t="n">
         <v>0.767</v>
       </c>
       <c r="G45" t="n">
-        <v>0.901</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="46">
@@ -1755,20 +1755,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Dean Wade</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-0.555</v>
+        <v>-1.239</v>
       </c>
       <c r="E46" t="n">
-        <v>19.5</v>
+        <v>21.2</v>
       </c>
       <c r="F46" t="n">
         <v>0.767</v>
       </c>
       <c r="G46" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="47">
@@ -1784,20 +1784,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Keon Ellis</t>
+          <t>Lonzo Ball</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.929</v>
+        <v>-1.358</v>
       </c>
       <c r="E47" t="n">
-        <v>26.7</v>
+        <v>17.6</v>
       </c>
       <c r="F47" t="n">
         <v>0.767</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.09</v>
+        <v>-0.216</v>
       </c>
     </row>
     <row r="48">
@@ -1817,16 +1817,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.769</v>
+        <v>3.049</v>
       </c>
       <c r="E48" t="n">
-        <v>33.5</v>
+        <v>34.3</v>
       </c>
       <c r="F48" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="G48" t="n">
-        <v>2.094</v>
+        <v>2.371</v>
       </c>
     </row>
     <row r="49">
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.213</v>
+        <v>2.514</v>
       </c>
       <c r="E49" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="G49" t="n">
-        <v>1.086</v>
+        <v>1.223</v>
       </c>
     </row>
     <row r="50">
@@ -1871,20 +1871,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Brandon Williams</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.557</v>
+        <v>1.198</v>
       </c>
       <c r="E50" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="F50" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="G50" t="n">
-        <v>0.839</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="51">
@@ -1900,20 +1900,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brandon Williams</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.197</v>
+        <v>0.575</v>
       </c>
       <c r="E51" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F51" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="G51" t="n">
-        <v>0.655</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="52">
@@ -1929,20 +1929,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.535</v>
+        <v>-1.477</v>
       </c>
       <c r="E52" t="n">
-        <v>28.5</v>
+        <v>20.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="G52" t="n">
-        <v>0.456</v>
+        <v>-0.517</v>
       </c>
     </row>
     <row r="53">
@@ -1958,20 +1958,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Ryan Nembhard</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1.563</v>
+        <v>-2.142</v>
       </c>
       <c r="E53" t="n">
-        <v>20.8</v>
+        <v>19.6</v>
       </c>
       <c r="F53" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.577</v>
+        <v>-0.764</v>
       </c>
     </row>
     <row r="54">
@@ -1991,16 +1991,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1.808</v>
+        <v>-1.841</v>
       </c>
       <c r="E54" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="F54" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.914</v>
+        <v>-0.913</v>
       </c>
     </row>
     <row r="55">
@@ -2026,10 +2026,10 @@
         <v>31.5</v>
       </c>
       <c r="F55" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="G55" t="n">
-        <v>-1.016</v>
+        <v>-0.993</v>
       </c>
     </row>
     <row r="56">
@@ -2049,16 +2049,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>18.051</v>
+        <v>18.047</v>
       </c>
       <c r="E56" t="n">
-        <v>36.3</v>
+        <v>37.1</v>
       </c>
       <c r="F56" t="n">
         <v>0.8</v>
       </c>
       <c r="G56" t="n">
-        <v>14.258</v>
+        <v>14.578</v>
       </c>
     </row>
     <row r="57">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9.124000000000001</v>
+        <v>9.057</v>
       </c>
       <c r="E57" t="n">
-        <v>35.7</v>
+        <v>37</v>
       </c>
       <c r="F57" t="n">
         <v>0.8</v>
       </c>
       <c r="G57" t="n">
-        <v>7.375</v>
+        <v>7.608</v>
       </c>
     </row>
     <row r="58">
@@ -2107,16 +2107,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.016</v>
+        <v>2.307</v>
       </c>
       <c r="E58" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="F58" t="n">
         <v>0.8</v>
       </c>
       <c r="G58" t="n">
-        <v>1.654</v>
+        <v>1.821</v>
       </c>
     </row>
     <row r="59">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.429</v>
+        <v>0.27</v>
       </c>
       <c r="E59" t="n">
         <v>24.1</v>
@@ -2145,7 +2145,7 @@
         <v>0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.616</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="60">
@@ -2165,16 +2165,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-0.672</v>
+        <v>-0.615</v>
       </c>
       <c r="E60" t="n">
-        <v>29.4</v>
+        <v>30.4</v>
       </c>
       <c r="F60" t="n">
         <v>0.8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.078</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="61">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-2.354</v>
+        <v>-2.353</v>
       </c>
       <c r="E61" t="n">
         <v>15.7</v>
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-1.69</v>
+        <v>-1.717</v>
       </c>
       <c r="E62" t="n">
-        <v>31.9</v>
+        <v>32.5</v>
       </c>
       <c r="F62" t="n">
         <v>0.8</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.591</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="63">
@@ -2252,16 +2252,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-2.752</v>
+        <v>-2.886</v>
       </c>
       <c r="E63" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="F63" t="n">
         <v>0.8</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.819</v>
+        <v>-0.882</v>
       </c>
     </row>
     <row r="64">
@@ -2277,20 +2277,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5.511</v>
+        <v>8.847</v>
       </c>
       <c r="E64" t="n">
-        <v>29.4</v>
+        <v>32.4</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G64" t="n">
-        <v>3.952</v>
+        <v>6.579</v>
       </c>
     </row>
     <row r="65">
@@ -2306,20 +2306,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.708</v>
+        <v>5.465</v>
       </c>
       <c r="E65" t="n">
-        <v>25.9</v>
+        <v>29.8</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G65" t="n">
-        <v>1.424</v>
+        <v>3.952</v>
       </c>
     </row>
     <row r="66">
@@ -2335,20 +2335,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.177</v>
+        <v>1.778</v>
       </c>
       <c r="E66" t="n">
-        <v>30.5</v>
+        <v>26.5</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G66" t="n">
-        <v>0.705</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="67">
@@ -2364,20 +2364,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-0.039</v>
+        <v>0.176</v>
       </c>
       <c r="E67" t="n">
-        <v>26.7</v>
+        <v>31.7</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G67" t="n">
-        <v>0.497</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="68">
@@ -2393,20 +2393,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-0.059</v>
+        <v>0.118</v>
       </c>
       <c r="E68" t="n">
-        <v>25.7</v>
+        <v>26.4</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G68" t="n">
-        <v>0.469</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -2422,20 +2422,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.136</v>
+        <v>-0.03</v>
       </c>
       <c r="E69" t="n">
-        <v>23.8</v>
+        <v>25.6</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G69" t="n">
-        <v>0.395</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="70">
@@ -2451,20 +2451,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Colby Jones</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.917</v>
+        <v>-0.135</v>
       </c>
       <c r="E70" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G70" t="n">
-        <v>0.008</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="71">
@@ -2480,20 +2480,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Caris LeVert</t>
+          <t>Colby Jones</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-1.611</v>
+        <v>-0.91</v>
       </c>
       <c r="E71" t="n">
-        <v>19</v>
+        <v>23.4</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.269</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="72">
@@ -2513,16 +2513,16 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7.585</v>
+        <v>7.767</v>
       </c>
       <c r="E72" t="n">
-        <v>30.4</v>
+        <v>29.9</v>
       </c>
       <c r="F72" t="n">
         <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>5.05</v>
+        <v>5.087</v>
       </c>
     </row>
     <row r="73">
@@ -2538,20 +2538,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4.1</v>
+        <v>2.168</v>
       </c>
       <c r="E73" t="n">
-        <v>22.8</v>
+        <v>31.4</v>
       </c>
       <c r="F73" t="n">
         <v>0.4</v>
       </c>
       <c r="G73" t="n">
-        <v>2.139</v>
+        <v>1.677</v>
       </c>
     </row>
     <row r="74">
@@ -2567,20 +2567,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Gary Payton II</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2.1</v>
+        <v>2.948</v>
       </c>
       <c r="E74" t="n">
-        <v>31.9</v>
+        <v>23.6</v>
       </c>
       <c r="F74" t="n">
         <v>0.4</v>
       </c>
       <c r="G74" t="n">
-        <v>1.66</v>
+        <v>1.647</v>
       </c>
     </row>
     <row r="75">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gary Payton II</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2.851</v>
+        <v>0.767</v>
       </c>
       <c r="E75" t="n">
-        <v>23.2</v>
+        <v>32.8</v>
       </c>
       <c r="F75" t="n">
         <v>0.4</v>
       </c>
       <c r="G75" t="n">
-        <v>1.572</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="76">
@@ -2625,20 +2625,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pat Spencer</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-0.395</v>
+        <v>-0.368</v>
       </c>
       <c r="E76" t="n">
-        <v>22.1</v>
+        <v>30.3</v>
       </c>
       <c r="F76" t="n">
         <v>0.4</v>
       </c>
       <c r="G76" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="77">
@@ -2654,20 +2654,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Pat Spencer</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-0.471</v>
+        <v>-0.528</v>
       </c>
       <c r="E77" t="n">
-        <v>30.6</v>
+        <v>23</v>
       </c>
       <c r="F77" t="n">
         <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.045</v>
+        <v>-0.061</v>
       </c>
     </row>
     <row r="78">
@@ -2687,16 +2687,16 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-1.095</v>
+        <v>-0.634</v>
       </c>
       <c r="E78" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="F78" t="n">
         <v>0.4</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.364</v>
+        <v>-0.122</v>
       </c>
     </row>
     <row r="79">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-1.357</v>
+        <v>-1.356</v>
       </c>
       <c r="E79" t="n">
         <v>23.8</v>
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6.705</v>
+        <v>6.809</v>
       </c>
       <c r="E80" t="n">
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="F80" t="n">
         <v>0.833</v>
       </c>
       <c r="G80" t="n">
-        <v>5.493</v>
+        <v>5.642</v>
       </c>
     </row>
     <row r="81">
@@ -2774,16 +2774,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6.323</v>
+        <v>6.209</v>
       </c>
       <c r="E81" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="F81" t="n">
         <v>0.833</v>
       </c>
       <c r="G81" t="n">
-        <v>4.749</v>
+        <v>4.692</v>
       </c>
     </row>
     <row r="82">
@@ -2803,16 +2803,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3.896</v>
+        <v>4.02</v>
       </c>
       <c r="E82" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="F82" t="n">
         <v>0.833</v>
       </c>
       <c r="G82" t="n">
-        <v>3.737</v>
+        <v>3.839</v>
       </c>
     </row>
     <row r="83">
@@ -2832,16 +2832,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3.663</v>
+        <v>3.661</v>
       </c>
       <c r="E83" t="n">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="F83" t="n">
         <v>0.833</v>
       </c>
       <c r="G83" t="n">
-        <v>2.776</v>
+        <v>2.703</v>
       </c>
     </row>
     <row r="84">
@@ -2861,16 +2861,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-0.477</v>
+        <v>-0.381</v>
       </c>
       <c r="E84" t="n">
-        <v>35.6</v>
+        <v>35.9</v>
       </c>
       <c r="F84" t="n">
         <v>0.833</v>
       </c>
       <c r="G84" t="n">
-        <v>0.264</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="85">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-1.754</v>
+        <v>-1.869</v>
       </c>
       <c r="E85" t="n">
         <v>24.2</v>
@@ -2899,7 +2899,7 @@
         <v>0.833</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.465</v>
+        <v>-0.522</v>
       </c>
     </row>
     <row r="86">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-2.961</v>
+        <v>-2.96</v>
       </c>
       <c r="E86" t="n">
         <v>16</v>
@@ -2977,16 +2977,16 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2.004</v>
+        <v>1.926</v>
       </c>
       <c r="E88" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="F88" t="n">
         <v>0.167</v>
       </c>
       <c r="G88" t="n">
-        <v>1.005</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -3006,16 +3006,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1.915</v>
+        <v>2.149</v>
       </c>
       <c r="E89" t="n">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
       <c r="F89" t="n">
         <v>0.167</v>
       </c>
       <c r="G89" t="n">
-        <v>0.725</v>
+        <v>0.853</v>
       </c>
     </row>
     <row r="90">
@@ -3031,20 +3031,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1.944</v>
+        <v>-0.445</v>
       </c>
       <c r="E90" t="n">
-        <v>16.1</v>
+        <v>18.4</v>
       </c>
       <c r="F90" t="n">
         <v>0.167</v>
       </c>
       <c r="G90" t="n">
-        <v>0.709</v>
+        <v>-0.107</v>
       </c>
     </row>
     <row r="91">
@@ -3060,20 +3060,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-0.179</v>
+        <v>-1.645</v>
       </c>
       <c r="E91" t="n">
-        <v>18.2</v>
+        <v>23.4</v>
       </c>
       <c r="F91" t="n">
         <v>0.167</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.005</v>
+        <v>-0.722</v>
       </c>
     </row>
     <row r="92">
@@ -3089,20 +3089,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-1.735</v>
+        <v>-1.594</v>
       </c>
       <c r="E92" t="n">
-        <v>22.3</v>
+        <v>29.3</v>
       </c>
       <c r="F92" t="n">
         <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.727</v>
+        <v>-0.872</v>
       </c>
     </row>
     <row r="93">
@@ -3118,20 +3118,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-1.51</v>
+        <v>-2.544</v>
       </c>
       <c r="E93" t="n">
-        <v>31.4</v>
+        <v>20.3</v>
       </c>
       <c r="F93" t="n">
         <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.878</v>
+        <v>-1.004</v>
       </c>
     </row>
     <row r="94">
@@ -3147,20 +3147,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Kam Jones</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-3.034</v>
+        <v>-3.039</v>
       </c>
       <c r="E94" t="n">
-        <v>18.6</v>
+        <v>21.7</v>
       </c>
       <c r="F94" t="n">
         <v>0.167</v>
       </c>
       <c r="G94" t="n">
-        <v>-1.113</v>
+        <v>-1.298</v>
       </c>
     </row>
     <row r="95">
@@ -3176,20 +3176,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kam Jones</t>
+          <t>Ethan Thompson</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.973</v>
+        <v>-4.803</v>
       </c>
       <c r="E95" t="n">
-        <v>21.9</v>
+        <v>19.6</v>
       </c>
       <c r="F95" t="n">
         <v>0.167</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.279</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="96">
@@ -3209,16 +3209,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.751</v>
+        <v>11.777</v>
       </c>
       <c r="E96" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="F96" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G96" t="n">
-        <v>7.841</v>
+        <v>7.912</v>
       </c>
     </row>
     <row r="97">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3.334</v>
+        <v>3.361</v>
       </c>
       <c r="E97" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G97" t="n">
-        <v>2.342</v>
+        <v>2.428</v>
       </c>
     </row>
     <row r="98">
@@ -3267,16 +3267,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.472</v>
+        <v>0.487</v>
       </c>
       <c r="E98" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G98" t="n">
-        <v>0.575</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="99">
@@ -3296,16 +3296,16 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.314</v>
+        <v>0.528</v>
       </c>
       <c r="E99" t="n">
-        <v>24.8</v>
+        <v>23.6</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G99" t="n">
-        <v>0.456</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="100">
@@ -3325,16 +3325,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-0.141</v>
+        <v>-0.15</v>
       </c>
       <c r="E100" t="n">
-        <v>28.8</v>
+        <v>27.8</v>
       </c>
       <c r="F100" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G100" t="n">
-        <v>0.256</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="101">
@@ -3354,16 +3354,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-0.294</v>
+        <v>-0.204</v>
       </c>
       <c r="E101" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="F101" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G101" t="n">
-        <v>0.146</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="102">
@@ -3383,16 +3383,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>-0.473</v>
+        <v>-0.436</v>
       </c>
       <c r="E102" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="F102" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G102" t="n">
-        <v>0.052</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="103">
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-1.54</v>
+        <v>-1.583</v>
       </c>
       <c r="E103" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="F103" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.578</v>
+        <v>-0.542</v>
       </c>
     </row>
     <row r="104">
@@ -3437,20 +3437,20 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2.267</v>
+        <v>6.013</v>
       </c>
       <c r="E104" t="n">
-        <v>21.2</v>
+        <v>34.6</v>
       </c>
       <c r="F104" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G104" t="n">
-        <v>1.281</v>
+        <v>4.723</v>
       </c>
     </row>
     <row r="105">
@@ -3466,20 +3466,20 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.5570000000000001</v>
+        <v>2.268</v>
       </c>
       <c r="E105" t="n">
-        <v>22.4</v>
+        <v>21.2</v>
       </c>
       <c r="F105" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G105" t="n">
-        <v>0.555</v>
+        <v>1.237</v>
       </c>
     </row>
     <row r="106">
@@ -3495,20 +3495,20 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.211</v>
+        <v>0.696</v>
       </c>
       <c r="E106" t="n">
-        <v>25.7</v>
+        <v>23.1</v>
       </c>
       <c r="F106" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G106" t="n">
-        <v>0.452</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="107">
@@ -3524,20 +3524,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-1.288</v>
+        <v>0.083</v>
       </c>
       <c r="E107" t="n">
-        <v>21</v>
+        <v>26.6</v>
       </c>
       <c r="F107" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.286</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="108">
@@ -3557,16 +3557,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>-1.863</v>
+        <v>-1.86</v>
       </c>
       <c r="E108" t="n">
         <v>15.8</v>
       </c>
       <c r="F108" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.404</v>
+        <v>-0.436</v>
       </c>
     </row>
     <row r="109">
@@ -3582,20 +3582,20 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jarred Vanderbilt</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>-2.217</v>
+        <v>-1.535</v>
       </c>
       <c r="E109" t="n">
-        <v>15.4</v>
+        <v>22.8</v>
       </c>
       <c r="F109" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.507</v>
+        <v>-0.475</v>
       </c>
     </row>
     <row r="110">
@@ -3615,16 +3615,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>-2.479</v>
+        <v>-2.277</v>
       </c>
       <c r="E110" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
       <c r="F110" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.93</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="111">
@@ -3644,16 +3644,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-6.512</v>
+        <v>-6.509</v>
       </c>
       <c r="E111" t="n">
         <v>15.5</v>
       </c>
       <c r="F111" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G111" t="n">
-        <v>-1.894</v>
+        <v>-1.925</v>
       </c>
     </row>
     <row r="112">
@@ -3673,16 +3673,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.213</v>
+        <v>1.214</v>
       </c>
       <c r="E112" t="n">
         <v>24.2</v>
       </c>
       <c r="F112" t="n">
-        <v>0.267</v>
+        <v>0.233</v>
       </c>
       <c r="G112" t="n">
-        <v>0.746</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="113">
@@ -3698,20 +3698,20 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Walter Clayton Jr.</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.124</v>
+        <v>-1.866</v>
       </c>
       <c r="E113" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="F113" t="n">
-        <v>0.267</v>
+        <v>0.233</v>
       </c>
       <c r="G113" t="n">
-        <v>0.194</v>
+        <v>-0.849</v>
       </c>
     </row>
     <row r="114">
@@ -3727,20 +3727,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Walter Clayton Jr.</t>
+          <t>Jahmai Mashack</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>-1.95</v>
+        <v>-5.138</v>
       </c>
       <c r="E114" t="n">
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="F114" t="n">
-        <v>0.267</v>
+        <v>0.233</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.874</v>
+        <v>-2.593</v>
       </c>
     </row>
     <row r="115">
@@ -3756,49 +3756,49 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Rayan Rupert</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>-1.942</v>
+        <v>-5.724</v>
       </c>
       <c r="E115" t="n">
-        <v>25.3</v>
+        <v>26.7</v>
       </c>
       <c r="F115" t="n">
-        <v>0.267</v>
+        <v>0.233</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.883</v>
+        <v>-3.053</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rayan Rupert</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-5.725</v>
+        <v>2.948</v>
       </c>
       <c r="E116" t="n">
-        <v>26.7</v>
+        <v>35.8</v>
       </c>
       <c r="F116" t="n">
-        <v>0.267</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G116" t="n">
-        <v>-3.034</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="117">
@@ -3814,20 +3814,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3.012</v>
+        <v>2.077</v>
       </c>
       <c r="E117" t="n">
-        <v>35.7</v>
+        <v>33.1</v>
       </c>
       <c r="F117" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G117" t="n">
-        <v>2.639</v>
+        <v>1.821</v>
       </c>
     </row>
     <row r="118">
@@ -3843,20 +3843,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2.269</v>
+        <v>2.122</v>
       </c>
       <c r="E118" t="n">
-        <v>32.7</v>
+        <v>27.8</v>
       </c>
       <c r="F118" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91</v>
+        <v>1.558</v>
       </c>
     </row>
     <row r="119">
@@ -3872,20 +3872,20 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2.403</v>
+        <v>1.893</v>
       </c>
       <c r="E119" t="n">
-        <v>28.3</v>
+        <v>28.6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>1.73</v>
+        <v>1.464</v>
       </c>
     </row>
     <row r="120">
@@ -3901,20 +3901,20 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1.716</v>
+        <v>2.573</v>
       </c>
       <c r="E120" t="n">
-        <v>28.6</v>
+        <v>21.5</v>
       </c>
       <c r="F120" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G120" t="n">
-        <v>1.339</v>
+        <v>1.406</v>
       </c>
     </row>
     <row r="121">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2.335</v>
+        <v>1.018</v>
       </c>
       <c r="E121" t="n">
-        <v>22</v>
+        <v>27.2</v>
       </c>
       <c r="F121" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>1.315</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="122">
@@ -3959,20 +3959,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1.015</v>
+        <v>0.4</v>
       </c>
       <c r="E122" t="n">
-        <v>26.8</v>
+        <v>28.6</v>
       </c>
       <c r="F122" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>0.865</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="123">
@@ -3988,49 +3988,49 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.411</v>
+        <v>-0.721</v>
       </c>
       <c r="E123" t="n">
-        <v>28.7</v>
+        <v>31</v>
       </c>
       <c r="F123" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G123" t="n">
-        <v>0.5639999999999999</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-0.52</v>
+        <v>3.972</v>
       </c>
       <c r="E124" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="F124" t="n">
-        <v>0.533</v>
+        <v>0.2</v>
       </c>
       <c r="G124" t="n">
-        <v>0.008999999999999999</v>
+        <v>2.784</v>
       </c>
     </row>
     <row r="125">
@@ -4046,20 +4046,20 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-0.629</v>
+        <v>0.518</v>
       </c>
       <c r="E125" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="F125" t="n">
         <v>0.2</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.213</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="126">
@@ -4075,20 +4075,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cole Anthony</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-2.029</v>
+        <v>-0.334</v>
       </c>
       <c r="E126" t="n">
-        <v>15.7</v>
+        <v>25.2</v>
       </c>
       <c r="F126" t="n">
         <v>0.2</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.6</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -4104,20 +4104,20 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Gary Harris</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>-3.391</v>
+        <v>-0.632</v>
       </c>
       <c r="E127" t="n">
-        <v>15.4</v>
+        <v>24.8</v>
       </c>
       <c r="F127" t="n">
         <v>0.2</v>
       </c>
       <c r="G127" t="n">
-        <v>-1.021</v>
+        <v>-0.223</v>
       </c>
     </row>
     <row r="128">
@@ -4133,20 +4133,20 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-3.637</v>
+        <v>-2.337</v>
       </c>
       <c r="E128" t="n">
-        <v>16.3</v>
+        <v>23.3</v>
       </c>
       <c r="F128" t="n">
         <v>0.2</v>
       </c>
       <c r="G128" t="n">
-        <v>-1.168</v>
+        <v>-1.039</v>
       </c>
     </row>
     <row r="129">
@@ -4166,16 +4166,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-2.615</v>
+        <v>-2.453</v>
       </c>
       <c r="E129" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="F129" t="n">
         <v>0.2</v>
       </c>
       <c r="G129" t="n">
-        <v>-1.171</v>
+        <v>-1.117</v>
       </c>
     </row>
     <row r="130">
@@ -4195,16 +4195,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>-2.483</v>
+        <v>-2.485</v>
       </c>
       <c r="E130" t="n">
-        <v>24.9</v>
+        <v>26.4</v>
       </c>
       <c r="F130" t="n">
         <v>0.2</v>
       </c>
       <c r="G130" t="n">
-        <v>-1.184</v>
+        <v>-1.255</v>
       </c>
     </row>
     <row r="131">
@@ -4220,49 +4220,49 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-3.168</v>
+        <v>-2.85</v>
       </c>
       <c r="E131" t="n">
-        <v>22.4</v>
+        <v>29.3</v>
       </c>
       <c r="F131" t="n">
         <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>-1.387</v>
+        <v>-1.619</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-2.561</v>
+        <v>4.005</v>
       </c>
       <c r="E132" t="n">
-        <v>29.1</v>
+        <v>31.7</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="G132" t="n">
-        <v>-1.433</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="133">
@@ -4278,20 +4278,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3.993</v>
+        <v>2.79</v>
       </c>
       <c r="E133" t="n">
-        <v>31.8</v>
+        <v>29.9</v>
       </c>
       <c r="F133" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G133" t="n">
-        <v>3.135</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="134">
@@ -4307,20 +4307,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2.946</v>
+        <v>2.196</v>
       </c>
       <c r="E134" t="n">
-        <v>29.2</v>
+        <v>22.5</v>
       </c>
       <c r="F134" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G134" t="n">
-        <v>2.235</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="135">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1.347</v>
+        <v>1.215</v>
       </c>
       <c r="E135" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="F135" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G135" t="n">
-        <v>1.289</v>
+        <v>1.193</v>
       </c>
     </row>
     <row r="136">
@@ -4369,16 +4369,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1.588</v>
+        <v>1.423</v>
       </c>
       <c r="E136" t="n">
         <v>25.6</v>
       </c>
       <c r="F136" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G136" t="n">
-        <v>1.239</v>
+        <v>1.132</v>
       </c>
     </row>
     <row r="137">
@@ -4394,20 +4394,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1.427</v>
+        <v>0.315</v>
       </c>
       <c r="E137" t="n">
-        <v>21.7</v>
+        <v>30.7</v>
       </c>
       <c r="F137" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G137" t="n">
-        <v>0.976</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="138">
@@ -4423,20 +4423,20 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.638</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>30.7</v>
+        <v>18.5</v>
       </c>
       <c r="F138" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G138" t="n">
-        <v>0.878</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="139">
@@ -4452,49 +4452,49 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Mike Conley</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>-0.228</v>
+        <v>-2.037</v>
       </c>
       <c r="E139" t="n">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="F139" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G139" t="n">
-        <v>0.191</v>
+        <v>-0.474</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mike Conley</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>-2.12</v>
+        <v>2.222</v>
       </c>
       <c r="E140" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F140" t="n">
-        <v>0.733</v>
+        <v>0.3</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.49</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="141">
@@ -4510,20 +4510,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>4.617</v>
+        <v>0.857</v>
       </c>
       <c r="E141" t="n">
-        <v>30.1</v>
+        <v>19.6</v>
       </c>
       <c r="F141" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G141" t="n">
-        <v>3.108</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="142">
@@ -4539,20 +4539,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2.221</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E142" t="n">
-        <v>32</v>
+        <v>23.3</v>
       </c>
       <c r="F142" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G142" t="n">
-        <v>1.702</v>
+        <v>-0.309</v>
       </c>
     </row>
     <row r="143">
@@ -4568,20 +4568,20 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1.002</v>
+        <v>-2.811</v>
       </c>
       <c r="E143" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="F143" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G143" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.983</v>
       </c>
     </row>
     <row r="144">
@@ -4597,20 +4597,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Micah Peavy</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>-0.986</v>
+        <v>-5.118</v>
       </c>
       <c r="E144" t="n">
-        <v>22.7</v>
+        <v>15.5</v>
       </c>
       <c r="F144" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.309</v>
+        <v>-1.555</v>
       </c>
     </row>
     <row r="145">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-2.677</v>
+        <v>-3.189</v>
       </c>
       <c r="E145" t="n">
-        <v>19.9</v>
+        <v>28</v>
       </c>
       <c r="F145" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.971</v>
+        <v>-1.684</v>
       </c>
     </row>
     <row r="146">
@@ -4655,78 +4655,78 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Micah Peavy</t>
+          <t>Jordan Hawkins</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>-5.119</v>
+        <v>-6.226</v>
       </c>
       <c r="E146" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="F146" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G146" t="n">
-        <v>-1.545</v>
+        <v>-1.921</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>-3.19</v>
+        <v>6.466</v>
       </c>
       <c r="E147" t="n">
-        <v>28</v>
+        <v>36.6</v>
       </c>
       <c r="F147" t="n">
-        <v>0.333</v>
+        <v>0.867</v>
       </c>
       <c r="G147" t="n">
-        <v>-1.665</v>
+        <v>5.584</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jordan Hawkins</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-6.227</v>
+        <v>4.451</v>
       </c>
       <c r="E148" t="n">
-        <v>15.6</v>
+        <v>30.1</v>
       </c>
       <c r="F148" t="n">
-        <v>0.333</v>
+        <v>0.867</v>
       </c>
       <c r="G148" t="n">
-        <v>-1.911</v>
+        <v>3.339</v>
       </c>
     </row>
     <row r="149">
@@ -4742,20 +4742,20 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>6.369</v>
+        <v>2.862</v>
       </c>
       <c r="E149" t="n">
-        <v>36.4</v>
+        <v>30.5</v>
       </c>
       <c r="F149" t="n">
         <v>0.867</v>
       </c>
       <c r="G149" t="n">
-        <v>5.483</v>
+        <v>2.372</v>
       </c>
     </row>
     <row r="150">
@@ -4771,20 +4771,20 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4.255</v>
+        <v>2.788</v>
       </c>
       <c r="E150" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="F150" t="n">
         <v>0.867</v>
       </c>
       <c r="G150" t="n">
-        <v>3.195</v>
+        <v>2.269</v>
       </c>
     </row>
     <row r="151">
@@ -4800,20 +4800,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2.984</v>
+        <v>2.053</v>
       </c>
       <c r="E151" t="n">
-        <v>29.7</v>
+        <v>34.7</v>
       </c>
       <c r="F151" t="n">
         <v>0.867</v>
       </c>
       <c r="G151" t="n">
-        <v>2.384</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="152">
@@ -4829,20 +4829,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2.848</v>
+        <v>3.496</v>
       </c>
       <c r="E152" t="n">
-        <v>30.1</v>
+        <v>20.2</v>
       </c>
       <c r="F152" t="n">
         <v>0.867</v>
       </c>
       <c r="G152" t="n">
-        <v>2.326</v>
+        <v>1.839</v>
       </c>
     </row>
     <row r="153">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2.018</v>
+        <v>0.293</v>
       </c>
       <c r="E153" t="n">
-        <v>34.3</v>
+        <v>26.1</v>
       </c>
       <c r="F153" t="n">
         <v>0.867</v>
       </c>
       <c r="G153" t="n">
-        <v>2.063</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="154">
@@ -4887,78 +4887,78 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3.283</v>
+        <v>-1.277</v>
       </c>
       <c r="E154" t="n">
-        <v>19.9</v>
+        <v>24.5</v>
       </c>
       <c r="F154" t="n">
         <v>0.867</v>
       </c>
       <c r="G154" t="n">
-        <v>1.723</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Kenrich Williams</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.361</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E155" t="n">
-        <v>26.8</v>
+        <v>16.3</v>
       </c>
       <c r="F155" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.362</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>-1.099</v>
+        <v>-1.793</v>
       </c>
       <c r="E156" t="n">
-        <v>24.4</v>
+        <v>17.3</v>
       </c>
       <c r="F156" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.119</v>
+        <v>-0.285</v>
       </c>
     </row>
     <row r="157">
@@ -4974,20 +4974,20 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>14.773</v>
+        <v>-2.24</v>
       </c>
       <c r="E157" t="n">
-        <v>34.1</v>
+        <v>16.8</v>
       </c>
       <c r="F157" t="n">
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>11.191</v>
+        <v>-0.433</v>
       </c>
     </row>
     <row r="158">
@@ -5003,194 +5003,194 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3.869</v>
+        <v>-4.092</v>
       </c>
       <c r="E158" t="n">
-        <v>28.8</v>
+        <v>24.4</v>
       </c>
       <c r="F158" t="n">
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>2.921</v>
+        <v>-1.571</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3.4</v>
+        <v>3.335</v>
       </c>
       <c r="E159" t="n">
-        <v>22.3</v>
+        <v>33.7</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G159" t="n">
-        <v>2.044</v>
+        <v>2.644</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1.816</v>
+        <v>3.162</v>
       </c>
       <c r="E160" t="n">
-        <v>25.4</v>
+        <v>35.2</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G160" t="n">
-        <v>1.49</v>
+        <v>2.638</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1.548</v>
+        <v>3.193</v>
       </c>
       <c r="E161" t="n">
-        <v>21.1</v>
+        <v>30.9</v>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G161" t="n">
-        <v>1.119</v>
+        <v>2.334</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jaylin Williams</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1.239</v>
+        <v>1.589</v>
       </c>
       <c r="E162" t="n">
-        <v>21</v>
+        <v>25.4</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G162" t="n">
-        <v>0.98</v>
+        <v>1.069</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>-0.021</v>
+        <v>0.33</v>
       </c>
       <c r="E163" t="n">
-        <v>24.5</v>
+        <v>28.7</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G163" t="n">
-        <v>0.5</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-4.439</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="E164" t="n">
-        <v>24.7</v>
+        <v>29.9</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="G164" t="n">
-        <v>-1.773</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="165">
@@ -5206,20 +5206,20 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3.246</v>
+        <v>-1.331</v>
       </c>
       <c r="E165" t="n">
-        <v>33.9</v>
+        <v>28.7</v>
       </c>
       <c r="F165" t="n">
         <v>0.433</v>
       </c>
       <c r="G165" t="n">
-        <v>2.601</v>
+        <v>-0.536</v>
       </c>
     </row>
     <row r="166">
@@ -5235,194 +5235,194 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Orlando Robinson</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3.03</v>
+        <v>-2.268</v>
       </c>
       <c r="E166" t="n">
-        <v>35.2</v>
+        <v>22.2</v>
       </c>
       <c r="F166" t="n">
         <v>0.433</v>
       </c>
       <c r="G166" t="n">
-        <v>2.537</v>
+        <v>-0.847</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2.939</v>
+        <v>8.903</v>
       </c>
       <c r="E167" t="n">
-        <v>30.6</v>
+        <v>37</v>
       </c>
       <c r="F167" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G167" t="n">
-        <v>2.149</v>
+        <v>7.218</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1.676</v>
+        <v>2.643</v>
       </c>
       <c r="E168" t="n">
-        <v>26</v>
+        <v>32.8</v>
       </c>
       <c r="F168" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G168" t="n">
-        <v>1.143</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.312</v>
+        <v>0.728</v>
       </c>
       <c r="E169" t="n">
-        <v>30.1</v>
+        <v>34</v>
       </c>
       <c r="F169" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G169" t="n">
-        <v>0.468</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-0.644</v>
+        <v>-0.516</v>
       </c>
       <c r="E170" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="F170" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.132</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Eric Gordon</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>-1.171</v>
+        <v>-0.762</v>
       </c>
       <c r="E171" t="n">
-        <v>28.7</v>
+        <v>23</v>
       </c>
       <c r="F171" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.442</v>
+        <v>-0.141</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Orlando Robinson</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-2.273</v>
+        <v>-1.263</v>
       </c>
       <c r="E172" t="n">
-        <v>22.2</v>
+        <v>23.4</v>
       </c>
       <c r="F172" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G172" t="n">
-        <v>-0.85</v>
+        <v>-0.389</v>
       </c>
     </row>
     <row r="173">
@@ -5438,20 +5438,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Adem Bona</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>9.098000000000001</v>
+        <v>-1.8</v>
       </c>
       <c r="E173" t="n">
-        <v>36.5</v>
+        <v>19.3</v>
       </c>
       <c r="F173" t="n">
         <v>0.467</v>
       </c>
       <c r="G173" t="n">
-        <v>7.268</v>
+        <v>-0.537</v>
       </c>
     </row>
     <row r="174">
@@ -5467,194 +5467,194 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5.211</v>
+        <v>-1.696</v>
       </c>
       <c r="E174" t="n">
-        <v>34.2</v>
+        <v>29.8</v>
       </c>
       <c r="F174" t="n">
         <v>0.467</v>
       </c>
       <c r="G174" t="n">
-        <v>4.046</v>
+        <v>-0.764</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2.811</v>
+        <v>3.893</v>
       </c>
       <c r="E175" t="n">
-        <v>32.4</v>
+        <v>27.5</v>
       </c>
       <c r="F175" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G175" t="n">
-        <v>2.216</v>
+        <v>2.521</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.76</v>
+        <v>2.683</v>
       </c>
       <c r="E176" t="n">
-        <v>32.6</v>
+        <v>26.8</v>
       </c>
       <c r="F176" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G176" t="n">
-        <v>0.832</v>
+        <v>1.778</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Mark Williams</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>-0.385</v>
+        <v>2.907</v>
       </c>
       <c r="E177" t="n">
-        <v>31.2</v>
+        <v>22.2</v>
       </c>
       <c r="F177" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G177" t="n">
-        <v>0.053</v>
+        <v>1.577</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Eric Gordon</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>-0.767</v>
+        <v>0.134</v>
       </c>
       <c r="E178" t="n">
-        <v>23</v>
+        <v>25.2</v>
       </c>
       <c r="F178" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.144</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>-1.381</v>
+        <v>-0.263</v>
       </c>
       <c r="E179" t="n">
-        <v>23.7</v>
+        <v>27.7</v>
       </c>
       <c r="F179" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.451</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>-1.51</v>
+        <v>-1.435</v>
       </c>
       <c r="E180" t="n">
-        <v>29.9</v>
+        <v>30.6</v>
       </c>
       <c r="F180" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.649</v>
+        <v>-0.597</v>
       </c>
     </row>
     <row r="181">
@@ -5670,20 +5670,20 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Rasheer Fleming</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>4.841</v>
+        <v>-2.783</v>
       </c>
       <c r="E181" t="n">
-        <v>33.7</v>
+        <v>18.2</v>
       </c>
       <c r="F181" t="n">
         <v>0.5</v>
       </c>
       <c r="G181" t="n">
-        <v>3.746</v>
+        <v>-0.866</v>
       </c>
     </row>
     <row r="182">
@@ -5699,194 +5699,194 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4.062</v>
+        <v>-2.341</v>
       </c>
       <c r="E182" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="F182" t="n">
         <v>0.5</v>
       </c>
       <c r="G182" t="n">
-        <v>2.791</v>
+        <v>-1.137</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>2.601</v>
+        <v>5.725</v>
       </c>
       <c r="E183" t="n">
-        <v>28.1</v>
+        <v>32.4</v>
       </c>
       <c r="F183" t="n">
-        <v>0.5</v>
+        <v>0.367</v>
       </c>
       <c r="G183" t="n">
-        <v>1.818</v>
+        <v>4.109</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.844</v>
+        <v>5.735</v>
       </c>
       <c r="E184" t="n">
-        <v>23.7</v>
+        <v>19</v>
       </c>
       <c r="F184" t="n">
-        <v>0.5</v>
+        <v>0.367</v>
       </c>
       <c r="G184" t="n">
-        <v>0.662</v>
+        <v>2.419</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.277</v>
+        <v>3.37</v>
       </c>
       <c r="E185" t="n">
-        <v>26.4</v>
+        <v>30.1</v>
       </c>
       <c r="F185" t="n">
-        <v>0.5</v>
+        <v>0.367</v>
       </c>
       <c r="G185" t="n">
-        <v>0.428</v>
+        <v>2.345</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>-0.385</v>
+        <v>3.093</v>
       </c>
       <c r="E186" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="F186" t="n">
-        <v>0.5</v>
+        <v>0.367</v>
       </c>
       <c r="G186" t="n">
-        <v>0.06900000000000001</v>
+        <v>1.928</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-1.103</v>
       </c>
       <c r="E187" t="n">
-        <v>30.2</v>
+        <v>31.3</v>
       </c>
       <c r="F187" t="n">
-        <v>0.5</v>
+        <v>0.367</v>
       </c>
       <c r="G187" t="n">
-        <v>-0.277</v>
+        <v>-0.481</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>-2.124</v>
+        <v>-1.909</v>
       </c>
       <c r="E188" t="n">
-        <v>29.5</v>
+        <v>25.1</v>
       </c>
       <c r="F188" t="n">
-        <v>0.5</v>
+        <v>0.367</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.997</v>
+        <v>-0.8080000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -5902,20 +5902,20 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Caleb Love</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>5.757</v>
+        <v>-2.934</v>
       </c>
       <c r="E189" t="n">
-        <v>29.8</v>
+        <v>22.2</v>
       </c>
       <c r="F189" t="n">
         <v>0.367</v>
       </c>
       <c r="G189" t="n">
-        <v>3.803</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="190">
@@ -5931,194 +5931,194 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>5.996</v>
+        <v>-3.442</v>
       </c>
       <c r="E190" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="F190" t="n">
         <v>0.367</v>
       </c>
       <c r="G190" t="n">
-        <v>2.52</v>
+        <v>-1.244</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>3.313</v>
+        <v>0.396</v>
       </c>
       <c r="E191" t="n">
-        <v>30</v>
+        <v>22.8</v>
       </c>
       <c r="F191" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G191" t="n">
-        <v>2.299</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>3.097</v>
+        <v>0.416</v>
       </c>
       <c r="E192" t="n">
-        <v>26.4</v>
+        <v>20.3</v>
       </c>
       <c r="F192" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G192" t="n">
-        <v>1.907</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>-1.27</v>
+        <v>0.061</v>
       </c>
       <c r="E193" t="n">
-        <v>31.6</v>
+        <v>30.8</v>
       </c>
       <c r="F193" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G193" t="n">
-        <v>-0.596</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>-2.075</v>
+        <v>-1.14</v>
       </c>
       <c r="E194" t="n">
-        <v>24.1</v>
+        <v>32.3</v>
       </c>
       <c r="F194" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G194" t="n">
-        <v>-0.857</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>-3.273</v>
+        <v>-1.678</v>
       </c>
       <c r="E195" t="n">
-        <v>19.1</v>
+        <v>22.8</v>
       </c>
       <c r="F195" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G195" t="n">
-        <v>-1.155</v>
+        <v>-0.751</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Caleb Love</t>
+          <t>Daeqwon Plowden</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>-2.973</v>
+        <v>-3.182</v>
       </c>
       <c r="E196" t="n">
-        <v>24.1</v>
+        <v>29.9</v>
       </c>
       <c r="F196" t="n">
-        <v>0.367</v>
+        <v>0.1</v>
       </c>
       <c r="G196" t="n">
-        <v>-1.308</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="197">
@@ -6134,20 +6134,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>DaQuan Jeffries</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.461</v>
+        <v>-3.99</v>
       </c>
       <c r="E197" t="n">
-        <v>23.7</v>
+        <v>26.4</v>
       </c>
       <c r="F197" t="n">
         <v>0.1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.277</v>
+        <v>-2.137</v>
       </c>
     </row>
     <row r="198">
@@ -6163,194 +6163,194 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.193</v>
+        <v>-4.07</v>
       </c>
       <c r="E198" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="F198" t="n">
         <v>0.1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.196</v>
+        <v>-2.793</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.058</v>
+        <v>11.787</v>
       </c>
       <c r="E199" t="n">
-        <v>20.6</v>
+        <v>30.6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G199" t="n">
-        <v>0.068</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-1.096</v>
+        <v>3.962</v>
       </c>
       <c r="E200" t="n">
-        <v>31.9</v>
+        <v>29.4</v>
       </c>
       <c r="F200" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G200" t="n">
-        <v>-0.661</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-1.692</v>
+        <v>3.498</v>
       </c>
       <c r="E201" t="n">
-        <v>22.4</v>
+        <v>31.4</v>
       </c>
       <c r="F201" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G201" t="n">
-        <v>-0.743</v>
+        <v>2.917</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Daeqwon Plowden</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>-3.151</v>
+        <v>1.804</v>
       </c>
       <c r="E202" t="n">
-        <v>28.9</v>
+        <v>23.9</v>
       </c>
       <c r="F202" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G202" t="n">
-        <v>-1.838</v>
+        <v>1.379</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>DaQuan Jeffries</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>-3.996</v>
+        <v>0.794</v>
       </c>
       <c r="E203" t="n">
-        <v>26.4</v>
+        <v>23</v>
       </c>
       <c r="F203" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G203" t="n">
-        <v>-2.14</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>-4.166</v>
+        <v>0.385</v>
       </c>
       <c r="E204" t="n">
-        <v>33.8</v>
+        <v>27.1</v>
       </c>
       <c r="F204" t="n">
-        <v>0.1</v>
+        <v>0.967</v>
       </c>
       <c r="G204" t="n">
-        <v>-2.867</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="205">
@@ -6366,11 +6366,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>11.787</v>
+        <v>0.15</v>
       </c>
       <c r="E205" t="n">
         <v>30.6</v>
@@ -6379,7 +6379,7 @@
         <v>0.967</v>
       </c>
       <c r="G205" t="n">
-        <v>8.119999999999999</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="206">
@@ -6395,194 +6395,194 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>4.028</v>
+        <v>-0.989</v>
       </c>
       <c r="E206" t="n">
-        <v>29.7</v>
+        <v>20.8</v>
       </c>
       <c r="F206" t="n">
         <v>0.967</v>
       </c>
       <c r="G206" t="n">
-        <v>3.086</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>3.497</v>
+        <v>6.22</v>
       </c>
       <c r="E207" t="n">
-        <v>31.4</v>
+        <v>31</v>
       </c>
       <c r="F207" t="n">
-        <v>0.967</v>
+        <v>0.6</v>
       </c>
       <c r="G207" t="n">
-        <v>2.916</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1.671</v>
+        <v>4.274</v>
       </c>
       <c r="E208" t="n">
-        <v>23.4</v>
+        <v>31.6</v>
       </c>
       <c r="F208" t="n">
-        <v>0.967</v>
+        <v>0.6</v>
       </c>
       <c r="G208" t="n">
-        <v>1.285</v>
+        <v>3.205</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.826</v>
+        <v>2.013</v>
       </c>
       <c r="E209" t="n">
-        <v>23</v>
+        <v>32.7</v>
       </c>
       <c r="F209" t="n">
-        <v>0.967</v>
+        <v>0.6</v>
       </c>
       <c r="G209" t="n">
-        <v>0.859</v>
+        <v>1.779</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.395</v>
+        <v>1.95</v>
       </c>
       <c r="E210" t="n">
-        <v>27.3</v>
+        <v>25.8</v>
       </c>
       <c r="F210" t="n">
-        <v>0.967</v>
+        <v>0.6</v>
       </c>
       <c r="G210" t="n">
-        <v>0.774</v>
+        <v>1.369</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.151</v>
+        <v>1.4</v>
       </c>
       <c r="E211" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="F211" t="n">
-        <v>0.967</v>
+        <v>0.6</v>
       </c>
       <c r="G211" t="n">
-        <v>0.713</v>
+        <v>1.287</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>-0.873</v>
+        <v>1.216</v>
       </c>
       <c r="E212" t="n">
-        <v>20.7</v>
+        <v>21.9</v>
       </c>
       <c r="F212" t="n">
-        <v>0.967</v>
+        <v>0.6</v>
       </c>
       <c r="G212" t="n">
-        <v>0.04</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="213">
@@ -6598,20 +6598,20 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>6.192</v>
+        <v>-0.442</v>
       </c>
       <c r="E213" t="n">
-        <v>31.5</v>
+        <v>25.2</v>
       </c>
       <c r="F213" t="n">
         <v>0.6</v>
       </c>
       <c r="G213" t="n">
-        <v>4.464</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="214">
@@ -6627,194 +6627,194 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>4.638</v>
+        <v>-0.77</v>
       </c>
       <c r="E214" t="n">
-        <v>33</v>
+        <v>24.5</v>
       </c>
       <c r="F214" t="n">
         <v>0.6</v>
       </c>
       <c r="G214" t="n">
-        <v>3.6</v>
+        <v>-0.08699999999999999</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>2.009</v>
+        <v>1.266</v>
       </c>
       <c r="E215" t="n">
-        <v>33.2</v>
+        <v>27</v>
       </c>
       <c r="F215" t="n">
-        <v>0.6</v>
+        <v>0.133</v>
       </c>
       <c r="G215" t="n">
-        <v>1.803</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Oscar Tshiebwe</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1.705</v>
+        <v>1.211</v>
       </c>
       <c r="E216" t="n">
-        <v>30.9</v>
+        <v>17.2</v>
       </c>
       <c r="F216" t="n">
-        <v>0.6</v>
+        <v>0.133</v>
       </c>
       <c r="G216" t="n">
-        <v>1.482</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Kevin Love</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1.981</v>
+        <v>1.115</v>
       </c>
       <c r="E217" t="n">
-        <v>26.6</v>
+        <v>15.5</v>
       </c>
       <c r="F217" t="n">
-        <v>0.6</v>
+        <v>0.133</v>
       </c>
       <c r="G217" t="n">
-        <v>1.433</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1.112</v>
+        <v>-1.114</v>
       </c>
       <c r="E218" t="n">
-        <v>22.7</v>
+        <v>19</v>
       </c>
       <c r="F218" t="n">
-        <v>0.6</v>
+        <v>0.133</v>
       </c>
       <c r="G218" t="n">
-        <v>0.8080000000000001</v>
+        <v>-0.389</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Svi Mykhailiuk</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>-0.309</v>
+        <v>-1.13</v>
       </c>
       <c r="E219" t="n">
-        <v>24.1</v>
+        <v>19.4</v>
       </c>
       <c r="F219" t="n">
-        <v>0.6</v>
+        <v>0.133</v>
       </c>
       <c r="G219" t="n">
-        <v>0.146</v>
+        <v>-0.403</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>-0.955</v>
+        <v>-2.059</v>
       </c>
       <c r="E220" t="n">
-        <v>23.7</v>
+        <v>30.3</v>
       </c>
       <c r="F220" t="n">
-        <v>0.6</v>
+        <v>0.133</v>
       </c>
       <c r="G220" t="n">
-        <v>-0.175</v>
+        <v>-1.216</v>
       </c>
     </row>
     <row r="221">
@@ -6830,223 +6830,223 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Cody Williams</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.255</v>
+        <v>-3.777</v>
       </c>
       <c r="E221" t="n">
-        <v>26.7</v>
+        <v>35</v>
       </c>
       <c r="F221" t="n">
         <v>0.133</v>
       </c>
       <c r="G221" t="n">
-        <v>0.771</v>
+        <v>-2.657</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1.102</v>
+        <v>1.698</v>
       </c>
       <c r="E222" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="F222" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G222" t="n">
-        <v>0.676</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Oscar Tshiebwe</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1.856</v>
+        <v>-0.655</v>
       </c>
       <c r="E223" t="n">
-        <v>16</v>
+        <v>24.9</v>
       </c>
       <c r="F223" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G223" t="n">
-        <v>0.664</v>
+        <v>-0.322</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Kevin Love</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1.114</v>
+        <v>-0.923</v>
       </c>
       <c r="E224" t="n">
-        <v>15.5</v>
+        <v>27.1</v>
       </c>
       <c r="F224" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G224" t="n">
-        <v>0.402</v>
+        <v>-0.502</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-0.186</v>
+        <v>-1.724</v>
       </c>
       <c r="E225" t="n">
-        <v>27.7</v>
+        <v>22.7</v>
       </c>
       <c r="F225" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.031</v>
+        <v>-0.799</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>Sharife Cooper</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>-1.114</v>
+        <v>-2.258</v>
       </c>
       <c r="E226" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="F226" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.389</v>
+        <v>-0.861</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Svi Mykhailiuk</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>-1.131</v>
+        <v>-1.899</v>
       </c>
       <c r="E227" t="n">
-        <v>19.4</v>
+        <v>27.2</v>
       </c>
       <c r="F227" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.403</v>
+        <v>-1.058</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Jaden Hardy</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-3.755</v>
+        <v>-3.191</v>
       </c>
       <c r="E228" t="n">
-        <v>35</v>
+        <v>21.3</v>
       </c>
       <c r="F228" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="G228" t="n">
-        <v>-2.639</v>
+        <v>-1.403</v>
       </c>
     </row>
     <row r="229">
@@ -7062,194 +7062,20 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1.793</v>
+        <v>-2.215</v>
       </c>
       <c r="E229" t="n">
-        <v>20.9</v>
+        <v>32.2</v>
       </c>
       <c r="F229" t="n">
         <v>0.033</v>
       </c>
       <c r="G229" t="n">
-        <v>0.795</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Anthony Gill</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>-0.9330000000000001</v>
-      </c>
-      <c r="E230" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F230" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G230" t="n">
-        <v>-0.455</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Bilal Coulibaly</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>-0.967</v>
-      </c>
-      <c r="E231" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="F231" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G231" t="n">
-        <v>-0.524</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Jamir Watkins</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>-1.613</v>
-      </c>
-      <c r="E232" t="n">
-        <v>21</v>
-      </c>
-      <c r="F232" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G232" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Sharife Cooper</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>-2.408</v>
-      </c>
-      <c r="E233" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F233" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G233" t="n">
-        <v>-0.899</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Bub Carrington</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>-1.908</v>
-      </c>
-      <c r="E234" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="F234" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G234" t="n">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Will Riley</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>-2.078</v>
-      </c>
-      <c r="E235" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F235" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G235" t="n">
-        <v>-1.37</v>
+        <v>-1.464</v>
       </c>
     </row>
   </sheetData>
@@ -7321,10 +7147,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>22.064</v>
+        <v>22.652</v>
       </c>
       <c r="F2" t="n">
-        <v>2.769</v>
+        <v>2.764</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7338,26 +7164,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>21.669</v>
+        <v>21.183</v>
       </c>
       <c r="F3" t="n">
-        <v>3.332</v>
+        <v>3.054</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
     </row>
@@ -7367,26 +7193,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>21.458</v>
+        <v>17.934</v>
       </c>
       <c r="F4" t="n">
-        <v>3.141</v>
+        <v>2.641</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -7396,26 +7222,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>18.472</v>
+        <v>17.744</v>
       </c>
       <c r="F5" t="n">
-        <v>2.773</v>
+        <v>2.674</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
     </row>
@@ -7425,26 +7251,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>17.793</v>
+        <v>14.834</v>
       </c>
       <c r="F6" t="n">
-        <v>2.685</v>
+        <v>1.908</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7454,26 +7280,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>17.741</v>
+        <v>14.117</v>
       </c>
       <c r="F7" t="n">
-        <v>2.627</v>
+        <v>1.914</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
     </row>
@@ -7483,26 +7309,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>14.876</v>
+        <v>13.712</v>
       </c>
       <c r="F8" t="n">
-        <v>1.938</v>
+        <v>1.086</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
     </row>
@@ -7512,26 +7338,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>13.574</v>
+        <v>12.864</v>
       </c>
       <c r="F9" t="n">
-        <v>1.074</v>
+        <v>1.983</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7541,26 +7367,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>13.561</v>
+        <v>12.588</v>
       </c>
       <c r="F10" t="n">
-        <v>2.047</v>
+        <v>1.829</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7570,26 +7396,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>13.171</v>
+        <v>11.741</v>
       </c>
       <c r="F11" t="n">
-        <v>1.73</v>
+        <v>1.522</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>James Harden</t>
         </is>
       </c>
     </row>
@@ -7599,26 +7425,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>12.681</v>
+        <v>11.679</v>
       </c>
       <c r="F12" t="n">
-        <v>1.908</v>
+        <v>1.722</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7628,26 +7454,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.09</v>
+        <v>10.245</v>
       </c>
       <c r="F13" t="n">
-        <v>1.678</v>
+        <v>1.539</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
     </row>
@@ -7657,26 +7483,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>10.371</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.228</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -7698,10 +7524,10 @@
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>9.539999999999999</v>
+        <v>8.571999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.665</v>
+        <v>1.346</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -7715,26 +7541,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>9.452999999999999</v>
+        <v>8.327</v>
       </c>
       <c r="F16" t="n">
-        <v>1.199</v>
+        <v>0.78</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7744,26 +7570,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>8.24</v>
+        <v>7.678</v>
       </c>
       <c r="F17" t="n">
-        <v>1.147</v>
+        <v>0.931</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
     </row>
@@ -7773,26 +7599,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>7.474</v>
+        <v>7.078</v>
       </c>
       <c r="F18" t="n">
-        <v>0.889</v>
+        <v>1.067</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
     </row>
@@ -7802,26 +7628,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>7.181</v>
+        <v>3.746</v>
       </c>
       <c r="F19" t="n">
-        <v>0.579</v>
+        <v>0.349</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
     </row>
@@ -7831,26 +7657,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>6.613</v>
+        <v>3.137</v>
       </c>
       <c r="F20" t="n">
-        <v>1.072</v>
+        <v>-0.39</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>LeBron James</t>
         </is>
       </c>
     </row>
@@ -7872,10 +7698,10 @@
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>2.623</v>
+        <v>1.586</v>
       </c>
       <c r="F21" t="n">
-        <v>0.39</v>
+        <v>0.012</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -7889,26 +7715,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.949</v>
+        <v>-1.927</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.107</v>
+        <v>-2.014</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Kenrich Williams</t>
         </is>
       </c>
     </row>
@@ -7918,26 +7744,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.031</v>
+        <v>-2.196</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.295</v>
+        <v>-0.825</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
     </row>
@@ -7947,26 +7773,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.563</v>
+        <v>-2.993</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.446</v>
+        <v>-0.641</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>John Konchar</t>
         </is>
       </c>
     </row>
@@ -7976,26 +7802,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.733</v>
+        <v>-3.486</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.416</v>
+        <v>-1.344</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Tre Jones</t>
         </is>
       </c>
     </row>
@@ -8005,26 +7831,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.63</v>
+        <v>-4.105</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.41</v>
+        <v>-1.249</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tre Jones</t>
+          <t>Jay Huff</t>
         </is>
       </c>
     </row>
@@ -8034,26 +7860,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.851</v>
+        <v>-4.299</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.656</v>
+        <v>-2.171</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
     </row>
@@ -8072,13 +7898,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.233</v>
+        <v>-5.598</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.159</v>
+        <v>-1.396</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -8092,26 +7918,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.708</v>
+        <v>-5.766</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.674</v>
+        <v>-2.878</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
     </row>
@@ -8121,26 +7947,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-8.177</v>
+        <v>-7.744</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.564</v>
+        <v>-1.648</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Malik Monk</t>
         </is>
       </c>
     </row>
@@ -8162,10 +7988,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>-10.102</v>
+        <v>-10.362</v>
       </c>
       <c r="F31" t="n">
-        <v>-4.02</v>
+        <v>-3.918</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G229"/>
+  <dimension ref="A1:G206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.125</v>
+        <v>7.933</v>
       </c>
       <c r="E2" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G2" t="n">
-        <v>6.579</v>
+        <v>6.455</v>
       </c>
     </row>
     <row r="3">
@@ -512,16 +512,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.872</v>
+        <v>3.829</v>
       </c>
       <c r="E3" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G3" t="n">
-        <v>3.199</v>
+        <v>3.208</v>
       </c>
     </row>
     <row r="4">
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.586</v>
+        <v>2.589</v>
       </c>
       <c r="E4" t="n">
         <v>32.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G4" t="n">
-        <v>2.208</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="5">
@@ -566,20 +566,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Keaton Wallace</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.43</v>
+        <v>-0.595</v>
       </c>
       <c r="E5" t="n">
-        <v>29.8</v>
+        <v>15.8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G5" t="n">
-        <v>1.901</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="6">
@@ -595,20 +595,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Corey Kispert</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.332</v>
+        <v>-1.271</v>
       </c>
       <c r="E6" t="n">
-        <v>29.6</v>
+        <v>15.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G6" t="n">
-        <v>1.828</v>
+        <v>-0.194</v>
       </c>
     </row>
     <row r="7">
@@ -624,20 +624,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Keaton Wallace</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.603</v>
+        <v>-1.824</v>
       </c>
       <c r="E7" t="n">
-        <v>15.8</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="8">
@@ -653,20 +653,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.716</v>
+        <v>-1.643</v>
       </c>
       <c r="E8" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.404</v>
+        <v>-0.449</v>
       </c>
     </row>
     <row r="9">
@@ -682,20 +682,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Caleb Houstan</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.764</v>
+        <v>-2.95</v>
       </c>
       <c r="E9" t="n">
-        <v>20.7</v>
+        <v>15.6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.487</v>
+        <v>-0.742</v>
       </c>
     </row>
     <row r="10">
@@ -711,20 +711,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Nikola Vučević</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.514</v>
+        <v>2.925</v>
       </c>
       <c r="E10" t="n">
-        <v>34.7</v>
+        <v>21.3</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.385</v>
+        <v>1.695</v>
       </c>
     </row>
     <row r="11">
@@ -740,20 +740,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Luka Garza</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.602</v>
+        <v>2.552</v>
       </c>
       <c r="E11" t="n">
-        <v>34.4</v>
+        <v>17.1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>4.679</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="12">
@@ -769,20 +769,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Chris Boucher</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.789</v>
+        <v>0.261</v>
       </c>
       <c r="E12" t="n">
-        <v>34.3</v>
+        <v>15.1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>4.092</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="13">
@@ -798,20 +798,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Jordan Walsh</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.067</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>31.9</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.322</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="14">
@@ -827,20 +827,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Dalano Banton</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.673</v>
+        <v>-1.193</v>
       </c>
       <c r="E14" t="n">
-        <v>28.4</v>
+        <v>17.4</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2.136</v>
+        <v>-0.106</v>
       </c>
     </row>
     <row r="15">
@@ -856,78 +856,78 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nikola Vučević</t>
+          <t>Baylor Scheierman</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.954</v>
+        <v>-1.296</v>
       </c>
       <c r="E15" t="n">
-        <v>21.2</v>
+        <v>23.4</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>1.714</v>
+        <v>-0.193</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Tyson Etienne</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.578</v>
+        <v>-0.929</v>
       </c>
       <c r="E16" t="n">
-        <v>25.4</v>
+        <v>18.9</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="G16" t="n">
-        <v>0.188</v>
+        <v>-0.341</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Baylor Scheierman</t>
+          <t>E.J. Liddell</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.593</v>
+        <v>-1.996</v>
       </c>
       <c r="E17" t="n">
-        <v>24.3</v>
+        <v>18.2</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.333</v>
+        <v>-0.732</v>
       </c>
     </row>
     <row r="18">
@@ -943,20 +943,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Josh Minott</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.944</v>
+        <v>-4.779</v>
       </c>
       <c r="E18" t="n">
-        <v>19.3</v>
+        <v>15.7</v>
       </c>
       <c r="F18" t="n">
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8090000000000001</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="19">
@@ -972,20 +972,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Jalen Wilson</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-4.787</v>
+        <v>-4.754</v>
       </c>
       <c r="E19" t="n">
-        <v>15.7</v>
+        <v>19.5</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.543</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="20">
@@ -1001,20 +1001,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jalen Wilson</t>
+          <t>Drake Powell</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-4.845</v>
+        <v>-5.032</v>
       </c>
       <c r="E20" t="n">
-        <v>16.1</v>
+        <v>26.7</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="21">
@@ -1030,78 +1030,78 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nolan Traore</t>
+          <t>Ben Saraf</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-4.857</v>
+        <v>-5.707</v>
       </c>
       <c r="E21" t="n">
-        <v>22.8</v>
+        <v>27.2</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.274</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Drake Powell</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-4.831</v>
+        <v>7.794</v>
       </c>
       <c r="E22" t="n">
-        <v>26.7</v>
+        <v>29.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.067</v>
+        <v>0.7</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.651</v>
+        <v>5.196</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ben Saraf</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-6.13</v>
+        <v>3.928</v>
       </c>
       <c r="E23" t="n">
-        <v>24.6</v>
+        <v>29.7</v>
       </c>
       <c r="F23" t="n">
-        <v>0.067</v>
+        <v>0.7</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.103</v>
+        <v>2.859</v>
       </c>
     </row>
     <row r="24">
@@ -1117,20 +1117,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7.509</v>
+        <v>2.716</v>
       </c>
       <c r="E24" t="n">
-        <v>28.4</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G24" t="n">
-        <v>4.884</v>
+        <v>2.206</v>
       </c>
     </row>
     <row r="25">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.224</v>
+        <v>1.906</v>
       </c>
       <c r="E25" t="n">
-        <v>29.7</v>
+        <v>28.4</v>
       </c>
       <c r="F25" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G25" t="n">
-        <v>3.068</v>
+        <v>1.541</v>
       </c>
     </row>
     <row r="26">
@@ -1175,20 +1175,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.754</v>
+        <v>1.085</v>
       </c>
       <c r="E26" t="n">
-        <v>31.3</v>
+        <v>27.5</v>
       </c>
       <c r="F26" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>2.271</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="27">
@@ -1204,20 +1204,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.793</v>
+        <v>0.76</v>
       </c>
       <c r="E27" t="n">
-        <v>28.9</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>1.52</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="28">
@@ -1233,20 +1233,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Grant Williams</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.165</v>
+        <v>-0.301</v>
       </c>
       <c r="E28" t="n">
-        <v>27.5</v>
+        <v>19.5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1.087</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="29">
@@ -1262,78 +1262,78 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Sion James</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.902</v>
+        <v>-3.623</v>
       </c>
       <c r="E29" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="F29" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6830000000000001</v>
+        <v>-1.181</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Tre Jones</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.282</v>
+        <v>4.493</v>
       </c>
       <c r="E30" t="n">
-        <v>18.7</v>
+        <v>27.7</v>
       </c>
       <c r="F30" t="n">
-        <v>0.733</v>
+        <v>0.3</v>
       </c>
       <c r="G30" t="n">
-        <v>0.176</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sion James</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-3.432</v>
+        <v>2.243</v>
       </c>
       <c r="E31" t="n">
-        <v>19.6</v>
+        <v>27.1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.733</v>
+        <v>0.3</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.101</v>
+        <v>1.434</v>
       </c>
     </row>
     <row r="32">
@@ -1349,20 +1349,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tre Jones</t>
+          <t>Leonard Miller</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.183</v>
+        <v>-0.029</v>
       </c>
       <c r="E32" t="n">
-        <v>28.3</v>
+        <v>27.1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G32" t="n">
-        <v>2.664</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="33">
@@ -1378,20 +1378,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Jaden Ivey</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.316</v>
+        <v>-0.612</v>
       </c>
       <c r="E33" t="n">
-        <v>27</v>
+        <v>19.6</v>
       </c>
       <c r="F33" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G33" t="n">
-        <v>1.491</v>
+        <v>-0.127</v>
       </c>
     </row>
     <row r="34">
@@ -1407,20 +1407,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jaden Ivey</t>
+          <t>Julian Phillips</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.62</v>
+        <v>-2.704</v>
       </c>
       <c r="E34" t="n">
-        <v>19.6</v>
+        <v>15.4</v>
       </c>
       <c r="F34" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.117</v>
+        <v>-0.773</v>
       </c>
     </row>
     <row r="35">
@@ -1436,20 +1436,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Leonard Miller</t>
+          <t>Patrick Williams</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-4.152</v>
       </c>
       <c r="E35" t="n">
-        <v>26.5</v>
+        <v>23.1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.194</v>
+        <v>-1.854</v>
       </c>
     </row>
     <row r="36">
@@ -1465,107 +1465,107 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Guerschon Yabusele</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-2.501</v>
+        <v>-6.206</v>
       </c>
       <c r="E36" t="n">
-        <v>25.1</v>
+        <v>22.5</v>
       </c>
       <c r="F36" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.133</v>
+        <v>-2.771</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Patrick Williams</t>
+          <t>Craig Porter Jr.</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-4.266</v>
+        <v>1.962</v>
       </c>
       <c r="E37" t="n">
-        <v>21.6</v>
+        <v>17.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.333</v>
+        <v>0.767</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.766</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-3.311</v>
+        <v>0.681</v>
       </c>
       <c r="E38" t="n">
-        <v>30.2</v>
+        <v>24.1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.333</v>
+        <v>0.767</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.872</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rob Dillingham</t>
+          <t>Max Strus</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-5.868</v>
+        <v>0.184</v>
       </c>
       <c r="E39" t="n">
-        <v>22.2</v>
+        <v>26.6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.333</v>
+        <v>0.767</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.559</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="40">
@@ -1581,20 +1581,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Lonzo Ball</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8.271000000000001</v>
+        <v>-1.349</v>
       </c>
       <c r="E40" t="n">
-        <v>34.9</v>
+        <v>17.6</v>
       </c>
       <c r="F40" t="n">
         <v>0.767</v>
       </c>
       <c r="G40" t="n">
-        <v>6.571</v>
+        <v>-0.213</v>
       </c>
     </row>
     <row r="41">
@@ -1610,194 +1610,194 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Nae'Qwan Tomlin</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.633</v>
+        <v>-1.522</v>
       </c>
       <c r="E41" t="n">
-        <v>30.1</v>
+        <v>16.2</v>
       </c>
       <c r="F41" t="n">
         <v>0.767</v>
       </c>
       <c r="G41" t="n">
-        <v>3.385</v>
+        <v>-0.254</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Moussa Cisse</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.22</v>
+        <v>-0.245</v>
       </c>
       <c r="E42" t="n">
-        <v>27.1</v>
+        <v>17.2</v>
       </c>
       <c r="F42" t="n">
-        <v>0.767</v>
+        <v>0.267</v>
       </c>
       <c r="G42" t="n">
-        <v>1.121</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Craig Porter Jr.</t>
+          <t>Dwight Powell</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.581</v>
+        <v>-1.814</v>
       </c>
       <c r="E43" t="n">
-        <v>16.7</v>
+        <v>15.2</v>
       </c>
       <c r="F43" t="n">
-        <v>0.767</v>
+        <v>0.267</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8169999999999999</v>
+        <v>-0.489</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-0.3</v>
+        <v>-1.638</v>
       </c>
       <c r="E44" t="n">
-        <v>20.1</v>
+        <v>21.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.767</v>
+        <v>0.267</v>
       </c>
       <c r="G44" t="n">
-        <v>0.195</v>
+        <v>-0.606</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Keon Ellis</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-0.629</v>
+        <v>-1.664</v>
       </c>
       <c r="E45" t="n">
-        <v>26.9</v>
+        <v>28.8</v>
       </c>
       <c r="F45" t="n">
-        <v>0.767</v>
+        <v>0.267</v>
       </c>
       <c r="G45" t="n">
-        <v>0.077</v>
+        <v>-0.839</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dean Wade</t>
+          <t>Ryan Nembhard</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-1.239</v>
+        <v>-2.114</v>
       </c>
       <c r="E46" t="n">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.767</v>
+        <v>0.267</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.209</v>
+        <v>-0.876</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lonzo Ball</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-1.358</v>
+        <v>-3.54</v>
       </c>
       <c r="E47" t="n">
-        <v>17.6</v>
+        <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.767</v>
+        <v>0.267</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.216</v>
+        <v>-1.296</v>
       </c>
     </row>
     <row r="48">
@@ -1813,5269 +1813,4602 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3.049</v>
+        <v>-4.441</v>
       </c>
       <c r="E48" t="n">
-        <v>34.3</v>
+        <v>17.6</v>
       </c>
       <c r="F48" t="n">
         <v>0.267</v>
       </c>
       <c r="G48" t="n">
-        <v>2.371</v>
+        <v>-1.531</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marvin Bagley III</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.514</v>
+        <v>17.887</v>
       </c>
       <c r="E49" t="n">
-        <v>21.1</v>
+        <v>36.5</v>
       </c>
       <c r="F49" t="n">
-        <v>0.267</v>
+        <v>0.833</v>
       </c>
       <c r="G49" t="n">
-        <v>1.223</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brandon Williams</t>
+          <t>Jonas Valančiūnas</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.198</v>
+        <v>1.302</v>
       </c>
       <c r="E50" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="F50" t="n">
-        <v>0.267</v>
+        <v>0.833</v>
       </c>
       <c r="G50" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Jalen Pickett</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.575</v>
+        <v>-1.597</v>
       </c>
       <c r="E51" t="n">
-        <v>29</v>
+        <v>15.7</v>
       </c>
       <c r="F51" t="n">
-        <v>0.267</v>
+        <v>0.833</v>
       </c>
       <c r="G51" t="n">
-        <v>0.509</v>
+        <v>-0.249</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-1.477</v>
+        <v>-2.346</v>
       </c>
       <c r="E52" t="n">
-        <v>20.5</v>
+        <v>15.7</v>
       </c>
       <c r="F52" t="n">
-        <v>0.267</v>
+        <v>0.833</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.517</v>
+        <v>-0.494</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ryan Nembhard</t>
+          <t>Zeke Nnaji</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-2.142</v>
+        <v>-2.441</v>
       </c>
       <c r="E53" t="n">
-        <v>19.6</v>
+        <v>15.2</v>
       </c>
       <c r="F53" t="n">
-        <v>0.267</v>
+        <v>0.833</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.764</v>
+        <v>-0.509</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1.841</v>
+        <v>-2.707</v>
       </c>
       <c r="E54" t="n">
-        <v>27.8</v>
+        <v>21.3</v>
       </c>
       <c r="F54" t="n">
-        <v>0.267</v>
+        <v>0.833</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.913</v>
+        <v>-0.833</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>KJ Simpson</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.779</v>
+        <v>-4.877</v>
       </c>
       <c r="E55" t="n">
-        <v>31.5</v>
+        <v>16.5</v>
       </c>
       <c r="F55" t="n">
-        <v>0.267</v>
+        <v>0.833</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.993</v>
+        <v>-1.392</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>18.047</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>37.1</v>
+        <v>31.4</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>14.578</v>
+        <v>6.367</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9.057</v>
+        <v>2.043</v>
       </c>
       <c r="E57" t="n">
-        <v>37</v>
+        <v>27.6</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>7.608</v>
+        <v>1.711</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.307</v>
+        <v>0.19</v>
       </c>
       <c r="E58" t="n">
-        <v>28.1</v>
+        <v>31.4</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>1.821</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.27</v>
+        <v>0.199</v>
       </c>
       <c r="E59" t="n">
-        <v>24.1</v>
+        <v>25.7</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.537</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-0.615</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>30.4</v>
+        <v>25.7</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>0.117</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Julian Strawther</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-2.353</v>
+        <v>0.03</v>
       </c>
       <c r="E61" t="n">
-        <v>15.7</v>
+        <v>24.1</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.507</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Isaiah Stewart</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-1.717</v>
+        <v>-0.089</v>
       </c>
       <c r="E62" t="n">
-        <v>32.5</v>
+        <v>20.9</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.62</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Colby Jones</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-2.886</v>
+        <v>-0.908</v>
       </c>
       <c r="E63" t="n">
-        <v>20.3</v>
+        <v>23.4</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.882</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>8.847</v>
+        <v>7.572</v>
       </c>
       <c r="E64" t="n">
-        <v>32.4</v>
+        <v>28.9</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G64" t="n">
-        <v>6.579</v>
+        <v>4.793</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5.465</v>
+        <v>3.338</v>
       </c>
       <c r="E65" t="n">
-        <v>29.8</v>
+        <v>23.6</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G65" t="n">
-        <v>3.952</v>
+        <v>1.835</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.778</v>
+        <v>2.249</v>
       </c>
       <c r="E66" t="n">
-        <v>26.5</v>
+        <v>30.9</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G66" t="n">
-        <v>1.48</v>
+        <v>1.706</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Al Horford</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.176</v>
+        <v>2.798</v>
       </c>
       <c r="E67" t="n">
-        <v>31.7</v>
+        <v>24.8</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G67" t="n">
-        <v>0.71</v>
+        <v>1.652</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.118</v>
+        <v>0.492</v>
       </c>
       <c r="E68" t="n">
-        <v>26.4</v>
+        <v>31.5</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.03</v>
+        <v>-0.387</v>
       </c>
       <c r="E69" t="n">
-        <v>25.6</v>
+        <v>29.6</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G69" t="n">
-        <v>0.463</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Pat Spencer</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.135</v>
+        <v>-0.578</v>
       </c>
       <c r="E70" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G70" t="n">
-        <v>0.378</v>
+        <v>-0.08599999999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Colby Jones</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-0.91</v>
+        <v>-0.588</v>
       </c>
       <c r="E71" t="n">
-        <v>23.4</v>
+        <v>24.5</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.005</v>
+        <v>-0.096</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Stephen Curry</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7.767</v>
+        <v>3.568</v>
       </c>
       <c r="E72" t="n">
-        <v>29.9</v>
+        <v>27.4</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G72" t="n">
-        <v>5.087</v>
+        <v>2.491</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Clint Capela</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.168</v>
+        <v>1.278</v>
       </c>
       <c r="E73" t="n">
-        <v>31.4</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G73" t="n">
-        <v>1.677</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gary Payton II</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2.948</v>
+        <v>-1.873</v>
       </c>
       <c r="E74" t="n">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G74" t="n">
-        <v>1.647</v>
+        <v>-0.556</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Aaron Holiday</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.767</v>
+        <v>-2.596</v>
       </c>
       <c r="E75" t="n">
-        <v>32.8</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G75" t="n">
-        <v>0.798</v>
+        <v>-0.5610000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Josh Okogie</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-0.368</v>
+        <v>-2.952</v>
       </c>
       <c r="E76" t="n">
-        <v>30.3</v>
+        <v>16</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G76" t="n">
-        <v>0.02</v>
+        <v>-0.715</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pat Spencer</t>
+          <t>Dorian Finney-Smith</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-0.528</v>
+        <v>-6.47</v>
       </c>
       <c r="E77" t="n">
-        <v>23</v>
+        <v>17.3</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.061</v>
+        <v>-2.049</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.634</v>
+        <v>2.706</v>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>18.4</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4</v>
+        <v>0.167</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.122</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Will Richard</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-1.356</v>
+        <v>2.111</v>
       </c>
       <c r="E79" t="n">
-        <v>23.8</v>
+        <v>21.6</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4</v>
+        <v>0.167</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.474</v>
+        <v>1.027</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6.809</v>
+        <v>2.22</v>
       </c>
       <c r="E80" t="n">
-        <v>35.4</v>
+        <v>17.6</v>
       </c>
       <c r="F80" t="n">
-        <v>0.833</v>
+        <v>0.167</v>
       </c>
       <c r="G80" t="n">
-        <v>5.642</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6.209</v>
+        <v>-0.516</v>
       </c>
       <c r="E81" t="n">
-        <v>32</v>
+        <v>19.6</v>
       </c>
       <c r="F81" t="n">
-        <v>0.833</v>
+        <v>0.167</v>
       </c>
       <c r="G81" t="n">
-        <v>4.692</v>
+        <v>-0.142</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.02</v>
+        <v>-1.886</v>
       </c>
       <c r="E82" t="n">
-        <v>38</v>
+        <v>24.3</v>
       </c>
       <c r="F82" t="n">
-        <v>0.833</v>
+        <v>0.167</v>
       </c>
       <c r="G82" t="n">
-        <v>3.839</v>
+        <v>-0.871</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3.661</v>
+        <v>-2.849</v>
       </c>
       <c r="E83" t="n">
-        <v>28.9</v>
+        <v>22.6</v>
       </c>
       <c r="F83" t="n">
-        <v>0.833</v>
+        <v>0.167</v>
       </c>
       <c r="G83" t="n">
-        <v>2.703</v>
+        <v>-1.264</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Kam Jones</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-0.381</v>
+        <v>-3.712</v>
       </c>
       <c r="E84" t="n">
-        <v>35.9</v>
+        <v>19.9</v>
       </c>
       <c r="F84" t="n">
-        <v>0.833</v>
+        <v>0.167</v>
       </c>
       <c r="G84" t="n">
-        <v>0.338</v>
+        <v>-1.472</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Ethan Thompson</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-1.869</v>
+        <v>-4.178</v>
       </c>
       <c r="E85" t="n">
-        <v>24.2</v>
+        <v>23</v>
       </c>
       <c r="F85" t="n">
-        <v>0.833</v>
+        <v>0.167</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.522</v>
+        <v>-1.919</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Josh Okogie</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-2.96</v>
+        <v>11.6</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>30.7</v>
       </c>
       <c r="F86" t="n">
-        <v>0.833</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.707</v>
+        <v>7.771</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dorian Finney-Smith</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-6.804</v>
+        <v>3.237</v>
       </c>
       <c r="E87" t="n">
-        <v>18.3</v>
+        <v>30.2</v>
       </c>
       <c r="F87" t="n">
-        <v>0.833</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>-2.273</v>
+        <v>2.393</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1.926</v>
+        <v>0.582</v>
       </c>
       <c r="E88" t="n">
-        <v>21.4</v>
+        <v>24.6</v>
       </c>
       <c r="F88" t="n">
-        <v>0.167</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Obi Toppin</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2.149</v>
+        <v>0.344</v>
       </c>
       <c r="E89" t="n">
-        <v>17.7</v>
+        <v>25.2</v>
       </c>
       <c r="F89" t="n">
-        <v>0.167</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>0.853</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-0.445</v>
+        <v>-0.211</v>
       </c>
       <c r="E90" t="n">
-        <v>18.4</v>
+        <v>27.2</v>
       </c>
       <c r="F90" t="n">
-        <v>0.167</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.107</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-1.645</v>
+        <v>-0.395</v>
       </c>
       <c r="E91" t="n">
-        <v>23.4</v>
+        <v>27.8</v>
       </c>
       <c r="F91" t="n">
-        <v>0.167</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.722</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-1.594</v>
+        <v>-0.397</v>
       </c>
       <c r="E92" t="n">
-        <v>29.3</v>
+        <v>25.9</v>
       </c>
       <c r="F92" t="n">
-        <v>0.167</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.872</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-2.544</v>
+        <v>-1.705</v>
       </c>
       <c r="E93" t="n">
-        <v>20.3</v>
+        <v>27.4</v>
       </c>
       <c r="F93" t="n">
-        <v>0.167</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>-1.004</v>
+        <v>-0.649</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kam Jones</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-3.039</v>
+        <v>6.648</v>
       </c>
       <c r="E94" t="n">
-        <v>21.7</v>
+        <v>34.4</v>
       </c>
       <c r="F94" t="n">
-        <v>0.167</v>
+        <v>0.633</v>
       </c>
       <c r="G94" t="n">
-        <v>-1.298</v>
+        <v>5.219</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ethan Thompson</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-4.803</v>
+        <v>1.058</v>
       </c>
       <c r="E95" t="n">
-        <v>19.6</v>
+        <v>24</v>
       </c>
       <c r="F95" t="n">
-        <v>0.167</v>
+        <v>0.633</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.89</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.777</v>
+        <v>0.183</v>
       </c>
       <c r="E96" t="n">
-        <v>30.5</v>
+        <v>27</v>
       </c>
       <c r="F96" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G96" t="n">
-        <v>7.912</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3.361</v>
+        <v>-1.328</v>
       </c>
       <c r="E97" t="n">
-        <v>28.9</v>
+        <v>23.8</v>
       </c>
       <c r="F97" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G97" t="n">
-        <v>2.428</v>
+        <v>-0.345</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Dalton Knecht</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.487</v>
+        <v>-1.854</v>
       </c>
       <c r="E98" t="n">
-        <v>25.6</v>
+        <v>15.8</v>
       </c>
       <c r="F98" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G98" t="n">
-        <v>0.616</v>
+        <v>-0.401</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.528</v>
+        <v>-2.241</v>
       </c>
       <c r="E99" t="n">
-        <v>23.6</v>
+        <v>25.4</v>
       </c>
       <c r="F99" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G99" t="n">
-        <v>0.587</v>
+        <v>-0.849</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-0.15</v>
+        <v>-2.186</v>
       </c>
       <c r="E100" t="n">
-        <v>27.8</v>
+        <v>29.4</v>
       </c>
       <c r="F100" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G100" t="n">
-        <v>0.299</v>
+        <v>-0.951</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Maxi Kleber</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-0.204</v>
+        <v>-6.504</v>
       </c>
       <c r="E101" t="n">
-        <v>25.9</v>
+        <v>15.5</v>
       </c>
       <c r="F101" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G101" t="n">
-        <v>0.249</v>
+        <v>-1.891</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Javon Small</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>-0.436</v>
+        <v>2.905</v>
       </c>
       <c r="E102" t="n">
-        <v>27</v>
+        <v>24.9</v>
       </c>
       <c r="F102" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="G102" t="n">
-        <v>0.13</v>
+        <v>1.613</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-1.583</v>
+        <v>1.222</v>
       </c>
       <c r="E103" t="n">
-        <v>28.4</v>
+        <v>24.2</v>
       </c>
       <c r="F103" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.542</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Jahmai Mashack</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6.013</v>
+        <v>-5.326</v>
       </c>
       <c r="E104" t="n">
-        <v>34.6</v>
+        <v>27.8</v>
       </c>
       <c r="F104" t="n">
-        <v>0.533</v>
+        <v>0.2</v>
       </c>
       <c r="G104" t="n">
-        <v>4.723</v>
+        <v>-2.969</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Rayan Rupert</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2.268</v>
+        <v>-5.101</v>
       </c>
       <c r="E105" t="n">
-        <v>21.2</v>
+        <v>30.2</v>
       </c>
       <c r="F105" t="n">
-        <v>0.533</v>
+        <v>0.2</v>
       </c>
       <c r="G105" t="n">
-        <v>1.237</v>
+        <v>-3.088</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.696</v>
+        <v>3.301</v>
       </c>
       <c r="E106" t="n">
-        <v>23.1</v>
+        <v>36</v>
       </c>
       <c r="F106" t="n">
         <v>0.533</v>
       </c>
       <c r="G106" t="n">
-        <v>0.592</v>
+        <v>2.877</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.083</v>
+        <v>2.032</v>
       </c>
       <c r="E107" t="n">
-        <v>26.6</v>
+        <v>33.1</v>
       </c>
       <c r="F107" t="n">
         <v>0.533</v>
       </c>
       <c r="G107" t="n">
-        <v>0.341</v>
+        <v>1.769</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dalton Knecht</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>-1.86</v>
+        <v>1.929</v>
       </c>
       <c r="E108" t="n">
-        <v>15.8</v>
+        <v>27</v>
       </c>
       <c r="F108" t="n">
         <v>0.533</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.436</v>
+        <v>1.387</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>-1.535</v>
+        <v>1.796</v>
       </c>
       <c r="E109" t="n">
-        <v>22.8</v>
+        <v>27.8</v>
       </c>
       <c r="F109" t="n">
         <v>0.533</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.475</v>
+        <v>1.349</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>-2.277</v>
+        <v>2.687</v>
       </c>
       <c r="E110" t="n">
-        <v>25.3</v>
+        <v>19.9</v>
       </c>
       <c r="F110" t="n">
         <v>0.533</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.92</v>
+        <v>1.336</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Maxi Kleber</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-6.509</v>
+        <v>1.201</v>
       </c>
       <c r="E111" t="n">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="F111" t="n">
         <v>0.533</v>
       </c>
       <c r="G111" t="n">
-        <v>-1.925</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.214</v>
+        <v>0.451</v>
       </c>
       <c r="E112" t="n">
-        <v>24.2</v>
+        <v>29.5</v>
       </c>
       <c r="F112" t="n">
-        <v>0.233</v>
+        <v>0.533</v>
       </c>
       <c r="G112" t="n">
-        <v>0.729</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Walter Clayton Jr.</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-1.866</v>
+        <v>-0.802</v>
       </c>
       <c r="E113" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F113" t="n">
-        <v>0.233</v>
+        <v>0.533</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.849</v>
+        <v>-0.173</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jahmai Mashack</t>
+          <t>Cole Anthony</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>-5.138</v>
+        <v>-2.02</v>
       </c>
       <c r="E114" t="n">
-        <v>25.4</v>
+        <v>15.7</v>
       </c>
       <c r="F114" t="n">
         <v>0.233</v>
       </c>
       <c r="G114" t="n">
-        <v>-2.593</v>
+        <v>-0.586</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rayan Rupert</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>-5.724</v>
+        <v>-1.431</v>
       </c>
       <c r="E115" t="n">
-        <v>26.7</v>
+        <v>25.2</v>
       </c>
       <c r="F115" t="n">
         <v>0.233</v>
       </c>
       <c r="G115" t="n">
-        <v>-3.053</v>
+        <v>-0.628</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2.948</v>
+        <v>-1.947</v>
       </c>
       <c r="E116" t="n">
-        <v>35.8</v>
+        <v>25.2</v>
       </c>
       <c r="F116" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.233</v>
       </c>
       <c r="G116" t="n">
-        <v>2.62</v>
+        <v>-0.899</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2.077</v>
+        <v>-1.967</v>
       </c>
       <c r="E117" t="n">
-        <v>33.1</v>
+        <v>28.7</v>
       </c>
       <c r="F117" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.233</v>
       </c>
       <c r="G117" t="n">
-        <v>1.821</v>
+        <v>-1.036</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2.122</v>
+        <v>-3.628</v>
       </c>
       <c r="E118" t="n">
-        <v>27.8</v>
+        <v>16.3</v>
       </c>
       <c r="F118" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.233</v>
       </c>
       <c r="G118" t="n">
-        <v>1.558</v>
+        <v>-1.153</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1.893</v>
+        <v>-2.774</v>
       </c>
       <c r="E119" t="n">
-        <v>28.6</v>
+        <v>29.5</v>
       </c>
       <c r="F119" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.233</v>
       </c>
       <c r="G119" t="n">
-        <v>1.464</v>
+        <v>-1.562</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2.573</v>
+        <v>1.299</v>
       </c>
       <c r="E120" t="n">
-        <v>21.5</v>
+        <v>29.5</v>
       </c>
       <c r="F120" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.733</v>
       </c>
       <c r="G120" t="n">
-        <v>1.406</v>
+        <v>1.249</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Johnny Juzang</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1.018</v>
+        <v>-2.466</v>
       </c>
       <c r="E121" t="n">
-        <v>27.2</v>
+        <v>15</v>
       </c>
       <c r="F121" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.733</v>
       </c>
       <c r="G121" t="n">
-        <v>0.9</v>
+        <v>-0.542</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="E122" t="n">
-        <v>28.6</v>
+        <v>22.2</v>
       </c>
       <c r="F122" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.333</v>
       </c>
       <c r="G122" t="n">
-        <v>0.576</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-0.721</v>
+        <v>-0.515</v>
       </c>
       <c r="E123" t="n">
-        <v>31</v>
+        <v>26.2</v>
       </c>
       <c r="F123" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.333</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.1</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3.972</v>
+        <v>-2.319</v>
       </c>
       <c r="E124" t="n">
-        <v>32</v>
+        <v>19.6</v>
       </c>
       <c r="F124" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="G124" t="n">
-        <v>2.784</v>
+        <v>-0.8110000000000001</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Micah Peavy</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.518</v>
+        <v>-5.11</v>
       </c>
       <c r="E125" t="n">
-        <v>22.9</v>
+        <v>15.5</v>
       </c>
       <c r="F125" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="G125" t="n">
-        <v>0.343</v>
+        <v>-1.542</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Jordan Hawkins</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-0.334</v>
+        <v>-6.218</v>
       </c>
       <c r="E126" t="n">
-        <v>25.2</v>
+        <v>15.6</v>
       </c>
       <c r="F126" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.908</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>-0.632</v>
+        <v>2.934</v>
       </c>
       <c r="E127" t="n">
-        <v>24.8</v>
+        <v>31.2</v>
       </c>
       <c r="F127" t="n">
-        <v>0.2</v>
+        <v>0.867</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.223</v>
+        <v>2.472</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-2.337</v>
+        <v>0.287</v>
       </c>
       <c r="E128" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="F128" t="n">
-        <v>0.2</v>
+        <v>0.867</v>
       </c>
       <c r="G128" t="n">
-        <v>-1.039</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Jose Alvarado</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-2.453</v>
+        <v>-0.111</v>
       </c>
       <c r="E129" t="n">
-        <v>23.8</v>
+        <v>15.5</v>
       </c>
       <c r="F129" t="n">
-        <v>0.2</v>
+        <v>0.867</v>
       </c>
       <c r="G129" t="n">
-        <v>-1.117</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Mohamed Diawara</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>-2.485</v>
+        <v>-2.463</v>
       </c>
       <c r="E130" t="n">
-        <v>26.4</v>
+        <v>15.3</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2</v>
+        <v>0.867</v>
       </c>
       <c r="G130" t="n">
-        <v>-1.255</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Jordan Clarkson</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-2.85</v>
+        <v>-3.248</v>
       </c>
       <c r="E131" t="n">
-        <v>29.3</v>
+        <v>18.2</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2</v>
+        <v>0.867</v>
       </c>
       <c r="G131" t="n">
-        <v>-1.619</v>
+        <v>-0.902</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Kenrich Williams</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4.005</v>
+        <v>0.078</v>
       </c>
       <c r="E132" t="n">
-        <v>31.7</v>
+        <v>16.3</v>
       </c>
       <c r="F132" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>3.11</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2.79</v>
+        <v>-1.669</v>
       </c>
       <c r="E133" t="n">
-        <v>29.9</v>
+        <v>15.7</v>
       </c>
       <c r="F133" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>2.175</v>
+        <v>-0.219</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2.196</v>
+        <v>-2.21</v>
       </c>
       <c r="E134" t="n">
-        <v>22.5</v>
+        <v>16.4</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>1.36</v>
+        <v>-0.414</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1.215</v>
+        <v>-4.06</v>
       </c>
       <c r="E135" t="n">
-        <v>29.9</v>
+        <v>23.1</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>1.193</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1.423</v>
+        <v>3.299</v>
       </c>
       <c r="E136" t="n">
-        <v>25.6</v>
+        <v>33.6</v>
       </c>
       <c r="F136" t="n">
-        <v>0.7</v>
+        <v>0.467</v>
       </c>
       <c r="G136" t="n">
-        <v>1.132</v>
+        <v>2.639</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.315</v>
+        <v>3.246</v>
       </c>
       <c r="E137" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F137" t="n">
-        <v>0.7</v>
+        <v>0.467</v>
       </c>
       <c r="G137" t="n">
-        <v>0.648</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-0.08500000000000001</v>
+        <v>3.196</v>
       </c>
       <c r="E138" t="n">
-        <v>18.5</v>
+        <v>30.2</v>
       </c>
       <c r="F138" t="n">
-        <v>0.7</v>
+        <v>0.467</v>
       </c>
       <c r="G138" t="n">
-        <v>0.236</v>
+        <v>2.306</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mike Conley</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>-2.037</v>
+        <v>1.729</v>
       </c>
       <c r="E139" t="n">
-        <v>17</v>
+        <v>24.3</v>
       </c>
       <c r="F139" t="n">
-        <v>0.7</v>
+        <v>0.467</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.474</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.222</v>
+        <v>0.251</v>
       </c>
       <c r="E140" t="n">
-        <v>32</v>
+        <v>26.3</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="G140" t="n">
-        <v>1.68</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.857</v>
+        <v>-0.647</v>
       </c>
       <c r="E141" t="n">
-        <v>19.6</v>
+        <v>28.3</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="G141" t="n">
-        <v>0.473</v>
+        <v>-0.106</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-1.235</v>
       </c>
       <c r="E142" t="n">
-        <v>23.3</v>
+        <v>26.6</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.309</v>
+        <v>-0.426</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Orlando Robinson</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>-2.811</v>
+        <v>-2.265</v>
       </c>
       <c r="E143" t="n">
-        <v>18.8</v>
+        <v>22.2</v>
       </c>
       <c r="F143" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.983</v>
+        <v>-0.831</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Micah Peavy</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>-5.118</v>
+        <v>8.847</v>
       </c>
       <c r="E144" t="n">
-        <v>15.5</v>
+        <v>36.8</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3</v>
+        <v>0.433</v>
       </c>
       <c r="G144" t="n">
-        <v>-1.555</v>
+        <v>7.108</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-3.189</v>
+        <v>2.118</v>
       </c>
       <c r="E145" t="n">
-        <v>28</v>
+        <v>32.5</v>
       </c>
       <c r="F145" t="n">
-        <v>0.3</v>
+        <v>0.433</v>
       </c>
       <c r="G145" t="n">
-        <v>-1.684</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jordan Hawkins</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>-6.226</v>
+        <v>0.827</v>
       </c>
       <c r="E146" t="n">
-        <v>15.6</v>
+        <v>35</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3</v>
+        <v>0.433</v>
       </c>
       <c r="G146" t="n">
-        <v>-1.921</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Andre Drummond</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>6.466</v>
+        <v>-0.344</v>
       </c>
       <c r="E147" t="n">
-        <v>36.6</v>
+        <v>19.3</v>
       </c>
       <c r="F147" t="n">
-        <v>0.867</v>
+        <v>0.433</v>
       </c>
       <c r="G147" t="n">
-        <v>5.584</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4.451</v>
+        <v>-0.644</v>
       </c>
       <c r="E148" t="n">
-        <v>30.1</v>
+        <v>28.1</v>
       </c>
       <c r="F148" t="n">
-        <v>0.867</v>
+        <v>0.433</v>
       </c>
       <c r="G148" t="n">
-        <v>3.339</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Eric Gordon</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2.862</v>
+        <v>-0.759</v>
       </c>
       <c r="E149" t="n">
-        <v>30.5</v>
+        <v>23</v>
       </c>
       <c r="F149" t="n">
-        <v>0.867</v>
+        <v>0.433</v>
       </c>
       <c r="G149" t="n">
-        <v>2.372</v>
+        <v>-0.156</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2.788</v>
+        <v>-1.344</v>
       </c>
       <c r="E150" t="n">
-        <v>29.8</v>
+        <v>22.3</v>
       </c>
       <c r="F150" t="n">
-        <v>0.867</v>
+        <v>0.433</v>
       </c>
       <c r="G150" t="n">
-        <v>2.269</v>
+        <v>-0.423</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2.053</v>
+        <v>-1.444</v>
       </c>
       <c r="E151" t="n">
-        <v>34.7</v>
+        <v>29.4</v>
       </c>
       <c r="F151" t="n">
-        <v>0.867</v>
+        <v>0.433</v>
       </c>
       <c r="G151" t="n">
-        <v>2.109</v>
+        <v>-0.618</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3.496</v>
+        <v>4.96</v>
       </c>
       <c r="E152" t="n">
-        <v>20.2</v>
+        <v>33.9</v>
       </c>
       <c r="F152" t="n">
-        <v>0.867</v>
+        <v>0.5</v>
       </c>
       <c r="G152" t="n">
-        <v>1.839</v>
+        <v>3.858</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.293</v>
+        <v>3.791</v>
       </c>
       <c r="E153" t="n">
-        <v>26.1</v>
+        <v>27.7</v>
       </c>
       <c r="F153" t="n">
-        <v>0.867</v>
+        <v>0.5</v>
       </c>
       <c r="G153" t="n">
-        <v>0.631</v>
+        <v>2.476</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-1.277</v>
+        <v>2.52</v>
       </c>
       <c r="E154" t="n">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="F154" t="n">
-        <v>0.867</v>
+        <v>0.5</v>
       </c>
       <c r="G154" t="n">
-        <v>-0.209</v>
+        <v>1.658</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Kenrich Williams</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.055</v>
       </c>
       <c r="E155" t="n">
-        <v>16.3</v>
+        <v>23.5</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G155" t="n">
-        <v>0.362</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>-1.793</v>
+        <v>0.278</v>
       </c>
       <c r="E156" t="n">
-        <v>17.3</v>
+        <v>25.5</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.285</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>-2.24</v>
+        <v>-0.294</v>
       </c>
       <c r="E157" t="n">
-        <v>16.8</v>
+        <v>27.2</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G157" t="n">
-        <v>-0.433</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>-4.092</v>
+        <v>-1.427</v>
       </c>
       <c r="E158" t="n">
-        <v>24.4</v>
+        <v>30.6</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G158" t="n">
-        <v>-1.571</v>
+        <v>-0.592</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3.335</v>
+        <v>-2.107</v>
       </c>
       <c r="E159" t="n">
-        <v>33.7</v>
+        <v>29.4</v>
       </c>
       <c r="F159" t="n">
-        <v>0.433</v>
+        <v>0.5</v>
       </c>
       <c r="G159" t="n">
-        <v>2.644</v>
+        <v>-0.985</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3.162</v>
+        <v>5.82</v>
       </c>
       <c r="E160" t="n">
-        <v>35.2</v>
+        <v>33.3</v>
       </c>
       <c r="F160" t="n">
-        <v>0.433</v>
+        <v>0.367</v>
       </c>
       <c r="G160" t="n">
-        <v>2.638</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3.193</v>
+        <v>3.032</v>
       </c>
       <c r="E161" t="n">
-        <v>30.9</v>
+        <v>30.5</v>
       </c>
       <c r="F161" t="n">
-        <v>0.433</v>
+        <v>0.367</v>
       </c>
       <c r="G161" t="n">
-        <v>2.334</v>
+        <v>2.161</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1.589</v>
+        <v>3.38</v>
       </c>
       <c r="E162" t="n">
-        <v>25.4</v>
+        <v>27.2</v>
       </c>
       <c r="F162" t="n">
-        <v>0.433</v>
+        <v>0.367</v>
       </c>
       <c r="G162" t="n">
-        <v>1.069</v>
+        <v>2.121</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.33</v>
+        <v>3.5</v>
       </c>
       <c r="E163" t="n">
-        <v>28.7</v>
+        <v>20.5</v>
       </c>
       <c r="F163" t="n">
-        <v>0.433</v>
+        <v>0.367</v>
       </c>
       <c r="G163" t="n">
-        <v>0.456</v>
+        <v>1.649</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-1.057</v>
       </c>
       <c r="E164" t="n">
-        <v>29.9</v>
+        <v>31.9</v>
       </c>
       <c r="F164" t="n">
-        <v>0.433</v>
+        <v>0.367</v>
       </c>
       <c r="G164" t="n">
-        <v>-0.08</v>
+        <v>-0.459</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-1.331</v>
+        <v>-1.297</v>
       </c>
       <c r="E165" t="n">
-        <v>28.7</v>
+        <v>30</v>
       </c>
       <c r="F165" t="n">
-        <v>0.433</v>
+        <v>0.367</v>
       </c>
       <c r="G165" t="n">
-        <v>-0.536</v>
+        <v>-0.581</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Orlando Robinson</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-2.268</v>
+        <v>-1.867</v>
       </c>
       <c r="E166" t="n">
-        <v>22.2</v>
+        <v>26.7</v>
       </c>
       <c r="F166" t="n">
-        <v>0.433</v>
+        <v>0.367</v>
       </c>
       <c r="G166" t="n">
-        <v>-0.847</v>
+        <v>-0.835</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>8.903</v>
+        <v>-3.375</v>
       </c>
       <c r="E167" t="n">
-        <v>37</v>
+        <v>20.2</v>
       </c>
       <c r="F167" t="n">
-        <v>0.467</v>
+        <v>0.367</v>
       </c>
       <c r="G167" t="n">
-        <v>7.218</v>
+        <v>-1.266</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2.643</v>
+        <v>0.675</v>
       </c>
       <c r="E168" t="n">
-        <v>32.8</v>
+        <v>19.8</v>
       </c>
       <c r="F168" t="n">
-        <v>0.467</v>
+        <v>0.1</v>
       </c>
       <c r="G168" t="n">
-        <v>2.125</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.728</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E169" t="n">
-        <v>34</v>
+        <v>29.4</v>
       </c>
       <c r="F169" t="n">
-        <v>0.467</v>
+        <v>0.1</v>
       </c>
       <c r="G169" t="n">
-        <v>0.846</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-0.516</v>
+        <v>-0.895</v>
       </c>
       <c r="E170" t="n">
-        <v>30</v>
+        <v>24.3</v>
       </c>
       <c r="F170" t="n">
-        <v>0.467</v>
+        <v>0.1</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.031</v>
+        <v>-0.402</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Eric Gordon</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>-0.762</v>
+        <v>-1.016</v>
       </c>
       <c r="E171" t="n">
-        <v>23</v>
+        <v>31.9</v>
       </c>
       <c r="F171" t="n">
-        <v>0.467</v>
+        <v>0.1</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.141</v>
+        <v>-0.608</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Doug McDermott</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-1.263</v>
+        <v>-3.019</v>
       </c>
       <c r="E172" t="n">
-        <v>23.4</v>
+        <v>19.5</v>
       </c>
       <c r="F172" t="n">
-        <v>0.467</v>
+        <v>0.1</v>
       </c>
       <c r="G172" t="n">
-        <v>-0.389</v>
+        <v>-1.188</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Adem Bona</t>
+          <t>Daeqwon Plowden</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-1.8</v>
+        <v>-2.735</v>
       </c>
       <c r="E173" t="n">
-        <v>19.3</v>
+        <v>30.6</v>
       </c>
       <c r="F173" t="n">
-        <v>0.467</v>
+        <v>0.1</v>
       </c>
       <c r="G173" t="n">
-        <v>-0.537</v>
+        <v>-1.682</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>DaQuan Jeffries</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-1.696</v>
+        <v>-3.987</v>
       </c>
       <c r="E174" t="n">
-        <v>29.8</v>
+        <v>26.4</v>
       </c>
       <c r="F174" t="n">
-        <v>0.467</v>
+        <v>0.1</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.764</v>
+        <v>-2.135</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>3.893</v>
+        <v>-4.117</v>
       </c>
       <c r="E175" t="n">
-        <v>27.5</v>
+        <v>33.3</v>
       </c>
       <c r="F175" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G175" t="n">
-        <v>2.521</v>
+        <v>-2.784</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>2.683</v>
+        <v>4.091</v>
       </c>
       <c r="E176" t="n">
-        <v>26.8</v>
+        <v>29.1</v>
       </c>
       <c r="F176" t="n">
-        <v>0.5</v>
+        <v>0.967</v>
       </c>
       <c r="G176" t="n">
-        <v>1.778</v>
+        <v>3.063</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Mark Williams</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2.907</v>
+        <v>3.622</v>
       </c>
       <c r="E177" t="n">
-        <v>22.2</v>
+        <v>31.1</v>
       </c>
       <c r="F177" t="n">
-        <v>0.5</v>
+        <v>0.967</v>
       </c>
       <c r="G177" t="n">
-        <v>1.577</v>
+        <v>2.972</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.134</v>
+        <v>1.766</v>
       </c>
       <c r="E178" t="n">
-        <v>25.2</v>
+        <v>24.7</v>
       </c>
       <c r="F178" t="n">
-        <v>0.5</v>
+        <v>0.967</v>
       </c>
       <c r="G178" t="n">
-        <v>0.333</v>
+        <v>1.406</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>-0.263</v>
+        <v>0.895</v>
       </c>
       <c r="E179" t="n">
-        <v>27.7</v>
+        <v>23.4</v>
       </c>
       <c r="F179" t="n">
-        <v>0.5</v>
+        <v>0.967</v>
       </c>
       <c r="G179" t="n">
-        <v>0.137</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>-1.435</v>
+        <v>0.412</v>
       </c>
       <c r="E180" t="n">
-        <v>30.6</v>
+        <v>27.4</v>
       </c>
       <c r="F180" t="n">
-        <v>0.5</v>
+        <v>0.967</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.597</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Rasheer Fleming</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-2.783</v>
+        <v>-0.021</v>
       </c>
       <c r="E181" t="n">
-        <v>18.2</v>
+        <v>30.1</v>
       </c>
       <c r="F181" t="n">
-        <v>0.5</v>
+        <v>0.967</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.866</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-2.341</v>
+        <v>-1.015</v>
       </c>
       <c r="E182" t="n">
-        <v>29.6</v>
+        <v>21.5</v>
       </c>
       <c r="F182" t="n">
-        <v>0.5</v>
+        <v>0.967</v>
       </c>
       <c r="G182" t="n">
-        <v>-1.137</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Carter Bryant</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>5.725</v>
+        <v>-3.736</v>
       </c>
       <c r="E183" t="n">
-        <v>32.4</v>
+        <v>15.6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.367</v>
+        <v>0.967</v>
       </c>
       <c r="G183" t="n">
-        <v>4.109</v>
+        <v>-0.901</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>5.735</v>
+        <v>6.142</v>
       </c>
       <c r="E184" t="n">
-        <v>19</v>
+        <v>30.4</v>
       </c>
       <c r="F184" t="n">
-        <v>0.367</v>
+        <v>0.6</v>
       </c>
       <c r="G184" t="n">
-        <v>2.419</v>
+        <v>4.277</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>3.37</v>
+        <v>4.276</v>
       </c>
       <c r="E185" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F185" t="n">
-        <v>0.367</v>
+        <v>0.6</v>
       </c>
       <c r="G185" t="n">
-        <v>2.345</v>
+        <v>3.154</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3.093</v>
+        <v>2.283</v>
       </c>
       <c r="E186" t="n">
-        <v>26.8</v>
+        <v>33.4</v>
       </c>
       <c r="F186" t="n">
-        <v>0.367</v>
+        <v>0.6</v>
       </c>
       <c r="G186" t="n">
-        <v>1.928</v>
+        <v>2.006</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>-1.103</v>
+        <v>1.462</v>
       </c>
       <c r="E187" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="F187" t="n">
-        <v>0.367</v>
+        <v>0.6</v>
       </c>
       <c r="G187" t="n">
-        <v>-0.481</v>
+        <v>1.347</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>-1.909</v>
+        <v>1.744</v>
       </c>
       <c r="E188" t="n">
-        <v>25.1</v>
+        <v>24.2</v>
       </c>
       <c r="F188" t="n">
-        <v>0.367</v>
+        <v>0.6</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.8080000000000001</v>
+        <v>1.183</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Caleb Love</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>-2.934</v>
+        <v>1.516</v>
       </c>
       <c r="E189" t="n">
-        <v>22.2</v>
+        <v>21.7</v>
       </c>
       <c r="F189" t="n">
-        <v>0.367</v>
+        <v>0.6</v>
       </c>
       <c r="G189" t="n">
-        <v>-1.19</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>-3.442</v>
+        <v>-0.588</v>
       </c>
       <c r="E190" t="n">
-        <v>19.4</v>
+        <v>25.4</v>
       </c>
       <c r="F190" t="n">
-        <v>0.367</v>
+        <v>0.6</v>
       </c>
       <c r="G190" t="n">
-        <v>-1.244</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.396</v>
+        <v>-0.679</v>
       </c>
       <c r="E191" t="n">
-        <v>22.8</v>
+        <v>25.8</v>
       </c>
       <c r="F191" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G191" t="n">
-        <v>0.236</v>
+        <v>-0.043</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.416</v>
+        <v>1.885</v>
       </c>
       <c r="E192" t="n">
-        <v>20.3</v>
+        <v>29</v>
       </c>
       <c r="F192" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G192" t="n">
-        <v>0.218</v>
+        <v>1.221</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Oscar Tshiebwe</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.061</v>
+        <v>1.451</v>
       </c>
       <c r="E193" t="n">
-        <v>30.8</v>
+        <v>18.9</v>
       </c>
       <c r="F193" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G193" t="n">
-        <v>0.103</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Kevin Love</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>-1.14</v>
+        <v>1.123</v>
       </c>
       <c r="E194" t="n">
-        <v>32.3</v>
+        <v>15.5</v>
       </c>
       <c r="F194" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G194" t="n">
-        <v>-0.7</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>-1.678</v>
+        <v>-0.053</v>
       </c>
       <c r="E195" t="n">
-        <v>22.8</v>
+        <v>29.5</v>
       </c>
       <c r="F195" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G195" t="n">
-        <v>-0.751</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Daeqwon Plowden</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>-3.182</v>
+        <v>-1.105</v>
       </c>
       <c r="E196" t="n">
-        <v>29.9</v>
+        <v>19</v>
       </c>
       <c r="F196" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G196" t="n">
-        <v>-1.92</v>
+        <v>-0.386</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DaQuan Jeffries</t>
+          <t>Svi Mykhailiuk</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>-3.99</v>
+        <v>-1.122</v>
       </c>
       <c r="E197" t="n">
-        <v>26.4</v>
+        <v>19.4</v>
       </c>
       <c r="F197" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G197" t="n">
-        <v>-2.137</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-4.07</v>
+        <v>-1.933</v>
       </c>
       <c r="E198" t="n">
-        <v>33.8</v>
+        <v>30.3</v>
       </c>
       <c r="F198" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G198" t="n">
-        <v>-2.793</v>
+        <v>-1.134</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Cody Williams</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>11.787</v>
+        <v>-3.937</v>
       </c>
       <c r="E199" t="n">
-        <v>30.6</v>
+        <v>34.1</v>
       </c>
       <c r="F199" t="n">
-        <v>0.967</v>
+        <v>0.133</v>
       </c>
       <c r="G199" t="n">
-        <v>8.119999999999999</v>
+        <v>-2.706</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>3.962</v>
+        <v>1.677</v>
       </c>
       <c r="E200" t="n">
-        <v>29.4</v>
+        <v>22.3</v>
       </c>
       <c r="F200" t="n">
-        <v>0.967</v>
+        <v>0.033</v>
       </c>
       <c r="G200" t="n">
-        <v>3.02</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Anthony Gill</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>3.498</v>
+        <v>-0.796</v>
       </c>
       <c r="E201" t="n">
-        <v>31.4</v>
+        <v>28.4</v>
       </c>
       <c r="F201" t="n">
-        <v>0.967</v>
+        <v>0.033</v>
       </c>
       <c r="G201" t="n">
-        <v>2.917</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Sharife Cooper</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1.804</v>
+        <v>-1.278</v>
       </c>
       <c r="E202" t="n">
-        <v>23.9</v>
+        <v>20.2</v>
       </c>
       <c r="F202" t="n">
-        <v>0.967</v>
+        <v>0.033</v>
       </c>
       <c r="G202" t="n">
-        <v>1.379</v>
+        <v>-0.524</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.794</v>
+        <v>-1.65</v>
       </c>
       <c r="E203" t="n">
-        <v>23</v>
+        <v>27.8</v>
       </c>
       <c r="F203" t="n">
-        <v>0.967</v>
+        <v>0.033</v>
       </c>
       <c r="G203" t="n">
-        <v>0.842</v>
+        <v>-0.9360000000000001</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Jamir Watkins</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.385</v>
+        <v>-2.052</v>
       </c>
       <c r="E204" t="n">
-        <v>27.1</v>
+        <v>24</v>
       </c>
       <c r="F204" t="n">
-        <v>0.967</v>
+        <v>0.033</v>
       </c>
       <c r="G204" t="n">
-        <v>0.764</v>
+        <v>-1.009</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.15</v>
+        <v>-2.134</v>
       </c>
       <c r="E205" t="n">
-        <v>30.6</v>
+        <v>32.5</v>
       </c>
       <c r="F205" t="n">
-        <v>0.967</v>
+        <v>0.033</v>
       </c>
       <c r="G205" t="n">
-        <v>0.711</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>Jaden Hardy</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-0.989</v>
+        <v>-3.329</v>
       </c>
       <c r="E206" t="n">
         <v>20.8</v>
       </c>
       <c r="F206" t="n">
-        <v>0.967</v>
+        <v>0.033</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Scottie Barnes</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="E207" t="n">
-        <v>31</v>
-      </c>
-      <c r="F207" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G207" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Immanuel Quickley</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>4.274</v>
-      </c>
-      <c r="E208" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="F208" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G208" t="n">
-        <v>3.205</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Brandon Ingram</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>2.013</v>
-      </c>
-      <c r="E209" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="F209" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G209" t="n">
-        <v>1.779</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Jakob Poeltl</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E210" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="F210" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G210" t="n">
-        <v>1.369</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>RJ Barrett</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E211" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="F211" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G211" t="n">
-        <v>1.287</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Collin Murray-Boyles</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>1.216</v>
-      </c>
-      <c r="E212" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="F212" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0.828</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Jamal Shead</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>-0.442</v>
-      </c>
-      <c r="E213" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="F213" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0.083</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Ja'Kobe Walter</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="E214" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G214" t="n">
-        <v>-0.08699999999999999</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>John Konchar</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>1.266</v>
-      </c>
-      <c r="E215" t="n">
-        <v>27</v>
-      </c>
-      <c r="F215" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G215" t="n">
-        <v>0.787</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Oscar Tshiebwe</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>1.211</v>
-      </c>
-      <c r="E216" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F216" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0.482</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Kevin Love</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="E217" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F217" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G217" t="n">
-        <v>0.403</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Vince Williams Jr.</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>-1.114</v>
-      </c>
-      <c r="E218" t="n">
-        <v>19</v>
-      </c>
-      <c r="F218" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G218" t="n">
-        <v>-0.389</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Svi Mykhailiuk</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="E219" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F219" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G219" t="n">
-        <v>-0.403</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Ace Bailey</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>-2.059</v>
-      </c>
-      <c r="E220" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="F220" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G220" t="n">
-        <v>-1.216</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Cody Williams</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>-3.777</v>
-      </c>
-      <c r="E221" t="n">
-        <v>35</v>
-      </c>
-      <c r="F221" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G221" t="n">
-        <v>-2.657</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Justin Champagnie</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>1.698</v>
-      </c>
-      <c r="E222" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F222" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G222" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Anthony Gill</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>-0.655</v>
-      </c>
-      <c r="E223" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="F223" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G223" t="n">
-        <v>-0.322</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Bilal Coulibaly</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>-0.923</v>
-      </c>
-      <c r="E224" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F224" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G224" t="n">
-        <v>-0.502</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Jamir Watkins</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>-1.724</v>
-      </c>
-      <c r="E225" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F225" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G225" t="n">
-        <v>-0.799</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Sharife Cooper</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>-2.258</v>
-      </c>
-      <c r="E226" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F226" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G226" t="n">
-        <v>-0.861</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Bub Carrington</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>-1.899</v>
-      </c>
-      <c r="E227" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="F227" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G227" t="n">
-        <v>-1.058</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Jaden Hardy</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>-3.191</v>
-      </c>
-      <c r="E228" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F228" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G228" t="n">
-        <v>-1.403</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Will Riley</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>-2.215</v>
-      </c>
-      <c r="E229" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F229" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="G229" t="n">
-        <v>-1.464</v>
+        <v>-1.428</v>
       </c>
     </row>
   </sheetData>
@@ -7135,26 +6468,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>22.652</v>
+        <v>12.885</v>
       </c>
       <c r="F2" t="n">
-        <v>2.764</v>
+        <v>2.019</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7164,26 +6497,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>21.183</v>
+        <v>12.413</v>
       </c>
       <c r="F3" t="n">
-        <v>3.054</v>
+        <v>1.783</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7193,26 +6526,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>17.934</v>
+        <v>11.453</v>
       </c>
       <c r="F4" t="n">
-        <v>2.641</v>
+        <v>0.746</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
     </row>
@@ -7222,26 +6555,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>17.744</v>
+        <v>10.974</v>
       </c>
       <c r="F5" t="n">
-        <v>2.674</v>
+        <v>1.632</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -7251,26 +6584,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>14.834</v>
+        <v>10.83</v>
       </c>
       <c r="F6" t="n">
-        <v>1.908</v>
+        <v>1.293</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
     </row>
@@ -7280,26 +6613,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>14.117</v>
+        <v>10.397</v>
       </c>
       <c r="F7" t="n">
-        <v>1.914</v>
+        <v>1.862</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
     </row>
@@ -7309,26 +6642,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>13.712</v>
+        <v>10.124</v>
       </c>
       <c r="F8" t="n">
-        <v>1.086</v>
+        <v>1.574</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
     </row>
@@ -7338,26 +6671,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>12.864</v>
+        <v>10.122</v>
       </c>
       <c r="F9" t="n">
-        <v>1.983</v>
+        <v>0.758</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -7367,26 +6700,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>12.588</v>
+        <v>8.808</v>
       </c>
       <c r="F10" t="n">
-        <v>1.829</v>
+        <v>0.752</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
     </row>
@@ -7396,26 +6729,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>11.741</v>
+        <v>8.472</v>
       </c>
       <c r="F11" t="n">
-        <v>1.522</v>
+        <v>0.907</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7425,26 +6758,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>11.679</v>
+        <v>7.707</v>
       </c>
       <c r="F12" t="n">
-        <v>1.722</v>
+        <v>1.097</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Devin Booker</t>
         </is>
       </c>
     </row>
@@ -7454,26 +6787,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>10.245</v>
+        <v>7.535</v>
       </c>
       <c r="F13" t="n">
-        <v>1.539</v>
+        <v>0.947</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
     </row>
@@ -7483,26 +6816,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>9.380000000000001</v>
+        <v>7.08</v>
       </c>
       <c r="F14" t="n">
-        <v>1.228</v>
+        <v>1.017</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
     </row>
@@ -7512,26 +6845,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>8.571999999999999</v>
+        <v>3.109</v>
       </c>
       <c r="F15" t="n">
-        <v>1.346</v>
+        <v>0.447</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Stephen Curry</t>
+          <t>Nikola Vučević</t>
         </is>
       </c>
     </row>
@@ -7541,26 +6874,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>8.327</v>
+        <v>2.088</v>
       </c>
       <c r="F16" t="n">
-        <v>0.78</v>
+        <v>-0.778</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>LeBron James</t>
         </is>
       </c>
     </row>
@@ -7570,26 +6903,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>7.678</v>
+        <v>1.922</v>
       </c>
       <c r="F17" t="n">
-        <v>0.931</v>
+        <v>-0.52</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
     </row>
@@ -7599,26 +6932,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>7.078</v>
+        <v>1.778</v>
       </c>
       <c r="F18" t="n">
-        <v>1.067</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Craig Porter Jr.</t>
         </is>
       </c>
     </row>
@@ -7628,26 +6961,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>3.746</v>
+        <v>0.707</v>
       </c>
       <c r="F19" t="n">
-        <v>0.349</v>
+        <v>-0.584</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
     </row>
@@ -7657,26 +6990,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>3.137</v>
+        <v>-0.741</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.39</v>
+        <v>-1.508</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
     </row>
@@ -7686,26 +7019,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>1.586</v>
+        <v>-1.173</v>
       </c>
       <c r="F21" t="n">
-        <v>0.012</v>
+        <v>-0.995</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Tre Jones</t>
         </is>
       </c>
     </row>
@@ -7727,10 +7060,10 @@
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.927</v>
+        <v>-1.738</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.014</v>
+        <v>-1.965</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -7744,26 +7077,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.196</v>
+        <v>-2.327</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.825</v>
+        <v>-0.461</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>John Konchar</t>
         </is>
       </c>
     </row>
@@ -7773,26 +7106,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.993</v>
+        <v>-2.668</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.641</v>
+        <v>-0.763</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
     </row>
@@ -7802,26 +7135,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.486</v>
+        <v>-3.697</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.344</v>
+        <v>-2.612</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tre Jones</t>
+          <t>Derik Queen</t>
         </is>
       </c>
     </row>
@@ -7831,26 +7164,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.105</v>
+        <v>-3.727</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.249</v>
+        <v>-1.575</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Javon Small</t>
         </is>
       </c>
     </row>
@@ -7860,26 +7193,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.299</v>
+        <v>-4.972</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.171</v>
+        <v>-1.366</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
     </row>
@@ -7889,26 +7222,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.598</v>
+        <v>-5.629</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.396</v>
+        <v>-2.208</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Moussa Cisse</t>
         </is>
       </c>
     </row>
@@ -7918,26 +7251,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.766</v>
+        <v>-5.864</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.878</v>
+        <v>-2.294</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Cole Anthony</t>
         </is>
       </c>
     </row>
@@ -7959,14 +7292,14 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.744</v>
+        <v>-8.462</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.648</v>
+        <v>-1.896</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
     </row>
@@ -7988,14 +7321,14 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>-10.362</v>
+        <v>-10.473</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.918</v>
+        <v>-3.866</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Josh Minott</t>
+          <t>Tyson Etienne</t>
         </is>
       </c>
     </row>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G206"/>
+  <dimension ref="A1:G226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,20 +566,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Keaton Wallace</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.595</v>
+        <v>2.414</v>
       </c>
       <c r="E5" t="n">
-        <v>15.8</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
         <v>0.667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.024</v>
+        <v>1.929</v>
       </c>
     </row>
     <row r="6">
@@ -595,20 +595,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Corey Kispert</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.271</v>
+        <v>2.26</v>
       </c>
       <c r="E6" t="n">
-        <v>15.4</v>
+        <v>29.9</v>
       </c>
       <c r="F6" t="n">
         <v>0.667</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.194</v>
+        <v>1.821</v>
       </c>
     </row>
     <row r="7">
@@ -624,20 +624,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Keaton Wallace</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.824</v>
+        <v>-0.595</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>15.8</v>
       </c>
       <c r="F7" t="n">
         <v>0.667</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.41</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="8">
@@ -653,20 +653,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.643</v>
+        <v>-1.824</v>
       </c>
       <c r="E8" t="n">
-        <v>22.1</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>0.667</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.449</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="9">
@@ -682,20 +682,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Caleb Houstan</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.95</v>
+        <v>-1.643</v>
       </c>
       <c r="E9" t="n">
-        <v>15.6</v>
+        <v>22.1</v>
       </c>
       <c r="F9" t="n">
         <v>0.667</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.742</v>
+        <v>-0.449</v>
       </c>
     </row>
     <row r="10">
@@ -711,20 +711,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nikola Vučević</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.925</v>
+        <v>6.407</v>
       </c>
       <c r="E10" t="n">
-        <v>21.3</v>
+        <v>35.3</v>
       </c>
       <c r="F10" t="n">
         <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>1.695</v>
+        <v>5.381</v>
       </c>
     </row>
     <row r="11">
@@ -740,20 +740,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luka Garza</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.552</v>
+        <v>4.606</v>
       </c>
       <c r="E11" t="n">
-        <v>17.1</v>
+        <v>34.8</v>
       </c>
       <c r="F11" t="n">
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>1.231</v>
+        <v>3.987</v>
       </c>
     </row>
     <row r="12">
@@ -769,20 +769,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chris Boucher</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.261</v>
+        <v>4.107</v>
       </c>
       <c r="E12" t="n">
-        <v>15.1</v>
+        <v>31.9</v>
       </c>
       <c r="F12" t="n">
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.364</v>
+        <v>3.331</v>
       </c>
     </row>
     <row r="13">
@@ -798,20 +798,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Walsh</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.5679999999999999</v>
+        <v>2.753</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>27.7</v>
       </c>
       <c r="F13" t="n">
         <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.118</v>
+        <v>2.104</v>
       </c>
     </row>
     <row r="14">
@@ -827,20 +827,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dalano Banton</t>
+          <t>Nikola Vučević</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.193</v>
+        <v>2.925</v>
       </c>
       <c r="E14" t="n">
-        <v>17.4</v>
+        <v>21.3</v>
       </c>
       <c r="F14" t="n">
         <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.106</v>
+        <v>1.695</v>
       </c>
     </row>
     <row r="15">
@@ -856,78 +856,78 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Baylor Scheierman</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.296</v>
+        <v>-0.625</v>
       </c>
       <c r="E15" t="n">
-        <v>23.4</v>
+        <v>25.2</v>
       </c>
       <c r="F15" t="n">
         <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.193</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tyson Etienne</t>
+          <t>Dalano Banton</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.929</v>
+        <v>-1.193</v>
       </c>
       <c r="E16" t="n">
-        <v>18.9</v>
+        <v>17.4</v>
       </c>
       <c r="F16" t="n">
-        <v>0.067</v>
+        <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.341</v>
+        <v>-0.106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>E.J. Liddell</t>
+          <t>Baylor Scheierman</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.996</v>
+        <v>-1.296</v>
       </c>
       <c r="E17" t="n">
-        <v>18.2</v>
+        <v>23.4</v>
       </c>
       <c r="F17" t="n">
-        <v>0.067</v>
+        <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.732</v>
+        <v>-0.193</v>
       </c>
     </row>
     <row r="18">
@@ -943,20 +943,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Tyson Etienne</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-4.779</v>
+        <v>-0.929</v>
       </c>
       <c r="E18" t="n">
-        <v>15.7</v>
+        <v>18.9</v>
       </c>
       <c r="F18" t="n">
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.54</v>
+        <v>-0.341</v>
       </c>
     </row>
     <row r="19">
@@ -972,20 +972,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jalen Wilson</t>
+          <t>E.J. Liddell</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-4.754</v>
+        <v>-1.996</v>
       </c>
       <c r="E19" t="n">
-        <v>19.5</v>
+        <v>18.2</v>
       </c>
       <c r="F19" t="n">
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9</v>
+        <v>-0.732</v>
       </c>
     </row>
     <row r="20">
@@ -1001,20 +1001,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Drake Powell</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-5.032</v>
+        <v>-4.779</v>
       </c>
       <c r="E20" t="n">
-        <v>26.7</v>
+        <v>15.7</v>
       </c>
       <c r="F20" t="n">
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.76</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="21">
@@ -1030,78 +1030,78 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ben Saraf</t>
+          <t>Jalen Wilson</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-5.707</v>
+        <v>-4.754</v>
       </c>
       <c r="E21" t="n">
-        <v>27.2</v>
+        <v>19.5</v>
       </c>
       <c r="F21" t="n">
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Drake Powell</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7.794</v>
+        <v>-5.032</v>
       </c>
       <c r="E22" t="n">
-        <v>29.4</v>
+        <v>26.7</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7</v>
+        <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>5.196</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Ben Saraf</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3.928</v>
+        <v>-5.707</v>
       </c>
       <c r="E23" t="n">
-        <v>29.7</v>
+        <v>27.2</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7</v>
+        <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>2.859</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="24">
@@ -1117,20 +1117,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.716</v>
+        <v>7.794</v>
       </c>
       <c r="E24" t="n">
-        <v>31</v>
+        <v>29.4</v>
       </c>
       <c r="F24" t="n">
         <v>0.7</v>
       </c>
       <c r="G24" t="n">
-        <v>2.206</v>
+        <v>5.196</v>
       </c>
     </row>
     <row r="25">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.906</v>
+        <v>3.928</v>
       </c>
       <c r="E25" t="n">
-        <v>28.4</v>
+        <v>29.7</v>
       </c>
       <c r="F25" t="n">
         <v>0.7</v>
       </c>
       <c r="G25" t="n">
-        <v>1.541</v>
+        <v>2.859</v>
       </c>
     </row>
     <row r="26">
@@ -1175,20 +1175,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.085</v>
+        <v>2.716</v>
       </c>
       <c r="E26" t="n">
-        <v>27.5</v>
+        <v>31</v>
       </c>
       <c r="F26" t="n">
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.022</v>
+        <v>2.206</v>
       </c>
     </row>
     <row r="27">
@@ -1204,20 +1204,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.76</v>
+        <v>1.906</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>28.4</v>
       </c>
       <c r="F27" t="n">
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>0.608</v>
+        <v>1.541</v>
       </c>
     </row>
     <row r="28">
@@ -1233,20 +1233,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.301</v>
+        <v>1.085</v>
       </c>
       <c r="E28" t="n">
-        <v>19.5</v>
+        <v>27.5</v>
       </c>
       <c r="F28" t="n">
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.162</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="29">
@@ -1262,78 +1262,78 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sion James</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-3.623</v>
+        <v>0.76</v>
       </c>
       <c r="E29" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.181</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tre Jones</t>
+          <t>Grant Williams</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4.493</v>
+        <v>-0.301</v>
       </c>
       <c r="E30" t="n">
-        <v>27.7</v>
+        <v>19.5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>2.765</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Sion James</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.243</v>
+        <v>-3.623</v>
       </c>
       <c r="E31" t="n">
-        <v>27.1</v>
+        <v>19.4</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>1.434</v>
+        <v>-1.181</v>
       </c>
     </row>
     <row r="32">
@@ -1349,20 +1349,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Leonard Miller</t>
+          <t>Tre Jones</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.029</v>
+        <v>4.493</v>
       </c>
       <c r="E32" t="n">
-        <v>27.1</v>
+        <v>27.7</v>
       </c>
       <c r="F32" t="n">
         <v>0.3</v>
       </c>
       <c r="G32" t="n">
-        <v>0.153</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="33">
@@ -1378,20 +1378,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jaden Ivey</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.612</v>
+        <v>2.243</v>
       </c>
       <c r="E33" t="n">
-        <v>19.6</v>
+        <v>27.1</v>
       </c>
       <c r="F33" t="n">
         <v>0.3</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.127</v>
+        <v>1.434</v>
       </c>
     </row>
     <row r="34">
@@ -1407,20 +1407,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Julian Phillips</t>
+          <t>Leonard Miller</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-2.704</v>
+        <v>-0.029</v>
       </c>
       <c r="E34" t="n">
-        <v>15.4</v>
+        <v>27.1</v>
       </c>
       <c r="F34" t="n">
         <v>0.3</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.773</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="35">
@@ -1436,20 +1436,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Patrick Williams</t>
+          <t>Jaden Ivey</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-4.152</v>
+        <v>-0.612</v>
       </c>
       <c r="E35" t="n">
-        <v>23.1</v>
+        <v>19.6</v>
       </c>
       <c r="F35" t="n">
         <v>0.3</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.854</v>
+        <v>-0.127</v>
       </c>
     </row>
     <row r="36">
@@ -1465,78 +1465,78 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rob Dillingham</t>
+          <t>Julian Phillips</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-6.206</v>
+        <v>-2.704</v>
       </c>
       <c r="E36" t="n">
-        <v>22.5</v>
+        <v>15.4</v>
       </c>
       <c r="F36" t="n">
         <v>0.3</v>
       </c>
       <c r="G36" t="n">
-        <v>-2.771</v>
+        <v>-0.773</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Craig Porter Jr.</t>
+          <t>Patrick Williams</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.962</v>
+        <v>-4.152</v>
       </c>
       <c r="E37" t="n">
-        <v>17.4</v>
+        <v>23.1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.767</v>
+        <v>0.3</v>
       </c>
       <c r="G37" t="n">
-        <v>0.991</v>
+        <v>-1.854</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.681</v>
+        <v>-6.206</v>
       </c>
       <c r="E38" t="n">
-        <v>24.1</v>
+        <v>22.5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.767</v>
+        <v>0.3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.727</v>
+        <v>-2.771</v>
       </c>
     </row>
     <row r="39">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.184</v>
+        <v>8.986000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>26.6</v>
+        <v>33.2</v>
       </c>
       <c r="F39" t="n">
         <v>0.767</v>
       </c>
       <c r="G39" t="n">
-        <v>0.527</v>
+        <v>6.754</v>
       </c>
     </row>
     <row r="40">
@@ -1581,20 +1581,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lonzo Ball</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1.349</v>
+        <v>8.132</v>
       </c>
       <c r="E40" t="n">
-        <v>17.6</v>
+        <v>34.6</v>
       </c>
       <c r="F40" t="n">
         <v>0.767</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.213</v>
+        <v>6.415</v>
       </c>
     </row>
     <row r="41">
@@ -1610,165 +1610,165 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nae'Qwan Tomlin</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-1.522</v>
+        <v>4.68</v>
       </c>
       <c r="E41" t="n">
-        <v>16.2</v>
+        <v>30.4</v>
       </c>
       <c r="F41" t="n">
         <v>0.767</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.254</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Moussa Cisse</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-0.245</v>
+        <v>3.927</v>
       </c>
       <c r="E42" t="n">
-        <v>17.2</v>
+        <v>27.3</v>
       </c>
       <c r="F42" t="n">
-        <v>0.267</v>
+        <v>0.767</v>
       </c>
       <c r="G42" t="n">
-        <v>0.008</v>
+        <v>2.666</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dwight Powell</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-1.814</v>
+        <v>0.879</v>
       </c>
       <c r="E43" t="n">
-        <v>15.2</v>
+        <v>29</v>
       </c>
       <c r="F43" t="n">
-        <v>0.267</v>
+        <v>0.767</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.489</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-1.638</v>
+        <v>0.681</v>
       </c>
       <c r="E44" t="n">
-        <v>21.2</v>
+        <v>24.1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.267</v>
+        <v>0.767</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.606</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Max Strus</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-1.664</v>
+        <v>0.184</v>
       </c>
       <c r="E45" t="n">
-        <v>28.8</v>
+        <v>26.6</v>
       </c>
       <c r="F45" t="n">
-        <v>0.267</v>
+        <v>0.767</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.839</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ryan Nembhard</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-2.114</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>22.8</v>
+        <v>26.7</v>
       </c>
       <c r="F46" t="n">
-        <v>0.267</v>
+        <v>0.767</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.876</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="47">
@@ -1784,20 +1784,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-3.54</v>
+        <v>1.566</v>
       </c>
       <c r="E47" t="n">
-        <v>19</v>
+        <v>22.5</v>
       </c>
       <c r="F47" t="n">
         <v>0.267</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.296</v>
+        <v>0.859</v>
       </c>
     </row>
     <row r="48">
@@ -1813,194 +1813,194 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Moussa Cisse</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-4.441</v>
+        <v>-0.245</v>
       </c>
       <c r="E48" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="F48" t="n">
         <v>0.267</v>
       </c>
       <c r="G48" t="n">
-        <v>-1.531</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Dwight Powell</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17.887</v>
+        <v>-1.814</v>
       </c>
       <c r="E49" t="n">
-        <v>36.5</v>
+        <v>15.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.833</v>
+        <v>0.267</v>
       </c>
       <c r="G49" t="n">
-        <v>14.24</v>
+        <v>-0.489</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jonas Valančiūnas</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.302</v>
+        <v>-1.638</v>
       </c>
       <c r="E50" t="n">
-        <v>15.5</v>
+        <v>21.2</v>
       </c>
       <c r="F50" t="n">
-        <v>0.833</v>
+        <v>0.267</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.606</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jalen Pickett</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-1.597</v>
+        <v>-1.664</v>
       </c>
       <c r="E51" t="n">
-        <v>15.7</v>
+        <v>28.8</v>
       </c>
       <c r="F51" t="n">
-        <v>0.833</v>
+        <v>0.267</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.249</v>
+        <v>-0.839</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Julian Strawther</t>
+          <t>Ryan Nembhard</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-2.346</v>
+        <v>-2.114</v>
       </c>
       <c r="E52" t="n">
-        <v>15.7</v>
+        <v>22.8</v>
       </c>
       <c r="F52" t="n">
-        <v>0.833</v>
+        <v>0.267</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.494</v>
+        <v>-0.876</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Zeke Nnaji</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-2.441</v>
+        <v>-3.54</v>
       </c>
       <c r="E53" t="n">
-        <v>15.2</v>
+        <v>19</v>
       </c>
       <c r="F53" t="n">
-        <v>0.833</v>
+        <v>0.267</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.509</v>
+        <v>-1.296</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-2.707</v>
+        <v>-4.441</v>
       </c>
       <c r="E54" t="n">
-        <v>21.3</v>
+        <v>17.6</v>
       </c>
       <c r="F54" t="n">
-        <v>0.833</v>
+        <v>0.267</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.833</v>
+        <v>-1.531</v>
       </c>
     </row>
     <row r="55">
@@ -2016,223 +2016,223 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KJ Simpson</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-4.877</v>
+        <v>17.887</v>
       </c>
       <c r="E55" t="n">
-        <v>16.5</v>
+        <v>36.5</v>
       </c>
       <c r="F55" t="n">
         <v>0.833</v>
       </c>
       <c r="G55" t="n">
-        <v>-1.392</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>8.789999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="E56" t="n">
-        <v>31.4</v>
+        <v>37</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="G56" t="n">
-        <v>6.367</v>
+        <v>7.605</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.043</v>
+        <v>2.312</v>
       </c>
       <c r="E57" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="G57" t="n">
-        <v>1.711</v>
+        <v>1.844</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.19</v>
+        <v>0.316</v>
       </c>
       <c r="E58" t="n">
-        <v>31.4</v>
+        <v>23.2</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>0.736</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.199</v>
+        <v>-0.61</v>
       </c>
       <c r="E59" t="n">
-        <v>25.7</v>
+        <v>30.4</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>0.607</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.08599999999999999</v>
+        <v>-1.712</v>
       </c>
       <c r="E60" t="n">
-        <v>25.7</v>
+        <v>32.5</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>0.546</v>
+        <v>-0.594</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.03</v>
+        <v>-2.707</v>
       </c>
       <c r="E61" t="n">
-        <v>24.1</v>
+        <v>21.3</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>0.483</v>
+        <v>-0.833</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Isaiah Stewart</t>
+          <t>KJ Simpson</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-0.089</v>
+        <v>-4.877</v>
       </c>
       <c r="E62" t="n">
-        <v>20.9</v>
+        <v>16.5</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>0.368</v>
+        <v>-1.392</v>
       </c>
     </row>
     <row r="63">
@@ -2248,223 +2248,223 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Colby Jones</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-0.908</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>23.4</v>
+        <v>31.4</v>
       </c>
       <c r="F63" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>0.012</v>
+        <v>6.367</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Stephen Curry</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7.572</v>
+        <v>2.043</v>
       </c>
       <c r="E64" t="n">
-        <v>28.9</v>
+        <v>27.6</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>4.793</v>
+        <v>1.711</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3.338</v>
+        <v>0.19</v>
       </c>
       <c r="E65" t="n">
-        <v>23.6</v>
+        <v>31.4</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>1.835</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2.249</v>
+        <v>0.199</v>
       </c>
       <c r="E66" t="n">
-        <v>30.9</v>
+        <v>25.7</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>1.706</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Al Horford</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2.798</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>24.8</v>
+        <v>25.7</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>1.652</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.492</v>
+        <v>0.03</v>
       </c>
       <c r="E68" t="n">
-        <v>31.5</v>
+        <v>24.1</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.585</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Isaiah Stewart</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.387</v>
+        <v>-0.089</v>
       </c>
       <c r="E69" t="n">
-        <v>29.6</v>
+        <v>20.9</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>0.008</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pat Spencer</t>
+          <t>Colby Jones</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.578</v>
+        <v>-0.908</v>
       </c>
       <c r="E70" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="71">
@@ -2480,3934 +2480,4514 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-0.588</v>
+        <v>7.572</v>
       </c>
       <c r="E71" t="n">
-        <v>24.5</v>
+        <v>28.9</v>
       </c>
       <c r="F71" t="n">
         <v>0.4</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.096</v>
+        <v>4.793</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3.568</v>
+        <v>3.338</v>
       </c>
       <c r="E72" t="n">
-        <v>27.4</v>
+        <v>23.6</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>2.491</v>
+        <v>1.835</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Clint Capela</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.278</v>
+        <v>2.249</v>
       </c>
       <c r="E73" t="n">
-        <v>15</v>
+        <v>30.9</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G73" t="n">
-        <v>0.649</v>
+        <v>1.706</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Al Horford</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>-1.873</v>
+        <v>2.798</v>
       </c>
       <c r="E74" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.556</v>
+        <v>1.652</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Aaron Holiday</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>-2.596</v>
+        <v>0.492</v>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>31.5</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Josh Okogie</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-2.952</v>
+        <v>-0.387</v>
       </c>
       <c r="E76" t="n">
-        <v>16</v>
+        <v>29.6</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.715</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dorian Finney-Smith</t>
+          <t>Pat Spencer</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-6.47</v>
+        <v>-0.578</v>
       </c>
       <c r="E77" t="n">
-        <v>17.3</v>
+        <v>23.2</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>-2.049</v>
+        <v>-0.08599999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Obi Toppin</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2.706</v>
+        <v>-0.588</v>
       </c>
       <c r="E78" t="n">
-        <v>18.4</v>
+        <v>24.5</v>
       </c>
       <c r="F78" t="n">
-        <v>0.167</v>
+        <v>0.4</v>
       </c>
       <c r="G78" t="n">
-        <v>1.1</v>
+        <v>-0.096</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2.111</v>
+        <v>5.977</v>
       </c>
       <c r="E79" t="n">
-        <v>21.6</v>
+        <v>32.3</v>
       </c>
       <c r="F79" t="n">
-        <v>0.167</v>
+        <v>0.8</v>
       </c>
       <c r="G79" t="n">
-        <v>1.027</v>
+        <v>4.566</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2.22</v>
+        <v>3.924</v>
       </c>
       <c r="E80" t="n">
-        <v>17.6</v>
+        <v>38.7</v>
       </c>
       <c r="F80" t="n">
-        <v>0.167</v>
+        <v>0.8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.873</v>
+        <v>3.813</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-0.516</v>
+        <v>3.568</v>
       </c>
       <c r="E81" t="n">
-        <v>19.6</v>
+        <v>27.4</v>
       </c>
       <c r="F81" t="n">
-        <v>0.167</v>
+        <v>0.8</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.142</v>
+        <v>2.491</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Clint Capela</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-1.886</v>
+        <v>1.278</v>
       </c>
       <c r="E82" t="n">
-        <v>24.3</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>0.167</v>
+        <v>0.8</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.871</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-2.849</v>
+        <v>-0.479</v>
       </c>
       <c r="E83" t="n">
-        <v>22.6</v>
+        <v>36.3</v>
       </c>
       <c r="F83" t="n">
-        <v>0.167</v>
+        <v>0.8</v>
       </c>
       <c r="G83" t="n">
-        <v>-1.264</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kam Jones</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-3.712</v>
+        <v>-1.873</v>
       </c>
       <c r="E84" t="n">
-        <v>19.9</v>
+        <v>24.9</v>
       </c>
       <c r="F84" t="n">
-        <v>0.167</v>
+        <v>0.8</v>
       </c>
       <c r="G84" t="n">
-        <v>-1.472</v>
+        <v>-0.556</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ethan Thompson</t>
+          <t>Josh Okogie</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-4.178</v>
+        <v>-2.952</v>
       </c>
       <c r="E85" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F85" t="n">
-        <v>0.167</v>
+        <v>0.8</v>
       </c>
       <c r="G85" t="n">
-        <v>-1.919</v>
+        <v>-0.715</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Dorian Finney-Smith</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.6</v>
+        <v>-6.47</v>
       </c>
       <c r="E86" t="n">
-        <v>30.7</v>
+        <v>17.3</v>
       </c>
       <c r="F86" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="G86" t="n">
-        <v>7.771</v>
+        <v>-2.049</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3.237</v>
+        <v>2.706</v>
       </c>
       <c r="E87" t="n">
-        <v>30.2</v>
+        <v>18.4</v>
       </c>
       <c r="F87" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.167</v>
       </c>
       <c r="G87" t="n">
-        <v>2.393</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.582</v>
+        <v>2.111</v>
       </c>
       <c r="E88" t="n">
-        <v>24.6</v>
+        <v>21.6</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.167</v>
       </c>
       <c r="G88" t="n">
-        <v>0.588</v>
+        <v>1.027</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.344</v>
+        <v>2.22</v>
       </c>
       <c r="E89" t="n">
-        <v>25.2</v>
+        <v>17.6</v>
       </c>
       <c r="F89" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.167</v>
       </c>
       <c r="G89" t="n">
-        <v>0.477</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-0.211</v>
+        <v>-0.516</v>
       </c>
       <c r="E90" t="n">
-        <v>27.2</v>
+        <v>19.6</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.167</v>
       </c>
       <c r="G90" t="n">
-        <v>0.202</v>
+        <v>-0.142</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-0.395</v>
+        <v>-1.886</v>
       </c>
       <c r="E91" t="n">
-        <v>27.8</v>
+        <v>24.3</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.167</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1</v>
+        <v>-0.871</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-0.397</v>
+        <v>-2.849</v>
       </c>
       <c r="E92" t="n">
-        <v>25.9</v>
+        <v>22.6</v>
       </c>
       <c r="F92" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>0.092</v>
+        <v>-1.264</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Kam Jones</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-1.705</v>
+        <v>-3.712</v>
       </c>
       <c r="E93" t="n">
-        <v>27.4</v>
+        <v>19.9</v>
       </c>
       <c r="F93" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.649</v>
+        <v>-1.472</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Ethan Thompson</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6.648</v>
+        <v>-4.178</v>
       </c>
       <c r="E94" t="n">
-        <v>34.4</v>
+        <v>23</v>
       </c>
       <c r="F94" t="n">
-        <v>0.633</v>
+        <v>0.167</v>
       </c>
       <c r="G94" t="n">
-        <v>5.219</v>
+        <v>-1.919</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1.058</v>
+        <v>11.6</v>
       </c>
       <c r="E95" t="n">
-        <v>24</v>
+        <v>30.7</v>
       </c>
       <c r="F95" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G95" t="n">
-        <v>0.847</v>
+        <v>7.749</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.183</v>
+        <v>3.237</v>
       </c>
       <c r="E96" t="n">
-        <v>27</v>
+        <v>30.2</v>
       </c>
       <c r="F96" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G96" t="n">
-        <v>0.459</v>
+        <v>2.372</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-1.328</v>
+        <v>0.582</v>
       </c>
       <c r="E97" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="F97" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.345</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dalton Knecht</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>-1.854</v>
+        <v>0.344</v>
       </c>
       <c r="E98" t="n">
-        <v>15.8</v>
+        <v>25.2</v>
       </c>
       <c r="F98" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.401</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-2.241</v>
+        <v>-0.211</v>
       </c>
       <c r="E99" t="n">
-        <v>25.4</v>
+        <v>27.2</v>
       </c>
       <c r="F99" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.849</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-2.186</v>
+        <v>-0.395</v>
       </c>
       <c r="E100" t="n">
-        <v>29.4</v>
+        <v>27.8</v>
       </c>
       <c r="F100" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.951</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Maxi Kleber</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-6.504</v>
+        <v>-0.397</v>
       </c>
       <c r="E101" t="n">
-        <v>15.5</v>
+        <v>25.9</v>
       </c>
       <c r="F101" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="G101" t="n">
-        <v>-1.891</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.905</v>
+        <v>-1.705</v>
       </c>
       <c r="E102" t="n">
-        <v>24.9</v>
+        <v>27.4</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2</v>
+        <v>0.533</v>
       </c>
       <c r="G102" t="n">
-        <v>1.613</v>
+        <v>-0.668</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1.222</v>
+        <v>6.648</v>
       </c>
       <c r="E103" t="n">
-        <v>24.2</v>
+        <v>34.4</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2</v>
+        <v>0.633</v>
       </c>
       <c r="G103" t="n">
-        <v>0.717</v>
+        <v>5.219</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jahmai Mashack</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-5.326</v>
+        <v>2.277</v>
       </c>
       <c r="E104" t="n">
-        <v>27.8</v>
+        <v>21.2</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2</v>
+        <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>-2.969</v>
+        <v>1.285</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rayan Rupert</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-5.101</v>
+        <v>1.058</v>
       </c>
       <c r="E105" t="n">
-        <v>30.2</v>
+        <v>24</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2</v>
+        <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>-3.088</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3.301</v>
+        <v>0.183</v>
       </c>
       <c r="E106" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F106" t="n">
-        <v>0.533</v>
+        <v>0.633</v>
       </c>
       <c r="G106" t="n">
-        <v>2.877</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2.032</v>
+        <v>-1.328</v>
       </c>
       <c r="E107" t="n">
-        <v>33.1</v>
+        <v>23.8</v>
       </c>
       <c r="F107" t="n">
-        <v>0.533</v>
+        <v>0.633</v>
       </c>
       <c r="G107" t="n">
-        <v>1.769</v>
+        <v>-0.345</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Dalton Knecht</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1.929</v>
+        <v>-1.854</v>
       </c>
       <c r="E108" t="n">
-        <v>27</v>
+        <v>15.8</v>
       </c>
       <c r="F108" t="n">
-        <v>0.533</v>
+        <v>0.633</v>
       </c>
       <c r="G108" t="n">
-        <v>1.387</v>
+        <v>-0.401</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.796</v>
+        <v>-2.241</v>
       </c>
       <c r="E109" t="n">
-        <v>27.8</v>
+        <v>25.4</v>
       </c>
       <c r="F109" t="n">
-        <v>0.533</v>
+        <v>0.633</v>
       </c>
       <c r="G109" t="n">
-        <v>1.349</v>
+        <v>-0.849</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2.687</v>
+        <v>-2.186</v>
       </c>
       <c r="E110" t="n">
-        <v>19.9</v>
+        <v>29.4</v>
       </c>
       <c r="F110" t="n">
-        <v>0.533</v>
+        <v>0.633</v>
       </c>
       <c r="G110" t="n">
-        <v>1.336</v>
+        <v>-0.951</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Javon Small</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1.201</v>
+        <v>2.905</v>
       </c>
       <c r="E111" t="n">
-        <v>27</v>
+        <v>24.9</v>
       </c>
       <c r="F111" t="n">
-        <v>0.533</v>
+        <v>0.2</v>
       </c>
       <c r="G111" t="n">
-        <v>0.975</v>
+        <v>1.613</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.451</v>
+        <v>1.222</v>
       </c>
       <c r="E112" t="n">
-        <v>29.5</v>
+        <v>24.2</v>
       </c>
       <c r="F112" t="n">
-        <v>0.533</v>
+        <v>0.2</v>
       </c>
       <c r="G112" t="n">
-        <v>0.604</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Jahmai Mashack</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-0.802</v>
+        <v>-5.326</v>
       </c>
       <c r="E113" t="n">
-        <v>31</v>
+        <v>27.8</v>
       </c>
       <c r="F113" t="n">
-        <v>0.533</v>
+        <v>0.2</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.173</v>
+        <v>-2.969</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cole Anthony</t>
+          <t>Rayan Rupert</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>-2.02</v>
+        <v>-5.101</v>
       </c>
       <c r="E114" t="n">
-        <v>15.7</v>
+        <v>30.2</v>
       </c>
       <c r="F114" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.586</v>
+        <v>-3.088</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>-1.431</v>
+        <v>2.032</v>
       </c>
       <c r="E115" t="n">
-        <v>25.2</v>
+        <v>33.1</v>
       </c>
       <c r="F115" t="n">
-        <v>0.233</v>
+        <v>0.6</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.628</v>
+        <v>1.815</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-1.947</v>
+        <v>1.929</v>
       </c>
       <c r="E116" t="n">
-        <v>25.2</v>
+        <v>27</v>
       </c>
       <c r="F116" t="n">
-        <v>0.233</v>
+        <v>0.6</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.899</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-1.967</v>
+        <v>1.796</v>
       </c>
       <c r="E117" t="n">
-        <v>28.7</v>
+        <v>27.8</v>
       </c>
       <c r="F117" t="n">
-        <v>0.233</v>
+        <v>0.6</v>
       </c>
       <c r="G117" t="n">
-        <v>-1.036</v>
+        <v>1.388</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-3.628</v>
+        <v>2.687</v>
       </c>
       <c r="E118" t="n">
-        <v>16.3</v>
+        <v>19.9</v>
       </c>
       <c r="F118" t="n">
-        <v>0.233</v>
+        <v>0.6</v>
       </c>
       <c r="G118" t="n">
-        <v>-1.153</v>
+        <v>1.363</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-2.774</v>
+        <v>1.201</v>
       </c>
       <c r="E119" t="n">
-        <v>29.5</v>
+        <v>27</v>
       </c>
       <c r="F119" t="n">
-        <v>0.233</v>
+        <v>0.6</v>
       </c>
       <c r="G119" t="n">
-        <v>-1.562</v>
+        <v>1.013</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1.299</v>
+        <v>0.451</v>
       </c>
       <c r="E120" t="n">
         <v>29.5</v>
       </c>
       <c r="F120" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="G120" t="n">
-        <v>1.249</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Johnny Juzang</t>
+          <t>Kasparas Jakučionis</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-2.466</v>
+        <v>-0.507</v>
       </c>
       <c r="E121" t="n">
-        <v>15</v>
+        <v>19.8</v>
       </c>
       <c r="F121" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.542</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1.1</v>
+        <v>-0.802</v>
       </c>
       <c r="E122" t="n">
-        <v>22.2</v>
+        <v>31</v>
       </c>
       <c r="F122" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="G122" t="n">
-        <v>0.663</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Cole Anthony</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-0.515</v>
+        <v>-2.02</v>
       </c>
       <c r="E123" t="n">
-        <v>26.2</v>
+        <v>15.7</v>
       </c>
       <c r="F123" t="n">
-        <v>0.333</v>
+        <v>0.233</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.099</v>
+        <v>-0.586</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-2.319</v>
+        <v>-1.431</v>
       </c>
       <c r="E124" t="n">
-        <v>19.6</v>
+        <v>25.2</v>
       </c>
       <c r="F124" t="n">
-        <v>0.333</v>
+        <v>0.233</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.628</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Micah Peavy</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-5.11</v>
+        <v>-1.947</v>
       </c>
       <c r="E125" t="n">
-        <v>15.5</v>
+        <v>25.2</v>
       </c>
       <c r="F125" t="n">
-        <v>0.333</v>
+        <v>0.233</v>
       </c>
       <c r="G125" t="n">
-        <v>-1.542</v>
+        <v>-0.899</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jordan Hawkins</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-6.218</v>
+        <v>-1.967</v>
       </c>
       <c r="E126" t="n">
-        <v>15.6</v>
+        <v>28.7</v>
       </c>
       <c r="F126" t="n">
-        <v>0.333</v>
+        <v>0.233</v>
       </c>
       <c r="G126" t="n">
-        <v>-1.908</v>
+        <v>-1.036</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2.934</v>
+        <v>-3.628</v>
       </c>
       <c r="E127" t="n">
-        <v>31.2</v>
+        <v>16.3</v>
       </c>
       <c r="F127" t="n">
-        <v>0.867</v>
+        <v>0.233</v>
       </c>
       <c r="G127" t="n">
-        <v>2.472</v>
+        <v>-1.153</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.287</v>
+        <v>-2.774</v>
       </c>
       <c r="E128" t="n">
-        <v>25.7</v>
+        <v>29.5</v>
       </c>
       <c r="F128" t="n">
-        <v>0.867</v>
+        <v>0.233</v>
       </c>
       <c r="G128" t="n">
-        <v>0.618</v>
+        <v>-1.562</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jose Alvarado</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.111</v>
+        <v>4.013</v>
       </c>
       <c r="E129" t="n">
-        <v>15.5</v>
+        <v>31.7</v>
       </c>
       <c r="F129" t="n">
-        <v>0.867</v>
+        <v>0.733</v>
       </c>
       <c r="G129" t="n">
-        <v>0.244</v>
+        <v>3.137</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Mohamed Diawara</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>-2.463</v>
+        <v>2.742</v>
       </c>
       <c r="E130" t="n">
-        <v>15.3</v>
+        <v>30.7</v>
       </c>
       <c r="F130" t="n">
-        <v>0.867</v>
+        <v>0.733</v>
       </c>
       <c r="G130" t="n">
-        <v>-0.51</v>
+        <v>2.223</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jordan Clarkson</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-3.248</v>
+        <v>2.204</v>
       </c>
       <c r="E131" t="n">
-        <v>18.2</v>
+        <v>22.5</v>
       </c>
       <c r="F131" t="n">
-        <v>0.867</v>
+        <v>0.733</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.902</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kenrich Williams</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.078</v>
+        <v>1.299</v>
       </c>
       <c r="E132" t="n">
-        <v>16.3</v>
+        <v>29.5</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>0.733</v>
       </c>
       <c r="G132" t="n">
-        <v>0.365</v>
+        <v>1.249</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-1.669</v>
+        <v>1.432</v>
       </c>
       <c r="E133" t="n">
-        <v>15.7</v>
+        <v>25.6</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>0.733</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.219</v>
+        <v>1.154</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-2.21</v>
+        <v>0.644</v>
       </c>
       <c r="E134" t="n">
-        <v>16.4</v>
+        <v>30.4</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>0.733</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.414</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-4.06</v>
+        <v>0.328</v>
       </c>
       <c r="E135" t="n">
-        <v>23.1</v>
+        <v>29.5</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>0.733</v>
       </c>
       <c r="G135" t="n">
-        <v>-1.47</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3.299</v>
+        <v>0.147</v>
       </c>
       <c r="E136" t="n">
-        <v>33.6</v>
+        <v>19.1</v>
       </c>
       <c r="F136" t="n">
-        <v>0.467</v>
+        <v>0.733</v>
       </c>
       <c r="G136" t="n">
-        <v>2.639</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3.246</v>
+        <v>1.1</v>
       </c>
       <c r="E137" t="n">
-        <v>31.7</v>
+        <v>22.2</v>
       </c>
       <c r="F137" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="G137" t="n">
-        <v>2.45</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3.196</v>
+        <v>-0.515</v>
       </c>
       <c r="E138" t="n">
-        <v>30.2</v>
+        <v>26.2</v>
       </c>
       <c r="F138" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="G138" t="n">
-        <v>2.306</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1.729</v>
+        <v>-2.319</v>
       </c>
       <c r="E139" t="n">
-        <v>24.3</v>
+        <v>19.6</v>
       </c>
       <c r="F139" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="G139" t="n">
-        <v>1.109</v>
+        <v>-0.8110000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Micah Peavy</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.251</v>
+        <v>-5.11</v>
       </c>
       <c r="E140" t="n">
-        <v>26.3</v>
+        <v>15.5</v>
       </c>
       <c r="F140" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="G140" t="n">
-        <v>0.394</v>
+        <v>-1.542</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>-0.647</v>
+        <v>-3.181</v>
       </c>
       <c r="E141" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="F141" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.106</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jordan Hawkins</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-1.235</v>
+        <v>-6.218</v>
       </c>
       <c r="E142" t="n">
-        <v>26.6</v>
+        <v>15.6</v>
       </c>
       <c r="F142" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.426</v>
+        <v>-1.908</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Orlando Robinson</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>-2.265</v>
+        <v>6.504</v>
       </c>
       <c r="E143" t="n">
-        <v>22.2</v>
+        <v>36.4</v>
       </c>
       <c r="F143" t="n">
-        <v>0.467</v>
+        <v>0.867</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.831</v>
+        <v>5.596</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>8.847</v>
+        <v>4.505</v>
       </c>
       <c r="E144" t="n">
-        <v>36.8</v>
+        <v>30</v>
       </c>
       <c r="F144" t="n">
-        <v>0.433</v>
+        <v>0.867</v>
       </c>
       <c r="G144" t="n">
-        <v>7.108</v>
+        <v>3.357</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2.118</v>
+        <v>2.934</v>
       </c>
       <c r="E145" t="n">
-        <v>32.5</v>
+        <v>31.2</v>
       </c>
       <c r="F145" t="n">
-        <v>0.433</v>
+        <v>0.867</v>
       </c>
       <c r="G145" t="n">
-        <v>1.728</v>
+        <v>2.472</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.827</v>
+        <v>2.906</v>
       </c>
       <c r="E146" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F146" t="n">
-        <v>0.433</v>
+        <v>0.867</v>
       </c>
       <c r="G146" t="n">
-        <v>0.92</v>
+        <v>2.361</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Andre Drummond</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>-0.344</v>
+        <v>2.007</v>
       </c>
       <c r="E147" t="n">
-        <v>19.3</v>
+        <v>34.6</v>
       </c>
       <c r="F147" t="n">
-        <v>0.433</v>
+        <v>0.867</v>
       </c>
       <c r="G147" t="n">
-        <v>0.036</v>
+        <v>2.069</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-0.644</v>
+        <v>3.513</v>
       </c>
       <c r="E148" t="n">
-        <v>28.1</v>
+        <v>20.2</v>
       </c>
       <c r="F148" t="n">
-        <v>0.433</v>
+        <v>0.867</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.123</v>
+        <v>1.846</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Eric Gordon</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-0.759</v>
+        <v>0.287</v>
       </c>
       <c r="E149" t="n">
-        <v>23</v>
+        <v>25.7</v>
       </c>
       <c r="F149" t="n">
-        <v>0.433</v>
+        <v>0.867</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.156</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-1.344</v>
+        <v>-1.405</v>
       </c>
       <c r="E150" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
       <c r="F150" t="n">
-        <v>0.433</v>
+        <v>0.867</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.423</v>
+        <v>-0.272</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-1.444</v>
+        <v>0.419</v>
       </c>
       <c r="E151" t="n">
-        <v>29.4</v>
+        <v>17.7</v>
       </c>
       <c r="F151" t="n">
-        <v>0.433</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.618</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Kenrich Williams</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4.96</v>
+        <v>0.078</v>
       </c>
       <c r="E152" t="n">
-        <v>33.9</v>
+        <v>16.3</v>
       </c>
       <c r="F152" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>3.858</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3.791</v>
+        <v>-1.669</v>
       </c>
       <c r="E153" t="n">
-        <v>27.7</v>
+        <v>15.7</v>
       </c>
       <c r="F153" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>2.476</v>
+        <v>-0.219</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2.52</v>
+        <v>-2.21</v>
       </c>
       <c r="E154" t="n">
-        <v>26.4</v>
+        <v>16.4</v>
       </c>
       <c r="F154" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>1.658</v>
+        <v>-0.414</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1.055</v>
+        <v>-4.06</v>
       </c>
       <c r="E155" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="F155" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0.761</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.278</v>
+        <v>3.299</v>
       </c>
       <c r="E156" t="n">
-        <v>25.5</v>
+        <v>33.6</v>
       </c>
       <c r="F156" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="G156" t="n">
-        <v>0.414</v>
+        <v>2.615</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>-0.294</v>
+        <v>3.246</v>
       </c>
       <c r="E157" t="n">
-        <v>27.2</v>
+        <v>31.7</v>
       </c>
       <c r="F157" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="G157" t="n">
-        <v>0.117</v>
+        <v>2.428</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>-1.427</v>
+        <v>3.196</v>
       </c>
       <c r="E158" t="n">
-        <v>30.6</v>
+        <v>30.2</v>
       </c>
       <c r="F158" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.592</v>
+        <v>2.285</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-2.107</v>
+        <v>1.729</v>
       </c>
       <c r="E159" t="n">
-        <v>29.4</v>
+        <v>24.3</v>
       </c>
       <c r="F159" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.985</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5.82</v>
+        <v>0.251</v>
       </c>
       <c r="E160" t="n">
-        <v>33.3</v>
+        <v>26.3</v>
       </c>
       <c r="F160" t="n">
-        <v>0.367</v>
+        <v>0.433</v>
       </c>
       <c r="G160" t="n">
-        <v>4.29</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3.032</v>
+        <v>-0.647</v>
       </c>
       <c r="E161" t="n">
-        <v>30.5</v>
+        <v>28.3</v>
       </c>
       <c r="F161" t="n">
-        <v>0.367</v>
+        <v>0.433</v>
       </c>
       <c r="G161" t="n">
-        <v>2.161</v>
+        <v>-0.126</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>3.38</v>
+        <v>-1.235</v>
       </c>
       <c r="E162" t="n">
-        <v>27.2</v>
+        <v>26.6</v>
       </c>
       <c r="F162" t="n">
-        <v>0.367</v>
+        <v>0.433</v>
       </c>
       <c r="G162" t="n">
-        <v>2.121</v>
+        <v>-0.444</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Orlando Robinson</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>3.5</v>
+        <v>-2.265</v>
       </c>
       <c r="E163" t="n">
-        <v>20.5</v>
+        <v>22.2</v>
       </c>
       <c r="F163" t="n">
-        <v>0.367</v>
+        <v>0.433</v>
       </c>
       <c r="G163" t="n">
-        <v>1.649</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-1.057</v>
+        <v>8.847</v>
       </c>
       <c r="E164" t="n">
-        <v>31.9</v>
+        <v>36.8</v>
       </c>
       <c r="F164" t="n">
-        <v>0.367</v>
+        <v>0.467</v>
       </c>
       <c r="G164" t="n">
-        <v>-0.459</v>
+        <v>7.134</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-1.297</v>
+        <v>2.118</v>
       </c>
       <c r="E165" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="F165" t="n">
-        <v>0.367</v>
+        <v>0.467</v>
       </c>
       <c r="G165" t="n">
-        <v>-0.581</v>
+        <v>1.751</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-1.867</v>
+        <v>0.827</v>
       </c>
       <c r="E166" t="n">
-        <v>26.7</v>
+        <v>35</v>
       </c>
       <c r="F166" t="n">
-        <v>0.367</v>
+        <v>0.467</v>
       </c>
       <c r="G166" t="n">
-        <v>-0.835</v>
+        <v>0.944</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Andre Drummond</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-3.375</v>
+        <v>-0.344</v>
       </c>
       <c r="E167" t="n">
-        <v>20.2</v>
+        <v>19.3</v>
       </c>
       <c r="F167" t="n">
-        <v>0.367</v>
+        <v>0.467</v>
       </c>
       <c r="G167" t="n">
-        <v>-1.266</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.675</v>
+        <v>-0.644</v>
       </c>
       <c r="E168" t="n">
-        <v>19.8</v>
+        <v>28.1</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1</v>
+        <v>0.467</v>
       </c>
       <c r="G168" t="n">
-        <v>0.32</v>
+        <v>-0.104</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Eric Gordon</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.759</v>
       </c>
       <c r="E169" t="n">
-        <v>29.4</v>
+        <v>23</v>
       </c>
       <c r="F169" t="n">
-        <v>0.1</v>
+        <v>0.467</v>
       </c>
       <c r="G169" t="n">
-        <v>0.017</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-0.895</v>
+        <v>-1.344</v>
       </c>
       <c r="E170" t="n">
-        <v>24.3</v>
+        <v>22.3</v>
       </c>
       <c r="F170" t="n">
-        <v>0.1</v>
+        <v>0.467</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.402</v>
+        <v>-0.408</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>-1.016</v>
+        <v>-1.444</v>
       </c>
       <c r="E171" t="n">
-        <v>31.9</v>
+        <v>29.4</v>
       </c>
       <c r="F171" t="n">
-        <v>0.1</v>
+        <v>0.467</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.608</v>
+        <v>-0.598</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Doug McDermott</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-3.019</v>
+        <v>4.96</v>
       </c>
       <c r="E172" t="n">
-        <v>19.5</v>
+        <v>33.9</v>
       </c>
       <c r="F172" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G172" t="n">
-        <v>-1.188</v>
+        <v>3.858</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Daeqwon Plowden</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-2.735</v>
+        <v>3.791</v>
       </c>
       <c r="E173" t="n">
-        <v>30.6</v>
+        <v>27.7</v>
       </c>
       <c r="F173" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G173" t="n">
-        <v>-1.682</v>
+        <v>2.476</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DaQuan Jeffries</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-3.987</v>
+        <v>2.52</v>
       </c>
       <c r="E174" t="n">
         <v>26.4</v>
       </c>
       <c r="F174" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G174" t="n">
-        <v>-2.135</v>
+        <v>1.658</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-4.117</v>
+        <v>1.055</v>
       </c>
       <c r="E175" t="n">
-        <v>33.3</v>
+        <v>23.5</v>
       </c>
       <c r="F175" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G175" t="n">
-        <v>-2.784</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>4.091</v>
+        <v>0.278</v>
       </c>
       <c r="E176" t="n">
-        <v>29.1</v>
+        <v>25.5</v>
       </c>
       <c r="F176" t="n">
-        <v>0.967</v>
+        <v>0.5</v>
       </c>
       <c r="G176" t="n">
-        <v>3.063</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>3.622</v>
+        <v>-0.294</v>
       </c>
       <c r="E177" t="n">
-        <v>31.1</v>
+        <v>27.2</v>
       </c>
       <c r="F177" t="n">
-        <v>0.967</v>
+        <v>0.5</v>
       </c>
       <c r="G177" t="n">
-        <v>2.972</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1.766</v>
+        <v>-1.427</v>
       </c>
       <c r="E178" t="n">
-        <v>24.7</v>
+        <v>30.6</v>
       </c>
       <c r="F178" t="n">
-        <v>0.967</v>
+        <v>0.5</v>
       </c>
       <c r="G178" t="n">
-        <v>1.406</v>
+        <v>-0.592</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.895</v>
+        <v>-2.107</v>
       </c>
       <c r="E179" t="n">
-        <v>23.4</v>
+        <v>29.4</v>
       </c>
       <c r="F179" t="n">
-        <v>0.967</v>
+        <v>0.5</v>
       </c>
       <c r="G179" t="n">
-        <v>0.909</v>
+        <v>-0.985</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.412</v>
+        <v>5.82</v>
       </c>
       <c r="E180" t="n">
-        <v>27.4</v>
+        <v>33.3</v>
       </c>
       <c r="F180" t="n">
-        <v>0.967</v>
+        <v>0.367</v>
       </c>
       <c r="G180" t="n">
-        <v>0.787</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-0.021</v>
+        <v>3.032</v>
       </c>
       <c r="E181" t="n">
-        <v>30.1</v>
+        <v>30.5</v>
       </c>
       <c r="F181" t="n">
-        <v>0.967</v>
+        <v>0.367</v>
       </c>
       <c r="G181" t="n">
-        <v>0.594</v>
+        <v>2.161</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-1.015</v>
+        <v>3.38</v>
       </c>
       <c r="E182" t="n">
-        <v>21.5</v>
+        <v>27.2</v>
       </c>
       <c r="F182" t="n">
-        <v>0.967</v>
+        <v>0.367</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.022</v>
+        <v>2.121</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Carter Bryant</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-3.736</v>
+        <v>3.5</v>
       </c>
       <c r="E183" t="n">
-        <v>15.6</v>
+        <v>20.5</v>
       </c>
       <c r="F183" t="n">
-        <v>0.967</v>
+        <v>0.367</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.901</v>
+        <v>1.649</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jerami Grant</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>6.142</v>
+        <v>0.187</v>
       </c>
       <c r="E184" t="n">
-        <v>30.4</v>
+        <v>31.8</v>
       </c>
       <c r="F184" t="n">
-        <v>0.6</v>
+        <v>0.367</v>
       </c>
       <c r="G184" t="n">
-        <v>4.277</v>
+        <v>0.367</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4.276</v>
+        <v>-1.057</v>
       </c>
       <c r="E185" t="n">
-        <v>31</v>
+        <v>31.9</v>
       </c>
       <c r="F185" t="n">
-        <v>0.6</v>
+        <v>0.367</v>
       </c>
       <c r="G185" t="n">
-        <v>3.154</v>
+        <v>-0.459</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2.283</v>
+        <v>-1.297</v>
       </c>
       <c r="E186" t="n">
-        <v>33.4</v>
+        <v>30</v>
       </c>
       <c r="F186" t="n">
-        <v>0.6</v>
+        <v>0.367</v>
       </c>
       <c r="G186" t="n">
-        <v>2.006</v>
+        <v>-0.581</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1.462</v>
+        <v>-1.867</v>
       </c>
       <c r="E187" t="n">
-        <v>31.4</v>
+        <v>26.7</v>
       </c>
       <c r="F187" t="n">
-        <v>0.6</v>
+        <v>0.367</v>
       </c>
       <c r="G187" t="n">
-        <v>1.347</v>
+        <v>-0.835</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1.744</v>
+        <v>0.675</v>
       </c>
       <c r="E188" t="n">
-        <v>24.2</v>
+        <v>19.8</v>
       </c>
       <c r="F188" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G188" t="n">
-        <v>1.183</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1.516</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E189" t="n">
-        <v>21.7</v>
+        <v>29.4</v>
       </c>
       <c r="F189" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G189" t="n">
-        <v>0.955</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>-0.588</v>
+        <v>-0.895</v>
       </c>
       <c r="E190" t="n">
-        <v>25.4</v>
+        <v>24.3</v>
       </c>
       <c r="F190" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.006</v>
+        <v>-0.402</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>-0.679</v>
+        <v>-1.016</v>
       </c>
       <c r="E191" t="n">
-        <v>25.8</v>
+        <v>31.9</v>
       </c>
       <c r="F191" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.043</v>
+        <v>-0.608</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Doug McDermott</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1.885</v>
+        <v>-3.019</v>
       </c>
       <c r="E192" t="n">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="F192" t="n">
-        <v>0.133</v>
+        <v>0.1</v>
       </c>
       <c r="G192" t="n">
-        <v>1.221</v>
+        <v>-1.188</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Oscar Tshiebwe</t>
+          <t>Daeqwon Plowden</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1.451</v>
+        <v>-2.735</v>
       </c>
       <c r="E193" t="n">
-        <v>18.9</v>
+        <v>30.6</v>
       </c>
       <c r="F193" t="n">
-        <v>0.133</v>
+        <v>0.1</v>
       </c>
       <c r="G193" t="n">
-        <v>0.624</v>
+        <v>-1.682</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Kevin Love</t>
+          <t>DaQuan Jeffries</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1.123</v>
+        <v>-3.987</v>
       </c>
       <c r="E194" t="n">
-        <v>15.5</v>
+        <v>26.4</v>
       </c>
       <c r="F194" t="n">
-        <v>0.133</v>
+        <v>0.1</v>
       </c>
       <c r="G194" t="n">
-        <v>0.405</v>
+        <v>-2.135</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>-0.053</v>
+        <v>-4.117</v>
       </c>
       <c r="E195" t="n">
-        <v>29.5</v>
+        <v>33.3</v>
       </c>
       <c r="F195" t="n">
-        <v>0.133</v>
+        <v>0.1</v>
       </c>
       <c r="G195" t="n">
-        <v>0.049</v>
+        <v>-2.784</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>-1.105</v>
+        <v>4.091</v>
       </c>
       <c r="E196" t="n">
-        <v>19</v>
+        <v>29.1</v>
       </c>
       <c r="F196" t="n">
-        <v>0.133</v>
+        <v>0.967</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.386</v>
+        <v>3.063</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Svi Mykhailiuk</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>-1.122</v>
+        <v>3.622</v>
       </c>
       <c r="E197" t="n">
-        <v>19.4</v>
+        <v>31.1</v>
       </c>
       <c r="F197" t="n">
-        <v>0.133</v>
+        <v>0.967</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.4</v>
+        <v>2.972</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-1.933</v>
+        <v>1.766</v>
       </c>
       <c r="E198" t="n">
-        <v>30.3</v>
+        <v>24.7</v>
       </c>
       <c r="F198" t="n">
-        <v>0.133</v>
+        <v>0.967</v>
       </c>
       <c r="G198" t="n">
-        <v>-1.134</v>
+        <v>1.406</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-3.937</v>
+        <v>0.895</v>
       </c>
       <c r="E199" t="n">
-        <v>34.1</v>
+        <v>23.4</v>
       </c>
       <c r="F199" t="n">
-        <v>0.133</v>
+        <v>0.967</v>
       </c>
       <c r="G199" t="n">
-        <v>-2.706</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1.677</v>
+        <v>0.412</v>
       </c>
       <c r="E200" t="n">
-        <v>22.3</v>
+        <v>27.4</v>
       </c>
       <c r="F200" t="n">
-        <v>0.033</v>
+        <v>0.967</v>
       </c>
       <c r="G200" t="n">
-        <v>0.795</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Anthony Gill</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-0.796</v>
+        <v>-0.021</v>
       </c>
       <c r="E201" t="n">
-        <v>28.4</v>
+        <v>30.1</v>
       </c>
       <c r="F201" t="n">
-        <v>0.033</v>
+        <v>0.967</v>
       </c>
       <c r="G201" t="n">
-        <v>-0.45</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Sharife Cooper</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>-1.278</v>
+        <v>-1.015</v>
       </c>
       <c r="E202" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
       <c r="F202" t="n">
-        <v>0.033</v>
+        <v>0.967</v>
       </c>
       <c r="G202" t="n">
-        <v>-0.524</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bub Carrington</t>
+          <t>Carter Bryant</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>-1.65</v>
+        <v>-3.736</v>
       </c>
       <c r="E203" t="n">
-        <v>27.8</v>
+        <v>15.6</v>
       </c>
       <c r="F203" t="n">
-        <v>0.033</v>
+        <v>0.967</v>
       </c>
       <c r="G203" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.901</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Jamir Watkins</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>-2.052</v>
+        <v>6.142</v>
       </c>
       <c r="E204" t="n">
-        <v>24</v>
+        <v>30.4</v>
       </c>
       <c r="F204" t="n">
-        <v>0.033</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G204" t="n">
-        <v>-1.009</v>
+        <v>4.256</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Will Riley</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-2.134</v>
+        <v>4.276</v>
       </c>
       <c r="E205" t="n">
-        <v>32.5</v>
+        <v>31</v>
       </c>
       <c r="F205" t="n">
-        <v>0.033</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G205" t="n">
-        <v>-1.42</v>
+        <v>3.133</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="E206" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1.982</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>RJ Barrett</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="E207" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1.325</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Jakob Poeltl</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1.744</v>
+      </c>
+      <c r="E208" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1.166</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Collin Murray-Boyles</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="E209" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Jamal Shead</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>-0.588</v>
+      </c>
+      <c r="E210" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G210" t="n">
+        <v>-0.011</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Ja'Kobe Walter</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>-0.679</v>
+      </c>
+      <c r="E211" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G211" t="n">
+        <v>-0.061</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>John Konchar</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="E212" t="n">
+        <v>29</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1.221</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Oscar Tshiebwe</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1.451</v>
+      </c>
+      <c r="E213" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.624</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Kevin Love</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="E214" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.405</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Brice Sensabaugh</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="E215" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Vince Williams Jr.</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>-1.105</v>
+      </c>
+      <c r="E216" t="n">
+        <v>19</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G216" t="n">
+        <v>-0.386</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Svi Mykhailiuk</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>-1.122</v>
+      </c>
+      <c r="E217" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G217" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Ace Bailey</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>-1.933</v>
+      </c>
+      <c r="E218" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G218" t="n">
+        <v>-1.134</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Cody Williams</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>-3.937</v>
+      </c>
+      <c r="E219" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G219" t="n">
+        <v>-2.706</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Justin Champagnie</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="E220" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.795</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Anthony Gill</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>-0.796</v>
+      </c>
+      <c r="E221" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="G221" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Sharife Cooper</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>-1.278</v>
+      </c>
+      <c r="E222" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="G222" t="n">
+        <v>-0.524</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Bub Carrington</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="E223" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="G223" t="n">
+        <v>-0.9360000000000001</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Jamir Watkins</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>-2.052</v>
+      </c>
+      <c r="E224" t="n">
+        <v>24</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="G224" t="n">
+        <v>-1.009</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Will Riley</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>-2.134</v>
+      </c>
+      <c r="E225" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="G225" t="n">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Jaden Hardy</t>
         </is>
       </c>
-      <c r="D206" t="n">
+      <c r="D226" t="n">
         <v>-3.329</v>
       </c>
-      <c r="E206" t="n">
+      <c r="E226" t="n">
         <v>20.8</v>
       </c>
-      <c r="F206" t="n">
+      <c r="F226" t="n">
         <v>0.033</v>
       </c>
-      <c r="G206" t="n">
+      <c r="G226" t="n">
         <v>-1.428</v>
       </c>
     </row>
@@ -6468,26 +7048,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>12.885</v>
+        <v>21.579</v>
       </c>
       <c r="F2" t="n">
-        <v>2.019</v>
+        <v>3.348</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
     </row>
@@ -6497,26 +7077,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>12.413</v>
+        <v>21.566</v>
       </c>
       <c r="F3" t="n">
-        <v>1.783</v>
+        <v>2.454</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
     </row>
@@ -6526,26 +7106,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>11.453</v>
+        <v>18.047</v>
       </c>
       <c r="F4" t="n">
-        <v>0.746</v>
+        <v>2.656</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
     </row>
@@ -6555,26 +7135,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>10.974</v>
+        <v>16.344</v>
       </c>
       <c r="F5" t="n">
-        <v>1.632</v>
+        <v>2.21</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
     </row>
@@ -6584,26 +7164,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>10.83</v>
+        <v>14.808</v>
       </c>
       <c r="F6" t="n">
-        <v>1.293</v>
+        <v>1.87</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
     </row>
@@ -6613,26 +7193,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>10.397</v>
+        <v>12.73</v>
       </c>
       <c r="F7" t="n">
-        <v>1.862</v>
+        <v>2.019</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stephen Curry</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -6642,26 +7222,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>10.124</v>
+        <v>12.413</v>
       </c>
       <c r="F8" t="n">
-        <v>1.574</v>
+        <v>1.783</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -6671,26 +7251,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>10.122</v>
+        <v>11.017</v>
       </c>
       <c r="F9" t="n">
-        <v>0.758</v>
+        <v>1.601</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Julius Randle</t>
         </is>
       </c>
     </row>
@@ -6700,26 +7280,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>8.808</v>
+        <v>10.83</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752</v>
+        <v>1.293</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
     </row>
@@ -6729,26 +7309,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>8.472</v>
+        <v>10.821</v>
       </c>
       <c r="F11" t="n">
-        <v>0.907</v>
+        <v>1.632</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
     </row>
@@ -6758,26 +7338,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>7.707</v>
+        <v>10.397</v>
       </c>
       <c r="F12" t="n">
-        <v>1.097</v>
+        <v>1.862</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
     </row>
@@ -6787,26 +7367,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>7.535</v>
+        <v>8.808</v>
       </c>
       <c r="F13" t="n">
-        <v>0.947</v>
+        <v>0.752</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
     </row>
@@ -6828,10 +7408,10 @@
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>7.08</v>
+        <v>8.712999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.017</v>
+        <v>1.462</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6845,26 +7425,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>3.109</v>
+        <v>8.629</v>
       </c>
       <c r="F15" t="n">
-        <v>0.447</v>
+        <v>0.907</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nikola Vučević</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -6874,26 +7454,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>2.088</v>
+        <v>8.442</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.778</v>
+        <v>0.372</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
     </row>
@@ -6903,26 +7483,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>1.922</v>
+        <v>7.707</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.52</v>
+        <v>1.097</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Devin Booker</t>
         </is>
       </c>
     </row>
@@ -6932,26 +7512,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>1.778</v>
+        <v>7.556</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.008999999999999999</v>
+        <v>1.098</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Craig Porter Jr.</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
     </row>
@@ -6961,26 +7541,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.707</v>
+        <v>7.38</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.584</v>
+        <v>0.947</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
     </row>
@@ -6990,26 +7570,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.741</v>
+        <v>5.264</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.508</v>
+        <v>0.32</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>LeBron James</t>
         </is>
       </c>
     </row>
@@ -7057,17 +7637,17 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.738</v>
+        <v>-1.213</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.965</v>
+        <v>-1.488</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kenrich Williams</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
     </row>
@@ -7135,26 +7715,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.697</v>
+        <v>-3.727</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.612</v>
+        <v>-1.575</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Javon Small</t>
         </is>
       </c>
     </row>
@@ -7164,26 +7744,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.727</v>
+        <v>-4.77</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.575</v>
+        <v>-1.736</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
     </row>
@@ -7222,26 +7802,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.629</v>
+        <v>-5.357</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.208</v>
+        <v>-2.707</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moussa Cisse</t>
+          <t>Derik Queen</t>
         </is>
       </c>
     </row>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.933</v>
+        <v>7.928</v>
       </c>
       <c r="E2" t="n">
         <v>36</v>
@@ -492,7 +492,7 @@
         <v>0.667</v>
       </c>
       <c r="G2" t="n">
-        <v>6.455</v>
+        <v>6.451</v>
       </c>
     </row>
     <row r="3">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.829</v>
+        <v>3.824</v>
       </c>
       <c r="E3" t="n">
         <v>34.2</v>
@@ -521,7 +521,7 @@
         <v>0.667</v>
       </c>
       <c r="G3" t="n">
-        <v>3.208</v>
+        <v>3.204</v>
       </c>
     </row>
     <row r="4">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.589</v>
+        <v>2.584</v>
       </c>
       <c r="E4" t="n">
         <v>32.9</v>
@@ -550,7 +550,7 @@
         <v>0.667</v>
       </c>
       <c r="G4" t="n">
-        <v>2.23</v>
+        <v>2.227</v>
       </c>
     </row>
     <row r="5">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.414</v>
+        <v>2.41</v>
       </c>
       <c r="E5" t="n">
         <v>30</v>
@@ -579,7 +579,7 @@
         <v>0.667</v>
       </c>
       <c r="G5" t="n">
-        <v>1.929</v>
+        <v>1.926</v>
       </c>
     </row>
     <row r="6">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.26</v>
+        <v>2.255</v>
       </c>
       <c r="E6" t="n">
         <v>29.9</v>
@@ -608,7 +608,7 @@
         <v>0.667</v>
       </c>
       <c r="G6" t="n">
-        <v>1.821</v>
+        <v>1.818</v>
       </c>
     </row>
     <row r="7">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.595</v>
+        <v>-0.599</v>
       </c>
       <c r="E7" t="n">
         <v>15.8</v>
@@ -637,7 +637,7 @@
         <v>0.667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.824</v>
+        <v>-1.829</v>
       </c>
       <c r="E8" t="n">
         <v>17</v>
@@ -666,7 +666,7 @@
         <v>0.667</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.41</v>
+        <v>-0.412</v>
       </c>
     </row>
     <row r="9">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.643</v>
+        <v>-1.648</v>
       </c>
       <c r="E9" t="n">
         <v>22.1</v>
@@ -695,7 +695,7 @@
         <v>0.667</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.449</v>
+        <v>-0.451</v>
       </c>
     </row>
     <row r="10">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.407</v>
+        <v>6.403</v>
       </c>
       <c r="E10" t="n">
         <v>35.3</v>
@@ -724,7 +724,7 @@
         <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.381</v>
+        <v>5.377</v>
       </c>
     </row>
     <row r="11">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.606</v>
+        <v>4.602</v>
       </c>
       <c r="E11" t="n">
         <v>34.8</v>
@@ -753,7 +753,7 @@
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>3.987</v>
+        <v>3.983</v>
       </c>
     </row>
     <row r="12">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.107</v>
+        <v>4.102</v>
       </c>
       <c r="E12" t="n">
         <v>31.9</v>
@@ -782,7 +782,7 @@
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>3.331</v>
+        <v>3.328</v>
       </c>
     </row>
     <row r="13">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.753</v>
+        <v>2.748</v>
       </c>
       <c r="E13" t="n">
         <v>27.7</v>
@@ -811,7 +811,7 @@
         <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>2.104</v>
+        <v>2.101</v>
       </c>
     </row>
     <row r="14">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.925</v>
+        <v>2.92</v>
       </c>
       <c r="E14" t="n">
         <v>21.3</v>
@@ -840,7 +840,7 @@
         <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.695</v>
+        <v>1.693</v>
       </c>
     </row>
     <row r="15">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.625</v>
+        <v>-0.63</v>
       </c>
       <c r="E15" t="n">
         <v>25.2</v>
@@ -869,7 +869,7 @@
         <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.145</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="16">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.193</v>
+        <v>-1.197</v>
       </c>
       <c r="E16" t="n">
         <v>17.4</v>
@@ -898,7 +898,7 @@
         <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.106</v>
+        <v>-0.107</v>
       </c>
     </row>
     <row r="17">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.296</v>
+        <v>-1.3</v>
       </c>
       <c r="E17" t="n">
         <v>23.4</v>
@@ -927,7 +927,7 @@
         <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.193</v>
+        <v>-0.195</v>
       </c>
     </row>
     <row r="18">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.929</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
@@ -956,7 +956,7 @@
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.341</v>
+        <v>-0.342</v>
       </c>
     </row>
     <row r="19">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.996</v>
+        <v>-2.001</v>
       </c>
       <c r="E19" t="n">
         <v>18.2</v>
@@ -985,7 +985,7 @@
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.732</v>
+        <v>-0.734</v>
       </c>
     </row>
     <row r="20">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-4.779</v>
+        <v>-4.784</v>
       </c>
       <c r="E20" t="n">
         <v>15.7</v>
@@ -1014,7 +1014,7 @@
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.54</v>
+        <v>-1.541</v>
       </c>
     </row>
     <row r="21">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-4.754</v>
+        <v>-4.759</v>
       </c>
       <c r="E21" t="n">
         <v>19.5</v>
@@ -1043,7 +1043,7 @@
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9</v>
+        <v>-1.902</v>
       </c>
     </row>
     <row r="22">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-5.032</v>
+        <v>-5.037</v>
       </c>
       <c r="E22" t="n">
         <v>26.7</v>
@@ -1072,7 +1072,7 @@
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.76</v>
+        <v>-2.763</v>
       </c>
     </row>
     <row r="23">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-5.707</v>
+        <v>-5.711</v>
       </c>
       <c r="E23" t="n">
         <v>27.2</v>
@@ -1101,7 +1101,7 @@
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2</v>
+        <v>-3.203</v>
       </c>
     </row>
     <row r="24">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7.794</v>
+        <v>7.661</v>
       </c>
       <c r="E24" t="n">
-        <v>29.4</v>
+        <v>30.5</v>
       </c>
       <c r="F24" t="n">
         <v>0.7</v>
       </c>
       <c r="G24" t="n">
-        <v>5.196</v>
+        <v>5.307</v>
       </c>
     </row>
     <row r="25">
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.928</v>
+        <v>3.646</v>
       </c>
       <c r="E25" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="F25" t="n">
         <v>0.7</v>
       </c>
       <c r="G25" t="n">
-        <v>2.859</v>
+        <v>2.681</v>
       </c>
     </row>
     <row r="26">
@@ -1179,16 +1179,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.716</v>
+        <v>2.836</v>
       </c>
       <c r="E26" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="F26" t="n">
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>2.206</v>
+        <v>2.275</v>
       </c>
     </row>
     <row r="27">
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.906</v>
+        <v>1.954</v>
       </c>
       <c r="E27" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="F27" t="n">
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>1.541</v>
+        <v>1.579</v>
       </c>
     </row>
     <row r="28">
@@ -1237,16 +1237,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.085</v>
+        <v>1.081</v>
       </c>
       <c r="E28" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="F28" t="n">
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1.022</v>
+        <v>1.013</v>
       </c>
     </row>
     <row r="29">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.76</v>
+        <v>1.092</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="F29" t="n">
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.608</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="30">
@@ -1295,16 +1295,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.301</v>
+        <v>-0.36</v>
       </c>
       <c r="E30" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="F30" t="n">
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>0.162</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="31">
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-3.623</v>
+        <v>-3.566</v>
       </c>
       <c r="E31" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="F31" t="n">
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.181</v>
+        <v>-1.141</v>
       </c>
     </row>
     <row r="32">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.493</v>
+        <v>4.488</v>
       </c>
       <c r="E32" t="n">
         <v>27.7</v>
@@ -1362,7 +1362,7 @@
         <v>0.3</v>
       </c>
       <c r="G32" t="n">
-        <v>2.765</v>
+        <v>2.762</v>
       </c>
     </row>
     <row r="33">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.243</v>
+        <v>2.238</v>
       </c>
       <c r="E33" t="n">
         <v>27.1</v>
@@ -1391,7 +1391,7 @@
         <v>0.3</v>
       </c>
       <c r="G33" t="n">
-        <v>1.434</v>
+        <v>1.431</v>
       </c>
     </row>
     <row r="34">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.029</v>
+        <v>-0.033</v>
       </c>
       <c r="E34" t="n">
         <v>27.1</v>
@@ -1420,7 +1420,7 @@
         <v>0.3</v>
       </c>
       <c r="G34" t="n">
-        <v>0.153</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="35">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.612</v>
+        <v>-0.617</v>
       </c>
       <c r="E35" t="n">
         <v>19.6</v>
@@ -1449,7 +1449,7 @@
         <v>0.3</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.127</v>
+        <v>-0.129</v>
       </c>
     </row>
     <row r="36">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-2.704</v>
+        <v>-2.755</v>
       </c>
       <c r="E36" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="F36" t="n">
         <v>0.3</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.773</v>
+        <v>-0.776</v>
       </c>
     </row>
     <row r="37">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-4.152</v>
+        <v>-4.157</v>
       </c>
       <c r="E37" t="n">
         <v>23.1</v>
@@ -1507,7 +1507,7 @@
         <v>0.3</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.854</v>
+        <v>-1.857</v>
       </c>
     </row>
     <row r="38">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-6.206</v>
+        <v>-6.211</v>
       </c>
       <c r="E38" t="n">
         <v>22.5</v>
@@ -1536,7 +1536,7 @@
         <v>0.3</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.771</v>
+        <v>-2.773</v>
       </c>
     </row>
     <row r="39">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8.986000000000001</v>
+        <v>8.981</v>
       </c>
       <c r="E39" t="n">
         <v>33.2</v>
@@ -1565,7 +1565,7 @@
         <v>0.767</v>
       </c>
       <c r="G39" t="n">
-        <v>6.754</v>
+        <v>6.751</v>
       </c>
     </row>
     <row r="40">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8.132</v>
+        <v>8.128</v>
       </c>
       <c r="E40" t="n">
         <v>34.6</v>
@@ -1594,7 +1594,7 @@
         <v>0.767</v>
       </c>
       <c r="G40" t="n">
-        <v>6.415</v>
+        <v>6.411</v>
       </c>
     </row>
     <row r="41">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.68</v>
+        <v>4.676</v>
       </c>
       <c r="E41" t="n">
         <v>30.4</v>
@@ -1623,7 +1623,7 @@
         <v>0.767</v>
       </c>
       <c r="G41" t="n">
-        <v>3.45</v>
+        <v>3.447</v>
       </c>
     </row>
     <row r="42">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.927</v>
+        <v>3.922</v>
       </c>
       <c r="E42" t="n">
         <v>27.3</v>
@@ -1652,7 +1652,7 @@
         <v>0.767</v>
       </c>
       <c r="G42" t="n">
-        <v>2.666</v>
+        <v>2.663</v>
       </c>
     </row>
     <row r="43">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.879</v>
+        <v>0.874</v>
       </c>
       <c r="E43" t="n">
         <v>29</v>
@@ -1681,7 +1681,7 @@
         <v>0.767</v>
       </c>
       <c r="G43" t="n">
-        <v>0.993</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="44">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.681</v>
+        <v>0.676</v>
       </c>
       <c r="E44" t="n">
         <v>24.1</v>
@@ -1710,7 +1710,7 @@
         <v>0.767</v>
       </c>
       <c r="G44" t="n">
-        <v>0.727</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="45">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.184</v>
+        <v>0.18</v>
       </c>
       <c r="E45" t="n">
         <v>26.6</v>
@@ -1739,7 +1739,7 @@
         <v>0.767</v>
       </c>
       <c r="G45" t="n">
-        <v>0.527</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="46">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="E46" t="n">
         <v>26.7</v>
@@ -1768,7 +1768,7 @@
         <v>0.767</v>
       </c>
       <c r="G46" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="47">
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.566</v>
+        <v>1.561</v>
       </c>
       <c r="E47" t="n">
         <v>22.5</v>
@@ -1797,7 +1797,7 @@
         <v>0.267</v>
       </c>
       <c r="G47" t="n">
-        <v>0.859</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="48">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.245</v>
+        <v>-0.25</v>
       </c>
       <c r="E48" t="n">
         <v>17.2</v>
@@ -1826,7 +1826,7 @@
         <v>0.267</v>
       </c>
       <c r="G48" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="49">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1.814</v>
+        <v>-1.819</v>
       </c>
       <c r="E49" t="n">
         <v>15.2</v>
@@ -1855,7 +1855,7 @@
         <v>0.267</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.489</v>
+        <v>-0.491</v>
       </c>
     </row>
     <row r="50">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-1.638</v>
+        <v>-1.643</v>
       </c>
       <c r="E50" t="n">
         <v>21.2</v>
@@ -1884,7 +1884,7 @@
         <v>0.267</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.606</v>
+        <v>-0.608</v>
       </c>
     </row>
     <row r="51">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-1.664</v>
+        <v>-1.668</v>
       </c>
       <c r="E51" t="n">
         <v>28.8</v>
@@ -1913,7 +1913,7 @@
         <v>0.267</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.839</v>
+        <v>-0.842</v>
       </c>
     </row>
     <row r="52">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-2.114</v>
+        <v>-2.119</v>
       </c>
       <c r="E52" t="n">
         <v>22.8</v>
@@ -1942,7 +1942,7 @@
         <v>0.267</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.876</v>
+        <v>-0.878</v>
       </c>
     </row>
     <row r="53">
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-3.54</v>
+        <v>-3.545</v>
       </c>
       <c r="E53" t="n">
         <v>19</v>
@@ -1971,7 +1971,7 @@
         <v>0.267</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.296</v>
+        <v>-1.298</v>
       </c>
     </row>
     <row r="54">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-4.441</v>
+        <v>-4.445</v>
       </c>
       <c r="E54" t="n">
         <v>17.6</v>
@@ -2000,7 +2000,7 @@
         <v>0.267</v>
       </c>
       <c r="G54" t="n">
-        <v>-1.531</v>
+        <v>-1.532</v>
       </c>
     </row>
     <row r="55">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17.887</v>
+        <v>17.882</v>
       </c>
       <c r="E55" t="n">
         <v>36.5</v>
@@ -2029,7 +2029,7 @@
         <v>0.833</v>
       </c>
       <c r="G55" t="n">
-        <v>14.24</v>
+        <v>14.236</v>
       </c>
     </row>
     <row r="56">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>9.02</v>
+        <v>9.015000000000001</v>
       </c>
       <c r="E56" t="n">
         <v>37</v>
@@ -2058,7 +2058,7 @@
         <v>0.833</v>
       </c>
       <c r="G56" t="n">
-        <v>7.605</v>
+        <v>7.602</v>
       </c>
     </row>
     <row r="57">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.312</v>
+        <v>2.307</v>
       </c>
       <c r="E57" t="n">
         <v>28.1</v>
@@ -2087,7 +2087,7 @@
         <v>0.833</v>
       </c>
       <c r="G57" t="n">
-        <v>1.844</v>
+        <v>1.841</v>
       </c>
     </row>
     <row r="58">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.316</v>
+        <v>0.311</v>
       </c>
       <c r="E58" t="n">
         <v>23.2</v>
@@ -2116,7 +2116,7 @@
         <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>0.555</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="59">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-0.61</v>
+        <v>-0.615</v>
       </c>
       <c r="E59" t="n">
         <v>30.4</v>
@@ -2145,7 +2145,7 @@
         <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="60">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-1.712</v>
+        <v>-1.716</v>
       </c>
       <c r="E60" t="n">
         <v>32.5</v>
@@ -2174,7 +2174,7 @@
         <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.594</v>
+        <v>-0.597</v>
       </c>
     </row>
     <row r="61">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-2.707</v>
+        <v>-2.712</v>
       </c>
       <c r="E61" t="n">
         <v>21.3</v>
@@ -2203,7 +2203,7 @@
         <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.833</v>
+        <v>-0.835</v>
       </c>
     </row>
     <row r="62">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-4.877</v>
+        <v>-4.882</v>
       </c>
       <c r="E62" t="n">
         <v>16.5</v>
@@ -2232,7 +2232,7 @@
         <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>-1.392</v>
+        <v>-1.393</v>
       </c>
     </row>
     <row r="63">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8.789999999999999</v>
+        <v>8.786</v>
       </c>
       <c r="E63" t="n">
         <v>31.4</v>
@@ -2261,7 +2261,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>6.367</v>
+        <v>6.364</v>
       </c>
     </row>
     <row r="64">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2.043</v>
+        <v>2.038</v>
       </c>
       <c r="E64" t="n">
         <v>27.6</v>
@@ -2290,7 +2290,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>1.711</v>
+        <v>1.709</v>
       </c>
     </row>
     <row r="65">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.19</v>
+        <v>0.185</v>
       </c>
       <c r="E65" t="n">
         <v>31.4</v>
@@ -2319,7 +2319,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>0.736</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="66">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.199</v>
+        <v>0.194</v>
       </c>
       <c r="E66" t="n">
         <v>25.7</v>
@@ -2348,7 +2348,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>0.607</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="67">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="E67" t="n">
         <v>25.7</v>
@@ -2377,7 +2377,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>0.546</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="68">
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="E68" t="n">
         <v>24.1</v>
@@ -2406,7 +2406,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.483</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="69">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.089</v>
+        <v>-0.093</v>
       </c>
       <c r="E69" t="n">
         <v>20.9</v>
@@ -2435,7 +2435,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="70">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.908</v>
+        <v>-0.912</v>
       </c>
       <c r="E70" t="n">
         <v>23.4</v>
@@ -2464,7 +2464,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="71">
@@ -2484,16 +2484,16 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>7.572</v>
+        <v>7.723</v>
       </c>
       <c r="E71" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="F71" t="n">
         <v>0.4</v>
       </c>
       <c r="G71" t="n">
-        <v>4.793</v>
+        <v>4.866</v>
       </c>
     </row>
     <row r="72">
@@ -2513,16 +2513,16 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3.338</v>
+        <v>3.626</v>
       </c>
       <c r="E72" t="n">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="F72" t="n">
         <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>1.835</v>
+        <v>2.047</v>
       </c>
     </row>
     <row r="73">
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.249</v>
+        <v>2.112</v>
       </c>
       <c r="E73" t="n">
-        <v>30.9</v>
+        <v>30.6</v>
       </c>
       <c r="F73" t="n">
         <v>0.4</v>
       </c>
       <c r="G73" t="n">
-        <v>1.706</v>
+        <v>1.604</v>
       </c>
     </row>
     <row r="74">
@@ -2571,16 +2571,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2.798</v>
+        <v>2.637</v>
       </c>
       <c r="E74" t="n">
-        <v>24.8</v>
+        <v>24.3</v>
       </c>
       <c r="F74" t="n">
         <v>0.4</v>
       </c>
       <c r="G74" t="n">
-        <v>1.652</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="75">
@@ -2600,16 +2600,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.492</v>
+        <v>0.555</v>
       </c>
       <c r="E75" t="n">
-        <v>31.5</v>
+        <v>30</v>
       </c>
       <c r="F75" t="n">
         <v>0.4</v>
       </c>
       <c r="G75" t="n">
-        <v>0.585</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="76">
@@ -2629,16 +2629,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-0.387</v>
+        <v>-0.26</v>
       </c>
       <c r="E76" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="F76" t="n">
         <v>0.4</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-0.578</v>
+        <v>-0.67</v>
       </c>
       <c r="E77" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="F77" t="n">
         <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="78">
@@ -2687,16 +2687,16 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.588</v>
+        <v>-0.753</v>
       </c>
       <c r="E78" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="F78" t="n">
         <v>0.4</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.096</v>
+        <v>-0.176</v>
       </c>
     </row>
     <row r="79">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5.977</v>
+        <v>5.972</v>
       </c>
       <c r="E79" t="n">
         <v>32.3</v>
@@ -2725,7 +2725,7 @@
         <v>0.8</v>
       </c>
       <c r="G79" t="n">
-        <v>4.566</v>
+        <v>4.563</v>
       </c>
     </row>
     <row r="80">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3.924</v>
+        <v>3.92</v>
       </c>
       <c r="E80" t="n">
         <v>38.7</v>
@@ -2754,7 +2754,7 @@
         <v>0.8</v>
       </c>
       <c r="G80" t="n">
-        <v>3.813</v>
+        <v>3.809</v>
       </c>
     </row>
     <row r="81">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3.568</v>
+        <v>3.563</v>
       </c>
       <c r="E81" t="n">
         <v>27.4</v>
@@ -2783,7 +2783,7 @@
         <v>0.8</v>
       </c>
       <c r="G81" t="n">
-        <v>2.491</v>
+        <v>2.488</v>
       </c>
     </row>
     <row r="82">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.278</v>
+        <v>1.273</v>
       </c>
       <c r="E82" t="n">
         <v>15</v>
@@ -2812,7 +2812,7 @@
         <v>0.8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.649</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="83">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-0.479</v>
+        <v>-0.484</v>
       </c>
       <c r="E83" t="n">
         <v>36.3</v>
@@ -2841,7 +2841,7 @@
         <v>0.8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.243</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="84">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-1.873</v>
+        <v>-1.877</v>
       </c>
       <c r="E84" t="n">
         <v>24.9</v>
@@ -2870,7 +2870,7 @@
         <v>0.8</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.556</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-2.952</v>
+        <v>-2.957</v>
       </c>
       <c r="E85" t="n">
         <v>16</v>
@@ -2899,7 +2899,7 @@
         <v>0.8</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.715</v>
+        <v>-0.717</v>
       </c>
     </row>
     <row r="86">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-6.47</v>
+        <v>-6.475</v>
       </c>
       <c r="E86" t="n">
         <v>17.3</v>
@@ -2928,7 +2928,7 @@
         <v>0.8</v>
       </c>
       <c r="G86" t="n">
-        <v>-2.049</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="87">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2.706</v>
+        <v>2.701</v>
       </c>
       <c r="E87" t="n">
         <v>18.4</v>
@@ -2957,7 +2957,7 @@
         <v>0.167</v>
       </c>
       <c r="G87" t="n">
-        <v>1.1</v>
+        <v>1.098</v>
       </c>
     </row>
     <row r="88">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2.111</v>
+        <v>2.106</v>
       </c>
       <c r="E88" t="n">
         <v>21.6</v>
@@ -2986,7 +2986,7 @@
         <v>0.167</v>
       </c>
       <c r="G88" t="n">
-        <v>1.027</v>
+        <v>1.025</v>
       </c>
     </row>
     <row r="89">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2.22</v>
+        <v>2.215</v>
       </c>
       <c r="E89" t="n">
         <v>17.6</v>
@@ -3015,7 +3015,7 @@
         <v>0.167</v>
       </c>
       <c r="G89" t="n">
-        <v>0.873</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="90">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-0.516</v>
+        <v>-0.52</v>
       </c>
       <c r="E90" t="n">
         <v>19.6</v>
@@ -3044,7 +3044,7 @@
         <v>0.167</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.142</v>
+        <v>-0.144</v>
       </c>
     </row>
     <row r="91">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-1.886</v>
+        <v>-1.891</v>
       </c>
       <c r="E91" t="n">
         <v>24.3</v>
@@ -3073,7 +3073,7 @@
         <v>0.167</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.871</v>
+        <v>-0.874</v>
       </c>
     </row>
     <row r="92">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-2.849</v>
+        <v>-2.854</v>
       </c>
       <c r="E92" t="n">
         <v>22.6</v>
@@ -3102,7 +3102,7 @@
         <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>-1.264</v>
+        <v>-1.266</v>
       </c>
     </row>
     <row r="93">
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-3.712</v>
+        <v>-3.717</v>
       </c>
       <c r="E93" t="n">
         <v>19.9</v>
@@ -3131,7 +3131,7 @@
         <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>-1.472</v>
+        <v>-1.474</v>
       </c>
     </row>
     <row r="94">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-4.178</v>
+        <v>-4.183</v>
       </c>
       <c r="E94" t="n">
         <v>23</v>
@@ -3160,7 +3160,7 @@
         <v>0.167</v>
       </c>
       <c r="G94" t="n">
-        <v>-1.919</v>
+        <v>-1.921</v>
       </c>
     </row>
     <row r="95">
@@ -3180,16 +3180,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.6</v>
+        <v>11.472</v>
       </c>
       <c r="E95" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="F95" t="n">
         <v>0.533</v>
       </c>
       <c r="G95" t="n">
-        <v>7.749</v>
+        <v>7.707</v>
       </c>
     </row>
     <row r="96">
@@ -3209,16 +3209,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3.237</v>
+        <v>3.083</v>
       </c>
       <c r="E96" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="F96" t="n">
         <v>0.533</v>
       </c>
       <c r="G96" t="n">
-        <v>2.372</v>
+        <v>2.256</v>
       </c>
     </row>
     <row r="97">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.582</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="E97" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="F97" t="n">
         <v>0.533</v>
       </c>
       <c r="G97" t="n">
-        <v>0.571</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="98">
@@ -3267,16 +3267,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="E98" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="F98" t="n">
         <v>0.533</v>
       </c>
       <c r="G98" t="n">
-        <v>0.46</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="99">
@@ -3296,16 +3296,16 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-0.211</v>
+        <v>-0.452</v>
       </c>
       <c r="E99" t="n">
-        <v>27.2</v>
+        <v>26.5</v>
       </c>
       <c r="F99" t="n">
         <v>0.533</v>
       </c>
       <c r="G99" t="n">
-        <v>0.183</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="100">
@@ -3321,20 +3321,20 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-0.395</v>
+        <v>-0.452</v>
       </c>
       <c r="E100" t="n">
-        <v>27.8</v>
+        <v>25.5</v>
       </c>
       <c r="F100" t="n">
         <v>0.533</v>
       </c>
       <c r="G100" t="n">
-        <v>0.08</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="101">
@@ -3350,20 +3350,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-0.397</v>
+        <v>-0.498</v>
       </c>
       <c r="E101" t="n">
-        <v>25.9</v>
+        <v>27.8</v>
       </c>
       <c r="F101" t="n">
         <v>0.533</v>
       </c>
       <c r="G101" t="n">
-        <v>0.074</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="102">
@@ -3383,16 +3383,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>-1.705</v>
+        <v>-1.536</v>
       </c>
       <c r="E102" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="F102" t="n">
         <v>0.533</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.668</v>
+        <v>-0.5679999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>6.648</v>
+        <v>6.643</v>
       </c>
       <c r="E103" t="n">
         <v>34.4</v>
@@ -3421,7 +3421,7 @@
         <v>0.633</v>
       </c>
       <c r="G103" t="n">
-        <v>5.219</v>
+        <v>5.216</v>
       </c>
     </row>
     <row r="104">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2.277</v>
+        <v>2.272</v>
       </c>
       <c r="E104" t="n">
         <v>21.2</v>
@@ -3450,7 +3450,7 @@
         <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>1.285</v>
+        <v>1.283</v>
       </c>
     </row>
     <row r="105">
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.058</v>
+        <v>1.053</v>
       </c>
       <c r="E105" t="n">
         <v>24</v>
@@ -3479,7 +3479,7 @@
         <v>0.633</v>
       </c>
       <c r="G105" t="n">
-        <v>0.847</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="106">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.183</v>
+        <v>0.178</v>
       </c>
       <c r="E106" t="n">
         <v>27</v>
@@ -3508,7 +3508,7 @@
         <v>0.633</v>
       </c>
       <c r="G106" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="107">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-1.328</v>
+        <v>-1.333</v>
       </c>
       <c r="E107" t="n">
         <v>23.8</v>
@@ -3537,7 +3537,7 @@
         <v>0.633</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.345</v>
+        <v>-0.347</v>
       </c>
     </row>
     <row r="108">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>-1.854</v>
+        <v>-1.858</v>
       </c>
       <c r="E108" t="n">
         <v>15.8</v>
@@ -3566,7 +3566,7 @@
         <v>0.633</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.401</v>
+        <v>-0.403</v>
       </c>
     </row>
     <row r="109">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>-2.241</v>
+        <v>-2.246</v>
       </c>
       <c r="E109" t="n">
         <v>25.4</v>
@@ -3595,7 +3595,7 @@
         <v>0.633</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.849</v>
+        <v>-0.852</v>
       </c>
     </row>
     <row r="110">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>-2.186</v>
+        <v>-2.191</v>
       </c>
       <c r="E110" t="n">
         <v>29.4</v>
@@ -3624,7 +3624,7 @@
         <v>0.633</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.951</v>
+        <v>-0.954</v>
       </c>
     </row>
     <row r="111">
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2.905</v>
+        <v>2.9</v>
       </c>
       <c r="E111" t="n">
         <v>24.9</v>
@@ -3653,7 +3653,7 @@
         <v>0.2</v>
       </c>
       <c r="G111" t="n">
-        <v>1.613</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="112">
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.222</v>
+        <v>1.218</v>
       </c>
       <c r="E112" t="n">
         <v>24.2</v>
@@ -3682,7 +3682,7 @@
         <v>0.2</v>
       </c>
       <c r="G112" t="n">
-        <v>0.717</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="113">
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-5.326</v>
+        <v>-5.33</v>
       </c>
       <c r="E113" t="n">
         <v>27.8</v>
@@ -3711,7 +3711,7 @@
         <v>0.2</v>
       </c>
       <c r="G113" t="n">
-        <v>-2.969</v>
+        <v>-2.972</v>
       </c>
     </row>
     <row r="114">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>-5.101</v>
+        <v>-5.105</v>
       </c>
       <c r="E114" t="n">
         <v>30.2</v>
@@ -3740,7 +3740,7 @@
         <v>0.2</v>
       </c>
       <c r="G114" t="n">
-        <v>-3.088</v>
+        <v>-3.091</v>
       </c>
     </row>
     <row r="115">
@@ -3760,16 +3760,16 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2.032</v>
+        <v>1.908</v>
       </c>
       <c r="E115" t="n">
-        <v>33.1</v>
+        <v>32.5</v>
       </c>
       <c r="F115" t="n">
         <v>0.6</v>
       </c>
       <c r="G115" t="n">
-        <v>1.815</v>
+        <v>1.699</v>
       </c>
     </row>
     <row r="116">
@@ -3789,16 +3789,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1.929</v>
+        <v>2.067</v>
       </c>
       <c r="E116" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="F116" t="n">
         <v>0.6</v>
       </c>
       <c r="G116" t="n">
-        <v>1.424</v>
+        <v>1.475</v>
       </c>
     </row>
     <row r="117">
@@ -3814,20 +3814,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1.796</v>
+        <v>2.727</v>
       </c>
       <c r="E117" t="n">
-        <v>27.8</v>
+        <v>20</v>
       </c>
       <c r="F117" t="n">
         <v>0.6</v>
       </c>
       <c r="G117" t="n">
-        <v>1.388</v>
+        <v>1.386</v>
       </c>
     </row>
     <row r="118">
@@ -3843,20 +3843,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2.687</v>
+        <v>1.616</v>
       </c>
       <c r="E118" t="n">
-        <v>19.9</v>
+        <v>27.6</v>
       </c>
       <c r="F118" t="n">
         <v>0.6</v>
       </c>
       <c r="G118" t="n">
-        <v>1.363</v>
+        <v>1.274</v>
       </c>
     </row>
     <row r="119">
@@ -3876,16 +3876,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1.201</v>
+        <v>1.371</v>
       </c>
       <c r="E119" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="F119" t="n">
         <v>0.6</v>
       </c>
       <c r="G119" t="n">
-        <v>1.013</v>
+        <v>1.098</v>
       </c>
     </row>
     <row r="120">
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.451</v>
+        <v>0.481</v>
       </c>
       <c r="E120" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="F120" t="n">
         <v>0.6</v>
       </c>
       <c r="G120" t="n">
-        <v>0.645</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="121">
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-0.507</v>
+        <v>-0.512</v>
       </c>
       <c r="E121" t="n">
         <v>19.8</v>
@@ -3943,7 +3943,7 @@
         <v>0.6</v>
       </c>
       <c r="G121" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="122">
@@ -3963,16 +3963,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-0.802</v>
+        <v>-0.728</v>
       </c>
       <c r="E122" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="F122" t="n">
         <v>0.6</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.13</v>
+        <v>-0.083</v>
       </c>
     </row>
     <row r="123">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-2.02</v>
+        <v>-1.953</v>
       </c>
       <c r="E123" t="n">
         <v>15.7</v>
@@ -4001,7 +4001,7 @@
         <v>0.233</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.586</v>
+        <v>-0.5629999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-1.431</v>
+        <v>-1.436</v>
       </c>
       <c r="E124" t="n">
         <v>25.2</v>
@@ -4030,7 +4030,7 @@
         <v>0.233</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.628</v>
+        <v>-0.631</v>
       </c>
     </row>
     <row r="125">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-1.947</v>
+        <v>-1.952</v>
       </c>
       <c r="E125" t="n">
         <v>25.2</v>
@@ -4059,7 +4059,7 @@
         <v>0.233</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.899</v>
+        <v>-0.902</v>
       </c>
     </row>
     <row r="126">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-1.967</v>
+        <v>-1.972</v>
       </c>
       <c r="E126" t="n">
         <v>28.7</v>
@@ -4088,7 +4088,7 @@
         <v>0.233</v>
       </c>
       <c r="G126" t="n">
-        <v>-1.036</v>
+        <v>-1.039</v>
       </c>
     </row>
     <row r="127">
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>-3.628</v>
+        <v>-3.633</v>
       </c>
       <c r="E127" t="n">
         <v>16.3</v>
@@ -4117,7 +4117,7 @@
         <v>0.233</v>
       </c>
       <c r="G127" t="n">
-        <v>-1.153</v>
+        <v>-1.155</v>
       </c>
     </row>
     <row r="128">
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-2.774</v>
+        <v>-2.779</v>
       </c>
       <c r="E128" t="n">
         <v>29.5</v>
@@ -4146,7 +4146,7 @@
         <v>0.233</v>
       </c>
       <c r="G128" t="n">
-        <v>-1.562</v>
+        <v>-1.564</v>
       </c>
     </row>
     <row r="129">
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4.013</v>
+        <v>4.009</v>
       </c>
       <c r="E129" t="n">
         <v>31.7</v>
@@ -4175,7 +4175,7 @@
         <v>0.733</v>
       </c>
       <c r="G129" t="n">
-        <v>3.137</v>
+        <v>3.134</v>
       </c>
     </row>
     <row r="130">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2.742</v>
+        <v>2.737</v>
       </c>
       <c r="E130" t="n">
         <v>30.7</v>
@@ -4204,7 +4204,7 @@
         <v>0.733</v>
       </c>
       <c r="G130" t="n">
-        <v>2.223</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="131">
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2.204</v>
+        <v>2.199</v>
       </c>
       <c r="E131" t="n">
         <v>22.5</v>
@@ -4233,7 +4233,7 @@
         <v>0.733</v>
       </c>
       <c r="G131" t="n">
-        <v>1.38</v>
+        <v>1.377</v>
       </c>
     </row>
     <row r="132">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1.299</v>
+        <v>1.294</v>
       </c>
       <c r="E132" t="n">
         <v>29.5</v>
@@ -4262,7 +4262,7 @@
         <v>0.733</v>
       </c>
       <c r="G132" t="n">
-        <v>1.249</v>
+        <v>1.246</v>
       </c>
     </row>
     <row r="133">
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1.432</v>
+        <v>1.427</v>
       </c>
       <c r="E133" t="n">
         <v>25.6</v>
@@ -4291,7 +4291,7 @@
         <v>0.733</v>
       </c>
       <c r="G133" t="n">
-        <v>1.154</v>
+        <v>1.152</v>
       </c>
     </row>
     <row r="134">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.644</v>
+        <v>0.64</v>
       </c>
       <c r="E134" t="n">
         <v>30.4</v>
@@ -4320,7 +4320,7 @@
         <v>0.733</v>
       </c>
       <c r="G134" t="n">
-        <v>0.872</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="135">
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.328</v>
+        <v>0.323</v>
       </c>
       <c r="E135" t="n">
         <v>29.5</v>
@@ -4349,7 +4349,7 @@
         <v>0.733</v>
       </c>
       <c r="G135" t="n">
-        <v>0.652</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="136">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.147</v>
+        <v>0.142</v>
       </c>
       <c r="E136" t="n">
         <v>19.1</v>
@@ -4378,7 +4378,7 @@
         <v>0.733</v>
       </c>
       <c r="G136" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="137">
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1.1</v>
+        <v>1.095</v>
       </c>
       <c r="E137" t="n">
         <v>22.2</v>
@@ -4407,7 +4407,7 @@
         <v>0.333</v>
       </c>
       <c r="G137" t="n">
-        <v>0.663</v>
+        <v>0.661</v>
       </c>
     </row>
     <row r="138">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-0.515</v>
+        <v>-0.52</v>
       </c>
       <c r="E138" t="n">
         <v>26.2</v>
@@ -4436,7 +4436,7 @@
         <v>0.333</v>
       </c>
       <c r="G138" t="n">
-        <v>-0.099</v>
+        <v>-0.102</v>
       </c>
     </row>
     <row r="139">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>-2.319</v>
+        <v>-2.324</v>
       </c>
       <c r="E139" t="n">
         <v>19.6</v>
@@ -4465,7 +4465,7 @@
         <v>0.333</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8129999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>-5.11</v>
+        <v>-5.114</v>
       </c>
       <c r="E140" t="n">
         <v>15.5</v>
@@ -4494,7 +4494,7 @@
         <v>0.333</v>
       </c>
       <c r="G140" t="n">
-        <v>-1.542</v>
+        <v>-1.544</v>
       </c>
     </row>
     <row r="141">
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>-3.181</v>
+        <v>-3.186</v>
       </c>
       <c r="E141" t="n">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>0.333</v>
       </c>
       <c r="G141" t="n">
-        <v>-1.66</v>
+        <v>-1.662</v>
       </c>
     </row>
     <row r="142">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-6.218</v>
+        <v>-6.223</v>
       </c>
       <c r="E142" t="n">
         <v>15.6</v>
@@ -4552,7 +4552,7 @@
         <v>0.333</v>
       </c>
       <c r="G142" t="n">
-        <v>-1.908</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="143">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6.504</v>
+        <v>6.5</v>
       </c>
       <c r="E143" t="n">
         <v>36.4</v>
@@ -4581,7 +4581,7 @@
         <v>0.867</v>
       </c>
       <c r="G143" t="n">
-        <v>5.596</v>
+        <v>5.592</v>
       </c>
     </row>
     <row r="144">
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4.505</v>
+        <v>4.5</v>
       </c>
       <c r="E144" t="n">
         <v>30</v>
@@ -4610,7 +4610,7 @@
         <v>0.867</v>
       </c>
       <c r="G144" t="n">
-        <v>3.357</v>
+        <v>3.354</v>
       </c>
     </row>
     <row r="145">
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2.934</v>
+        <v>2.929</v>
       </c>
       <c r="E145" t="n">
         <v>31.2</v>
@@ -4639,7 +4639,7 @@
         <v>0.867</v>
       </c>
       <c r="G145" t="n">
-        <v>2.472</v>
+        <v>2.469</v>
       </c>
     </row>
     <row r="146">
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2.906</v>
+        <v>2.901</v>
       </c>
       <c r="E146" t="n">
         <v>30</v>
@@ -4668,7 +4668,7 @@
         <v>0.867</v>
       </c>
       <c r="G146" t="n">
-        <v>2.361</v>
+        <v>2.358</v>
       </c>
     </row>
     <row r="147">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2.007</v>
+        <v>2.003</v>
       </c>
       <c r="E147" t="n">
         <v>34.6</v>
@@ -4697,7 +4697,7 @@
         <v>0.867</v>
       </c>
       <c r="G147" t="n">
-        <v>2.069</v>
+        <v>2.066</v>
       </c>
     </row>
     <row r="148">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3.513</v>
+        <v>3.508</v>
       </c>
       <c r="E148" t="n">
         <v>20.2</v>
@@ -4726,7 +4726,7 @@
         <v>0.867</v>
       </c>
       <c r="G148" t="n">
-        <v>1.846</v>
+        <v>1.844</v>
       </c>
     </row>
     <row r="149">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.287</v>
+        <v>0.282</v>
       </c>
       <c r="E149" t="n">
         <v>25.7</v>
@@ -4755,7 +4755,7 @@
         <v>0.867</v>
       </c>
       <c r="G149" t="n">
-        <v>0.618</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="150">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-1.405</v>
+        <v>-1.409</v>
       </c>
       <c r="E150" t="n">
         <v>24.3</v>
@@ -4784,7 +4784,7 @@
         <v>0.867</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.272</v>
+        <v>-0.274</v>
       </c>
     </row>
     <row r="151">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.419</v>
+        <v>0.414</v>
       </c>
       <c r="E151" t="n">
         <v>17.7</v>
@@ -4813,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.525</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="152">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.078</v>
+        <v>0.073</v>
       </c>
       <c r="E152" t="n">
         <v>16.3</v>
@@ -4842,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="153">
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-1.669</v>
+        <v>-1.674</v>
       </c>
       <c r="E153" t="n">
         <v>15.7</v>
@@ -4871,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.219</v>
+        <v>-0.221</v>
       </c>
     </row>
     <row r="154">
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-2.21</v>
+        <v>-2.215</v>
       </c>
       <c r="E154" t="n">
         <v>16.4</v>
@@ -4900,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>-0.414</v>
+        <v>-0.416</v>
       </c>
     </row>
     <row r="155">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-4.06</v>
+        <v>-4.065</v>
       </c>
       <c r="E155" t="n">
         <v>23.1</v>
@@ -4929,7 +4929,7 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>-1.47</v>
+        <v>-1.473</v>
       </c>
     </row>
     <row r="156">
@@ -4949,16 +4949,16 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3.299</v>
+        <v>2.998</v>
       </c>
       <c r="E156" t="n">
-        <v>33.6</v>
+        <v>33.9</v>
       </c>
       <c r="F156" t="n">
         <v>0.433</v>
       </c>
       <c r="G156" t="n">
-        <v>2.615</v>
+        <v>2.426</v>
       </c>
     </row>
     <row r="157">
@@ -4978,16 +4978,16 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3.246</v>
+        <v>3.295</v>
       </c>
       <c r="E157" t="n">
-        <v>31.7</v>
+        <v>31</v>
       </c>
       <c r="F157" t="n">
         <v>0.433</v>
       </c>
       <c r="G157" t="n">
-        <v>2.428</v>
+        <v>2.408</v>
       </c>
     </row>
     <row r="158">
@@ -5007,16 +5007,16 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3.196</v>
+        <v>2.973</v>
       </c>
       <c r="E158" t="n">
-        <v>30.2</v>
+        <v>30.7</v>
       </c>
       <c r="F158" t="n">
         <v>0.433</v>
       </c>
       <c r="G158" t="n">
-        <v>2.285</v>
+        <v>2.178</v>
       </c>
     </row>
     <row r="159">
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1.729</v>
+        <v>1.4</v>
       </c>
       <c r="E159" t="n">
-        <v>24.3</v>
+        <v>23.8</v>
       </c>
       <c r="F159" t="n">
         <v>0.433</v>
       </c>
       <c r="G159" t="n">
-        <v>1.093</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="160">
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.251</v>
+        <v>0.256</v>
       </c>
       <c r="E160" t="n">
-        <v>26.3</v>
+        <v>25.3</v>
       </c>
       <c r="F160" t="n">
         <v>0.433</v>
       </c>
       <c r="G160" t="n">
-        <v>0.375</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="161">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-0.647</v>
+        <v>-0.855</v>
       </c>
       <c r="E161" t="n">
         <v>28.3</v>
@@ -5103,7 +5103,7 @@
         <v>0.433</v>
       </c>
       <c r="G161" t="n">
-        <v>-0.126</v>
+        <v>-0.248</v>
       </c>
     </row>
     <row r="162">
@@ -5123,16 +5123,16 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>-1.235</v>
+        <v>-1.305</v>
       </c>
       <c r="E162" t="n">
-        <v>26.6</v>
+        <v>25.1</v>
       </c>
       <c r="F162" t="n">
         <v>0.433</v>
       </c>
       <c r="G162" t="n">
-        <v>-0.444</v>
+        <v>-0.456</v>
       </c>
     </row>
     <row r="163">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>-2.265</v>
+        <v>-2.268</v>
       </c>
       <c r="E163" t="n">
         <v>22.2</v>
@@ -5161,7 +5161,7 @@
         <v>0.433</v>
       </c>
       <c r="G163" t="n">
-        <v>-0.846</v>
+        <v>-0.848</v>
       </c>
     </row>
     <row r="164">
@@ -5181,16 +5181,16 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>8.847</v>
+        <v>8.781000000000001</v>
       </c>
       <c r="E164" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="F164" t="n">
         <v>0.467</v>
       </c>
       <c r="G164" t="n">
-        <v>7.134</v>
+        <v>6.974</v>
       </c>
     </row>
     <row r="165">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2.118</v>
+        <v>2.104</v>
       </c>
       <c r="E165" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="F165" t="n">
         <v>0.467</v>
       </c>
       <c r="G165" t="n">
-        <v>1.751</v>
+        <v>1.712</v>
       </c>
     </row>
     <row r="166">
@@ -5239,16 +5239,16 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.827</v>
+        <v>0.886</v>
       </c>
       <c r="E166" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="F166" t="n">
         <v>0.467</v>
       </c>
       <c r="G166" t="n">
-        <v>0.944</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="167">
@@ -5268,16 +5268,16 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-0.344</v>
+        <v>-0.143</v>
       </c>
       <c r="E167" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="F167" t="n">
         <v>0.467</v>
       </c>
       <c r="G167" t="n">
-        <v>0.05</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="168">
@@ -5297,16 +5297,16 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>-0.644</v>
+        <v>-0.526</v>
       </c>
       <c r="E168" t="n">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="F168" t="n">
         <v>0.467</v>
       </c>
       <c r="G168" t="n">
-        <v>-0.104</v>
+        <v>-0.034</v>
       </c>
     </row>
     <row r="169">
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-0.759</v>
+        <v>-0.763</v>
       </c>
       <c r="E169" t="n">
         <v>23</v>
@@ -5335,7 +5335,7 @@
         <v>0.467</v>
       </c>
       <c r="G169" t="n">
-        <v>-0.14</v>
+        <v>-0.142</v>
       </c>
     </row>
     <row r="170">
@@ -5355,16 +5355,16 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-1.344</v>
+        <v>-1.302</v>
       </c>
       <c r="E170" t="n">
-        <v>22.3</v>
+        <v>21.4</v>
       </c>
       <c r="F170" t="n">
         <v>0.467</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.408</v>
+        <v>-0.373</v>
       </c>
     </row>
     <row r="171">
@@ -5384,16 +5384,16 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>-1.444</v>
+        <v>-1.44</v>
       </c>
       <c r="E171" t="n">
-        <v>29.4</v>
+        <v>28.6</v>
       </c>
       <c r="F171" t="n">
         <v>0.467</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.598</v>
+        <v>-0.579</v>
       </c>
     </row>
     <row r="172">
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4.96</v>
+        <v>4.825</v>
       </c>
       <c r="E172" t="n">
-        <v>33.9</v>
+        <v>34.3</v>
       </c>
       <c r="F172" t="n">
         <v>0.5</v>
       </c>
       <c r="G172" t="n">
-        <v>3.858</v>
+        <v>3.807</v>
       </c>
     </row>
     <row r="173">
@@ -5442,16 +5442,16 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3.791</v>
+        <v>3.718</v>
       </c>
       <c r="E173" t="n">
-        <v>27.7</v>
+        <v>26.5</v>
       </c>
       <c r="F173" t="n">
         <v>0.5</v>
       </c>
       <c r="G173" t="n">
-        <v>2.476</v>
+        <v>2.329</v>
       </c>
     </row>
     <row r="174">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2.52</v>
+        <v>2.516</v>
       </c>
       <c r="E174" t="n">
         <v>26.4</v>
@@ -5480,7 +5480,7 @@
         <v>0.5</v>
       </c>
       <c r="G174" t="n">
-        <v>1.658</v>
+        <v>1.656</v>
       </c>
     </row>
     <row r="175">
@@ -5500,16 +5500,16 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1.055</v>
+        <v>1.084</v>
       </c>
       <c r="E175" t="n">
-        <v>23.5</v>
+        <v>24.2</v>
       </c>
       <c r="F175" t="n">
         <v>0.5</v>
       </c>
       <c r="G175" t="n">
-        <v>0.761</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="176">
@@ -5529,16 +5529,16 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.278</v>
+        <v>0.44</v>
       </c>
       <c r="E176" t="n">
-        <v>25.5</v>
+        <v>24.4</v>
       </c>
       <c r="F176" t="n">
         <v>0.5</v>
       </c>
       <c r="G176" t="n">
-        <v>0.414</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="177">
@@ -5558,16 +5558,16 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>-0.294</v>
+        <v>-0.23</v>
       </c>
       <c r="E177" t="n">
-        <v>27.2</v>
+        <v>25.9</v>
       </c>
       <c r="F177" t="n">
         <v>0.5</v>
       </c>
       <c r="G177" t="n">
-        <v>0.117</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="178">
@@ -5587,16 +5587,16 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>-1.427</v>
+        <v>-1.688</v>
       </c>
       <c r="E178" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F178" t="n">
         <v>0.5</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.592</v>
+        <v>-0.717</v>
       </c>
     </row>
     <row r="179">
@@ -5616,16 +5616,16 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>-2.107</v>
+        <v>-2.077</v>
       </c>
       <c r="E179" t="n">
-        <v>29.4</v>
+        <v>28.8</v>
       </c>
       <c r="F179" t="n">
         <v>0.5</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.985</v>
+        <v>-0.947</v>
       </c>
     </row>
     <row r="180">
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5.82</v>
+        <v>5.917</v>
       </c>
       <c r="E180" t="n">
         <v>33.3</v>
@@ -5654,7 +5654,7 @@
         <v>0.367</v>
       </c>
       <c r="G180" t="n">
-        <v>4.29</v>
+        <v>4.366</v>
       </c>
     </row>
     <row r="181">
@@ -5674,16 +5674,16 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>3.032</v>
+        <v>2.985</v>
       </c>
       <c r="E181" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="F181" t="n">
         <v>0.367</v>
       </c>
       <c r="G181" t="n">
-        <v>2.161</v>
+        <v>2.134</v>
       </c>
     </row>
     <row r="182">
@@ -5703,16 +5703,16 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>3.38</v>
+        <v>3.348</v>
       </c>
       <c r="E182" t="n">
-        <v>27.2</v>
+        <v>26.4</v>
       </c>
       <c r="F182" t="n">
         <v>0.367</v>
       </c>
       <c r="G182" t="n">
-        <v>2.121</v>
+        <v>2.045</v>
       </c>
     </row>
     <row r="183">
@@ -5728,20 +5728,20 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Jerami Grant</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>3.5</v>
+        <v>0.126</v>
       </c>
       <c r="E183" t="n">
-        <v>20.5</v>
+        <v>31.7</v>
       </c>
       <c r="F183" t="n">
         <v>0.367</v>
       </c>
       <c r="G183" t="n">
-        <v>1.649</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="184">
@@ -5757,20 +5757,20 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.187</v>
+        <v>-1.07</v>
       </c>
       <c r="E184" t="n">
-        <v>31.8</v>
+        <v>32.6</v>
       </c>
       <c r="F184" t="n">
         <v>0.367</v>
       </c>
       <c r="G184" t="n">
-        <v>0.367</v>
+        <v>-0.478</v>
       </c>
     </row>
     <row r="185">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>-1.057</v>
+        <v>-1.318</v>
       </c>
       <c r="E185" t="n">
-        <v>31.9</v>
+        <v>28.8</v>
       </c>
       <c r="F185" t="n">
         <v>0.367</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.459</v>
+        <v>-0.571</v>
       </c>
     </row>
     <row r="186">
@@ -5815,20 +5815,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>-1.297</v>
+        <v>-1.812</v>
       </c>
       <c r="E186" t="n">
-        <v>30</v>
+        <v>26.5</v>
       </c>
       <c r="F186" t="n">
         <v>0.367</v>
       </c>
       <c r="G186" t="n">
-        <v>-0.581</v>
+        <v>-0.798</v>
       </c>
     </row>
     <row r="187">
@@ -5844,20 +5844,20 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>-1.867</v>
+        <v>-3.122</v>
       </c>
       <c r="E187" t="n">
-        <v>26.7</v>
+        <v>21.4</v>
       </c>
       <c r="F187" t="n">
         <v>0.367</v>
       </c>
       <c r="G187" t="n">
-        <v>-0.835</v>
+        <v>-1.227</v>
       </c>
     </row>
     <row r="188">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.675</v>
+        <v>0.671</v>
       </c>
       <c r="E188" t="n">
         <v>19.8</v>
@@ -5886,7 +5886,7 @@
         <v>0.1</v>
       </c>
       <c r="G188" t="n">
-        <v>0.32</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="189">
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.077</v>
       </c>
       <c r="E189" t="n">
         <v>29.4</v>
@@ -5915,7 +5915,7 @@
         <v>0.1</v>
       </c>
       <c r="G189" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="190">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>-0.895</v>
+        <v>-0.899</v>
       </c>
       <c r="E190" t="n">
         <v>24.3</v>
@@ -5944,7 +5944,7 @@
         <v>0.1</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.402</v>
+        <v>-0.404</v>
       </c>
     </row>
     <row r="191">
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>-1.016</v>
+        <v>-1.021</v>
       </c>
       <c r="E191" t="n">
         <v>31.9</v>
@@ -5973,7 +5973,7 @@
         <v>0.1</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.608</v>
+        <v>-0.611</v>
       </c>
     </row>
     <row r="192">
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-3.019</v>
+        <v>-3.024</v>
       </c>
       <c r="E192" t="n">
         <v>19.5</v>
@@ -6002,7 +6002,7 @@
         <v>0.1</v>
       </c>
       <c r="G192" t="n">
-        <v>-1.188</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="193">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>-2.735</v>
+        <v>-2.74</v>
       </c>
       <c r="E193" t="n">
         <v>30.6</v>
@@ -6031,7 +6031,7 @@
         <v>0.1</v>
       </c>
       <c r="G193" t="n">
-        <v>-1.682</v>
+        <v>-1.685</v>
       </c>
     </row>
     <row r="194">
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>-3.987</v>
+        <v>-3.991</v>
       </c>
       <c r="E194" t="n">
         <v>26.4</v>
@@ -6060,7 +6060,7 @@
         <v>0.1</v>
       </c>
       <c r="G194" t="n">
-        <v>-2.135</v>
+        <v>-2.137</v>
       </c>
     </row>
     <row r="195">
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>-4.117</v>
+        <v>-4.122</v>
       </c>
       <c r="E195" t="n">
         <v>33.3</v>
@@ -6089,7 +6089,7 @@
         <v>0.1</v>
       </c>
       <c r="G195" t="n">
-        <v>-2.784</v>
+        <v>-2.787</v>
       </c>
     </row>
     <row r="196">
@@ -6109,7 +6109,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>4.091</v>
+        <v>4.086</v>
       </c>
       <c r="E196" t="n">
         <v>29.1</v>
@@ -6118,7 +6118,7 @@
         <v>0.967</v>
       </c>
       <c r="G196" t="n">
-        <v>3.063</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="197">
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>3.622</v>
+        <v>3.617</v>
       </c>
       <c r="E197" t="n">
         <v>31.1</v>
@@ -6147,7 +6147,7 @@
         <v>0.967</v>
       </c>
       <c r="G197" t="n">
-        <v>2.972</v>
+        <v>2.968</v>
       </c>
     </row>
     <row r="198">
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1.766</v>
+        <v>1.761</v>
       </c>
       <c r="E198" t="n">
         <v>24.7</v>
@@ -6176,7 +6176,7 @@
         <v>0.967</v>
       </c>
       <c r="G198" t="n">
-        <v>1.406</v>
+        <v>1.403</v>
       </c>
     </row>
     <row r="199">
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.895</v>
+        <v>0.89</v>
       </c>
       <c r="E199" t="n">
         <v>23.4</v>
@@ -6205,7 +6205,7 @@
         <v>0.967</v>
       </c>
       <c r="G199" t="n">
-        <v>0.909</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="200">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.412</v>
+        <v>0.407</v>
       </c>
       <c r="E200" t="n">
         <v>27.4</v>
@@ -6234,7 +6234,7 @@
         <v>0.967</v>
       </c>
       <c r="G200" t="n">
-        <v>0.787</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="201">
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-0.021</v>
+        <v>-0.025</v>
       </c>
       <c r="E201" t="n">
         <v>30.1</v>
@@ -6263,7 +6263,7 @@
         <v>0.967</v>
       </c>
       <c r="G201" t="n">
-        <v>0.594</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="202">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>-1.015</v>
+        <v>-1.02</v>
       </c>
       <c r="E202" t="n">
         <v>21.5</v>
@@ -6292,7 +6292,7 @@
         <v>0.967</v>
       </c>
       <c r="G202" t="n">
-        <v>-0.022</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="203">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>-3.736</v>
+        <v>-3.741</v>
       </c>
       <c r="E203" t="n">
         <v>15.6</v>
@@ -6321,7 +6321,7 @@
         <v>0.967</v>
       </c>
       <c r="G203" t="n">
-        <v>-0.901</v>
+        <v>-0.903</v>
       </c>
     </row>
     <row r="204">
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>6.142</v>
+        <v>6.137</v>
       </c>
       <c r="E204" t="n">
         <v>30.4</v>
@@ -6350,7 +6350,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G204" t="n">
-        <v>4.256</v>
+        <v>4.253</v>
       </c>
     </row>
     <row r="205">
@@ -6366,20 +6366,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>4.276</v>
+        <v>2.278</v>
       </c>
       <c r="E205" t="n">
-        <v>31</v>
+        <v>33.4</v>
       </c>
       <c r="F205" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G205" t="n">
-        <v>3.133</v>
+        <v>1.979</v>
       </c>
     </row>
     <row r="206">
@@ -6395,20 +6395,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>2.283</v>
+        <v>3.602</v>
       </c>
       <c r="E206" t="n">
-        <v>33.4</v>
+        <v>21.6</v>
       </c>
       <c r="F206" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="G206" t="n">
-        <v>1.982</v>
+        <v>1.879</v>
       </c>
     </row>
     <row r="207">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1.462</v>
+        <v>1.457</v>
       </c>
       <c r="E207" t="n">
         <v>31.4</v>
@@ -6437,7 +6437,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G207" t="n">
-        <v>1.325</v>
+        <v>1.322</v>
       </c>
     </row>
     <row r="208">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1.744</v>
+        <v>1.739</v>
       </c>
       <c r="E208" t="n">
         <v>24.2</v>
@@ -6466,7 +6466,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G208" t="n">
-        <v>1.166</v>
+        <v>1.163</v>
       </c>
     </row>
     <row r="209">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1.516</v>
+        <v>1.511</v>
       </c>
       <c r="E209" t="n">
         <v>21.7</v>
@@ -6495,7 +6495,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G209" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="210">
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>-0.588</v>
+        <v>-0.593</v>
       </c>
       <c r="E210" t="n">
         <v>25.4</v>
@@ -6524,7 +6524,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G210" t="n">
-        <v>-0.011</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="211">
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>-0.679</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="E211" t="n">
         <v>25.8</v>
@@ -6553,7 +6553,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G211" t="n">
-        <v>-0.061</v>
+        <v>-0.063</v>
       </c>
     </row>
     <row r="212">
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1.885</v>
+        <v>1.88</v>
       </c>
       <c r="E212" t="n">
         <v>29</v>
@@ -6582,7 +6582,7 @@
         <v>0.133</v>
       </c>
       <c r="G212" t="n">
-        <v>1.221</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="213">
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1.451</v>
+        <v>1.446</v>
       </c>
       <c r="E213" t="n">
         <v>18.9</v>
@@ -6611,7 +6611,7 @@
         <v>0.133</v>
       </c>
       <c r="G213" t="n">
-        <v>0.624</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="214">
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1.123</v>
+        <v>1.118</v>
       </c>
       <c r="E214" t="n">
         <v>15.5</v>
@@ -6640,7 +6640,7 @@
         <v>0.133</v>
       </c>
       <c r="G214" t="n">
-        <v>0.405</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="215">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>-0.053</v>
+        <v>-0.058</v>
       </c>
       <c r="E215" t="n">
         <v>29.5</v>
@@ -6669,7 +6669,7 @@
         <v>0.133</v>
       </c>
       <c r="G215" t="n">
-        <v>0.049</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="216">
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>-1.105</v>
+        <v>-1.11</v>
       </c>
       <c r="E216" t="n">
         <v>19</v>
@@ -6698,7 +6698,7 @@
         <v>0.133</v>
       </c>
       <c r="G216" t="n">
-        <v>-0.386</v>
+        <v>-0.388</v>
       </c>
     </row>
     <row r="217">
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>-1.122</v>
+        <v>-1.127</v>
       </c>
       <c r="E217" t="n">
         <v>19.4</v>
@@ -6727,7 +6727,7 @@
         <v>0.133</v>
       </c>
       <c r="G217" t="n">
-        <v>-0.4</v>
+        <v>-0.402</v>
       </c>
     </row>
     <row r="218">
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>-1.933</v>
+        <v>-1.938</v>
       </c>
       <c r="E218" t="n">
         <v>30.3</v>
@@ -6756,7 +6756,7 @@
         <v>0.133</v>
       </c>
       <c r="G218" t="n">
-        <v>-1.134</v>
+        <v>-1.137</v>
       </c>
     </row>
     <row r="219">
@@ -6776,7 +6776,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>-3.937</v>
+        <v>-3.942</v>
       </c>
       <c r="E219" t="n">
         <v>34.1</v>
@@ -6785,7 +6785,7 @@
         <v>0.133</v>
       </c>
       <c r="G219" t="n">
-        <v>-2.706</v>
+        <v>-2.709</v>
       </c>
     </row>
     <row r="220">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1.677</v>
+        <v>1.672</v>
       </c>
       <c r="E220" t="n">
         <v>22.3</v>
@@ -6814,7 +6814,7 @@
         <v>0.033</v>
       </c>
       <c r="G220" t="n">
-        <v>0.795</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="221">
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>-0.796</v>
+        <v>-0.801</v>
       </c>
       <c r="E221" t="n">
         <v>28.4</v>
@@ -6843,7 +6843,7 @@
         <v>0.033</v>
       </c>
       <c r="G221" t="n">
-        <v>-0.45</v>
+        <v>-0.453</v>
       </c>
     </row>
     <row r="222">
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>-1.278</v>
+        <v>-1.283</v>
       </c>
       <c r="E222" t="n">
         <v>20.2</v>
@@ -6872,7 +6872,7 @@
         <v>0.033</v>
       </c>
       <c r="G222" t="n">
-        <v>-0.524</v>
+        <v>-0.526</v>
       </c>
     </row>
     <row r="223">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>-1.65</v>
+        <v>-1.655</v>
       </c>
       <c r="E223" t="n">
         <v>27.8</v>
@@ -6901,7 +6901,7 @@
         <v>0.033</v>
       </c>
       <c r="G223" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9389999999999999</v>
       </c>
     </row>
     <row r="224">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-2.052</v>
+        <v>-2.057</v>
       </c>
       <c r="E224" t="n">
         <v>24</v>
@@ -6930,7 +6930,7 @@
         <v>0.033</v>
       </c>
       <c r="G224" t="n">
-        <v>-1.009</v>
+        <v>-1.011</v>
       </c>
     </row>
     <row r="225">
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-2.134</v>
+        <v>-2.139</v>
       </c>
       <c r="E225" t="n">
         <v>32.5</v>
@@ -6959,7 +6959,7 @@
         <v>0.033</v>
       </c>
       <c r="G225" t="n">
-        <v>-1.42</v>
+        <v>-1.423</v>
       </c>
     </row>
     <row r="226">
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>-3.329</v>
+        <v>-3.334</v>
       </c>
       <c r="E226" t="n">
         <v>20.8</v>
@@ -6988,7 +6988,7 @@
         <v>0.033</v>
       </c>
       <c r="G226" t="n">
-        <v>-1.428</v>
+        <v>-1.43</v>
       </c>
     </row>
   </sheetData>
@@ -7060,10 +7060,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>21.579</v>
+        <v>21.557</v>
       </c>
       <c r="F2" t="n">
-        <v>3.348</v>
+        <v>3.344</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7089,10 +7089,10 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>21.566</v>
+        <v>21.544</v>
       </c>
       <c r="F3" t="n">
-        <v>2.454</v>
+        <v>2.449</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>18.047</v>
+        <v>18.025</v>
       </c>
       <c r="F4" t="n">
-        <v>2.656</v>
+        <v>2.652</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7147,10 +7147,10 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>16.344</v>
+        <v>16.322</v>
       </c>
       <c r="F5" t="n">
-        <v>2.21</v>
+        <v>2.206</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -7176,10 +7176,10 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>14.808</v>
+        <v>14.785</v>
       </c>
       <c r="F6" t="n">
-        <v>1.87</v>
+        <v>1.866</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7193,26 +7193,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>12.73</v>
+        <v>12.605</v>
       </c>
       <c r="F7" t="n">
-        <v>2.019</v>
+        <v>1.793</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
     </row>
@@ -7222,26 +7222,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>12.413</v>
+        <v>11.457</v>
       </c>
       <c r="F8" t="n">
-        <v>1.783</v>
+        <v>1.931</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
     </row>
@@ -7263,10 +7263,10 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>11.017</v>
+        <v>10.995</v>
       </c>
       <c r="F9" t="n">
-        <v>1.601</v>
+        <v>1.596</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -7292,10 +7292,10 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>10.83</v>
+        <v>10.811</v>
       </c>
       <c r="F10" t="n">
-        <v>1.293</v>
+        <v>1.288</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>10.821</v>
+        <v>10.585</v>
       </c>
       <c r="F11" t="n">
-        <v>1.632</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -7350,10 +7350,10 @@
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>10.397</v>
+        <v>10.434</v>
       </c>
       <c r="F12" t="n">
-        <v>1.862</v>
+        <v>1.871</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -7379,10 +7379,10 @@
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>8.808</v>
+        <v>8.785</v>
       </c>
       <c r="F13" t="n">
-        <v>0.752</v>
+        <v>0.747</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -7396,26 +7396,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>8.712999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="F14" t="n">
-        <v>1.462</v>
+        <v>0.95</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
     </row>
@@ -7425,26 +7425,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>8.629</v>
+        <v>8.422000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.907</v>
+        <v>0.367</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
     </row>
@@ -7454,26 +7454,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>8.442</v>
+        <v>7.551</v>
       </c>
       <c r="F16" t="n">
-        <v>0.372</v>
+        <v>1.116</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
     </row>
@@ -7495,10 +7495,10 @@
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>7.707</v>
+        <v>7.549</v>
       </c>
       <c r="F17" t="n">
-        <v>1.097</v>
+        <v>1.074</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -7512,26 +7512,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>7.556</v>
+        <v>6.732</v>
       </c>
       <c r="F18" t="n">
-        <v>1.098</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
     </row>
@@ -7541,26 +7541,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>7.38</v>
+        <v>5.796</v>
       </c>
       <c r="F19" t="n">
-        <v>0.947</v>
+        <v>0.632</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
     </row>
@@ -7582,10 +7582,10 @@
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.264</v>
+        <v>5.244</v>
       </c>
       <c r="F20" t="n">
-        <v>0.32</v>
+        <v>0.315</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -7611,10 +7611,10 @@
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.173</v>
+        <v>-1.191</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.995</v>
+        <v>-1.007</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.213</v>
+        <v>-1.224</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.488</v>
+        <v>-1.493</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -7669,10 +7669,10 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.327</v>
+        <v>-2.346</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.461</v>
+        <v>-0.466</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -7698,10 +7698,10 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.668</v>
+        <v>-2.685</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.763</v>
+        <v>-0.768</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -7727,10 +7727,10 @@
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.727</v>
+        <v>-3.739</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.575</v>
+        <v>-1.579</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -7756,10 +7756,10 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.77</v>
+        <v>-4.786</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.736</v>
+        <v>-1.741</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -7785,10 +7785,10 @@
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.972</v>
+        <v>-4.989</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.366</v>
+        <v>-1.371</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.357</v>
+        <v>-5.37</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.707</v>
+        <v>-2.712</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -7843,10 +7843,10 @@
         <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.864</v>
+        <v>-5.854</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.294</v>
+        <v>-2.288</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -7872,10 +7872,10 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>-8.462</v>
+        <v>-8.481999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.896</v>
+        <v>-1.9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -7901,10 +7901,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>-10.473</v>
+        <v>-10.485</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.866</v>
+        <v>-3.871</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/nba/public/data/nba_roster_bpm.xlsx
+++ b/nba/public/data/nba_roster_bpm.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G226"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.928</v>
+        <v>7.646</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>35.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.667</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>6.451</v>
+        <v>6.022</v>
       </c>
     </row>
     <row r="3">
@@ -512,16 +512,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.824</v>
+        <v>3.696</v>
       </c>
       <c r="E3" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.667</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>3.204</v>
+        <v>3.047</v>
       </c>
     </row>
     <row r="4">
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.584</v>
+        <v>2.72</v>
       </c>
       <c r="E4" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.667</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>2.227</v>
@@ -566,20 +566,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.41</v>
+        <v>2.433</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="F5" t="n">
-        <v>0.667</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.926</v>
+        <v>1.869</v>
       </c>
     </row>
     <row r="6">
@@ -595,20 +595,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.255</v>
+        <v>2.283</v>
       </c>
       <c r="E6" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.667</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.818</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="7">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.599</v>
+        <v>-0.612</v>
       </c>
       <c r="E7" t="n">
         <v>15.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.667</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.022</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="8">
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.829</v>
+        <v>-1.788</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.667</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.412</v>
+        <v>-0.421</v>
       </c>
     </row>
     <row r="9">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.648</v>
+        <v>-1.797</v>
       </c>
       <c r="E9" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.667</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.451</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.403</v>
+        <v>6.148</v>
       </c>
       <c r="E10" t="n">
-        <v>35.3</v>
+        <v>34.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>5.377</v>
+        <v>5.092</v>
       </c>
     </row>
     <row r="11">
@@ -740,20 +740,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.602</v>
+        <v>5.247</v>
       </c>
       <c r="E11" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>3.983</v>
+        <v>4.473</v>
       </c>
     </row>
     <row r="12">
@@ -769,20 +769,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.102</v>
+        <v>4.501</v>
       </c>
       <c r="E12" t="n">
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>3.328</v>
+        <v>3.732</v>
       </c>
     </row>
     <row r="13">
@@ -798,20 +798,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.748</v>
+        <v>4.089</v>
       </c>
       <c r="E13" t="n">
-        <v>27.7</v>
+        <v>31.6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.101</v>
+        <v>3.307</v>
       </c>
     </row>
     <row r="14">
@@ -827,20 +827,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nikola Vučević</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.92</v>
+        <v>2.883</v>
       </c>
       <c r="E14" t="n">
-        <v>21.3</v>
+        <v>26.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.693</v>
+        <v>2.104</v>
       </c>
     </row>
     <row r="15">
@@ -856,20 +856,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Nikola Vučević</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.63</v>
+        <v>2.974</v>
       </c>
       <c r="E15" t="n">
-        <v>25.2</v>
+        <v>20.3</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.142</v>
+        <v>1.649</v>
       </c>
     </row>
     <row r="16">
@@ -885,20 +885,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dalano Banton</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.197</v>
+        <v>-0.241</v>
       </c>
       <c r="E16" t="n">
-        <v>17.4</v>
+        <v>25.4</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.107</v>
+        <v>0.367</v>
       </c>
     </row>
     <row r="17">
@@ -918,16 +918,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.3</v>
+        <v>-1.056</v>
       </c>
       <c r="E17" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.195</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="18">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.946</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
@@ -956,7 +956,7 @@
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.342</v>
+        <v>-0.347</v>
       </c>
     </row>
     <row r="19">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-2.001</v>
+        <v>-2.015</v>
       </c>
       <c r="E19" t="n">
         <v>18.2</v>
@@ -985,7 +985,7 @@
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.734</v>
+        <v>-0.739</v>
       </c>
     </row>
     <row r="20">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-4.784</v>
+        <v>-4.797</v>
       </c>
       <c r="E20" t="n">
         <v>15.7</v>
@@ -1014,7 +1014,7 @@
         <v>0.067</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.541</v>
+        <v>-1.546</v>
       </c>
     </row>
     <row r="21">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-4.759</v>
+        <v>-4.772</v>
       </c>
       <c r="E21" t="n">
         <v>19.5</v>
@@ -1043,7 +1043,7 @@
         <v>0.067</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.902</v>
+        <v>-1.907</v>
       </c>
     </row>
     <row r="22">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-5.037</v>
+        <v>-5.05</v>
       </c>
       <c r="E22" t="n">
         <v>26.7</v>
@@ -1072,7 +1072,7 @@
         <v>0.067</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.763</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="23">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-5.711</v>
+        <v>-5.725</v>
       </c>
       <c r="E23" t="n">
         <v>27.2</v>
@@ -1101,7 +1101,7 @@
         <v>0.067</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.203</v>
+        <v>-3.211</v>
       </c>
     </row>
     <row r="24">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7.661</v>
+        <v>7.647</v>
       </c>
       <c r="E24" t="n">
         <v>30.5</v>
@@ -1130,7 +1130,7 @@
         <v>0.7</v>
       </c>
       <c r="G24" t="n">
-        <v>5.307</v>
+        <v>5.298</v>
       </c>
     </row>
     <row r="25">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.646</v>
+        <v>3.632</v>
       </c>
       <c r="E25" t="n">
         <v>29.6</v>
@@ -1159,7 +1159,7 @@
         <v>0.7</v>
       </c>
       <c r="G25" t="n">
-        <v>2.681</v>
+        <v>2.672</v>
       </c>
     </row>
     <row r="26">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.836</v>
+        <v>2.822</v>
       </c>
       <c r="E26" t="n">
         <v>30.9</v>
@@ -1188,7 +1188,7 @@
         <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>2.275</v>
+        <v>2.266</v>
       </c>
     </row>
     <row r="27">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.954</v>
+        <v>1.94</v>
       </c>
       <c r="E27" t="n">
         <v>28.6</v>
@@ -1217,7 +1217,7 @@
         <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>1.579</v>
+        <v>1.571</v>
       </c>
     </row>
     <row r="28">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.081</v>
+        <v>1.068</v>
       </c>
       <c r="E28" t="n">
         <v>27.3</v>
@@ -1246,7 +1246,7 @@
         <v>0.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1.013</v>
+        <v>1.005</v>
       </c>
     </row>
     <row r="29">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.092</v>
+        <v>1.079</v>
       </c>
       <c r="E29" t="n">
         <v>20.1</v>
@@ -1275,7 +1275,7 @@
         <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.752</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="30">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.36</v>
+        <v>-0.373</v>
       </c>
       <c r="E30" t="n">
         <v>19.6</v>
@@ -1304,7 +1304,7 @@
         <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>0.139</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="31">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-3.566</v>
+        <v>-3.579</v>
       </c>
       <c r="E31" t="n">
         <v>19.1</v>
@@ -1333,7 +1333,7 @@
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.141</v>
+        <v>-1.146</v>
       </c>
     </row>
     <row r="32">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.488</v>
+        <v>4.475</v>
       </c>
       <c r="E32" t="n">
         <v>27.7</v>
@@ -1362,7 +1362,7 @@
         <v>0.3</v>
       </c>
       <c r="G32" t="n">
-        <v>2.762</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="33">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.238</v>
+        <v>2.224</v>
       </c>
       <c r="E33" t="n">
         <v>27.1</v>
@@ -1391,7 +1391,7 @@
         <v>0.3</v>
       </c>
       <c r="G33" t="n">
-        <v>1.431</v>
+        <v>1.423</v>
       </c>
     </row>
     <row r="34">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.033</v>
+        <v>-0.047</v>
       </c>
       <c r="E34" t="n">
         <v>27.1</v>
@@ -1420,7 +1420,7 @@
         <v>0.3</v>
       </c>
       <c r="G34" t="n">
-        <v>0.151</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="35">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.617</v>
+        <v>-0.63</v>
       </c>
       <c r="E35" t="n">
         <v>19.6</v>
@@ -1449,7 +1449,7 @@
         <v>0.3</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.129</v>
+        <v>-0.135</v>
       </c>
     </row>
     <row r="36">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-2.755</v>
+        <v>-2.756</v>
       </c>
       <c r="E36" t="n">
         <v>15.2</v>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-4.157</v>
+        <v>-4.171</v>
       </c>
       <c r="E37" t="n">
         <v>23.1</v>
@@ -1507,7 +1507,7 @@
         <v>0.3</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.857</v>
+        <v>-1.863</v>
       </c>
     </row>
     <row r="38">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-6.211</v>
+        <v>-6.224</v>
       </c>
       <c r="E38" t="n">
         <v>22.5</v>
@@ -1536,7 +1536,7 @@
         <v>0.3</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.773</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="39">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8.981</v>
+        <v>8.959</v>
       </c>
       <c r="E39" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="F39" t="n">
         <v>0.767</v>
       </c>
       <c r="G39" t="n">
-        <v>6.751</v>
+        <v>6.747</v>
       </c>
     </row>
     <row r="40">
@@ -1585,16 +1585,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8.128</v>
+        <v>7.986</v>
       </c>
       <c r="E40" t="n">
-        <v>34.6</v>
+        <v>34.1</v>
       </c>
       <c r="F40" t="n">
         <v>0.767</v>
       </c>
       <c r="G40" t="n">
-        <v>6.411</v>
+        <v>6.215</v>
       </c>
     </row>
     <row r="41">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.676</v>
+        <v>4.439</v>
       </c>
       <c r="E41" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="F41" t="n">
         <v>0.767</v>
       </c>
       <c r="G41" t="n">
-        <v>3.447</v>
+        <v>3.261</v>
       </c>
     </row>
     <row r="42">
@@ -1643,16 +1643,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.922</v>
+        <v>3.633</v>
       </c>
       <c r="E42" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="F42" t="n">
         <v>0.767</v>
       </c>
       <c r="G42" t="n">
-        <v>2.663</v>
+        <v>2.439</v>
       </c>
     </row>
     <row r="43">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.874</v>
+        <v>0.795</v>
       </c>
       <c r="E43" t="n">
-        <v>29</v>
+        <v>27.9</v>
       </c>
       <c r="F43" t="n">
         <v>0.767</v>
       </c>
       <c r="G43" t="n">
-        <v>0.991</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="44">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Max Strus</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.676</v>
+        <v>0.411</v>
       </c>
       <c r="E44" t="n">
-        <v>24.1</v>
+        <v>26</v>
       </c>
       <c r="F44" t="n">
         <v>0.767</v>
       </c>
       <c r="G44" t="n">
-        <v>0.725</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="45">
@@ -1726,20 +1726,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.18</v>
+        <v>0.479</v>
       </c>
       <c r="E45" t="n">
-        <v>26.6</v>
+        <v>24.1</v>
       </c>
       <c r="F45" t="n">
         <v>0.767</v>
       </c>
       <c r="G45" t="n">
-        <v>0.525</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="46">
@@ -1759,16 +1759,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.882</v>
       </c>
       <c r="E46" t="n">
-        <v>26.7</v>
+        <v>25.1</v>
       </c>
       <c r="F46" t="n">
         <v>0.767</v>
       </c>
       <c r="G46" t="n">
-        <v>0.044</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="47">
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.561</v>
+        <v>1.548</v>
       </c>
       <c r="E47" t="n">
         <v>22.5</v>
@@ -1797,7 +1797,7 @@
         <v>0.267</v>
       </c>
       <c r="G47" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="48">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.25</v>
+        <v>-0.263</v>
       </c>
       <c r="E48" t="n">
         <v>17.2</v>
@@ -1826,7 +1826,7 @@
         <v>0.267</v>
       </c>
       <c r="G48" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="49">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1.819</v>
+        <v>-1.833</v>
       </c>
       <c r="E49" t="n">
         <v>15.2</v>
@@ -1855,7 +1855,7 @@
         <v>0.267</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.491</v>
+        <v>-0.495</v>
       </c>
     </row>
     <row r="50">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-1.643</v>
+        <v>-1.656</v>
       </c>
       <c r="E50" t="n">
         <v>21.2</v>
@@ -1884,7 +1884,7 @@
         <v>0.267</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.608</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="51">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-1.668</v>
+        <v>-1.682</v>
       </c>
       <c r="E51" t="n">
         <v>28.8</v>
@@ -1913,7 +1913,7 @@
         <v>0.267</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.842</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="52">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-2.119</v>
+        <v>-2.132</v>
       </c>
       <c r="E52" t="n">
         <v>22.8</v>
@@ -1942,7 +1942,7 @@
         <v>0.267</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.878</v>
+        <v>-0.885</v>
       </c>
     </row>
     <row r="53">
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-3.545</v>
+        <v>-3.558</v>
       </c>
       <c r="E53" t="n">
         <v>19</v>
@@ -1971,7 +1971,7 @@
         <v>0.267</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.298</v>
+        <v>-1.303</v>
       </c>
     </row>
     <row r="54">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-4.445</v>
+        <v>-4.457</v>
       </c>
       <c r="E54" t="n">
         <v>17.6</v>
@@ -2000,7 +2000,7 @@
         <v>0.267</v>
       </c>
       <c r="G54" t="n">
-        <v>-1.532</v>
+        <v>-1.537</v>
       </c>
     </row>
     <row r="55">
@@ -2020,16 +2020,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17.882</v>
+        <v>17.768</v>
       </c>
       <c r="E55" t="n">
-        <v>36.5</v>
+        <v>35.8</v>
       </c>
       <c r="F55" t="n">
         <v>0.833</v>
       </c>
       <c r="G55" t="n">
-        <v>14.236</v>
+        <v>13.864</v>
       </c>
     </row>
     <row r="56">
@@ -2049,16 +2049,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>9.015000000000001</v>
+        <v>8.769</v>
       </c>
       <c r="E56" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="F56" t="n">
         <v>0.833</v>
       </c>
       <c r="G56" t="n">
-        <v>7.602</v>
+        <v>7.492</v>
       </c>
     </row>
     <row r="57">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.307</v>
+        <v>2.207</v>
       </c>
       <c r="E57" t="n">
-        <v>28.1</v>
+        <v>27.2</v>
       </c>
       <c r="F57" t="n">
         <v>0.833</v>
       </c>
       <c r="G57" t="n">
-        <v>1.841</v>
+        <v>1.724</v>
       </c>
     </row>
     <row r="58">
@@ -2107,16 +2107,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.311</v>
+        <v>0.194</v>
       </c>
       <c r="E58" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="F58" t="n">
         <v>0.833</v>
       </c>
       <c r="G58" t="n">
-        <v>0.552</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="59">
@@ -2136,16 +2136,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-0.615</v>
+        <v>-0.702</v>
       </c>
       <c r="E59" t="n">
-        <v>30.4</v>
+        <v>31.4</v>
       </c>
       <c r="F59" t="n">
         <v>0.833</v>
       </c>
       <c r="G59" t="n">
-        <v>0.138</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2165,16 +2165,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-1.716</v>
+        <v>-1.782</v>
       </c>
       <c r="E60" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="F60" t="n">
         <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.597</v>
+        <v>-0.639</v>
       </c>
     </row>
     <row r="61">
@@ -2194,16 +2194,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-2.712</v>
+        <v>-2.432</v>
       </c>
       <c r="E61" t="n">
-        <v>21.3</v>
+        <v>22.1</v>
       </c>
       <c r="F61" t="n">
         <v>0.833</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.835</v>
+        <v>-0.738</v>
       </c>
     </row>
     <row r="62">
@@ -2219,20 +2219,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KJ Simpson</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-4.882</v>
+        <v>-3.061</v>
       </c>
       <c r="E62" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="F62" t="n">
         <v>0.833</v>
       </c>
       <c r="G62" t="n">
-        <v>-1.393</v>
+        <v>-0.788</v>
       </c>
     </row>
     <row r="63">
@@ -2252,16 +2252,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8.786</v>
+        <v>8.712999999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G63" t="n">
-        <v>6.364</v>
+        <v>6.182</v>
       </c>
     </row>
     <row r="64">
@@ -2277,20 +2277,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2.038</v>
+        <v>5.653</v>
       </c>
       <c r="E64" t="n">
-        <v>27.6</v>
+        <v>30.6</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G64" t="n">
-        <v>1.709</v>
+        <v>4.178</v>
       </c>
     </row>
     <row r="65">
@@ -2306,20 +2306,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.185</v>
+        <v>2.053</v>
       </c>
       <c r="E65" t="n">
-        <v>31.4</v>
+        <v>27.4</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G65" t="n">
-        <v>0.733</v>
+        <v>1.688</v>
       </c>
     </row>
     <row r="66">
@@ -2335,20 +2335,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.194</v>
+        <v>0.414</v>
       </c>
       <c r="E66" t="n">
         <v>25.7</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G66" t="n">
-        <v>0.605</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="67">
@@ -2364,20 +2364,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.081</v>
+        <v>0.179</v>
       </c>
       <c r="E67" t="n">
-        <v>25.7</v>
+        <v>26.1</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G67" t="n">
-        <v>0.543</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="68">
@@ -2397,16 +2397,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.025</v>
+        <v>0.24</v>
       </c>
       <c r="E68" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G68" t="n">
-        <v>0.48</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -2422,20 +2422,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Isaiah Stewart</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.093</v>
+        <v>-0.05</v>
       </c>
       <c r="E69" t="n">
-        <v>20.9</v>
+        <v>31.3</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G69" t="n">
-        <v>0.366</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="70">
@@ -2461,10 +2461,10 @@
         <v>23.4</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G70" t="n">
-        <v>0.011</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="71">
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>7.723</v>
+        <v>7.709</v>
       </c>
       <c r="E71" t="n">
         <v>28.8</v>
@@ -2493,7 +2493,7 @@
         <v>0.4</v>
       </c>
       <c r="G71" t="n">
-        <v>4.866</v>
+        <v>4.858</v>
       </c>
     </row>
     <row r="72">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3.626</v>
+        <v>3.613</v>
       </c>
       <c r="E72" t="n">
         <v>24.4</v>
@@ -2522,7 +2522,7 @@
         <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>2.047</v>
+        <v>2.041</v>
       </c>
     </row>
     <row r="73">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.112</v>
+        <v>2.098</v>
       </c>
       <c r="E73" t="n">
         <v>30.6</v>
@@ -2551,7 +2551,7 @@
         <v>0.4</v>
       </c>
       <c r="G73" t="n">
-        <v>1.604</v>
+        <v>1.595</v>
       </c>
     </row>
     <row r="74">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2.637</v>
+        <v>2.623</v>
       </c>
       <c r="E74" t="n">
         <v>24.3</v>
@@ -2580,7 +2580,7 @@
         <v>0.4</v>
       </c>
       <c r="G74" t="n">
-        <v>1.54</v>
+        <v>1.533</v>
       </c>
     </row>
     <row r="75">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.555</v>
+        <v>0.541</v>
       </c>
       <c r="E75" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         <v>0.4</v>
       </c>
       <c r="G75" t="n">
-        <v>0.597</v>
+        <v>0.589</v>
       </c>
     </row>
     <row r="76">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-0.26</v>
+        <v>-0.273</v>
       </c>
       <c r="E76" t="n">
         <v>29.4</v>
@@ -2638,7 +2638,7 @@
         <v>0.4</v>
       </c>
       <c r="G76" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="77">
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-0.67</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="E77" t="n">
         <v>23</v>
@@ -2667,7 +2667,7 @@
         <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.13</v>
+        <v>-0.136</v>
       </c>
     </row>
     <row r="78">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.753</v>
+        <v>-0.767</v>
       </c>
       <c r="E78" t="n">
         <v>24</v>
@@ -2696,7 +2696,7 @@
         <v>0.4</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.176</v>
+        <v>-0.183</v>
       </c>
     </row>
     <row r="79">
@@ -2712,20 +2712,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5.972</v>
+        <v>6.838</v>
       </c>
       <c r="E79" t="n">
-        <v>32.3</v>
+        <v>36.1</v>
       </c>
       <c r="F79" t="n">
         <v>0.8</v>
       </c>
       <c r="G79" t="n">
-        <v>4.563</v>
+        <v>5.751</v>
       </c>
     </row>
     <row r="80">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3.92</v>
+        <v>5.892</v>
       </c>
       <c r="E80" t="n">
-        <v>38.7</v>
+        <v>33.1</v>
       </c>
       <c r="F80" t="n">
         <v>0.8</v>
       </c>
       <c r="G80" t="n">
-        <v>3.809</v>
+        <v>4.609</v>
       </c>
     </row>
     <row r="81">
@@ -2770,20 +2770,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3.563</v>
+        <v>4.075</v>
       </c>
       <c r="E81" t="n">
-        <v>27.4</v>
+        <v>39</v>
       </c>
       <c r="F81" t="n">
         <v>0.8</v>
       </c>
       <c r="G81" t="n">
-        <v>2.488</v>
+        <v>3.962</v>
       </c>
     </row>
     <row r="82">
@@ -2799,20 +2799,20 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Clint Capela</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.273</v>
+        <v>3.516</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>27.6</v>
       </c>
       <c r="F82" t="n">
         <v>0.8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.648</v>
+        <v>2.482</v>
       </c>
     </row>
     <row r="83">
@@ -2832,16 +2832,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-0.484</v>
+        <v>-0.546</v>
       </c>
       <c r="E83" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="F83" t="n">
         <v>0.8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.239</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="84">
@@ -2861,16 +2861,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-1.877</v>
+        <v>-1.551</v>
       </c>
       <c r="E84" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="F84" t="n">
         <v>0.8</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.371</v>
       </c>
     </row>
     <row r="85">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-2.957</v>
+        <v>-2.97</v>
       </c>
       <c r="E85" t="n">
         <v>16</v>
@@ -2899,7 +2899,7 @@
         <v>0.8</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.717</v>
+        <v>-0.721</v>
       </c>
     </row>
     <row r="86">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-6.475</v>
+        <v>-6.489</v>
       </c>
       <c r="E86" t="n">
         <v>17.3</v>
@@ -2928,7 +2928,7 @@
         <v>0.8</v>
       </c>
       <c r="G86" t="n">
-        <v>-2.05</v>
+        <v>-2.055</v>
       </c>
     </row>
     <row r="87">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2.701</v>
+        <v>2.688</v>
       </c>
       <c r="E87" t="n">
         <v>18.4</v>
@@ -2957,7 +2957,7 @@
         <v>0.167</v>
       </c>
       <c r="G87" t="n">
-        <v>1.098</v>
+        <v>1.094</v>
       </c>
     </row>
     <row r="88">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2.106</v>
+        <v>2.093</v>
       </c>
       <c r="E88" t="n">
         <v>21.6</v>
@@ -2986,7 +2986,7 @@
         <v>0.167</v>
       </c>
       <c r="G88" t="n">
-        <v>1.025</v>
+        <v>1.019</v>
       </c>
     </row>
     <row r="89">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2.215</v>
+        <v>2.202</v>
       </c>
       <c r="E89" t="n">
         <v>17.6</v>
@@ -3015,7 +3015,7 @@
         <v>0.167</v>
       </c>
       <c r="G89" t="n">
-        <v>0.871</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="90">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-0.52</v>
+        <v>-0.534</v>
       </c>
       <c r="E90" t="n">
         <v>19.6</v>
@@ -3044,7 +3044,7 @@
         <v>0.167</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.144</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="91">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-1.891</v>
+        <v>-1.905</v>
       </c>
       <c r="E91" t="n">
         <v>24.3</v>
@@ -3073,7 +3073,7 @@
         <v>0.167</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.874</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="92">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-2.854</v>
+        <v>-2.868</v>
       </c>
       <c r="E92" t="n">
         <v>22.6</v>
@@ -3102,7 +3102,7 @@
         <v>0.167</v>
       </c>
       <c r="G92" t="n">
-        <v>-1.266</v>
+        <v>-1.273</v>
       </c>
     </row>
     <row r="93">
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-3.717</v>
+        <v>-3.73</v>
       </c>
       <c r="E93" t="n">
         <v>19.9</v>
@@ -3131,7 +3131,7 @@
         <v>0.167</v>
       </c>
       <c r="G93" t="n">
-        <v>-1.474</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="94">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-4.183</v>
+        <v>-4.197</v>
       </c>
       <c r="E94" t="n">
         <v>23</v>
@@ -3160,7 +3160,7 @@
         <v>0.167</v>
       </c>
       <c r="G94" t="n">
-        <v>-1.921</v>
+        <v>-1.927</v>
       </c>
     </row>
     <row r="95">
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.472</v>
+        <v>11.458</v>
       </c>
       <c r="E95" t="n">
         <v>30.8</v>
@@ -3189,7 +3189,7 @@
         <v>0.533</v>
       </c>
       <c r="G95" t="n">
-        <v>7.707</v>
+        <v>7.698</v>
       </c>
     </row>
     <row r="96">
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3.083</v>
+        <v>3.07</v>
       </c>
       <c r="E96" t="n">
         <v>29.9</v>
@@ -3218,7 +3218,7 @@
         <v>0.533</v>
       </c>
       <c r="G96" t="n">
-        <v>2.256</v>
+        <v>2.248</v>
       </c>
     </row>
     <row r="97">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="E97" t="n">
         <v>24.8</v>
@@ -3247,7 +3247,7 @@
         <v>0.533</v>
       </c>
       <c r="G97" t="n">
-        <v>0.627</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="98">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.342</v>
+        <v>0.328</v>
       </c>
       <c r="E98" t="n">
         <v>24.9</v>
@@ -3276,7 +3276,7 @@
         <v>0.533</v>
       </c>
       <c r="G98" t="n">
-        <v>0.454</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="99">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-0.452</v>
+        <v>-0.466</v>
       </c>
       <c r="E99" t="n">
         <v>26.5</v>
@@ -3305,7 +3305,7 @@
         <v>0.533</v>
       </c>
       <c r="G99" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="100">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-0.452</v>
+        <v>-0.466</v>
       </c>
       <c r="E100" t="n">
         <v>25.5</v>
@@ -3334,7 +3334,7 @@
         <v>0.533</v>
       </c>
       <c r="G100" t="n">
-        <v>0.043</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="101">
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-0.498</v>
+        <v>-0.511</v>
       </c>
       <c r="E101" t="n">
         <v>27.8</v>
@@ -3363,7 +3363,7 @@
         <v>0.533</v>
       </c>
       <c r="G101" t="n">
-        <v>0.021</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="102">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>-1.536</v>
+        <v>-1.55</v>
       </c>
       <c r="E102" t="n">
         <v>27.2</v>
@@ -3392,7 +3392,7 @@
         <v>0.533</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.575</v>
       </c>
     </row>
     <row r="103">
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>6.643</v>
+        <v>6.797</v>
       </c>
       <c r="E103" t="n">
-        <v>34.4</v>
+        <v>33.2</v>
       </c>
       <c r="F103" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G103" t="n">
-        <v>5.216</v>
+        <v>5.159</v>
       </c>
     </row>
     <row r="104">
@@ -3441,16 +3441,16 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2.272</v>
+        <v>2.192</v>
       </c>
       <c r="E104" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="F104" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G104" t="n">
-        <v>1.283</v>
+        <v>1.221</v>
       </c>
     </row>
     <row r="105">
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.053</v>
+        <v>1.114</v>
       </c>
       <c r="E105" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="F105" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G105" t="n">
-        <v>0.845</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -3499,16 +3499,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.178</v>
+        <v>0.391</v>
       </c>
       <c r="E106" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="F106" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G106" t="n">
-        <v>0.456</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="107">
@@ -3528,16 +3528,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-1.333</v>
+        <v>-1.28</v>
       </c>
       <c r="E107" t="n">
-        <v>23.8</v>
+        <v>25.1</v>
       </c>
       <c r="F107" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.347</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="108">
@@ -3557,16 +3557,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>-1.858</v>
+        <v>-1.867</v>
       </c>
       <c r="E108" t="n">
         <v>15.8</v>
       </c>
       <c r="F108" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.403</v>
+        <v>-0.395</v>
       </c>
     </row>
     <row r="109">
@@ -3586,16 +3586,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>-2.246</v>
+        <v>-2.033</v>
       </c>
       <c r="E109" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="F109" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.852</v>
+        <v>-0.733</v>
       </c>
     </row>
     <row r="110">
@@ -3615,16 +3615,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>-2.191</v>
+        <v>-2.218</v>
       </c>
       <c r="E110" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
       <c r="F110" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.954</v>
+        <v>-0.962</v>
       </c>
     </row>
     <row r="111">
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2.9</v>
+        <v>2.887</v>
       </c>
       <c r="E111" t="n">
         <v>24.9</v>
@@ -3653,7 +3653,7 @@
         <v>0.2</v>
       </c>
       <c r="G111" t="n">
-        <v>1.61</v>
+        <v>1.603</v>
       </c>
     </row>
     <row r="112">
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.218</v>
+        <v>1.204</v>
       </c>
       <c r="E112" t="n">
         <v>24.2</v>
@@ -3682,7 +3682,7 @@
         <v>0.2</v>
       </c>
       <c r="G112" t="n">
-        <v>0.714</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="113">
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-5.33</v>
+        <v>-5.344</v>
       </c>
       <c r="E113" t="n">
         <v>27.8</v>
@@ -3711,7 +3711,7 @@
         <v>0.2</v>
       </c>
       <c r="G113" t="n">
-        <v>-2.972</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="114">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>-5.105</v>
+        <v>-5.119</v>
       </c>
       <c r="E114" t="n">
         <v>30.2</v>
@@ -3740,7 +3740,7 @@
         <v>0.2</v>
       </c>
       <c r="G114" t="n">
-        <v>-3.091</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="115">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.908</v>
+        <v>1.894</v>
       </c>
       <c r="E115" t="n">
         <v>32.5</v>
@@ -3769,7 +3769,7 @@
         <v>0.6</v>
       </c>
       <c r="G115" t="n">
-        <v>1.699</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="116">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2.067</v>
+        <v>2.053</v>
       </c>
       <c r="E116" t="n">
         <v>26.5</v>
@@ -3798,7 +3798,7 @@
         <v>0.6</v>
       </c>
       <c r="G116" t="n">
-        <v>1.475</v>
+        <v>1.467</v>
       </c>
     </row>
     <row r="117">
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2.727</v>
+        <v>2.714</v>
       </c>
       <c r="E117" t="n">
         <v>20</v>
@@ -3827,7 +3827,7 @@
         <v>0.6</v>
       </c>
       <c r="G117" t="n">
-        <v>1.386</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="118">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1.616</v>
+        <v>1.602</v>
       </c>
       <c r="E118" t="n">
         <v>27.6</v>
@@ -3856,7 +3856,7 @@
         <v>0.6</v>
       </c>
       <c r="G118" t="n">
-        <v>1.274</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="119">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1.371</v>
+        <v>1.358</v>
       </c>
       <c r="E119" t="n">
         <v>26.8</v>
@@ -3885,7 +3885,7 @@
         <v>0.6</v>
       </c>
       <c r="G119" t="n">
-        <v>1.098</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="120">
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.481</v>
+        <v>0.467</v>
       </c>
       <c r="E120" t="n">
         <v>29.6</v>
@@ -3914,7 +3914,7 @@
         <v>0.6</v>
       </c>
       <c r="G120" t="n">
-        <v>0.666</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="121">
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-0.512</v>
+        <v>-0.526</v>
       </c>
       <c r="E121" t="n">
         <v>19.8</v>
@@ -3943,7 +3943,7 @@
         <v>0.6</v>
       </c>
       <c r="G121" t="n">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="122">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-0.728</v>
+        <v>-0.741</v>
       </c>
       <c r="E122" t="n">
         <v>31.1</v>
@@ -3972,7 +3972,7 @@
         <v>0.6</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.083</v>
+        <v>-0.092</v>
       </c>
     </row>
     <row r="123">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-1.953</v>
+        <v>-1.964</v>
       </c>
       <c r="E123" t="n">
         <v>15.7</v>
@@ -4001,7 +4001,7 @@
         <v>0.233</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5659999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-1.436</v>
+        <v>-1.449</v>
       </c>
       <c r="E124" t="n">
         <v>25.2</v>
@@ -4030,7 +4030,7 @@
         <v>0.233</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.631</v>
+        <v>-0.638</v>
       </c>
     </row>
     <row r="125">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-1.952</v>
+        <v>-1.965</v>
       </c>
       <c r="E125" t="n">
         <v>25.2</v>
@@ -4059,7 +4059,7 @@
         <v>0.233</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.902</v>
+        <v>-0.909</v>
       </c>
     </row>
     <row r="126">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-1.972</v>
+        <v>-1.986</v>
       </c>
       <c r="E126" t="n">
         <v>28.7</v>
@@ -4088,7 +4088,7 @@
         <v>0.233</v>
       </c>
       <c r="G126" t="n">
-        <v>-1.039</v>
+        <v>-1.047</v>
       </c>
     </row>
     <row r="127">
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>-3.633</v>
+        <v>-3.647</v>
       </c>
       <c r="E127" t="n">
         <v>16.3</v>
@@ -4117,7 +4117,7 @@
         <v>0.233</v>
       </c>
       <c r="G127" t="n">
-        <v>-1.155</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="128">
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-2.779</v>
+        <v>-2.793</v>
       </c>
       <c r="E128" t="n">
         <v>29.5</v>
@@ -4146,7 +4146,7 @@
         <v>0.233</v>
       </c>
       <c r="G128" t="n">
-        <v>-1.564</v>
+        <v>-1.573</v>
       </c>
     </row>
     <row r="129">
@@ -4162,20 +4162,20 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4.009</v>
+        <v>6.61</v>
       </c>
       <c r="E129" t="n">
-        <v>31.7</v>
+        <v>33.7</v>
       </c>
       <c r="F129" t="n">
         <v>0.733</v>
       </c>
       <c r="G129" t="n">
-        <v>3.134</v>
+        <v>5.148</v>
       </c>
     </row>
     <row r="130">
@@ -4191,20 +4191,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2.737</v>
+        <v>3.739</v>
       </c>
       <c r="E130" t="n">
-        <v>30.7</v>
+        <v>32.2</v>
       </c>
       <c r="F130" t="n">
         <v>0.733</v>
       </c>
       <c r="G130" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4220,20 +4220,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2.199</v>
+        <v>2.653</v>
       </c>
       <c r="E131" t="n">
-        <v>22.5</v>
+        <v>30.6</v>
       </c>
       <c r="F131" t="n">
         <v>0.733</v>
       </c>
       <c r="G131" t="n">
-        <v>1.377</v>
+        <v>2.157</v>
       </c>
     </row>
     <row r="132">
@@ -4253,16 +4253,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1.294</v>
+        <v>1.261</v>
       </c>
       <c r="E132" t="n">
-        <v>29.5</v>
+        <v>28.3</v>
       </c>
       <c r="F132" t="n">
         <v>0.733</v>
       </c>
       <c r="G132" t="n">
-        <v>1.246</v>
+        <v>1.175</v>
       </c>
     </row>
     <row r="133">
@@ -4278,20 +4278,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1.427</v>
+        <v>1.762</v>
       </c>
       <c r="E133" t="n">
-        <v>25.6</v>
+        <v>22.3</v>
       </c>
       <c r="F133" t="n">
         <v>0.733</v>
       </c>
       <c r="G133" t="n">
-        <v>1.152</v>
+        <v>1.161</v>
       </c>
     </row>
     <row r="134">
@@ -4307,20 +4307,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.64</v>
+        <v>1.398</v>
       </c>
       <c r="E134" t="n">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="F134" t="n">
         <v>0.733</v>
       </c>
       <c r="G134" t="n">
-        <v>0.869</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="135">
@@ -4336,20 +4336,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.323</v>
+        <v>0.592</v>
       </c>
       <c r="E135" t="n">
-        <v>29.5</v>
+        <v>31.1</v>
       </c>
       <c r="F135" t="n">
         <v>0.733</v>
       </c>
       <c r="G135" t="n">
-        <v>0.649</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="136">
@@ -4365,20 +4365,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.142</v>
+        <v>0.213</v>
       </c>
       <c r="E136" t="n">
-        <v>19.1</v>
+        <v>29.7</v>
       </c>
       <c r="F136" t="n">
         <v>0.733</v>
       </c>
       <c r="G136" t="n">
-        <v>0.348</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="137">
@@ -4394,20 +4394,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1.095</v>
+        <v>2.212</v>
       </c>
       <c r="E137" t="n">
-        <v>22.2</v>
+        <v>32</v>
       </c>
       <c r="F137" t="n">
         <v>0.333</v>
       </c>
       <c r="G137" t="n">
-        <v>0.661</v>
+        <v>1.696</v>
       </c>
     </row>
     <row r="138">
@@ -4423,20 +4423,20 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-0.52</v>
+        <v>1.082</v>
       </c>
       <c r="E138" t="n">
-        <v>26.2</v>
+        <v>22.2</v>
       </c>
       <c r="F138" t="n">
         <v>0.333</v>
       </c>
       <c r="G138" t="n">
-        <v>-0.102</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="139">
@@ -4452,20 +4452,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>-2.324</v>
+        <v>-0.534</v>
       </c>
       <c r="E139" t="n">
-        <v>19.6</v>
+        <v>26.2</v>
       </c>
       <c r="F139" t="n">
         <v>0.333</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.109</v>
       </c>
     </row>
     <row r="140">
@@ -4481,20 +4481,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Micah Peavy</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>-5.114</v>
+        <v>-2.337</v>
       </c>
       <c r="E140" t="n">
-        <v>15.5</v>
+        <v>19.6</v>
       </c>
       <c r="F140" t="n">
         <v>0.333</v>
       </c>
       <c r="G140" t="n">
-        <v>-1.544</v>
+        <v>-0.819</v>
       </c>
     </row>
     <row r="141">
@@ -4510,20 +4510,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Micah Peavy</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>-3.186</v>
+        <v>-5.128</v>
       </c>
       <c r="E141" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="F141" t="n">
         <v>0.333</v>
       </c>
       <c r="G141" t="n">
-        <v>-1.662</v>
+        <v>-1.548</v>
       </c>
     </row>
     <row r="142">
@@ -4539,49 +4539,49 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jordan Hawkins</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-6.223</v>
+        <v>-3.199</v>
       </c>
       <c r="E142" t="n">
-        <v>15.6</v>
+        <v>28</v>
       </c>
       <c r="F142" t="n">
         <v>0.333</v>
       </c>
       <c r="G142" t="n">
-        <v>-1.91</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Jordan Hawkins</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6.5</v>
+        <v>-6.235</v>
       </c>
       <c r="E143" t="n">
-        <v>36.4</v>
+        <v>15.6</v>
       </c>
       <c r="F143" t="n">
-        <v>0.867</v>
+        <v>0.333</v>
       </c>
       <c r="G143" t="n">
-        <v>5.592</v>
+        <v>-1.913</v>
       </c>
     </row>
     <row r="144">
@@ -4597,20 +4597,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4.5</v>
+        <v>6.542</v>
       </c>
       <c r="E144" t="n">
-        <v>30</v>
+        <v>35.9</v>
       </c>
       <c r="F144" t="n">
         <v>0.867</v>
       </c>
       <c r="G144" t="n">
-        <v>3.354</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="145">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2.929</v>
+        <v>4.665</v>
       </c>
       <c r="E145" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="F145" t="n">
         <v>0.867</v>
       </c>
       <c r="G145" t="n">
-        <v>2.469</v>
+        <v>3.467</v>
       </c>
     </row>
     <row r="146">
@@ -4659,16 +4659,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2.901</v>
+        <v>2.728</v>
       </c>
       <c r="E146" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="F146" t="n">
         <v>0.867</v>
       </c>
       <c r="G146" t="n">
-        <v>2.358</v>
+        <v>2.336</v>
       </c>
     </row>
     <row r="147">
@@ -4684,20 +4684,20 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2.003</v>
+        <v>2.805</v>
       </c>
       <c r="E147" t="n">
-        <v>34.6</v>
+        <v>29.6</v>
       </c>
       <c r="F147" t="n">
         <v>0.867</v>
       </c>
       <c r="G147" t="n">
-        <v>2.066</v>
+        <v>2.261</v>
       </c>
     </row>
     <row r="148">
@@ -4713,20 +4713,20 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3.508</v>
+        <v>1.926</v>
       </c>
       <c r="E148" t="n">
-        <v>20.2</v>
+        <v>33.6</v>
       </c>
       <c r="F148" t="n">
         <v>0.867</v>
       </c>
       <c r="G148" t="n">
-        <v>1.844</v>
+        <v>1.953</v>
       </c>
     </row>
     <row r="149">
@@ -4742,20 +4742,20 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.282</v>
+        <v>3.604</v>
       </c>
       <c r="E149" t="n">
-        <v>25.7</v>
+        <v>20.2</v>
       </c>
       <c r="F149" t="n">
         <v>0.867</v>
       </c>
       <c r="G149" t="n">
-        <v>0.616</v>
+        <v>1.877</v>
       </c>
     </row>
     <row r="150">
@@ -4771,49 +4771,49 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-1.409</v>
+        <v>0.329</v>
       </c>
       <c r="E150" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="F150" t="n">
         <v>0.867</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.274</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.414</v>
+        <v>-1.635</v>
       </c>
       <c r="E151" t="n">
-        <v>17.7</v>
+        <v>24.1</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
       <c r="G151" t="n">
-        <v>0.523</v>
+        <v>-0.385</v>
       </c>
     </row>
     <row r="152">
@@ -4829,20 +4829,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Kenrich Williams</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.073</v>
+        <v>14.672</v>
       </c>
       <c r="E152" t="n">
-        <v>16.3</v>
+        <v>32.6</v>
       </c>
       <c r="F152" t="n">
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.363</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="153">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-1.674</v>
+        <v>4.445</v>
       </c>
       <c r="E153" t="n">
-        <v>15.7</v>
+        <v>27.5</v>
       </c>
       <c r="F153" t="n">
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.221</v>
+        <v>3.115</v>
       </c>
     </row>
     <row r="154">
@@ -4887,20 +4887,20 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-2.215</v>
+        <v>3.476</v>
       </c>
       <c r="E154" t="n">
-        <v>16.4</v>
+        <v>21.1</v>
       </c>
       <c r="F154" t="n">
         <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>-0.416</v>
+        <v>1.963</v>
       </c>
     </row>
     <row r="155">
@@ -4916,136 +4916,136 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-4.065</v>
+        <v>2.082</v>
       </c>
       <c r="E155" t="n">
-        <v>23.1</v>
+        <v>27.1</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>-1.473</v>
+        <v>1.739</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2.998</v>
+        <v>1.666</v>
       </c>
       <c r="E156" t="n">
-        <v>33.9</v>
+        <v>24.6</v>
       </c>
       <c r="F156" t="n">
-        <v>0.433</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>2.426</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3.295</v>
+        <v>1.935</v>
       </c>
       <c r="E157" t="n">
-        <v>31</v>
+        <v>18.9</v>
       </c>
       <c r="F157" t="n">
-        <v>0.433</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>2.408</v>
+        <v>1.155</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2.973</v>
+        <v>0.006</v>
       </c>
       <c r="E158" t="n">
-        <v>30.7</v>
+        <v>22.9</v>
       </c>
       <c r="F158" t="n">
-        <v>0.433</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>2.178</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1.4</v>
+        <v>-4.023</v>
       </c>
       <c r="E159" t="n">
-        <v>23.8</v>
+        <v>22.2</v>
       </c>
       <c r="F159" t="n">
-        <v>0.433</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>0.908</v>
+        <v>-1.397</v>
       </c>
     </row>
     <row r="160">
@@ -5061,20 +5061,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.256</v>
+        <v>3.09</v>
       </c>
       <c r="E160" t="n">
-        <v>25.3</v>
+        <v>34.2</v>
       </c>
       <c r="F160" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G160" t="n">
-        <v>0.364</v>
+        <v>2.536</v>
       </c>
     </row>
     <row r="161">
@@ -5090,20 +5090,20 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-0.855</v>
+        <v>3.144</v>
       </c>
       <c r="E161" t="n">
-        <v>28.3</v>
+        <v>31.6</v>
       </c>
       <c r="F161" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G161" t="n">
-        <v>-0.248</v>
+        <v>2.377</v>
       </c>
     </row>
     <row r="162">
@@ -5119,20 +5119,20 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>-1.305</v>
+        <v>2.975</v>
       </c>
       <c r="E162" t="n">
-        <v>25.1</v>
+        <v>30.3</v>
       </c>
       <c r="F162" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G162" t="n">
-        <v>-0.456</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="163">
@@ -5148,136 +5148,136 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Orlando Robinson</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>-2.268</v>
+        <v>1.497</v>
       </c>
       <c r="E163" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="F163" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G163" t="n">
-        <v>-0.848</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>8.781000000000001</v>
+        <v>0.118</v>
       </c>
       <c r="E164" t="n">
-        <v>36.2</v>
+        <v>24.6</v>
       </c>
       <c r="F164" t="n">
         <v>0.467</v>
       </c>
       <c r="G164" t="n">
-        <v>6.974</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2.104</v>
+        <v>-0.796</v>
       </c>
       <c r="E165" t="n">
-        <v>32</v>
+        <v>28.1</v>
       </c>
       <c r="F165" t="n">
         <v>0.467</v>
       </c>
       <c r="G165" t="n">
-        <v>1.712</v>
+        <v>-0.193</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.886</v>
+        <v>-1.4</v>
       </c>
       <c r="E166" t="n">
-        <v>34.8</v>
+        <v>24.9</v>
       </c>
       <c r="F166" t="n">
         <v>0.467</v>
       </c>
       <c r="G166" t="n">
-        <v>0.98</v>
+        <v>-0.484</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Andre Drummond</t>
+          <t>Orlando Robinson</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-0.143</v>
+        <v>-2.27</v>
       </c>
       <c r="E167" t="n">
-        <v>19.6</v>
+        <v>22.2</v>
       </c>
       <c r="F167" t="n">
         <v>0.467</v>
       </c>
       <c r="G167" t="n">
-        <v>0.132</v>
+        <v>-0.833</v>
       </c>
     </row>
     <row r="168">
@@ -5293,20 +5293,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>-0.526</v>
+        <v>8.557</v>
       </c>
       <c r="E168" t="n">
-        <v>27.8</v>
+        <v>36.7</v>
       </c>
       <c r="F168" t="n">
-        <v>0.467</v>
+        <v>0.433</v>
       </c>
       <c r="G168" t="n">
-        <v>-0.034</v>
+        <v>6.874</v>
       </c>
     </row>
     <row r="169">
@@ -5322,20 +5322,20 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Eric Gordon</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-0.763</v>
+        <v>1.901</v>
       </c>
       <c r="E169" t="n">
-        <v>23</v>
+        <v>31.8</v>
       </c>
       <c r="F169" t="n">
-        <v>0.467</v>
+        <v>0.433</v>
       </c>
       <c r="G169" t="n">
-        <v>-0.142</v>
+        <v>1.546</v>
       </c>
     </row>
     <row r="170">
@@ -5351,20 +5351,20 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-1.302</v>
+        <v>0.663</v>
       </c>
       <c r="E170" t="n">
-        <v>21.4</v>
+        <v>36</v>
       </c>
       <c r="F170" t="n">
-        <v>0.467</v>
+        <v>0.433</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.373</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="171">
@@ -5380,136 +5380,136 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Andre Drummond</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>-1.44</v>
+        <v>0.05</v>
       </c>
       <c r="E171" t="n">
-        <v>28.6</v>
+        <v>19.8</v>
       </c>
       <c r="F171" t="n">
-        <v>0.467</v>
+        <v>0.433</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.579</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4.825</v>
+        <v>-0.642</v>
       </c>
       <c r="E172" t="n">
-        <v>34.3</v>
+        <v>26</v>
       </c>
       <c r="F172" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="G172" t="n">
-        <v>3.807</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Eric Gordon</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3.718</v>
+        <v>-0.765</v>
       </c>
       <c r="E173" t="n">
-        <v>26.5</v>
+        <v>23</v>
       </c>
       <c r="F173" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="G173" t="n">
-        <v>2.329</v>
+        <v>-0.159</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2.516</v>
+        <v>-1.514</v>
       </c>
       <c r="E174" t="n">
-        <v>26.4</v>
+        <v>19.9</v>
       </c>
       <c r="F174" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="G174" t="n">
-        <v>1.656</v>
+        <v>-0.448</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1.084</v>
+        <v>-1.633</v>
       </c>
       <c r="E175" t="n">
-        <v>24.2</v>
+        <v>29.2</v>
       </c>
       <c r="F175" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="G175" t="n">
-        <v>0.798</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="176">
@@ -5525,20 +5525,20 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.44</v>
+        <v>4.826</v>
       </c>
       <c r="E176" t="n">
-        <v>24.4</v>
+        <v>34.9</v>
       </c>
       <c r="F176" t="n">
         <v>0.5</v>
       </c>
       <c r="G176" t="n">
-        <v>0.477</v>
+        <v>3.871</v>
       </c>
     </row>
     <row r="177">
@@ -5554,20 +5554,20 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>-0.23</v>
+        <v>3.645</v>
       </c>
       <c r="E177" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="F177" t="n">
         <v>0.5</v>
       </c>
       <c r="G177" t="n">
-        <v>0.146</v>
+        <v>2.257</v>
       </c>
     </row>
     <row r="178">
@@ -5583,20 +5583,20 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Mark Williams</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>-1.688</v>
+        <v>2.942</v>
       </c>
       <c r="E178" t="n">
-        <v>29</v>
+        <v>22.3</v>
       </c>
       <c r="F178" t="n">
         <v>0.5</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.717</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="179">
@@ -5612,136 +5612,136 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>-2.077</v>
+        <v>1.439</v>
       </c>
       <c r="E179" t="n">
-        <v>28.8</v>
+        <v>25.3</v>
       </c>
       <c r="F179" t="n">
         <v>0.5</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.947</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5.917</v>
+        <v>0.334</v>
       </c>
       <c r="E180" t="n">
-        <v>33.3</v>
+        <v>23.9</v>
       </c>
       <c r="F180" t="n">
-        <v>0.367</v>
+        <v>0.5</v>
       </c>
       <c r="G180" t="n">
-        <v>4.366</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2.985</v>
+        <v>-0.205</v>
       </c>
       <c r="E181" t="n">
-        <v>30.6</v>
+        <v>25.4</v>
       </c>
       <c r="F181" t="n">
-        <v>0.367</v>
+        <v>0.5</v>
       </c>
       <c r="G181" t="n">
-        <v>2.134</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>3.348</v>
+        <v>-0.649</v>
       </c>
       <c r="E182" t="n">
-        <v>26.4</v>
+        <v>29.3</v>
       </c>
       <c r="F182" t="n">
-        <v>0.367</v>
+        <v>0.5</v>
       </c>
       <c r="G182" t="n">
-        <v>2.045</v>
+        <v>-0.091</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.126</v>
+        <v>-2.244</v>
       </c>
       <c r="E183" t="n">
-        <v>31.7</v>
+        <v>29.2</v>
       </c>
       <c r="F183" t="n">
-        <v>0.367</v>
+        <v>0.5</v>
       </c>
       <c r="G183" t="n">
-        <v>0.325</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="184">
@@ -5757,20 +5757,20 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>-1.07</v>
+        <v>6.287</v>
       </c>
       <c r="E184" t="n">
-        <v>32.6</v>
+        <v>33.7</v>
       </c>
       <c r="F184" t="n">
         <v>0.367</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.478</v>
+        <v>4.677</v>
       </c>
     </row>
     <row r="185">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>-1.318</v>
+        <v>2.716</v>
       </c>
       <c r="E185" t="n">
-        <v>28.8</v>
+        <v>32</v>
       </c>
       <c r="F185" t="n">
         <v>0.367</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.571</v>
+        <v>2.058</v>
       </c>
     </row>
     <row r="186">
@@ -5815,20 +5815,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>-1.812</v>
+        <v>3.155</v>
       </c>
       <c r="E186" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="F186" t="n">
         <v>0.367</v>
       </c>
       <c r="G186" t="n">
-        <v>-0.798</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="187">
@@ -5844,136 +5844,136 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>-3.122</v>
+        <v>2.993</v>
       </c>
       <c r="E187" t="n">
-        <v>21.4</v>
+        <v>20.2</v>
       </c>
       <c r="F187" t="n">
         <v>0.367</v>
       </c>
       <c r="G187" t="n">
-        <v>-1.227</v>
+        <v>1.414</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Dylan Cardwell</t>
+          <t>Jerami Grant</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.671</v>
+        <v>0.047</v>
       </c>
       <c r="E188" t="n">
-        <v>19.8</v>
+        <v>29.6</v>
       </c>
       <c r="F188" t="n">
-        <v>0.1</v>
+        <v>0.367</v>
       </c>
       <c r="G188" t="n">
-        <v>0.318</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>-0.077</v>
+        <v>-1.176</v>
       </c>
       <c r="E189" t="n">
-        <v>29.4</v>
+        <v>33</v>
       </c>
       <c r="F189" t="n">
-        <v>0.1</v>
+        <v>0.367</v>
       </c>
       <c r="G189" t="n">
-        <v>0.014</v>
+        <v>-0.556</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>-0.899</v>
+        <v>-1.451</v>
       </c>
       <c r="E190" t="n">
-        <v>24.3</v>
+        <v>27.5</v>
       </c>
       <c r="F190" t="n">
-        <v>0.1</v>
+        <v>0.367</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.404</v>
+        <v>-0.621</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>-1.021</v>
+        <v>-1.522</v>
       </c>
       <c r="E191" t="n">
-        <v>31.9</v>
+        <v>26.5</v>
       </c>
       <c r="F191" t="n">
-        <v>0.1</v>
+        <v>0.367</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.611</v>
+        <v>-0.639</v>
       </c>
     </row>
     <row r="192">
@@ -5989,20 +5989,20 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Doug McDermott</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-3.024</v>
+        <v>0.657</v>
       </c>
       <c r="E192" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="F19